--- a/data/Quiniela.xlsx
+++ b/data/Quiniela.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cindy\Desktop\QuinielaMundial\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A71E58F9-9220-42D0-8A71-CF91CB60962C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE8FEF95-A8B8-4D47-952E-A8E35ECBB587}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{9503E40F-C0E1-49CE-B4EA-3C401754995E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9503E40F-C0E1-49CE-B4EA-3C401754995E}"/>
   </bookViews>
   <sheets>
     <sheet name="Resultados" sheetId="1" r:id="rId1"/>
@@ -1239,6 +1239,24 @@
     <xf numFmtId="0" fontId="5" fillId="23" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="20" fillId="20" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="20" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="20" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="20" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="20" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="20" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1407,72 +1425,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="20" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="20" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="20" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="20" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="20" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="20" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1566,6 +1518,54 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1924,26 +1924,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="63" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="65"/>
+      <c r="A1" s="69" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="71"/>
     </row>
     <row r="2" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="66"/>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="68"/>
+      <c r="A2" s="72"/>
+      <c r="B2" s="73"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="74"/>
     </row>
     <row r="3" spans="1:8" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -1970,7 +1970,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="90" t="s">
+      <c r="A4" s="96" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -1985,10 +1985,10 @@
       <c r="E4" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="11">
-        <v>2</v>
-      </c>
-      <c r="G4" s="11">
+      <c r="F4" s="62">
+        <v>2</v>
+      </c>
+      <c r="G4" s="62">
         <v>0</v>
       </c>
       <c r="H4" s="20" t="s">
@@ -1996,7 +1996,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="91"/>
+      <c r="A5" s="97"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -2009,10 +2009,10 @@
       <c r="E5" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="11">
-        <v>2</v>
-      </c>
-      <c r="G5" s="11">
+      <c r="F5" s="62">
+        <v>2</v>
+      </c>
+      <c r="G5" s="62">
         <v>1</v>
       </c>
       <c r="H5" s="20" t="s">
@@ -2020,7 +2020,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="91"/>
+      <c r="A6" s="97"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -2040,7 +2040,7 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="91"/>
+      <c r="A7" s="97"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -2060,7 +2060,7 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="91"/>
+      <c r="A8" s="97"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -2080,7 +2080,7 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="92"/>
+      <c r="A9" s="98"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -2134,7 +2134,7 @@
       </c>
     </row>
     <row r="12" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="93" t="s">
+      <c r="A12" s="99" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -2149,10 +2149,10 @@
       <c r="E12" s="60" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="11">
-        <v>1</v>
-      </c>
-      <c r="G12" s="11">
+      <c r="F12" s="62">
+        <v>1</v>
+      </c>
+      <c r="G12" s="62">
         <v>1</v>
       </c>
       <c r="H12" s="61" t="s">
@@ -2160,7 +2160,7 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="94"/>
+      <c r="A13" s="100"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -2173,10 +2173,10 @@
       <c r="E13" s="60" t="s">
         <v>18</v>
       </c>
-      <c r="F13" s="11">
-        <v>1</v>
-      </c>
-      <c r="G13" s="11">
+      <c r="F13" s="62">
+        <v>1</v>
+      </c>
+      <c r="G13" s="62">
         <v>1</v>
       </c>
       <c r="H13" s="61" t="s">
@@ -2184,7 +2184,7 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="94"/>
+      <c r="A14" s="100"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -2204,7 +2204,7 @@
       </c>
     </row>
     <row r="15" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="94"/>
+      <c r="A15" s="100"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -2224,7 +2224,7 @@
       </c>
     </row>
     <row r="16" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="94"/>
+      <c r="A16" s="100"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -2244,7 +2244,7 @@
       </c>
     </row>
     <row r="17" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="95"/>
+      <c r="A17" s="101"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -2298,7 +2298,7 @@
       </c>
     </row>
     <row r="20" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="96" t="s">
+      <c r="A20" s="102" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -2313,10 +2313,10 @@
       <c r="E20" s="60" t="s">
         <v>21</v>
       </c>
-      <c r="F20" s="11">
-        <v>1</v>
-      </c>
-      <c r="G20" s="11">
+      <c r="F20" s="62">
+        <v>1</v>
+      </c>
+      <c r="G20" s="62">
         <v>1</v>
       </c>
       <c r="H20" s="61" t="s">
@@ -2324,7 +2324,7 @@
       </c>
     </row>
     <row r="21" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="97"/>
+      <c r="A21" s="103"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -2337,10 +2337,10 @@
       <c r="E21" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="F21" s="26">
-        <v>0</v>
-      </c>
-      <c r="G21" s="26">
+      <c r="F21" s="62">
+        <v>0</v>
+      </c>
+      <c r="G21" s="62">
         <v>1</v>
       </c>
       <c r="H21" s="27" t="s">
@@ -2348,7 +2348,7 @@
       </c>
     </row>
     <row r="22" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="97"/>
+      <c r="A22" s="103"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -2368,7 +2368,7 @@
       </c>
     </row>
     <row r="23" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="97"/>
+      <c r="A23" s="103"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -2388,7 +2388,7 @@
       </c>
     </row>
     <row r="24" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="97"/>
+      <c r="A24" s="103"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -2408,7 +2408,7 @@
       </c>
     </row>
     <row r="25" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="98"/>
+      <c r="A25" s="104"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -2462,7 +2462,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="99" t="s">
+      <c r="A28" s="105" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -2477,10 +2477,10 @@
       <c r="E28" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="F28" s="11">
+      <c r="F28" s="62">
         <v>4</v>
       </c>
-      <c r="G28" s="11">
+      <c r="G28" s="62">
         <v>1</v>
       </c>
       <c r="H28" s="21" t="s">
@@ -2488,7 +2488,7 @@
       </c>
     </row>
     <row r="29" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="100"/>
+      <c r="A29" s="106"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -2512,7 +2512,7 @@
       </c>
     </row>
     <row r="30" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="100"/>
+      <c r="A30" s="106"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -2532,7 +2532,7 @@
       </c>
     </row>
     <row r="31" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="100"/>
+      <c r="A31" s="106"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -2552,7 +2552,7 @@
       </c>
     </row>
     <row r="32" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="100"/>
+      <c r="A32" s="106"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -2572,7 +2572,7 @@
       </c>
     </row>
     <row r="33" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="101"/>
+      <c r="A33" s="107"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -2626,7 +2626,7 @@
       </c>
     </row>
     <row r="36" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="102" t="s">
+      <c r="A36" s="108" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -2652,7 +2652,7 @@
       </c>
     </row>
     <row r="37" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="103"/>
+      <c r="A37" s="109"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -2665,10 +2665,10 @@
       <c r="E37" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F37" s="26">
-        <v>1</v>
-      </c>
-      <c r="G37" s="26">
+      <c r="F37" s="62">
+        <v>1</v>
+      </c>
+      <c r="G37" s="62">
         <v>0</v>
       </c>
       <c r="H37" s="21" t="s">
@@ -2676,7 +2676,7 @@
       </c>
     </row>
     <row r="38" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="103"/>
+      <c r="A38" s="109"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -2696,7 +2696,7 @@
       </c>
     </row>
     <row r="39" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="103"/>
+      <c r="A39" s="109"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -2716,7 +2716,7 @@
       </c>
     </row>
     <row r="40" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="103"/>
+      <c r="A40" s="109"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -2736,7 +2736,7 @@
       </c>
     </row>
     <row r="41" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="104"/>
+      <c r="A41" s="110"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -2790,7 +2790,7 @@
       </c>
     </row>
     <row r="44" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="72" t="s">
+      <c r="A44" s="78" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -2816,7 +2816,7 @@
       </c>
     </row>
     <row r="45" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="73"/>
+      <c r="A45" s="79"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -2826,13 +2826,13 @@
       <c r="D45" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="E45" s="10" t="s">
+      <c r="E45" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="F45" s="26">
+      <c r="F45" s="62">
         <v>5</v>
       </c>
-      <c r="G45" s="26">
+      <c r="G45" s="62">
         <v>1</v>
       </c>
       <c r="H45" s="21" t="s">
@@ -2840,7 +2840,7 @@
       </c>
     </row>
     <row r="46" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="73"/>
+      <c r="A46" s="79"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -2860,7 +2860,7 @@
       </c>
     </row>
     <row r="47" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="73"/>
+      <c r="A47" s="79"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -2880,7 +2880,7 @@
       </c>
     </row>
     <row r="48" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="73"/>
+      <c r="A48" s="79"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -2900,7 +2900,7 @@
       </c>
     </row>
     <row r="49" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="74"/>
+      <c r="A49" s="80"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -2954,7 +2954,7 @@
       </c>
     </row>
     <row r="52" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="75" t="s">
+      <c r="A52" s="81" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -2966,17 +2966,21 @@
       <c r="D52" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="E52" s="10" t="s">
+      <c r="E52" s="61" t="s">
         <v>41</v>
       </c>
-      <c r="F52" s="26"/>
-      <c r="G52" s="26"/>
-      <c r="H52" s="21" t="s">
+      <c r="F52" s="62">
+        <v>1</v>
+      </c>
+      <c r="G52" s="62">
+        <v>1</v>
+      </c>
+      <c r="H52" s="61" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="76"/>
+      <c r="A53" s="82"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -2996,7 +3000,7 @@
       </c>
     </row>
     <row r="54" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="76"/>
+      <c r="A54" s="82"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -3016,7 +3020,7 @@
       </c>
     </row>
     <row r="55" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="76"/>
+      <c r="A55" s="82"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -3036,7 +3040,7 @@
       </c>
     </row>
     <row r="56" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="76"/>
+      <c r="A56" s="82"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -3056,7 +3060,7 @@
       </c>
     </row>
     <row r="57" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="77"/>
+      <c r="A57" s="83"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -3110,7 +3114,7 @@
       </c>
     </row>
     <row r="60" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="78" t="s">
+      <c r="A60" s="84" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -3122,17 +3126,21 @@
       <c r="D60" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="E60" s="10" t="s">
+      <c r="E60" s="61" t="s">
         <v>46</v>
       </c>
-      <c r="F60" s="26"/>
-      <c r="G60" s="26"/>
-      <c r="H60" s="21" t="s">
+      <c r="F60" s="62">
+        <v>0</v>
+      </c>
+      <c r="G60" s="62">
+        <v>0</v>
+      </c>
+      <c r="H60" s="61" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="79"/>
+      <c r="A61" s="85"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -3142,17 +3150,21 @@
       <c r="D61" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="E61" s="10" t="s">
+      <c r="E61" s="61" t="s">
         <v>48</v>
       </c>
-      <c r="F61" s="26"/>
-      <c r="G61" s="26"/>
-      <c r="H61" s="21" t="s">
+      <c r="F61" s="62">
+        <v>1</v>
+      </c>
+      <c r="G61" s="62">
+        <v>1</v>
+      </c>
+      <c r="H61" s="61" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="79"/>
+      <c r="A62" s="85"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -3172,7 +3184,7 @@
       </c>
     </row>
     <row r="63" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="79"/>
+      <c r="A63" s="85"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -3192,7 +3204,7 @@
       </c>
     </row>
     <row r="64" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="79"/>
+      <c r="A64" s="85"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -3212,7 +3224,7 @@
       </c>
     </row>
     <row r="65" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="80"/>
+      <c r="A65" s="86"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -3266,7 +3278,7 @@
       </c>
     </row>
     <row r="68" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="81" t="s">
+      <c r="A68" s="87" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -3288,7 +3300,7 @@
       </c>
     </row>
     <row r="69" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="82"/>
+      <c r="A69" s="88"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -3308,7 +3320,7 @@
       </c>
     </row>
     <row r="70" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="82"/>
+      <c r="A70" s="88"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -3328,7 +3340,7 @@
       </c>
     </row>
     <row r="71" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="82"/>
+      <c r="A71" s="88"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -3348,7 +3360,7 @@
       </c>
     </row>
     <row r="72" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="82"/>
+      <c r="A72" s="88"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -3368,7 +3380,7 @@
       </c>
     </row>
     <row r="73" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="83"/>
+      <c r="A73" s="89"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -3422,7 +3434,7 @@
       </c>
     </row>
     <row r="76" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="84" t="s">
+      <c r="A76" s="90" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -3444,7 +3456,7 @@
       </c>
     </row>
     <row r="77" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="85"/>
+      <c r="A77" s="91"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -3464,7 +3476,7 @@
       </c>
     </row>
     <row r="78" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="85"/>
+      <c r="A78" s="91"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -3484,7 +3496,7 @@
       </c>
     </row>
     <row r="79" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="85"/>
+      <c r="A79" s="91"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -3504,7 +3516,7 @@
       </c>
     </row>
     <row r="80" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="85"/>
+      <c r="A80" s="91"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -3524,7 +3536,7 @@
       </c>
     </row>
     <row r="81" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="86"/>
+      <c r="A81" s="92"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -3578,7 +3590,7 @@
       </c>
     </row>
     <row r="84" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="87" t="s">
+      <c r="A84" s="93" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -3600,7 +3612,7 @@
       </c>
     </row>
     <row r="85" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="88"/>
+      <c r="A85" s="94"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -3620,7 +3632,7 @@
       </c>
     </row>
     <row r="86" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="88"/>
+      <c r="A86" s="94"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -3640,7 +3652,7 @@
       </c>
     </row>
     <row r="87" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="88"/>
+      <c r="A87" s="94"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -3660,7 +3672,7 @@
       </c>
     </row>
     <row r="88" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="88"/>
+      <c r="A88" s="94"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -3680,7 +3692,7 @@
       </c>
     </row>
     <row r="89" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="89"/>
+      <c r="A89" s="95"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -3734,7 +3746,7 @@
       </c>
     </row>
     <row r="92" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="69" t="s">
+      <c r="A92" s="75" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -3756,7 +3768,7 @@
       </c>
     </row>
     <row r="93" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="70"/>
+      <c r="A93" s="76"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -3776,7 +3788,7 @@
       </c>
     </row>
     <row r="94" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="70"/>
+      <c r="A94" s="76"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -3796,7 +3808,7 @@
       </c>
     </row>
     <row r="95" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="70"/>
+      <c r="A95" s="76"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -3816,7 +3828,7 @@
       </c>
     </row>
     <row r="96" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="70"/>
+      <c r="A96" s="76"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -3836,7 +3848,7 @@
       </c>
     </row>
     <row r="97" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="71"/>
+      <c r="A97" s="77"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -3896,26 +3908,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="63" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="65"/>
+      <c r="A1" s="69" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="71"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="66"/>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="68"/>
+      <c r="A2" s="72"/>
+      <c r="B2" s="73"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="74"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -3948,7 +3960,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="90" t="s">
+      <c r="A4" s="96" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -3978,7 +3990,7 @@
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="91"/>
+      <c r="A5" s="97"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -4002,7 +4014,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="91"/>
+      <c r="A6" s="97"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -4030,7 +4042,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="91"/>
+      <c r="A7" s="97"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -4058,7 +4070,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="91"/>
+      <c r="A8" s="97"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -4086,7 +4098,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="92"/>
+      <c r="A9" s="98"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -4148,7 +4160,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="93" t="s">
+      <c r="A12" s="99" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -4174,7 +4186,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="94"/>
+      <c r="A13" s="100"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -4198,7 +4210,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="94"/>
+      <c r="A14" s="100"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -4226,7 +4238,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="94"/>
+      <c r="A15" s="100"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -4254,7 +4266,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="94"/>
+      <c r="A16" s="100"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -4282,7 +4294,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="95"/>
+      <c r="A17" s="101"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -4344,7 +4356,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="96" t="s">
+      <c r="A20" s="102" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -4370,7 +4382,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="97"/>
+      <c r="A21" s="103"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -4398,7 +4410,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="97"/>
+      <c r="A22" s="103"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -4426,7 +4438,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="97"/>
+      <c r="A23" s="103"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -4454,7 +4466,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="97"/>
+      <c r="A24" s="103"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -4482,7 +4494,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="98"/>
+      <c r="A25" s="104"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -4544,7 +4556,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="99" t="s">
+      <c r="A28" s="105" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -4570,7 +4582,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="100"/>
+      <c r="A29" s="106"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -4598,7 +4610,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="100"/>
+      <c r="A30" s="106"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -4626,7 +4638,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="100"/>
+      <c r="A31" s="106"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -4654,7 +4666,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="100"/>
+      <c r="A32" s="106"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -4682,7 +4694,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="101"/>
+      <c r="A33" s="107"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -4744,7 +4756,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="102" t="s">
+      <c r="A36" s="108" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -4774,7 +4786,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="103"/>
+      <c r="A37" s="109"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -4802,7 +4814,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="103"/>
+      <c r="A38" s="109"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -4830,7 +4842,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="103"/>
+      <c r="A39" s="109"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -4858,7 +4870,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="103"/>
+      <c r="A40" s="109"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -4886,7 +4898,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="104"/>
+      <c r="A41" s="110"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -4948,7 +4960,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="72" t="s">
+      <c r="A44" s="78" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -4978,7 +4990,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="73"/>
+      <c r="A45" s="79"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -5006,7 +5018,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="73"/>
+      <c r="A46" s="79"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -5034,7 +5046,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="73"/>
+      <c r="A47" s="79"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -5062,7 +5074,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="73"/>
+      <c r="A48" s="79"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -5090,7 +5102,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="74"/>
+      <c r="A49" s="80"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -5152,7 +5164,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="75" t="s">
+      <c r="A52" s="81" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -5176,13 +5188,13 @@
       <c r="H52" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="J52" s="1" t="str">
+      <c r="J52" s="1">
         <f>IF(OR(Resultados!F52="",Resultados!G52=""),"",IF(AND(F52=Resultados!F52,G52=Resultados!G52),2,IF(((F52&gt;G52)=(Resultados!F52&gt;Resultados!G52))*((F52&lt;G52)=(Resultados!F52&lt;Resultados!G52)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="76"/>
+      <c r="A53" s="82"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -5210,7 +5222,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="76"/>
+      <c r="A54" s="82"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -5238,7 +5250,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="76"/>
+      <c r="A55" s="82"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -5266,7 +5278,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="76"/>
+      <c r="A56" s="82"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -5294,7 +5306,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="77"/>
+      <c r="A57" s="83"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -5356,7 +5368,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="78" t="s">
+      <c r="A60" s="84" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -5380,13 +5392,13 @@
       <c r="H60" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="J60" s="1" t="str">
+      <c r="J60" s="1">
         <f>IF(OR(Resultados!F60="",Resultados!G60=""),"",IF(AND(F60=Resultados!F60,G60=Resultados!G60),2,IF(((F60&gt;G60)=(Resultados!F60&gt;Resultados!G60))*((F60&lt;G60)=(Resultados!F60&lt;Resultados!G60)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="79"/>
+      <c r="A61" s="85"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -5408,13 +5420,13 @@
       <c r="H61" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="J61" s="1" t="str">
+      <c r="J61" s="1">
         <f>IF(OR(Resultados!F61="",Resultados!G61=""),"",IF(AND(F61=Resultados!F61,G61=Resultados!G61),2,IF(((F61&gt;G61)=(Resultados!F61&gt;Resultados!G61))*((F61&lt;G61)=(Resultados!F61&lt;Resultados!G61)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="79"/>
+      <c r="A62" s="85"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -5442,7 +5454,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="79"/>
+      <c r="A63" s="85"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -5470,7 +5482,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="79"/>
+      <c r="A64" s="85"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -5498,7 +5510,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="80"/>
+      <c r="A65" s="86"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -5560,7 +5572,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="81" t="s">
+      <c r="A68" s="87" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -5590,7 +5602,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="82"/>
+      <c r="A69" s="88"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -5618,7 +5630,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="82"/>
+      <c r="A70" s="88"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -5646,7 +5658,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="82"/>
+      <c r="A71" s="88"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -5674,7 +5686,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="82"/>
+      <c r="A72" s="88"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -5702,7 +5714,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="83"/>
+      <c r="A73" s="89"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -5764,7 +5776,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="84" t="s">
+      <c r="A76" s="90" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -5794,7 +5806,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="85"/>
+      <c r="A77" s="91"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -5822,7 +5834,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="85"/>
+      <c r="A78" s="91"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -5850,7 +5862,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="85"/>
+      <c r="A79" s="91"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -5878,7 +5890,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="85"/>
+      <c r="A80" s="91"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -5906,7 +5918,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="86"/>
+      <c r="A81" s="92"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -5968,7 +5980,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="87" t="s">
+      <c r="A84" s="93" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -5998,7 +6010,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="88"/>
+      <c r="A85" s="94"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -6026,7 +6038,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="88"/>
+      <c r="A86" s="94"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -6054,7 +6066,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="88"/>
+      <c r="A87" s="94"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -6082,7 +6094,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="88"/>
+      <c r="A88" s="94"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -6110,7 +6122,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="89"/>
+      <c r="A89" s="95"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -6172,7 +6184,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="69" t="s">
+      <c r="A92" s="75" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -6202,7 +6214,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="70"/>
+      <c r="A93" s="76"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -6230,7 +6242,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="70"/>
+      <c r="A94" s="76"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -6258,7 +6270,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="70"/>
+      <c r="A95" s="76"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -6286,7 +6298,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="70"/>
+      <c r="A96" s="76"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -6314,7 +6326,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="71"/>
+      <c r="A97" s="77"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -6343,6 +6355,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A28:A33"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:A9"/>
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="A20:A25"/>
     <mergeCell ref="A84:A89"/>
     <mergeCell ref="A92:A97"/>
     <mergeCell ref="A36:A41"/>
@@ -6351,12 +6369,6 @@
     <mergeCell ref="A60:A65"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="A76:A81"/>
-    <mergeCell ref="A28:A33"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A4:A9"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="A20:A25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -6384,26 +6396,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="63" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="65"/>
+      <c r="A1" s="69" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="71"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="66"/>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="68"/>
+      <c r="A2" s="72"/>
+      <c r="B2" s="73"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="74"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -6436,7 +6448,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="90" t="s">
+      <c r="A4" s="96" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -6462,11 +6474,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="91"/>
+      <c r="A5" s="97"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -6490,7 +6502,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="91"/>
+      <c r="A6" s="97"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -6518,7 +6530,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="91"/>
+      <c r="A7" s="97"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -6546,7 +6558,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="91"/>
+      <c r="A8" s="97"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -6574,7 +6586,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="92"/>
+      <c r="A9" s="98"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -6636,7 +6648,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="93" t="s">
+      <c r="A12" s="99" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -6662,7 +6674,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="94"/>
+      <c r="A13" s="100"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -6686,7 +6698,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="94"/>
+      <c r="A14" s="100"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -6714,7 +6726,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="94"/>
+      <c r="A15" s="100"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -6742,7 +6754,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="94"/>
+      <c r="A16" s="100"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -6770,7 +6782,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="95"/>
+      <c r="A17" s="101"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -6832,7 +6844,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="96" t="s">
+      <c r="A20" s="102" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -6858,7 +6870,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="97"/>
+      <c r="A21" s="103"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -6886,7 +6898,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="97"/>
+      <c r="A22" s="103"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -6914,7 +6926,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="97"/>
+      <c r="A23" s="103"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -6942,7 +6954,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="97"/>
+      <c r="A24" s="103"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -6970,7 +6982,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="98"/>
+      <c r="A25" s="104"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -7032,7 +7044,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="99" t="s">
+      <c r="A28" s="105" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -7058,7 +7070,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="100"/>
+      <c r="A29" s="106"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -7086,7 +7098,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="100"/>
+      <c r="A30" s="106"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -7114,7 +7126,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="100"/>
+      <c r="A31" s="106"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -7142,7 +7154,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="100"/>
+      <c r="A32" s="106"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -7170,7 +7182,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="101"/>
+      <c r="A33" s="107"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -7232,7 +7244,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="102" t="s">
+      <c r="A36" s="108" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -7262,7 +7274,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="103"/>
+      <c r="A37" s="109"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -7290,7 +7302,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="103"/>
+      <c r="A38" s="109"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -7318,7 +7330,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="103"/>
+      <c r="A39" s="109"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -7346,7 +7358,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="103"/>
+      <c r="A40" s="109"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -7374,7 +7386,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="104"/>
+      <c r="A41" s="110"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -7436,7 +7448,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="72" t="s">
+      <c r="A44" s="78" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -7466,7 +7478,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="73"/>
+      <c r="A45" s="79"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -7494,7 +7506,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="73"/>
+      <c r="A46" s="79"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -7522,7 +7534,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="73"/>
+      <c r="A47" s="79"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -7550,7 +7562,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="73"/>
+      <c r="A48" s="79"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -7578,7 +7590,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="74"/>
+      <c r="A49" s="80"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -7640,7 +7652,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="75" t="s">
+      <c r="A52" s="81" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -7664,13 +7676,13 @@
       <c r="H52" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="J52" s="1" t="str">
+      <c r="J52" s="1">
         <f>IF(OR(Resultados!F52="",Resultados!G52=""),"",IF(AND(F52=Resultados!F52,G52=Resultados!G52),2,IF(((F52&gt;G52)=(Resultados!F52&gt;Resultados!G52))*((F52&lt;G52)=(Resultados!F52&lt;Resultados!G52)),1,0)))</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="76"/>
+      <c r="A53" s="82"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -7698,7 +7710,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="76"/>
+      <c r="A54" s="82"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -7726,7 +7738,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="76"/>
+      <c r="A55" s="82"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -7754,7 +7766,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="76"/>
+      <c r="A56" s="82"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -7782,7 +7794,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="77"/>
+      <c r="A57" s="83"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -7844,7 +7856,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="78" t="s">
+      <c r="A60" s="84" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -7868,13 +7880,13 @@
       <c r="H60" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="J60" s="1" t="str">
+      <c r="J60" s="1">
         <f>IF(OR(Resultados!F60="",Resultados!G60=""),"",IF(AND(F60=Resultados!F60,G60=Resultados!G60),2,IF(((F60&gt;G60)=(Resultados!F60&gt;Resultados!G60))*((F60&lt;G60)=(Resultados!F60&lt;Resultados!G60)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="79"/>
+      <c r="A61" s="85"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -7896,13 +7908,13 @@
       <c r="H61" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="J61" s="1" t="str">
+      <c r="J61" s="1">
         <f>IF(OR(Resultados!F61="",Resultados!G61=""),"",IF(AND(F61=Resultados!F61,G61=Resultados!G61),2,IF(((F61&gt;G61)=(Resultados!F61&gt;Resultados!G61))*((F61&lt;G61)=(Resultados!F61&lt;Resultados!G61)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="79"/>
+      <c r="A62" s="85"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -7930,7 +7942,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="79"/>
+      <c r="A63" s="85"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -7958,7 +7970,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="79"/>
+      <c r="A64" s="85"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -7986,7 +7998,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="80"/>
+      <c r="A65" s="86"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -8048,7 +8060,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="81" t="s">
+      <c r="A68" s="87" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -8078,7 +8090,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="82"/>
+      <c r="A69" s="88"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -8106,7 +8118,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="82"/>
+      <c r="A70" s="88"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -8134,7 +8146,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="82"/>
+      <c r="A71" s="88"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -8162,7 +8174,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="82"/>
+      <c r="A72" s="88"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -8190,7 +8202,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="83"/>
+      <c r="A73" s="89"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -8252,7 +8264,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="84" t="s">
+      <c r="A76" s="90" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -8282,7 +8294,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="85"/>
+      <c r="A77" s="91"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -8310,7 +8322,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="85"/>
+      <c r="A78" s="91"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -8338,7 +8350,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="85"/>
+      <c r="A79" s="91"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -8366,7 +8378,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="85"/>
+      <c r="A80" s="91"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -8394,7 +8406,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="86"/>
+      <c r="A81" s="92"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -8456,7 +8468,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="87" t="s">
+      <c r="A84" s="93" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -8486,7 +8498,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="88"/>
+      <c r="A85" s="94"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -8514,7 +8526,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="88"/>
+      <c r="A86" s="94"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -8542,7 +8554,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="88"/>
+      <c r="A87" s="94"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -8570,7 +8582,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="88"/>
+      <c r="A88" s="94"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -8598,7 +8610,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="89"/>
+      <c r="A89" s="95"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -8660,7 +8672,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="69" t="s">
+      <c r="A92" s="75" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -8690,7 +8702,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="70"/>
+      <c r="A93" s="76"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -8718,7 +8730,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="70"/>
+      <c r="A94" s="76"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -8746,7 +8758,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="70"/>
+      <c r="A95" s="76"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -8774,7 +8786,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="70"/>
+      <c r="A96" s="76"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -8802,7 +8814,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="71"/>
+      <c r="A97" s="77"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -8831,6 +8843,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A28:A33"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:A9"/>
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="A20:A25"/>
     <mergeCell ref="A84:A89"/>
     <mergeCell ref="A92:A97"/>
     <mergeCell ref="A36:A41"/>
@@ -8839,12 +8857,6 @@
     <mergeCell ref="A60:A65"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="A76:A81"/>
-    <mergeCell ref="A28:A33"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A4:A9"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="A20:A25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -8867,18 +8879,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D1" s="105" t="s">
+      <c r="D1" s="63" t="s">
         <v>74</v>
       </c>
-      <c r="E1" s="106"/>
-      <c r="F1" s="107"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="65"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D2" s="108" t="s">
+      <c r="D2" s="66" t="s">
         <v>75</v>
       </c>
-      <c r="E2" s="109"/>
-      <c r="F2" s="110"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="68"/>
     </row>
     <row r="4" spans="1:6" s="29" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="57" t="s">
@@ -8910,7 +8922,7 @@
       </c>
       <c r="E5" s="59" t="str" cm="1">
         <f t="array" ref="E5:F13">_xlfn._xlws.SORT(A5:B13,2,-1)</f>
-        <v>Lennon</v>
+        <v>Erik</v>
       </c>
       <c r="F5" s="59">
         <v>6</v>
@@ -8928,10 +8940,10 @@
         <v>2</v>
       </c>
       <c r="E6" s="55" t="str">
-        <v>Bere</v>
+        <v>Lennon</v>
       </c>
       <c r="F6" s="55">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -8946,10 +8958,10 @@
         <v>3</v>
       </c>
       <c r="E7" s="56" t="str">
-        <v>Wendy</v>
+        <v>Yulian</v>
       </c>
       <c r="F7" s="56">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -8964,10 +8976,10 @@
         <v>4</v>
       </c>
       <c r="E8" s="28" t="str">
-        <v>Jimmy</v>
+        <v>Bere</v>
       </c>
       <c r="F8" s="28">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -8976,13 +8988,13 @@
       </c>
       <c r="B9" s="58">
         <f>Erik!L4</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D9" s="28">
         <v>5</v>
       </c>
       <c r="E9" s="28" t="str">
-        <v>Erick</v>
+        <v>Wendy</v>
       </c>
       <c r="F9" s="28">
         <v>4</v>
@@ -9000,7 +9012,7 @@
         <v>6</v>
       </c>
       <c r="E10" s="28" t="str">
-        <v>Erik</v>
+        <v>Jimmy</v>
       </c>
       <c r="F10" s="28">
         <v>4</v>
@@ -9012,16 +9024,16 @@
       </c>
       <c r="B11" s="58">
         <f>Yulian!L4</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D11" s="28">
         <v>7</v>
       </c>
       <c r="E11" s="28" t="str">
-        <v>Cindy</v>
+        <v>Erick</v>
       </c>
       <c r="F11" s="28">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -9036,7 +9048,7 @@
         <v>8</v>
       </c>
       <c r="E12" s="28" t="str">
-        <v>Yulian</v>
+        <v>Cindy</v>
       </c>
       <c r="F12" s="28">
         <v>3</v>
@@ -9091,26 +9103,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="63" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="65"/>
+      <c r="A1" s="69" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="71"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="66"/>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="68"/>
+      <c r="A2" s="72"/>
+      <c r="B2" s="73"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="74"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="31"/>
@@ -9143,7 +9155,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="114" t="s">
+      <c r="A4" s="138" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="35">
@@ -9173,7 +9185,7 @@
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="115"/>
+      <c r="A5" s="139"/>
       <c r="B5" s="35">
         <v>46185</v>
       </c>
@@ -9197,7 +9209,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="115"/>
+      <c r="A6" s="139"/>
       <c r="B6" s="35">
         <v>46191</v>
       </c>
@@ -9225,7 +9237,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="115"/>
+      <c r="A7" s="139"/>
       <c r="B7" s="35">
         <v>46192</v>
       </c>
@@ -9253,7 +9265,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="115"/>
+      <c r="A8" s="139"/>
       <c r="B8" s="35">
         <v>46198</v>
       </c>
@@ -9281,7 +9293,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="116"/>
+      <c r="A9" s="140"/>
       <c r="B9" s="42">
         <v>46198</v>
       </c>
@@ -9343,7 +9355,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="117" t="s">
+      <c r="A12" s="141" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="35">
@@ -9369,7 +9381,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="118"/>
+      <c r="A13" s="142"/>
       <c r="B13" s="35">
         <v>46186</v>
       </c>
@@ -9393,7 +9405,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="118"/>
+      <c r="A14" s="142"/>
       <c r="B14" s="35">
         <v>46191</v>
       </c>
@@ -9421,7 +9433,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="118"/>
+      <c r="A15" s="142"/>
       <c r="B15" s="35">
         <v>46192</v>
       </c>
@@ -9449,7 +9461,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="118"/>
+      <c r="A16" s="142"/>
       <c r="B16" s="35">
         <v>46197</v>
       </c>
@@ -9477,7 +9489,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="119"/>
+      <c r="A17" s="143"/>
       <c r="B17" s="42">
         <v>46197</v>
       </c>
@@ -9539,7 +9551,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="120" t="s">
+      <c r="A20" s="144" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="35">
@@ -9565,7 +9577,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="121"/>
+      <c r="A21" s="145"/>
       <c r="B21" s="35">
         <v>46187</v>
       </c>
@@ -9593,7 +9605,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="121"/>
+      <c r="A22" s="145"/>
       <c r="B22" s="35">
         <v>46193</v>
       </c>
@@ -9621,7 +9633,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="121"/>
+      <c r="A23" s="145"/>
       <c r="B23" s="35">
         <v>46193</v>
       </c>
@@ -9649,7 +9661,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="121"/>
+      <c r="A24" s="145"/>
       <c r="B24" s="35">
         <v>46198</v>
       </c>
@@ -9677,7 +9689,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="122"/>
+      <c r="A25" s="146"/>
       <c r="B25" s="42">
         <v>46198</v>
       </c>
@@ -9739,7 +9751,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="111" t="s">
+      <c r="A28" s="135" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="35">
@@ -9765,7 +9777,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="112"/>
+      <c r="A29" s="136"/>
       <c r="B29" s="35">
         <v>46187</v>
       </c>
@@ -9793,7 +9805,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="112"/>
+      <c r="A30" s="136"/>
       <c r="B30" s="35">
         <v>46192</v>
       </c>
@@ -9821,7 +9833,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="112"/>
+      <c r="A31" s="136"/>
       <c r="B31" s="35">
         <v>46193</v>
       </c>
@@ -9849,7 +9861,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="112"/>
+      <c r="A32" s="136"/>
       <c r="B32" s="35">
         <v>46199</v>
       </c>
@@ -9877,7 +9889,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="113"/>
+      <c r="A33" s="137"/>
       <c r="B33" s="42">
         <v>46199</v>
       </c>
@@ -9939,7 +9951,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="129" t="s">
+      <c r="A36" s="117" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="35">
@@ -9969,7 +9981,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="130"/>
+      <c r="A37" s="118"/>
       <c r="B37" s="35">
         <v>46188</v>
       </c>
@@ -9997,7 +10009,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="130"/>
+      <c r="A38" s="118"/>
       <c r="B38" s="35">
         <v>46193</v>
       </c>
@@ -10025,7 +10037,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="130"/>
+      <c r="A39" s="118"/>
       <c r="B39" s="35">
         <v>46194</v>
       </c>
@@ -10053,7 +10065,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="130"/>
+      <c r="A40" s="118"/>
       <c r="B40" s="35">
         <v>46198</v>
       </c>
@@ -10081,7 +10093,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="131"/>
+      <c r="A41" s="119"/>
       <c r="B41" s="42">
         <v>46198</v>
       </c>
@@ -10143,7 +10155,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="132" t="s">
+      <c r="A44" s="120" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="35">
@@ -10173,7 +10185,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="133"/>
+      <c r="A45" s="121"/>
       <c r="B45" s="35">
         <v>46188</v>
       </c>
@@ -10201,7 +10213,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="133"/>
+      <c r="A46" s="121"/>
       <c r="B46" s="35">
         <v>46193</v>
       </c>
@@ -10229,7 +10241,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="133"/>
+      <c r="A47" s="121"/>
       <c r="B47" s="35">
         <v>46194</v>
       </c>
@@ -10257,7 +10269,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="133"/>
+      <c r="A48" s="121"/>
       <c r="B48" s="35">
         <v>46199</v>
       </c>
@@ -10285,7 +10297,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="134"/>
+      <c r="A49" s="122"/>
       <c r="B49" s="42">
         <v>46199</v>
       </c>
@@ -10347,7 +10359,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="135" t="s">
+      <c r="A52" s="123" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="35">
@@ -10371,13 +10383,13 @@
       <c r="H52" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="J52" s="1" t="str">
+      <c r="J52" s="1">
         <f>IF(OR(Resultados!F52="",Resultados!G52=""),"",IF(AND(F52=Resultados!F52,G52=Resultados!G52),2,IF(((F52&gt;G52)=(Resultados!F52&gt;Resultados!G52))*((F52&lt;G52)=(Resultados!F52&lt;Resultados!G52)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="136"/>
+      <c r="A53" s="124"/>
       <c r="B53" s="35">
         <v>46189</v>
       </c>
@@ -10405,7 +10417,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="136"/>
+      <c r="A54" s="124"/>
       <c r="B54" s="35">
         <v>46194</v>
       </c>
@@ -10433,7 +10445,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="136"/>
+      <c r="A55" s="124"/>
       <c r="B55" s="35">
         <v>46195</v>
       </c>
@@ -10461,7 +10473,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="136"/>
+      <c r="A56" s="124"/>
       <c r="B56" s="35">
         <v>46200</v>
       </c>
@@ -10489,7 +10501,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="137"/>
+      <c r="A57" s="125"/>
       <c r="B57" s="42">
         <v>46200</v>
       </c>
@@ -10551,7 +10563,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="138" t="s">
+      <c r="A60" s="126" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="35">
@@ -10575,13 +10587,13 @@
       <c r="H60" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="J60" s="1" t="str">
+      <c r="J60" s="1">
         <f>IF(OR(Resultados!F60="",Resultados!G60=""),"",IF(AND(F60=Resultados!F60,G60=Resultados!G60),2,IF(((F60&gt;G60)=(Resultados!F60&gt;Resultados!G60))*((F60&lt;G60)=(Resultados!F60&lt;Resultados!G60)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="139"/>
+      <c r="A61" s="127"/>
       <c r="B61" s="35">
         <v>46189</v>
       </c>
@@ -10603,13 +10615,13 @@
       <c r="H61" s="46" t="s">
         <v>49</v>
       </c>
-      <c r="J61" s="1" t="str">
+      <c r="J61" s="1">
         <f>IF(OR(Resultados!F61="",Resultados!G61=""),"",IF(AND(F61=Resultados!F61,G61=Resultados!G61),2,IF(((F61&gt;G61)=(Resultados!F61&gt;Resultados!G61))*((F61&lt;G61)=(Resultados!F61&lt;Resultados!G61)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="139"/>
+      <c r="A62" s="127"/>
       <c r="B62" s="35">
         <v>46194</v>
       </c>
@@ -10637,7 +10649,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="139"/>
+      <c r="A63" s="127"/>
       <c r="B63" s="35">
         <v>46195</v>
       </c>
@@ -10665,7 +10677,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="139"/>
+      <c r="A64" s="127"/>
       <c r="B64" s="35">
         <v>46200</v>
       </c>
@@ -10693,7 +10705,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="140"/>
+      <c r="A65" s="128"/>
       <c r="B65" s="42">
         <v>46200</v>
       </c>
@@ -10755,7 +10767,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="141" t="s">
+      <c r="A68" s="129" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="35">
@@ -10785,7 +10797,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="142"/>
+      <c r="A69" s="130"/>
       <c r="B69" s="35">
         <v>46190</v>
       </c>
@@ -10813,7 +10825,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="142"/>
+      <c r="A70" s="130"/>
       <c r="B70" s="35">
         <v>46195</v>
       </c>
@@ -10841,7 +10853,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="142"/>
+      <c r="A71" s="130"/>
       <c r="B71" s="35">
         <v>46196</v>
       </c>
@@ -10869,7 +10881,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="142"/>
+      <c r="A72" s="130"/>
       <c r="B72" s="35">
         <v>46199</v>
       </c>
@@ -10897,7 +10909,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="143"/>
+      <c r="A73" s="131"/>
       <c r="B73" s="42">
         <v>46199</v>
       </c>
@@ -10959,7 +10971,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="144" t="s">
+      <c r="A76" s="132" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="35">
@@ -10989,7 +11001,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="145"/>
+      <c r="A77" s="133"/>
       <c r="B77" s="35">
         <v>46190</v>
       </c>
@@ -11017,7 +11029,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="145"/>
+      <c r="A78" s="133"/>
       <c r="B78" s="35">
         <v>46195</v>
       </c>
@@ -11045,7 +11057,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="145"/>
+      <c r="A79" s="133"/>
       <c r="B79" s="35">
         <v>46196</v>
       </c>
@@ -11073,7 +11085,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="145"/>
+      <c r="A80" s="133"/>
       <c r="B80" s="35">
         <v>46201</v>
       </c>
@@ -11101,7 +11113,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="146"/>
+      <c r="A81" s="134"/>
       <c r="B81" s="42">
         <v>46201</v>
       </c>
@@ -11163,7 +11175,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="123" t="s">
+      <c r="A84" s="111" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="35">
@@ -11193,7 +11205,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="124"/>
+      <c r="A85" s="112"/>
       <c r="B85" s="35">
         <v>46191</v>
       </c>
@@ -11221,7 +11233,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="124"/>
+      <c r="A86" s="112"/>
       <c r="B86" s="35">
         <v>46196</v>
       </c>
@@ -11249,7 +11261,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="124"/>
+      <c r="A87" s="112"/>
       <c r="B87" s="35">
         <v>46197</v>
       </c>
@@ -11277,7 +11289,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="124"/>
+      <c r="A88" s="112"/>
       <c r="B88" s="35">
         <v>46201</v>
       </c>
@@ -11305,7 +11317,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="125"/>
+      <c r="A89" s="113"/>
       <c r="B89" s="42">
         <v>46201</v>
       </c>
@@ -11367,7 +11379,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="126" t="s">
+      <c r="A92" s="114" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="35">
@@ -11397,7 +11409,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="127"/>
+      <c r="A93" s="115"/>
       <c r="B93" s="35">
         <v>46191</v>
       </c>
@@ -11425,7 +11437,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="127"/>
+      <c r="A94" s="115"/>
       <c r="B94" s="35">
         <v>46196</v>
       </c>
@@ -11453,7 +11465,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="127"/>
+      <c r="A95" s="115"/>
       <c r="B95" s="35">
         <v>46197</v>
       </c>
@@ -11481,7 +11493,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="127"/>
+      <c r="A96" s="115"/>
       <c r="B96" s="35">
         <v>46200</v>
       </c>
@@ -11509,7 +11521,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="128"/>
+      <c r="A97" s="116"/>
       <c r="B97" s="42">
         <v>46200</v>
       </c>
@@ -11538,6 +11550,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A28:A33"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:A9"/>
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="A20:A25"/>
     <mergeCell ref="A84:A89"/>
     <mergeCell ref="A92:A97"/>
     <mergeCell ref="A36:A41"/>
@@ -11546,12 +11564,6 @@
     <mergeCell ref="A60:A65"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="A76:A81"/>
-    <mergeCell ref="A28:A33"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A4:A9"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="A20:A25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -11580,26 +11592,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="63" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="65"/>
+      <c r="A1" s="69" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="71"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="66"/>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="68"/>
+      <c r="A2" s="72"/>
+      <c r="B2" s="73"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="74"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="31"/>
@@ -11632,7 +11644,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="114" t="s">
+      <c r="A4" s="138" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="35">
@@ -11662,7 +11674,7 @@
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="115"/>
+      <c r="A5" s="139"/>
       <c r="B5" s="35">
         <v>46185</v>
       </c>
@@ -11686,7 +11698,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="115"/>
+      <c r="A6" s="139"/>
       <c r="B6" s="35">
         <v>46191</v>
       </c>
@@ -11714,7 +11726,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="115"/>
+      <c r="A7" s="139"/>
       <c r="B7" s="35">
         <v>46192</v>
       </c>
@@ -11742,7 +11754,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="115"/>
+      <c r="A8" s="139"/>
       <c r="B8" s="35">
         <v>46198</v>
       </c>
@@ -11770,7 +11782,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="116"/>
+      <c r="A9" s="140"/>
       <c r="B9" s="42">
         <v>46198</v>
       </c>
@@ -11832,7 +11844,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="117" t="s">
+      <c r="A12" s="141" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="35">
@@ -11858,7 +11870,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="118"/>
+      <c r="A13" s="142"/>
       <c r="B13" s="35">
         <v>46186</v>
       </c>
@@ -11882,7 +11894,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="118"/>
+      <c r="A14" s="142"/>
       <c r="B14" s="35">
         <v>46191</v>
       </c>
@@ -11910,7 +11922,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="118"/>
+      <c r="A15" s="142"/>
       <c r="B15" s="35">
         <v>46192</v>
       </c>
@@ -11938,7 +11950,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="118"/>
+      <c r="A16" s="142"/>
       <c r="B16" s="35">
         <v>46197</v>
       </c>
@@ -11966,7 +11978,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="119"/>
+      <c r="A17" s="143"/>
       <c r="B17" s="42">
         <v>46197</v>
       </c>
@@ -12028,7 +12040,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="120" t="s">
+      <c r="A20" s="144" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="35">
@@ -12054,7 +12066,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="121"/>
+      <c r="A21" s="145"/>
       <c r="B21" s="35">
         <v>46187</v>
       </c>
@@ -12082,7 +12094,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="121"/>
+      <c r="A22" s="145"/>
       <c r="B22" s="35">
         <v>46193</v>
       </c>
@@ -12110,7 +12122,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="121"/>
+      <c r="A23" s="145"/>
       <c r="B23" s="35">
         <v>46193</v>
       </c>
@@ -12138,7 +12150,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="121"/>
+      <c r="A24" s="145"/>
       <c r="B24" s="35">
         <v>46198</v>
       </c>
@@ -12166,7 +12178,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="122"/>
+      <c r="A25" s="146"/>
       <c r="B25" s="42">
         <v>46198</v>
       </c>
@@ -12228,7 +12240,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="111" t="s">
+      <c r="A28" s="135" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="35">
@@ -12254,7 +12266,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="112"/>
+      <c r="A29" s="136"/>
       <c r="B29" s="35">
         <v>46187</v>
       </c>
@@ -12282,7 +12294,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="112"/>
+      <c r="A30" s="136"/>
       <c r="B30" s="35">
         <v>46192</v>
       </c>
@@ -12310,7 +12322,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="112"/>
+      <c r="A31" s="136"/>
       <c r="B31" s="35">
         <v>46193</v>
       </c>
@@ -12338,7 +12350,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="112"/>
+      <c r="A32" s="136"/>
       <c r="B32" s="35">
         <v>46199</v>
       </c>
@@ -12366,7 +12378,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="113"/>
+      <c r="A33" s="137"/>
       <c r="B33" s="42">
         <v>46199</v>
       </c>
@@ -12428,7 +12440,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="129" t="s">
+      <c r="A36" s="117" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="35">
@@ -12458,7 +12470,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="130"/>
+      <c r="A37" s="118"/>
       <c r="B37" s="35">
         <v>46188</v>
       </c>
@@ -12486,7 +12498,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="130"/>
+      <c r="A38" s="118"/>
       <c r="B38" s="35">
         <v>46193</v>
       </c>
@@ -12514,7 +12526,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="130"/>
+      <c r="A39" s="118"/>
       <c r="B39" s="35">
         <v>46194</v>
       </c>
@@ -12542,7 +12554,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="130"/>
+      <c r="A40" s="118"/>
       <c r="B40" s="35">
         <v>46198</v>
       </c>
@@ -12570,7 +12582,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="131"/>
+      <c r="A41" s="119"/>
       <c r="B41" s="42">
         <v>46198</v>
       </c>
@@ -12632,7 +12644,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="132" t="s">
+      <c r="A44" s="120" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="35">
@@ -12662,7 +12674,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="133"/>
+      <c r="A45" s="121"/>
       <c r="B45" s="35">
         <v>46188</v>
       </c>
@@ -12690,7 +12702,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="133"/>
+      <c r="A46" s="121"/>
       <c r="B46" s="35">
         <v>46193</v>
       </c>
@@ -12718,7 +12730,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="133"/>
+      <c r="A47" s="121"/>
       <c r="B47" s="35">
         <v>46194</v>
       </c>
@@ -12746,7 +12758,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="133"/>
+      <c r="A48" s="121"/>
       <c r="B48" s="35">
         <v>46199</v>
       </c>
@@ -12774,7 +12786,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="134"/>
+      <c r="A49" s="122"/>
       <c r="B49" s="42">
         <v>46199</v>
       </c>
@@ -12836,7 +12848,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="135" t="s">
+      <c r="A52" s="123" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="35">
@@ -12860,13 +12872,13 @@
       <c r="H52" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="J52" s="1" t="str">
+      <c r="J52" s="1">
         <f>IF(OR(Resultados!F52="",Resultados!G52=""),"",IF(AND(F52=Resultados!F52,G52=Resultados!G52),2,IF(((F52&gt;G52)=(Resultados!F52&gt;Resultados!G52))*((F52&lt;G52)=(Resultados!F52&lt;Resultados!G52)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="136"/>
+      <c r="A53" s="124"/>
       <c r="B53" s="35">
         <v>46189</v>
       </c>
@@ -12894,7 +12906,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="136"/>
+      <c r="A54" s="124"/>
       <c r="B54" s="35">
         <v>46194</v>
       </c>
@@ -12922,7 +12934,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="136"/>
+      <c r="A55" s="124"/>
       <c r="B55" s="35">
         <v>46195</v>
       </c>
@@ -12950,7 +12962,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="136"/>
+      <c r="A56" s="124"/>
       <c r="B56" s="35">
         <v>46200</v>
       </c>
@@ -12978,7 +12990,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="137"/>
+      <c r="A57" s="125"/>
       <c r="B57" s="42">
         <v>46200</v>
       </c>
@@ -13040,7 +13052,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="138" t="s">
+      <c r="A60" s="126" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="35">
@@ -13064,13 +13076,13 @@
       <c r="H60" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="J60" s="1" t="str">
+      <c r="J60" s="1">
         <f>IF(OR(Resultados!F60="",Resultados!G60=""),"",IF(AND(F60=Resultados!F60,G60=Resultados!G60),2,IF(((F60&gt;G60)=(Resultados!F60&gt;Resultados!G60))*((F60&lt;G60)=(Resultados!F60&lt;Resultados!G60)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="139"/>
+      <c r="A61" s="127"/>
       <c r="B61" s="35">
         <v>46189</v>
       </c>
@@ -13092,13 +13104,13 @@
       <c r="H61" s="46" t="s">
         <v>49</v>
       </c>
-      <c r="J61" s="1" t="str">
+      <c r="J61" s="1">
         <f>IF(OR(Resultados!F61="",Resultados!G61=""),"",IF(AND(F61=Resultados!F61,G61=Resultados!G61),2,IF(((F61&gt;G61)=(Resultados!F61&gt;Resultados!G61))*((F61&lt;G61)=(Resultados!F61&lt;Resultados!G61)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="139"/>
+      <c r="A62" s="127"/>
       <c r="B62" s="35">
         <v>46194</v>
       </c>
@@ -13126,7 +13138,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="139"/>
+      <c r="A63" s="127"/>
       <c r="B63" s="35">
         <v>46195</v>
       </c>
@@ -13154,7 +13166,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="139"/>
+      <c r="A64" s="127"/>
       <c r="B64" s="35">
         <v>46200</v>
       </c>
@@ -13182,7 +13194,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="140"/>
+      <c r="A65" s="128"/>
       <c r="B65" s="42">
         <v>46200</v>
       </c>
@@ -13244,7 +13256,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="141" t="s">
+      <c r="A68" s="129" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="35">
@@ -13274,7 +13286,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="142"/>
+      <c r="A69" s="130"/>
       <c r="B69" s="35">
         <v>46190</v>
       </c>
@@ -13302,7 +13314,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="142"/>
+      <c r="A70" s="130"/>
       <c r="B70" s="35">
         <v>46195</v>
       </c>
@@ -13330,7 +13342,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="142"/>
+      <c r="A71" s="130"/>
       <c r="B71" s="35">
         <v>46196</v>
       </c>
@@ -13358,7 +13370,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="142"/>
+      <c r="A72" s="130"/>
       <c r="B72" s="35">
         <v>46199</v>
       </c>
@@ -13386,7 +13398,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="143"/>
+      <c r="A73" s="131"/>
       <c r="B73" s="42">
         <v>46199</v>
       </c>
@@ -13448,7 +13460,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="144" t="s">
+      <c r="A76" s="132" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="35">
@@ -13478,7 +13490,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="145"/>
+      <c r="A77" s="133"/>
       <c r="B77" s="35">
         <v>46190</v>
       </c>
@@ -13506,7 +13518,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="145"/>
+      <c r="A78" s="133"/>
       <c r="B78" s="35">
         <v>46195</v>
       </c>
@@ -13534,7 +13546,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="145"/>
+      <c r="A79" s="133"/>
       <c r="B79" s="35">
         <v>46196</v>
       </c>
@@ -13562,7 +13574,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="145"/>
+      <c r="A80" s="133"/>
       <c r="B80" s="35">
         <v>46201</v>
       </c>
@@ -13590,7 +13602,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="146"/>
+      <c r="A81" s="134"/>
       <c r="B81" s="42">
         <v>46201</v>
       </c>
@@ -13652,7 +13664,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="123" t="s">
+      <c r="A84" s="111" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="35">
@@ -13682,7 +13694,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="124"/>
+      <c r="A85" s="112"/>
       <c r="B85" s="35">
         <v>46191</v>
       </c>
@@ -13710,7 +13722,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="124"/>
+      <c r="A86" s="112"/>
       <c r="B86" s="35">
         <v>46196</v>
       </c>
@@ -13738,7 +13750,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="124"/>
+      <c r="A87" s="112"/>
       <c r="B87" s="35">
         <v>46197</v>
       </c>
@@ -13766,7 +13778,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="124"/>
+      <c r="A88" s="112"/>
       <c r="B88" s="35">
         <v>46201</v>
       </c>
@@ -13794,7 +13806,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="125"/>
+      <c r="A89" s="113"/>
       <c r="B89" s="42">
         <v>46201</v>
       </c>
@@ -13856,7 +13868,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="126" t="s">
+      <c r="A92" s="114" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="35">
@@ -13886,7 +13898,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="127"/>
+      <c r="A93" s="115"/>
       <c r="B93" s="35">
         <v>46191</v>
       </c>
@@ -13914,7 +13926,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="127"/>
+      <c r="A94" s="115"/>
       <c r="B94" s="35">
         <v>46196</v>
       </c>
@@ -13942,7 +13954,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="127"/>
+      <c r="A95" s="115"/>
       <c r="B95" s="35">
         <v>46197</v>
       </c>
@@ -13970,7 +13982,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="127"/>
+      <c r="A96" s="115"/>
       <c r="B96" s="35">
         <v>46200</v>
       </c>
@@ -13998,7 +14010,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="128"/>
+      <c r="A97" s="116"/>
       <c r="B97" s="42">
         <v>46200</v>
       </c>
@@ -14027,6 +14039,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A28:A33"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:A9"/>
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="A20:A25"/>
     <mergeCell ref="A84:A89"/>
     <mergeCell ref="A92:A97"/>
     <mergeCell ref="A36:A41"/>
@@ -14035,12 +14053,6 @@
     <mergeCell ref="A60:A65"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="A76:A81"/>
-    <mergeCell ref="A28:A33"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A4:A9"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="A20:A25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -14068,26 +14080,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="63" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="65"/>
+      <c r="A1" s="69" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="71"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="66"/>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="68"/>
+      <c r="A2" s="72"/>
+      <c r="B2" s="73"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="74"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -14120,7 +14132,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="90" t="s">
+      <c r="A4" s="96" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -14150,7 +14162,7 @@
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="91"/>
+      <c r="A5" s="97"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -14174,7 +14186,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="91"/>
+      <c r="A6" s="97"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -14202,7 +14214,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="91"/>
+      <c r="A7" s="97"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -14230,7 +14242,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="91"/>
+      <c r="A8" s="97"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -14258,7 +14270,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="92"/>
+      <c r="A9" s="98"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -14320,7 +14332,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="93" t="s">
+      <c r="A12" s="99" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -14346,7 +14358,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="94"/>
+      <c r="A13" s="100"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -14370,7 +14382,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="94"/>
+      <c r="A14" s="100"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -14398,7 +14410,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="94"/>
+      <c r="A15" s="100"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -14426,7 +14438,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="94"/>
+      <c r="A16" s="100"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -14454,7 +14466,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="95"/>
+      <c r="A17" s="101"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -14516,7 +14528,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="96" t="s">
+      <c r="A20" s="102" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -14542,7 +14554,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="97"/>
+      <c r="A21" s="103"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -14570,7 +14582,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="97"/>
+      <c r="A22" s="103"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -14598,7 +14610,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="97"/>
+      <c r="A23" s="103"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -14626,7 +14638,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="97"/>
+      <c r="A24" s="103"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -14654,7 +14666,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="98"/>
+      <c r="A25" s="104"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -14716,7 +14728,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="99" t="s">
+      <c r="A28" s="105" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -14742,7 +14754,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="100"/>
+      <c r="A29" s="106"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -14770,7 +14782,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="100"/>
+      <c r="A30" s="106"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -14798,7 +14810,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="100"/>
+      <c r="A31" s="106"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -14826,7 +14838,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="100"/>
+      <c r="A32" s="106"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -14854,7 +14866,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="101"/>
+      <c r="A33" s="107"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -14916,7 +14928,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="102" t="s">
+      <c r="A36" s="108" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -14946,7 +14958,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="103"/>
+      <c r="A37" s="109"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -14974,7 +14986,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="103"/>
+      <c r="A38" s="109"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -15002,7 +15014,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="103"/>
+      <c r="A39" s="109"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -15030,7 +15042,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="103"/>
+      <c r="A40" s="109"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -15058,7 +15070,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="104"/>
+      <c r="A41" s="110"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -15120,7 +15132,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="72" t="s">
+      <c r="A44" s="78" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -15150,7 +15162,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="73"/>
+      <c r="A45" s="79"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -15178,7 +15190,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="73"/>
+      <c r="A46" s="79"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -15206,7 +15218,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="73"/>
+      <c r="A47" s="79"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -15234,7 +15246,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="73"/>
+      <c r="A48" s="79"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -15262,7 +15274,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="74"/>
+      <c r="A49" s="80"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -15324,7 +15336,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="75" t="s">
+      <c r="A52" s="81" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -15348,13 +15360,13 @@
       <c r="H52" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="J52" s="1" t="str">
+      <c r="J52" s="1">
         <f>IF(OR(Resultados!F52="",Resultados!G52=""),"",IF(AND(F52=Resultados!F52,G52=Resultados!G52),2,IF(((F52&gt;G52)=(Resultados!F52&gt;Resultados!G52))*((F52&lt;G52)=(Resultados!F52&lt;Resultados!G52)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="76"/>
+      <c r="A53" s="82"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -15382,7 +15394,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="76"/>
+      <c r="A54" s="82"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -15410,7 +15422,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="76"/>
+      <c r="A55" s="82"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -15438,7 +15450,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="76"/>
+      <c r="A56" s="82"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -15466,7 +15478,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="77"/>
+      <c r="A57" s="83"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -15528,7 +15540,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="78" t="s">
+      <c r="A60" s="84" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -15552,13 +15564,13 @@
       <c r="H60" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="J60" s="1" t="str">
+      <c r="J60" s="1">
         <f>IF(OR(Resultados!F60="",Resultados!G60=""),"",IF(AND(F60=Resultados!F60,G60=Resultados!G60),2,IF(((F60&gt;G60)=(Resultados!F60&gt;Resultados!G60))*((F60&lt;G60)=(Resultados!F60&lt;Resultados!G60)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="79"/>
+      <c r="A61" s="85"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -15580,13 +15592,13 @@
       <c r="H61" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="J61" s="1" t="str">
+      <c r="J61" s="1">
         <f>IF(OR(Resultados!F61="",Resultados!G61=""),"",IF(AND(F61=Resultados!F61,G61=Resultados!G61),2,IF(((F61&gt;G61)=(Resultados!F61&gt;Resultados!G61))*((F61&lt;G61)=(Resultados!F61&lt;Resultados!G61)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="79"/>
+      <c r="A62" s="85"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -15614,7 +15626,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="79"/>
+      <c r="A63" s="85"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -15642,7 +15654,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="79"/>
+      <c r="A64" s="85"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -15670,7 +15682,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="80"/>
+      <c r="A65" s="86"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -15732,7 +15744,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="81" t="s">
+      <c r="A68" s="87" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -15762,7 +15774,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="82"/>
+      <c r="A69" s="88"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -15790,7 +15802,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="82"/>
+      <c r="A70" s="88"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -15818,7 +15830,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="82"/>
+      <c r="A71" s="88"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -15846,7 +15858,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="82"/>
+      <c r="A72" s="88"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -15874,7 +15886,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="83"/>
+      <c r="A73" s="89"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -15936,7 +15948,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="84" t="s">
+      <c r="A76" s="90" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -15966,7 +15978,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="85"/>
+      <c r="A77" s="91"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -15994,7 +16006,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="85"/>
+      <c r="A78" s="91"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -16022,7 +16034,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="85"/>
+      <c r="A79" s="91"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -16050,7 +16062,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="85"/>
+      <c r="A80" s="91"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -16078,7 +16090,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="86"/>
+      <c r="A81" s="92"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -16140,7 +16152,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="87" t="s">
+      <c r="A84" s="93" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -16170,7 +16182,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="88"/>
+      <c r="A85" s="94"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -16198,7 +16210,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="88"/>
+      <c r="A86" s="94"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -16226,7 +16238,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="88"/>
+      <c r="A87" s="94"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -16254,7 +16266,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="88"/>
+      <c r="A88" s="94"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -16282,7 +16294,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="89"/>
+      <c r="A89" s="95"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -16344,7 +16356,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="69" t="s">
+      <c r="A92" s="75" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -16374,7 +16386,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="70"/>
+      <c r="A93" s="76"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -16402,7 +16414,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="70"/>
+      <c r="A94" s="76"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -16430,7 +16442,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="70"/>
+      <c r="A95" s="76"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -16458,7 +16470,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="70"/>
+      <c r="A96" s="76"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -16486,7 +16498,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="71"/>
+      <c r="A97" s="77"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -16515,6 +16527,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A28:A33"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:A9"/>
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="A20:A25"/>
     <mergeCell ref="A84:A89"/>
     <mergeCell ref="A92:A97"/>
     <mergeCell ref="A36:A41"/>
@@ -16523,12 +16541,6 @@
     <mergeCell ref="A60:A65"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="A76:A81"/>
-    <mergeCell ref="A28:A33"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A4:A9"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="A20:A25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -16556,26 +16568,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="63" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="65"/>
+      <c r="A1" s="69" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="71"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="66"/>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="68"/>
+      <c r="A2" s="72"/>
+      <c r="B2" s="73"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="74"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -16608,7 +16620,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="90" t="s">
+      <c r="A4" s="96" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -16638,7 +16650,7 @@
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="91"/>
+      <c r="A5" s="97"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -16662,7 +16674,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="91"/>
+      <c r="A6" s="97"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -16690,7 +16702,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="91"/>
+      <c r="A7" s="97"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -16718,7 +16730,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="91"/>
+      <c r="A8" s="97"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -16746,7 +16758,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="92"/>
+      <c r="A9" s="98"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -16808,7 +16820,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="93" t="s">
+      <c r="A12" s="99" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -16834,7 +16846,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="94"/>
+      <c r="A13" s="100"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -16858,7 +16870,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="94"/>
+      <c r="A14" s="100"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -16886,7 +16898,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="94"/>
+      <c r="A15" s="100"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -16914,7 +16926,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="94"/>
+      <c r="A16" s="100"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -16942,7 +16954,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="95"/>
+      <c r="A17" s="101"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -17004,7 +17016,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="96" t="s">
+      <c r="A20" s="102" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -17030,7 +17042,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="97"/>
+      <c r="A21" s="103"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -17058,7 +17070,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="97"/>
+      <c r="A22" s="103"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -17086,7 +17098,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="97"/>
+      <c r="A23" s="103"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -17114,7 +17126,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="97"/>
+      <c r="A24" s="103"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -17142,7 +17154,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="98"/>
+      <c r="A25" s="104"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -17204,7 +17216,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="99" t="s">
+      <c r="A28" s="105" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -17230,7 +17242,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="100"/>
+      <c r="A29" s="106"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -17258,7 +17270,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="100"/>
+      <c r="A30" s="106"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -17286,7 +17298,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="100"/>
+      <c r="A31" s="106"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -17314,7 +17326,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="100"/>
+      <c r="A32" s="106"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -17342,7 +17354,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="101"/>
+      <c r="A33" s="107"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -17404,7 +17416,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="102" t="s">
+      <c r="A36" s="108" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -17434,7 +17446,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="103"/>
+      <c r="A37" s="109"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -17462,7 +17474,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="103"/>
+      <c r="A38" s="109"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -17490,7 +17502,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="103"/>
+      <c r="A39" s="109"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -17518,7 +17530,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="103"/>
+      <c r="A40" s="109"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -17546,7 +17558,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="104"/>
+      <c r="A41" s="110"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -17608,7 +17620,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="72" t="s">
+      <c r="A44" s="78" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -17638,7 +17650,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="73"/>
+      <c r="A45" s="79"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -17666,7 +17678,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="73"/>
+      <c r="A46" s="79"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -17694,7 +17706,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="73"/>
+      <c r="A47" s="79"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -17722,7 +17734,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="73"/>
+      <c r="A48" s="79"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -17750,7 +17762,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="74"/>
+      <c r="A49" s="80"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -17812,7 +17824,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="75" t="s">
+      <c r="A52" s="81" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -17836,13 +17848,13 @@
       <c r="H52" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="J52" s="1" t="str">
+      <c r="J52" s="1">
         <f>IF(OR(Resultados!F52="",Resultados!G52=""),"",IF(AND(F52=Resultados!F52,G52=Resultados!G52),2,IF(((F52&gt;G52)=(Resultados!F52&gt;Resultados!G52))*((F52&lt;G52)=(Resultados!F52&lt;Resultados!G52)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="76"/>
+      <c r="A53" s="82"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -17870,7 +17882,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="76"/>
+      <c r="A54" s="82"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -17898,7 +17910,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="76"/>
+      <c r="A55" s="82"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -17926,7 +17938,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="76"/>
+      <c r="A56" s="82"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -17954,7 +17966,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="77"/>
+      <c r="A57" s="83"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -18016,7 +18028,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="78" t="s">
+      <c r="A60" s="84" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -18040,13 +18052,13 @@
       <c r="H60" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="J60" s="1" t="str">
+      <c r="J60" s="1">
         <f>IF(OR(Resultados!F60="",Resultados!G60=""),"",IF(AND(F60=Resultados!F60,G60=Resultados!G60),2,IF(((F60&gt;G60)=(Resultados!F60&gt;Resultados!G60))*((F60&lt;G60)=(Resultados!F60&lt;Resultados!G60)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="79"/>
+      <c r="A61" s="85"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -18068,13 +18080,13 @@
       <c r="H61" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="J61" s="1" t="str">
+      <c r="J61" s="1">
         <f>IF(OR(Resultados!F61="",Resultados!G61=""),"",IF(AND(F61=Resultados!F61,G61=Resultados!G61),2,IF(((F61&gt;G61)=(Resultados!F61&gt;Resultados!G61))*((F61&lt;G61)=(Resultados!F61&lt;Resultados!G61)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="79"/>
+      <c r="A62" s="85"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -18102,7 +18114,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="79"/>
+      <c r="A63" s="85"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -18130,7 +18142,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="79"/>
+      <c r="A64" s="85"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -18158,7 +18170,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="80"/>
+      <c r="A65" s="86"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -18220,7 +18232,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="81" t="s">
+      <c r="A68" s="87" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -18250,7 +18262,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="82"/>
+      <c r="A69" s="88"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -18278,7 +18290,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="82"/>
+      <c r="A70" s="88"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -18306,7 +18318,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="82"/>
+      <c r="A71" s="88"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -18334,7 +18346,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="82"/>
+      <c r="A72" s="88"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -18362,7 +18374,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="83"/>
+      <c r="A73" s="89"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -18424,7 +18436,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="84" t="s">
+      <c r="A76" s="90" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -18454,7 +18466,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="85"/>
+      <c r="A77" s="91"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -18482,7 +18494,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="85"/>
+      <c r="A78" s="91"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -18510,7 +18522,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="85"/>
+      <c r="A79" s="91"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -18538,7 +18550,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="85"/>
+      <c r="A80" s="91"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -18566,7 +18578,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="86"/>
+      <c r="A81" s="92"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -18628,7 +18640,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="87" t="s">
+      <c r="A84" s="93" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -18658,7 +18670,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="88"/>
+      <c r="A85" s="94"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -18686,7 +18698,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="88"/>
+      <c r="A86" s="94"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -18714,7 +18726,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="88"/>
+      <c r="A87" s="94"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -18742,7 +18754,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="88"/>
+      <c r="A88" s="94"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -18770,7 +18782,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="89"/>
+      <c r="A89" s="95"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -18832,7 +18844,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="69" t="s">
+      <c r="A92" s="75" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -18862,7 +18874,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="70"/>
+      <c r="A93" s="76"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -18890,7 +18902,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="70"/>
+      <c r="A94" s="76"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -18918,7 +18930,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="70"/>
+      <c r="A95" s="76"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -18946,7 +18958,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="70"/>
+      <c r="A96" s="76"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -18974,7 +18986,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="71"/>
+      <c r="A97" s="77"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -19003,6 +19015,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A28:A33"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:A9"/>
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="A20:A25"/>
     <mergeCell ref="A84:A89"/>
     <mergeCell ref="A92:A97"/>
     <mergeCell ref="A36:A41"/>
@@ -19011,12 +19029,6 @@
     <mergeCell ref="A60:A65"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="A76:A81"/>
-    <mergeCell ref="A28:A33"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A4:A9"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="A20:A25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19044,26 +19056,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="63" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="65"/>
+      <c r="A1" s="69" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="71"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="66"/>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="68"/>
+      <c r="A2" s="72"/>
+      <c r="B2" s="73"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="74"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -19096,7 +19108,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="90" t="s">
+      <c r="A4" s="96" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -19126,7 +19138,7 @@
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="91"/>
+      <c r="A5" s="97"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -19150,7 +19162,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="91"/>
+      <c r="A6" s="97"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -19178,7 +19190,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="91"/>
+      <c r="A7" s="97"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -19206,7 +19218,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="91"/>
+      <c r="A8" s="97"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -19234,7 +19246,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="92"/>
+      <c r="A9" s="98"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -19296,7 +19308,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="93" t="s">
+      <c r="A12" s="99" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -19322,7 +19334,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="94"/>
+      <c r="A13" s="100"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -19346,7 +19358,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="94"/>
+      <c r="A14" s="100"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -19374,7 +19386,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="94"/>
+      <c r="A15" s="100"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -19402,7 +19414,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="94"/>
+      <c r="A16" s="100"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -19430,7 +19442,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="95"/>
+      <c r="A17" s="101"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -19492,7 +19504,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="96" t="s">
+      <c r="A20" s="102" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -19518,7 +19530,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="97"/>
+      <c r="A21" s="103"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -19546,7 +19558,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="97"/>
+      <c r="A22" s="103"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -19574,7 +19586,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="97"/>
+      <c r="A23" s="103"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -19602,7 +19614,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="97"/>
+      <c r="A24" s="103"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -19630,7 +19642,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="98"/>
+      <c r="A25" s="104"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -19692,7 +19704,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="99" t="s">
+      <c r="A28" s="105" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -19718,7 +19730,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="100"/>
+      <c r="A29" s="106"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -19746,7 +19758,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="100"/>
+      <c r="A30" s="106"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -19774,7 +19786,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="100"/>
+      <c r="A31" s="106"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -19802,7 +19814,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="100"/>
+      <c r="A32" s="106"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -19826,7 +19838,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="101"/>
+      <c r="A33" s="107"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -19884,7 +19896,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="102" t="s">
+      <c r="A36" s="108" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -19914,7 +19926,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="103"/>
+      <c r="A37" s="109"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -19942,7 +19954,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="103"/>
+      <c r="A38" s="109"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -19966,7 +19978,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="103"/>
+      <c r="A39" s="109"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -19990,7 +20002,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="103"/>
+      <c r="A40" s="109"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -20014,7 +20026,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="104"/>
+      <c r="A41" s="110"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -20072,7 +20084,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="72" t="s">
+      <c r="A44" s="78" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -20102,7 +20114,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="73"/>
+      <c r="A45" s="79"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -20130,7 +20142,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="73"/>
+      <c r="A46" s="79"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -20154,7 +20166,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="73"/>
+      <c r="A47" s="79"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -20178,7 +20190,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="73"/>
+      <c r="A48" s="79"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -20202,7 +20214,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="74"/>
+      <c r="A49" s="80"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -20260,7 +20272,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="75" t="s">
+      <c r="A52" s="81" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -20284,13 +20296,13 @@
       <c r="H52" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="J52" s="1" t="str">
+      <c r="J52" s="1">
         <f>IF(OR(Resultados!F52="",Resultados!G52=""),"",IF(AND(F52=Resultados!F52,G52=Resultados!G52),2,IF(((F52&gt;G52)=(Resultados!F52&gt;Resultados!G52))*((F52&lt;G52)=(Resultados!F52&lt;Resultados!G52)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="76"/>
+      <c r="A53" s="82"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -20318,7 +20330,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="76"/>
+      <c r="A54" s="82"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -20342,7 +20354,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="76"/>
+      <c r="A55" s="82"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -20366,7 +20378,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="76"/>
+      <c r="A56" s="82"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -20390,7 +20402,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="77"/>
+      <c r="A57" s="83"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -20448,7 +20460,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="78" t="s">
+      <c r="A60" s="84" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -20463,18 +20475,22 @@
       <c r="E60" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="F60" s="26"/>
-      <c r="G60" s="26"/>
+      <c r="F60" s="26">
+        <v>4</v>
+      </c>
+      <c r="G60" s="26">
+        <v>0</v>
+      </c>
       <c r="H60" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="J60" s="1" t="str">
+      <c r="J60" s="1">
         <f>IF(OR(Resultados!F60="",Resultados!G60=""),"",IF(AND(F60=Resultados!F60,G60=Resultados!G60),2,IF(((F60&gt;G60)=(Resultados!F60&gt;Resultados!G60))*((F60&lt;G60)=(Resultados!F60&lt;Resultados!G60)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="79"/>
+      <c r="A61" s="85"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -20487,18 +20503,22 @@
       <c r="E61" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="F61" s="26"/>
-      <c r="G61" s="26"/>
+      <c r="F61" s="26">
+        <v>0</v>
+      </c>
+      <c r="G61" s="26">
+        <v>2</v>
+      </c>
       <c r="H61" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="J61" s="1" t="str">
+      <c r="J61" s="1">
         <f>IF(OR(Resultados!F61="",Resultados!G61=""),"",IF(AND(F61=Resultados!F61,G61=Resultados!G61),2,IF(((F61&gt;G61)=(Resultados!F61&gt;Resultados!G61))*((F61&lt;G61)=(Resultados!F61&lt;Resultados!G61)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="79"/>
+      <c r="A62" s="85"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -20522,7 +20542,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="79"/>
+      <c r="A63" s="85"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -20546,7 +20566,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="79"/>
+      <c r="A64" s="85"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -20570,7 +20590,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="80"/>
+      <c r="A65" s="86"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -20628,7 +20648,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="81" t="s">
+      <c r="A68" s="87" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -20643,8 +20663,12 @@
       <c r="E68" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F68" s="26"/>
-      <c r="G68" s="26"/>
+      <c r="F68" s="26">
+        <v>3</v>
+      </c>
+      <c r="G68" s="26">
+        <v>1</v>
+      </c>
       <c r="H68" s="21" t="s">
         <v>52</v>
       </c>
@@ -20654,7 +20678,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="82"/>
+      <c r="A69" s="88"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -20667,8 +20691,12 @@
       <c r="E69" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="F69" s="26"/>
-      <c r="G69" s="26"/>
+      <c r="F69" s="26">
+        <v>0</v>
+      </c>
+      <c r="G69" s="26">
+        <v>2</v>
+      </c>
       <c r="H69" s="21" t="s">
         <v>54</v>
       </c>
@@ -20678,7 +20706,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="82"/>
+      <c r="A70" s="88"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -20702,7 +20730,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="82"/>
+      <c r="A71" s="88"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -20726,7 +20754,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="82"/>
+      <c r="A72" s="88"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -20750,7 +20778,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="83"/>
+      <c r="A73" s="89"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -20808,7 +20836,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="84" t="s">
+      <c r="A76" s="90" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -20823,8 +20851,12 @@
       <c r="E76" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="F76" s="26"/>
-      <c r="G76" s="26"/>
+      <c r="F76" s="26">
+        <v>2</v>
+      </c>
+      <c r="G76" s="26">
+        <v>1</v>
+      </c>
       <c r="H76" s="21" t="s">
         <v>57</v>
       </c>
@@ -20834,7 +20866,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="85"/>
+      <c r="A77" s="91"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -20847,8 +20879,12 @@
       <c r="E77" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="F77" s="26"/>
-      <c r="G77" s="26"/>
+      <c r="F77" s="26">
+        <v>2</v>
+      </c>
+      <c r="G77" s="26">
+        <v>0</v>
+      </c>
       <c r="H77" s="21" t="s">
         <v>59</v>
       </c>
@@ -20858,7 +20894,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="85"/>
+      <c r="A78" s="91"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -20882,7 +20918,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="85"/>
+      <c r="A79" s="91"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -20906,7 +20942,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="85"/>
+      <c r="A80" s="91"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -20930,7 +20966,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="86"/>
+      <c r="A81" s="92"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -20988,7 +21024,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="87" t="s">
+      <c r="A84" s="93" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -21003,8 +21039,12 @@
       <c r="E84" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="F84" s="26"/>
-      <c r="G84" s="26"/>
+      <c r="F84" s="26">
+        <v>4</v>
+      </c>
+      <c r="G84" s="26">
+        <v>0</v>
+      </c>
       <c r="H84" s="21" t="s">
         <v>62</v>
       </c>
@@ -21014,7 +21054,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="88"/>
+      <c r="A85" s="94"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -21027,8 +21067,12 @@
       <c r="E85" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="F85" s="26"/>
-      <c r="G85" s="26"/>
+      <c r="F85" s="26">
+        <v>0</v>
+      </c>
+      <c r="G85" s="26">
+        <v>2</v>
+      </c>
       <c r="H85" s="21" t="s">
         <v>64</v>
       </c>
@@ -21038,7 +21082,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="88"/>
+      <c r="A86" s="94"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -21062,7 +21106,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="88"/>
+      <c r="A87" s="94"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -21086,7 +21130,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="88"/>
+      <c r="A88" s="94"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -21110,7 +21154,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="89"/>
+      <c r="A89" s="95"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -21168,7 +21212,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="69" t="s">
+      <c r="A92" s="75" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -21183,8 +21227,12 @@
       <c r="E92" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="F92" s="26"/>
-      <c r="G92" s="26"/>
+      <c r="F92" s="26">
+        <v>2</v>
+      </c>
+      <c r="G92" s="26">
+        <v>1</v>
+      </c>
       <c r="H92" s="21" t="s">
         <v>67</v>
       </c>
@@ -21194,7 +21242,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="70"/>
+      <c r="A93" s="76"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -21207,8 +21255,12 @@
       <c r="E93" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="F93" s="26"/>
-      <c r="G93" s="26"/>
+      <c r="F93" s="26">
+        <v>1</v>
+      </c>
+      <c r="G93" s="26">
+        <v>0</v>
+      </c>
       <c r="H93" s="21" t="s">
         <v>69</v>
       </c>
@@ -21218,7 +21270,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="70"/>
+      <c r="A94" s="76"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -21242,7 +21294,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="70"/>
+      <c r="A95" s="76"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -21266,7 +21318,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="70"/>
+      <c r="A96" s="76"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -21290,7 +21342,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="71"/>
+      <c r="A97" s="77"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -21315,6 +21367,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A28:A33"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:A9"/>
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="A20:A25"/>
     <mergeCell ref="A84:A89"/>
     <mergeCell ref="A92:A97"/>
     <mergeCell ref="A36:A41"/>
@@ -21323,12 +21381,6 @@
     <mergeCell ref="A60:A65"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="A76:A81"/>
-    <mergeCell ref="A28:A33"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A4:A9"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="A20:A25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21356,26 +21408,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="63" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="65"/>
+      <c r="A1" s="69" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="71"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="66"/>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="68"/>
+      <c r="A2" s="72"/>
+      <c r="B2" s="73"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="74"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -21408,7 +21460,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="90" t="s">
+      <c r="A4" s="96" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -21438,7 +21490,7 @@
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="91"/>
+      <c r="A5" s="97"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -21462,7 +21514,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="91"/>
+      <c r="A6" s="97"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -21490,7 +21542,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="91"/>
+      <c r="A7" s="97"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -21518,7 +21570,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="91"/>
+      <c r="A8" s="97"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -21546,7 +21598,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="92"/>
+      <c r="A9" s="98"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -21608,7 +21660,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="93" t="s">
+      <c r="A12" s="99" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -21634,7 +21686,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="94"/>
+      <c r="A13" s="100"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -21658,7 +21710,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="94"/>
+      <c r="A14" s="100"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -21686,7 +21738,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="94"/>
+      <c r="A15" s="100"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -21714,7 +21766,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="94"/>
+      <c r="A16" s="100"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -21742,7 +21794,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="95"/>
+      <c r="A17" s="101"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -21804,7 +21856,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="96" t="s">
+      <c r="A20" s="102" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -21830,7 +21882,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="97"/>
+      <c r="A21" s="103"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -21858,7 +21910,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="97"/>
+      <c r="A22" s="103"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -21886,7 +21938,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="97"/>
+      <c r="A23" s="103"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -21914,7 +21966,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="97"/>
+      <c r="A24" s="103"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -21942,7 +21994,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="98"/>
+      <c r="A25" s="104"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -22004,7 +22056,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="99" t="s">
+      <c r="A28" s="105" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -22030,7 +22082,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="100"/>
+      <c r="A29" s="106"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -22058,7 +22110,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="100"/>
+      <c r="A30" s="106"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -22086,7 +22138,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="100"/>
+      <c r="A31" s="106"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -22114,7 +22166,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="100"/>
+      <c r="A32" s="106"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -22142,7 +22194,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="101"/>
+      <c r="A33" s="107"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -22204,7 +22256,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="102" t="s">
+      <c r="A36" s="108" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -22234,7 +22286,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="103"/>
+      <c r="A37" s="109"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -22262,7 +22314,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="103"/>
+      <c r="A38" s="109"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -22290,7 +22342,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="103"/>
+      <c r="A39" s="109"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -22318,7 +22370,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="103"/>
+      <c r="A40" s="109"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -22346,7 +22398,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="104"/>
+      <c r="A41" s="110"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -22408,7 +22460,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="72" t="s">
+      <c r="A44" s="78" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -22438,7 +22490,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="73"/>
+      <c r="A45" s="79"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -22466,7 +22518,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="73"/>
+      <c r="A46" s="79"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -22494,7 +22546,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="73"/>
+      <c r="A47" s="79"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -22522,7 +22574,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="73"/>
+      <c r="A48" s="79"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -22550,7 +22602,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="74"/>
+      <c r="A49" s="80"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -22612,7 +22664,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="75" t="s">
+      <c r="A52" s="81" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -22636,13 +22688,13 @@
       <c r="H52" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="J52" s="1" t="str">
+      <c r="J52" s="1">
         <f>IF(OR(Resultados!F52="",Resultados!G52=""),"",IF(AND(F52=Resultados!F52,G52=Resultados!G52),2,IF(((F52&gt;G52)=(Resultados!F52&gt;Resultados!G52))*((F52&lt;G52)=(Resultados!F52&lt;Resultados!G52)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="76"/>
+      <c r="A53" s="82"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -22670,7 +22722,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="76"/>
+      <c r="A54" s="82"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -22698,7 +22750,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="76"/>
+      <c r="A55" s="82"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -22726,7 +22778,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="76"/>
+      <c r="A56" s="82"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -22754,7 +22806,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="77"/>
+      <c r="A57" s="83"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -22816,7 +22868,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="78" t="s">
+      <c r="A60" s="84" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -22840,13 +22892,13 @@
       <c r="H60" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="J60" s="1" t="str">
+      <c r="J60" s="1">
         <f>IF(OR(Resultados!F60="",Resultados!G60=""),"",IF(AND(F60=Resultados!F60,G60=Resultados!G60),2,IF(((F60&gt;G60)=(Resultados!F60&gt;Resultados!G60))*((F60&lt;G60)=(Resultados!F60&lt;Resultados!G60)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="79"/>
+      <c r="A61" s="85"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -22868,13 +22920,13 @@
       <c r="H61" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="J61" s="1" t="str">
+      <c r="J61" s="1">
         <f>IF(OR(Resultados!F61="",Resultados!G61=""),"",IF(AND(F61=Resultados!F61,G61=Resultados!G61),2,IF(((F61&gt;G61)=(Resultados!F61&gt;Resultados!G61))*((F61&lt;G61)=(Resultados!F61&lt;Resultados!G61)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="79"/>
+      <c r="A62" s="85"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -22902,7 +22954,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="79"/>
+      <c r="A63" s="85"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -22930,7 +22982,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="79"/>
+      <c r="A64" s="85"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -22958,7 +23010,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="80"/>
+      <c r="A65" s="86"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -23020,7 +23072,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="81" t="s">
+      <c r="A68" s="87" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -23050,7 +23102,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="82"/>
+      <c r="A69" s="88"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -23078,7 +23130,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="82"/>
+      <c r="A70" s="88"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -23106,7 +23158,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="82"/>
+      <c r="A71" s="88"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -23134,7 +23186,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="82"/>
+      <c r="A72" s="88"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -23162,7 +23214,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="83"/>
+      <c r="A73" s="89"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -23224,7 +23276,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="84" t="s">
+      <c r="A76" s="90" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -23254,7 +23306,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="85"/>
+      <c r="A77" s="91"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -23282,7 +23334,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="85"/>
+      <c r="A78" s="91"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -23310,7 +23362,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="85"/>
+      <c r="A79" s="91"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -23338,7 +23390,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="85"/>
+      <c r="A80" s="91"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -23366,7 +23418,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="86"/>
+      <c r="A81" s="92"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -23428,7 +23480,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="87" t="s">
+      <c r="A84" s="93" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -23458,7 +23510,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="88"/>
+      <c r="A85" s="94"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -23486,7 +23538,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="88"/>
+      <c r="A86" s="94"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -23514,7 +23566,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="88"/>
+      <c r="A87" s="94"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -23542,7 +23594,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="88"/>
+      <c r="A88" s="94"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -23570,7 +23622,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="89"/>
+      <c r="A89" s="95"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -23632,7 +23684,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="69" t="s">
+      <c r="A92" s="75" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -23662,7 +23714,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="70"/>
+      <c r="A93" s="76"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -23690,7 +23742,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="70"/>
+      <c r="A94" s="76"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -23718,7 +23770,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="70"/>
+      <c r="A95" s="76"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -23746,7 +23798,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="70"/>
+      <c r="A96" s="76"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -23774,7 +23826,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="71"/>
+      <c r="A97" s="77"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -23803,6 +23855,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A28:A33"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:A9"/>
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="A20:A25"/>
     <mergeCell ref="A84:A89"/>
     <mergeCell ref="A92:A97"/>
     <mergeCell ref="A36:A41"/>
@@ -23811,12 +23869,6 @@
     <mergeCell ref="A60:A65"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="A76:A81"/>
-    <mergeCell ref="A28:A33"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A4:A9"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="A20:A25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -23844,26 +23896,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="63" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="65"/>
+      <c r="A1" s="69" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="71"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="66"/>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="68"/>
+      <c r="A2" s="72"/>
+      <c r="B2" s="73"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="74"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -23896,7 +23948,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="90" t="s">
+      <c r="A4" s="96" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -23922,11 +23974,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="91"/>
+      <c r="A5" s="97"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -23950,7 +24002,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="91"/>
+      <c r="A6" s="97"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -23978,7 +24030,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="91"/>
+      <c r="A7" s="97"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -24006,7 +24058,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="91"/>
+      <c r="A8" s="97"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -24034,7 +24086,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="92"/>
+      <c r="A9" s="98"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -24096,7 +24148,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="93" t="s">
+      <c r="A12" s="99" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -24122,7 +24174,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="94"/>
+      <c r="A13" s="100"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -24146,7 +24198,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="94"/>
+      <c r="A14" s="100"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -24174,7 +24226,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="94"/>
+      <c r="A15" s="100"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -24202,7 +24254,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="94"/>
+      <c r="A16" s="100"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -24230,7 +24282,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="95"/>
+      <c r="A17" s="101"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -24292,7 +24344,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="96" t="s">
+      <c r="A20" s="102" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -24318,7 +24370,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="97"/>
+      <c r="A21" s="103"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -24346,7 +24398,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="97"/>
+      <c r="A22" s="103"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -24374,7 +24426,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="97"/>
+      <c r="A23" s="103"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -24402,7 +24454,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="97"/>
+      <c r="A24" s="103"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -24430,7 +24482,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="98"/>
+      <c r="A25" s="104"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -24492,7 +24544,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="99" t="s">
+      <c r="A28" s="105" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -24518,7 +24570,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="100"/>
+      <c r="A29" s="106"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -24546,7 +24598,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="100"/>
+      <c r="A30" s="106"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -24574,7 +24626,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="100"/>
+      <c r="A31" s="106"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -24602,7 +24654,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="100"/>
+      <c r="A32" s="106"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -24630,7 +24682,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="101"/>
+      <c r="A33" s="107"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -24692,7 +24744,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="102" t="s">
+      <c r="A36" s="108" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -24722,7 +24774,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="103"/>
+      <c r="A37" s="109"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -24750,7 +24802,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="103"/>
+      <c r="A38" s="109"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -24778,7 +24830,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="103"/>
+      <c r="A39" s="109"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -24806,7 +24858,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="103"/>
+      <c r="A40" s="109"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -24834,7 +24886,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="104"/>
+      <c r="A41" s="110"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -24896,7 +24948,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="72" t="s">
+      <c r="A44" s="78" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -24926,7 +24978,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="73"/>
+      <c r="A45" s="79"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -24954,7 +25006,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="73"/>
+      <c r="A46" s="79"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -24982,7 +25034,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="73"/>
+      <c r="A47" s="79"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -25010,7 +25062,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="73"/>
+      <c r="A48" s="79"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -25038,7 +25090,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="74"/>
+      <c r="A49" s="80"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -25100,7 +25152,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="75" t="s">
+      <c r="A52" s="81" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -25124,13 +25176,13 @@
       <c r="H52" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="J52" s="1" t="str">
+      <c r="J52" s="1">
         <f>IF(OR(Resultados!F52="",Resultados!G52=""),"",IF(AND(F52=Resultados!F52,G52=Resultados!G52),2,IF(((F52&gt;G52)=(Resultados!F52&gt;Resultados!G52))*((F52&lt;G52)=(Resultados!F52&lt;Resultados!G52)),1,0)))</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="76"/>
+      <c r="A53" s="82"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -25158,7 +25210,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="76"/>
+      <c r="A54" s="82"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -25186,7 +25238,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="76"/>
+      <c r="A55" s="82"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -25214,7 +25266,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="76"/>
+      <c r="A56" s="82"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -25242,7 +25294,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="77"/>
+      <c r="A57" s="83"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -25304,7 +25356,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="78" t="s">
+      <c r="A60" s="84" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -25328,13 +25380,13 @@
       <c r="H60" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="J60" s="1" t="str">
+      <c r="J60" s="1">
         <f>IF(OR(Resultados!F60="",Resultados!G60=""),"",IF(AND(F60=Resultados!F60,G60=Resultados!G60),2,IF(((F60&gt;G60)=(Resultados!F60&gt;Resultados!G60))*((F60&lt;G60)=(Resultados!F60&lt;Resultados!G60)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="79"/>
+      <c r="A61" s="85"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -25356,13 +25408,13 @@
       <c r="H61" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="J61" s="1" t="str">
+      <c r="J61" s="1">
         <f>IF(OR(Resultados!F61="",Resultados!G61=""),"",IF(AND(F61=Resultados!F61,G61=Resultados!G61),2,IF(((F61&gt;G61)=(Resultados!F61&gt;Resultados!G61))*((F61&lt;G61)=(Resultados!F61&lt;Resultados!G61)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="79"/>
+      <c r="A62" s="85"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -25390,7 +25442,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="79"/>
+      <c r="A63" s="85"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -25418,7 +25470,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="79"/>
+      <c r="A64" s="85"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -25446,7 +25498,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="80"/>
+      <c r="A65" s="86"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -25508,7 +25560,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="81" t="s">
+      <c r="A68" s="87" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -25538,7 +25590,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="82"/>
+      <c r="A69" s="88"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -25566,7 +25618,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="82"/>
+      <c r="A70" s="88"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -25594,7 +25646,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="82"/>
+      <c r="A71" s="88"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -25622,7 +25674,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="82"/>
+      <c r="A72" s="88"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -25650,7 +25702,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="83"/>
+      <c r="A73" s="89"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -25712,7 +25764,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="84" t="s">
+      <c r="A76" s="90" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -25742,7 +25794,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="85"/>
+      <c r="A77" s="91"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -25770,7 +25822,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="85"/>
+      <c r="A78" s="91"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -25798,7 +25850,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="85"/>
+      <c r="A79" s="91"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -25826,7 +25878,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="85"/>
+      <c r="A80" s="91"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -25854,7 +25906,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="86"/>
+      <c r="A81" s="92"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -25916,7 +25968,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="87" t="s">
+      <c r="A84" s="93" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -25946,7 +25998,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="88"/>
+      <c r="A85" s="94"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -25974,7 +26026,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="88"/>
+      <c r="A86" s="94"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -26002,7 +26054,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="88"/>
+      <c r="A87" s="94"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -26030,7 +26082,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="88"/>
+      <c r="A88" s="94"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -26058,7 +26110,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="89"/>
+      <c r="A89" s="95"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -26120,7 +26172,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="69" t="s">
+      <c r="A92" s="75" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -26150,7 +26202,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="70"/>
+      <c r="A93" s="76"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -26178,7 +26230,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="70"/>
+      <c r="A94" s="76"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -26206,7 +26258,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="70"/>
+      <c r="A95" s="76"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -26234,7 +26286,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="70"/>
+      <c r="A96" s="76"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -26262,7 +26314,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="71"/>
+      <c r="A97" s="77"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -26291,6 +26343,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A28:A33"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:A9"/>
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="A20:A25"/>
     <mergeCell ref="A84:A89"/>
     <mergeCell ref="A92:A97"/>
     <mergeCell ref="A36:A41"/>
@@ -26299,12 +26357,6 @@
     <mergeCell ref="A60:A65"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="A76:A81"/>
-    <mergeCell ref="A28:A33"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A4:A9"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="A20:A25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -26314,15 +26366,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002C0F7B7ABDCE27479D95CFC7ADDC4572" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c0771701eba7f6410c1e0f3fe0c7bdcf">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="7461ab22-4e70-4395-beb5-078d6ab567bf" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d6892b64abf6d5feebd4f731b4cb1b60" ns3:_="">
     <xsd:import namespace="7461ab22-4e70-4395-beb5-078d6ab567bf"/>
@@ -26522,6 +26565,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -26531,14 +26583,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5511D132-9333-423C-BAEC-48101CE7245F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8EF7CC95-797E-486E-895B-7264851EBF4B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -26552,6 +26596,14 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5511D132-9333-423C-BAEC-48101CE7245F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data/Quiniela.xlsx
+++ b/data/Quiniela.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cindy\Desktop\QuinielaMundial\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE8FEF95-A8B8-4D47-952E-A8E35ECBB587}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7ED3C1E-993C-4D3B-9852-589ED0D28698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9503E40F-C0E1-49CE-B4EA-3C401754995E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{9503E40F-C0E1-49CE-B4EA-3C401754995E}"/>
   </bookViews>
   <sheets>
     <sheet name="Resultados" sheetId="1" r:id="rId1"/>
@@ -1425,6 +1425,54 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1518,54 +1566,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2662,7 +2662,7 @@
       <c r="D37" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="E37" s="10" t="s">
+      <c r="E37" s="27" t="s">
         <v>33</v>
       </c>
       <c r="F37" s="62">
@@ -2990,12 +2990,16 @@
       <c r="D53" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="E53" s="10" t="s">
+      <c r="E53" s="61" t="s">
         <v>43</v>
       </c>
-      <c r="F53" s="26"/>
-      <c r="G53" s="26"/>
-      <c r="H53" s="21" t="s">
+      <c r="F53" s="26">
+        <v>2</v>
+      </c>
+      <c r="G53" s="26">
+        <v>2</v>
+      </c>
+      <c r="H53" s="61" t="s">
         <v>44</v>
       </c>
     </row>
@@ -3986,7 +3990,7 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -5216,9 +5220,9 @@
       <c r="H53" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="J53" s="1" t="str">
+      <c r="J53" s="1">
         <f>IF(OR(Resultados!F53="",Resultados!G53=""),"",IF(AND(F53=Resultados!F53,G53=Resultados!G53),2,IF(((F53&gt;G53)=(Resultados!F53&gt;Resultados!G53))*((F53&lt;G53)=(Resultados!F53&lt;Resultados!G53)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -6355,12 +6359,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A28:A33"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A4:A9"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="A20:A25"/>
     <mergeCell ref="A84:A89"/>
     <mergeCell ref="A92:A97"/>
     <mergeCell ref="A36:A41"/>
@@ -6369,6 +6367,12 @@
     <mergeCell ref="A60:A65"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="A76:A81"/>
+    <mergeCell ref="A28:A33"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:A9"/>
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="A20:A25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -6474,7 +6478,7 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -7704,9 +7708,9 @@
       <c r="H53" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="J53" s="1" t="str">
+      <c r="J53" s="1">
         <f>IF(OR(Resultados!F53="",Resultados!G53=""),"",IF(AND(F53=Resultados!F53,G53=Resultados!G53),2,IF(((F53&gt;G53)=(Resultados!F53&gt;Resultados!G53))*((F53&lt;G53)=(Resultados!F53&lt;Resultados!G53)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -8843,12 +8847,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A28:A33"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A4:A9"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="A20:A25"/>
     <mergeCell ref="A84:A89"/>
     <mergeCell ref="A92:A97"/>
     <mergeCell ref="A36:A41"/>
@@ -8857,6 +8855,12 @@
     <mergeCell ref="A60:A65"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="A76:A81"/>
+    <mergeCell ref="A28:A33"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:A9"/>
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="A20:A25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -8922,10 +8926,10 @@
       </c>
       <c r="E5" s="59" t="str" cm="1">
         <f t="array" ref="E5:F13">_xlfn._xlws.SORT(A5:B13,2,-1)</f>
-        <v>Erik</v>
+        <v>Lennon</v>
       </c>
       <c r="F5" s="59">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -8934,13 +8938,13 @@
       </c>
       <c r="B6" s="58">
         <f>Wendy!L4</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" s="55">
         <v>2</v>
       </c>
       <c r="E6" s="55" t="str">
-        <v>Lennon</v>
+        <v>Erik</v>
       </c>
       <c r="F6" s="55">
         <v>6</v>
@@ -8961,7 +8965,7 @@
         <v>Yulian</v>
       </c>
       <c r="F7" s="56">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -8976,7 +8980,7 @@
         <v>4</v>
       </c>
       <c r="E8" s="28" t="str">
-        <v>Bere</v>
+        <v>Wendy</v>
       </c>
       <c r="F8" s="28">
         <v>5</v>
@@ -8994,10 +8998,10 @@
         <v>5</v>
       </c>
       <c r="E9" s="28" t="str">
-        <v>Wendy</v>
+        <v>Packy</v>
       </c>
       <c r="F9" s="28">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -9006,16 +9010,16 @@
       </c>
       <c r="B10" s="58">
         <f>Lennon!L4</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10" s="28">
         <v>6</v>
       </c>
       <c r="E10" s="28" t="str">
-        <v>Jimmy</v>
+        <v>Bere</v>
       </c>
       <c r="F10" s="28">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -9024,13 +9028,13 @@
       </c>
       <c r="B11" s="58">
         <f>Yulian!L4</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D11" s="28">
         <v>7</v>
       </c>
       <c r="E11" s="28" t="str">
-        <v>Erick</v>
+        <v>Jimmy</v>
       </c>
       <c r="F11" s="28">
         <v>4</v>
@@ -9042,16 +9046,16 @@
       </c>
       <c r="B12" s="58">
         <f>Packy!L4</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D12" s="28">
         <v>8</v>
       </c>
       <c r="E12" s="28" t="str">
-        <v>Cindy</v>
+        <v>Erick</v>
       </c>
       <c r="F12" s="28">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -9066,7 +9070,7 @@
         <v>9</v>
       </c>
       <c r="E13" s="28" t="str">
-        <v>Packy</v>
+        <v>Cindy</v>
       </c>
       <c r="F13" s="28">
         <v>3</v>
@@ -9155,7 +9159,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="138" t="s">
+      <c r="A4" s="114" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="35">
@@ -9185,7 +9189,7 @@
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="139"/>
+      <c r="A5" s="115"/>
       <c r="B5" s="35">
         <v>46185</v>
       </c>
@@ -9209,7 +9213,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="139"/>
+      <c r="A6" s="115"/>
       <c r="B6" s="35">
         <v>46191</v>
       </c>
@@ -9237,7 +9241,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="139"/>
+      <c r="A7" s="115"/>
       <c r="B7" s="35">
         <v>46192</v>
       </c>
@@ -9265,7 +9269,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="139"/>
+      <c r="A8" s="115"/>
       <c r="B8" s="35">
         <v>46198</v>
       </c>
@@ -9293,7 +9297,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="140"/>
+      <c r="A9" s="116"/>
       <c r="B9" s="42">
         <v>46198</v>
       </c>
@@ -9355,7 +9359,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="141" t="s">
+      <c r="A12" s="117" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="35">
@@ -9381,7 +9385,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="142"/>
+      <c r="A13" s="118"/>
       <c r="B13" s="35">
         <v>46186</v>
       </c>
@@ -9405,7 +9409,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="142"/>
+      <c r="A14" s="118"/>
       <c r="B14" s="35">
         <v>46191</v>
       </c>
@@ -9433,7 +9437,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="142"/>
+      <c r="A15" s="118"/>
       <c r="B15" s="35">
         <v>46192</v>
       </c>
@@ -9461,7 +9465,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="142"/>
+      <c r="A16" s="118"/>
       <c r="B16" s="35">
         <v>46197</v>
       </c>
@@ -9489,7 +9493,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="143"/>
+      <c r="A17" s="119"/>
       <c r="B17" s="42">
         <v>46197</v>
       </c>
@@ -9551,7 +9555,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="144" t="s">
+      <c r="A20" s="120" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="35">
@@ -9577,7 +9581,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="145"/>
+      <c r="A21" s="121"/>
       <c r="B21" s="35">
         <v>46187</v>
       </c>
@@ -9605,7 +9609,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="145"/>
+      <c r="A22" s="121"/>
       <c r="B22" s="35">
         <v>46193</v>
       </c>
@@ -9633,7 +9637,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="145"/>
+      <c r="A23" s="121"/>
       <c r="B23" s="35">
         <v>46193</v>
       </c>
@@ -9661,7 +9665,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="145"/>
+      <c r="A24" s="121"/>
       <c r="B24" s="35">
         <v>46198</v>
       </c>
@@ -9689,7 +9693,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="146"/>
+      <c r="A25" s="122"/>
       <c r="B25" s="42">
         <v>46198</v>
       </c>
@@ -9751,7 +9755,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="135" t="s">
+      <c r="A28" s="111" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="35">
@@ -9777,7 +9781,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="136"/>
+      <c r="A29" s="112"/>
       <c r="B29" s="35">
         <v>46187</v>
       </c>
@@ -9805,7 +9809,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="136"/>
+      <c r="A30" s="112"/>
       <c r="B30" s="35">
         <v>46192</v>
       </c>
@@ -9833,7 +9837,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="136"/>
+      <c r="A31" s="112"/>
       <c r="B31" s="35">
         <v>46193</v>
       </c>
@@ -9861,7 +9865,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="136"/>
+      <c r="A32" s="112"/>
       <c r="B32" s="35">
         <v>46199</v>
       </c>
@@ -9889,7 +9893,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="137"/>
+      <c r="A33" s="113"/>
       <c r="B33" s="42">
         <v>46199</v>
       </c>
@@ -9951,7 +9955,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="117" t="s">
+      <c r="A36" s="129" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="35">
@@ -9981,7 +9985,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="118"/>
+      <c r="A37" s="130"/>
       <c r="B37" s="35">
         <v>46188</v>
       </c>
@@ -10009,7 +10013,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="118"/>
+      <c r="A38" s="130"/>
       <c r="B38" s="35">
         <v>46193</v>
       </c>
@@ -10037,7 +10041,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="118"/>
+      <c r="A39" s="130"/>
       <c r="B39" s="35">
         <v>46194</v>
       </c>
@@ -10065,7 +10069,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="118"/>
+      <c r="A40" s="130"/>
       <c r="B40" s="35">
         <v>46198</v>
       </c>
@@ -10093,7 +10097,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="119"/>
+      <c r="A41" s="131"/>
       <c r="B41" s="42">
         <v>46198</v>
       </c>
@@ -10155,7 +10159,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="120" t="s">
+      <c r="A44" s="132" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="35">
@@ -10185,7 +10189,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="121"/>
+      <c r="A45" s="133"/>
       <c r="B45" s="35">
         <v>46188</v>
       </c>
@@ -10213,7 +10217,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="121"/>
+      <c r="A46" s="133"/>
       <c r="B46" s="35">
         <v>46193</v>
       </c>
@@ -10241,7 +10245,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="121"/>
+      <c r="A47" s="133"/>
       <c r="B47" s="35">
         <v>46194</v>
       </c>
@@ -10269,7 +10273,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="121"/>
+      <c r="A48" s="133"/>
       <c r="B48" s="35">
         <v>46199</v>
       </c>
@@ -10297,7 +10301,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="122"/>
+      <c r="A49" s="134"/>
       <c r="B49" s="42">
         <v>46199</v>
       </c>
@@ -10359,7 +10363,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="123" t="s">
+      <c r="A52" s="135" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="35">
@@ -10389,7 +10393,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="124"/>
+      <c r="A53" s="136"/>
       <c r="B53" s="35">
         <v>46189</v>
       </c>
@@ -10411,13 +10415,13 @@
       <c r="H53" s="46" t="s">
         <v>44</v>
       </c>
-      <c r="J53" s="1" t="str">
+      <c r="J53" s="1">
         <f>IF(OR(Resultados!F53="",Resultados!G53=""),"",IF(AND(F53=Resultados!F53,G53=Resultados!G53),2,IF(((F53&gt;G53)=(Resultados!F53&gt;Resultados!G53))*((F53&lt;G53)=(Resultados!F53&lt;Resultados!G53)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="124"/>
+      <c r="A54" s="136"/>
       <c r="B54" s="35">
         <v>46194</v>
       </c>
@@ -10445,7 +10449,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="124"/>
+      <c r="A55" s="136"/>
       <c r="B55" s="35">
         <v>46195</v>
       </c>
@@ -10473,7 +10477,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="124"/>
+      <c r="A56" s="136"/>
       <c r="B56" s="35">
         <v>46200</v>
       </c>
@@ -10501,7 +10505,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="125"/>
+      <c r="A57" s="137"/>
       <c r="B57" s="42">
         <v>46200</v>
       </c>
@@ -10563,7 +10567,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="126" t="s">
+      <c r="A60" s="138" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="35">
@@ -10593,7 +10597,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="127"/>
+      <c r="A61" s="139"/>
       <c r="B61" s="35">
         <v>46189</v>
       </c>
@@ -10621,7 +10625,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="127"/>
+      <c r="A62" s="139"/>
       <c r="B62" s="35">
         <v>46194</v>
       </c>
@@ -10649,7 +10653,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="127"/>
+      <c r="A63" s="139"/>
       <c r="B63" s="35">
         <v>46195</v>
       </c>
@@ -10677,7 +10681,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="127"/>
+      <c r="A64" s="139"/>
       <c r="B64" s="35">
         <v>46200</v>
       </c>
@@ -10705,7 +10709,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="128"/>
+      <c r="A65" s="140"/>
       <c r="B65" s="42">
         <v>46200</v>
       </c>
@@ -10767,7 +10771,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="129" t="s">
+      <c r="A68" s="141" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="35">
@@ -10797,7 +10801,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="130"/>
+      <c r="A69" s="142"/>
       <c r="B69" s="35">
         <v>46190</v>
       </c>
@@ -10825,7 +10829,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="130"/>
+      <c r="A70" s="142"/>
       <c r="B70" s="35">
         <v>46195</v>
       </c>
@@ -10853,7 +10857,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="130"/>
+      <c r="A71" s="142"/>
       <c r="B71" s="35">
         <v>46196</v>
       </c>
@@ -10881,7 +10885,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="130"/>
+      <c r="A72" s="142"/>
       <c r="B72" s="35">
         <v>46199</v>
       </c>
@@ -10909,7 +10913,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="131"/>
+      <c r="A73" s="143"/>
       <c r="B73" s="42">
         <v>46199</v>
       </c>
@@ -10971,7 +10975,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="132" t="s">
+      <c r="A76" s="144" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="35">
@@ -11001,7 +11005,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="133"/>
+      <c r="A77" s="145"/>
       <c r="B77" s="35">
         <v>46190</v>
       </c>
@@ -11029,7 +11033,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="133"/>
+      <c r="A78" s="145"/>
       <c r="B78" s="35">
         <v>46195</v>
       </c>
@@ -11057,7 +11061,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="133"/>
+      <c r="A79" s="145"/>
       <c r="B79" s="35">
         <v>46196</v>
       </c>
@@ -11085,7 +11089,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="133"/>
+      <c r="A80" s="145"/>
       <c r="B80" s="35">
         <v>46201</v>
       </c>
@@ -11113,7 +11117,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="134"/>
+      <c r="A81" s="146"/>
       <c r="B81" s="42">
         <v>46201</v>
       </c>
@@ -11175,7 +11179,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="111" t="s">
+      <c r="A84" s="123" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="35">
@@ -11205,7 +11209,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="112"/>
+      <c r="A85" s="124"/>
       <c r="B85" s="35">
         <v>46191</v>
       </c>
@@ -11233,7 +11237,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="112"/>
+      <c r="A86" s="124"/>
       <c r="B86" s="35">
         <v>46196</v>
       </c>
@@ -11261,7 +11265,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="112"/>
+      <c r="A87" s="124"/>
       <c r="B87" s="35">
         <v>46197</v>
       </c>
@@ -11289,7 +11293,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="112"/>
+      <c r="A88" s="124"/>
       <c r="B88" s="35">
         <v>46201</v>
       </c>
@@ -11317,7 +11321,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="113"/>
+      <c r="A89" s="125"/>
       <c r="B89" s="42">
         <v>46201</v>
       </c>
@@ -11379,7 +11383,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="114" t="s">
+      <c r="A92" s="126" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="35">
@@ -11409,7 +11413,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="115"/>
+      <c r="A93" s="127"/>
       <c r="B93" s="35">
         <v>46191</v>
       </c>
@@ -11437,7 +11441,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="115"/>
+      <c r="A94" s="127"/>
       <c r="B94" s="35">
         <v>46196</v>
       </c>
@@ -11465,7 +11469,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="115"/>
+      <c r="A95" s="127"/>
       <c r="B95" s="35">
         <v>46197</v>
       </c>
@@ -11493,7 +11497,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="115"/>
+      <c r="A96" s="127"/>
       <c r="B96" s="35">
         <v>46200</v>
       </c>
@@ -11521,7 +11525,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="116"/>
+      <c r="A97" s="128"/>
       <c r="B97" s="42">
         <v>46200</v>
       </c>
@@ -11550,12 +11554,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A28:A33"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A4:A9"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="A20:A25"/>
     <mergeCell ref="A84:A89"/>
     <mergeCell ref="A92:A97"/>
     <mergeCell ref="A36:A41"/>
@@ -11564,6 +11562,12 @@
     <mergeCell ref="A60:A65"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="A76:A81"/>
+    <mergeCell ref="A28:A33"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:A9"/>
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="A20:A25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -11644,7 +11648,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="138" t="s">
+      <c r="A4" s="114" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="35">
@@ -11670,11 +11674,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="139"/>
+      <c r="A5" s="115"/>
       <c r="B5" s="35">
         <v>46185</v>
       </c>
@@ -11698,7 +11702,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="139"/>
+      <c r="A6" s="115"/>
       <c r="B6" s="35">
         <v>46191</v>
       </c>
@@ -11726,7 +11730,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="139"/>
+      <c r="A7" s="115"/>
       <c r="B7" s="35">
         <v>46192</v>
       </c>
@@ -11754,7 +11758,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="139"/>
+      <c r="A8" s="115"/>
       <c r="B8" s="35">
         <v>46198</v>
       </c>
@@ -11782,7 +11786,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="140"/>
+      <c r="A9" s="116"/>
       <c r="B9" s="42">
         <v>46198</v>
       </c>
@@ -11844,7 +11848,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="141" t="s">
+      <c r="A12" s="117" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="35">
@@ -11870,7 +11874,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="142"/>
+      <c r="A13" s="118"/>
       <c r="B13" s="35">
         <v>46186</v>
       </c>
@@ -11894,7 +11898,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="142"/>
+      <c r="A14" s="118"/>
       <c r="B14" s="35">
         <v>46191</v>
       </c>
@@ -11922,7 +11926,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="142"/>
+      <c r="A15" s="118"/>
       <c r="B15" s="35">
         <v>46192</v>
       </c>
@@ -11950,7 +11954,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="142"/>
+      <c r="A16" s="118"/>
       <c r="B16" s="35">
         <v>46197</v>
       </c>
@@ -11978,7 +11982,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="143"/>
+      <c r="A17" s="119"/>
       <c r="B17" s="42">
         <v>46197</v>
       </c>
@@ -12040,7 +12044,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="144" t="s">
+      <c r="A20" s="120" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="35">
@@ -12066,7 +12070,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="145"/>
+      <c r="A21" s="121"/>
       <c r="B21" s="35">
         <v>46187</v>
       </c>
@@ -12094,7 +12098,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="145"/>
+      <c r="A22" s="121"/>
       <c r="B22" s="35">
         <v>46193</v>
       </c>
@@ -12122,7 +12126,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="145"/>
+      <c r="A23" s="121"/>
       <c r="B23" s="35">
         <v>46193</v>
       </c>
@@ -12150,7 +12154,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="145"/>
+      <c r="A24" s="121"/>
       <c r="B24" s="35">
         <v>46198</v>
       </c>
@@ -12178,7 +12182,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="146"/>
+      <c r="A25" s="122"/>
       <c r="B25" s="42">
         <v>46198</v>
       </c>
@@ -12240,7 +12244,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="135" t="s">
+      <c r="A28" s="111" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="35">
@@ -12266,7 +12270,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="136"/>
+      <c r="A29" s="112"/>
       <c r="B29" s="35">
         <v>46187</v>
       </c>
@@ -12294,7 +12298,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="136"/>
+      <c r="A30" s="112"/>
       <c r="B30" s="35">
         <v>46192</v>
       </c>
@@ -12322,7 +12326,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="136"/>
+      <c r="A31" s="112"/>
       <c r="B31" s="35">
         <v>46193</v>
       </c>
@@ -12350,7 +12354,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="136"/>
+      <c r="A32" s="112"/>
       <c r="B32" s="35">
         <v>46199</v>
       </c>
@@ -12378,7 +12382,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="137"/>
+      <c r="A33" s="113"/>
       <c r="B33" s="42">
         <v>46199</v>
       </c>
@@ -12440,7 +12444,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="117" t="s">
+      <c r="A36" s="129" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="35">
@@ -12470,7 +12474,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="118"/>
+      <c r="A37" s="130"/>
       <c r="B37" s="35">
         <v>46188</v>
       </c>
@@ -12498,7 +12502,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="118"/>
+      <c r="A38" s="130"/>
       <c r="B38" s="35">
         <v>46193</v>
       </c>
@@ -12526,7 +12530,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="118"/>
+      <c r="A39" s="130"/>
       <c r="B39" s="35">
         <v>46194</v>
       </c>
@@ -12554,7 +12558,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="118"/>
+      <c r="A40" s="130"/>
       <c r="B40" s="35">
         <v>46198</v>
       </c>
@@ -12582,7 +12586,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="119"/>
+      <c r="A41" s="131"/>
       <c r="B41" s="42">
         <v>46198</v>
       </c>
@@ -12644,7 +12648,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="120" t="s">
+      <c r="A44" s="132" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="35">
@@ -12674,7 +12678,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="121"/>
+      <c r="A45" s="133"/>
       <c r="B45" s="35">
         <v>46188</v>
       </c>
@@ -12702,7 +12706,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="121"/>
+      <c r="A46" s="133"/>
       <c r="B46" s="35">
         <v>46193</v>
       </c>
@@ -12730,7 +12734,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="121"/>
+      <c r="A47" s="133"/>
       <c r="B47" s="35">
         <v>46194</v>
       </c>
@@ -12758,7 +12762,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="121"/>
+      <c r="A48" s="133"/>
       <c r="B48" s="35">
         <v>46199</v>
       </c>
@@ -12786,7 +12790,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="122"/>
+      <c r="A49" s="134"/>
       <c r="B49" s="42">
         <v>46199</v>
       </c>
@@ -12848,7 +12852,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="123" t="s">
+      <c r="A52" s="135" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="35">
@@ -12878,7 +12882,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="124"/>
+      <c r="A53" s="136"/>
       <c r="B53" s="35">
         <v>46189</v>
       </c>
@@ -12900,13 +12904,13 @@
       <c r="H53" s="46" t="s">
         <v>44</v>
       </c>
-      <c r="J53" s="1" t="str">
+      <c r="J53" s="1">
         <f>IF(OR(Resultados!F53="",Resultados!G53=""),"",IF(AND(F53=Resultados!F53,G53=Resultados!G53),2,IF(((F53&gt;G53)=(Resultados!F53&gt;Resultados!G53))*((F53&lt;G53)=(Resultados!F53&lt;Resultados!G53)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="124"/>
+      <c r="A54" s="136"/>
       <c r="B54" s="35">
         <v>46194</v>
       </c>
@@ -12934,7 +12938,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="124"/>
+      <c r="A55" s="136"/>
       <c r="B55" s="35">
         <v>46195</v>
       </c>
@@ -12962,7 +12966,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="124"/>
+      <c r="A56" s="136"/>
       <c r="B56" s="35">
         <v>46200</v>
       </c>
@@ -12990,7 +12994,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="125"/>
+      <c r="A57" s="137"/>
       <c r="B57" s="42">
         <v>46200</v>
       </c>
@@ -13052,7 +13056,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="126" t="s">
+      <c r="A60" s="138" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="35">
@@ -13082,7 +13086,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="127"/>
+      <c r="A61" s="139"/>
       <c r="B61" s="35">
         <v>46189</v>
       </c>
@@ -13110,7 +13114,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="127"/>
+      <c r="A62" s="139"/>
       <c r="B62" s="35">
         <v>46194</v>
       </c>
@@ -13138,7 +13142,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="127"/>
+      <c r="A63" s="139"/>
       <c r="B63" s="35">
         <v>46195</v>
       </c>
@@ -13166,7 +13170,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="127"/>
+      <c r="A64" s="139"/>
       <c r="B64" s="35">
         <v>46200</v>
       </c>
@@ -13194,7 +13198,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="128"/>
+      <c r="A65" s="140"/>
       <c r="B65" s="42">
         <v>46200</v>
       </c>
@@ -13256,7 +13260,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="129" t="s">
+      <c r="A68" s="141" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="35">
@@ -13286,7 +13290,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="130"/>
+      <c r="A69" s="142"/>
       <c r="B69" s="35">
         <v>46190</v>
       </c>
@@ -13314,7 +13318,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="130"/>
+      <c r="A70" s="142"/>
       <c r="B70" s="35">
         <v>46195</v>
       </c>
@@ -13342,7 +13346,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="130"/>
+      <c r="A71" s="142"/>
       <c r="B71" s="35">
         <v>46196</v>
       </c>
@@ -13370,7 +13374,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="130"/>
+      <c r="A72" s="142"/>
       <c r="B72" s="35">
         <v>46199</v>
       </c>
@@ -13398,7 +13402,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="131"/>
+      <c r="A73" s="143"/>
       <c r="B73" s="42">
         <v>46199</v>
       </c>
@@ -13460,7 +13464,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="132" t="s">
+      <c r="A76" s="144" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="35">
@@ -13490,7 +13494,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="133"/>
+      <c r="A77" s="145"/>
       <c r="B77" s="35">
         <v>46190</v>
       </c>
@@ -13518,7 +13522,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="133"/>
+      <c r="A78" s="145"/>
       <c r="B78" s="35">
         <v>46195</v>
       </c>
@@ -13546,7 +13550,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="133"/>
+      <c r="A79" s="145"/>
       <c r="B79" s="35">
         <v>46196</v>
       </c>
@@ -13574,7 +13578,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="133"/>
+      <c r="A80" s="145"/>
       <c r="B80" s="35">
         <v>46201</v>
       </c>
@@ -13602,7 +13606,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="134"/>
+      <c r="A81" s="146"/>
       <c r="B81" s="42">
         <v>46201</v>
       </c>
@@ -13664,7 +13668,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="111" t="s">
+      <c r="A84" s="123" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="35">
@@ -13694,7 +13698,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="112"/>
+      <c r="A85" s="124"/>
       <c r="B85" s="35">
         <v>46191</v>
       </c>
@@ -13722,7 +13726,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="112"/>
+      <c r="A86" s="124"/>
       <c r="B86" s="35">
         <v>46196</v>
       </c>
@@ -13750,7 +13754,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="112"/>
+      <c r="A87" s="124"/>
       <c r="B87" s="35">
         <v>46197</v>
       </c>
@@ -13778,7 +13782,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="112"/>
+      <c r="A88" s="124"/>
       <c r="B88" s="35">
         <v>46201</v>
       </c>
@@ -13806,7 +13810,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="113"/>
+      <c r="A89" s="125"/>
       <c r="B89" s="42">
         <v>46201</v>
       </c>
@@ -13868,7 +13872,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="114" t="s">
+      <c r="A92" s="126" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="35">
@@ -13898,7 +13902,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="115"/>
+      <c r="A93" s="127"/>
       <c r="B93" s="35">
         <v>46191</v>
       </c>
@@ -13926,7 +13930,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="115"/>
+      <c r="A94" s="127"/>
       <c r="B94" s="35">
         <v>46196</v>
       </c>
@@ -13954,7 +13958,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="115"/>
+      <c r="A95" s="127"/>
       <c r="B95" s="35">
         <v>46197</v>
       </c>
@@ -13982,7 +13986,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="115"/>
+      <c r="A96" s="127"/>
       <c r="B96" s="35">
         <v>46200</v>
       </c>
@@ -14010,7 +14014,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="116"/>
+      <c r="A97" s="128"/>
       <c r="B97" s="42">
         <v>46200</v>
       </c>
@@ -14039,12 +14043,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A28:A33"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A4:A9"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="A20:A25"/>
     <mergeCell ref="A84:A89"/>
     <mergeCell ref="A92:A97"/>
     <mergeCell ref="A36:A41"/>
@@ -14053,6 +14051,12 @@
     <mergeCell ref="A60:A65"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="A76:A81"/>
+    <mergeCell ref="A28:A33"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:A9"/>
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="A20:A25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -14158,7 +14162,7 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -15388,9 +15392,9 @@
       <c r="H53" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="J53" s="1" t="str">
+      <c r="J53" s="1">
         <f>IF(OR(Resultados!F53="",Resultados!G53=""),"",IF(AND(F53=Resultados!F53,G53=Resultados!G53),2,IF(((F53&gt;G53)=(Resultados!F53&gt;Resultados!G53))*((F53&lt;G53)=(Resultados!F53&lt;Resultados!G53)),1,0)))</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -16527,12 +16531,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A28:A33"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A4:A9"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="A20:A25"/>
     <mergeCell ref="A84:A89"/>
     <mergeCell ref="A92:A97"/>
     <mergeCell ref="A36:A41"/>
@@ -16541,6 +16539,12 @@
     <mergeCell ref="A60:A65"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="A76:A81"/>
+    <mergeCell ref="A28:A33"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:A9"/>
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="A20:A25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -17876,9 +17880,9 @@
       <c r="H53" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="J53" s="1" t="str">
+      <c r="J53" s="1">
         <f>IF(OR(Resultados!F53="",Resultados!G53=""),"",IF(AND(F53=Resultados!F53,G53=Resultados!G53),2,IF(((F53&gt;G53)=(Resultados!F53&gt;Resultados!G53))*((F53&lt;G53)=(Resultados!F53&lt;Resultados!G53)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -19015,12 +19019,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A28:A33"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A4:A9"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="A20:A25"/>
     <mergeCell ref="A84:A89"/>
     <mergeCell ref="A92:A97"/>
     <mergeCell ref="A36:A41"/>
@@ -19029,6 +19027,12 @@
     <mergeCell ref="A60:A65"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="A76:A81"/>
+    <mergeCell ref="A28:A33"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:A9"/>
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="A20:A25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -20324,9 +20328,9 @@
       <c r="H53" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="J53" s="1" t="str">
+      <c r="J53" s="1">
         <f>IF(OR(Resultados!F53="",Resultados!G53=""),"",IF(AND(F53=Resultados!F53,G53=Resultados!G53),2,IF(((F53&gt;G53)=(Resultados!F53&gt;Resultados!G53))*((F53&lt;G53)=(Resultados!F53&lt;Resultados!G53)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -21367,12 +21371,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A28:A33"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A4:A9"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="A20:A25"/>
     <mergeCell ref="A84:A89"/>
     <mergeCell ref="A92:A97"/>
     <mergeCell ref="A36:A41"/>
@@ -21381,6 +21379,12 @@
     <mergeCell ref="A60:A65"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="A76:A81"/>
+    <mergeCell ref="A28:A33"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:A9"/>
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="A20:A25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -22716,9 +22720,9 @@
       <c r="H53" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="J53" s="1" t="str">
+      <c r="J53" s="1">
         <f>IF(OR(Resultados!F53="",Resultados!G53=""),"",IF(AND(F53=Resultados!F53,G53=Resultados!G53),2,IF(((F53&gt;G53)=(Resultados!F53&gt;Resultados!G53))*((F53&lt;G53)=(Resultados!F53&lt;Resultados!G53)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -23855,12 +23859,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A28:A33"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A4:A9"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="A20:A25"/>
     <mergeCell ref="A84:A89"/>
     <mergeCell ref="A92:A97"/>
     <mergeCell ref="A36:A41"/>
@@ -23869,6 +23867,12 @@
     <mergeCell ref="A60:A65"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="A76:A81"/>
+    <mergeCell ref="A28:A33"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:A9"/>
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="A20:A25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -25204,9 +25208,9 @@
       <c r="H53" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="J53" s="1" t="str">
+      <c r="J53" s="1">
         <f>IF(OR(Resultados!F53="",Resultados!G53=""),"",IF(AND(F53=Resultados!F53,G53=Resultados!G53),2,IF(((F53&gt;G53)=(Resultados!F53&gt;Resultados!G53))*((F53&lt;G53)=(Resultados!F53&lt;Resultados!G53)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -26343,12 +26347,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A28:A33"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A4:A9"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="A20:A25"/>
     <mergeCell ref="A84:A89"/>
     <mergeCell ref="A92:A97"/>
     <mergeCell ref="A36:A41"/>
@@ -26357,6 +26355,12 @@
     <mergeCell ref="A60:A65"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="A76:A81"/>
+    <mergeCell ref="A28:A33"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:A9"/>
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="A20:A25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -26566,20 +26570,20 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="7461ab22-4e70-4395-beb5-078d6ab567bf" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="7461ab22-4e70-4395-beb5-078d6ab567bf" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -26601,14 +26605,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5511D132-9333-423C-BAEC-48101CE7245F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7DE79FC7-1424-4D12-B735-3F81ACD8E888}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
@@ -26622,4 +26618,12 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5511D132-9333-423C-BAEC-48101CE7245F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/Quiniela.xlsx
+++ b/data/Quiniela.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cindy\Desktop\QuinielaMundial\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7ED3C1E-993C-4D3B-9852-589ED0D28698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B61D972A-375D-4215-9A91-FD08ADFD78DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{9503E40F-C0E1-49CE-B4EA-3C401754995E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9503E40F-C0E1-49CE-B4EA-3C401754995E}"/>
   </bookViews>
   <sheets>
     <sheet name="Resultados" sheetId="1" r:id="rId1"/>
@@ -475,7 +475,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="24">
+  <fills count="25">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -611,6 +611,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1001,7 +1007,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="147">
+  <cellXfs count="148">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1237,6 +1243,9 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="23" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="20" fillId="20" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1924,26 +1933,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="69" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="71"/>
+      <c r="A1" s="70" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="72"/>
     </row>
     <row r="2" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="72"/>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="74"/>
+      <c r="A2" s="73"/>
+      <c r="B2" s="74"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="75"/>
     </row>
     <row r="3" spans="1:8" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -1970,7 +1979,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="96" t="s">
+      <c r="A4" s="97" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -1996,7 +2005,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="97"/>
+      <c r="A5" s="98"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -2020,7 +2029,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="97"/>
+      <c r="A6" s="98"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -2040,7 +2049,7 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="97"/>
+      <c r="A7" s="98"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -2060,7 +2069,7 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="97"/>
+      <c r="A8" s="98"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -2080,7 +2089,7 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="98"/>
+      <c r="A9" s="99"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -2134,7 +2143,7 @@
       </c>
     </row>
     <row r="12" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="99" t="s">
+      <c r="A12" s="100" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -2160,7 +2169,7 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="100"/>
+      <c r="A13" s="101"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -2184,7 +2193,7 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="100"/>
+      <c r="A14" s="101"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -2204,7 +2213,7 @@
       </c>
     </row>
     <row r="15" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="100"/>
+      <c r="A15" s="101"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -2224,7 +2233,7 @@
       </c>
     </row>
     <row r="16" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="100"/>
+      <c r="A16" s="101"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -2244,7 +2253,7 @@
       </c>
     </row>
     <row r="17" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="101"/>
+      <c r="A17" s="102"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -2298,7 +2307,7 @@
       </c>
     </row>
     <row r="20" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="102" t="s">
+      <c r="A20" s="103" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -2324,7 +2333,7 @@
       </c>
     </row>
     <row r="21" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="103"/>
+      <c r="A21" s="104"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -2348,7 +2357,7 @@
       </c>
     </row>
     <row r="22" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="103"/>
+      <c r="A22" s="104"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -2368,7 +2377,7 @@
       </c>
     </row>
     <row r="23" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="103"/>
+      <c r="A23" s="104"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -2388,7 +2397,7 @@
       </c>
     </row>
     <row r="24" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="103"/>
+      <c r="A24" s="104"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -2408,7 +2417,7 @@
       </c>
     </row>
     <row r="25" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="104"/>
+      <c r="A25" s="105"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -2462,7 +2471,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="105" t="s">
+      <c r="A28" s="106" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -2488,7 +2497,7 @@
       </c>
     </row>
     <row r="29" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="106"/>
+      <c r="A29" s="107"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -2512,7 +2521,7 @@
       </c>
     </row>
     <row r="30" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="106"/>
+      <c r="A30" s="107"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -2532,7 +2541,7 @@
       </c>
     </row>
     <row r="31" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="106"/>
+      <c r="A31" s="107"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -2552,7 +2561,7 @@
       </c>
     </row>
     <row r="32" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="106"/>
+      <c r="A32" s="107"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -2572,7 +2581,7 @@
       </c>
     </row>
     <row r="33" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="107"/>
+      <c r="A33" s="108"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -2626,7 +2635,7 @@
       </c>
     </row>
     <row r="36" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="108" t="s">
+      <c r="A36" s="109" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -2652,7 +2661,7 @@
       </c>
     </row>
     <row r="37" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="109"/>
+      <c r="A37" s="110"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -2676,7 +2685,7 @@
       </c>
     </row>
     <row r="38" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="109"/>
+      <c r="A38" s="110"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -2696,7 +2705,7 @@
       </c>
     </row>
     <row r="39" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="109"/>
+      <c r="A39" s="110"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -2716,7 +2725,7 @@
       </c>
     </row>
     <row r="40" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="109"/>
+      <c r="A40" s="110"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -2736,7 +2745,7 @@
       </c>
     </row>
     <row r="41" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="110"/>
+      <c r="A41" s="111"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -2790,7 +2799,7 @@
       </c>
     </row>
     <row r="44" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="78" t="s">
+      <c r="A44" s="79" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -2816,7 +2825,7 @@
       </c>
     </row>
     <row r="45" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="79"/>
+      <c r="A45" s="80"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -2840,7 +2849,7 @@
       </c>
     </row>
     <row r="46" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="79"/>
+      <c r="A46" s="80"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -2860,7 +2869,7 @@
       </c>
     </row>
     <row r="47" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="79"/>
+      <c r="A47" s="80"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -2880,7 +2889,7 @@
       </c>
     </row>
     <row r="48" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="79"/>
+      <c r="A48" s="80"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -2900,7 +2909,7 @@
       </c>
     </row>
     <row r="49" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="80"/>
+      <c r="A49" s="81"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -2954,7 +2963,7 @@
       </c>
     </row>
     <row r="52" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="81" t="s">
+      <c r="A52" s="82" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -2980,7 +2989,7 @@
       </c>
     </row>
     <row r="53" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="82"/>
+      <c r="A53" s="83"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -2993,10 +3002,10 @@
       <c r="E53" s="61" t="s">
         <v>43</v>
       </c>
-      <c r="F53" s="26">
-        <v>2</v>
-      </c>
-      <c r="G53" s="26">
+      <c r="F53" s="63">
+        <v>2</v>
+      </c>
+      <c r="G53" s="63">
         <v>2</v>
       </c>
       <c r="H53" s="61" t="s">
@@ -3004,7 +3013,7 @@
       </c>
     </row>
     <row r="54" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="82"/>
+      <c r="A54" s="83"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -3024,7 +3033,7 @@
       </c>
     </row>
     <row r="55" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="82"/>
+      <c r="A55" s="83"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -3044,7 +3053,7 @@
       </c>
     </row>
     <row r="56" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="82"/>
+      <c r="A56" s="83"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -3064,7 +3073,7 @@
       </c>
     </row>
     <row r="57" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="83"/>
+      <c r="A57" s="84"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -3118,7 +3127,7 @@
       </c>
     </row>
     <row r="60" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="84" t="s">
+      <c r="A60" s="85" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -3144,7 +3153,7 @@
       </c>
     </row>
     <row r="61" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="85"/>
+      <c r="A61" s="86"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -3168,7 +3177,7 @@
       </c>
     </row>
     <row r="62" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="85"/>
+      <c r="A62" s="86"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -3188,7 +3197,7 @@
       </c>
     </row>
     <row r="63" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="85"/>
+      <c r="A63" s="86"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -3208,7 +3217,7 @@
       </c>
     </row>
     <row r="64" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="85"/>
+      <c r="A64" s="86"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -3228,7 +3237,7 @@
       </c>
     </row>
     <row r="65" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="86"/>
+      <c r="A65" s="87"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -3282,7 +3291,7 @@
       </c>
     </row>
     <row r="68" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="87" t="s">
+      <c r="A68" s="88" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -3294,17 +3303,21 @@
       <c r="D68" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="E68" s="10" t="s">
+      <c r="E68" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="F68" s="26"/>
-      <c r="G68" s="26"/>
+      <c r="F68" s="62">
+        <v>3</v>
+      </c>
+      <c r="G68" s="62">
+        <v>1</v>
+      </c>
       <c r="H68" s="21" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="88"/>
+      <c r="A69" s="89"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -3317,14 +3330,18 @@
       <c r="E69" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="F69" s="26"/>
-      <c r="G69" s="26"/>
-      <c r="H69" s="21" t="s">
+      <c r="F69" s="62">
+        <v>1</v>
+      </c>
+      <c r="G69" s="62">
+        <v>4</v>
+      </c>
+      <c r="H69" s="27" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="88"/>
+      <c r="A70" s="89"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -3344,7 +3361,7 @@
       </c>
     </row>
     <row r="71" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="88"/>
+      <c r="A71" s="89"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -3364,7 +3381,7 @@
       </c>
     </row>
     <row r="72" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="88"/>
+      <c r="A72" s="89"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -3384,7 +3401,7 @@
       </c>
     </row>
     <row r="73" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="89"/>
+      <c r="A73" s="90"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -3438,7 +3455,7 @@
       </c>
     </row>
     <row r="76" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="90" t="s">
+      <c r="A76" s="91" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -3450,17 +3467,21 @@
       <c r="D76" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="E76" s="10" t="s">
+      <c r="E76" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="F76" s="26"/>
-      <c r="G76" s="26"/>
+      <c r="F76" s="62">
+        <v>3</v>
+      </c>
+      <c r="G76" s="62">
+        <v>0</v>
+      </c>
       <c r="H76" s="21" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="91"/>
+      <c r="A77" s="92"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -3480,7 +3501,7 @@
       </c>
     </row>
     <row r="78" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="91"/>
+      <c r="A78" s="92"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -3500,7 +3521,7 @@
       </c>
     </row>
     <row r="79" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="91"/>
+      <c r="A79" s="92"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -3520,7 +3541,7 @@
       </c>
     </row>
     <row r="80" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="91"/>
+      <c r="A80" s="92"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -3540,7 +3561,7 @@
       </c>
     </row>
     <row r="81" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="92"/>
+      <c r="A81" s="93"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -3594,7 +3615,7 @@
       </c>
     </row>
     <row r="84" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="93" t="s">
+      <c r="A84" s="94" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -3616,7 +3637,7 @@
       </c>
     </row>
     <row r="85" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="94"/>
+      <c r="A85" s="95"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -3636,7 +3657,7 @@
       </c>
     </row>
     <row r="86" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="94"/>
+      <c r="A86" s="95"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -3656,7 +3677,7 @@
       </c>
     </row>
     <row r="87" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="94"/>
+      <c r="A87" s="95"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -3676,7 +3697,7 @@
       </c>
     </row>
     <row r="88" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="94"/>
+      <c r="A88" s="95"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -3696,7 +3717,7 @@
       </c>
     </row>
     <row r="89" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="95"/>
+      <c r="A89" s="96"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -3750,7 +3771,7 @@
       </c>
     </row>
     <row r="92" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="75" t="s">
+      <c r="A92" s="76" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -3772,7 +3793,7 @@
       </c>
     </row>
     <row r="93" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="76"/>
+      <c r="A93" s="77"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -3792,7 +3813,7 @@
       </c>
     </row>
     <row r="94" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="76"/>
+      <c r="A94" s="77"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -3812,7 +3833,7 @@
       </c>
     </row>
     <row r="95" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="76"/>
+      <c r="A95" s="77"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -3832,7 +3853,7 @@
       </c>
     </row>
     <row r="96" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="76"/>
+      <c r="A96" s="77"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -3852,7 +3873,7 @@
       </c>
     </row>
     <row r="97" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="77"/>
+      <c r="A97" s="78"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -3912,26 +3933,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="69" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="71"/>
+      <c r="A1" s="70" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="72"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="72"/>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="74"/>
+      <c r="A2" s="73"/>
+      <c r="B2" s="74"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="75"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -3964,7 +3985,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="96" t="s">
+      <c r="A4" s="97" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -3990,11 +4011,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="97"/>
+      <c r="A5" s="98"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -4018,7 +4039,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="97"/>
+      <c r="A6" s="98"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -4046,7 +4067,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="97"/>
+      <c r="A7" s="98"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -4074,7 +4095,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="97"/>
+      <c r="A8" s="98"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -4102,7 +4123,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="98"/>
+      <c r="A9" s="99"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -4164,7 +4185,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="99" t="s">
+      <c r="A12" s="100" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -4190,7 +4211,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="100"/>
+      <c r="A13" s="101"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -4214,7 +4235,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="100"/>
+      <c r="A14" s="101"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -4242,7 +4263,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="100"/>
+      <c r="A15" s="101"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -4270,7 +4291,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="100"/>
+      <c r="A16" s="101"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -4298,7 +4319,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="101"/>
+      <c r="A17" s="102"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -4360,7 +4381,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="102" t="s">
+      <c r="A20" s="103" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -4386,7 +4407,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="103"/>
+      <c r="A21" s="104"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -4414,7 +4435,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="103"/>
+      <c r="A22" s="104"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -4442,7 +4463,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="103"/>
+      <c r="A23" s="104"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -4470,7 +4491,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="103"/>
+      <c r="A24" s="104"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -4498,7 +4519,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="104"/>
+      <c r="A25" s="105"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -4560,7 +4581,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="105" t="s">
+      <c r="A28" s="106" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -4586,7 +4607,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="106"/>
+      <c r="A29" s="107"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -4614,7 +4635,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="106"/>
+      <c r="A30" s="107"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -4642,7 +4663,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="106"/>
+      <c r="A31" s="107"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -4670,7 +4691,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="106"/>
+      <c r="A32" s="107"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -4698,7 +4719,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="107"/>
+      <c r="A33" s="108"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -4760,7 +4781,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="108" t="s">
+      <c r="A36" s="109" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -4790,7 +4811,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="109"/>
+      <c r="A37" s="110"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -4818,7 +4839,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="109"/>
+      <c r="A38" s="110"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -4846,7 +4867,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="109"/>
+      <c r="A39" s="110"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -4874,7 +4895,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="109"/>
+      <c r="A40" s="110"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -4902,7 +4923,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="110"/>
+      <c r="A41" s="111"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -4964,7 +4985,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="78" t="s">
+      <c r="A44" s="79" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -4994,7 +5015,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="79"/>
+      <c r="A45" s="80"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -5022,7 +5043,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="79"/>
+      <c r="A46" s="80"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -5050,7 +5071,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="79"/>
+      <c r="A47" s="80"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -5078,7 +5099,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="79"/>
+      <c r="A48" s="80"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -5106,7 +5127,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="80"/>
+      <c r="A49" s="81"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -5168,7 +5189,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="81" t="s">
+      <c r="A52" s="82" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -5198,7 +5219,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="82"/>
+      <c r="A53" s="83"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -5226,7 +5247,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="82"/>
+      <c r="A54" s="83"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -5254,7 +5275,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="82"/>
+      <c r="A55" s="83"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -5282,7 +5303,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="82"/>
+      <c r="A56" s="83"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -5310,7 +5331,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="83"/>
+      <c r="A57" s="84"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -5372,7 +5393,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="84" t="s">
+      <c r="A60" s="85" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -5402,7 +5423,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="85"/>
+      <c r="A61" s="86"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -5430,7 +5451,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="85"/>
+      <c r="A62" s="86"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -5458,7 +5479,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="85"/>
+      <c r="A63" s="86"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -5486,7 +5507,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="85"/>
+      <c r="A64" s="86"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -5514,7 +5535,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="86"/>
+      <c r="A65" s="87"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -5576,7 +5597,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="87" t="s">
+      <c r="A68" s="88" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -5600,13 +5621,13 @@
       <c r="H68" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="J68" s="1" t="str">
+      <c r="J68" s="1">
         <f>IF(OR(Resultados!F68="",Resultados!G68=""),"",IF(AND(F68=Resultados!F68,G68=Resultados!G68),2,IF(((F68&gt;G68)=(Resultados!F68&gt;Resultados!G68))*((F68&lt;G68)=(Resultados!F68&lt;Resultados!G68)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="88"/>
+      <c r="A69" s="89"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -5628,13 +5649,13 @@
       <c r="H69" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="J69" s="1" t="str">
+      <c r="J69" s="1">
         <f>IF(OR(Resultados!F69="",Resultados!G69=""),"",IF(AND(F69=Resultados!F69,G69=Resultados!G69),2,IF(((F69&gt;G69)=(Resultados!F69&gt;Resultados!G69))*((F69&lt;G69)=(Resultados!F69&lt;Resultados!G69)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="88"/>
+      <c r="A70" s="89"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -5662,7 +5683,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="88"/>
+      <c r="A71" s="89"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -5690,7 +5711,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="88"/>
+      <c r="A72" s="89"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -5718,7 +5739,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="89"/>
+      <c r="A73" s="90"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -5780,7 +5801,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="90" t="s">
+      <c r="A76" s="91" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -5804,13 +5825,13 @@
       <c r="H76" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="J76" s="1" t="str">
+      <c r="J76" s="1">
         <f>IF(OR(Resultados!F76="",Resultados!G76=""),"",IF(AND(F76=Resultados!F76,G76=Resultados!G76),2,IF(((F76&gt;G76)=(Resultados!F76&gt;Resultados!G76))*((F76&lt;G76)=(Resultados!F76&lt;Resultados!G76)),1,0)))</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="91"/>
+      <c r="A77" s="92"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -5838,7 +5859,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="91"/>
+      <c r="A78" s="92"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -5866,7 +5887,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="91"/>
+      <c r="A79" s="92"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -5894,7 +5915,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="91"/>
+      <c r="A80" s="92"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -5922,7 +5943,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="92"/>
+      <c r="A81" s="93"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -5984,7 +6005,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="93" t="s">
+      <c r="A84" s="94" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -6014,7 +6035,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="94"/>
+      <c r="A85" s="95"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -6042,7 +6063,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="94"/>
+      <c r="A86" s="95"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -6070,7 +6091,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="94"/>
+      <c r="A87" s="95"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -6098,7 +6119,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="94"/>
+      <c r="A88" s="95"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -6126,7 +6147,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="95"/>
+      <c r="A89" s="96"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -6188,7 +6209,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="75" t="s">
+      <c r="A92" s="76" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -6218,7 +6239,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="76"/>
+      <c r="A93" s="77"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -6246,7 +6267,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="76"/>
+      <c r="A94" s="77"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -6274,7 +6295,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="76"/>
+      <c r="A95" s="77"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -6302,7 +6323,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="76"/>
+      <c r="A96" s="77"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -6330,7 +6351,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="77"/>
+      <c r="A97" s="78"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -6400,26 +6421,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="69" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="71"/>
+      <c r="A1" s="70" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="72"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="72"/>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="74"/>
+      <c r="A2" s="73"/>
+      <c r="B2" s="74"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="75"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -6452,7 +6473,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="96" t="s">
+      <c r="A4" s="97" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -6478,11 +6499,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="97"/>
+      <c r="A5" s="98"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -6506,7 +6527,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="97"/>
+      <c r="A6" s="98"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -6534,7 +6555,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="97"/>
+      <c r="A7" s="98"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -6562,7 +6583,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="97"/>
+      <c r="A8" s="98"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -6590,7 +6611,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="98"/>
+      <c r="A9" s="99"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -6652,7 +6673,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="99" t="s">
+      <c r="A12" s="100" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -6678,7 +6699,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="100"/>
+      <c r="A13" s="101"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -6702,7 +6723,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="100"/>
+      <c r="A14" s="101"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -6730,7 +6751,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="100"/>
+      <c r="A15" s="101"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -6758,7 +6779,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="100"/>
+      <c r="A16" s="101"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -6786,7 +6807,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="101"/>
+      <c r="A17" s="102"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -6848,7 +6869,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="102" t="s">
+      <c r="A20" s="103" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -6874,7 +6895,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="103"/>
+      <c r="A21" s="104"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -6902,7 +6923,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="103"/>
+      <c r="A22" s="104"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -6930,7 +6951,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="103"/>
+      <c r="A23" s="104"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -6958,7 +6979,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="103"/>
+      <c r="A24" s="104"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -6986,7 +7007,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="104"/>
+      <c r="A25" s="105"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -7048,7 +7069,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="105" t="s">
+      <c r="A28" s="106" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -7074,7 +7095,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="106"/>
+      <c r="A29" s="107"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -7102,7 +7123,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="106"/>
+      <c r="A30" s="107"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -7130,7 +7151,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="106"/>
+      <c r="A31" s="107"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -7158,7 +7179,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="106"/>
+      <c r="A32" s="107"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -7186,7 +7207,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="107"/>
+      <c r="A33" s="108"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -7248,7 +7269,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="108" t="s">
+      <c r="A36" s="109" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -7278,7 +7299,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="109"/>
+      <c r="A37" s="110"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -7306,7 +7327,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="109"/>
+      <c r="A38" s="110"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -7334,7 +7355,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="109"/>
+      <c r="A39" s="110"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -7362,7 +7383,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="109"/>
+      <c r="A40" s="110"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -7390,7 +7411,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="110"/>
+      <c r="A41" s="111"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -7452,7 +7473,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="78" t="s">
+      <c r="A44" s="79" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -7482,7 +7503,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="79"/>
+      <c r="A45" s="80"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -7510,7 +7531,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="79"/>
+      <c r="A46" s="80"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -7538,7 +7559,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="79"/>
+      <c r="A47" s="80"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -7566,7 +7587,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="79"/>
+      <c r="A48" s="80"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -7594,7 +7615,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="80"/>
+      <c r="A49" s="81"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -7656,7 +7677,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="81" t="s">
+      <c r="A52" s="82" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -7686,7 +7707,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="82"/>
+      <c r="A53" s="83"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -7714,7 +7735,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="82"/>
+      <c r="A54" s="83"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -7742,7 +7763,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="82"/>
+      <c r="A55" s="83"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -7770,7 +7791,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="82"/>
+      <c r="A56" s="83"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -7798,7 +7819,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="83"/>
+      <c r="A57" s="84"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -7860,7 +7881,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="84" t="s">
+      <c r="A60" s="85" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -7890,7 +7911,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="85"/>
+      <c r="A61" s="86"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -7918,7 +7939,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="85"/>
+      <c r="A62" s="86"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -7946,7 +7967,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="85"/>
+      <c r="A63" s="86"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -7974,7 +7995,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="85"/>
+      <c r="A64" s="86"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -8002,7 +8023,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="86"/>
+      <c r="A65" s="87"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -8064,7 +8085,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="87" t="s">
+      <c r="A68" s="88" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -8088,13 +8109,13 @@
       <c r="H68" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="J68" s="1" t="str">
+      <c r="J68" s="1">
         <f>IF(OR(Resultados!F68="",Resultados!G68=""),"",IF(AND(F68=Resultados!F68,G68=Resultados!G68),2,IF(((F68&gt;G68)=(Resultados!F68&gt;Resultados!G68))*((F68&lt;G68)=(Resultados!F68&lt;Resultados!G68)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="88"/>
+      <c r="A69" s="89"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -8116,13 +8137,13 @@
       <c r="H69" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="J69" s="1" t="str">
+      <c r="J69" s="1">
         <f>IF(OR(Resultados!F69="",Resultados!G69=""),"",IF(AND(F69=Resultados!F69,G69=Resultados!G69),2,IF(((F69&gt;G69)=(Resultados!F69&gt;Resultados!G69))*((F69&lt;G69)=(Resultados!F69&lt;Resultados!G69)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="88"/>
+      <c r="A70" s="89"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -8150,7 +8171,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="88"/>
+      <c r="A71" s="89"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -8178,7 +8199,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="88"/>
+      <c r="A72" s="89"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -8206,7 +8227,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="89"/>
+      <c r="A73" s="90"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -8268,7 +8289,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="90" t="s">
+      <c r="A76" s="91" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -8292,13 +8313,13 @@
       <c r="H76" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="J76" s="1" t="str">
+      <c r="J76" s="1">
         <f>IF(OR(Resultados!F76="",Resultados!G76=""),"",IF(AND(F76=Resultados!F76,G76=Resultados!G76),2,IF(((F76&gt;G76)=(Resultados!F76&gt;Resultados!G76))*((F76&lt;G76)=(Resultados!F76&lt;Resultados!G76)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="91"/>
+      <c r="A77" s="92"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -8326,7 +8347,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="91"/>
+      <c r="A78" s="92"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -8354,7 +8375,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="91"/>
+      <c r="A79" s="92"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -8382,7 +8403,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="91"/>
+      <c r="A80" s="92"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -8410,7 +8431,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="92"/>
+      <c r="A81" s="93"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -8472,7 +8493,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="93" t="s">
+      <c r="A84" s="94" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -8502,7 +8523,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="94"/>
+      <c r="A85" s="95"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -8530,7 +8551,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="94"/>
+      <c r="A86" s="95"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -8558,7 +8579,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="94"/>
+      <c r="A87" s="95"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -8586,7 +8607,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="94"/>
+      <c r="A88" s="95"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -8614,7 +8635,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="95"/>
+      <c r="A89" s="96"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -8676,7 +8697,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="75" t="s">
+      <c r="A92" s="76" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -8706,7 +8727,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="76"/>
+      <c r="A93" s="77"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -8734,7 +8755,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="76"/>
+      <c r="A94" s="77"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -8762,7 +8783,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="76"/>
+      <c r="A95" s="77"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -8790,7 +8811,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="76"/>
+      <c r="A96" s="77"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -8818,7 +8839,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="77"/>
+      <c r="A97" s="78"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -8883,18 +8904,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D1" s="63" t="s">
+      <c r="D1" s="64" t="s">
         <v>74</v>
       </c>
-      <c r="E1" s="64"/>
-      <c r="F1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="66"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D2" s="66" t="s">
+      <c r="D2" s="67" t="s">
         <v>75</v>
       </c>
-      <c r="E2" s="67"/>
-      <c r="F2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="69"/>
     </row>
     <row r="4" spans="1:6" s="29" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="57" t="s">
@@ -8919,7 +8940,7 @@
       </c>
       <c r="B5" s="58">
         <f>Cindy!L4</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D5" s="59">
         <v>1</v>
@@ -8929,7 +8950,7 @@
         <v>Lennon</v>
       </c>
       <c r="F5" s="59">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -8938,16 +8959,16 @@
       </c>
       <c r="B6" s="58">
         <f>Wendy!L4</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D6" s="55">
         <v>2</v>
       </c>
       <c r="E6" s="55" t="str">
-        <v>Erik</v>
+        <v>Wendy</v>
       </c>
       <c r="F6" s="55">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -8956,16 +8977,16 @@
       </c>
       <c r="B7" s="58">
         <f>Jimmy!L4</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D7" s="56">
         <v>3</v>
       </c>
       <c r="E7" s="56" t="str">
-        <v>Yulian</v>
+        <v>Erik</v>
       </c>
       <c r="F7" s="56">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -8974,16 +8995,16 @@
       </c>
       <c r="B8" s="58">
         <f>Erick!L4</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D8" s="28">
         <v>4</v>
       </c>
       <c r="E8" s="28" t="str">
-        <v>Wendy</v>
+        <v>Yulian</v>
       </c>
       <c r="F8" s="28">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -8992,7 +9013,7 @@
       </c>
       <c r="B9" s="58">
         <f>Erik!L4</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D9" s="28">
         <v>5</v>
@@ -9001,7 +9022,7 @@
         <v>Packy</v>
       </c>
       <c r="F9" s="28">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -9010,7 +9031,7 @@
       </c>
       <c r="B10" s="58">
         <f>Lennon!L4</f>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D10" s="28">
         <v>6</v>
@@ -9019,7 +9040,7 @@
         <v>Bere</v>
       </c>
       <c r="F10" s="28">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -9028,7 +9049,7 @@
       </c>
       <c r="B11" s="58">
         <f>Yulian!L4</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D11" s="28">
         <v>7</v>
@@ -9037,7 +9058,7 @@
         <v>Jimmy</v>
       </c>
       <c r="F11" s="28">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -9046,16 +9067,16 @@
       </c>
       <c r="B12" s="58">
         <f>Packy!L4</f>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D12" s="28">
         <v>8</v>
       </c>
       <c r="E12" s="28" t="str">
-        <v>Erick</v>
+        <v>Cindy</v>
       </c>
       <c r="F12" s="28">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -9064,16 +9085,16 @@
       </c>
       <c r="B13" s="58">
         <f>Bere!L4</f>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D13" s="28">
         <v>9</v>
       </c>
       <c r="E13" s="28" t="str">
-        <v>Cindy</v>
+        <v>Erick</v>
       </c>
       <c r="F13" s="28">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -9107,26 +9128,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="69" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="71"/>
+      <c r="A1" s="70" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="72"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="72"/>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="74"/>
+      <c r="A2" s="73"/>
+      <c r="B2" s="74"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="75"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="31"/>
@@ -9159,7 +9180,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="114" t="s">
+      <c r="A4" s="115" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="35">
@@ -9185,11 +9206,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="115"/>
+      <c r="A5" s="116"/>
       <c r="B5" s="35">
         <v>46185</v>
       </c>
@@ -9213,7 +9234,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="115"/>
+      <c r="A6" s="116"/>
       <c r="B6" s="35">
         <v>46191</v>
       </c>
@@ -9241,7 +9262,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="115"/>
+      <c r="A7" s="116"/>
       <c r="B7" s="35">
         <v>46192</v>
       </c>
@@ -9269,7 +9290,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="115"/>
+      <c r="A8" s="116"/>
       <c r="B8" s="35">
         <v>46198</v>
       </c>
@@ -9297,7 +9318,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="116"/>
+      <c r="A9" s="117"/>
       <c r="B9" s="42">
         <v>46198</v>
       </c>
@@ -9359,7 +9380,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="117" t="s">
+      <c r="A12" s="118" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="35">
@@ -9385,7 +9406,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="118"/>
+      <c r="A13" s="119"/>
       <c r="B13" s="35">
         <v>46186</v>
       </c>
@@ -9409,7 +9430,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="118"/>
+      <c r="A14" s="119"/>
       <c r="B14" s="35">
         <v>46191</v>
       </c>
@@ -9437,7 +9458,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="118"/>
+      <c r="A15" s="119"/>
       <c r="B15" s="35">
         <v>46192</v>
       </c>
@@ -9465,7 +9486,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="118"/>
+      <c r="A16" s="119"/>
       <c r="B16" s="35">
         <v>46197</v>
       </c>
@@ -9493,7 +9514,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="119"/>
+      <c r="A17" s="120"/>
       <c r="B17" s="42">
         <v>46197</v>
       </c>
@@ -9555,7 +9576,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="120" t="s">
+      <c r="A20" s="121" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="35">
@@ -9581,7 +9602,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="121"/>
+      <c r="A21" s="122"/>
       <c r="B21" s="35">
         <v>46187</v>
       </c>
@@ -9609,7 +9630,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="121"/>
+      <c r="A22" s="122"/>
       <c r="B22" s="35">
         <v>46193</v>
       </c>
@@ -9637,7 +9658,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="121"/>
+      <c r="A23" s="122"/>
       <c r="B23" s="35">
         <v>46193</v>
       </c>
@@ -9665,7 +9686,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="121"/>
+      <c r="A24" s="122"/>
       <c r="B24" s="35">
         <v>46198</v>
       </c>
@@ -9693,7 +9714,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="122"/>
+      <c r="A25" s="123"/>
       <c r="B25" s="42">
         <v>46198</v>
       </c>
@@ -9755,7 +9776,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="111" t="s">
+      <c r="A28" s="112" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="35">
@@ -9781,7 +9802,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="112"/>
+      <c r="A29" s="113"/>
       <c r="B29" s="35">
         <v>46187</v>
       </c>
@@ -9809,7 +9830,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="112"/>
+      <c r="A30" s="113"/>
       <c r="B30" s="35">
         <v>46192</v>
       </c>
@@ -9837,7 +9858,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="112"/>
+      <c r="A31" s="113"/>
       <c r="B31" s="35">
         <v>46193</v>
       </c>
@@ -9865,7 +9886,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="112"/>
+      <c r="A32" s="113"/>
       <c r="B32" s="35">
         <v>46199</v>
       </c>
@@ -9893,7 +9914,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="113"/>
+      <c r="A33" s="114"/>
       <c r="B33" s="42">
         <v>46199</v>
       </c>
@@ -9955,7 +9976,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="129" t="s">
+      <c r="A36" s="130" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="35">
@@ -9985,7 +10006,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="130"/>
+      <c r="A37" s="131"/>
       <c r="B37" s="35">
         <v>46188</v>
       </c>
@@ -10013,7 +10034,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="130"/>
+      <c r="A38" s="131"/>
       <c r="B38" s="35">
         <v>46193</v>
       </c>
@@ -10041,7 +10062,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="130"/>
+      <c r="A39" s="131"/>
       <c r="B39" s="35">
         <v>46194</v>
       </c>
@@ -10069,7 +10090,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="130"/>
+      <c r="A40" s="131"/>
       <c r="B40" s="35">
         <v>46198</v>
       </c>
@@ -10097,7 +10118,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="131"/>
+      <c r="A41" s="132"/>
       <c r="B41" s="42">
         <v>46198</v>
       </c>
@@ -10159,7 +10180,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="132" t="s">
+      <c r="A44" s="133" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="35">
@@ -10189,7 +10210,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="133"/>
+      <c r="A45" s="134"/>
       <c r="B45" s="35">
         <v>46188</v>
       </c>
@@ -10217,7 +10238,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="133"/>
+      <c r="A46" s="134"/>
       <c r="B46" s="35">
         <v>46193</v>
       </c>
@@ -10245,7 +10266,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="133"/>
+      <c r="A47" s="134"/>
       <c r="B47" s="35">
         <v>46194</v>
       </c>
@@ -10273,7 +10294,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="133"/>
+      <c r="A48" s="134"/>
       <c r="B48" s="35">
         <v>46199</v>
       </c>
@@ -10301,7 +10322,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="134"/>
+      <c r="A49" s="135"/>
       <c r="B49" s="42">
         <v>46199</v>
       </c>
@@ -10363,7 +10384,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="135" t="s">
+      <c r="A52" s="136" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="35">
@@ -10393,7 +10414,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="136"/>
+      <c r="A53" s="137"/>
       <c r="B53" s="35">
         <v>46189</v>
       </c>
@@ -10421,7 +10442,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="136"/>
+      <c r="A54" s="137"/>
       <c r="B54" s="35">
         <v>46194</v>
       </c>
@@ -10449,7 +10470,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="136"/>
+      <c r="A55" s="137"/>
       <c r="B55" s="35">
         <v>46195</v>
       </c>
@@ -10477,7 +10498,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="136"/>
+      <c r="A56" s="137"/>
       <c r="B56" s="35">
         <v>46200</v>
       </c>
@@ -10505,7 +10526,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="137"/>
+      <c r="A57" s="138"/>
       <c r="B57" s="42">
         <v>46200</v>
       </c>
@@ -10567,7 +10588,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="138" t="s">
+      <c r="A60" s="139" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="35">
@@ -10597,7 +10618,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="139"/>
+      <c r="A61" s="140"/>
       <c r="B61" s="35">
         <v>46189</v>
       </c>
@@ -10625,7 +10646,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="139"/>
+      <c r="A62" s="140"/>
       <c r="B62" s="35">
         <v>46194</v>
       </c>
@@ -10653,7 +10674,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="139"/>
+      <c r="A63" s="140"/>
       <c r="B63" s="35">
         <v>46195</v>
       </c>
@@ -10681,7 +10702,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="139"/>
+      <c r="A64" s="140"/>
       <c r="B64" s="35">
         <v>46200</v>
       </c>
@@ -10709,7 +10730,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="140"/>
+      <c r="A65" s="141"/>
       <c r="B65" s="42">
         <v>46200</v>
       </c>
@@ -10771,7 +10792,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="141" t="s">
+      <c r="A68" s="142" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="35">
@@ -10795,13 +10816,13 @@
       <c r="H68" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="J68" s="1" t="str">
+      <c r="J68" s="1">
         <f>IF(OR(Resultados!F68="",Resultados!G68=""),"",IF(AND(F68=Resultados!F68,G68=Resultados!G68),2,IF(((F68&gt;G68)=(Resultados!F68&gt;Resultados!G68))*((F68&lt;G68)=(Resultados!F68&lt;Resultados!G68)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="142"/>
+      <c r="A69" s="143"/>
       <c r="B69" s="35">
         <v>46190</v>
       </c>
@@ -10823,13 +10844,13 @@
       <c r="H69" s="46" t="s">
         <v>54</v>
       </c>
-      <c r="J69" s="1" t="str">
+      <c r="J69" s="1">
         <f>IF(OR(Resultados!F69="",Resultados!G69=""),"",IF(AND(F69=Resultados!F69,G69=Resultados!G69),2,IF(((F69&gt;G69)=(Resultados!F69&gt;Resultados!G69))*((F69&lt;G69)=(Resultados!F69&lt;Resultados!G69)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="142"/>
+      <c r="A70" s="143"/>
       <c r="B70" s="35">
         <v>46195</v>
       </c>
@@ -10857,7 +10878,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="142"/>
+      <c r="A71" s="143"/>
       <c r="B71" s="35">
         <v>46196</v>
       </c>
@@ -10885,7 +10906,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="142"/>
+      <c r="A72" s="143"/>
       <c r="B72" s="35">
         <v>46199</v>
       </c>
@@ -10913,7 +10934,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="143"/>
+      <c r="A73" s="144"/>
       <c r="B73" s="42">
         <v>46199</v>
       </c>
@@ -10975,7 +10996,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="144" t="s">
+      <c r="A76" s="145" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="35">
@@ -10999,13 +11020,13 @@
       <c r="H76" s="46" t="s">
         <v>57</v>
       </c>
-      <c r="J76" s="1" t="str">
+      <c r="J76" s="1">
         <f>IF(OR(Resultados!F76="",Resultados!G76=""),"",IF(AND(F76=Resultados!F76,G76=Resultados!G76),2,IF(((F76&gt;G76)=(Resultados!F76&gt;Resultados!G76))*((F76&lt;G76)=(Resultados!F76&lt;Resultados!G76)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="145"/>
+      <c r="A77" s="146"/>
       <c r="B77" s="35">
         <v>46190</v>
       </c>
@@ -11033,7 +11054,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="145"/>
+      <c r="A78" s="146"/>
       <c r="B78" s="35">
         <v>46195</v>
       </c>
@@ -11061,7 +11082,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="145"/>
+      <c r="A79" s="146"/>
       <c r="B79" s="35">
         <v>46196</v>
       </c>
@@ -11089,7 +11110,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="145"/>
+      <c r="A80" s="146"/>
       <c r="B80" s="35">
         <v>46201</v>
       </c>
@@ -11117,7 +11138,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="146"/>
+      <c r="A81" s="147"/>
       <c r="B81" s="42">
         <v>46201</v>
       </c>
@@ -11179,7 +11200,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="123" t="s">
+      <c r="A84" s="124" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="35">
@@ -11209,7 +11230,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="124"/>
+      <c r="A85" s="125"/>
       <c r="B85" s="35">
         <v>46191</v>
       </c>
@@ -11237,7 +11258,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="124"/>
+      <c r="A86" s="125"/>
       <c r="B86" s="35">
         <v>46196</v>
       </c>
@@ -11265,7 +11286,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="124"/>
+      <c r="A87" s="125"/>
       <c r="B87" s="35">
         <v>46197</v>
       </c>
@@ -11293,7 +11314,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="124"/>
+      <c r="A88" s="125"/>
       <c r="B88" s="35">
         <v>46201</v>
       </c>
@@ -11321,7 +11342,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="125"/>
+      <c r="A89" s="126"/>
       <c r="B89" s="42">
         <v>46201</v>
       </c>
@@ -11383,7 +11404,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="126" t="s">
+      <c r="A92" s="127" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="35">
@@ -11413,7 +11434,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="127"/>
+      <c r="A93" s="128"/>
       <c r="B93" s="35">
         <v>46191</v>
       </c>
@@ -11441,7 +11462,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="127"/>
+      <c r="A94" s="128"/>
       <c r="B94" s="35">
         <v>46196</v>
       </c>
@@ -11469,7 +11490,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="127"/>
+      <c r="A95" s="128"/>
       <c r="B95" s="35">
         <v>46197</v>
       </c>
@@ -11497,7 +11518,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="127"/>
+      <c r="A96" s="128"/>
       <c r="B96" s="35">
         <v>46200</v>
       </c>
@@ -11525,7 +11546,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="128"/>
+      <c r="A97" s="129"/>
       <c r="B97" s="42">
         <v>46200</v>
       </c>
@@ -11596,26 +11617,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="69" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="71"/>
+      <c r="A1" s="70" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="72"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="72"/>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="74"/>
+      <c r="A2" s="73"/>
+      <c r="B2" s="74"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="75"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="31"/>
@@ -11648,7 +11669,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="114" t="s">
+      <c r="A4" s="115" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="35">
@@ -11674,11 +11695,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="115"/>
+      <c r="A5" s="116"/>
       <c r="B5" s="35">
         <v>46185</v>
       </c>
@@ -11702,7 +11723,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="115"/>
+      <c r="A6" s="116"/>
       <c r="B6" s="35">
         <v>46191</v>
       </c>
@@ -11730,7 +11751,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="115"/>
+      <c r="A7" s="116"/>
       <c r="B7" s="35">
         <v>46192</v>
       </c>
@@ -11758,7 +11779,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="115"/>
+      <c r="A8" s="116"/>
       <c r="B8" s="35">
         <v>46198</v>
       </c>
@@ -11786,7 +11807,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="116"/>
+      <c r="A9" s="117"/>
       <c r="B9" s="42">
         <v>46198</v>
       </c>
@@ -11848,7 +11869,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="117" t="s">
+      <c r="A12" s="118" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="35">
@@ -11874,7 +11895,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="118"/>
+      <c r="A13" s="119"/>
       <c r="B13" s="35">
         <v>46186</v>
       </c>
@@ -11898,7 +11919,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="118"/>
+      <c r="A14" s="119"/>
       <c r="B14" s="35">
         <v>46191</v>
       </c>
@@ -11926,7 +11947,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="118"/>
+      <c r="A15" s="119"/>
       <c r="B15" s="35">
         <v>46192</v>
       </c>
@@ -11954,7 +11975,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="118"/>
+      <c r="A16" s="119"/>
       <c r="B16" s="35">
         <v>46197</v>
       </c>
@@ -11982,7 +12003,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="119"/>
+      <c r="A17" s="120"/>
       <c r="B17" s="42">
         <v>46197</v>
       </c>
@@ -12044,7 +12065,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="120" t="s">
+      <c r="A20" s="121" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="35">
@@ -12070,7 +12091,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="121"/>
+      <c r="A21" s="122"/>
       <c r="B21" s="35">
         <v>46187</v>
       </c>
@@ -12098,7 +12119,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="121"/>
+      <c r="A22" s="122"/>
       <c r="B22" s="35">
         <v>46193</v>
       </c>
@@ -12126,7 +12147,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="121"/>
+      <c r="A23" s="122"/>
       <c r="B23" s="35">
         <v>46193</v>
       </c>
@@ -12154,7 +12175,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="121"/>
+      <c r="A24" s="122"/>
       <c r="B24" s="35">
         <v>46198</v>
       </c>
@@ -12182,7 +12203,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="122"/>
+      <c r="A25" s="123"/>
       <c r="B25" s="42">
         <v>46198</v>
       </c>
@@ -12244,7 +12265,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="111" t="s">
+      <c r="A28" s="112" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="35">
@@ -12270,7 +12291,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="112"/>
+      <c r="A29" s="113"/>
       <c r="B29" s="35">
         <v>46187</v>
       </c>
@@ -12298,7 +12319,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="112"/>
+      <c r="A30" s="113"/>
       <c r="B30" s="35">
         <v>46192</v>
       </c>
@@ -12326,7 +12347,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="112"/>
+      <c r="A31" s="113"/>
       <c r="B31" s="35">
         <v>46193</v>
       </c>
@@ -12354,7 +12375,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="112"/>
+      <c r="A32" s="113"/>
       <c r="B32" s="35">
         <v>46199</v>
       </c>
@@ -12382,7 +12403,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="113"/>
+      <c r="A33" s="114"/>
       <c r="B33" s="42">
         <v>46199</v>
       </c>
@@ -12444,7 +12465,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="129" t="s">
+      <c r="A36" s="130" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="35">
@@ -12474,7 +12495,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="130"/>
+      <c r="A37" s="131"/>
       <c r="B37" s="35">
         <v>46188</v>
       </c>
@@ -12502,7 +12523,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="130"/>
+      <c r="A38" s="131"/>
       <c r="B38" s="35">
         <v>46193</v>
       </c>
@@ -12530,7 +12551,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="130"/>
+      <c r="A39" s="131"/>
       <c r="B39" s="35">
         <v>46194</v>
       </c>
@@ -12558,7 +12579,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="130"/>
+      <c r="A40" s="131"/>
       <c r="B40" s="35">
         <v>46198</v>
       </c>
@@ -12586,7 +12607,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="131"/>
+      <c r="A41" s="132"/>
       <c r="B41" s="42">
         <v>46198</v>
       </c>
@@ -12648,7 +12669,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="132" t="s">
+      <c r="A44" s="133" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="35">
@@ -12678,7 +12699,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="133"/>
+      <c r="A45" s="134"/>
       <c r="B45" s="35">
         <v>46188</v>
       </c>
@@ -12706,7 +12727,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="133"/>
+      <c r="A46" s="134"/>
       <c r="B46" s="35">
         <v>46193</v>
       </c>
@@ -12734,7 +12755,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="133"/>
+      <c r="A47" s="134"/>
       <c r="B47" s="35">
         <v>46194</v>
       </c>
@@ -12762,7 +12783,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="133"/>
+      <c r="A48" s="134"/>
       <c r="B48" s="35">
         <v>46199</v>
       </c>
@@ -12790,7 +12811,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="134"/>
+      <c r="A49" s="135"/>
       <c r="B49" s="42">
         <v>46199</v>
       </c>
@@ -12852,7 +12873,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="135" t="s">
+      <c r="A52" s="136" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="35">
@@ -12882,7 +12903,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="136"/>
+      <c r="A53" s="137"/>
       <c r="B53" s="35">
         <v>46189</v>
       </c>
@@ -12910,7 +12931,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="136"/>
+      <c r="A54" s="137"/>
       <c r="B54" s="35">
         <v>46194</v>
       </c>
@@ -12938,7 +12959,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="136"/>
+      <c r="A55" s="137"/>
       <c r="B55" s="35">
         <v>46195</v>
       </c>
@@ -12966,7 +12987,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="136"/>
+      <c r="A56" s="137"/>
       <c r="B56" s="35">
         <v>46200</v>
       </c>
@@ -12994,7 +13015,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="137"/>
+      <c r="A57" s="138"/>
       <c r="B57" s="42">
         <v>46200</v>
       </c>
@@ -13056,7 +13077,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="138" t="s">
+      <c r="A60" s="139" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="35">
@@ -13086,7 +13107,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="139"/>
+      <c r="A61" s="140"/>
       <c r="B61" s="35">
         <v>46189</v>
       </c>
@@ -13114,7 +13135,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="139"/>
+      <c r="A62" s="140"/>
       <c r="B62" s="35">
         <v>46194</v>
       </c>
@@ -13142,7 +13163,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="139"/>
+      <c r="A63" s="140"/>
       <c r="B63" s="35">
         <v>46195</v>
       </c>
@@ -13170,7 +13191,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="139"/>
+      <c r="A64" s="140"/>
       <c r="B64" s="35">
         <v>46200</v>
       </c>
@@ -13198,7 +13219,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="140"/>
+      <c r="A65" s="141"/>
       <c r="B65" s="42">
         <v>46200</v>
       </c>
@@ -13260,7 +13281,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="141" t="s">
+      <c r="A68" s="142" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="35">
@@ -13284,13 +13305,13 @@
       <c r="H68" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="J68" s="1" t="str">
+      <c r="J68" s="1">
         <f>IF(OR(Resultados!F68="",Resultados!G68=""),"",IF(AND(F68=Resultados!F68,G68=Resultados!G68),2,IF(((F68&gt;G68)=(Resultados!F68&gt;Resultados!G68))*((F68&lt;G68)=(Resultados!F68&lt;Resultados!G68)),1,0)))</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="142"/>
+      <c r="A69" s="143"/>
       <c r="B69" s="35">
         <v>46190</v>
       </c>
@@ -13312,13 +13333,13 @@
       <c r="H69" s="46" t="s">
         <v>54</v>
       </c>
-      <c r="J69" s="1" t="str">
+      <c r="J69" s="1">
         <f>IF(OR(Resultados!F69="",Resultados!G69=""),"",IF(AND(F69=Resultados!F69,G69=Resultados!G69),2,IF(((F69&gt;G69)=(Resultados!F69&gt;Resultados!G69))*((F69&lt;G69)=(Resultados!F69&lt;Resultados!G69)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="142"/>
+      <c r="A70" s="143"/>
       <c r="B70" s="35">
         <v>46195</v>
       </c>
@@ -13346,7 +13367,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="142"/>
+      <c r="A71" s="143"/>
       <c r="B71" s="35">
         <v>46196</v>
       </c>
@@ -13374,7 +13395,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="142"/>
+      <c r="A72" s="143"/>
       <c r="B72" s="35">
         <v>46199</v>
       </c>
@@ -13402,7 +13423,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="143"/>
+      <c r="A73" s="144"/>
       <c r="B73" s="42">
         <v>46199</v>
       </c>
@@ -13464,7 +13485,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="144" t="s">
+      <c r="A76" s="145" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="35">
@@ -13488,13 +13509,13 @@
       <c r="H76" s="46" t="s">
         <v>57</v>
       </c>
-      <c r="J76" s="1" t="str">
+      <c r="J76" s="1">
         <f>IF(OR(Resultados!F76="",Resultados!G76=""),"",IF(AND(F76=Resultados!F76,G76=Resultados!G76),2,IF(((F76&gt;G76)=(Resultados!F76&gt;Resultados!G76))*((F76&lt;G76)=(Resultados!F76&lt;Resultados!G76)),1,0)))</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="145"/>
+      <c r="A77" s="146"/>
       <c r="B77" s="35">
         <v>46190</v>
       </c>
@@ -13522,7 +13543,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="145"/>
+      <c r="A78" s="146"/>
       <c r="B78" s="35">
         <v>46195</v>
       </c>
@@ -13550,7 +13571,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="145"/>
+      <c r="A79" s="146"/>
       <c r="B79" s="35">
         <v>46196</v>
       </c>
@@ -13578,7 +13599,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="145"/>
+      <c r="A80" s="146"/>
       <c r="B80" s="35">
         <v>46201</v>
       </c>
@@ -13606,7 +13627,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="146"/>
+      <c r="A81" s="147"/>
       <c r="B81" s="42">
         <v>46201</v>
       </c>
@@ -13668,7 +13689,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="123" t="s">
+      <c r="A84" s="124" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="35">
@@ -13698,7 +13719,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="124"/>
+      <c r="A85" s="125"/>
       <c r="B85" s="35">
         <v>46191</v>
       </c>
@@ -13726,7 +13747,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="124"/>
+      <c r="A86" s="125"/>
       <c r="B86" s="35">
         <v>46196</v>
       </c>
@@ -13754,7 +13775,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="124"/>
+      <c r="A87" s="125"/>
       <c r="B87" s="35">
         <v>46197</v>
       </c>
@@ -13782,7 +13803,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="124"/>
+      <c r="A88" s="125"/>
       <c r="B88" s="35">
         <v>46201</v>
       </c>
@@ -13810,7 +13831,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="125"/>
+      <c r="A89" s="126"/>
       <c r="B89" s="42">
         <v>46201</v>
       </c>
@@ -13872,7 +13893,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="126" t="s">
+      <c r="A92" s="127" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="35">
@@ -13902,7 +13923,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="127"/>
+      <c r="A93" s="128"/>
       <c r="B93" s="35">
         <v>46191</v>
       </c>
@@ -13930,7 +13951,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="127"/>
+      <c r="A94" s="128"/>
       <c r="B94" s="35">
         <v>46196</v>
       </c>
@@ -13958,7 +13979,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="127"/>
+      <c r="A95" s="128"/>
       <c r="B95" s="35">
         <v>46197</v>
       </c>
@@ -13986,7 +14007,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="127"/>
+      <c r="A96" s="128"/>
       <c r="B96" s="35">
         <v>46200</v>
       </c>
@@ -14014,7 +14035,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="128"/>
+      <c r="A97" s="129"/>
       <c r="B97" s="42">
         <v>46200</v>
       </c>
@@ -14084,26 +14105,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="69" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="71"/>
+      <c r="A1" s="70" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="72"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="72"/>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="74"/>
+      <c r="A2" s="73"/>
+      <c r="B2" s="74"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="75"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -14136,7 +14157,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="96" t="s">
+      <c r="A4" s="97" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -14162,11 +14183,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="97"/>
+      <c r="A5" s="98"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -14190,7 +14211,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="97"/>
+      <c r="A6" s="98"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -14218,7 +14239,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="97"/>
+      <c r="A7" s="98"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -14246,7 +14267,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="97"/>
+      <c r="A8" s="98"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -14274,7 +14295,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="98"/>
+      <c r="A9" s="99"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -14336,7 +14357,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="99" t="s">
+      <c r="A12" s="100" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -14362,7 +14383,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="100"/>
+      <c r="A13" s="101"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -14386,7 +14407,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="100"/>
+      <c r="A14" s="101"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -14414,7 +14435,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="100"/>
+      <c r="A15" s="101"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -14442,7 +14463,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="100"/>
+      <c r="A16" s="101"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -14470,7 +14491,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="101"/>
+      <c r="A17" s="102"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -14532,7 +14553,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="102" t="s">
+      <c r="A20" s="103" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -14558,7 +14579,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="103"/>
+      <c r="A21" s="104"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -14586,7 +14607,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="103"/>
+      <c r="A22" s="104"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -14614,7 +14635,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="103"/>
+      <c r="A23" s="104"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -14642,7 +14663,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="103"/>
+      <c r="A24" s="104"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -14670,7 +14691,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="104"/>
+      <c r="A25" s="105"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -14732,7 +14753,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="105" t="s">
+      <c r="A28" s="106" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -14758,7 +14779,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="106"/>
+      <c r="A29" s="107"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -14786,7 +14807,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="106"/>
+      <c r="A30" s="107"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -14814,7 +14835,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="106"/>
+      <c r="A31" s="107"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -14842,7 +14863,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="106"/>
+      <c r="A32" s="107"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -14870,7 +14891,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="107"/>
+      <c r="A33" s="108"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -14932,7 +14953,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="108" t="s">
+      <c r="A36" s="109" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -14962,7 +14983,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="109"/>
+      <c r="A37" s="110"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -14990,7 +15011,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="109"/>
+      <c r="A38" s="110"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -15018,7 +15039,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="109"/>
+      <c r="A39" s="110"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -15046,7 +15067,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="109"/>
+      <c r="A40" s="110"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -15074,7 +15095,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="110"/>
+      <c r="A41" s="111"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -15136,7 +15157,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="78" t="s">
+      <c r="A44" s="79" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -15166,7 +15187,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="79"/>
+      <c r="A45" s="80"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -15194,7 +15215,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="79"/>
+      <c r="A46" s="80"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -15222,7 +15243,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="79"/>
+      <c r="A47" s="80"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -15250,7 +15271,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="79"/>
+      <c r="A48" s="80"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -15278,7 +15299,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="80"/>
+      <c r="A49" s="81"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -15340,7 +15361,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="81" t="s">
+      <c r="A52" s="82" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -15370,7 +15391,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="82"/>
+      <c r="A53" s="83"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -15398,7 +15419,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="82"/>
+      <c r="A54" s="83"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -15426,7 +15447,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="82"/>
+      <c r="A55" s="83"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -15454,7 +15475,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="82"/>
+      <c r="A56" s="83"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -15482,7 +15503,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="83"/>
+      <c r="A57" s="84"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -15544,7 +15565,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="84" t="s">
+      <c r="A60" s="85" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -15574,7 +15595,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="85"/>
+      <c r="A61" s="86"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -15602,7 +15623,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="85"/>
+      <c r="A62" s="86"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -15630,7 +15651,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="85"/>
+      <c r="A63" s="86"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -15658,7 +15679,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="85"/>
+      <c r="A64" s="86"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -15686,7 +15707,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="86"/>
+      <c r="A65" s="87"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -15748,7 +15769,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="87" t="s">
+      <c r="A68" s="88" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -15772,13 +15793,13 @@
       <c r="H68" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="J68" s="1" t="str">
+      <c r="J68" s="1">
         <f>IF(OR(Resultados!F68="",Resultados!G68=""),"",IF(AND(F68=Resultados!F68,G68=Resultados!G68),2,IF(((F68&gt;G68)=(Resultados!F68&gt;Resultados!G68))*((F68&lt;G68)=(Resultados!F68&lt;Resultados!G68)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="88"/>
+      <c r="A69" s="89"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -15800,13 +15821,13 @@
       <c r="H69" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="J69" s="1" t="str">
+      <c r="J69" s="1">
         <f>IF(OR(Resultados!F69="",Resultados!G69=""),"",IF(AND(F69=Resultados!F69,G69=Resultados!G69),2,IF(((F69&gt;G69)=(Resultados!F69&gt;Resultados!G69))*((F69&lt;G69)=(Resultados!F69&lt;Resultados!G69)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="88"/>
+      <c r="A70" s="89"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -15834,7 +15855,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="88"/>
+      <c r="A71" s="89"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -15862,7 +15883,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="88"/>
+      <c r="A72" s="89"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -15890,7 +15911,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="89"/>
+      <c r="A73" s="90"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -15952,7 +15973,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="90" t="s">
+      <c r="A76" s="91" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -15976,13 +15997,13 @@
       <c r="H76" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="J76" s="1" t="str">
+      <c r="J76" s="1">
         <f>IF(OR(Resultados!F76="",Resultados!G76=""),"",IF(AND(F76=Resultados!F76,G76=Resultados!G76),2,IF(((F76&gt;G76)=(Resultados!F76&gt;Resultados!G76))*((F76&lt;G76)=(Resultados!F76&lt;Resultados!G76)),1,0)))</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="91"/>
+      <c r="A77" s="92"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -16010,7 +16031,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="91"/>
+      <c r="A78" s="92"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -16038,7 +16059,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="91"/>
+      <c r="A79" s="92"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -16066,7 +16087,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="91"/>
+      <c r="A80" s="92"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -16094,7 +16115,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="92"/>
+      <c r="A81" s="93"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -16156,7 +16177,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="93" t="s">
+      <c r="A84" s="94" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -16186,7 +16207,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="94"/>
+      <c r="A85" s="95"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -16214,7 +16235,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="94"/>
+      <c r="A86" s="95"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -16242,7 +16263,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="94"/>
+      <c r="A87" s="95"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -16270,7 +16291,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="94"/>
+      <c r="A88" s="95"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -16298,7 +16319,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="95"/>
+      <c r="A89" s="96"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -16360,7 +16381,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="75" t="s">
+      <c r="A92" s="76" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -16390,7 +16411,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="76"/>
+      <c r="A93" s="77"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -16418,7 +16439,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="76"/>
+      <c r="A94" s="77"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -16446,7 +16467,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="76"/>
+      <c r="A95" s="77"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -16474,7 +16495,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="76"/>
+      <c r="A96" s="77"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -16502,7 +16523,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="77"/>
+      <c r="A97" s="78"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -16572,26 +16593,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="69" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="71"/>
+      <c r="A1" s="70" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="72"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="72"/>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="74"/>
+      <c r="A2" s="73"/>
+      <c r="B2" s="74"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="75"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -16624,7 +16645,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="96" t="s">
+      <c r="A4" s="97" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -16650,11 +16671,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="97"/>
+      <c r="A5" s="98"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -16678,7 +16699,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="97"/>
+      <c r="A6" s="98"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -16706,7 +16727,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="97"/>
+      <c r="A7" s="98"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -16734,7 +16755,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="97"/>
+      <c r="A8" s="98"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -16762,7 +16783,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="98"/>
+      <c r="A9" s="99"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -16824,7 +16845,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="99" t="s">
+      <c r="A12" s="100" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -16850,7 +16871,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="100"/>
+      <c r="A13" s="101"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -16874,7 +16895,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="100"/>
+      <c r="A14" s="101"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -16902,7 +16923,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="100"/>
+      <c r="A15" s="101"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -16930,7 +16951,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="100"/>
+      <c r="A16" s="101"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -16958,7 +16979,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="101"/>
+      <c r="A17" s="102"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -17020,7 +17041,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="102" t="s">
+      <c r="A20" s="103" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -17046,7 +17067,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="103"/>
+      <c r="A21" s="104"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -17074,7 +17095,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="103"/>
+      <c r="A22" s="104"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -17102,7 +17123,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="103"/>
+      <c r="A23" s="104"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -17130,7 +17151,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="103"/>
+      <c r="A24" s="104"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -17158,7 +17179,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="104"/>
+      <c r="A25" s="105"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -17220,7 +17241,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="105" t="s">
+      <c r="A28" s="106" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -17246,7 +17267,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="106"/>
+      <c r="A29" s="107"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -17274,7 +17295,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="106"/>
+      <c r="A30" s="107"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -17302,7 +17323,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="106"/>
+      <c r="A31" s="107"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -17330,7 +17351,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="106"/>
+      <c r="A32" s="107"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -17358,7 +17379,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="107"/>
+      <c r="A33" s="108"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -17420,7 +17441,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="108" t="s">
+      <c r="A36" s="109" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -17450,7 +17471,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="109"/>
+      <c r="A37" s="110"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -17478,7 +17499,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="109"/>
+      <c r="A38" s="110"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -17506,7 +17527,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="109"/>
+      <c r="A39" s="110"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -17534,7 +17555,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="109"/>
+      <c r="A40" s="110"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -17562,7 +17583,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="110"/>
+      <c r="A41" s="111"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -17624,7 +17645,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="78" t="s">
+      <c r="A44" s="79" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -17654,7 +17675,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="79"/>
+      <c r="A45" s="80"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -17682,7 +17703,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="79"/>
+      <c r="A46" s="80"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -17710,7 +17731,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="79"/>
+      <c r="A47" s="80"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -17738,7 +17759,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="79"/>
+      <c r="A48" s="80"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -17766,7 +17787,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="80"/>
+      <c r="A49" s="81"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -17828,7 +17849,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="81" t="s">
+      <c r="A52" s="82" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -17858,7 +17879,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="82"/>
+      <c r="A53" s="83"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -17886,7 +17907,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="82"/>
+      <c r="A54" s="83"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -17914,7 +17935,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="82"/>
+      <c r="A55" s="83"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -17942,7 +17963,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="82"/>
+      <c r="A56" s="83"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -17970,7 +17991,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="83"/>
+      <c r="A57" s="84"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -18032,7 +18053,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="84" t="s">
+      <c r="A60" s="85" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -18062,7 +18083,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="85"/>
+      <c r="A61" s="86"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -18090,7 +18111,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="85"/>
+      <c r="A62" s="86"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -18118,7 +18139,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="85"/>
+      <c r="A63" s="86"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -18146,7 +18167,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="85"/>
+      <c r="A64" s="86"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -18174,7 +18195,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="86"/>
+      <c r="A65" s="87"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -18236,7 +18257,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="87" t="s">
+      <c r="A68" s="88" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -18260,13 +18281,13 @@
       <c r="H68" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="J68" s="1" t="str">
+      <c r="J68" s="1">
         <f>IF(OR(Resultados!F68="",Resultados!G68=""),"",IF(AND(F68=Resultados!F68,G68=Resultados!G68),2,IF(((F68&gt;G68)=(Resultados!F68&gt;Resultados!G68))*((F68&lt;G68)=(Resultados!F68&lt;Resultados!G68)),1,0)))</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="88"/>
+      <c r="A69" s="89"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -18288,13 +18309,13 @@
       <c r="H69" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="J69" s="1" t="str">
+      <c r="J69" s="1">
         <f>IF(OR(Resultados!F69="",Resultados!G69=""),"",IF(AND(F69=Resultados!F69,G69=Resultados!G69),2,IF(((F69&gt;G69)=(Resultados!F69&gt;Resultados!G69))*((F69&lt;G69)=(Resultados!F69&lt;Resultados!G69)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="88"/>
+      <c r="A70" s="89"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -18322,7 +18343,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="88"/>
+      <c r="A71" s="89"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -18350,7 +18371,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="88"/>
+      <c r="A72" s="89"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -18378,7 +18399,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="89"/>
+      <c r="A73" s="90"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -18440,7 +18461,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="90" t="s">
+      <c r="A76" s="91" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -18464,13 +18485,13 @@
       <c r="H76" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="J76" s="1" t="str">
+      <c r="J76" s="1">
         <f>IF(OR(Resultados!F76="",Resultados!G76=""),"",IF(AND(F76=Resultados!F76,G76=Resultados!G76),2,IF(((F76&gt;G76)=(Resultados!F76&gt;Resultados!G76))*((F76&lt;G76)=(Resultados!F76&lt;Resultados!G76)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="91"/>
+      <c r="A77" s="92"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -18498,7 +18519,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="91"/>
+      <c r="A78" s="92"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -18526,7 +18547,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="91"/>
+      <c r="A79" s="92"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -18554,7 +18575,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="91"/>
+      <c r="A80" s="92"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -18582,7 +18603,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="92"/>
+      <c r="A81" s="93"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -18644,7 +18665,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="93" t="s">
+      <c r="A84" s="94" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -18674,7 +18695,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="94"/>
+      <c r="A85" s="95"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -18702,7 +18723,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="94"/>
+      <c r="A86" s="95"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -18730,7 +18751,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="94"/>
+      <c r="A87" s="95"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -18758,7 +18779,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="94"/>
+      <c r="A88" s="95"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -18786,7 +18807,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="95"/>
+      <c r="A89" s="96"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -18848,7 +18869,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="75" t="s">
+      <c r="A92" s="76" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -18878,7 +18899,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="76"/>
+      <c r="A93" s="77"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -18906,7 +18927,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="76"/>
+      <c r="A94" s="77"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -18934,7 +18955,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="76"/>
+      <c r="A95" s="77"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -18962,7 +18983,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="76"/>
+      <c r="A96" s="77"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -18990,7 +19011,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="77"/>
+      <c r="A97" s="78"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -19060,26 +19081,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="69" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="71"/>
+      <c r="A1" s="70" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="72"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="72"/>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="74"/>
+      <c r="A2" s="73"/>
+      <c r="B2" s="74"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="75"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -19112,7 +19133,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="96" t="s">
+      <c r="A4" s="97" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -19138,11 +19159,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="97"/>
+      <c r="A5" s="98"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -19166,7 +19187,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="97"/>
+      <c r="A6" s="98"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -19194,7 +19215,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="97"/>
+      <c r="A7" s="98"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -19222,7 +19243,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="97"/>
+      <c r="A8" s="98"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -19250,7 +19271,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="98"/>
+      <c r="A9" s="99"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -19312,7 +19333,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="99" t="s">
+      <c r="A12" s="100" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -19338,7 +19359,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="100"/>
+      <c r="A13" s="101"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -19362,7 +19383,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="100"/>
+      <c r="A14" s="101"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -19390,7 +19411,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="100"/>
+      <c r="A15" s="101"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -19418,7 +19439,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="100"/>
+      <c r="A16" s="101"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -19446,7 +19467,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="101"/>
+      <c r="A17" s="102"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -19508,7 +19529,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="102" t="s">
+      <c r="A20" s="103" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -19534,7 +19555,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="103"/>
+      <c r="A21" s="104"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -19562,7 +19583,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="103"/>
+      <c r="A22" s="104"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -19590,7 +19611,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="103"/>
+      <c r="A23" s="104"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -19618,7 +19639,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="103"/>
+      <c r="A24" s="104"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -19646,7 +19667,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="104"/>
+      <c r="A25" s="105"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -19708,7 +19729,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="105" t="s">
+      <c r="A28" s="106" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -19734,7 +19755,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="106"/>
+      <c r="A29" s="107"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -19762,7 +19783,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="106"/>
+      <c r="A30" s="107"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -19790,7 +19811,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="106"/>
+      <c r="A31" s="107"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -19818,7 +19839,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="106"/>
+      <c r="A32" s="107"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -19842,7 +19863,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="107"/>
+      <c r="A33" s="108"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -19900,7 +19921,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="108" t="s">
+      <c r="A36" s="109" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -19930,7 +19951,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="109"/>
+      <c r="A37" s="110"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -19958,7 +19979,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="109"/>
+      <c r="A38" s="110"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -19982,7 +20003,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="109"/>
+      <c r="A39" s="110"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -20006,7 +20027,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="109"/>
+      <c r="A40" s="110"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -20030,7 +20051,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="110"/>
+      <c r="A41" s="111"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -20088,7 +20109,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="78" t="s">
+      <c r="A44" s="79" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -20118,7 +20139,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="79"/>
+      <c r="A45" s="80"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -20146,7 +20167,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="79"/>
+      <c r="A46" s="80"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -20170,7 +20191,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="79"/>
+      <c r="A47" s="80"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -20194,7 +20215,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="79"/>
+      <c r="A48" s="80"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -20218,7 +20239,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="80"/>
+      <c r="A49" s="81"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -20276,7 +20297,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="81" t="s">
+      <c r="A52" s="82" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -20306,7 +20327,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="82"/>
+      <c r="A53" s="83"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -20334,7 +20355,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="82"/>
+      <c r="A54" s="83"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -20358,7 +20379,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="82"/>
+      <c r="A55" s="83"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -20382,7 +20403,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="82"/>
+      <c r="A56" s="83"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -20406,7 +20427,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="83"/>
+      <c r="A57" s="84"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -20464,7 +20485,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="84" t="s">
+      <c r="A60" s="85" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -20494,7 +20515,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="85"/>
+      <c r="A61" s="86"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -20522,7 +20543,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="85"/>
+      <c r="A62" s="86"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -20546,7 +20567,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="85"/>
+      <c r="A63" s="86"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -20570,7 +20591,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="85"/>
+      <c r="A64" s="86"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -20594,7 +20615,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="86"/>
+      <c r="A65" s="87"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -20652,7 +20673,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="87" t="s">
+      <c r="A68" s="88" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -20676,13 +20697,13 @@
       <c r="H68" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="J68" s="1" t="str">
+      <c r="J68" s="1">
         <f>IF(OR(Resultados!F68="",Resultados!G68=""),"",IF(AND(F68=Resultados!F68,G68=Resultados!G68),2,IF(((F68&gt;G68)=(Resultados!F68&gt;Resultados!G68))*((F68&lt;G68)=(Resultados!F68&lt;Resultados!G68)),1,0)))</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="88"/>
+      <c r="A69" s="89"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -20704,13 +20725,13 @@
       <c r="H69" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="J69" s="1" t="str">
+      <c r="J69" s="1">
         <f>IF(OR(Resultados!F69="",Resultados!G69=""),"",IF(AND(F69=Resultados!F69,G69=Resultados!G69),2,IF(((F69&gt;G69)=(Resultados!F69&gt;Resultados!G69))*((F69&lt;G69)=(Resultados!F69&lt;Resultados!G69)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="88"/>
+      <c r="A70" s="89"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -20734,7 +20755,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="88"/>
+      <c r="A71" s="89"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -20758,7 +20779,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="88"/>
+      <c r="A72" s="89"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -20782,7 +20803,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="89"/>
+      <c r="A73" s="90"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -20840,7 +20861,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="90" t="s">
+      <c r="A76" s="91" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -20864,13 +20885,13 @@
       <c r="H76" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="J76" s="1" t="str">
+      <c r="J76" s="1">
         <f>IF(OR(Resultados!F76="",Resultados!G76=""),"",IF(AND(F76=Resultados!F76,G76=Resultados!G76),2,IF(((F76&gt;G76)=(Resultados!F76&gt;Resultados!G76))*((F76&lt;G76)=(Resultados!F76&lt;Resultados!G76)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="91"/>
+      <c r="A77" s="92"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -20898,7 +20919,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="91"/>
+      <c r="A78" s="92"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -20922,7 +20943,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="91"/>
+      <c r="A79" s="92"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -20946,7 +20967,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="91"/>
+      <c r="A80" s="92"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -20970,7 +20991,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="92"/>
+      <c r="A81" s="93"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -21028,7 +21049,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="93" t="s">
+      <c r="A84" s="94" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -21058,7 +21079,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="94"/>
+      <c r="A85" s="95"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -21086,7 +21107,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="94"/>
+      <c r="A86" s="95"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -21110,7 +21131,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="94"/>
+      <c r="A87" s="95"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -21134,7 +21155,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="94"/>
+      <c r="A88" s="95"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -21158,7 +21179,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="95"/>
+      <c r="A89" s="96"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -21216,7 +21237,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="75" t="s">
+      <c r="A92" s="76" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -21246,7 +21267,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="76"/>
+      <c r="A93" s="77"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -21274,7 +21295,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="76"/>
+      <c r="A94" s="77"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -21298,7 +21319,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="76"/>
+      <c r="A95" s="77"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -21322,7 +21343,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="76"/>
+      <c r="A96" s="77"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -21346,7 +21367,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="77"/>
+      <c r="A97" s="78"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -21412,26 +21433,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="69" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="71"/>
+      <c r="A1" s="70" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="72"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="72"/>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="74"/>
+      <c r="A2" s="73"/>
+      <c r="B2" s="74"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="75"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -21464,7 +21485,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="96" t="s">
+      <c r="A4" s="97" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -21490,11 +21511,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="97"/>
+      <c r="A5" s="98"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -21518,7 +21539,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="97"/>
+      <c r="A6" s="98"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -21546,7 +21567,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="97"/>
+      <c r="A7" s="98"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -21574,7 +21595,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="97"/>
+      <c r="A8" s="98"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -21602,7 +21623,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="98"/>
+      <c r="A9" s="99"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -21664,7 +21685,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="99" t="s">
+      <c r="A12" s="100" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -21690,7 +21711,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="100"/>
+      <c r="A13" s="101"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -21714,7 +21735,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="100"/>
+      <c r="A14" s="101"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -21742,7 +21763,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="100"/>
+      <c r="A15" s="101"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -21770,7 +21791,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="100"/>
+      <c r="A16" s="101"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -21798,7 +21819,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="101"/>
+      <c r="A17" s="102"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -21860,7 +21881,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="102" t="s">
+      <c r="A20" s="103" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -21886,7 +21907,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="103"/>
+      <c r="A21" s="104"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -21914,7 +21935,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="103"/>
+      <c r="A22" s="104"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -21942,7 +21963,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="103"/>
+      <c r="A23" s="104"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -21970,7 +21991,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="103"/>
+      <c r="A24" s="104"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -21998,7 +22019,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="104"/>
+      <c r="A25" s="105"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -22060,7 +22081,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="105" t="s">
+      <c r="A28" s="106" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -22086,7 +22107,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="106"/>
+      <c r="A29" s="107"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -22114,7 +22135,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="106"/>
+      <c r="A30" s="107"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -22142,7 +22163,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="106"/>
+      <c r="A31" s="107"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -22170,7 +22191,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="106"/>
+      <c r="A32" s="107"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -22198,7 +22219,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="107"/>
+      <c r="A33" s="108"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -22260,7 +22281,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="108" t="s">
+      <c r="A36" s="109" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -22290,7 +22311,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="109"/>
+      <c r="A37" s="110"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -22318,7 +22339,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="109"/>
+      <c r="A38" s="110"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -22346,7 +22367,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="109"/>
+      <c r="A39" s="110"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -22374,7 +22395,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="109"/>
+      <c r="A40" s="110"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -22402,7 +22423,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="110"/>
+      <c r="A41" s="111"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -22464,7 +22485,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="78" t="s">
+      <c r="A44" s="79" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -22494,7 +22515,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="79"/>
+      <c r="A45" s="80"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -22522,7 +22543,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="79"/>
+      <c r="A46" s="80"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -22550,7 +22571,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="79"/>
+      <c r="A47" s="80"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -22578,7 +22599,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="79"/>
+      <c r="A48" s="80"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -22606,7 +22627,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="80"/>
+      <c r="A49" s="81"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -22668,7 +22689,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="81" t="s">
+      <c r="A52" s="82" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -22698,7 +22719,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="82"/>
+      <c r="A53" s="83"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -22726,7 +22747,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="82"/>
+      <c r="A54" s="83"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -22754,7 +22775,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="82"/>
+      <c r="A55" s="83"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -22782,7 +22803,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="82"/>
+      <c r="A56" s="83"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -22810,7 +22831,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="83"/>
+      <c r="A57" s="84"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -22872,7 +22893,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="84" t="s">
+      <c r="A60" s="85" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -22902,7 +22923,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="85"/>
+      <c r="A61" s="86"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -22930,7 +22951,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="85"/>
+      <c r="A62" s="86"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -22958,7 +22979,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="85"/>
+      <c r="A63" s="86"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -22986,7 +23007,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="85"/>
+      <c r="A64" s="86"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -23014,7 +23035,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="86"/>
+      <c r="A65" s="87"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -23076,7 +23097,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="87" t="s">
+      <c r="A68" s="88" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -23100,13 +23121,13 @@
       <c r="H68" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="J68" s="1" t="str">
+      <c r="J68" s="1">
         <f>IF(OR(Resultados!F68="",Resultados!G68=""),"",IF(AND(F68=Resultados!F68,G68=Resultados!G68),2,IF(((F68&gt;G68)=(Resultados!F68&gt;Resultados!G68))*((F68&lt;G68)=(Resultados!F68&lt;Resultados!G68)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="88"/>
+      <c r="A69" s="89"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -23128,13 +23149,13 @@
       <c r="H69" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="J69" s="1" t="str">
+      <c r="J69" s="1">
         <f>IF(OR(Resultados!F69="",Resultados!G69=""),"",IF(AND(F69=Resultados!F69,G69=Resultados!G69),2,IF(((F69&gt;G69)=(Resultados!F69&gt;Resultados!G69))*((F69&lt;G69)=(Resultados!F69&lt;Resultados!G69)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="88"/>
+      <c r="A70" s="89"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -23162,7 +23183,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="88"/>
+      <c r="A71" s="89"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -23190,7 +23211,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="88"/>
+      <c r="A72" s="89"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -23218,7 +23239,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="89"/>
+      <c r="A73" s="90"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -23280,7 +23301,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="90" t="s">
+      <c r="A76" s="91" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -23304,13 +23325,13 @@
       <c r="H76" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="J76" s="1" t="str">
+      <c r="J76" s="1">
         <f>IF(OR(Resultados!F76="",Resultados!G76=""),"",IF(AND(F76=Resultados!F76,G76=Resultados!G76),2,IF(((F76&gt;G76)=(Resultados!F76&gt;Resultados!G76))*((F76&lt;G76)=(Resultados!F76&lt;Resultados!G76)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="91"/>
+      <c r="A77" s="92"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -23338,7 +23359,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="91"/>
+      <c r="A78" s="92"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -23366,7 +23387,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="91"/>
+      <c r="A79" s="92"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -23394,7 +23415,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="91"/>
+      <c r="A80" s="92"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -23422,7 +23443,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="92"/>
+      <c r="A81" s="93"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -23484,7 +23505,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="93" t="s">
+      <c r="A84" s="94" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -23514,7 +23535,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="94"/>
+      <c r="A85" s="95"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -23542,7 +23563,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="94"/>
+      <c r="A86" s="95"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -23570,7 +23591,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="94"/>
+      <c r="A87" s="95"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -23598,7 +23619,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="94"/>
+      <c r="A88" s="95"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -23626,7 +23647,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="95"/>
+      <c r="A89" s="96"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -23688,7 +23709,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="75" t="s">
+      <c r="A92" s="76" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -23718,7 +23739,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="76"/>
+      <c r="A93" s="77"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -23746,7 +23767,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="76"/>
+      <c r="A94" s="77"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -23774,7 +23795,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="76"/>
+      <c r="A95" s="77"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -23802,7 +23823,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="76"/>
+      <c r="A96" s="77"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -23830,7 +23851,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="77"/>
+      <c r="A97" s="78"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -23900,26 +23921,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="69" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="71"/>
+      <c r="A1" s="70" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="72"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="72"/>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="74"/>
+      <c r="A2" s="73"/>
+      <c r="B2" s="74"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="75"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -23952,7 +23973,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="96" t="s">
+      <c r="A4" s="97" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -23978,11 +23999,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="97"/>
+      <c r="A5" s="98"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -24006,7 +24027,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="97"/>
+      <c r="A6" s="98"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -24034,7 +24055,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="97"/>
+      <c r="A7" s="98"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -24062,7 +24083,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="97"/>
+      <c r="A8" s="98"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -24090,7 +24111,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="98"/>
+      <c r="A9" s="99"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -24152,7 +24173,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="99" t="s">
+      <c r="A12" s="100" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -24178,7 +24199,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="100"/>
+      <c r="A13" s="101"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -24202,7 +24223,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="100"/>
+      <c r="A14" s="101"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -24230,7 +24251,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="100"/>
+      <c r="A15" s="101"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -24258,7 +24279,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="100"/>
+      <c r="A16" s="101"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -24286,7 +24307,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="101"/>
+      <c r="A17" s="102"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -24348,7 +24369,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="102" t="s">
+      <c r="A20" s="103" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -24374,7 +24395,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="103"/>
+      <c r="A21" s="104"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -24402,7 +24423,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="103"/>
+      <c r="A22" s="104"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -24430,7 +24451,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="103"/>
+      <c r="A23" s="104"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -24458,7 +24479,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="103"/>
+      <c r="A24" s="104"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -24486,7 +24507,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="104"/>
+      <c r="A25" s="105"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -24548,7 +24569,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="105" t="s">
+      <c r="A28" s="106" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -24574,7 +24595,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="106"/>
+      <c r="A29" s="107"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -24602,7 +24623,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="106"/>
+      <c r="A30" s="107"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -24630,7 +24651,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="106"/>
+      <c r="A31" s="107"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -24658,7 +24679,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="106"/>
+      <c r="A32" s="107"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -24686,7 +24707,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="107"/>
+      <c r="A33" s="108"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -24748,7 +24769,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="108" t="s">
+      <c r="A36" s="109" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -24778,7 +24799,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="109"/>
+      <c r="A37" s="110"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -24806,7 +24827,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="109"/>
+      <c r="A38" s="110"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -24834,7 +24855,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="109"/>
+      <c r="A39" s="110"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -24862,7 +24883,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="109"/>
+      <c r="A40" s="110"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -24890,7 +24911,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="110"/>
+      <c r="A41" s="111"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -24952,7 +24973,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="78" t="s">
+      <c r="A44" s="79" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -24982,7 +25003,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="79"/>
+      <c r="A45" s="80"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -25010,7 +25031,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="79"/>
+      <c r="A46" s="80"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -25038,7 +25059,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="79"/>
+      <c r="A47" s="80"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -25066,7 +25087,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="79"/>
+      <c r="A48" s="80"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -25094,7 +25115,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="80"/>
+      <c r="A49" s="81"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -25156,7 +25177,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="81" t="s">
+      <c r="A52" s="82" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -25186,7 +25207,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="82"/>
+      <c r="A53" s="83"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -25214,7 +25235,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="82"/>
+      <c r="A54" s="83"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -25242,7 +25263,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="82"/>
+      <c r="A55" s="83"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -25270,7 +25291,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="82"/>
+      <c r="A56" s="83"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -25298,7 +25319,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="83"/>
+      <c r="A57" s="84"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -25360,7 +25381,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="84" t="s">
+      <c r="A60" s="85" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -25390,7 +25411,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="85"/>
+      <c r="A61" s="86"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -25418,7 +25439,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="85"/>
+      <c r="A62" s="86"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -25446,7 +25467,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="85"/>
+      <c r="A63" s="86"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -25474,7 +25495,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="85"/>
+      <c r="A64" s="86"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -25502,7 +25523,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="86"/>
+      <c r="A65" s="87"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -25564,7 +25585,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="87" t="s">
+      <c r="A68" s="88" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -25588,13 +25609,13 @@
       <c r="H68" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="J68" s="1" t="str">
+      <c r="J68" s="1">
         <f>IF(OR(Resultados!F68="",Resultados!G68=""),"",IF(AND(F68=Resultados!F68,G68=Resultados!G68),2,IF(((F68&gt;G68)=(Resultados!F68&gt;Resultados!G68))*((F68&lt;G68)=(Resultados!F68&lt;Resultados!G68)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="88"/>
+      <c r="A69" s="89"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -25616,13 +25637,13 @@
       <c r="H69" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="J69" s="1" t="str">
+      <c r="J69" s="1">
         <f>IF(OR(Resultados!F69="",Resultados!G69=""),"",IF(AND(F69=Resultados!F69,G69=Resultados!G69),2,IF(((F69&gt;G69)=(Resultados!F69&gt;Resultados!G69))*((F69&lt;G69)=(Resultados!F69&lt;Resultados!G69)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="88"/>
+      <c r="A70" s="89"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -25650,7 +25671,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="88"/>
+      <c r="A71" s="89"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -25678,7 +25699,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="88"/>
+      <c r="A72" s="89"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -25706,7 +25727,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="89"/>
+      <c r="A73" s="90"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -25768,7 +25789,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="90" t="s">
+      <c r="A76" s="91" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -25792,13 +25813,13 @@
       <c r="H76" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="J76" s="1" t="str">
+      <c r="J76" s="1">
         <f>IF(OR(Resultados!F76="",Resultados!G76=""),"",IF(AND(F76=Resultados!F76,G76=Resultados!G76),2,IF(((F76&gt;G76)=(Resultados!F76&gt;Resultados!G76))*((F76&lt;G76)=(Resultados!F76&lt;Resultados!G76)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="91"/>
+      <c r="A77" s="92"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -25826,7 +25847,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="91"/>
+      <c r="A78" s="92"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -25854,7 +25875,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="91"/>
+      <c r="A79" s="92"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -25882,7 +25903,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="91"/>
+      <c r="A80" s="92"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -25910,7 +25931,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="92"/>
+      <c r="A81" s="93"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -25972,7 +25993,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="93" t="s">
+      <c r="A84" s="94" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -26002,7 +26023,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="94"/>
+      <c r="A85" s="95"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -26030,7 +26051,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="94"/>
+      <c r="A86" s="95"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -26058,7 +26079,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="94"/>
+      <c r="A87" s="95"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -26086,7 +26107,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="94"/>
+      <c r="A88" s="95"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -26114,7 +26135,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="95"/>
+      <c r="A89" s="96"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -26176,7 +26197,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="75" t="s">
+      <c r="A92" s="76" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -26206,7 +26227,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="76"/>
+      <c r="A93" s="77"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -26234,7 +26255,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="76"/>
+      <c r="A94" s="77"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -26262,7 +26283,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="76"/>
+      <c r="A95" s="77"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -26290,7 +26311,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="76"/>
+      <c r="A96" s="77"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -26318,7 +26339,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="77"/>
+      <c r="A97" s="78"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>

--- a/data/Quiniela.xlsx
+++ b/data/Quiniela.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cindy\Desktop\QuinielaMundial\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B61D972A-375D-4215-9A91-FD08ADFD78DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4DB6324-544A-4C53-AB14-09E2F23C5591}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9503E40F-C0E1-49CE-B4EA-3C401754995E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{9503E40F-C0E1-49CE-B4EA-3C401754995E}"/>
   </bookViews>
   <sheets>
     <sheet name="Resultados" sheetId="1" r:id="rId1"/>
@@ -1248,24 +1248,6 @@
     <xf numFmtId="0" fontId="5" fillId="24" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="20" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="20" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="20" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="20" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="20" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="20" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1433,6 +1415,24 @@
     <xf numFmtId="0" fontId="7" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="20" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="20" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="20" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="20" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="20" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="20" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1922,37 +1922,37 @@
   <dimension ref="A1:H97"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="4.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="3.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="3.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="16384" width="11.5546875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="70" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="72"/>
+      <c r="A1" s="64" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="66"/>
     </row>
     <row r="2" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="73"/>
-      <c r="B2" s="74"/>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="75"/>
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="69"/>
     </row>
     <row r="3" spans="1:8" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -1979,7 +1979,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="97" t="s">
+      <c r="A4" s="91" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -2005,7 +2005,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="98"/>
+      <c r="A5" s="92"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -2029,7 +2029,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="98"/>
+      <c r="A6" s="92"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -2049,7 +2049,7 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="98"/>
+      <c r="A7" s="92"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -2069,7 +2069,7 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="98"/>
+      <c r="A8" s="92"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -2089,7 +2089,7 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="99"/>
+      <c r="A9" s="93"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -2143,7 +2143,7 @@
       </c>
     </row>
     <row r="12" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="100" t="s">
+      <c r="A12" s="94" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -2169,7 +2169,7 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="101"/>
+      <c r="A13" s="95"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -2193,7 +2193,7 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="101"/>
+      <c r="A14" s="95"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -2213,7 +2213,7 @@
       </c>
     </row>
     <row r="15" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="101"/>
+      <c r="A15" s="95"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -2233,7 +2233,7 @@
       </c>
     </row>
     <row r="16" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="101"/>
+      <c r="A16" s="95"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -2253,7 +2253,7 @@
       </c>
     </row>
     <row r="17" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="102"/>
+      <c r="A17" s="96"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -2307,7 +2307,7 @@
       </c>
     </row>
     <row r="20" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="103" t="s">
+      <c r="A20" s="97" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -2333,7 +2333,7 @@
       </c>
     </row>
     <row r="21" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="104"/>
+      <c r="A21" s="98"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -2357,7 +2357,7 @@
       </c>
     </row>
     <row r="22" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="104"/>
+      <c r="A22" s="98"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -2377,7 +2377,7 @@
       </c>
     </row>
     <row r="23" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="104"/>
+      <c r="A23" s="98"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -2397,7 +2397,7 @@
       </c>
     </row>
     <row r="24" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="104"/>
+      <c r="A24" s="98"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -2417,7 +2417,7 @@
       </c>
     </row>
     <row r="25" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="105"/>
+      <c r="A25" s="99"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -2471,7 +2471,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="106" t="s">
+      <c r="A28" s="100" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -2497,7 +2497,7 @@
       </c>
     </row>
     <row r="29" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="107"/>
+      <c r="A29" s="101"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -2521,7 +2521,7 @@
       </c>
     </row>
     <row r="30" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="107"/>
+      <c r="A30" s="101"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -2541,7 +2541,7 @@
       </c>
     </row>
     <row r="31" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="107"/>
+      <c r="A31" s="101"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -2561,7 +2561,7 @@
       </c>
     </row>
     <row r="32" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="107"/>
+      <c r="A32" s="101"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -2581,7 +2581,7 @@
       </c>
     </row>
     <row r="33" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="108"/>
+      <c r="A33" s="102"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -2635,7 +2635,7 @@
       </c>
     </row>
     <row r="36" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="109" t="s">
+      <c r="A36" s="103" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -2661,7 +2661,7 @@
       </c>
     </row>
     <row r="37" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="110"/>
+      <c r="A37" s="104"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -2685,7 +2685,7 @@
       </c>
     </row>
     <row r="38" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="110"/>
+      <c r="A38" s="104"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -2705,7 +2705,7 @@
       </c>
     </row>
     <row r="39" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="110"/>
+      <c r="A39" s="104"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -2725,7 +2725,7 @@
       </c>
     </row>
     <row r="40" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="110"/>
+      <c r="A40" s="104"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -2745,7 +2745,7 @@
       </c>
     </row>
     <row r="41" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="111"/>
+      <c r="A41" s="105"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -2799,7 +2799,7 @@
       </c>
     </row>
     <row r="44" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="79" t="s">
+      <c r="A44" s="73" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -2825,7 +2825,7 @@
       </c>
     </row>
     <row r="45" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="80"/>
+      <c r="A45" s="74"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -2849,7 +2849,7 @@
       </c>
     </row>
     <row r="46" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="80"/>
+      <c r="A46" s="74"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -2869,7 +2869,7 @@
       </c>
     </row>
     <row r="47" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="80"/>
+      <c r="A47" s="74"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -2889,7 +2889,7 @@
       </c>
     </row>
     <row r="48" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="80"/>
+      <c r="A48" s="74"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -2909,7 +2909,7 @@
       </c>
     </row>
     <row r="49" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="81"/>
+      <c r="A49" s="75"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -2963,7 +2963,7 @@
       </c>
     </row>
     <row r="52" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="82" t="s">
+      <c r="A52" s="76" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -2989,7 +2989,7 @@
       </c>
     </row>
     <row r="53" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="83"/>
+      <c r="A53" s="77"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -3013,7 +3013,7 @@
       </c>
     </row>
     <row r="54" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="83"/>
+      <c r="A54" s="77"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -3033,7 +3033,7 @@
       </c>
     </row>
     <row r="55" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="83"/>
+      <c r="A55" s="77"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -3053,7 +3053,7 @@
       </c>
     </row>
     <row r="56" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="83"/>
+      <c r="A56" s="77"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -3073,7 +3073,7 @@
       </c>
     </row>
     <row r="57" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="84"/>
+      <c r="A57" s="78"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -3127,7 +3127,7 @@
       </c>
     </row>
     <row r="60" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="85" t="s">
+      <c r="A60" s="79" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -3153,7 +3153,7 @@
       </c>
     </row>
     <row r="61" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="86"/>
+      <c r="A61" s="80"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -3177,7 +3177,7 @@
       </c>
     </row>
     <row r="62" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="86"/>
+      <c r="A62" s="80"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -3197,7 +3197,7 @@
       </c>
     </row>
     <row r="63" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="86"/>
+      <c r="A63" s="80"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -3217,7 +3217,7 @@
       </c>
     </row>
     <row r="64" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="86"/>
+      <c r="A64" s="80"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -3237,7 +3237,7 @@
       </c>
     </row>
     <row r="65" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="87"/>
+      <c r="A65" s="81"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -3291,7 +3291,7 @@
       </c>
     </row>
     <row r="68" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="88" t="s">
+      <c r="A68" s="82" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -3317,7 +3317,7 @@
       </c>
     </row>
     <row r="69" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="89"/>
+      <c r="A69" s="83"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -3341,7 +3341,7 @@
       </c>
     </row>
     <row r="70" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="89"/>
+      <c r="A70" s="83"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -3361,7 +3361,7 @@
       </c>
     </row>
     <row r="71" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="89"/>
+      <c r="A71" s="83"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -3381,7 +3381,7 @@
       </c>
     </row>
     <row r="72" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="89"/>
+      <c r="A72" s="83"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -3401,7 +3401,7 @@
       </c>
     </row>
     <row r="73" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="90"/>
+      <c r="A73" s="84"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -3455,7 +3455,7 @@
       </c>
     </row>
     <row r="76" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="91" t="s">
+      <c r="A76" s="85" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -3481,7 +3481,7 @@
       </c>
     </row>
     <row r="77" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="92"/>
+      <c r="A77" s="86"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -3491,17 +3491,21 @@
       <c r="D77" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="E77" s="10" t="s">
+      <c r="E77" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="F77" s="26"/>
-      <c r="G77" s="26"/>
+      <c r="F77" s="62">
+        <v>3</v>
+      </c>
+      <c r="G77" s="62">
+        <v>1</v>
+      </c>
       <c r="H77" s="21" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="78" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="92"/>
+      <c r="A78" s="86"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -3521,7 +3525,7 @@
       </c>
     </row>
     <row r="79" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="92"/>
+      <c r="A79" s="86"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -3541,7 +3545,7 @@
       </c>
     </row>
     <row r="80" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="92"/>
+      <c r="A80" s="86"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -3561,7 +3565,7 @@
       </c>
     </row>
     <row r="81" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="93"/>
+      <c r="A81" s="87"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -3615,7 +3619,7 @@
       </c>
     </row>
     <row r="84" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="94" t="s">
+      <c r="A84" s="88" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -3637,7 +3641,7 @@
       </c>
     </row>
     <row r="85" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="95"/>
+      <c r="A85" s="89"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -3657,7 +3661,7 @@
       </c>
     </row>
     <row r="86" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="95"/>
+      <c r="A86" s="89"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -3677,7 +3681,7 @@
       </c>
     </row>
     <row r="87" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="95"/>
+      <c r="A87" s="89"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -3697,7 +3701,7 @@
       </c>
     </row>
     <row r="88" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="95"/>
+      <c r="A88" s="89"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -3717,7 +3721,7 @@
       </c>
     </row>
     <row r="89" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="96"/>
+      <c r="A89" s="90"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -3771,7 +3775,7 @@
       </c>
     </row>
     <row r="92" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="76" t="s">
+      <c r="A92" s="70" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -3793,7 +3797,7 @@
       </c>
     </row>
     <row r="93" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="77"/>
+      <c r="A93" s="71"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -3813,7 +3817,7 @@
       </c>
     </row>
     <row r="94" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="77"/>
+      <c r="A94" s="71"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -3833,7 +3837,7 @@
       </c>
     </row>
     <row r="95" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="77"/>
+      <c r="A95" s="71"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -3853,7 +3857,7 @@
       </c>
     </row>
     <row r="96" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="77"/>
+      <c r="A96" s="71"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -3873,7 +3877,7 @@
       </c>
     </row>
     <row r="97" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="78"/>
+      <c r="A97" s="72"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -3933,26 +3937,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="70" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="72"/>
+      <c r="A1" s="64" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="66"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="73"/>
-      <c r="B2" s="74"/>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="75"/>
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="69"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -3985,7 +3989,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="97" t="s">
+      <c r="A4" s="91" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -4015,7 +4019,7 @@
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="98"/>
+      <c r="A5" s="92"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -4039,7 +4043,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="98"/>
+      <c r="A6" s="92"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -4067,7 +4071,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="98"/>
+      <c r="A7" s="92"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -4095,7 +4099,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="98"/>
+      <c r="A8" s="92"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -4123,7 +4127,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="99"/>
+      <c r="A9" s="93"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -4185,7 +4189,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="100" t="s">
+      <c r="A12" s="94" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -4211,7 +4215,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="101"/>
+      <c r="A13" s="95"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -4235,7 +4239,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="101"/>
+      <c r="A14" s="95"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -4263,7 +4267,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="101"/>
+      <c r="A15" s="95"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -4291,7 +4295,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="101"/>
+      <c r="A16" s="95"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -4319,7 +4323,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="102"/>
+      <c r="A17" s="96"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -4381,7 +4385,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="103" t="s">
+      <c r="A20" s="97" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -4407,7 +4411,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="104"/>
+      <c r="A21" s="98"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -4435,7 +4439,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="104"/>
+      <c r="A22" s="98"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -4463,7 +4467,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="104"/>
+      <c r="A23" s="98"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -4491,7 +4495,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="104"/>
+      <c r="A24" s="98"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -4519,7 +4523,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="105"/>
+      <c r="A25" s="99"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -4581,7 +4585,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="106" t="s">
+      <c r="A28" s="100" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -4607,7 +4611,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="107"/>
+      <c r="A29" s="101"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -4635,7 +4639,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="107"/>
+      <c r="A30" s="101"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -4663,7 +4667,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="107"/>
+      <c r="A31" s="101"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -4691,7 +4695,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="107"/>
+      <c r="A32" s="101"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -4719,7 +4723,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="108"/>
+      <c r="A33" s="102"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -4781,7 +4785,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="109" t="s">
+      <c r="A36" s="103" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -4811,7 +4815,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="110"/>
+      <c r="A37" s="104"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -4839,7 +4843,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="110"/>
+      <c r="A38" s="104"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -4867,7 +4871,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="110"/>
+      <c r="A39" s="104"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -4895,7 +4899,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="110"/>
+      <c r="A40" s="104"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -4923,7 +4927,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="111"/>
+      <c r="A41" s="105"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -4985,7 +4989,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="79" t="s">
+      <c r="A44" s="73" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -5015,7 +5019,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="80"/>
+      <c r="A45" s="74"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -5043,7 +5047,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="80"/>
+      <c r="A46" s="74"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -5071,7 +5075,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="80"/>
+      <c r="A47" s="74"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -5099,7 +5103,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="80"/>
+      <c r="A48" s="74"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -5127,7 +5131,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="81"/>
+      <c r="A49" s="75"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -5189,7 +5193,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="82" t="s">
+      <c r="A52" s="76" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -5219,7 +5223,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="83"/>
+      <c r="A53" s="77"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -5247,7 +5251,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="83"/>
+      <c r="A54" s="77"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -5275,7 +5279,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="83"/>
+      <c r="A55" s="77"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -5303,7 +5307,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="83"/>
+      <c r="A56" s="77"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -5331,7 +5335,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="84"/>
+      <c r="A57" s="78"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -5393,7 +5397,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="85" t="s">
+      <c r="A60" s="79" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -5423,7 +5427,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="86"/>
+      <c r="A61" s="80"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -5451,7 +5455,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="86"/>
+      <c r="A62" s="80"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -5479,7 +5483,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="86"/>
+      <c r="A63" s="80"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -5507,7 +5511,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="86"/>
+      <c r="A64" s="80"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -5535,7 +5539,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="87"/>
+      <c r="A65" s="81"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -5597,7 +5601,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="88" t="s">
+      <c r="A68" s="82" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -5627,7 +5631,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="89"/>
+      <c r="A69" s="83"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -5655,7 +5659,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="89"/>
+      <c r="A70" s="83"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -5683,7 +5687,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="89"/>
+      <c r="A71" s="83"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -5711,7 +5715,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="89"/>
+      <c r="A72" s="83"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -5739,7 +5743,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="90"/>
+      <c r="A73" s="84"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -5801,7 +5805,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="91" t="s">
+      <c r="A76" s="85" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -5831,7 +5835,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="92"/>
+      <c r="A77" s="86"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -5853,13 +5857,13 @@
       <c r="H77" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="J77" s="1" t="str">
+      <c r="J77" s="1">
         <f>IF(OR(Resultados!F77="",Resultados!G77=""),"",IF(AND(F77=Resultados!F77,G77=Resultados!G77),2,IF(((F77&gt;G77)=(Resultados!F77&gt;Resultados!G77))*((F77&lt;G77)=(Resultados!F77&lt;Resultados!G77)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="92"/>
+      <c r="A78" s="86"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -5887,7 +5891,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="92"/>
+      <c r="A79" s="86"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -5915,7 +5919,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="92"/>
+      <c r="A80" s="86"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -5943,7 +5947,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="93"/>
+      <c r="A81" s="87"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -6005,7 +6009,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="94" t="s">
+      <c r="A84" s="88" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -6035,7 +6039,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="95"/>
+      <c r="A85" s="89"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -6063,7 +6067,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="95"/>
+      <c r="A86" s="89"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -6091,7 +6095,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="95"/>
+      <c r="A87" s="89"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -6119,7 +6123,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="95"/>
+      <c r="A88" s="89"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -6147,7 +6151,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="96"/>
+      <c r="A89" s="90"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -6209,7 +6213,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="76" t="s">
+      <c r="A92" s="70" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -6239,7 +6243,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="77"/>
+      <c r="A93" s="71"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -6267,7 +6271,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="77"/>
+      <c r="A94" s="71"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -6295,7 +6299,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="77"/>
+      <c r="A95" s="71"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -6323,7 +6327,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="77"/>
+      <c r="A96" s="71"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -6351,7 +6355,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="78"/>
+      <c r="A97" s="72"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -6421,26 +6425,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="70" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="72"/>
+      <c r="A1" s="64" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="66"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="73"/>
-      <c r="B2" s="74"/>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="75"/>
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="69"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -6473,7 +6477,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="97" t="s">
+      <c r="A4" s="91" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -6499,11 +6503,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="98"/>
+      <c r="A5" s="92"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -6527,7 +6531,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="98"/>
+      <c r="A6" s="92"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -6555,7 +6559,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="98"/>
+      <c r="A7" s="92"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -6583,7 +6587,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="98"/>
+      <c r="A8" s="92"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -6611,7 +6615,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="99"/>
+      <c r="A9" s="93"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -6673,7 +6677,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="100" t="s">
+      <c r="A12" s="94" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -6699,7 +6703,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="101"/>
+      <c r="A13" s="95"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -6723,7 +6727,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="101"/>
+      <c r="A14" s="95"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -6751,7 +6755,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="101"/>
+      <c r="A15" s="95"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -6779,7 +6783,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="101"/>
+      <c r="A16" s="95"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -6807,7 +6811,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="102"/>
+      <c r="A17" s="96"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -6869,7 +6873,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="103" t="s">
+      <c r="A20" s="97" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -6895,7 +6899,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="104"/>
+      <c r="A21" s="98"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -6923,7 +6927,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="104"/>
+      <c r="A22" s="98"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -6951,7 +6955,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="104"/>
+      <c r="A23" s="98"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -6979,7 +6983,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="104"/>
+      <c r="A24" s="98"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -7007,7 +7011,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="105"/>
+      <c r="A25" s="99"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -7069,7 +7073,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="106" t="s">
+      <c r="A28" s="100" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -7095,7 +7099,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="107"/>
+      <c r="A29" s="101"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -7123,7 +7127,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="107"/>
+      <c r="A30" s="101"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -7151,7 +7155,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="107"/>
+      <c r="A31" s="101"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -7179,7 +7183,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="107"/>
+      <c r="A32" s="101"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -7207,7 +7211,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="108"/>
+      <c r="A33" s="102"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -7269,7 +7273,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="109" t="s">
+      <c r="A36" s="103" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -7299,7 +7303,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="110"/>
+      <c r="A37" s="104"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -7327,7 +7331,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="110"/>
+      <c r="A38" s="104"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -7355,7 +7359,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="110"/>
+      <c r="A39" s="104"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -7383,7 +7387,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="110"/>
+      <c r="A40" s="104"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -7411,7 +7415,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="111"/>
+      <c r="A41" s="105"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -7473,7 +7477,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="79" t="s">
+      <c r="A44" s="73" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -7503,7 +7507,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="80"/>
+      <c r="A45" s="74"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -7531,7 +7535,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="80"/>
+      <c r="A46" s="74"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -7559,7 +7563,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="80"/>
+      <c r="A47" s="74"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -7587,7 +7591,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="80"/>
+      <c r="A48" s="74"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -7615,7 +7619,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="81"/>
+      <c r="A49" s="75"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -7677,7 +7681,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="82" t="s">
+      <c r="A52" s="76" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -7707,7 +7711,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="83"/>
+      <c r="A53" s="77"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -7735,7 +7739,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="83"/>
+      <c r="A54" s="77"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -7763,7 +7767,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="83"/>
+      <c r="A55" s="77"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -7791,7 +7795,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="83"/>
+      <c r="A56" s="77"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -7819,7 +7823,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="84"/>
+      <c r="A57" s="78"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -7881,7 +7885,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="85" t="s">
+      <c r="A60" s="79" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -7911,7 +7915,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="86"/>
+      <c r="A61" s="80"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -7939,7 +7943,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="86"/>
+      <c r="A62" s="80"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -7967,7 +7971,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="86"/>
+      <c r="A63" s="80"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -7995,7 +7999,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="86"/>
+      <c r="A64" s="80"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -8023,7 +8027,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="87"/>
+      <c r="A65" s="81"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -8085,7 +8089,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="88" t="s">
+      <c r="A68" s="82" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -8115,7 +8119,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="89"/>
+      <c r="A69" s="83"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -8143,7 +8147,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="89"/>
+      <c r="A70" s="83"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -8171,7 +8175,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="89"/>
+      <c r="A71" s="83"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -8199,7 +8203,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="89"/>
+      <c r="A72" s="83"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -8227,7 +8231,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="90"/>
+      <c r="A73" s="84"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -8289,7 +8293,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="91" t="s">
+      <c r="A76" s="85" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -8319,7 +8323,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="92"/>
+      <c r="A77" s="86"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -8341,13 +8345,13 @@
       <c r="H77" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="J77" s="1" t="str">
+      <c r="J77" s="1">
         <f>IF(OR(Resultados!F77="",Resultados!G77=""),"",IF(AND(F77=Resultados!F77,G77=Resultados!G77),2,IF(((F77&gt;G77)=(Resultados!F77&gt;Resultados!G77))*((F77&lt;G77)=(Resultados!F77&lt;Resultados!G77)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="92"/>
+      <c r="A78" s="86"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -8375,7 +8379,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="92"/>
+      <c r="A79" s="86"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -8403,7 +8407,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="92"/>
+      <c r="A80" s="86"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -8431,7 +8435,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="93"/>
+      <c r="A81" s="87"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -8493,7 +8497,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="94" t="s">
+      <c r="A84" s="88" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -8523,7 +8527,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="95"/>
+      <c r="A85" s="89"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -8551,7 +8555,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="95"/>
+      <c r="A86" s="89"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -8579,7 +8583,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="95"/>
+      <c r="A87" s="89"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -8607,7 +8611,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="95"/>
+      <c r="A88" s="89"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -8635,7 +8639,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="96"/>
+      <c r="A89" s="90"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -8697,7 +8701,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="76" t="s">
+      <c r="A92" s="70" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -8727,7 +8731,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="77"/>
+      <c r="A93" s="71"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -8755,7 +8759,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="77"/>
+      <c r="A94" s="71"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -8783,7 +8787,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="77"/>
+      <c r="A95" s="71"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -8811,7 +8815,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="77"/>
+      <c r="A96" s="71"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -8839,7 +8843,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="78"/>
+      <c r="A97" s="72"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -8904,18 +8908,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D1" s="64" t="s">
+      <c r="D1" s="106" t="s">
         <v>74</v>
       </c>
-      <c r="E1" s="65"/>
-      <c r="F1" s="66"/>
+      <c r="E1" s="107"/>
+      <c r="F1" s="108"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D2" s="67" t="s">
+      <c r="D2" s="109" t="s">
         <v>75</v>
       </c>
-      <c r="E2" s="68"/>
-      <c r="F2" s="69"/>
+      <c r="E2" s="110"/>
+      <c r="F2" s="111"/>
     </row>
     <row r="4" spans="1:6" s="29" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="57" t="s">
@@ -8940,14 +8944,14 @@
       </c>
       <c r="B5" s="58">
         <f>Cindy!L4</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" s="59">
         <v>1</v>
       </c>
       <c r="E5" s="59" t="str" cm="1">
         <f t="array" ref="E5:F13">_xlfn._xlws.SORT(A5:B13,2,-1)</f>
-        <v>Lennon</v>
+        <v>Wendy</v>
       </c>
       <c r="F5" s="59">
         <v>11</v>
@@ -8959,16 +8963,16 @@
       </c>
       <c r="B6" s="58">
         <f>Wendy!L4</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D6" s="55">
         <v>2</v>
       </c>
       <c r="E6" s="55" t="str">
-        <v>Wendy</v>
+        <v>Lennon</v>
       </c>
       <c r="F6" s="55">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -8977,7 +8981,7 @@
       </c>
       <c r="B7" s="58">
         <f>Jimmy!L4</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" s="56">
         <v>3</v>
@@ -8986,7 +8990,7 @@
         <v>Erik</v>
       </c>
       <c r="F7" s="56">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -9004,7 +9008,7 @@
         <v>Yulian</v>
       </c>
       <c r="F8" s="28">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -9013,7 +9017,7 @@
       </c>
       <c r="B9" s="58">
         <f>Erik!L4</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" s="28">
         <v>5</v>
@@ -9022,7 +9026,7 @@
         <v>Packy</v>
       </c>
       <c r="F9" s="28">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -9040,7 +9044,7 @@
         <v>Bere</v>
       </c>
       <c r="F10" s="28">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -9049,7 +9053,7 @@
       </c>
       <c r="B11" s="58">
         <f>Yulian!L4</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" s="28">
         <v>7</v>
@@ -9058,7 +9062,7 @@
         <v>Jimmy</v>
       </c>
       <c r="F11" s="28">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -9067,7 +9071,7 @@
       </c>
       <c r="B12" s="58">
         <f>Packy!L4</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" s="28">
         <v>8</v>
@@ -9076,7 +9080,7 @@
         <v>Cindy</v>
       </c>
       <c r="F12" s="28">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -9085,7 +9089,7 @@
       </c>
       <c r="B13" s="58">
         <f>Bere!L4</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D13" s="28">
         <v>9</v>
@@ -9128,26 +9132,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="70" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="72"/>
+      <c r="A1" s="64" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="66"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="73"/>
-      <c r="B2" s="74"/>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="75"/>
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="69"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="31"/>
@@ -9206,7 +9210,7 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -11048,9 +11052,9 @@
       <c r="H77" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="J77" s="1" t="str">
+      <c r="J77" s="1">
         <f>IF(OR(Resultados!F77="",Resultados!G77=""),"",IF(AND(F77=Resultados!F77,G77=Resultados!G77),2,IF(((F77&gt;G77)=(Resultados!F77&gt;Resultados!G77))*((F77&lt;G77)=(Resultados!F77&lt;Resultados!G77)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -11617,26 +11621,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="70" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="72"/>
+      <c r="A1" s="64" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="66"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="73"/>
-      <c r="B2" s="74"/>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="75"/>
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="69"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="31"/>
@@ -11695,7 +11699,7 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -13537,9 +13541,9 @@
       <c r="H77" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="J77" s="1" t="str">
+      <c r="J77" s="1">
         <f>IF(OR(Resultados!F77="",Resultados!G77=""),"",IF(AND(F77=Resultados!F77,G77=Resultados!G77),2,IF(((F77&gt;G77)=(Resultados!F77&gt;Resultados!G77))*((F77&lt;G77)=(Resultados!F77&lt;Resultados!G77)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -14105,26 +14109,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="70" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="72"/>
+      <c r="A1" s="64" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="66"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="73"/>
-      <c r="B2" s="74"/>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="75"/>
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="69"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -14157,7 +14161,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="97" t="s">
+      <c r="A4" s="91" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -14183,11 +14187,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="98"/>
+      <c r="A5" s="92"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -14211,7 +14215,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="98"/>
+      <c r="A6" s="92"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -14239,7 +14243,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="98"/>
+      <c r="A7" s="92"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -14267,7 +14271,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="98"/>
+      <c r="A8" s="92"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -14295,7 +14299,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="99"/>
+      <c r="A9" s="93"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -14357,7 +14361,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="100" t="s">
+      <c r="A12" s="94" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -14383,7 +14387,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="101"/>
+      <c r="A13" s="95"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -14407,7 +14411,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="101"/>
+      <c r="A14" s="95"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -14435,7 +14439,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="101"/>
+      <c r="A15" s="95"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -14463,7 +14467,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="101"/>
+      <c r="A16" s="95"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -14491,7 +14495,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="102"/>
+      <c r="A17" s="96"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -14553,7 +14557,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="103" t="s">
+      <c r="A20" s="97" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -14579,7 +14583,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="104"/>
+      <c r="A21" s="98"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -14607,7 +14611,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="104"/>
+      <c r="A22" s="98"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -14635,7 +14639,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="104"/>
+      <c r="A23" s="98"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -14663,7 +14667,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="104"/>
+      <c r="A24" s="98"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -14691,7 +14695,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="105"/>
+      <c r="A25" s="99"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -14753,7 +14757,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="106" t="s">
+      <c r="A28" s="100" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -14779,7 +14783,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="107"/>
+      <c r="A29" s="101"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -14807,7 +14811,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="107"/>
+      <c r="A30" s="101"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -14835,7 +14839,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="107"/>
+      <c r="A31" s="101"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -14863,7 +14867,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="107"/>
+      <c r="A32" s="101"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -14891,7 +14895,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="108"/>
+      <c r="A33" s="102"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -14953,7 +14957,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="109" t="s">
+      <c r="A36" s="103" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -14983,7 +14987,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="110"/>
+      <c r="A37" s="104"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -15011,7 +15015,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="110"/>
+      <c r="A38" s="104"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -15039,7 +15043,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="110"/>
+      <c r="A39" s="104"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -15067,7 +15071,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="110"/>
+      <c r="A40" s="104"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -15095,7 +15099,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="111"/>
+      <c r="A41" s="105"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -15157,7 +15161,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="79" t="s">
+      <c r="A44" s="73" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -15187,7 +15191,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="80"/>
+      <c r="A45" s="74"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -15215,7 +15219,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="80"/>
+      <c r="A46" s="74"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -15243,7 +15247,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="80"/>
+      <c r="A47" s="74"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -15271,7 +15275,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="80"/>
+      <c r="A48" s="74"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -15299,7 +15303,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="81"/>
+      <c r="A49" s="75"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -15361,7 +15365,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="82" t="s">
+      <c r="A52" s="76" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -15391,7 +15395,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="83"/>
+      <c r="A53" s="77"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -15419,7 +15423,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="83"/>
+      <c r="A54" s="77"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -15447,7 +15451,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="83"/>
+      <c r="A55" s="77"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -15475,7 +15479,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="83"/>
+      <c r="A56" s="77"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -15503,7 +15507,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="84"/>
+      <c r="A57" s="78"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -15565,7 +15569,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="85" t="s">
+      <c r="A60" s="79" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -15595,7 +15599,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="86"/>
+      <c r="A61" s="80"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -15623,7 +15627,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="86"/>
+      <c r="A62" s="80"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -15651,7 +15655,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="86"/>
+      <c r="A63" s="80"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -15679,7 +15683,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="86"/>
+      <c r="A64" s="80"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -15707,7 +15711,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="87"/>
+      <c r="A65" s="81"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -15769,7 +15773,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="88" t="s">
+      <c r="A68" s="82" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -15799,7 +15803,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="89"/>
+      <c r="A69" s="83"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -15827,7 +15831,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="89"/>
+      <c r="A70" s="83"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -15855,7 +15859,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="89"/>
+      <c r="A71" s="83"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -15883,7 +15887,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="89"/>
+      <c r="A72" s="83"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -15911,7 +15915,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="90"/>
+      <c r="A73" s="84"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -15973,7 +15977,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="91" t="s">
+      <c r="A76" s="85" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -16003,7 +16007,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="92"/>
+      <c r="A77" s="86"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -16025,13 +16029,13 @@
       <c r="H77" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="J77" s="1" t="str">
+      <c r="J77" s="1">
         <f>IF(OR(Resultados!F77="",Resultados!G77=""),"",IF(AND(F77=Resultados!F77,G77=Resultados!G77),2,IF(((F77&gt;G77)=(Resultados!F77&gt;Resultados!G77))*((F77&lt;G77)=(Resultados!F77&lt;Resultados!G77)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="92"/>
+      <c r="A78" s="86"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -16059,7 +16063,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="92"/>
+      <c r="A79" s="86"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -16087,7 +16091,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="92"/>
+      <c r="A80" s="86"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -16115,7 +16119,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="93"/>
+      <c r="A81" s="87"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -16177,7 +16181,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="94" t="s">
+      <c r="A84" s="88" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -16207,7 +16211,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="95"/>
+      <c r="A85" s="89"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -16235,7 +16239,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="95"/>
+      <c r="A86" s="89"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -16263,7 +16267,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="95"/>
+      <c r="A87" s="89"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -16291,7 +16295,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="95"/>
+      <c r="A88" s="89"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -16319,7 +16323,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="96"/>
+      <c r="A89" s="90"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -16381,7 +16385,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="76" t="s">
+      <c r="A92" s="70" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -16411,7 +16415,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="77"/>
+      <c r="A93" s="71"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -16439,7 +16443,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="77"/>
+      <c r="A94" s="71"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -16467,7 +16471,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="77"/>
+      <c r="A95" s="71"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -16495,7 +16499,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="77"/>
+      <c r="A96" s="71"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -16523,7 +16527,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="78"/>
+      <c r="A97" s="72"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -16593,26 +16597,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="70" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="72"/>
+      <c r="A1" s="64" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="66"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="73"/>
-      <c r="B2" s="74"/>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="75"/>
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="69"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -16645,7 +16649,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="97" t="s">
+      <c r="A4" s="91" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -16671,11 +16675,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="98"/>
+      <c r="A5" s="92"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -16699,7 +16703,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="98"/>
+      <c r="A6" s="92"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -16727,7 +16731,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="98"/>
+      <c r="A7" s="92"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -16755,7 +16759,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="98"/>
+      <c r="A8" s="92"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -16783,7 +16787,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="99"/>
+      <c r="A9" s="93"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -16845,7 +16849,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="100" t="s">
+      <c r="A12" s="94" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -16871,7 +16875,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="101"/>
+      <c r="A13" s="95"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -16895,7 +16899,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="101"/>
+      <c r="A14" s="95"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -16923,7 +16927,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="101"/>
+      <c r="A15" s="95"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -16951,7 +16955,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="101"/>
+      <c r="A16" s="95"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -16979,7 +16983,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="102"/>
+      <c r="A17" s="96"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -17041,7 +17045,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="103" t="s">
+      <c r="A20" s="97" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -17067,7 +17071,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="104"/>
+      <c r="A21" s="98"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -17095,7 +17099,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="104"/>
+      <c r="A22" s="98"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -17123,7 +17127,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="104"/>
+      <c r="A23" s="98"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -17151,7 +17155,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="104"/>
+      <c r="A24" s="98"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -17179,7 +17183,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="105"/>
+      <c r="A25" s="99"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -17241,7 +17245,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="106" t="s">
+      <c r="A28" s="100" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -17267,7 +17271,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="107"/>
+      <c r="A29" s="101"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -17295,7 +17299,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="107"/>
+      <c r="A30" s="101"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -17323,7 +17327,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="107"/>
+      <c r="A31" s="101"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -17351,7 +17355,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="107"/>
+      <c r="A32" s="101"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -17379,7 +17383,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="108"/>
+      <c r="A33" s="102"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -17441,7 +17445,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="109" t="s">
+      <c r="A36" s="103" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -17471,7 +17475,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="110"/>
+      <c r="A37" s="104"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -17499,7 +17503,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="110"/>
+      <c r="A38" s="104"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -17527,7 +17531,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="110"/>
+      <c r="A39" s="104"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -17555,7 +17559,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="110"/>
+      <c r="A40" s="104"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -17583,7 +17587,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="111"/>
+      <c r="A41" s="105"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -17645,7 +17649,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="79" t="s">
+      <c r="A44" s="73" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -17675,7 +17679,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="80"/>
+      <c r="A45" s="74"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -17703,7 +17707,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="80"/>
+      <c r="A46" s="74"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -17731,7 +17735,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="80"/>
+      <c r="A47" s="74"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -17759,7 +17763,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="80"/>
+      <c r="A48" s="74"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -17787,7 +17791,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="81"/>
+      <c r="A49" s="75"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -17849,7 +17853,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="82" t="s">
+      <c r="A52" s="76" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -17879,7 +17883,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="83"/>
+      <c r="A53" s="77"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -17907,7 +17911,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="83"/>
+      <c r="A54" s="77"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -17935,7 +17939,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="83"/>
+      <c r="A55" s="77"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -17963,7 +17967,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="83"/>
+      <c r="A56" s="77"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -17991,7 +17995,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="84"/>
+      <c r="A57" s="78"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -18053,7 +18057,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="85" t="s">
+      <c r="A60" s="79" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -18083,7 +18087,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="86"/>
+      <c r="A61" s="80"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -18111,7 +18115,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="86"/>
+      <c r="A62" s="80"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -18139,7 +18143,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="86"/>
+      <c r="A63" s="80"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -18167,7 +18171,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="86"/>
+      <c r="A64" s="80"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -18195,7 +18199,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="87"/>
+      <c r="A65" s="81"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -18257,7 +18261,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="88" t="s">
+      <c r="A68" s="82" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -18287,7 +18291,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="89"/>
+      <c r="A69" s="83"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -18315,7 +18319,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="89"/>
+      <c r="A70" s="83"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -18343,7 +18347,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="89"/>
+      <c r="A71" s="83"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -18371,7 +18375,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="89"/>
+      <c r="A72" s="83"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -18399,7 +18403,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="90"/>
+      <c r="A73" s="84"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -18461,7 +18465,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="91" t="s">
+      <c r="A76" s="85" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -18491,7 +18495,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="92"/>
+      <c r="A77" s="86"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -18513,13 +18517,13 @@
       <c r="H77" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="J77" s="1" t="str">
+      <c r="J77" s="1">
         <f>IF(OR(Resultados!F77="",Resultados!G77=""),"",IF(AND(F77=Resultados!F77,G77=Resultados!G77),2,IF(((F77&gt;G77)=(Resultados!F77&gt;Resultados!G77))*((F77&lt;G77)=(Resultados!F77&lt;Resultados!G77)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="92"/>
+      <c r="A78" s="86"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -18547,7 +18551,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="92"/>
+      <c r="A79" s="86"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -18575,7 +18579,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="92"/>
+      <c r="A80" s="86"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -18603,7 +18607,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="93"/>
+      <c r="A81" s="87"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -18665,7 +18669,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="94" t="s">
+      <c r="A84" s="88" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -18695,7 +18699,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="95"/>
+      <c r="A85" s="89"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -18723,7 +18727,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="95"/>
+      <c r="A86" s="89"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -18751,7 +18755,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="95"/>
+      <c r="A87" s="89"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -18779,7 +18783,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="95"/>
+      <c r="A88" s="89"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -18807,7 +18811,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="96"/>
+      <c r="A89" s="90"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -18869,7 +18873,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="76" t="s">
+      <c r="A92" s="70" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -18899,7 +18903,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="77"/>
+      <c r="A93" s="71"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -18927,7 +18931,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="77"/>
+      <c r="A94" s="71"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -18955,7 +18959,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="77"/>
+      <c r="A95" s="71"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -18983,7 +18987,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="77"/>
+      <c r="A96" s="71"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -19011,7 +19015,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="78"/>
+      <c r="A97" s="72"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -19081,26 +19085,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="70" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="72"/>
+      <c r="A1" s="64" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="66"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="73"/>
-      <c r="B2" s="74"/>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="75"/>
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="69"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -19133,7 +19137,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="97" t="s">
+      <c r="A4" s="91" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -19159,11 +19163,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="98"/>
+      <c r="A5" s="92"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -19187,7 +19191,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="98"/>
+      <c r="A6" s="92"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -19215,7 +19219,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="98"/>
+      <c r="A7" s="92"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -19243,7 +19247,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="98"/>
+      <c r="A8" s="92"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -19271,7 +19275,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="99"/>
+      <c r="A9" s="93"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -19333,7 +19337,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="100" t="s">
+      <c r="A12" s="94" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -19359,7 +19363,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="101"/>
+      <c r="A13" s="95"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -19383,7 +19387,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="101"/>
+      <c r="A14" s="95"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -19411,7 +19415,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="101"/>
+      <c r="A15" s="95"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -19439,7 +19443,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="101"/>
+      <c r="A16" s="95"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -19467,7 +19471,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="102"/>
+      <c r="A17" s="96"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -19529,7 +19533,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="103" t="s">
+      <c r="A20" s="97" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -19555,7 +19559,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="104"/>
+      <c r="A21" s="98"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -19583,7 +19587,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="104"/>
+      <c r="A22" s="98"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -19611,7 +19615,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="104"/>
+      <c r="A23" s="98"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -19639,7 +19643,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="104"/>
+      <c r="A24" s="98"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -19667,7 +19671,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="105"/>
+      <c r="A25" s="99"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -19729,7 +19733,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="106" t="s">
+      <c r="A28" s="100" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -19755,7 +19759,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="107"/>
+      <c r="A29" s="101"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -19783,7 +19787,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="107"/>
+      <c r="A30" s="101"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -19811,7 +19815,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="107"/>
+      <c r="A31" s="101"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -19839,7 +19843,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="107"/>
+      <c r="A32" s="101"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -19863,7 +19867,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="108"/>
+      <c r="A33" s="102"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -19921,7 +19925,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="109" t="s">
+      <c r="A36" s="103" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -19951,7 +19955,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="110"/>
+      <c r="A37" s="104"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -19979,7 +19983,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="110"/>
+      <c r="A38" s="104"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -20003,7 +20007,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="110"/>
+      <c r="A39" s="104"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -20027,7 +20031,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="110"/>
+      <c r="A40" s="104"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -20051,7 +20055,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="111"/>
+      <c r="A41" s="105"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -20109,7 +20113,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="79" t="s">
+      <c r="A44" s="73" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -20139,7 +20143,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="80"/>
+      <c r="A45" s="74"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -20167,7 +20171,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="80"/>
+      <c r="A46" s="74"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -20191,7 +20195,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="80"/>
+      <c r="A47" s="74"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -20215,7 +20219,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="80"/>
+      <c r="A48" s="74"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -20239,7 +20243,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="81"/>
+      <c r="A49" s="75"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -20297,7 +20301,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="82" t="s">
+      <c r="A52" s="76" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -20327,7 +20331,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="83"/>
+      <c r="A53" s="77"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -20355,7 +20359,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="83"/>
+      <c r="A54" s="77"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -20379,7 +20383,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="83"/>
+      <c r="A55" s="77"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -20403,7 +20407,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="83"/>
+      <c r="A56" s="77"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -20427,7 +20431,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="84"/>
+      <c r="A57" s="78"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -20485,7 +20489,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="85" t="s">
+      <c r="A60" s="79" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -20515,7 +20519,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="86"/>
+      <c r="A61" s="80"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -20543,7 +20547,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="86"/>
+      <c r="A62" s="80"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -20567,7 +20571,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="86"/>
+      <c r="A63" s="80"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -20591,7 +20595,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="86"/>
+      <c r="A64" s="80"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -20615,7 +20619,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="87"/>
+      <c r="A65" s="81"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -20673,7 +20677,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="88" t="s">
+      <c r="A68" s="82" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -20703,7 +20707,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="89"/>
+      <c r="A69" s="83"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -20731,7 +20735,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="89"/>
+      <c r="A70" s="83"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -20755,7 +20759,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="89"/>
+      <c r="A71" s="83"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -20779,7 +20783,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="89"/>
+      <c r="A72" s="83"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -20803,7 +20807,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="90"/>
+      <c r="A73" s="84"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -20861,7 +20865,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="91" t="s">
+      <c r="A76" s="85" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -20891,7 +20895,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="92"/>
+      <c r="A77" s="86"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -20913,13 +20917,13 @@
       <c r="H77" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="J77" s="1" t="str">
+      <c r="J77" s="1">
         <f>IF(OR(Resultados!F77="",Resultados!G77=""),"",IF(AND(F77=Resultados!F77,G77=Resultados!G77),2,IF(((F77&gt;G77)=(Resultados!F77&gt;Resultados!G77))*((F77&lt;G77)=(Resultados!F77&lt;Resultados!G77)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="92"/>
+      <c r="A78" s="86"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -20943,7 +20947,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="92"/>
+      <c r="A79" s="86"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -20967,7 +20971,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="92"/>
+      <c r="A80" s="86"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -20991,7 +20995,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="93"/>
+      <c r="A81" s="87"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -21049,7 +21053,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="94" t="s">
+      <c r="A84" s="88" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -21079,7 +21083,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="95"/>
+      <c r="A85" s="89"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -21107,7 +21111,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="95"/>
+      <c r="A86" s="89"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -21131,7 +21135,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="95"/>
+      <c r="A87" s="89"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -21155,7 +21159,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="95"/>
+      <c r="A88" s="89"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -21179,7 +21183,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="96"/>
+      <c r="A89" s="90"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -21237,7 +21241,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="76" t="s">
+      <c r="A92" s="70" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -21267,7 +21271,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="77"/>
+      <c r="A93" s="71"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -21295,7 +21299,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="77"/>
+      <c r="A94" s="71"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -21319,7 +21323,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="77"/>
+      <c r="A95" s="71"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -21343,7 +21347,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="77"/>
+      <c r="A96" s="71"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -21367,7 +21371,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="78"/>
+      <c r="A97" s="72"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -21433,26 +21437,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="70" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="72"/>
+      <c r="A1" s="64" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="66"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="73"/>
-      <c r="B2" s="74"/>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="75"/>
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="69"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -21485,7 +21489,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="97" t="s">
+      <c r="A4" s="91" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -21515,7 +21519,7 @@
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="98"/>
+      <c r="A5" s="92"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -21539,7 +21543,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="98"/>
+      <c r="A6" s="92"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -21567,7 +21571,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="98"/>
+      <c r="A7" s="92"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -21595,7 +21599,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="98"/>
+      <c r="A8" s="92"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -21623,7 +21627,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="99"/>
+      <c r="A9" s="93"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -21685,7 +21689,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="100" t="s">
+      <c r="A12" s="94" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -21711,7 +21715,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="101"/>
+      <c r="A13" s="95"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -21735,7 +21739,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="101"/>
+      <c r="A14" s="95"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -21763,7 +21767,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="101"/>
+      <c r="A15" s="95"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -21791,7 +21795,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="101"/>
+      <c r="A16" s="95"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -21819,7 +21823,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="102"/>
+      <c r="A17" s="96"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -21881,7 +21885,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="103" t="s">
+      <c r="A20" s="97" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -21907,7 +21911,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="104"/>
+      <c r="A21" s="98"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -21935,7 +21939,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="104"/>
+      <c r="A22" s="98"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -21963,7 +21967,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="104"/>
+      <c r="A23" s="98"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -21991,7 +21995,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="104"/>
+      <c r="A24" s="98"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -22019,7 +22023,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="105"/>
+      <c r="A25" s="99"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -22081,7 +22085,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="106" t="s">
+      <c r="A28" s="100" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -22107,7 +22111,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="107"/>
+      <c r="A29" s="101"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -22135,7 +22139,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="107"/>
+      <c r="A30" s="101"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -22163,7 +22167,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="107"/>
+      <c r="A31" s="101"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -22191,7 +22195,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="107"/>
+      <c r="A32" s="101"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -22219,7 +22223,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="108"/>
+      <c r="A33" s="102"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -22281,7 +22285,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="109" t="s">
+      <c r="A36" s="103" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -22311,7 +22315,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="110"/>
+      <c r="A37" s="104"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -22339,7 +22343,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="110"/>
+      <c r="A38" s="104"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -22367,7 +22371,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="110"/>
+      <c r="A39" s="104"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -22395,7 +22399,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="110"/>
+      <c r="A40" s="104"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -22423,7 +22427,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="111"/>
+      <c r="A41" s="105"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -22485,7 +22489,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="79" t="s">
+      <c r="A44" s="73" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -22515,7 +22519,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="80"/>
+      <c r="A45" s="74"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -22543,7 +22547,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="80"/>
+      <c r="A46" s="74"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -22571,7 +22575,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="80"/>
+      <c r="A47" s="74"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -22599,7 +22603,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="80"/>
+      <c r="A48" s="74"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -22627,7 +22631,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="81"/>
+      <c r="A49" s="75"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -22689,7 +22693,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="82" t="s">
+      <c r="A52" s="76" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -22719,7 +22723,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="83"/>
+      <c r="A53" s="77"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -22747,7 +22751,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="83"/>
+      <c r="A54" s="77"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -22775,7 +22779,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="83"/>
+      <c r="A55" s="77"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -22803,7 +22807,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="83"/>
+      <c r="A56" s="77"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -22831,7 +22835,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="84"/>
+      <c r="A57" s="78"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -22893,7 +22897,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="85" t="s">
+      <c r="A60" s="79" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -22923,7 +22927,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="86"/>
+      <c r="A61" s="80"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -22951,7 +22955,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="86"/>
+      <c r="A62" s="80"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -22979,7 +22983,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="86"/>
+      <c r="A63" s="80"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -23007,7 +23011,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="86"/>
+      <c r="A64" s="80"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -23035,7 +23039,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="87"/>
+      <c r="A65" s="81"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -23097,7 +23101,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="88" t="s">
+      <c r="A68" s="82" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -23127,7 +23131,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="89"/>
+      <c r="A69" s="83"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -23155,7 +23159,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="89"/>
+      <c r="A70" s="83"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -23183,7 +23187,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="89"/>
+      <c r="A71" s="83"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -23211,7 +23215,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="89"/>
+      <c r="A72" s="83"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -23239,7 +23243,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="90"/>
+      <c r="A73" s="84"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -23301,7 +23305,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="91" t="s">
+      <c r="A76" s="85" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -23331,7 +23335,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="92"/>
+      <c r="A77" s="86"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -23353,13 +23357,13 @@
       <c r="H77" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="J77" s="1" t="str">
+      <c r="J77" s="1">
         <f>IF(OR(Resultados!F77="",Resultados!G77=""),"",IF(AND(F77=Resultados!F77,G77=Resultados!G77),2,IF(((F77&gt;G77)=(Resultados!F77&gt;Resultados!G77))*((F77&lt;G77)=(Resultados!F77&lt;Resultados!G77)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="92"/>
+      <c r="A78" s="86"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -23387,7 +23391,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="92"/>
+      <c r="A79" s="86"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -23415,7 +23419,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="92"/>
+      <c r="A80" s="86"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -23443,7 +23447,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="93"/>
+      <c r="A81" s="87"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -23505,7 +23509,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="94" t="s">
+      <c r="A84" s="88" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -23535,7 +23539,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="95"/>
+      <c r="A85" s="89"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -23563,7 +23567,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="95"/>
+      <c r="A86" s="89"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -23591,7 +23595,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="95"/>
+      <c r="A87" s="89"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -23619,7 +23623,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="95"/>
+      <c r="A88" s="89"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -23647,7 +23651,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="96"/>
+      <c r="A89" s="90"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -23709,7 +23713,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="76" t="s">
+      <c r="A92" s="70" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -23739,7 +23743,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="77"/>
+      <c r="A93" s="71"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -23767,7 +23771,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="77"/>
+      <c r="A94" s="71"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -23795,7 +23799,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="77"/>
+      <c r="A95" s="71"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -23823,7 +23827,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="77"/>
+      <c r="A96" s="71"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -23851,7 +23855,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="78"/>
+      <c r="A97" s="72"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -23921,26 +23925,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="70" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="72"/>
+      <c r="A1" s="64" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="66"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="73"/>
-      <c r="B2" s="74"/>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="75"/>
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="69"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -23973,7 +23977,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="97" t="s">
+      <c r="A4" s="91" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -23999,11 +24003,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="98"/>
+      <c r="A5" s="92"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -24027,7 +24031,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="98"/>
+      <c r="A6" s="92"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -24055,7 +24059,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="98"/>
+      <c r="A7" s="92"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -24083,7 +24087,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="98"/>
+      <c r="A8" s="92"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -24111,7 +24115,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="99"/>
+      <c r="A9" s="93"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -24173,7 +24177,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="100" t="s">
+      <c r="A12" s="94" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -24199,7 +24203,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="101"/>
+      <c r="A13" s="95"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -24223,7 +24227,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="101"/>
+      <c r="A14" s="95"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -24251,7 +24255,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="101"/>
+      <c r="A15" s="95"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -24279,7 +24283,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="101"/>
+      <c r="A16" s="95"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -24307,7 +24311,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="102"/>
+      <c r="A17" s="96"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -24369,7 +24373,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="103" t="s">
+      <c r="A20" s="97" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -24395,7 +24399,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="104"/>
+      <c r="A21" s="98"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -24423,7 +24427,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="104"/>
+      <c r="A22" s="98"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -24451,7 +24455,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="104"/>
+      <c r="A23" s="98"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -24479,7 +24483,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="104"/>
+      <c r="A24" s="98"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -24507,7 +24511,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="105"/>
+      <c r="A25" s="99"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -24569,7 +24573,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="106" t="s">
+      <c r="A28" s="100" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -24595,7 +24599,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="107"/>
+      <c r="A29" s="101"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -24623,7 +24627,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="107"/>
+      <c r="A30" s="101"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -24651,7 +24655,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="107"/>
+      <c r="A31" s="101"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -24679,7 +24683,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="107"/>
+      <c r="A32" s="101"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -24707,7 +24711,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="108"/>
+      <c r="A33" s="102"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -24769,7 +24773,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="109" t="s">
+      <c r="A36" s="103" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -24799,7 +24803,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="110"/>
+      <c r="A37" s="104"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -24827,7 +24831,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="110"/>
+      <c r="A38" s="104"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -24855,7 +24859,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="110"/>
+      <c r="A39" s="104"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -24883,7 +24887,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="110"/>
+      <c r="A40" s="104"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -24911,7 +24915,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="111"/>
+      <c r="A41" s="105"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -24973,7 +24977,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="79" t="s">
+      <c r="A44" s="73" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -25003,7 +25007,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="80"/>
+      <c r="A45" s="74"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -25031,7 +25035,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="80"/>
+      <c r="A46" s="74"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -25059,7 +25063,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="80"/>
+      <c r="A47" s="74"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -25087,7 +25091,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="80"/>
+      <c r="A48" s="74"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -25115,7 +25119,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="81"/>
+      <c r="A49" s="75"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -25177,7 +25181,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="82" t="s">
+      <c r="A52" s="76" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -25207,7 +25211,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="83"/>
+      <c r="A53" s="77"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -25235,7 +25239,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="83"/>
+      <c r="A54" s="77"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -25263,7 +25267,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="83"/>
+      <c r="A55" s="77"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -25291,7 +25295,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="83"/>
+      <c r="A56" s="77"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -25319,7 +25323,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="84"/>
+      <c r="A57" s="78"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -25381,7 +25385,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="85" t="s">
+      <c r="A60" s="79" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -25411,7 +25415,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="86"/>
+      <c r="A61" s="80"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -25439,7 +25443,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="86"/>
+      <c r="A62" s="80"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -25467,7 +25471,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="86"/>
+      <c r="A63" s="80"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -25495,7 +25499,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="86"/>
+      <c r="A64" s="80"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -25523,7 +25527,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="87"/>
+      <c r="A65" s="81"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -25585,7 +25589,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="88" t="s">
+      <c r="A68" s="82" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -25615,7 +25619,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="89"/>
+      <c r="A69" s="83"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -25643,7 +25647,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="89"/>
+      <c r="A70" s="83"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -25671,7 +25675,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="89"/>
+      <c r="A71" s="83"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -25699,7 +25703,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="89"/>
+      <c r="A72" s="83"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -25727,7 +25731,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="90"/>
+      <c r="A73" s="84"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -25789,7 +25793,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="91" t="s">
+      <c r="A76" s="85" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -25819,7 +25823,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="92"/>
+      <c r="A77" s="86"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -25841,13 +25845,13 @@
       <c r="H77" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="J77" s="1" t="str">
+      <c r="J77" s="1">
         <f>IF(OR(Resultados!F77="",Resultados!G77=""),"",IF(AND(F77=Resultados!F77,G77=Resultados!G77),2,IF(((F77&gt;G77)=(Resultados!F77&gt;Resultados!G77))*((F77&lt;G77)=(Resultados!F77&lt;Resultados!G77)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="92"/>
+      <c r="A78" s="86"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -25875,7 +25879,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="92"/>
+      <c r="A79" s="86"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -25903,7 +25907,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="92"/>
+      <c r="A80" s="86"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -25931,7 +25935,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="93"/>
+      <c r="A81" s="87"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -25993,7 +25997,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="94" t="s">
+      <c r="A84" s="88" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -26023,7 +26027,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="95"/>
+      <c r="A85" s="89"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -26051,7 +26055,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="95"/>
+      <c r="A86" s="89"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -26079,7 +26083,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="95"/>
+      <c r="A87" s="89"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -26107,7 +26111,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="95"/>
+      <c r="A88" s="89"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -26135,7 +26139,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="96"/>
+      <c r="A89" s="90"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -26197,7 +26201,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="76" t="s">
+      <c r="A92" s="70" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -26227,7 +26231,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="77"/>
+      <c r="A93" s="71"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -26255,7 +26259,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="77"/>
+      <c r="A94" s="71"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -26283,7 +26287,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="77"/>
+      <c r="A95" s="71"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -26311,7 +26315,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="77"/>
+      <c r="A96" s="71"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -26339,7 +26343,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="78"/>
+      <c r="A97" s="72"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>

--- a/data/Quiniela.xlsx
+++ b/data/Quiniela.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cindy\Desktop\QuinielaMundial\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4DB6324-544A-4C53-AB14-09E2F23C5591}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D1D9EC3-0E9B-488E-BCD2-9424AE0D46C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{9503E40F-C0E1-49CE-B4EA-3C401754995E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="6" xr2:uid="{9503E40F-C0E1-49CE-B4EA-3C401754995E}"/>
   </bookViews>
   <sheets>
     <sheet name="Resultados" sheetId="1" r:id="rId1"/>
@@ -1248,6 +1248,24 @@
     <xf numFmtId="0" fontId="5" fillId="24" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="20" fillId="20" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="20" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="20" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="20" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="20" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="20" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1416,72 +1434,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="20" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="20" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="20" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="20" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="20" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="20" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1575,6 +1527,54 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1933,26 +1933,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="64" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="66"/>
+      <c r="A1" s="70" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="72"/>
     </row>
     <row r="2" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="67"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="69"/>
+      <c r="A2" s="73"/>
+      <c r="B2" s="74"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="75"/>
     </row>
     <row r="3" spans="1:8" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -1979,7 +1979,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="91" t="s">
+      <c r="A4" s="97" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -2005,7 +2005,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="92"/>
+      <c r="A5" s="98"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -2029,7 +2029,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="92"/>
+      <c r="A6" s="98"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -2049,7 +2049,7 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="92"/>
+      <c r="A7" s="98"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -2069,7 +2069,7 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="92"/>
+      <c r="A8" s="98"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -2089,7 +2089,7 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="93"/>
+      <c r="A9" s="99"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -2143,7 +2143,7 @@
       </c>
     </row>
     <row r="12" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="94" t="s">
+      <c r="A12" s="100" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -2169,7 +2169,7 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="95"/>
+      <c r="A13" s="101"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -2193,7 +2193,7 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="95"/>
+      <c r="A14" s="101"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -2213,7 +2213,7 @@
       </c>
     </row>
     <row r="15" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="95"/>
+      <c r="A15" s="101"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -2233,7 +2233,7 @@
       </c>
     </row>
     <row r="16" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="95"/>
+      <c r="A16" s="101"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -2253,7 +2253,7 @@
       </c>
     </row>
     <row r="17" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="96"/>
+      <c r="A17" s="102"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -2307,7 +2307,7 @@
       </c>
     </row>
     <row r="20" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="97" t="s">
+      <c r="A20" s="103" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -2333,7 +2333,7 @@
       </c>
     </row>
     <row r="21" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="98"/>
+      <c r="A21" s="104"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -2357,7 +2357,7 @@
       </c>
     </row>
     <row r="22" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="98"/>
+      <c r="A22" s="104"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -2377,7 +2377,7 @@
       </c>
     </row>
     <row r="23" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="98"/>
+      <c r="A23" s="104"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -2397,7 +2397,7 @@
       </c>
     </row>
     <row r="24" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="98"/>
+      <c r="A24" s="104"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -2417,7 +2417,7 @@
       </c>
     </row>
     <row r="25" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="99"/>
+      <c r="A25" s="105"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -2471,7 +2471,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="100" t="s">
+      <c r="A28" s="106" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -2497,7 +2497,7 @@
       </c>
     </row>
     <row r="29" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="101"/>
+      <c r="A29" s="107"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -2521,7 +2521,7 @@
       </c>
     </row>
     <row r="30" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="101"/>
+      <c r="A30" s="107"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -2541,7 +2541,7 @@
       </c>
     </row>
     <row r="31" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="101"/>
+      <c r="A31" s="107"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -2561,7 +2561,7 @@
       </c>
     </row>
     <row r="32" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="101"/>
+      <c r="A32" s="107"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -2581,7 +2581,7 @@
       </c>
     </row>
     <row r="33" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="102"/>
+      <c r="A33" s="108"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -2635,7 +2635,7 @@
       </c>
     </row>
     <row r="36" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="103" t="s">
+      <c r="A36" s="109" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -2661,7 +2661,7 @@
       </c>
     </row>
     <row r="37" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="104"/>
+      <c r="A37" s="110"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -2685,7 +2685,7 @@
       </c>
     </row>
     <row r="38" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="104"/>
+      <c r="A38" s="110"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -2705,7 +2705,7 @@
       </c>
     </row>
     <row r="39" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="104"/>
+      <c r="A39" s="110"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -2725,7 +2725,7 @@
       </c>
     </row>
     <row r="40" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="104"/>
+      <c r="A40" s="110"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -2745,7 +2745,7 @@
       </c>
     </row>
     <row r="41" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="105"/>
+      <c r="A41" s="111"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -2799,7 +2799,7 @@
       </c>
     </row>
     <row r="44" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="73" t="s">
+      <c r="A44" s="79" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -2825,7 +2825,7 @@
       </c>
     </row>
     <row r="45" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="74"/>
+      <c r="A45" s="80"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -2849,7 +2849,7 @@
       </c>
     </row>
     <row r="46" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="74"/>
+      <c r="A46" s="80"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -2869,7 +2869,7 @@
       </c>
     </row>
     <row r="47" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="74"/>
+      <c r="A47" s="80"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -2889,7 +2889,7 @@
       </c>
     </row>
     <row r="48" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="74"/>
+      <c r="A48" s="80"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -2909,7 +2909,7 @@
       </c>
     </row>
     <row r="49" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="75"/>
+      <c r="A49" s="81"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -2963,7 +2963,7 @@
       </c>
     </row>
     <row r="52" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="76" t="s">
+      <c r="A52" s="82" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -2989,7 +2989,7 @@
       </c>
     </row>
     <row r="53" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="77"/>
+      <c r="A53" s="83"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -3013,7 +3013,7 @@
       </c>
     </row>
     <row r="54" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="77"/>
+      <c r="A54" s="83"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -3033,7 +3033,7 @@
       </c>
     </row>
     <row r="55" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="77"/>
+      <c r="A55" s="83"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -3053,7 +3053,7 @@
       </c>
     </row>
     <row r="56" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="77"/>
+      <c r="A56" s="83"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -3073,7 +3073,7 @@
       </c>
     </row>
     <row r="57" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="78"/>
+      <c r="A57" s="84"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -3127,7 +3127,7 @@
       </c>
     </row>
     <row r="60" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="79" t="s">
+      <c r="A60" s="85" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -3153,7 +3153,7 @@
       </c>
     </row>
     <row r="61" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="80"/>
+      <c r="A61" s="86"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -3177,7 +3177,7 @@
       </c>
     </row>
     <row r="62" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="80"/>
+      <c r="A62" s="86"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -3197,7 +3197,7 @@
       </c>
     </row>
     <row r="63" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="80"/>
+      <c r="A63" s="86"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -3217,7 +3217,7 @@
       </c>
     </row>
     <row r="64" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="80"/>
+      <c r="A64" s="86"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -3237,7 +3237,7 @@
       </c>
     </row>
     <row r="65" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="81"/>
+      <c r="A65" s="87"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -3291,7 +3291,7 @@
       </c>
     </row>
     <row r="68" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="82" t="s">
+      <c r="A68" s="88" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -3317,7 +3317,7 @@
       </c>
     </row>
     <row r="69" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="83"/>
+      <c r="A69" s="89"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -3341,7 +3341,7 @@
       </c>
     </row>
     <row r="70" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="83"/>
+      <c r="A70" s="89"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -3361,7 +3361,7 @@
       </c>
     </row>
     <row r="71" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="83"/>
+      <c r="A71" s="89"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -3381,7 +3381,7 @@
       </c>
     </row>
     <row r="72" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="83"/>
+      <c r="A72" s="89"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -3401,7 +3401,7 @@
       </c>
     </row>
     <row r="73" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="84"/>
+      <c r="A73" s="90"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -3455,7 +3455,7 @@
       </c>
     </row>
     <row r="76" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="85" t="s">
+      <c r="A76" s="91" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -3481,7 +3481,7 @@
       </c>
     </row>
     <row r="77" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="86"/>
+      <c r="A77" s="92"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -3505,7 +3505,7 @@
       </c>
     </row>
     <row r="78" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="86"/>
+      <c r="A78" s="92"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -3525,7 +3525,7 @@
       </c>
     </row>
     <row r="79" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="86"/>
+      <c r="A79" s="92"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -3545,7 +3545,7 @@
       </c>
     </row>
     <row r="80" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="86"/>
+      <c r="A80" s="92"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -3565,7 +3565,7 @@
       </c>
     </row>
     <row r="81" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="87"/>
+      <c r="A81" s="93"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -3619,7 +3619,7 @@
       </c>
     </row>
     <row r="84" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="88" t="s">
+      <c r="A84" s="94" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -3631,17 +3631,21 @@
       <c r="D84" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="E84" s="10" t="s">
+      <c r="E84" s="61" t="s">
         <v>61</v>
       </c>
-      <c r="F84" s="26"/>
-      <c r="G84" s="26"/>
-      <c r="H84" s="21" t="s">
+      <c r="F84" s="62">
+        <v>1</v>
+      </c>
+      <c r="G84" s="62">
+        <v>1</v>
+      </c>
+      <c r="H84" s="61" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="85" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="89"/>
+      <c r="A85" s="95"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -3661,7 +3665,7 @@
       </c>
     </row>
     <row r="86" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="89"/>
+      <c r="A86" s="95"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -3681,7 +3685,7 @@
       </c>
     </row>
     <row r="87" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="89"/>
+      <c r="A87" s="95"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -3701,7 +3705,7 @@
       </c>
     </row>
     <row r="88" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="89"/>
+      <c r="A88" s="95"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -3721,7 +3725,7 @@
       </c>
     </row>
     <row r="89" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="90"/>
+      <c r="A89" s="96"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -3775,7 +3779,7 @@
       </c>
     </row>
     <row r="92" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="70" t="s">
+      <c r="A92" s="76" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -3787,17 +3791,21 @@
       <c r="D92" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="E92" s="10" t="s">
+      <c r="E92" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="F92" s="26"/>
-      <c r="G92" s="26"/>
+      <c r="F92" s="26">
+        <v>4</v>
+      </c>
+      <c r="G92" s="26">
+        <v>2</v>
+      </c>
       <c r="H92" s="21" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="93" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="71"/>
+      <c r="A93" s="77"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -3807,17 +3815,21 @@
       <c r="D93" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="E93" s="10" t="s">
+      <c r="E93" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="F93" s="26"/>
-      <c r="G93" s="26"/>
+      <c r="F93" s="26">
+        <v>1</v>
+      </c>
+      <c r="G93" s="26">
+        <v>0</v>
+      </c>
       <c r="H93" s="21" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="94" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="71"/>
+      <c r="A94" s="77"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -3837,7 +3849,7 @@
       </c>
     </row>
     <row r="95" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="71"/>
+      <c r="A95" s="77"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -3857,7 +3869,7 @@
       </c>
     </row>
     <row r="96" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="71"/>
+      <c r="A96" s="77"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -3877,7 +3889,7 @@
       </c>
     </row>
     <row r="97" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="72"/>
+      <c r="A97" s="78"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -3937,26 +3949,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="64" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="66"/>
+      <c r="A1" s="70" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="72"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="67"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="69"/>
+      <c r="A2" s="73"/>
+      <c r="B2" s="74"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="75"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -3989,7 +4001,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="91" t="s">
+      <c r="A4" s="97" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -4019,7 +4031,7 @@
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="92"/>
+      <c r="A5" s="98"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -4043,7 +4055,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="92"/>
+      <c r="A6" s="98"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -4071,7 +4083,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="92"/>
+      <c r="A7" s="98"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -4099,7 +4111,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="92"/>
+      <c r="A8" s="98"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -4127,7 +4139,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="93"/>
+      <c r="A9" s="99"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -4189,7 +4201,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="94" t="s">
+      <c r="A12" s="100" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -4215,7 +4227,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="95"/>
+      <c r="A13" s="101"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -4239,7 +4251,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="95"/>
+      <c r="A14" s="101"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -4267,7 +4279,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="95"/>
+      <c r="A15" s="101"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -4295,7 +4307,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="95"/>
+      <c r="A16" s="101"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -4323,7 +4335,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="96"/>
+      <c r="A17" s="102"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -4385,7 +4397,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="97" t="s">
+      <c r="A20" s="103" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -4411,7 +4423,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="98"/>
+      <c r="A21" s="104"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -4439,7 +4451,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="98"/>
+      <c r="A22" s="104"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -4467,7 +4479,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="98"/>
+      <c r="A23" s="104"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -4495,7 +4507,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="98"/>
+      <c r="A24" s="104"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -4523,7 +4535,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="99"/>
+      <c r="A25" s="105"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -4585,7 +4597,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="100" t="s">
+      <c r="A28" s="106" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -4611,7 +4623,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="101"/>
+      <c r="A29" s="107"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -4639,7 +4651,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="101"/>
+      <c r="A30" s="107"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -4667,7 +4679,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="101"/>
+      <c r="A31" s="107"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -4695,7 +4707,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="101"/>
+      <c r="A32" s="107"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -4723,7 +4735,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="102"/>
+      <c r="A33" s="108"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -4785,7 +4797,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="103" t="s">
+      <c r="A36" s="109" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -4815,7 +4827,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="104"/>
+      <c r="A37" s="110"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -4843,7 +4855,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="104"/>
+      <c r="A38" s="110"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -4871,7 +4883,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="104"/>
+      <c r="A39" s="110"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -4899,7 +4911,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="104"/>
+      <c r="A40" s="110"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -4927,7 +4939,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="105"/>
+      <c r="A41" s="111"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -4989,7 +5001,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="73" t="s">
+      <c r="A44" s="79" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -5019,7 +5031,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="74"/>
+      <c r="A45" s="80"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -5047,7 +5059,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="74"/>
+      <c r="A46" s="80"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -5075,7 +5087,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="74"/>
+      <c r="A47" s="80"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -5103,7 +5115,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="74"/>
+      <c r="A48" s="80"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -5131,7 +5143,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="75"/>
+      <c r="A49" s="81"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -5193,7 +5205,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="76" t="s">
+      <c r="A52" s="82" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -5223,7 +5235,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="77"/>
+      <c r="A53" s="83"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -5251,7 +5263,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="77"/>
+      <c r="A54" s="83"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -5279,7 +5291,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="77"/>
+      <c r="A55" s="83"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -5307,7 +5319,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="77"/>
+      <c r="A56" s="83"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -5335,7 +5347,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="78"/>
+      <c r="A57" s="84"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -5397,7 +5409,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="79" t="s">
+      <c r="A60" s="85" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -5427,7 +5439,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="80"/>
+      <c r="A61" s="86"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -5455,7 +5467,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="80"/>
+      <c r="A62" s="86"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -5483,7 +5495,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="80"/>
+      <c r="A63" s="86"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -5511,7 +5523,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="80"/>
+      <c r="A64" s="86"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -5539,7 +5551,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="81"/>
+      <c r="A65" s="87"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -5601,7 +5613,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="82" t="s">
+      <c r="A68" s="88" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -5631,7 +5643,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="83"/>
+      <c r="A69" s="89"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -5659,7 +5671,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="83"/>
+      <c r="A70" s="89"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -5687,7 +5699,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="83"/>
+      <c r="A71" s="89"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -5715,7 +5727,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="83"/>
+      <c r="A72" s="89"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -5743,7 +5755,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="84"/>
+      <c r="A73" s="90"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -5805,7 +5817,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="85" t="s">
+      <c r="A76" s="91" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -5835,7 +5847,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="86"/>
+      <c r="A77" s="92"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -5863,7 +5875,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="86"/>
+      <c r="A78" s="92"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -5891,7 +5903,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="86"/>
+      <c r="A79" s="92"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -5919,7 +5931,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="86"/>
+      <c r="A80" s="92"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -5947,7 +5959,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="87"/>
+      <c r="A81" s="93"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -6009,7 +6021,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="88" t="s">
+      <c r="A84" s="94" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -6033,13 +6045,13 @@
       <c r="H84" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="J84" s="1" t="str">
+      <c r="J84" s="1">
         <f>IF(OR(Resultados!F84="",Resultados!G84=""),"",IF(AND(F84=Resultados!F84,G84=Resultados!G84),2,IF(((F84&gt;G84)=(Resultados!F84&gt;Resultados!G84))*((F84&lt;G84)=(Resultados!F84&lt;Resultados!G84)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="89"/>
+      <c r="A85" s="95"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -6067,7 +6079,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="89"/>
+      <c r="A86" s="95"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -6095,7 +6107,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="89"/>
+      <c r="A87" s="95"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -6123,7 +6135,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="89"/>
+      <c r="A88" s="95"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -6151,7 +6163,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="90"/>
+      <c r="A89" s="96"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -6213,7 +6225,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="70" t="s">
+      <c r="A92" s="76" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -6237,13 +6249,13 @@
       <c r="H92" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="J92" s="1" t="str">
+      <c r="J92" s="1">
         <f>IF(OR(Resultados!F92="",Resultados!G92=""),"",IF(AND(F92=Resultados!F92,G92=Resultados!G92),2,IF(((F92&gt;G92)=(Resultados!F92&gt;Resultados!G92))*((F92&lt;G92)=(Resultados!F92&lt;Resultados!G92)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="71"/>
+      <c r="A93" s="77"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -6265,13 +6277,13 @@
       <c r="H93" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="J93" s="1" t="str">
+      <c r="J93" s="1">
         <f>IF(OR(Resultados!F93="",Resultados!G93=""),"",IF(AND(F93=Resultados!F93,G93=Resultados!G93),2,IF(((F93&gt;G93)=(Resultados!F93&gt;Resultados!G93))*((F93&lt;G93)=(Resultados!F93&lt;Resultados!G93)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="71"/>
+      <c r="A94" s="77"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -6299,7 +6311,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="71"/>
+      <c r="A95" s="77"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -6327,7 +6339,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="71"/>
+      <c r="A96" s="77"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -6355,7 +6367,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="72"/>
+      <c r="A97" s="78"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -6384,6 +6396,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A28:A33"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:A9"/>
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="A20:A25"/>
     <mergeCell ref="A84:A89"/>
     <mergeCell ref="A92:A97"/>
     <mergeCell ref="A36:A41"/>
@@ -6392,12 +6410,6 @@
     <mergeCell ref="A60:A65"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="A76:A81"/>
-    <mergeCell ref="A28:A33"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A4:A9"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="A20:A25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -6425,26 +6437,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="64" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="66"/>
+      <c r="A1" s="70" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="72"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="67"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="69"/>
+      <c r="A2" s="73"/>
+      <c r="B2" s="74"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="75"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -6477,7 +6489,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="91" t="s">
+      <c r="A4" s="97" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -6503,11 +6515,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="92"/>
+      <c r="A5" s="98"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -6531,7 +6543,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="92"/>
+      <c r="A6" s="98"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -6559,7 +6571,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="92"/>
+      <c r="A7" s="98"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -6587,7 +6599,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="92"/>
+      <c r="A8" s="98"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -6615,7 +6627,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="93"/>
+      <c r="A9" s="99"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -6677,7 +6689,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="94" t="s">
+      <c r="A12" s="100" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -6703,7 +6715,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="95"/>
+      <c r="A13" s="101"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -6727,7 +6739,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="95"/>
+      <c r="A14" s="101"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -6755,7 +6767,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="95"/>
+      <c r="A15" s="101"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -6783,7 +6795,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="95"/>
+      <c r="A16" s="101"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -6811,7 +6823,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="96"/>
+      <c r="A17" s="102"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -6873,7 +6885,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="97" t="s">
+      <c r="A20" s="103" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -6899,7 +6911,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="98"/>
+      <c r="A21" s="104"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -6927,7 +6939,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="98"/>
+      <c r="A22" s="104"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -6955,7 +6967,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="98"/>
+      <c r="A23" s="104"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -6983,7 +6995,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="98"/>
+      <c r="A24" s="104"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -7011,7 +7023,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="99"/>
+      <c r="A25" s="105"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -7073,7 +7085,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="100" t="s">
+      <c r="A28" s="106" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -7099,7 +7111,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="101"/>
+      <c r="A29" s="107"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -7127,7 +7139,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="101"/>
+      <c r="A30" s="107"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -7155,7 +7167,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="101"/>
+      <c r="A31" s="107"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -7183,7 +7195,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="101"/>
+      <c r="A32" s="107"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -7211,7 +7223,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="102"/>
+      <c r="A33" s="108"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -7273,7 +7285,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="103" t="s">
+      <c r="A36" s="109" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -7303,7 +7315,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="104"/>
+      <c r="A37" s="110"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -7331,7 +7343,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="104"/>
+      <c r="A38" s="110"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -7359,7 +7371,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="104"/>
+      <c r="A39" s="110"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -7387,7 +7399,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="104"/>
+      <c r="A40" s="110"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -7415,7 +7427,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="105"/>
+      <c r="A41" s="111"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -7477,7 +7489,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="73" t="s">
+      <c r="A44" s="79" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -7507,7 +7519,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="74"/>
+      <c r="A45" s="80"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -7535,7 +7547,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="74"/>
+      <c r="A46" s="80"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -7563,7 +7575,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="74"/>
+      <c r="A47" s="80"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -7591,7 +7603,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="74"/>
+      <c r="A48" s="80"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -7619,7 +7631,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="75"/>
+      <c r="A49" s="81"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -7681,7 +7693,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="76" t="s">
+      <c r="A52" s="82" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -7711,7 +7723,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="77"/>
+      <c r="A53" s="83"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -7739,7 +7751,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="77"/>
+      <c r="A54" s="83"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -7767,7 +7779,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="77"/>
+      <c r="A55" s="83"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -7795,7 +7807,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="77"/>
+      <c r="A56" s="83"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -7823,7 +7835,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="78"/>
+      <c r="A57" s="84"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -7885,7 +7897,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="79" t="s">
+      <c r="A60" s="85" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -7915,7 +7927,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="80"/>
+      <c r="A61" s="86"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -7943,7 +7955,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="80"/>
+      <c r="A62" s="86"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -7971,7 +7983,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="80"/>
+      <c r="A63" s="86"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -7999,7 +8011,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="80"/>
+      <c r="A64" s="86"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -8027,7 +8039,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="81"/>
+      <c r="A65" s="87"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -8089,7 +8101,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="82" t="s">
+      <c r="A68" s="88" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -8119,7 +8131,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="83"/>
+      <c r="A69" s="89"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -8147,7 +8159,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="83"/>
+      <c r="A70" s="89"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -8175,7 +8187,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="83"/>
+      <c r="A71" s="89"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -8203,7 +8215,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="83"/>
+      <c r="A72" s="89"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -8231,7 +8243,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="84"/>
+      <c r="A73" s="90"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -8293,7 +8305,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="85" t="s">
+      <c r="A76" s="91" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -8323,7 +8335,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="86"/>
+      <c r="A77" s="92"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -8351,7 +8363,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="86"/>
+      <c r="A78" s="92"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -8379,7 +8391,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="86"/>
+      <c r="A79" s="92"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -8407,7 +8419,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="86"/>
+      <c r="A80" s="92"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -8435,7 +8447,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="87"/>
+      <c r="A81" s="93"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -8497,7 +8509,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="88" t="s">
+      <c r="A84" s="94" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -8521,13 +8533,13 @@
       <c r="H84" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="J84" s="1" t="str">
+      <c r="J84" s="1">
         <f>IF(OR(Resultados!F84="",Resultados!G84=""),"",IF(AND(F84=Resultados!F84,G84=Resultados!G84),2,IF(((F84&gt;G84)=(Resultados!F84&gt;Resultados!G84))*((F84&lt;G84)=(Resultados!F84&lt;Resultados!G84)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="89"/>
+      <c r="A85" s="95"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -8555,7 +8567,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="89"/>
+      <c r="A86" s="95"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -8583,7 +8595,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="89"/>
+      <c r="A87" s="95"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -8611,7 +8623,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="89"/>
+      <c r="A88" s="95"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -8639,7 +8651,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="90"/>
+      <c r="A89" s="96"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -8701,7 +8713,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="70" t="s">
+      <c r="A92" s="76" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -8725,13 +8737,13 @@
       <c r="H92" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="J92" s="1" t="str">
+      <c r="J92" s="1">
         <f>IF(OR(Resultados!F92="",Resultados!G92=""),"",IF(AND(F92=Resultados!F92,G92=Resultados!G92),2,IF(((F92&gt;G92)=(Resultados!F92&gt;Resultados!G92))*((F92&lt;G92)=(Resultados!F92&lt;Resultados!G92)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="71"/>
+      <c r="A93" s="77"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -8753,13 +8765,13 @@
       <c r="H93" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="J93" s="1" t="str">
+      <c r="J93" s="1">
         <f>IF(OR(Resultados!F93="",Resultados!G93=""),"",IF(AND(F93=Resultados!F93,G93=Resultados!G93),2,IF(((F93&gt;G93)=(Resultados!F93&gt;Resultados!G93))*((F93&lt;G93)=(Resultados!F93&lt;Resultados!G93)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="71"/>
+      <c r="A94" s="77"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -8787,7 +8799,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="71"/>
+      <c r="A95" s="77"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -8815,7 +8827,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="71"/>
+      <c r="A96" s="77"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -8843,7 +8855,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="72"/>
+      <c r="A97" s="78"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -8872,6 +8884,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A28:A33"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:A9"/>
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="A20:A25"/>
     <mergeCell ref="A84:A89"/>
     <mergeCell ref="A92:A97"/>
     <mergeCell ref="A36:A41"/>
@@ -8880,12 +8898,6 @@
     <mergeCell ref="A60:A65"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="A76:A81"/>
-    <mergeCell ref="A28:A33"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A4:A9"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="A20:A25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -8908,18 +8920,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D1" s="106" t="s">
+      <c r="D1" s="64" t="s">
         <v>74</v>
       </c>
-      <c r="E1" s="107"/>
-      <c r="F1" s="108"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="66"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D2" s="109" t="s">
+      <c r="D2" s="67" t="s">
         <v>75</v>
       </c>
-      <c r="E2" s="110"/>
-      <c r="F2" s="111"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="69"/>
     </row>
     <row r="4" spans="1:6" s="29" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="57" t="s">
@@ -8944,17 +8956,17 @@
       </c>
       <c r="B5" s="58">
         <f>Cindy!L4</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D5" s="59">
         <v>1</v>
       </c>
       <c r="E5" s="59" t="str" cm="1">
         <f t="array" ref="E5:F13">_xlfn._xlws.SORT(A5:B13,2,-1)</f>
-        <v>Wendy</v>
+        <v>Packy</v>
       </c>
       <c r="F5" s="59">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -8969,10 +8981,10 @@
         <v>2</v>
       </c>
       <c r="E6" s="55" t="str">
-        <v>Lennon</v>
+        <v>Bere</v>
       </c>
       <c r="F6" s="55">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -8981,16 +8993,16 @@
       </c>
       <c r="B7" s="58">
         <f>Jimmy!L4</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D7" s="56">
         <v>3</v>
       </c>
       <c r="E7" s="56" t="str">
-        <v>Erik</v>
+        <v>Wendy</v>
       </c>
       <c r="F7" s="56">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -8999,16 +9011,16 @@
       </c>
       <c r="B8" s="58">
         <f>Erick!L4</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D8" s="28">
         <v>4</v>
       </c>
       <c r="E8" s="28" t="str">
-        <v>Yulian</v>
+        <v>Jimmy</v>
       </c>
       <c r="F8" s="28">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -9017,16 +9029,16 @@
       </c>
       <c r="B9" s="58">
         <f>Erik!L4</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D9" s="28">
         <v>5</v>
       </c>
       <c r="E9" s="28" t="str">
-        <v>Packy</v>
+        <v>Erik</v>
       </c>
       <c r="F9" s="28">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -9041,10 +9053,10 @@
         <v>6</v>
       </c>
       <c r="E10" s="28" t="str">
-        <v>Bere</v>
+        <v>Lennon</v>
       </c>
       <c r="F10" s="28">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -9053,16 +9065,16 @@
       </c>
       <c r="B11" s="58">
         <f>Yulian!L4</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D11" s="28">
         <v>7</v>
       </c>
       <c r="E11" s="28" t="str">
-        <v>Jimmy</v>
+        <v>Yulian</v>
       </c>
       <c r="F11" s="28">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -9071,7 +9083,7 @@
       </c>
       <c r="B12" s="58">
         <f>Packy!L4</f>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D12" s="28">
         <v>8</v>
@@ -9080,7 +9092,7 @@
         <v>Cindy</v>
       </c>
       <c r="F12" s="28">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -9089,7 +9101,7 @@
       </c>
       <c r="B13" s="58">
         <f>Bere!L4</f>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D13" s="28">
         <v>9</v>
@@ -9098,7 +9110,7 @@
         <v>Erick</v>
       </c>
       <c r="F13" s="28">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -9132,26 +9144,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="64" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="66"/>
+      <c r="A1" s="70" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="72"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="67"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="69"/>
+      <c r="A2" s="73"/>
+      <c r="B2" s="74"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="75"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="31"/>
@@ -9184,7 +9196,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="115" t="s">
+      <c r="A4" s="139" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="35">
@@ -9210,11 +9222,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="116"/>
+      <c r="A5" s="140"/>
       <c r="B5" s="35">
         <v>46185</v>
       </c>
@@ -9238,7 +9250,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="116"/>
+      <c r="A6" s="140"/>
       <c r="B6" s="35">
         <v>46191</v>
       </c>
@@ -9266,7 +9278,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="116"/>
+      <c r="A7" s="140"/>
       <c r="B7" s="35">
         <v>46192</v>
       </c>
@@ -9294,7 +9306,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="116"/>
+      <c r="A8" s="140"/>
       <c r="B8" s="35">
         <v>46198</v>
       </c>
@@ -9322,7 +9334,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="117"/>
+      <c r="A9" s="141"/>
       <c r="B9" s="42">
         <v>46198</v>
       </c>
@@ -9384,7 +9396,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="118" t="s">
+      <c r="A12" s="142" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="35">
@@ -9410,7 +9422,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="119"/>
+      <c r="A13" s="143"/>
       <c r="B13" s="35">
         <v>46186</v>
       </c>
@@ -9434,7 +9446,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="119"/>
+      <c r="A14" s="143"/>
       <c r="B14" s="35">
         <v>46191</v>
       </c>
@@ -9462,7 +9474,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="119"/>
+      <c r="A15" s="143"/>
       <c r="B15" s="35">
         <v>46192</v>
       </c>
@@ -9490,7 +9502,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="119"/>
+      <c r="A16" s="143"/>
       <c r="B16" s="35">
         <v>46197</v>
       </c>
@@ -9518,7 +9530,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="120"/>
+      <c r="A17" s="144"/>
       <c r="B17" s="42">
         <v>46197</v>
       </c>
@@ -9580,7 +9592,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="121" t="s">
+      <c r="A20" s="145" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="35">
@@ -9606,7 +9618,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="122"/>
+      <c r="A21" s="146"/>
       <c r="B21" s="35">
         <v>46187</v>
       </c>
@@ -9634,7 +9646,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="122"/>
+      <c r="A22" s="146"/>
       <c r="B22" s="35">
         <v>46193</v>
       </c>
@@ -9662,7 +9674,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="122"/>
+      <c r="A23" s="146"/>
       <c r="B23" s="35">
         <v>46193</v>
       </c>
@@ -9690,7 +9702,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="122"/>
+      <c r="A24" s="146"/>
       <c r="B24" s="35">
         <v>46198</v>
       </c>
@@ -9718,7 +9730,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="123"/>
+      <c r="A25" s="147"/>
       <c r="B25" s="42">
         <v>46198</v>
       </c>
@@ -9780,7 +9792,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="112" t="s">
+      <c r="A28" s="136" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="35">
@@ -9806,7 +9818,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="113"/>
+      <c r="A29" s="137"/>
       <c r="B29" s="35">
         <v>46187</v>
       </c>
@@ -9834,7 +9846,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="113"/>
+      <c r="A30" s="137"/>
       <c r="B30" s="35">
         <v>46192</v>
       </c>
@@ -9862,7 +9874,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="113"/>
+      <c r="A31" s="137"/>
       <c r="B31" s="35">
         <v>46193</v>
       </c>
@@ -9890,7 +9902,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="113"/>
+      <c r="A32" s="137"/>
       <c r="B32" s="35">
         <v>46199</v>
       </c>
@@ -9918,7 +9930,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="114"/>
+      <c r="A33" s="138"/>
       <c r="B33" s="42">
         <v>46199</v>
       </c>
@@ -9980,7 +9992,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="130" t="s">
+      <c r="A36" s="118" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="35">
@@ -10010,7 +10022,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="131"/>
+      <c r="A37" s="119"/>
       <c r="B37" s="35">
         <v>46188</v>
       </c>
@@ -10038,7 +10050,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="131"/>
+      <c r="A38" s="119"/>
       <c r="B38" s="35">
         <v>46193</v>
       </c>
@@ -10066,7 +10078,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="131"/>
+      <c r="A39" s="119"/>
       <c r="B39" s="35">
         <v>46194</v>
       </c>
@@ -10094,7 +10106,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="131"/>
+      <c r="A40" s="119"/>
       <c r="B40" s="35">
         <v>46198</v>
       </c>
@@ -10122,7 +10134,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="132"/>
+      <c r="A41" s="120"/>
       <c r="B41" s="42">
         <v>46198</v>
       </c>
@@ -10184,7 +10196,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="133" t="s">
+      <c r="A44" s="121" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="35">
@@ -10214,7 +10226,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="134"/>
+      <c r="A45" s="122"/>
       <c r="B45" s="35">
         <v>46188</v>
       </c>
@@ -10242,7 +10254,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="134"/>
+      <c r="A46" s="122"/>
       <c r="B46" s="35">
         <v>46193</v>
       </c>
@@ -10270,7 +10282,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="134"/>
+      <c r="A47" s="122"/>
       <c r="B47" s="35">
         <v>46194</v>
       </c>
@@ -10298,7 +10310,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="134"/>
+      <c r="A48" s="122"/>
       <c r="B48" s="35">
         <v>46199</v>
       </c>
@@ -10326,7 +10338,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="135"/>
+      <c r="A49" s="123"/>
       <c r="B49" s="42">
         <v>46199</v>
       </c>
@@ -10388,7 +10400,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="136" t="s">
+      <c r="A52" s="124" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="35">
@@ -10418,7 +10430,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="137"/>
+      <c r="A53" s="125"/>
       <c r="B53" s="35">
         <v>46189</v>
       </c>
@@ -10446,7 +10458,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="137"/>
+      <c r="A54" s="125"/>
       <c r="B54" s="35">
         <v>46194</v>
       </c>
@@ -10474,7 +10486,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="137"/>
+      <c r="A55" s="125"/>
       <c r="B55" s="35">
         <v>46195</v>
       </c>
@@ -10502,7 +10514,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="137"/>
+      <c r="A56" s="125"/>
       <c r="B56" s="35">
         <v>46200</v>
       </c>
@@ -10530,7 +10542,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="138"/>
+      <c r="A57" s="126"/>
       <c r="B57" s="42">
         <v>46200</v>
       </c>
@@ -10592,7 +10604,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="139" t="s">
+      <c r="A60" s="127" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="35">
@@ -10622,7 +10634,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="140"/>
+      <c r="A61" s="128"/>
       <c r="B61" s="35">
         <v>46189</v>
       </c>
@@ -10650,7 +10662,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="140"/>
+      <c r="A62" s="128"/>
       <c r="B62" s="35">
         <v>46194</v>
       </c>
@@ -10678,7 +10690,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="140"/>
+      <c r="A63" s="128"/>
       <c r="B63" s="35">
         <v>46195</v>
       </c>
@@ -10706,7 +10718,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="140"/>
+      <c r="A64" s="128"/>
       <c r="B64" s="35">
         <v>46200</v>
       </c>
@@ -10734,7 +10746,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="141"/>
+      <c r="A65" s="129"/>
       <c r="B65" s="42">
         <v>46200</v>
       </c>
@@ -10796,7 +10808,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="142" t="s">
+      <c r="A68" s="130" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="35">
@@ -10826,7 +10838,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="143"/>
+      <c r="A69" s="131"/>
       <c r="B69" s="35">
         <v>46190</v>
       </c>
@@ -10854,7 +10866,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="143"/>
+      <c r="A70" s="131"/>
       <c r="B70" s="35">
         <v>46195</v>
       </c>
@@ -10882,7 +10894,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="143"/>
+      <c r="A71" s="131"/>
       <c r="B71" s="35">
         <v>46196</v>
       </c>
@@ -10910,7 +10922,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="143"/>
+      <c r="A72" s="131"/>
       <c r="B72" s="35">
         <v>46199</v>
       </c>
@@ -10938,7 +10950,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="144"/>
+      <c r="A73" s="132"/>
       <c r="B73" s="42">
         <v>46199</v>
       </c>
@@ -11000,7 +11012,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="145" t="s">
+      <c r="A76" s="133" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="35">
@@ -11030,7 +11042,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="146"/>
+      <c r="A77" s="134"/>
       <c r="B77" s="35">
         <v>46190</v>
       </c>
@@ -11058,7 +11070,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="146"/>
+      <c r="A78" s="134"/>
       <c r="B78" s="35">
         <v>46195</v>
       </c>
@@ -11086,7 +11098,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="146"/>
+      <c r="A79" s="134"/>
       <c r="B79" s="35">
         <v>46196</v>
       </c>
@@ -11114,7 +11126,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="146"/>
+      <c r="A80" s="134"/>
       <c r="B80" s="35">
         <v>46201</v>
       </c>
@@ -11142,7 +11154,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="147"/>
+      <c r="A81" s="135"/>
       <c r="B81" s="42">
         <v>46201</v>
       </c>
@@ -11204,7 +11216,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="124" t="s">
+      <c r="A84" s="112" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="35">
@@ -11228,13 +11240,13 @@
       <c r="H84" s="46" t="s">
         <v>62</v>
       </c>
-      <c r="J84" s="1" t="str">
+      <c r="J84" s="1">
         <f>IF(OR(Resultados!F84="",Resultados!G84=""),"",IF(AND(F84=Resultados!F84,G84=Resultados!G84),2,IF(((F84&gt;G84)=(Resultados!F84&gt;Resultados!G84))*((F84&lt;G84)=(Resultados!F84&lt;Resultados!G84)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="125"/>
+      <c r="A85" s="113"/>
       <c r="B85" s="35">
         <v>46191</v>
       </c>
@@ -11262,7 +11274,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="125"/>
+      <c r="A86" s="113"/>
       <c r="B86" s="35">
         <v>46196</v>
       </c>
@@ -11290,7 +11302,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="125"/>
+      <c r="A87" s="113"/>
       <c r="B87" s="35">
         <v>46197</v>
       </c>
@@ -11318,7 +11330,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="125"/>
+      <c r="A88" s="113"/>
       <c r="B88" s="35">
         <v>46201</v>
       </c>
@@ -11346,7 +11358,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="126"/>
+      <c r="A89" s="114"/>
       <c r="B89" s="42">
         <v>46201</v>
       </c>
@@ -11408,7 +11420,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="127" t="s">
+      <c r="A92" s="115" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="35">
@@ -11432,13 +11444,13 @@
       <c r="H92" s="46" t="s">
         <v>67</v>
       </c>
-      <c r="J92" s="1" t="str">
+      <c r="J92" s="1">
         <f>IF(OR(Resultados!F92="",Resultados!G92=""),"",IF(AND(F92=Resultados!F92,G92=Resultados!G92),2,IF(((F92&gt;G92)=(Resultados!F92&gt;Resultados!G92))*((F92&lt;G92)=(Resultados!F92&lt;Resultados!G92)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="128"/>
+      <c r="A93" s="116"/>
       <c r="B93" s="35">
         <v>46191</v>
       </c>
@@ -11460,13 +11472,13 @@
       <c r="H93" s="46" t="s">
         <v>69</v>
       </c>
-      <c r="J93" s="1" t="str">
+      <c r="J93" s="1">
         <f>IF(OR(Resultados!F93="",Resultados!G93=""),"",IF(AND(F93=Resultados!F93,G93=Resultados!G93),2,IF(((F93&gt;G93)=(Resultados!F93&gt;Resultados!G93))*((F93&lt;G93)=(Resultados!F93&lt;Resultados!G93)),1,0)))</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="128"/>
+      <c r="A94" s="116"/>
       <c r="B94" s="35">
         <v>46196</v>
       </c>
@@ -11494,7 +11506,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="128"/>
+      <c r="A95" s="116"/>
       <c r="B95" s="35">
         <v>46197</v>
       </c>
@@ -11522,7 +11534,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="128"/>
+      <c r="A96" s="116"/>
       <c r="B96" s="35">
         <v>46200</v>
       </c>
@@ -11550,7 +11562,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="129"/>
+      <c r="A97" s="117"/>
       <c r="B97" s="42">
         <v>46200</v>
       </c>
@@ -11579,6 +11591,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A28:A33"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:A9"/>
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="A20:A25"/>
     <mergeCell ref="A84:A89"/>
     <mergeCell ref="A92:A97"/>
     <mergeCell ref="A36:A41"/>
@@ -11587,12 +11605,6 @@
     <mergeCell ref="A60:A65"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="A76:A81"/>
-    <mergeCell ref="A28:A33"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A4:A9"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="A20:A25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -11621,26 +11633,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="64" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="66"/>
+      <c r="A1" s="70" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="72"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="67"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="69"/>
+      <c r="A2" s="73"/>
+      <c r="B2" s="74"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="75"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="31"/>
@@ -11673,7 +11685,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="115" t="s">
+      <c r="A4" s="139" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="35">
@@ -11703,7 +11715,7 @@
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="116"/>
+      <c r="A5" s="140"/>
       <c r="B5" s="35">
         <v>46185</v>
       </c>
@@ -11727,7 +11739,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="116"/>
+      <c r="A6" s="140"/>
       <c r="B6" s="35">
         <v>46191</v>
       </c>
@@ -11755,7 +11767,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="116"/>
+      <c r="A7" s="140"/>
       <c r="B7" s="35">
         <v>46192</v>
       </c>
@@ -11783,7 +11795,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="116"/>
+      <c r="A8" s="140"/>
       <c r="B8" s="35">
         <v>46198</v>
       </c>
@@ -11811,7 +11823,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="117"/>
+      <c r="A9" s="141"/>
       <c r="B9" s="42">
         <v>46198</v>
       </c>
@@ -11873,7 +11885,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="118" t="s">
+      <c r="A12" s="142" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="35">
@@ -11899,7 +11911,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="119"/>
+      <c r="A13" s="143"/>
       <c r="B13" s="35">
         <v>46186</v>
       </c>
@@ -11923,7 +11935,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="119"/>
+      <c r="A14" s="143"/>
       <c r="B14" s="35">
         <v>46191</v>
       </c>
@@ -11951,7 +11963,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="119"/>
+      <c r="A15" s="143"/>
       <c r="B15" s="35">
         <v>46192</v>
       </c>
@@ -11979,7 +11991,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="119"/>
+      <c r="A16" s="143"/>
       <c r="B16" s="35">
         <v>46197</v>
       </c>
@@ -12007,7 +12019,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="120"/>
+      <c r="A17" s="144"/>
       <c r="B17" s="42">
         <v>46197</v>
       </c>
@@ -12069,7 +12081,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="121" t="s">
+      <c r="A20" s="145" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="35">
@@ -12095,7 +12107,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="122"/>
+      <c r="A21" s="146"/>
       <c r="B21" s="35">
         <v>46187</v>
       </c>
@@ -12123,7 +12135,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="122"/>
+      <c r="A22" s="146"/>
       <c r="B22" s="35">
         <v>46193</v>
       </c>
@@ -12151,7 +12163,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="122"/>
+      <c r="A23" s="146"/>
       <c r="B23" s="35">
         <v>46193</v>
       </c>
@@ -12179,7 +12191,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="122"/>
+      <c r="A24" s="146"/>
       <c r="B24" s="35">
         <v>46198</v>
       </c>
@@ -12207,7 +12219,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="123"/>
+      <c r="A25" s="147"/>
       <c r="B25" s="42">
         <v>46198</v>
       </c>
@@ -12269,7 +12281,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="112" t="s">
+      <c r="A28" s="136" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="35">
@@ -12295,7 +12307,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="113"/>
+      <c r="A29" s="137"/>
       <c r="B29" s="35">
         <v>46187</v>
       </c>
@@ -12323,7 +12335,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="113"/>
+      <c r="A30" s="137"/>
       <c r="B30" s="35">
         <v>46192</v>
       </c>
@@ -12351,7 +12363,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="113"/>
+      <c r="A31" s="137"/>
       <c r="B31" s="35">
         <v>46193</v>
       </c>
@@ -12379,7 +12391,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="113"/>
+      <c r="A32" s="137"/>
       <c r="B32" s="35">
         <v>46199</v>
       </c>
@@ -12407,7 +12419,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="114"/>
+      <c r="A33" s="138"/>
       <c r="B33" s="42">
         <v>46199</v>
       </c>
@@ -12469,7 +12481,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="130" t="s">
+      <c r="A36" s="118" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="35">
@@ -12499,7 +12511,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="131"/>
+      <c r="A37" s="119"/>
       <c r="B37" s="35">
         <v>46188</v>
       </c>
@@ -12527,7 +12539,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="131"/>
+      <c r="A38" s="119"/>
       <c r="B38" s="35">
         <v>46193</v>
       </c>
@@ -12555,7 +12567,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="131"/>
+      <c r="A39" s="119"/>
       <c r="B39" s="35">
         <v>46194</v>
       </c>
@@ -12583,7 +12595,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="131"/>
+      <c r="A40" s="119"/>
       <c r="B40" s="35">
         <v>46198</v>
       </c>
@@ -12611,7 +12623,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="132"/>
+      <c r="A41" s="120"/>
       <c r="B41" s="42">
         <v>46198</v>
       </c>
@@ -12673,7 +12685,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="133" t="s">
+      <c r="A44" s="121" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="35">
@@ -12703,7 +12715,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="134"/>
+      <c r="A45" s="122"/>
       <c r="B45" s="35">
         <v>46188</v>
       </c>
@@ -12731,7 +12743,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="134"/>
+      <c r="A46" s="122"/>
       <c r="B46" s="35">
         <v>46193</v>
       </c>
@@ -12759,7 +12771,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="134"/>
+      <c r="A47" s="122"/>
       <c r="B47" s="35">
         <v>46194</v>
       </c>
@@ -12787,7 +12799,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="134"/>
+      <c r="A48" s="122"/>
       <c r="B48" s="35">
         <v>46199</v>
       </c>
@@ -12815,7 +12827,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="135"/>
+      <c r="A49" s="123"/>
       <c r="B49" s="42">
         <v>46199</v>
       </c>
@@ -12877,7 +12889,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="136" t="s">
+      <c r="A52" s="124" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="35">
@@ -12907,7 +12919,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="137"/>
+      <c r="A53" s="125"/>
       <c r="B53" s="35">
         <v>46189</v>
       </c>
@@ -12935,7 +12947,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="137"/>
+      <c r="A54" s="125"/>
       <c r="B54" s="35">
         <v>46194</v>
       </c>
@@ -12963,7 +12975,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="137"/>
+      <c r="A55" s="125"/>
       <c r="B55" s="35">
         <v>46195</v>
       </c>
@@ -12991,7 +13003,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="137"/>
+      <c r="A56" s="125"/>
       <c r="B56" s="35">
         <v>46200</v>
       </c>
@@ -13019,7 +13031,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="138"/>
+      <c r="A57" s="126"/>
       <c r="B57" s="42">
         <v>46200</v>
       </c>
@@ -13081,7 +13093,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="139" t="s">
+      <c r="A60" s="127" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="35">
@@ -13111,7 +13123,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="140"/>
+      <c r="A61" s="128"/>
       <c r="B61" s="35">
         <v>46189</v>
       </c>
@@ -13139,7 +13151,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="140"/>
+      <c r="A62" s="128"/>
       <c r="B62" s="35">
         <v>46194</v>
       </c>
@@ -13167,7 +13179,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="140"/>
+      <c r="A63" s="128"/>
       <c r="B63" s="35">
         <v>46195</v>
       </c>
@@ -13195,7 +13207,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="140"/>
+      <c r="A64" s="128"/>
       <c r="B64" s="35">
         <v>46200</v>
       </c>
@@ -13223,7 +13235,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="141"/>
+      <c r="A65" s="129"/>
       <c r="B65" s="42">
         <v>46200</v>
       </c>
@@ -13285,7 +13297,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="142" t="s">
+      <c r="A68" s="130" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="35">
@@ -13315,7 +13327,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="143"/>
+      <c r="A69" s="131"/>
       <c r="B69" s="35">
         <v>46190</v>
       </c>
@@ -13343,7 +13355,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="143"/>
+      <c r="A70" s="131"/>
       <c r="B70" s="35">
         <v>46195</v>
       </c>
@@ -13371,7 +13383,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="143"/>
+      <c r="A71" s="131"/>
       <c r="B71" s="35">
         <v>46196</v>
       </c>
@@ -13399,7 +13411,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="143"/>
+      <c r="A72" s="131"/>
       <c r="B72" s="35">
         <v>46199</v>
       </c>
@@ -13427,7 +13439,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="144"/>
+      <c r="A73" s="132"/>
       <c r="B73" s="42">
         <v>46199</v>
       </c>
@@ -13489,7 +13501,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="145" t="s">
+      <c r="A76" s="133" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="35">
@@ -13519,7 +13531,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="146"/>
+      <c r="A77" s="134"/>
       <c r="B77" s="35">
         <v>46190</v>
       </c>
@@ -13547,7 +13559,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="146"/>
+      <c r="A78" s="134"/>
       <c r="B78" s="35">
         <v>46195</v>
       </c>
@@ -13575,7 +13587,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="146"/>
+      <c r="A79" s="134"/>
       <c r="B79" s="35">
         <v>46196</v>
       </c>
@@ -13603,7 +13615,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="146"/>
+      <c r="A80" s="134"/>
       <c r="B80" s="35">
         <v>46201</v>
       </c>
@@ -13631,7 +13643,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="147"/>
+      <c r="A81" s="135"/>
       <c r="B81" s="42">
         <v>46201</v>
       </c>
@@ -13693,7 +13705,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="124" t="s">
+      <c r="A84" s="112" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="35">
@@ -13717,13 +13729,13 @@
       <c r="H84" s="46" t="s">
         <v>62</v>
       </c>
-      <c r="J84" s="1" t="str">
+      <c r="J84" s="1">
         <f>IF(OR(Resultados!F84="",Resultados!G84=""),"",IF(AND(F84=Resultados!F84,G84=Resultados!G84),2,IF(((F84&gt;G84)=(Resultados!F84&gt;Resultados!G84))*((F84&lt;G84)=(Resultados!F84&lt;Resultados!G84)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="125"/>
+      <c r="A85" s="113"/>
       <c r="B85" s="35">
         <v>46191</v>
       </c>
@@ -13751,7 +13763,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="125"/>
+      <c r="A86" s="113"/>
       <c r="B86" s="35">
         <v>46196</v>
       </c>
@@ -13779,7 +13791,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="125"/>
+      <c r="A87" s="113"/>
       <c r="B87" s="35">
         <v>46197</v>
       </c>
@@ -13807,7 +13819,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="125"/>
+      <c r="A88" s="113"/>
       <c r="B88" s="35">
         <v>46201</v>
       </c>
@@ -13835,7 +13847,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="126"/>
+      <c r="A89" s="114"/>
       <c r="B89" s="42">
         <v>46201</v>
       </c>
@@ -13897,7 +13909,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="127" t="s">
+      <c r="A92" s="115" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="35">
@@ -13921,13 +13933,13 @@
       <c r="H92" s="46" t="s">
         <v>67</v>
       </c>
-      <c r="J92" s="1" t="str">
+      <c r="J92" s="1">
         <f>IF(OR(Resultados!F92="",Resultados!G92=""),"",IF(AND(F92=Resultados!F92,G92=Resultados!G92),2,IF(((F92&gt;G92)=(Resultados!F92&gt;Resultados!G92))*((F92&lt;G92)=(Resultados!F92&lt;Resultados!G92)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="128"/>
+      <c r="A93" s="116"/>
       <c r="B93" s="35">
         <v>46191</v>
       </c>
@@ -13949,13 +13961,13 @@
       <c r="H93" s="46" t="s">
         <v>69</v>
       </c>
-      <c r="J93" s="1" t="str">
+      <c r="J93" s="1">
         <f>IF(OR(Resultados!F93="",Resultados!G93=""),"",IF(AND(F93=Resultados!F93,G93=Resultados!G93),2,IF(((F93&gt;G93)=(Resultados!F93&gt;Resultados!G93))*((F93&lt;G93)=(Resultados!F93&lt;Resultados!G93)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="128"/>
+      <c r="A94" s="116"/>
       <c r="B94" s="35">
         <v>46196</v>
       </c>
@@ -13983,7 +13995,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="128"/>
+      <c r="A95" s="116"/>
       <c r="B95" s="35">
         <v>46197</v>
       </c>
@@ -14011,7 +14023,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="128"/>
+      <c r="A96" s="116"/>
       <c r="B96" s="35">
         <v>46200</v>
       </c>
@@ -14039,7 +14051,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="129"/>
+      <c r="A97" s="117"/>
       <c r="B97" s="42">
         <v>46200</v>
       </c>
@@ -14068,6 +14080,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A28:A33"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:A9"/>
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="A20:A25"/>
     <mergeCell ref="A84:A89"/>
     <mergeCell ref="A92:A97"/>
     <mergeCell ref="A36:A41"/>
@@ -14076,12 +14094,6 @@
     <mergeCell ref="A60:A65"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="A76:A81"/>
-    <mergeCell ref="A28:A33"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A4:A9"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="A20:A25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -14109,26 +14121,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="64" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="66"/>
+      <c r="A1" s="70" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="72"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="67"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="69"/>
+      <c r="A2" s="73"/>
+      <c r="B2" s="74"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="75"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -14161,7 +14173,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="91" t="s">
+      <c r="A4" s="97" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -14187,11 +14199,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="92"/>
+      <c r="A5" s="98"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -14215,7 +14227,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="92"/>
+      <c r="A6" s="98"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -14243,7 +14255,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="92"/>
+      <c r="A7" s="98"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -14271,7 +14283,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="92"/>
+      <c r="A8" s="98"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -14299,7 +14311,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="93"/>
+      <c r="A9" s="99"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -14361,7 +14373,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="94" t="s">
+      <c r="A12" s="100" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -14387,7 +14399,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="95"/>
+      <c r="A13" s="101"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -14411,7 +14423,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="95"/>
+      <c r="A14" s="101"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -14439,7 +14451,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="95"/>
+      <c r="A15" s="101"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -14467,7 +14479,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="95"/>
+      <c r="A16" s="101"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -14495,7 +14507,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="96"/>
+      <c r="A17" s="102"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -14557,7 +14569,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="97" t="s">
+      <c r="A20" s="103" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -14583,7 +14595,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="98"/>
+      <c r="A21" s="104"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -14611,7 +14623,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="98"/>
+      <c r="A22" s="104"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -14639,7 +14651,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="98"/>
+      <c r="A23" s="104"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -14667,7 +14679,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="98"/>
+      <c r="A24" s="104"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -14695,7 +14707,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="99"/>
+      <c r="A25" s="105"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -14757,7 +14769,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="100" t="s">
+      <c r="A28" s="106" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -14783,7 +14795,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="101"/>
+      <c r="A29" s="107"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -14811,7 +14823,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="101"/>
+      <c r="A30" s="107"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -14839,7 +14851,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="101"/>
+      <c r="A31" s="107"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -14867,7 +14879,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="101"/>
+      <c r="A32" s="107"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -14895,7 +14907,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="102"/>
+      <c r="A33" s="108"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -14957,7 +14969,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="103" t="s">
+      <c r="A36" s="109" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -14987,7 +14999,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="104"/>
+      <c r="A37" s="110"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -15015,7 +15027,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="104"/>
+      <c r="A38" s="110"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -15043,7 +15055,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="104"/>
+      <c r="A39" s="110"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -15071,7 +15083,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="104"/>
+      <c r="A40" s="110"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -15099,7 +15111,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="105"/>
+      <c r="A41" s="111"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -15161,7 +15173,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="73" t="s">
+      <c r="A44" s="79" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -15191,7 +15203,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="74"/>
+      <c r="A45" s="80"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -15219,7 +15231,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="74"/>
+      <c r="A46" s="80"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -15247,7 +15259,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="74"/>
+      <c r="A47" s="80"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -15275,7 +15287,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="74"/>
+      <c r="A48" s="80"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -15303,7 +15315,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="75"/>
+      <c r="A49" s="81"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -15365,7 +15377,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="76" t="s">
+      <c r="A52" s="82" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -15395,7 +15407,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="77"/>
+      <c r="A53" s="83"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -15423,7 +15435,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="77"/>
+      <c r="A54" s="83"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -15451,7 +15463,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="77"/>
+      <c r="A55" s="83"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -15479,7 +15491,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="77"/>
+      <c r="A56" s="83"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -15507,7 +15519,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="78"/>
+      <c r="A57" s="84"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -15569,7 +15581,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="79" t="s">
+      <c r="A60" s="85" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -15599,7 +15611,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="80"/>
+      <c r="A61" s="86"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -15627,7 +15639,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="80"/>
+      <c r="A62" s="86"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -15655,7 +15667,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="80"/>
+      <c r="A63" s="86"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -15683,7 +15695,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="80"/>
+      <c r="A64" s="86"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -15711,7 +15723,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="81"/>
+      <c r="A65" s="87"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -15773,7 +15785,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="82" t="s">
+      <c r="A68" s="88" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -15803,7 +15815,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="83"/>
+      <c r="A69" s="89"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -15831,7 +15843,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="83"/>
+      <c r="A70" s="89"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -15859,7 +15871,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="83"/>
+      <c r="A71" s="89"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -15887,7 +15899,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="83"/>
+      <c r="A72" s="89"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -15915,7 +15927,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="84"/>
+      <c r="A73" s="90"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -15977,7 +15989,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="85" t="s">
+      <c r="A76" s="91" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -16007,7 +16019,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="86"/>
+      <c r="A77" s="92"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -16035,7 +16047,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="86"/>
+      <c r="A78" s="92"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -16063,7 +16075,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="86"/>
+      <c r="A79" s="92"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -16091,7 +16103,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="86"/>
+      <c r="A80" s="92"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -16119,7 +16131,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="87"/>
+      <c r="A81" s="93"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -16181,7 +16193,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="88" t="s">
+      <c r="A84" s="94" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -16205,13 +16217,13 @@
       <c r="H84" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="J84" s="1" t="str">
+      <c r="J84" s="1">
         <f>IF(OR(Resultados!F84="",Resultados!G84=""),"",IF(AND(F84=Resultados!F84,G84=Resultados!G84),2,IF(((F84&gt;G84)=(Resultados!F84&gt;Resultados!G84))*((F84&lt;G84)=(Resultados!F84&lt;Resultados!G84)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="89"/>
+      <c r="A85" s="95"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -16239,7 +16251,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="89"/>
+      <c r="A86" s="95"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -16267,7 +16279,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="89"/>
+      <c r="A87" s="95"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -16295,7 +16307,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="89"/>
+      <c r="A88" s="95"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -16323,7 +16335,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="90"/>
+      <c r="A89" s="96"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -16385,7 +16397,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="70" t="s">
+      <c r="A92" s="76" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -16409,13 +16421,13 @@
       <c r="H92" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="J92" s="1" t="str">
+      <c r="J92" s="1">
         <f>IF(OR(Resultados!F92="",Resultados!G92=""),"",IF(AND(F92=Resultados!F92,G92=Resultados!G92),2,IF(((F92&gt;G92)=(Resultados!F92&gt;Resultados!G92))*((F92&lt;G92)=(Resultados!F92&lt;Resultados!G92)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="71"/>
+      <c r="A93" s="77"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -16437,13 +16449,13 @@
       <c r="H93" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="J93" s="1" t="str">
+      <c r="J93" s="1">
         <f>IF(OR(Resultados!F93="",Resultados!G93=""),"",IF(AND(F93=Resultados!F93,G93=Resultados!G93),2,IF(((F93&gt;G93)=(Resultados!F93&gt;Resultados!G93))*((F93&lt;G93)=(Resultados!F93&lt;Resultados!G93)),1,0)))</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="71"/>
+      <c r="A94" s="77"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -16471,7 +16483,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="71"/>
+      <c r="A95" s="77"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -16499,7 +16511,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="71"/>
+      <c r="A96" s="77"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -16527,7 +16539,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="72"/>
+      <c r="A97" s="78"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -16556,6 +16568,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A28:A33"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:A9"/>
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="A20:A25"/>
     <mergeCell ref="A84:A89"/>
     <mergeCell ref="A92:A97"/>
     <mergeCell ref="A36:A41"/>
@@ -16564,12 +16582,6 @@
     <mergeCell ref="A60:A65"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="A76:A81"/>
-    <mergeCell ref="A28:A33"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A4:A9"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="A20:A25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -16597,26 +16609,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="64" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="66"/>
+      <c r="A1" s="70" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="72"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="67"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="69"/>
+      <c r="A2" s="73"/>
+      <c r="B2" s="74"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="75"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -16649,7 +16661,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="91" t="s">
+      <c r="A4" s="97" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -16675,11 +16687,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="92"/>
+      <c r="A5" s="98"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -16703,7 +16715,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="92"/>
+      <c r="A6" s="98"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -16731,7 +16743,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="92"/>
+      <c r="A7" s="98"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -16759,7 +16771,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="92"/>
+      <c r="A8" s="98"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -16787,7 +16799,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="93"/>
+      <c r="A9" s="99"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -16849,7 +16861,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="94" t="s">
+      <c r="A12" s="100" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -16875,7 +16887,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="95"/>
+      <c r="A13" s="101"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -16899,7 +16911,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="95"/>
+      <c r="A14" s="101"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -16927,7 +16939,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="95"/>
+      <c r="A15" s="101"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -16955,7 +16967,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="95"/>
+      <c r="A16" s="101"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -16983,7 +16995,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="96"/>
+      <c r="A17" s="102"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -17045,7 +17057,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="97" t="s">
+      <c r="A20" s="103" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -17071,7 +17083,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="98"/>
+      <c r="A21" s="104"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -17099,7 +17111,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="98"/>
+      <c r="A22" s="104"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -17127,7 +17139,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="98"/>
+      <c r="A23" s="104"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -17155,7 +17167,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="98"/>
+      <c r="A24" s="104"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -17183,7 +17195,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="99"/>
+      <c r="A25" s="105"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -17245,7 +17257,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="100" t="s">
+      <c r="A28" s="106" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -17271,7 +17283,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="101"/>
+      <c r="A29" s="107"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -17299,7 +17311,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="101"/>
+      <c r="A30" s="107"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -17327,7 +17339,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="101"/>
+      <c r="A31" s="107"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -17355,7 +17367,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="101"/>
+      <c r="A32" s="107"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -17383,7 +17395,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="102"/>
+      <c r="A33" s="108"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -17445,7 +17457,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="103" t="s">
+      <c r="A36" s="109" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -17475,7 +17487,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="104"/>
+      <c r="A37" s="110"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -17503,7 +17515,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="104"/>
+      <c r="A38" s="110"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -17531,7 +17543,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="104"/>
+      <c r="A39" s="110"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -17559,7 +17571,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="104"/>
+      <c r="A40" s="110"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -17587,7 +17599,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="105"/>
+      <c r="A41" s="111"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -17649,7 +17661,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="73" t="s">
+      <c r="A44" s="79" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -17679,7 +17691,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="74"/>
+      <c r="A45" s="80"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -17707,7 +17719,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="74"/>
+      <c r="A46" s="80"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -17735,7 +17747,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="74"/>
+      <c r="A47" s="80"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -17763,7 +17775,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="74"/>
+      <c r="A48" s="80"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -17791,7 +17803,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="75"/>
+      <c r="A49" s="81"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -17853,7 +17865,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="76" t="s">
+      <c r="A52" s="82" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -17883,7 +17895,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="77"/>
+      <c r="A53" s="83"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -17911,7 +17923,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="77"/>
+      <c r="A54" s="83"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -17939,7 +17951,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="77"/>
+      <c r="A55" s="83"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -17967,7 +17979,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="77"/>
+      <c r="A56" s="83"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -17995,7 +18007,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="78"/>
+      <c r="A57" s="84"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -18057,7 +18069,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="79" t="s">
+      <c r="A60" s="85" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -18087,7 +18099,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="80"/>
+      <c r="A61" s="86"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -18115,7 +18127,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="80"/>
+      <c r="A62" s="86"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -18143,7 +18155,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="80"/>
+      <c r="A63" s="86"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -18171,7 +18183,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="80"/>
+      <c r="A64" s="86"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -18199,7 +18211,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="81"/>
+      <c r="A65" s="87"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -18261,7 +18273,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="82" t="s">
+      <c r="A68" s="88" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -18291,7 +18303,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="83"/>
+      <c r="A69" s="89"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -18319,7 +18331,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="83"/>
+      <c r="A70" s="89"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -18347,7 +18359,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="83"/>
+      <c r="A71" s="89"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -18375,7 +18387,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="83"/>
+      <c r="A72" s="89"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -18403,7 +18415,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="84"/>
+      <c r="A73" s="90"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -18465,7 +18477,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="85" t="s">
+      <c r="A76" s="91" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -18495,7 +18507,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="86"/>
+      <c r="A77" s="92"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -18523,7 +18535,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="86"/>
+      <c r="A78" s="92"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -18551,7 +18563,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="86"/>
+      <c r="A79" s="92"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -18579,7 +18591,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="86"/>
+      <c r="A80" s="92"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -18607,7 +18619,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="87"/>
+      <c r="A81" s="93"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -18669,7 +18681,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="88" t="s">
+      <c r="A84" s="94" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -18693,13 +18705,13 @@
       <c r="H84" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="J84" s="1" t="str">
+      <c r="J84" s="1">
         <f>IF(OR(Resultados!F84="",Resultados!G84=""),"",IF(AND(F84=Resultados!F84,G84=Resultados!G84),2,IF(((F84&gt;G84)=(Resultados!F84&gt;Resultados!G84))*((F84&lt;G84)=(Resultados!F84&lt;Resultados!G84)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="89"/>
+      <c r="A85" s="95"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -18727,7 +18739,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="89"/>
+      <c r="A86" s="95"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -18755,7 +18767,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="89"/>
+      <c r="A87" s="95"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -18783,7 +18795,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="89"/>
+      <c r="A88" s="95"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -18811,7 +18823,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="90"/>
+      <c r="A89" s="96"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -18873,7 +18885,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="70" t="s">
+      <c r="A92" s="76" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -18897,13 +18909,13 @@
       <c r="H92" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="J92" s="1" t="str">
+      <c r="J92" s="1">
         <f>IF(OR(Resultados!F92="",Resultados!G92=""),"",IF(AND(F92=Resultados!F92,G92=Resultados!G92),2,IF(((F92&gt;G92)=(Resultados!F92&gt;Resultados!G92))*((F92&lt;G92)=(Resultados!F92&lt;Resultados!G92)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="71"/>
+      <c r="A93" s="77"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -18925,13 +18937,13 @@
       <c r="H93" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="J93" s="1" t="str">
+      <c r="J93" s="1">
         <f>IF(OR(Resultados!F93="",Resultados!G93=""),"",IF(AND(F93=Resultados!F93,G93=Resultados!G93),2,IF(((F93&gt;G93)=(Resultados!F93&gt;Resultados!G93))*((F93&lt;G93)=(Resultados!F93&lt;Resultados!G93)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="71"/>
+      <c r="A94" s="77"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -18959,7 +18971,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="71"/>
+      <c r="A95" s="77"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -18987,7 +18999,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="71"/>
+      <c r="A96" s="77"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -19015,7 +19027,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="72"/>
+      <c r="A97" s="78"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -19044,6 +19056,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A28:A33"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:A9"/>
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="A20:A25"/>
     <mergeCell ref="A84:A89"/>
     <mergeCell ref="A92:A97"/>
     <mergeCell ref="A36:A41"/>
@@ -19052,12 +19070,6 @@
     <mergeCell ref="A60:A65"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="A76:A81"/>
-    <mergeCell ref="A28:A33"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A4:A9"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="A20:A25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19085,26 +19097,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="64" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="66"/>
+      <c r="A1" s="70" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="72"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="67"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="69"/>
+      <c r="A2" s="73"/>
+      <c r="B2" s="74"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="75"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -19137,7 +19149,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="91" t="s">
+      <c r="A4" s="97" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -19163,11 +19175,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="92"/>
+      <c r="A5" s="98"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -19191,7 +19203,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="92"/>
+      <c r="A6" s="98"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -19219,7 +19231,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="92"/>
+      <c r="A7" s="98"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -19247,7 +19259,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="92"/>
+      <c r="A8" s="98"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -19275,7 +19287,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="93"/>
+      <c r="A9" s="99"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -19337,7 +19349,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="94" t="s">
+      <c r="A12" s="100" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -19363,7 +19375,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="95"/>
+      <c r="A13" s="101"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -19387,7 +19399,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="95"/>
+      <c r="A14" s="101"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -19415,7 +19427,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="95"/>
+      <c r="A15" s="101"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -19443,7 +19455,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="95"/>
+      <c r="A16" s="101"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -19471,7 +19483,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="96"/>
+      <c r="A17" s="102"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -19533,7 +19545,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="97" t="s">
+      <c r="A20" s="103" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -19559,7 +19571,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="98"/>
+      <c r="A21" s="104"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -19587,7 +19599,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="98"/>
+      <c r="A22" s="104"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -19615,7 +19627,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="98"/>
+      <c r="A23" s="104"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -19643,7 +19655,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="98"/>
+      <c r="A24" s="104"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -19671,7 +19683,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="99"/>
+      <c r="A25" s="105"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -19733,7 +19745,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="100" t="s">
+      <c r="A28" s="106" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -19759,7 +19771,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="101"/>
+      <c r="A29" s="107"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -19787,7 +19799,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="101"/>
+      <c r="A30" s="107"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -19815,7 +19827,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="101"/>
+      <c r="A31" s="107"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -19843,7 +19855,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="101"/>
+      <c r="A32" s="107"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -19867,7 +19879,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="102"/>
+      <c r="A33" s="108"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -19925,7 +19937,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="103" t="s">
+      <c r="A36" s="109" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -19955,7 +19967,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="104"/>
+      <c r="A37" s="110"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -19983,7 +19995,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="104"/>
+      <c r="A38" s="110"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -20007,7 +20019,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="104"/>
+      <c r="A39" s="110"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -20031,7 +20043,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="104"/>
+      <c r="A40" s="110"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -20055,7 +20067,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="105"/>
+      <c r="A41" s="111"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -20113,7 +20125,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="73" t="s">
+      <c r="A44" s="79" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -20143,7 +20155,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="74"/>
+      <c r="A45" s="80"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -20171,7 +20183,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="74"/>
+      <c r="A46" s="80"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -20195,7 +20207,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="74"/>
+      <c r="A47" s="80"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -20219,7 +20231,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="74"/>
+      <c r="A48" s="80"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -20243,7 +20255,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="75"/>
+      <c r="A49" s="81"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -20301,7 +20313,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="76" t="s">
+      <c r="A52" s="82" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -20331,7 +20343,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="77"/>
+      <c r="A53" s="83"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -20359,7 +20371,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="77"/>
+      <c r="A54" s="83"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -20383,7 +20395,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="77"/>
+      <c r="A55" s="83"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -20407,7 +20419,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="77"/>
+      <c r="A56" s="83"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -20431,7 +20443,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="78"/>
+      <c r="A57" s="84"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -20489,7 +20501,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="79" t="s">
+      <c r="A60" s="85" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -20519,7 +20531,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="80"/>
+      <c r="A61" s="86"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -20547,7 +20559,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="80"/>
+      <c r="A62" s="86"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -20571,7 +20583,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="80"/>
+      <c r="A63" s="86"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -20595,7 +20607,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="80"/>
+      <c r="A64" s="86"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -20619,7 +20631,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="81"/>
+      <c r="A65" s="87"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -20677,7 +20689,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="82" t="s">
+      <c r="A68" s="88" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -20707,7 +20719,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="83"/>
+      <c r="A69" s="89"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -20735,7 +20747,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="83"/>
+      <c r="A70" s="89"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -20759,7 +20771,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="83"/>
+      <c r="A71" s="89"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -20783,7 +20795,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="83"/>
+      <c r="A72" s="89"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -20807,7 +20819,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="84"/>
+      <c r="A73" s="90"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -20865,7 +20877,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="85" t="s">
+      <c r="A76" s="91" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -20895,7 +20907,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="86"/>
+      <c r="A77" s="92"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -20923,7 +20935,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="86"/>
+      <c r="A78" s="92"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -20947,7 +20959,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="86"/>
+      <c r="A79" s="92"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -20971,7 +20983,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="86"/>
+      <c r="A80" s="92"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -20995,7 +21007,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="87"/>
+      <c r="A81" s="93"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -21053,7 +21065,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="88" t="s">
+      <c r="A84" s="94" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -21077,13 +21089,13 @@
       <c r="H84" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="J84" s="1" t="str">
+      <c r="J84" s="1">
         <f>IF(OR(Resultados!F84="",Resultados!G84=""),"",IF(AND(F84=Resultados!F84,G84=Resultados!G84),2,IF(((F84&gt;G84)=(Resultados!F84&gt;Resultados!G84))*((F84&lt;G84)=(Resultados!F84&lt;Resultados!G84)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="89"/>
+      <c r="A85" s="95"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -21111,7 +21123,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="89"/>
+      <c r="A86" s="95"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -21135,7 +21147,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="89"/>
+      <c r="A87" s="95"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -21159,7 +21171,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="89"/>
+      <c r="A88" s="95"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -21183,7 +21195,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="90"/>
+      <c r="A89" s="96"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -21241,7 +21253,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="70" t="s">
+      <c r="A92" s="76" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -21265,13 +21277,13 @@
       <c r="H92" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="J92" s="1" t="str">
+      <c r="J92" s="1">
         <f>IF(OR(Resultados!F92="",Resultados!G92=""),"",IF(AND(F92=Resultados!F92,G92=Resultados!G92),2,IF(((F92&gt;G92)=(Resultados!F92&gt;Resultados!G92))*((F92&lt;G92)=(Resultados!F92&lt;Resultados!G92)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="71"/>
+      <c r="A93" s="77"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -21293,13 +21305,13 @@
       <c r="H93" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="J93" s="1" t="str">
+      <c r="J93" s="1">
         <f>IF(OR(Resultados!F93="",Resultados!G93=""),"",IF(AND(F93=Resultados!F93,G93=Resultados!G93),2,IF(((F93&gt;G93)=(Resultados!F93&gt;Resultados!G93))*((F93&lt;G93)=(Resultados!F93&lt;Resultados!G93)),1,0)))</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="71"/>
+      <c r="A94" s="77"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -21323,7 +21335,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="71"/>
+      <c r="A95" s="77"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -21347,7 +21359,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="71"/>
+      <c r="A96" s="77"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -21371,7 +21383,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="72"/>
+      <c r="A97" s="78"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -21396,6 +21408,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A28:A33"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:A9"/>
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="A20:A25"/>
     <mergeCell ref="A84:A89"/>
     <mergeCell ref="A92:A97"/>
     <mergeCell ref="A36:A41"/>
@@ -21404,12 +21422,6 @@
     <mergeCell ref="A60:A65"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="A76:A81"/>
-    <mergeCell ref="A28:A33"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A4:A9"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="A20:A25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21437,26 +21449,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="64" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="66"/>
+      <c r="A1" s="70" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="72"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="67"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="69"/>
+      <c r="A2" s="73"/>
+      <c r="B2" s="74"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="75"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -21489,7 +21501,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="91" t="s">
+      <c r="A4" s="97" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -21515,11 +21527,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="92"/>
+      <c r="A5" s="98"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -21543,7 +21555,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="92"/>
+      <c r="A6" s="98"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -21571,7 +21583,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="92"/>
+      <c r="A7" s="98"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -21599,7 +21611,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="92"/>
+      <c r="A8" s="98"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -21627,7 +21639,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="93"/>
+      <c r="A9" s="99"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -21689,7 +21701,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="94" t="s">
+      <c r="A12" s="100" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -21715,7 +21727,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="95"/>
+      <c r="A13" s="101"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -21739,7 +21751,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="95"/>
+      <c r="A14" s="101"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -21767,7 +21779,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="95"/>
+      <c r="A15" s="101"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -21795,7 +21807,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="95"/>
+      <c r="A16" s="101"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -21823,7 +21835,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="96"/>
+      <c r="A17" s="102"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -21885,7 +21897,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="97" t="s">
+      <c r="A20" s="103" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -21911,7 +21923,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="98"/>
+      <c r="A21" s="104"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -21939,7 +21951,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="98"/>
+      <c r="A22" s="104"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -21967,7 +21979,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="98"/>
+      <c r="A23" s="104"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -21995,7 +22007,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="98"/>
+      <c r="A24" s="104"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -22023,7 +22035,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="99"/>
+      <c r="A25" s="105"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -22085,7 +22097,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="100" t="s">
+      <c r="A28" s="106" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -22111,7 +22123,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="101"/>
+      <c r="A29" s="107"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -22139,7 +22151,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="101"/>
+      <c r="A30" s="107"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -22167,7 +22179,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="101"/>
+      <c r="A31" s="107"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -22195,7 +22207,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="101"/>
+      <c r="A32" s="107"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -22223,7 +22235,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="102"/>
+      <c r="A33" s="108"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -22285,7 +22297,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="103" t="s">
+      <c r="A36" s="109" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -22315,7 +22327,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="104"/>
+      <c r="A37" s="110"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -22343,7 +22355,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="104"/>
+      <c r="A38" s="110"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -22371,7 +22383,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="104"/>
+      <c r="A39" s="110"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -22399,7 +22411,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="104"/>
+      <c r="A40" s="110"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -22427,7 +22439,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="105"/>
+      <c r="A41" s="111"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -22489,7 +22501,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="73" t="s">
+      <c r="A44" s="79" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -22519,7 +22531,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="74"/>
+      <c r="A45" s="80"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -22547,7 +22559,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="74"/>
+      <c r="A46" s="80"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -22575,7 +22587,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="74"/>
+      <c r="A47" s="80"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -22603,7 +22615,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="74"/>
+      <c r="A48" s="80"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -22631,7 +22643,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="75"/>
+      <c r="A49" s="81"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -22693,7 +22705,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="76" t="s">
+      <c r="A52" s="82" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -22723,7 +22735,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="77"/>
+      <c r="A53" s="83"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -22751,7 +22763,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="77"/>
+      <c r="A54" s="83"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -22779,7 +22791,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="77"/>
+      <c r="A55" s="83"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -22807,7 +22819,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="77"/>
+      <c r="A56" s="83"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -22835,7 +22847,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="78"/>
+      <c r="A57" s="84"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -22897,7 +22909,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="79" t="s">
+      <c r="A60" s="85" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -22927,7 +22939,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="80"/>
+      <c r="A61" s="86"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -22955,7 +22967,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="80"/>
+      <c r="A62" s="86"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -22983,7 +22995,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="80"/>
+      <c r="A63" s="86"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -23011,7 +23023,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="80"/>
+      <c r="A64" s="86"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -23039,7 +23051,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="81"/>
+      <c r="A65" s="87"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -23101,7 +23113,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="82" t="s">
+      <c r="A68" s="88" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -23131,7 +23143,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="83"/>
+      <c r="A69" s="89"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -23159,7 +23171,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="83"/>
+      <c r="A70" s="89"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -23187,7 +23199,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="83"/>
+      <c r="A71" s="89"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -23215,7 +23227,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="83"/>
+      <c r="A72" s="89"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -23243,7 +23255,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="84"/>
+      <c r="A73" s="90"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -23305,7 +23317,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="85" t="s">
+      <c r="A76" s="91" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -23335,7 +23347,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="86"/>
+      <c r="A77" s="92"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -23363,7 +23375,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="86"/>
+      <c r="A78" s="92"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -23391,7 +23403,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="86"/>
+      <c r="A79" s="92"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -23419,7 +23431,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="86"/>
+      <c r="A80" s="92"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -23447,7 +23459,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="87"/>
+      <c r="A81" s="93"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -23509,7 +23521,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="88" t="s">
+      <c r="A84" s="94" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -23533,13 +23545,13 @@
       <c r="H84" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="J84" s="1" t="str">
+      <c r="J84" s="1">
         <f>IF(OR(Resultados!F84="",Resultados!G84=""),"",IF(AND(F84=Resultados!F84,G84=Resultados!G84),2,IF(((F84&gt;G84)=(Resultados!F84&gt;Resultados!G84))*((F84&lt;G84)=(Resultados!F84&lt;Resultados!G84)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="89"/>
+      <c r="A85" s="95"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -23567,7 +23579,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="89"/>
+      <c r="A86" s="95"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -23595,7 +23607,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="89"/>
+      <c r="A87" s="95"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -23623,7 +23635,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="89"/>
+      <c r="A88" s="95"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -23651,7 +23663,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="90"/>
+      <c r="A89" s="96"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -23713,7 +23725,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="70" t="s">
+      <c r="A92" s="76" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -23737,13 +23749,13 @@
       <c r="H92" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="J92" s="1" t="str">
+      <c r="J92" s="1">
         <f>IF(OR(Resultados!F92="",Resultados!G92=""),"",IF(AND(F92=Resultados!F92,G92=Resultados!G92),2,IF(((F92&gt;G92)=(Resultados!F92&gt;Resultados!G92))*((F92&lt;G92)=(Resultados!F92&lt;Resultados!G92)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="71"/>
+      <c r="A93" s="77"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -23765,13 +23777,13 @@
       <c r="H93" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="J93" s="1" t="str">
+      <c r="J93" s="1">
         <f>IF(OR(Resultados!F93="",Resultados!G93=""),"",IF(AND(F93=Resultados!F93,G93=Resultados!G93),2,IF(((F93&gt;G93)=(Resultados!F93&gt;Resultados!G93))*((F93&lt;G93)=(Resultados!F93&lt;Resultados!G93)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="71"/>
+      <c r="A94" s="77"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -23799,7 +23811,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="71"/>
+      <c r="A95" s="77"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -23827,7 +23839,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="71"/>
+      <c r="A96" s="77"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -23855,7 +23867,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="72"/>
+      <c r="A97" s="78"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -23884,6 +23896,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A28:A33"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:A9"/>
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="A20:A25"/>
     <mergeCell ref="A84:A89"/>
     <mergeCell ref="A92:A97"/>
     <mergeCell ref="A36:A41"/>
@@ -23892,12 +23910,6 @@
     <mergeCell ref="A60:A65"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="A76:A81"/>
-    <mergeCell ref="A28:A33"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A4:A9"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="A20:A25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -23925,26 +23937,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="64" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="66"/>
+      <c r="A1" s="70" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="72"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="67"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="69"/>
+      <c r="A2" s="73"/>
+      <c r="B2" s="74"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="75"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -23977,7 +23989,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="91" t="s">
+      <c r="A4" s="97" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -24003,11 +24015,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="92"/>
+      <c r="A5" s="98"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -24031,7 +24043,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="92"/>
+      <c r="A6" s="98"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -24059,7 +24071,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="92"/>
+      <c r="A7" s="98"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -24087,7 +24099,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="92"/>
+      <c r="A8" s="98"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -24115,7 +24127,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="93"/>
+      <c r="A9" s="99"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -24177,7 +24189,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="94" t="s">
+      <c r="A12" s="100" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -24203,7 +24215,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="95"/>
+      <c r="A13" s="101"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -24227,7 +24239,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="95"/>
+      <c r="A14" s="101"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -24255,7 +24267,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="95"/>
+      <c r="A15" s="101"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -24283,7 +24295,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="95"/>
+      <c r="A16" s="101"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -24311,7 +24323,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="96"/>
+      <c r="A17" s="102"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -24373,7 +24385,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="97" t="s">
+      <c r="A20" s="103" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -24399,7 +24411,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="98"/>
+      <c r="A21" s="104"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -24427,7 +24439,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="98"/>
+      <c r="A22" s="104"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -24455,7 +24467,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="98"/>
+      <c r="A23" s="104"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -24483,7 +24495,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="98"/>
+      <c r="A24" s="104"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -24511,7 +24523,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="99"/>
+      <c r="A25" s="105"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -24573,7 +24585,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="100" t="s">
+      <c r="A28" s="106" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -24599,7 +24611,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="101"/>
+      <c r="A29" s="107"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -24627,7 +24639,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="101"/>
+      <c r="A30" s="107"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -24655,7 +24667,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="101"/>
+      <c r="A31" s="107"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -24683,7 +24695,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="101"/>
+      <c r="A32" s="107"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -24711,7 +24723,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="102"/>
+      <c r="A33" s="108"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -24773,7 +24785,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="103" t="s">
+      <c r="A36" s="109" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -24803,7 +24815,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="104"/>
+      <c r="A37" s="110"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -24831,7 +24843,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="104"/>
+      <c r="A38" s="110"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -24859,7 +24871,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="104"/>
+      <c r="A39" s="110"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -24887,7 +24899,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="104"/>
+      <c r="A40" s="110"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -24915,7 +24927,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="105"/>
+      <c r="A41" s="111"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -24977,7 +24989,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="73" t="s">
+      <c r="A44" s="79" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -25007,7 +25019,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="74"/>
+      <c r="A45" s="80"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -25035,7 +25047,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="74"/>
+      <c r="A46" s="80"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -25063,7 +25075,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="74"/>
+      <c r="A47" s="80"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -25091,7 +25103,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="74"/>
+      <c r="A48" s="80"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -25119,7 +25131,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="75"/>
+      <c r="A49" s="81"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -25181,7 +25193,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="76" t="s">
+      <c r="A52" s="82" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -25211,7 +25223,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="77"/>
+      <c r="A53" s="83"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -25239,7 +25251,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="77"/>
+      <c r="A54" s="83"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -25267,7 +25279,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="77"/>
+      <c r="A55" s="83"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -25295,7 +25307,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="77"/>
+      <c r="A56" s="83"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -25323,7 +25335,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="78"/>
+      <c r="A57" s="84"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -25385,7 +25397,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="79" t="s">
+      <c r="A60" s="85" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -25415,7 +25427,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="80"/>
+      <c r="A61" s="86"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -25443,7 +25455,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="80"/>
+      <c r="A62" s="86"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -25471,7 +25483,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="80"/>
+      <c r="A63" s="86"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -25499,7 +25511,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="80"/>
+      <c r="A64" s="86"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -25527,7 +25539,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="81"/>
+      <c r="A65" s="87"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -25589,7 +25601,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="82" t="s">
+      <c r="A68" s="88" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -25619,7 +25631,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="83"/>
+      <c r="A69" s="89"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -25647,7 +25659,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="83"/>
+      <c r="A70" s="89"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -25675,7 +25687,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="83"/>
+      <c r="A71" s="89"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -25703,7 +25715,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="83"/>
+      <c r="A72" s="89"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -25731,7 +25743,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="84"/>
+      <c r="A73" s="90"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -25793,7 +25805,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="85" t="s">
+      <c r="A76" s="91" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -25823,7 +25835,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="86"/>
+      <c r="A77" s="92"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -25851,7 +25863,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="86"/>
+      <c r="A78" s="92"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -25879,7 +25891,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="86"/>
+      <c r="A79" s="92"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -25907,7 +25919,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="86"/>
+      <c r="A80" s="92"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -25935,7 +25947,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="87"/>
+      <c r="A81" s="93"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -25997,7 +26009,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="88" t="s">
+      <c r="A84" s="94" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -26021,13 +26033,13 @@
       <c r="H84" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="J84" s="1" t="str">
+      <c r="J84" s="1">
         <f>IF(OR(Resultados!F84="",Resultados!G84=""),"",IF(AND(F84=Resultados!F84,G84=Resultados!G84),2,IF(((F84&gt;G84)=(Resultados!F84&gt;Resultados!G84))*((F84&lt;G84)=(Resultados!F84&lt;Resultados!G84)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="89"/>
+      <c r="A85" s="95"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -26055,7 +26067,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="89"/>
+      <c r="A86" s="95"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -26083,7 +26095,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="89"/>
+      <c r="A87" s="95"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -26111,7 +26123,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="89"/>
+      <c r="A88" s="95"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -26139,7 +26151,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="90"/>
+      <c r="A89" s="96"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -26201,7 +26213,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="70" t="s">
+      <c r="A92" s="76" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -26225,13 +26237,13 @@
       <c r="H92" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="J92" s="1" t="str">
+      <c r="J92" s="1">
         <f>IF(OR(Resultados!F92="",Resultados!G92=""),"",IF(AND(F92=Resultados!F92,G92=Resultados!G92),2,IF(((F92&gt;G92)=(Resultados!F92&gt;Resultados!G92))*((F92&lt;G92)=(Resultados!F92&lt;Resultados!G92)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="71"/>
+      <c r="A93" s="77"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -26253,13 +26265,13 @@
       <c r="H93" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="J93" s="1" t="str">
+      <c r="J93" s="1">
         <f>IF(OR(Resultados!F93="",Resultados!G93=""),"",IF(AND(F93=Resultados!F93,G93=Resultados!G93),2,IF(((F93&gt;G93)=(Resultados!F93&gt;Resultados!G93))*((F93&lt;G93)=(Resultados!F93&lt;Resultados!G93)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="71"/>
+      <c r="A94" s="77"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -26287,7 +26299,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="71"/>
+      <c r="A95" s="77"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -26315,7 +26327,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="71"/>
+      <c r="A96" s="77"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -26343,7 +26355,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="72"/>
+      <c r="A97" s="78"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -26372,6 +26384,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A28:A33"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:A9"/>
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="A20:A25"/>
     <mergeCell ref="A84:A89"/>
     <mergeCell ref="A92:A97"/>
     <mergeCell ref="A36:A41"/>
@@ -26380,12 +26398,6 @@
     <mergeCell ref="A60:A65"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="A76:A81"/>
-    <mergeCell ref="A28:A33"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A4:A9"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="A20:A25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -26595,20 +26607,20 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="7461ab22-4e70-4395-beb5-078d6ab567bf" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="7461ab22-4e70-4395-beb5-078d6ab567bf" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -26630,6 +26642,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5511D132-9333-423C-BAEC-48101CE7245F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7DE79FC7-1424-4D12-B735-3F81ACD8E888}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
@@ -26643,12 +26663,4 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5511D132-9333-423C-BAEC-48101CE7245F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/Quiniela.xlsx
+++ b/data/Quiniela.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cindy\Desktop\QuinielaMundial\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D1D9EC3-0E9B-488E-BCD2-9424AE0D46C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BD9B628-7B3D-4101-B0CA-55C77DA724B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="6" xr2:uid="{9503E40F-C0E1-49CE-B4EA-3C401754995E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9503E40F-C0E1-49CE-B4EA-3C401754995E}"/>
   </bookViews>
   <sheets>
     <sheet name="Resultados" sheetId="1" r:id="rId1"/>
@@ -1248,24 +1248,6 @@
     <xf numFmtId="0" fontId="5" fillId="24" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="20" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="20" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="20" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="20" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="20" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="20" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1433,6 +1415,24 @@
     <xf numFmtId="0" fontId="7" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="20" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="20" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="20" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="20" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="20" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="20" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1933,26 +1933,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="70" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="72"/>
+      <c r="A1" s="64" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="66"/>
     </row>
     <row r="2" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="73"/>
-      <c r="B2" s="74"/>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="75"/>
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="69"/>
     </row>
     <row r="3" spans="1:8" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -1979,7 +1979,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="97" t="s">
+      <c r="A4" s="91" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -2005,7 +2005,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="98"/>
+      <c r="A5" s="92"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -2029,7 +2029,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="98"/>
+      <c r="A6" s="92"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -2049,7 +2049,7 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="98"/>
+      <c r="A7" s="92"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -2069,7 +2069,7 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="98"/>
+      <c r="A8" s="92"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -2089,7 +2089,7 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="99"/>
+      <c r="A9" s="93"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -2143,7 +2143,7 @@
       </c>
     </row>
     <row r="12" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="100" t="s">
+      <c r="A12" s="94" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -2169,7 +2169,7 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="101"/>
+      <c r="A13" s="95"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -2193,7 +2193,7 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="101"/>
+      <c r="A14" s="95"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -2213,7 +2213,7 @@
       </c>
     </row>
     <row r="15" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="101"/>
+      <c r="A15" s="95"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -2233,7 +2233,7 @@
       </c>
     </row>
     <row r="16" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="101"/>
+      <c r="A16" s="95"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -2253,7 +2253,7 @@
       </c>
     </row>
     <row r="17" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="102"/>
+      <c r="A17" s="96"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -2307,7 +2307,7 @@
       </c>
     </row>
     <row r="20" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="103" t="s">
+      <c r="A20" s="97" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -2333,7 +2333,7 @@
       </c>
     </row>
     <row r="21" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="104"/>
+      <c r="A21" s="98"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -2357,7 +2357,7 @@
       </c>
     </row>
     <row r="22" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="104"/>
+      <c r="A22" s="98"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -2377,7 +2377,7 @@
       </c>
     </row>
     <row r="23" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="104"/>
+      <c r="A23" s="98"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -2397,7 +2397,7 @@
       </c>
     </row>
     <row r="24" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="104"/>
+      <c r="A24" s="98"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -2417,7 +2417,7 @@
       </c>
     </row>
     <row r="25" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="105"/>
+      <c r="A25" s="99"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -2471,7 +2471,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="106" t="s">
+      <c r="A28" s="100" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -2497,7 +2497,7 @@
       </c>
     </row>
     <row r="29" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="107"/>
+      <c r="A29" s="101"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -2521,7 +2521,7 @@
       </c>
     </row>
     <row r="30" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="107"/>
+      <c r="A30" s="101"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -2541,7 +2541,7 @@
       </c>
     </row>
     <row r="31" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="107"/>
+      <c r="A31" s="101"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -2561,7 +2561,7 @@
       </c>
     </row>
     <row r="32" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="107"/>
+      <c r="A32" s="101"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -2581,7 +2581,7 @@
       </c>
     </row>
     <row r="33" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="108"/>
+      <c r="A33" s="102"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -2635,7 +2635,7 @@
       </c>
     </row>
     <row r="36" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="109" t="s">
+      <c r="A36" s="103" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -2661,7 +2661,7 @@
       </c>
     </row>
     <row r="37" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="110"/>
+      <c r="A37" s="104"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -2685,7 +2685,7 @@
       </c>
     </row>
     <row r="38" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="110"/>
+      <c r="A38" s="104"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -2705,7 +2705,7 @@
       </c>
     </row>
     <row r="39" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="110"/>
+      <c r="A39" s="104"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -2725,7 +2725,7 @@
       </c>
     </row>
     <row r="40" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="110"/>
+      <c r="A40" s="104"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -2745,7 +2745,7 @@
       </c>
     </row>
     <row r="41" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="111"/>
+      <c r="A41" s="105"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -2799,7 +2799,7 @@
       </c>
     </row>
     <row r="44" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="79" t="s">
+      <c r="A44" s="73" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -2825,7 +2825,7 @@
       </c>
     </row>
     <row r="45" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="80"/>
+      <c r="A45" s="74"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -2849,7 +2849,7 @@
       </c>
     </row>
     <row r="46" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="80"/>
+      <c r="A46" s="74"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -2869,7 +2869,7 @@
       </c>
     </row>
     <row r="47" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="80"/>
+      <c r="A47" s="74"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -2889,7 +2889,7 @@
       </c>
     </row>
     <row r="48" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="80"/>
+      <c r="A48" s="74"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -2909,7 +2909,7 @@
       </c>
     </row>
     <row r="49" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="81"/>
+      <c r="A49" s="75"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -2963,7 +2963,7 @@
       </c>
     </row>
     <row r="52" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="82" t="s">
+      <c r="A52" s="76" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -2989,7 +2989,7 @@
       </c>
     </row>
     <row r="53" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="83"/>
+      <c r="A53" s="77"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -3013,7 +3013,7 @@
       </c>
     </row>
     <row r="54" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="83"/>
+      <c r="A54" s="77"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -3033,7 +3033,7 @@
       </c>
     </row>
     <row r="55" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="83"/>
+      <c r="A55" s="77"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -3053,7 +3053,7 @@
       </c>
     </row>
     <row r="56" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="83"/>
+      <c r="A56" s="77"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -3073,7 +3073,7 @@
       </c>
     </row>
     <row r="57" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="84"/>
+      <c r="A57" s="78"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -3127,7 +3127,7 @@
       </c>
     </row>
     <row r="60" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="85" t="s">
+      <c r="A60" s="79" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -3153,7 +3153,7 @@
       </c>
     </row>
     <row r="61" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="86"/>
+      <c r="A61" s="80"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -3177,7 +3177,7 @@
       </c>
     </row>
     <row r="62" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="86"/>
+      <c r="A62" s="80"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -3197,7 +3197,7 @@
       </c>
     </row>
     <row r="63" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="86"/>
+      <c r="A63" s="80"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -3217,7 +3217,7 @@
       </c>
     </row>
     <row r="64" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="86"/>
+      <c r="A64" s="80"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -3237,7 +3237,7 @@
       </c>
     </row>
     <row r="65" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="87"/>
+      <c r="A65" s="81"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -3291,7 +3291,7 @@
       </c>
     </row>
     <row r="68" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="88" t="s">
+      <c r="A68" s="82" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -3317,7 +3317,7 @@
       </c>
     </row>
     <row r="69" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="89"/>
+      <c r="A69" s="83"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -3341,7 +3341,7 @@
       </c>
     </row>
     <row r="70" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="89"/>
+      <c r="A70" s="83"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -3361,7 +3361,7 @@
       </c>
     </row>
     <row r="71" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="89"/>
+      <c r="A71" s="83"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -3381,7 +3381,7 @@
       </c>
     </row>
     <row r="72" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="89"/>
+      <c r="A72" s="83"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -3401,7 +3401,7 @@
       </c>
     </row>
     <row r="73" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="90"/>
+      <c r="A73" s="84"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -3455,7 +3455,7 @@
       </c>
     </row>
     <row r="76" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="91" t="s">
+      <c r="A76" s="85" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -3481,7 +3481,7 @@
       </c>
     </row>
     <row r="77" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="92"/>
+      <c r="A77" s="86"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -3505,7 +3505,7 @@
       </c>
     </row>
     <row r="78" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="92"/>
+      <c r="A78" s="86"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -3525,7 +3525,7 @@
       </c>
     </row>
     <row r="79" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="92"/>
+      <c r="A79" s="86"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -3545,7 +3545,7 @@
       </c>
     </row>
     <row r="80" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="92"/>
+      <c r="A80" s="86"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -3565,7 +3565,7 @@
       </c>
     </row>
     <row r="81" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="93"/>
+      <c r="A81" s="87"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -3619,7 +3619,7 @@
       </c>
     </row>
     <row r="84" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="94" t="s">
+      <c r="A84" s="88" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -3645,7 +3645,7 @@
       </c>
     </row>
     <row r="85" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="95"/>
+      <c r="A85" s="89"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -3658,14 +3658,18 @@
       <c r="E85" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="F85" s="26"/>
-      <c r="G85" s="26"/>
-      <c r="H85" s="21" t="s">
+      <c r="F85" s="26">
+        <v>1</v>
+      </c>
+      <c r="G85" s="26">
+        <v>3</v>
+      </c>
+      <c r="H85" s="27" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="86" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="95"/>
+      <c r="A86" s="89"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -3685,7 +3689,7 @@
       </c>
     </row>
     <row r="87" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="95"/>
+      <c r="A87" s="89"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -3705,7 +3709,7 @@
       </c>
     </row>
     <row r="88" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="95"/>
+      <c r="A88" s="89"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -3725,7 +3729,7 @@
       </c>
     </row>
     <row r="89" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="96"/>
+      <c r="A89" s="90"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -3779,7 +3783,7 @@
       </c>
     </row>
     <row r="92" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="76" t="s">
+      <c r="A92" s="70" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -3805,7 +3809,7 @@
       </c>
     </row>
     <row r="93" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="77"/>
+      <c r="A93" s="71"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -3829,7 +3833,7 @@
       </c>
     </row>
     <row r="94" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="77"/>
+      <c r="A94" s="71"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -3849,7 +3853,7 @@
       </c>
     </row>
     <row r="95" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="77"/>
+      <c r="A95" s="71"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -3869,7 +3873,7 @@
       </c>
     </row>
     <row r="96" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="77"/>
+      <c r="A96" s="71"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -3889,7 +3893,7 @@
       </c>
     </row>
     <row r="97" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="78"/>
+      <c r="A97" s="72"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -3949,26 +3953,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="70" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="72"/>
+      <c r="A1" s="64" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="66"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="73"/>
-      <c r="B2" s="74"/>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="75"/>
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="69"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -4001,7 +4005,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="97" t="s">
+      <c r="A4" s="91" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -4027,11 +4031,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="98"/>
+      <c r="A5" s="92"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -4055,7 +4059,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="98"/>
+      <c r="A6" s="92"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -4083,7 +4087,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="98"/>
+      <c r="A7" s="92"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -4111,7 +4115,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="98"/>
+      <c r="A8" s="92"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -4139,7 +4143,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="99"/>
+      <c r="A9" s="93"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -4201,7 +4205,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="100" t="s">
+      <c r="A12" s="94" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -4227,7 +4231,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="101"/>
+      <c r="A13" s="95"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -4251,7 +4255,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="101"/>
+      <c r="A14" s="95"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -4279,7 +4283,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="101"/>
+      <c r="A15" s="95"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -4307,7 +4311,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="101"/>
+      <c r="A16" s="95"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -4335,7 +4339,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="102"/>
+      <c r="A17" s="96"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -4397,7 +4401,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="103" t="s">
+      <c r="A20" s="97" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -4423,7 +4427,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="104"/>
+      <c r="A21" s="98"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -4451,7 +4455,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="104"/>
+      <c r="A22" s="98"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -4479,7 +4483,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="104"/>
+      <c r="A23" s="98"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -4507,7 +4511,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="104"/>
+      <c r="A24" s="98"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -4535,7 +4539,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="105"/>
+      <c r="A25" s="99"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -4597,7 +4601,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="106" t="s">
+      <c r="A28" s="100" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -4623,7 +4627,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="107"/>
+      <c r="A29" s="101"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -4651,7 +4655,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="107"/>
+      <c r="A30" s="101"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -4679,7 +4683,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="107"/>
+      <c r="A31" s="101"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -4707,7 +4711,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="107"/>
+      <c r="A32" s="101"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -4735,7 +4739,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="108"/>
+      <c r="A33" s="102"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -4797,7 +4801,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="109" t="s">
+      <c r="A36" s="103" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -4827,7 +4831,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="110"/>
+      <c r="A37" s="104"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -4855,7 +4859,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="110"/>
+      <c r="A38" s="104"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -4883,7 +4887,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="110"/>
+      <c r="A39" s="104"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -4911,7 +4915,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="110"/>
+      <c r="A40" s="104"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -4939,7 +4943,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="111"/>
+      <c r="A41" s="105"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -5001,7 +5005,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="79" t="s">
+      <c r="A44" s="73" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -5031,7 +5035,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="80"/>
+      <c r="A45" s="74"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -5059,7 +5063,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="80"/>
+      <c r="A46" s="74"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -5087,7 +5091,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="80"/>
+      <c r="A47" s="74"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -5115,7 +5119,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="80"/>
+      <c r="A48" s="74"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -5143,7 +5147,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="81"/>
+      <c r="A49" s="75"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -5205,7 +5209,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="82" t="s">
+      <c r="A52" s="76" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -5235,7 +5239,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="83"/>
+      <c r="A53" s="77"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -5263,7 +5267,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="83"/>
+      <c r="A54" s="77"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -5291,7 +5295,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="83"/>
+      <c r="A55" s="77"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -5319,7 +5323,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="83"/>
+      <c r="A56" s="77"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -5347,7 +5351,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="84"/>
+      <c r="A57" s="78"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -5409,7 +5413,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="85" t="s">
+      <c r="A60" s="79" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -5439,7 +5443,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="86"/>
+      <c r="A61" s="80"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -5467,7 +5471,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="86"/>
+      <c r="A62" s="80"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -5495,7 +5499,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="86"/>
+      <c r="A63" s="80"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -5523,7 +5527,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="86"/>
+      <c r="A64" s="80"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -5551,7 +5555,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="87"/>
+      <c r="A65" s="81"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -5613,7 +5617,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="88" t="s">
+      <c r="A68" s="82" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -5643,7 +5647,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="89"/>
+      <c r="A69" s="83"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -5671,7 +5675,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="89"/>
+      <c r="A70" s="83"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -5699,7 +5703,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="89"/>
+      <c r="A71" s="83"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -5727,7 +5731,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="89"/>
+      <c r="A72" s="83"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -5755,7 +5759,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="90"/>
+      <c r="A73" s="84"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -5817,7 +5821,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="91" t="s">
+      <c r="A76" s="85" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -5847,7 +5851,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="92"/>
+      <c r="A77" s="86"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -5875,7 +5879,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="92"/>
+      <c r="A78" s="86"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -5903,7 +5907,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="92"/>
+      <c r="A79" s="86"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -5931,7 +5935,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="92"/>
+      <c r="A80" s="86"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -5959,7 +5963,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="93"/>
+      <c r="A81" s="87"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -6021,7 +6025,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="94" t="s">
+      <c r="A84" s="88" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -6051,7 +6055,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="95"/>
+      <c r="A85" s="89"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -6073,13 +6077,13 @@
       <c r="H85" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="J85" s="1" t="str">
+      <c r="J85" s="1">
         <f>IF(OR(Resultados!F85="",Resultados!G85=""),"",IF(AND(F85=Resultados!F85,G85=Resultados!G85),2,IF(((F85&gt;G85)=(Resultados!F85&gt;Resultados!G85))*((F85&lt;G85)=(Resultados!F85&lt;Resultados!G85)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="95"/>
+      <c r="A86" s="89"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -6107,7 +6111,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="95"/>
+      <c r="A87" s="89"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -6135,7 +6139,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="95"/>
+      <c r="A88" s="89"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -6163,7 +6167,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="96"/>
+      <c r="A89" s="90"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -6225,7 +6229,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="76" t="s">
+      <c r="A92" s="70" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -6255,7 +6259,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="77"/>
+      <c r="A93" s="71"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -6283,7 +6287,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="77"/>
+      <c r="A94" s="71"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -6311,7 +6315,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="77"/>
+      <c r="A95" s="71"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -6339,7 +6343,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="77"/>
+      <c r="A96" s="71"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -6367,7 +6371,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="78"/>
+      <c r="A97" s="72"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -6437,26 +6441,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="70" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="72"/>
+      <c r="A1" s="64" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="66"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="73"/>
-      <c r="B2" s="74"/>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="75"/>
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="69"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -6489,7 +6493,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="97" t="s">
+      <c r="A4" s="91" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -6515,11 +6519,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="98"/>
+      <c r="A5" s="92"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -6543,7 +6547,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="98"/>
+      <c r="A6" s="92"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -6571,7 +6575,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="98"/>
+      <c r="A7" s="92"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -6599,7 +6603,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="98"/>
+      <c r="A8" s="92"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -6627,7 +6631,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="99"/>
+      <c r="A9" s="93"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -6689,7 +6693,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="100" t="s">
+      <c r="A12" s="94" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -6715,7 +6719,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="101"/>
+      <c r="A13" s="95"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -6739,7 +6743,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="101"/>
+      <c r="A14" s="95"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -6767,7 +6771,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="101"/>
+      <c r="A15" s="95"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -6795,7 +6799,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="101"/>
+      <c r="A16" s="95"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -6823,7 +6827,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="102"/>
+      <c r="A17" s="96"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -6885,7 +6889,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="103" t="s">
+      <c r="A20" s="97" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -6911,7 +6915,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="104"/>
+      <c r="A21" s="98"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -6939,7 +6943,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="104"/>
+      <c r="A22" s="98"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -6967,7 +6971,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="104"/>
+      <c r="A23" s="98"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -6995,7 +6999,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="104"/>
+      <c r="A24" s="98"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -7023,7 +7027,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="105"/>
+      <c r="A25" s="99"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -7085,7 +7089,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="106" t="s">
+      <c r="A28" s="100" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -7111,7 +7115,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="107"/>
+      <c r="A29" s="101"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -7139,7 +7143,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="107"/>
+      <c r="A30" s="101"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -7167,7 +7171,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="107"/>
+      <c r="A31" s="101"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -7195,7 +7199,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="107"/>
+      <c r="A32" s="101"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -7223,7 +7227,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="108"/>
+      <c r="A33" s="102"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -7285,7 +7289,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="109" t="s">
+      <c r="A36" s="103" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -7315,7 +7319,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="110"/>
+      <c r="A37" s="104"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -7343,7 +7347,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="110"/>
+      <c r="A38" s="104"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -7371,7 +7375,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="110"/>
+      <c r="A39" s="104"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -7399,7 +7403,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="110"/>
+      <c r="A40" s="104"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -7427,7 +7431,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="111"/>
+      <c r="A41" s="105"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -7489,7 +7493,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="79" t="s">
+      <c r="A44" s="73" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -7519,7 +7523,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="80"/>
+      <c r="A45" s="74"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -7547,7 +7551,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="80"/>
+      <c r="A46" s="74"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -7575,7 +7579,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="80"/>
+      <c r="A47" s="74"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -7603,7 +7607,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="80"/>
+      <c r="A48" s="74"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -7631,7 +7635,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="81"/>
+      <c r="A49" s="75"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -7693,7 +7697,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="82" t="s">
+      <c r="A52" s="76" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -7723,7 +7727,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="83"/>
+      <c r="A53" s="77"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -7751,7 +7755,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="83"/>
+      <c r="A54" s="77"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -7779,7 +7783,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="83"/>
+      <c r="A55" s="77"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -7807,7 +7811,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="83"/>
+      <c r="A56" s="77"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -7835,7 +7839,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="84"/>
+      <c r="A57" s="78"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -7897,7 +7901,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="85" t="s">
+      <c r="A60" s="79" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -7927,7 +7931,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="86"/>
+      <c r="A61" s="80"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -7955,7 +7959,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="86"/>
+      <c r="A62" s="80"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -7983,7 +7987,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="86"/>
+      <c r="A63" s="80"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -8011,7 +8015,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="86"/>
+      <c r="A64" s="80"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -8039,7 +8043,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="87"/>
+      <c r="A65" s="81"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -8101,7 +8105,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="88" t="s">
+      <c r="A68" s="82" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -8131,7 +8135,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="89"/>
+      <c r="A69" s="83"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -8159,7 +8163,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="89"/>
+      <c r="A70" s="83"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -8187,7 +8191,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="89"/>
+      <c r="A71" s="83"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -8215,7 +8219,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="89"/>
+      <c r="A72" s="83"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -8243,7 +8247,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="90"/>
+      <c r="A73" s="84"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -8305,7 +8309,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="91" t="s">
+      <c r="A76" s="85" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -8335,7 +8339,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="92"/>
+      <c r="A77" s="86"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -8363,7 +8367,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="92"/>
+      <c r="A78" s="86"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -8391,7 +8395,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="92"/>
+      <c r="A79" s="86"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -8419,7 +8423,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="92"/>
+      <c r="A80" s="86"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -8447,7 +8451,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="93"/>
+      <c r="A81" s="87"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -8509,7 +8513,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="94" t="s">
+      <c r="A84" s="88" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -8539,7 +8543,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="95"/>
+      <c r="A85" s="89"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -8561,13 +8565,13 @@
       <c r="H85" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="J85" s="1" t="str">
+      <c r="J85" s="1">
         <f>IF(OR(Resultados!F85="",Resultados!G85=""),"",IF(AND(F85=Resultados!F85,G85=Resultados!G85),2,IF(((F85&gt;G85)=(Resultados!F85&gt;Resultados!G85))*((F85&lt;G85)=(Resultados!F85&lt;Resultados!G85)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="95"/>
+      <c r="A86" s="89"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -8595,7 +8599,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="95"/>
+      <c r="A87" s="89"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -8623,7 +8627,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="95"/>
+      <c r="A88" s="89"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -8651,7 +8655,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="96"/>
+      <c r="A89" s="90"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -8713,7 +8717,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="76" t="s">
+      <c r="A92" s="70" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -8743,7 +8747,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="77"/>
+      <c r="A93" s="71"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -8771,7 +8775,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="77"/>
+      <c r="A94" s="71"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -8799,7 +8803,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="77"/>
+      <c r="A95" s="71"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -8827,7 +8831,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="77"/>
+      <c r="A96" s="71"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -8855,7 +8859,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="78"/>
+      <c r="A97" s="72"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -8920,18 +8924,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D1" s="64" t="s">
+      <c r="D1" s="106" t="s">
         <v>74</v>
       </c>
-      <c r="E1" s="65"/>
-      <c r="F1" s="66"/>
+      <c r="E1" s="107"/>
+      <c r="F1" s="108"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D2" s="67" t="s">
+      <c r="D2" s="109" t="s">
         <v>75</v>
       </c>
-      <c r="E2" s="68"/>
-      <c r="F2" s="69"/>
+      <c r="E2" s="110"/>
+      <c r="F2" s="111"/>
     </row>
     <row r="4" spans="1:6" s="29" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="57" t="s">
@@ -8956,7 +8960,7 @@
       </c>
       <c r="B5" s="58">
         <f>Cindy!L4</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" s="59">
         <v>1</v>
@@ -8966,7 +8970,7 @@
         <v>Packy</v>
       </c>
       <c r="F5" s="59">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -8975,7 +8979,7 @@
       </c>
       <c r="B6" s="58">
         <f>Wendy!L4</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6" s="55">
         <v>2</v>
@@ -8984,7 +8988,7 @@
         <v>Bere</v>
       </c>
       <c r="F6" s="55">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -8993,16 +8997,16 @@
       </c>
       <c r="B7" s="58">
         <f>Jimmy!L4</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D7" s="56">
         <v>3</v>
       </c>
       <c r="E7" s="56" t="str">
-        <v>Wendy</v>
+        <v>Jimmy</v>
       </c>
       <c r="F7" s="56">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -9011,16 +9015,16 @@
       </c>
       <c r="B8" s="58">
         <f>Erick!L4</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" s="28">
         <v>4</v>
       </c>
       <c r="E8" s="28" t="str">
-        <v>Jimmy</v>
+        <v>Erik</v>
       </c>
       <c r="F8" s="28">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -9029,16 +9033,16 @@
       </c>
       <c r="B9" s="58">
         <f>Erik!L4</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D9" s="28">
         <v>5</v>
       </c>
       <c r="E9" s="28" t="str">
-        <v>Erik</v>
+        <v>Wendy</v>
       </c>
       <c r="F9" s="28">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -9047,7 +9051,7 @@
       </c>
       <c r="B10" s="58">
         <f>Lennon!L4</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D10" s="28">
         <v>6</v>
@@ -9056,7 +9060,7 @@
         <v>Lennon</v>
       </c>
       <c r="F10" s="28">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -9065,7 +9069,7 @@
       </c>
       <c r="B11" s="58">
         <f>Yulian!L4</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D11" s="28">
         <v>7</v>
@@ -9074,7 +9078,7 @@
         <v>Yulian</v>
       </c>
       <c r="F11" s="28">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -9083,7 +9087,7 @@
       </c>
       <c r="B12" s="58">
         <f>Packy!L4</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D12" s="28">
         <v>8</v>
@@ -9092,7 +9096,7 @@
         <v>Cindy</v>
       </c>
       <c r="F12" s="28">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -9101,7 +9105,7 @@
       </c>
       <c r="B13" s="58">
         <f>Bere!L4</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D13" s="28">
         <v>9</v>
@@ -9110,7 +9114,7 @@
         <v>Erick</v>
       </c>
       <c r="F13" s="28">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -9144,26 +9148,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="70" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="72"/>
+      <c r="A1" s="64" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="66"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="73"/>
-      <c r="B2" s="74"/>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="75"/>
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="69"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="31"/>
@@ -9222,7 +9226,7 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -11268,9 +11272,9 @@
       <c r="H85" s="46" t="s">
         <v>64</v>
       </c>
-      <c r="J85" s="1" t="str">
+      <c r="J85" s="1">
         <f>IF(OR(Resultados!F85="",Resultados!G85=""),"",IF(AND(F85=Resultados!F85,G85=Resultados!G85),2,IF(((F85&gt;G85)=(Resultados!F85&gt;Resultados!G85))*((F85&lt;G85)=(Resultados!F85&lt;Resultados!G85)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -11633,26 +11637,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="70" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="72"/>
+      <c r="A1" s="64" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="66"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="73"/>
-      <c r="B2" s="74"/>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="75"/>
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="69"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="31"/>
@@ -11711,7 +11715,7 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -13757,9 +13761,9 @@
       <c r="H85" s="46" t="s">
         <v>64</v>
       </c>
-      <c r="J85" s="1" t="str">
+      <c r="J85" s="1">
         <f>IF(OR(Resultados!F85="",Resultados!G85=""),"",IF(AND(F85=Resultados!F85,G85=Resultados!G85),2,IF(((F85&gt;G85)=(Resultados!F85&gt;Resultados!G85))*((F85&lt;G85)=(Resultados!F85&lt;Resultados!G85)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -14121,26 +14125,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="70" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="72"/>
+      <c r="A1" s="64" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="66"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="73"/>
-      <c r="B2" s="74"/>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="75"/>
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="69"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -14173,7 +14177,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="97" t="s">
+      <c r="A4" s="91" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -14199,11 +14203,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="98"/>
+      <c r="A5" s="92"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -14227,7 +14231,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="98"/>
+      <c r="A6" s="92"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -14255,7 +14259,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="98"/>
+      <c r="A7" s="92"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -14283,7 +14287,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="98"/>
+      <c r="A8" s="92"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -14311,7 +14315,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="99"/>
+      <c r="A9" s="93"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -14373,7 +14377,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="100" t="s">
+      <c r="A12" s="94" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -14399,7 +14403,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="101"/>
+      <c r="A13" s="95"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -14423,7 +14427,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="101"/>
+      <c r="A14" s="95"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -14451,7 +14455,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="101"/>
+      <c r="A15" s="95"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -14479,7 +14483,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="101"/>
+      <c r="A16" s="95"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -14507,7 +14511,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="102"/>
+      <c r="A17" s="96"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -14569,7 +14573,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="103" t="s">
+      <c r="A20" s="97" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -14595,7 +14599,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="104"/>
+      <c r="A21" s="98"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -14623,7 +14627,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="104"/>
+      <c r="A22" s="98"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -14651,7 +14655,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="104"/>
+      <c r="A23" s="98"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -14679,7 +14683,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="104"/>
+      <c r="A24" s="98"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -14707,7 +14711,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="105"/>
+      <c r="A25" s="99"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -14769,7 +14773,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="106" t="s">
+      <c r="A28" s="100" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -14795,7 +14799,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="107"/>
+      <c r="A29" s="101"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -14823,7 +14827,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="107"/>
+      <c r="A30" s="101"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -14851,7 +14855,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="107"/>
+      <c r="A31" s="101"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -14879,7 +14883,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="107"/>
+      <c r="A32" s="101"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -14907,7 +14911,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="108"/>
+      <c r="A33" s="102"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -14969,7 +14973,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="109" t="s">
+      <c r="A36" s="103" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -14999,7 +15003,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="110"/>
+      <c r="A37" s="104"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -15027,7 +15031,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="110"/>
+      <c r="A38" s="104"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -15055,7 +15059,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="110"/>
+      <c r="A39" s="104"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -15083,7 +15087,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="110"/>
+      <c r="A40" s="104"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -15111,7 +15115,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="111"/>
+      <c r="A41" s="105"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -15173,7 +15177,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="79" t="s">
+      <c r="A44" s="73" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -15203,7 +15207,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="80"/>
+      <c r="A45" s="74"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -15231,7 +15235,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="80"/>
+      <c r="A46" s="74"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -15259,7 +15263,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="80"/>
+      <c r="A47" s="74"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -15287,7 +15291,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="80"/>
+      <c r="A48" s="74"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -15315,7 +15319,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="81"/>
+      <c r="A49" s="75"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -15377,7 +15381,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="82" t="s">
+      <c r="A52" s="76" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -15407,7 +15411,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="83"/>
+      <c r="A53" s="77"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -15435,7 +15439,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="83"/>
+      <c r="A54" s="77"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -15463,7 +15467,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="83"/>
+      <c r="A55" s="77"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -15491,7 +15495,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="83"/>
+      <c r="A56" s="77"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -15519,7 +15523,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="84"/>
+      <c r="A57" s="78"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -15581,7 +15585,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="85" t="s">
+      <c r="A60" s="79" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -15611,7 +15615,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="86"/>
+      <c r="A61" s="80"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -15639,7 +15643,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="86"/>
+      <c r="A62" s="80"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -15667,7 +15671,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="86"/>
+      <c r="A63" s="80"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -15695,7 +15699,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="86"/>
+      <c r="A64" s="80"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -15723,7 +15727,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="87"/>
+      <c r="A65" s="81"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -15785,7 +15789,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="88" t="s">
+      <c r="A68" s="82" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -15815,7 +15819,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="89"/>
+      <c r="A69" s="83"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -15843,7 +15847,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="89"/>
+      <c r="A70" s="83"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -15871,7 +15875,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="89"/>
+      <c r="A71" s="83"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -15899,7 +15903,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="89"/>
+      <c r="A72" s="83"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -15927,7 +15931,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="90"/>
+      <c r="A73" s="84"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -15989,7 +15993,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="91" t="s">
+      <c r="A76" s="85" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -16019,7 +16023,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="92"/>
+      <c r="A77" s="86"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -16047,7 +16051,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="92"/>
+      <c r="A78" s="86"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -16075,7 +16079,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="92"/>
+      <c r="A79" s="86"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -16103,7 +16107,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="92"/>
+      <c r="A80" s="86"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -16131,7 +16135,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="93"/>
+      <c r="A81" s="87"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -16193,7 +16197,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="94" t="s">
+      <c r="A84" s="88" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -16223,7 +16227,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="95"/>
+      <c r="A85" s="89"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -16245,13 +16249,13 @@
       <c r="H85" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="J85" s="1" t="str">
+      <c r="J85" s="1">
         <f>IF(OR(Resultados!F85="",Resultados!G85=""),"",IF(AND(F85=Resultados!F85,G85=Resultados!G85),2,IF(((F85&gt;G85)=(Resultados!F85&gt;Resultados!G85))*((F85&lt;G85)=(Resultados!F85&lt;Resultados!G85)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="95"/>
+      <c r="A86" s="89"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -16279,7 +16283,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="95"/>
+      <c r="A87" s="89"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -16307,7 +16311,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="95"/>
+      <c r="A88" s="89"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -16335,7 +16339,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="96"/>
+      <c r="A89" s="90"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -16397,7 +16401,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="76" t="s">
+      <c r="A92" s="70" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -16427,7 +16431,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="77"/>
+      <c r="A93" s="71"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -16455,7 +16459,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="77"/>
+      <c r="A94" s="71"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -16483,7 +16487,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="77"/>
+      <c r="A95" s="71"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -16511,7 +16515,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="77"/>
+      <c r="A96" s="71"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -16539,7 +16543,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="78"/>
+      <c r="A97" s="72"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -16609,26 +16613,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="70" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="72"/>
+      <c r="A1" s="64" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="66"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="73"/>
-      <c r="B2" s="74"/>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="75"/>
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="69"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -16661,7 +16665,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="97" t="s">
+      <c r="A4" s="91" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -16687,11 +16691,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="98"/>
+      <c r="A5" s="92"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -16715,7 +16719,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="98"/>
+      <c r="A6" s="92"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -16743,7 +16747,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="98"/>
+      <c r="A7" s="92"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -16771,7 +16775,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="98"/>
+      <c r="A8" s="92"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -16799,7 +16803,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="99"/>
+      <c r="A9" s="93"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -16861,7 +16865,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="100" t="s">
+      <c r="A12" s="94" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -16887,7 +16891,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="101"/>
+      <c r="A13" s="95"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -16911,7 +16915,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="101"/>
+      <c r="A14" s="95"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -16939,7 +16943,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="101"/>
+      <c r="A15" s="95"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -16967,7 +16971,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="101"/>
+      <c r="A16" s="95"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -16995,7 +16999,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="102"/>
+      <c r="A17" s="96"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -17057,7 +17061,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="103" t="s">
+      <c r="A20" s="97" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -17083,7 +17087,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="104"/>
+      <c r="A21" s="98"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -17111,7 +17115,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="104"/>
+      <c r="A22" s="98"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -17139,7 +17143,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="104"/>
+      <c r="A23" s="98"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -17167,7 +17171,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="104"/>
+      <c r="A24" s="98"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -17195,7 +17199,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="105"/>
+      <c r="A25" s="99"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -17257,7 +17261,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="106" t="s">
+      <c r="A28" s="100" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -17283,7 +17287,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="107"/>
+      <c r="A29" s="101"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -17311,7 +17315,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="107"/>
+      <c r="A30" s="101"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -17339,7 +17343,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="107"/>
+      <c r="A31" s="101"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -17367,7 +17371,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="107"/>
+      <c r="A32" s="101"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -17395,7 +17399,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="108"/>
+      <c r="A33" s="102"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -17457,7 +17461,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="109" t="s">
+      <c r="A36" s="103" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -17487,7 +17491,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="110"/>
+      <c r="A37" s="104"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -17515,7 +17519,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="110"/>
+      <c r="A38" s="104"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -17543,7 +17547,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="110"/>
+      <c r="A39" s="104"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -17571,7 +17575,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="110"/>
+      <c r="A40" s="104"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -17599,7 +17603,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="111"/>
+      <c r="A41" s="105"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -17661,7 +17665,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="79" t="s">
+      <c r="A44" s="73" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -17691,7 +17695,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="80"/>
+      <c r="A45" s="74"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -17719,7 +17723,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="80"/>
+      <c r="A46" s="74"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -17747,7 +17751,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="80"/>
+      <c r="A47" s="74"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -17775,7 +17779,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="80"/>
+      <c r="A48" s="74"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -17803,7 +17807,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="81"/>
+      <c r="A49" s="75"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -17865,7 +17869,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="82" t="s">
+      <c r="A52" s="76" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -17895,7 +17899,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="83"/>
+      <c r="A53" s="77"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -17923,7 +17927,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="83"/>
+      <c r="A54" s="77"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -17951,7 +17955,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="83"/>
+      <c r="A55" s="77"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -17979,7 +17983,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="83"/>
+      <c r="A56" s="77"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -18007,7 +18011,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="84"/>
+      <c r="A57" s="78"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -18069,7 +18073,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="85" t="s">
+      <c r="A60" s="79" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -18099,7 +18103,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="86"/>
+      <c r="A61" s="80"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -18127,7 +18131,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="86"/>
+      <c r="A62" s="80"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -18155,7 +18159,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="86"/>
+      <c r="A63" s="80"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -18183,7 +18187,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="86"/>
+      <c r="A64" s="80"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -18211,7 +18215,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="87"/>
+      <c r="A65" s="81"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -18273,7 +18277,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="88" t="s">
+      <c r="A68" s="82" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -18303,7 +18307,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="89"/>
+      <c r="A69" s="83"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -18331,7 +18335,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="89"/>
+      <c r="A70" s="83"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -18359,7 +18363,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="89"/>
+      <c r="A71" s="83"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -18387,7 +18391,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="89"/>
+      <c r="A72" s="83"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -18415,7 +18419,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="90"/>
+      <c r="A73" s="84"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -18477,7 +18481,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="91" t="s">
+      <c r="A76" s="85" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -18507,7 +18511,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="92"/>
+      <c r="A77" s="86"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -18535,7 +18539,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="92"/>
+      <c r="A78" s="86"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -18563,7 +18567,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="92"/>
+      <c r="A79" s="86"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -18591,7 +18595,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="92"/>
+      <c r="A80" s="86"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -18619,7 +18623,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="93"/>
+      <c r="A81" s="87"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -18681,7 +18685,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="94" t="s">
+      <c r="A84" s="88" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -18711,7 +18715,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="95"/>
+      <c r="A85" s="89"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -18733,13 +18737,13 @@
       <c r="H85" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="J85" s="1" t="str">
+      <c r="J85" s="1">
         <f>IF(OR(Resultados!F85="",Resultados!G85=""),"",IF(AND(F85=Resultados!F85,G85=Resultados!G85),2,IF(((F85&gt;G85)=(Resultados!F85&gt;Resultados!G85))*((F85&lt;G85)=(Resultados!F85&lt;Resultados!G85)),1,0)))</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="95"/>
+      <c r="A86" s="89"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -18767,7 +18771,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="95"/>
+      <c r="A87" s="89"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -18795,7 +18799,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="95"/>
+      <c r="A88" s="89"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -18823,7 +18827,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="96"/>
+      <c r="A89" s="90"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -18885,7 +18889,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="76" t="s">
+      <c r="A92" s="70" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -18915,7 +18919,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="77"/>
+      <c r="A93" s="71"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -18943,7 +18947,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="77"/>
+      <c r="A94" s="71"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -18971,7 +18975,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="77"/>
+      <c r="A95" s="71"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -18999,7 +19003,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="77"/>
+      <c r="A96" s="71"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -19027,7 +19031,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="78"/>
+      <c r="A97" s="72"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -19097,26 +19101,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="70" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="72"/>
+      <c r="A1" s="64" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="66"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="73"/>
-      <c r="B2" s="74"/>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="75"/>
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="69"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -19149,7 +19153,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="97" t="s">
+      <c r="A4" s="91" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -19175,11 +19179,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="98"/>
+      <c r="A5" s="92"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -19203,7 +19207,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="98"/>
+      <c r="A6" s="92"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -19231,7 +19235,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="98"/>
+      <c r="A7" s="92"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -19259,7 +19263,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="98"/>
+      <c r="A8" s="92"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -19287,7 +19291,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="99"/>
+      <c r="A9" s="93"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -19349,7 +19353,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="100" t="s">
+      <c r="A12" s="94" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -19375,7 +19379,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="101"/>
+      <c r="A13" s="95"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -19399,7 +19403,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="101"/>
+      <c r="A14" s="95"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -19427,7 +19431,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="101"/>
+      <c r="A15" s="95"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -19455,7 +19459,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="101"/>
+      <c r="A16" s="95"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -19483,7 +19487,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="102"/>
+      <c r="A17" s="96"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -19545,7 +19549,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="103" t="s">
+      <c r="A20" s="97" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -19571,7 +19575,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="104"/>
+      <c r="A21" s="98"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -19599,7 +19603,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="104"/>
+      <c r="A22" s="98"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -19627,7 +19631,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="104"/>
+      <c r="A23" s="98"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -19655,7 +19659,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="104"/>
+      <c r="A24" s="98"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -19683,7 +19687,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="105"/>
+      <c r="A25" s="99"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -19745,7 +19749,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="106" t="s">
+      <c r="A28" s="100" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -19771,7 +19775,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="107"/>
+      <c r="A29" s="101"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -19799,7 +19803,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="107"/>
+      <c r="A30" s="101"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -19827,7 +19831,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="107"/>
+      <c r="A31" s="101"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -19855,7 +19859,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="107"/>
+      <c r="A32" s="101"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -19879,7 +19883,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="108"/>
+      <c r="A33" s="102"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -19937,7 +19941,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="109" t="s">
+      <c r="A36" s="103" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -19967,7 +19971,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="110"/>
+      <c r="A37" s="104"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -19995,7 +19999,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="110"/>
+      <c r="A38" s="104"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -20019,7 +20023,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="110"/>
+      <c r="A39" s="104"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -20043,7 +20047,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="110"/>
+      <c r="A40" s="104"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -20067,7 +20071,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="111"/>
+      <c r="A41" s="105"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -20125,7 +20129,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="79" t="s">
+      <c r="A44" s="73" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -20155,7 +20159,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="80"/>
+      <c r="A45" s="74"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -20183,7 +20187,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="80"/>
+      <c r="A46" s="74"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -20207,7 +20211,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="80"/>
+      <c r="A47" s="74"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -20231,7 +20235,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="80"/>
+      <c r="A48" s="74"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -20255,7 +20259,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="81"/>
+      <c r="A49" s="75"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -20313,7 +20317,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="82" t="s">
+      <c r="A52" s="76" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -20343,7 +20347,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="83"/>
+      <c r="A53" s="77"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -20371,7 +20375,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="83"/>
+      <c r="A54" s="77"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -20395,7 +20399,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="83"/>
+      <c r="A55" s="77"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -20419,7 +20423,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="83"/>
+      <c r="A56" s="77"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -20443,7 +20447,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="84"/>
+      <c r="A57" s="78"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -20501,7 +20505,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="85" t="s">
+      <c r="A60" s="79" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -20531,7 +20535,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="86"/>
+      <c r="A61" s="80"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -20559,7 +20563,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="86"/>
+      <c r="A62" s="80"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -20583,7 +20587,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="86"/>
+      <c r="A63" s="80"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -20607,7 +20611,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="86"/>
+      <c r="A64" s="80"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -20631,7 +20635,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="87"/>
+      <c r="A65" s="81"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -20689,7 +20693,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="88" t="s">
+      <c r="A68" s="82" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -20719,7 +20723,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="89"/>
+      <c r="A69" s="83"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -20747,7 +20751,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="89"/>
+      <c r="A70" s="83"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -20771,7 +20775,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="89"/>
+      <c r="A71" s="83"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -20795,7 +20799,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="89"/>
+      <c r="A72" s="83"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -20819,7 +20823,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="90"/>
+      <c r="A73" s="84"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -20877,7 +20881,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="91" t="s">
+      <c r="A76" s="85" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -20907,7 +20911,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="92"/>
+      <c r="A77" s="86"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -20935,7 +20939,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="92"/>
+      <c r="A78" s="86"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -20959,7 +20963,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="92"/>
+      <c r="A79" s="86"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -20983,7 +20987,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="92"/>
+      <c r="A80" s="86"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -21007,7 +21011,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="93"/>
+      <c r="A81" s="87"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -21065,7 +21069,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="94" t="s">
+      <c r="A84" s="88" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -21095,7 +21099,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="95"/>
+      <c r="A85" s="89"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -21117,13 +21121,13 @@
       <c r="H85" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="J85" s="1" t="str">
+      <c r="J85" s="1">
         <f>IF(OR(Resultados!F85="",Resultados!G85=""),"",IF(AND(F85=Resultados!F85,G85=Resultados!G85),2,IF(((F85&gt;G85)=(Resultados!F85&gt;Resultados!G85))*((F85&lt;G85)=(Resultados!F85&lt;Resultados!G85)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="95"/>
+      <c r="A86" s="89"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -21147,7 +21151,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="95"/>
+      <c r="A87" s="89"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -21171,7 +21175,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="95"/>
+      <c r="A88" s="89"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -21195,7 +21199,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="96"/>
+      <c r="A89" s="90"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -21253,7 +21257,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="76" t="s">
+      <c r="A92" s="70" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -21283,7 +21287,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="77"/>
+      <c r="A93" s="71"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -21311,7 +21315,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="77"/>
+      <c r="A94" s="71"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -21335,7 +21339,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="77"/>
+      <c r="A95" s="71"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -21359,7 +21363,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="77"/>
+      <c r="A96" s="71"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -21383,7 +21387,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="78"/>
+      <c r="A97" s="72"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -21449,26 +21453,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="70" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="72"/>
+      <c r="A1" s="64" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="66"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="73"/>
-      <c r="B2" s="74"/>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="75"/>
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="69"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -21501,7 +21505,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="97" t="s">
+      <c r="A4" s="91" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -21527,11 +21531,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="98"/>
+      <c r="A5" s="92"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -21555,7 +21559,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="98"/>
+      <c r="A6" s="92"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -21583,7 +21587,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="98"/>
+      <c r="A7" s="92"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -21611,7 +21615,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="98"/>
+      <c r="A8" s="92"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -21639,7 +21643,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="99"/>
+      <c r="A9" s="93"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -21701,7 +21705,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="100" t="s">
+      <c r="A12" s="94" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -21727,7 +21731,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="101"/>
+      <c r="A13" s="95"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -21751,7 +21755,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="101"/>
+      <c r="A14" s="95"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -21779,7 +21783,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="101"/>
+      <c r="A15" s="95"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -21807,7 +21811,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="101"/>
+      <c r="A16" s="95"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -21835,7 +21839,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="102"/>
+      <c r="A17" s="96"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -21897,7 +21901,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="103" t="s">
+      <c r="A20" s="97" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -21923,7 +21927,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="104"/>
+      <c r="A21" s="98"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -21951,7 +21955,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="104"/>
+      <c r="A22" s="98"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -21979,7 +21983,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="104"/>
+      <c r="A23" s="98"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -22007,7 +22011,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="104"/>
+      <c r="A24" s="98"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -22035,7 +22039,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="105"/>
+      <c r="A25" s="99"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -22097,7 +22101,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="106" t="s">
+      <c r="A28" s="100" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -22123,7 +22127,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="107"/>
+      <c r="A29" s="101"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -22151,7 +22155,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="107"/>
+      <c r="A30" s="101"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -22179,7 +22183,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="107"/>
+      <c r="A31" s="101"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -22207,7 +22211,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="107"/>
+      <c r="A32" s="101"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -22235,7 +22239,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="108"/>
+      <c r="A33" s="102"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -22297,7 +22301,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="109" t="s">
+      <c r="A36" s="103" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -22327,7 +22331,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="110"/>
+      <c r="A37" s="104"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -22355,7 +22359,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="110"/>
+      <c r="A38" s="104"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -22383,7 +22387,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="110"/>
+      <c r="A39" s="104"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -22411,7 +22415,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="110"/>
+      <c r="A40" s="104"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -22439,7 +22443,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="111"/>
+      <c r="A41" s="105"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -22501,7 +22505,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="79" t="s">
+      <c r="A44" s="73" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -22531,7 +22535,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="80"/>
+      <c r="A45" s="74"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -22559,7 +22563,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="80"/>
+      <c r="A46" s="74"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -22587,7 +22591,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="80"/>
+      <c r="A47" s="74"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -22615,7 +22619,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="80"/>
+      <c r="A48" s="74"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -22643,7 +22647,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="81"/>
+      <c r="A49" s="75"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -22705,7 +22709,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="82" t="s">
+      <c r="A52" s="76" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -22735,7 +22739,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="83"/>
+      <c r="A53" s="77"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -22763,7 +22767,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="83"/>
+      <c r="A54" s="77"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -22791,7 +22795,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="83"/>
+      <c r="A55" s="77"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -22819,7 +22823,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="83"/>
+      <c r="A56" s="77"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -22847,7 +22851,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="84"/>
+      <c r="A57" s="78"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -22909,7 +22913,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="85" t="s">
+      <c r="A60" s="79" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -22939,7 +22943,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="86"/>
+      <c r="A61" s="80"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -22967,7 +22971,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="86"/>
+      <c r="A62" s="80"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -22995,7 +22999,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="86"/>
+      <c r="A63" s="80"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -23023,7 +23027,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="86"/>
+      <c r="A64" s="80"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -23051,7 +23055,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="87"/>
+      <c r="A65" s="81"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -23113,7 +23117,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="88" t="s">
+      <c r="A68" s="82" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -23143,7 +23147,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="89"/>
+      <c r="A69" s="83"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -23171,7 +23175,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="89"/>
+      <c r="A70" s="83"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -23199,7 +23203,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="89"/>
+      <c r="A71" s="83"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -23227,7 +23231,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="89"/>
+      <c r="A72" s="83"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -23255,7 +23259,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="90"/>
+      <c r="A73" s="84"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -23317,7 +23321,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="91" t="s">
+      <c r="A76" s="85" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -23347,7 +23351,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="92"/>
+      <c r="A77" s="86"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -23375,7 +23379,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="92"/>
+      <c r="A78" s="86"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -23403,7 +23407,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="92"/>
+      <c r="A79" s="86"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -23431,7 +23435,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="92"/>
+      <c r="A80" s="86"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -23459,7 +23463,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="93"/>
+      <c r="A81" s="87"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -23521,7 +23525,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="94" t="s">
+      <c r="A84" s="88" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -23551,7 +23555,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="95"/>
+      <c r="A85" s="89"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -23573,13 +23577,13 @@
       <c r="H85" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="J85" s="1" t="str">
+      <c r="J85" s="1">
         <f>IF(OR(Resultados!F85="",Resultados!G85=""),"",IF(AND(F85=Resultados!F85,G85=Resultados!G85),2,IF(((F85&gt;G85)=(Resultados!F85&gt;Resultados!G85))*((F85&lt;G85)=(Resultados!F85&lt;Resultados!G85)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="95"/>
+      <c r="A86" s="89"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -23607,7 +23611,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="95"/>
+      <c r="A87" s="89"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -23635,7 +23639,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="95"/>
+      <c r="A88" s="89"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -23663,7 +23667,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="96"/>
+      <c r="A89" s="90"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -23725,7 +23729,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="76" t="s">
+      <c r="A92" s="70" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -23755,7 +23759,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="77"/>
+      <c r="A93" s="71"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -23783,7 +23787,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="77"/>
+      <c r="A94" s="71"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -23811,7 +23815,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="77"/>
+      <c r="A95" s="71"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -23839,7 +23843,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="77"/>
+      <c r="A96" s="71"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -23867,7 +23871,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="78"/>
+      <c r="A97" s="72"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -23937,26 +23941,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="70" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="72"/>
+      <c r="A1" s="64" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="66"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="73"/>
-      <c r="B2" s="74"/>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="75"/>
+      <c r="A2" s="67"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="69"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -23989,7 +23993,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="97" t="s">
+      <c r="A4" s="91" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -24015,11 +24019,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="98"/>
+      <c r="A5" s="92"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -24043,7 +24047,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="98"/>
+      <c r="A6" s="92"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -24071,7 +24075,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="98"/>
+      <c r="A7" s="92"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -24099,7 +24103,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="98"/>
+      <c r="A8" s="92"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -24127,7 +24131,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="99"/>
+      <c r="A9" s="93"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -24189,7 +24193,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="100" t="s">
+      <c r="A12" s="94" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -24215,7 +24219,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="101"/>
+      <c r="A13" s="95"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -24239,7 +24243,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="101"/>
+      <c r="A14" s="95"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -24267,7 +24271,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="101"/>
+      <c r="A15" s="95"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -24295,7 +24299,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="101"/>
+      <c r="A16" s="95"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -24323,7 +24327,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="102"/>
+      <c r="A17" s="96"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -24385,7 +24389,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="103" t="s">
+      <c r="A20" s="97" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -24411,7 +24415,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="104"/>
+      <c r="A21" s="98"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -24439,7 +24443,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="104"/>
+      <c r="A22" s="98"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -24467,7 +24471,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="104"/>
+      <c r="A23" s="98"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -24495,7 +24499,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="104"/>
+      <c r="A24" s="98"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -24523,7 +24527,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="105"/>
+      <c r="A25" s="99"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -24585,7 +24589,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="106" t="s">
+      <c r="A28" s="100" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -24611,7 +24615,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="107"/>
+      <c r="A29" s="101"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -24639,7 +24643,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="107"/>
+      <c r="A30" s="101"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -24667,7 +24671,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="107"/>
+      <c r="A31" s="101"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -24695,7 +24699,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="107"/>
+      <c r="A32" s="101"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -24723,7 +24727,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="108"/>
+      <c r="A33" s="102"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -24785,7 +24789,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="109" t="s">
+      <c r="A36" s="103" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -24815,7 +24819,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="110"/>
+      <c r="A37" s="104"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -24843,7 +24847,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="110"/>
+      <c r="A38" s="104"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -24871,7 +24875,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="110"/>
+      <c r="A39" s="104"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -24899,7 +24903,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="110"/>
+      <c r="A40" s="104"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -24927,7 +24931,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="111"/>
+      <c r="A41" s="105"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -24989,7 +24993,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="79" t="s">
+      <c r="A44" s="73" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -25019,7 +25023,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="80"/>
+      <c r="A45" s="74"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -25047,7 +25051,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="80"/>
+      <c r="A46" s="74"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -25075,7 +25079,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="80"/>
+      <c r="A47" s="74"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -25103,7 +25107,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="80"/>
+      <c r="A48" s="74"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -25131,7 +25135,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="81"/>
+      <c r="A49" s="75"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -25193,7 +25197,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="82" t="s">
+      <c r="A52" s="76" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -25223,7 +25227,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="83"/>
+      <c r="A53" s="77"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -25251,7 +25255,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="83"/>
+      <c r="A54" s="77"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -25279,7 +25283,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="83"/>
+      <c r="A55" s="77"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -25307,7 +25311,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="83"/>
+      <c r="A56" s="77"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -25335,7 +25339,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="84"/>
+      <c r="A57" s="78"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -25397,7 +25401,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="85" t="s">
+      <c r="A60" s="79" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -25427,7 +25431,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="86"/>
+      <c r="A61" s="80"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -25455,7 +25459,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="86"/>
+      <c r="A62" s="80"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -25483,7 +25487,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="86"/>
+      <c r="A63" s="80"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -25511,7 +25515,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="86"/>
+      <c r="A64" s="80"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -25539,7 +25543,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="87"/>
+      <c r="A65" s="81"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -25601,7 +25605,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="88" t="s">
+      <c r="A68" s="82" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -25631,7 +25635,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="89"/>
+      <c r="A69" s="83"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -25659,7 +25663,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="89"/>
+      <c r="A70" s="83"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -25687,7 +25691,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="89"/>
+      <c r="A71" s="83"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -25715,7 +25719,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="89"/>
+      <c r="A72" s="83"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -25743,7 +25747,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="90"/>
+      <c r="A73" s="84"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -25805,7 +25809,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="91" t="s">
+      <c r="A76" s="85" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -25835,7 +25839,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="92"/>
+      <c r="A77" s="86"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -25863,7 +25867,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="92"/>
+      <c r="A78" s="86"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -25891,7 +25895,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="92"/>
+      <c r="A79" s="86"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -25919,7 +25923,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="92"/>
+      <c r="A80" s="86"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -25947,7 +25951,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="93"/>
+      <c r="A81" s="87"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -26009,7 +26013,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="94" t="s">
+      <c r="A84" s="88" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -26039,7 +26043,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="95"/>
+      <c r="A85" s="89"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -26061,13 +26065,13 @@
       <c r="H85" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="J85" s="1" t="str">
+      <c r="J85" s="1">
         <f>IF(OR(Resultados!F85="",Resultados!G85=""),"",IF(AND(F85=Resultados!F85,G85=Resultados!G85),2,IF(((F85&gt;G85)=(Resultados!F85&gt;Resultados!G85))*((F85&lt;G85)=(Resultados!F85&lt;Resultados!G85)),1,0)))</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="95"/>
+      <c r="A86" s="89"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -26095,7 +26099,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="95"/>
+      <c r="A87" s="89"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -26123,7 +26127,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="95"/>
+      <c r="A88" s="89"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -26151,7 +26155,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="96"/>
+      <c r="A89" s="90"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -26213,7 +26217,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="76" t="s">
+      <c r="A92" s="70" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -26243,7 +26247,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="77"/>
+      <c r="A93" s="71"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -26271,7 +26275,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="77"/>
+      <c r="A94" s="71"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -26299,7 +26303,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="77"/>
+      <c r="A95" s="71"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -26327,7 +26331,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="77"/>
+      <c r="A96" s="71"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -26355,7 +26359,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="78"/>
+      <c r="A97" s="72"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>

--- a/data/Quiniela.xlsx
+++ b/data/Quiniela.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cindy\Desktop\QuinielaMundial\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BD9B628-7B3D-4101-B0CA-55C77DA724B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94C55DEB-12F1-4435-B2D5-079D08705703}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9503E40F-C0E1-49CE-B4EA-3C401754995E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{9503E40F-C0E1-49CE-B4EA-3C401754995E}"/>
   </bookViews>
   <sheets>
     <sheet name="Resultados" sheetId="1" r:id="rId1"/>
@@ -475,7 +475,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="25">
+  <fills count="26">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -617,6 +617,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1007,7 +1013,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="148">
+  <cellXfs count="151">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1248,6 +1254,26 @@
     <xf numFmtId="0" fontId="5" fillId="24" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1272,6 +1298,54 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1281,6 +1355,18 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="17" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1344,78 +1430,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="49" fontId="20" fillId="20" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1433,6 +1447,54 @@
     </xf>
     <xf numFmtId="49" fontId="20" fillId="20" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1530,51 +1592,7 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1933,26 +1951,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="64" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="66"/>
+      <c r="A1" s="69" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="71"/>
     </row>
     <row r="2" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="67"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="69"/>
+      <c r="A2" s="72"/>
+      <c r="B2" s="73"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="74"/>
     </row>
     <row r="3" spans="1:8" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -1979,7 +1997,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="91" t="s">
+      <c r="A4" s="75" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -2005,7 +2023,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="92"/>
+      <c r="A5" s="76"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -2029,7 +2047,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="92"/>
+      <c r="A6" s="76"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -2039,17 +2057,21 @@
       <c r="D6" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="20" t="s">
+      <c r="F6" s="150">
+        <v>1</v>
+      </c>
+      <c r="G6" s="150">
+        <v>1</v>
+      </c>
+      <c r="H6" s="61" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="92"/>
+      <c r="A7" s="76"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -2059,17 +2081,21 @@
       <c r="D7" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="25"/>
-      <c r="G7" s="25"/>
+      <c r="F7" s="150">
+        <v>1</v>
+      </c>
+      <c r="G7" s="150">
+        <v>0</v>
+      </c>
       <c r="H7" s="20" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="92"/>
+      <c r="A8" s="76"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -2089,7 +2115,7 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="93"/>
+      <c r="A9" s="77"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -2143,7 +2169,7 @@
       </c>
     </row>
     <row r="12" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="94" t="s">
+      <c r="A12" s="78" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -2169,7 +2195,7 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="95"/>
+      <c r="A13" s="79"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -2193,7 +2219,7 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="95"/>
+      <c r="A14" s="79"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -2203,17 +2229,21 @@
       <c r="D14" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="F14" s="25"/>
-      <c r="G14" s="25"/>
+      <c r="F14" s="150">
+        <v>4</v>
+      </c>
+      <c r="G14" s="150">
+        <v>1</v>
+      </c>
       <c r="H14" s="21" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="95"/>
+      <c r="A15" s="79"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -2223,17 +2253,21 @@
       <c r="D15" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="10" t="s">
+      <c r="E15" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
+      <c r="F15" s="150">
+        <v>6</v>
+      </c>
+      <c r="G15" s="150">
+        <v>0</v>
+      </c>
       <c r="H15" s="21" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="95"/>
+      <c r="A16" s="79"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -2253,7 +2287,7 @@
       </c>
     </row>
     <row r="17" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="96"/>
+      <c r="A17" s="80"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -2307,7 +2341,7 @@
       </c>
     </row>
     <row r="20" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="97" t="s">
+      <c r="A20" s="81" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -2333,7 +2367,7 @@
       </c>
     </row>
     <row r="21" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="98"/>
+      <c r="A21" s="82"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -2357,7 +2391,7 @@
       </c>
     </row>
     <row r="22" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="98"/>
+      <c r="A22" s="82"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -2377,7 +2411,7 @@
       </c>
     </row>
     <row r="23" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="98"/>
+      <c r="A23" s="82"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -2397,7 +2431,7 @@
       </c>
     </row>
     <row r="24" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="98"/>
+      <c r="A24" s="82"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -2417,7 +2451,7 @@
       </c>
     </row>
     <row r="25" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="99"/>
+      <c r="A25" s="83"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -2471,7 +2505,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="100" t="s">
+      <c r="A28" s="66" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -2497,7 +2531,7 @@
       </c>
     </row>
     <row r="29" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="101"/>
+      <c r="A29" s="67"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -2521,7 +2555,7 @@
       </c>
     </row>
     <row r="30" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="101"/>
+      <c r="A30" s="67"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -2541,7 +2575,7 @@
       </c>
     </row>
     <row r="31" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="101"/>
+      <c r="A31" s="67"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -2561,7 +2595,7 @@
       </c>
     </row>
     <row r="32" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="101"/>
+      <c r="A32" s="67"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -2581,7 +2615,7 @@
       </c>
     </row>
     <row r="33" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="102"/>
+      <c r="A33" s="68"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -2635,7 +2669,7 @@
       </c>
     </row>
     <row r="36" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="103" t="s">
+      <c r="A36" s="90" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -2661,7 +2695,7 @@
       </c>
     </row>
     <row r="37" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="104"/>
+      <c r="A37" s="91"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -2685,7 +2719,7 @@
       </c>
     </row>
     <row r="38" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="104"/>
+      <c r="A38" s="91"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -2705,7 +2739,7 @@
       </c>
     </row>
     <row r="39" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="104"/>
+      <c r="A39" s="91"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -2725,7 +2759,7 @@
       </c>
     </row>
     <row r="40" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="104"/>
+      <c r="A40" s="91"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -2745,7 +2779,7 @@
       </c>
     </row>
     <row r="41" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="105"/>
+      <c r="A41" s="92"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -2799,7 +2833,7 @@
       </c>
     </row>
     <row r="44" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="73" t="s">
+      <c r="A44" s="93" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -2825,7 +2859,7 @@
       </c>
     </row>
     <row r="45" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="74"/>
+      <c r="A45" s="94"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -2849,7 +2883,7 @@
       </c>
     </row>
     <row r="46" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="74"/>
+      <c r="A46" s="94"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -2869,7 +2903,7 @@
       </c>
     </row>
     <row r="47" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="74"/>
+      <c r="A47" s="94"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -2889,7 +2923,7 @@
       </c>
     </row>
     <row r="48" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="74"/>
+      <c r="A48" s="94"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -2909,7 +2943,7 @@
       </c>
     </row>
     <row r="49" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="75"/>
+      <c r="A49" s="95"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -2963,7 +2997,7 @@
       </c>
     </row>
     <row r="52" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="76" t="s">
+      <c r="A52" s="96" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -2989,7 +3023,7 @@
       </c>
     </row>
     <row r="53" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="77"/>
+      <c r="A53" s="97"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -3013,7 +3047,7 @@
       </c>
     </row>
     <row r="54" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="77"/>
+      <c r="A54" s="97"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -3033,7 +3067,7 @@
       </c>
     </row>
     <row r="55" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="77"/>
+      <c r="A55" s="97"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -3053,7 +3087,7 @@
       </c>
     </row>
     <row r="56" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="77"/>
+      <c r="A56" s="97"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -3073,7 +3107,7 @@
       </c>
     </row>
     <row r="57" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="78"/>
+      <c r="A57" s="98"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -3127,7 +3161,7 @@
       </c>
     </row>
     <row r="60" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="79" t="s">
+      <c r="A60" s="99" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -3153,7 +3187,7 @@
       </c>
     </row>
     <row r="61" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="80"/>
+      <c r="A61" s="100"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -3177,7 +3211,7 @@
       </c>
     </row>
     <row r="62" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="80"/>
+      <c r="A62" s="100"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -3197,7 +3231,7 @@
       </c>
     </row>
     <row r="63" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="80"/>
+      <c r="A63" s="100"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -3217,7 +3251,7 @@
       </c>
     </row>
     <row r="64" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="80"/>
+      <c r="A64" s="100"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -3237,7 +3271,7 @@
       </c>
     </row>
     <row r="65" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="81"/>
+      <c r="A65" s="101"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -3291,7 +3325,7 @@
       </c>
     </row>
     <row r="68" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="82" t="s">
+      <c r="A68" s="102" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -3317,7 +3351,7 @@
       </c>
     </row>
     <row r="69" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="83"/>
+      <c r="A69" s="103"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -3341,7 +3375,7 @@
       </c>
     </row>
     <row r="70" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="83"/>
+      <c r="A70" s="103"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -3361,7 +3395,7 @@
       </c>
     </row>
     <row r="71" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="83"/>
+      <c r="A71" s="103"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -3381,7 +3415,7 @@
       </c>
     </row>
     <row r="72" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="83"/>
+      <c r="A72" s="103"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -3401,7 +3435,7 @@
       </c>
     </row>
     <row r="73" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="84"/>
+      <c r="A73" s="104"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -3455,7 +3489,7 @@
       </c>
     </row>
     <row r="76" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="85" t="s">
+      <c r="A76" s="105" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -3481,7 +3515,7 @@
       </c>
     </row>
     <row r="77" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="86"/>
+      <c r="A77" s="106"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -3505,7 +3539,7 @@
       </c>
     </row>
     <row r="78" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="86"/>
+      <c r="A78" s="106"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -3525,7 +3559,7 @@
       </c>
     </row>
     <row r="79" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="86"/>
+      <c r="A79" s="106"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -3545,7 +3579,7 @@
       </c>
     </row>
     <row r="80" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="86"/>
+      <c r="A80" s="106"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -3565,7 +3599,7 @@
       </c>
     </row>
     <row r="81" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="87"/>
+      <c r="A81" s="107"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -3619,7 +3653,7 @@
       </c>
     </row>
     <row r="84" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="88" t="s">
+      <c r="A84" s="84" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -3645,7 +3679,7 @@
       </c>
     </row>
     <row r="85" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="89"/>
+      <c r="A85" s="85"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -3669,7 +3703,7 @@
       </c>
     </row>
     <row r="86" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="89"/>
+      <c r="A86" s="85"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -3689,7 +3723,7 @@
       </c>
     </row>
     <row r="87" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="89"/>
+      <c r="A87" s="85"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -3709,7 +3743,7 @@
       </c>
     </row>
     <row r="88" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="89"/>
+      <c r="A88" s="85"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -3729,7 +3763,7 @@
       </c>
     </row>
     <row r="89" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="90"/>
+      <c r="A89" s="86"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -3783,7 +3817,7 @@
       </c>
     </row>
     <row r="92" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="70" t="s">
+      <c r="A92" s="87" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -3809,7 +3843,7 @@
       </c>
     </row>
     <row r="93" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="71"/>
+      <c r="A93" s="88"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -3833,7 +3867,7 @@
       </c>
     </row>
     <row r="94" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="71"/>
+      <c r="A94" s="88"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -3853,7 +3887,7 @@
       </c>
     </row>
     <row r="95" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="71"/>
+      <c r="A95" s="88"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -3873,7 +3907,7 @@
       </c>
     </row>
     <row r="96" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="71"/>
+      <c r="A96" s="88"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -3893,7 +3927,7 @@
       </c>
     </row>
     <row r="97" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="72"/>
+      <c r="A97" s="89"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -3953,26 +3987,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="64" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="66"/>
+      <c r="A1" s="69" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="71"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="67"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="69"/>
+      <c r="A2" s="72"/>
+      <c r="B2" s="73"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="74"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -4005,7 +4039,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="91" t="s">
+      <c r="A4" s="75" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -4035,7 +4069,7 @@
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="92"/>
+      <c r="A5" s="76"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -4059,7 +4093,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="92"/>
+      <c r="A6" s="76"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -4081,13 +4115,13 @@
       <c r="H6" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="J6" s="1" t="str">
+      <c r="J6" s="1">
         <f>IF(OR(Resultados!F6="",Resultados!G6=""),"",IF(AND(F6=Resultados!F6,G6=Resultados!G6),2,IF(((F6&gt;G6)=(Resultados!F6&gt;Resultados!G6))*((F6&lt;G6)=(Resultados!F6&lt;Resultados!G6)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="92"/>
+      <c r="A7" s="76"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -4109,13 +4143,13 @@
       <c r="H7" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="J7" s="1" t="str">
+      <c r="J7" s="1">
         <f>IF(OR(Resultados!F7="",Resultados!G7=""),"",IF(AND(F7=Resultados!F7,G7=Resultados!G7),2,IF(((F7&gt;G7)=(Resultados!F7&gt;Resultados!G7))*((F7&lt;G7)=(Resultados!F7&lt;Resultados!G7)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="92"/>
+      <c r="A8" s="76"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -4143,7 +4177,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="93"/>
+      <c r="A9" s="77"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -4205,7 +4239,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="94" t="s">
+      <c r="A12" s="78" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -4231,7 +4265,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="95"/>
+      <c r="A13" s="79"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -4255,7 +4289,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="95"/>
+      <c r="A14" s="79"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -4277,13 +4311,13 @@
       <c r="H14" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="J14" s="1" t="str">
+      <c r="J14" s="1">
         <f>IF(OR(Resultados!F14="",Resultados!G14=""),"",IF(AND(F14=Resultados!F14,G14=Resultados!G14),2,IF(((F14&gt;G14)=(Resultados!F14&gt;Resultados!G14))*((F14&lt;G14)=(Resultados!F14&lt;Resultados!G14)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="95"/>
+      <c r="A15" s="79"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -4305,13 +4339,13 @@
       <c r="H15" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="J15" s="1" t="str">
+      <c r="J15" s="1">
         <f>IF(OR(Resultados!F15="",Resultados!G15=""),"",IF(AND(F15=Resultados!F15,G15=Resultados!G15),2,IF(((F15&gt;G15)=(Resultados!F15&gt;Resultados!G15))*((F15&lt;G15)=(Resultados!F15&lt;Resultados!G15)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="95"/>
+      <c r="A16" s="79"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -4339,7 +4373,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="96"/>
+      <c r="A17" s="80"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -4401,7 +4435,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="97" t="s">
+      <c r="A20" s="81" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -4427,7 +4461,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="98"/>
+      <c r="A21" s="82"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -4449,13 +4483,13 @@
       <c r="H21" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="J21" s="1">
+      <c r="J21" s="64">
         <f>IF(OR(Resultados!F21="",Resultados!G21=""),"",IF(AND(F21=Resultados!F21,G21=Resultados!G21),2,IF(((F21&gt;G21)=(Resultados!F21&gt;Resultados!G21))*((F21&lt;G21)=(Resultados!F21&lt;Resultados!G21)),1,0)))</f>
         <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="98"/>
+      <c r="A22" s="82"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -4483,7 +4517,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="98"/>
+      <c r="A23" s="82"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -4511,7 +4545,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="98"/>
+      <c r="A24" s="82"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -4539,7 +4573,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="99"/>
+      <c r="A25" s="83"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -4601,7 +4635,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="100" t="s">
+      <c r="A28" s="66" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -4627,7 +4661,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="101"/>
+      <c r="A29" s="67"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -4655,7 +4689,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="101"/>
+      <c r="A30" s="67"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -4683,7 +4717,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="101"/>
+      <c r="A31" s="67"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -4711,7 +4745,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="101"/>
+      <c r="A32" s="67"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -4739,7 +4773,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="102"/>
+      <c r="A33" s="68"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -4801,7 +4835,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="103" t="s">
+      <c r="A36" s="90" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -4825,13 +4859,13 @@
       <c r="H36" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="J36" s="1">
+      <c r="J36" s="65">
         <f>IF(OR(Resultados!F36="",Resultados!G36=""),"",IF(AND(F36=Resultados!F36,G36=Resultados!G36),2,IF(((F36&gt;G36)=(Resultados!F36&gt;Resultados!G36))*((F36&lt;G36)=(Resultados!F36&lt;Resultados!G36)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="104"/>
+      <c r="A37" s="91"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -4859,7 +4893,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="104"/>
+      <c r="A38" s="91"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -4887,7 +4921,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="104"/>
+      <c r="A39" s="91"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -4915,7 +4949,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="104"/>
+      <c r="A40" s="91"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -4943,7 +4977,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="105"/>
+      <c r="A41" s="92"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -5005,7 +5039,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="73" t="s">
+      <c r="A44" s="93" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -5029,13 +5063,13 @@
       <c r="H44" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="J44" s="1">
+      <c r="J44" s="64">
         <f>IF(OR(Resultados!F44="",Resultados!G44=""),"",IF(AND(F44=Resultados!F44,G44=Resultados!G44),2,IF(((F44&gt;G44)=(Resultados!F44&gt;Resultados!G44))*((F44&lt;G44)=(Resultados!F44&lt;Resultados!G44)),1,0)))</f>
         <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="74"/>
+      <c r="A45" s="94"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -5057,13 +5091,13 @@
       <c r="H45" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="J45" s="1">
+      <c r="J45" s="65">
         <f>IF(OR(Resultados!F45="",Resultados!G45=""),"",IF(AND(F45=Resultados!F45,G45=Resultados!G45),2,IF(((F45&gt;G45)=(Resultados!F45&gt;Resultados!G45))*((F45&lt;G45)=(Resultados!F45&lt;Resultados!G45)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="74"/>
+      <c r="A46" s="94"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -5091,7 +5125,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="74"/>
+      <c r="A47" s="94"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -5119,7 +5153,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="74"/>
+      <c r="A48" s="94"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -5147,7 +5181,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="75"/>
+      <c r="A49" s="95"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -5209,7 +5243,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="76" t="s">
+      <c r="A52" s="96" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -5239,7 +5273,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="77"/>
+      <c r="A53" s="97"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -5261,13 +5295,13 @@
       <c r="H53" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="J53" s="1">
+      <c r="J53" s="65">
         <f>IF(OR(Resultados!F53="",Resultados!G53=""),"",IF(AND(F53=Resultados!F53,G53=Resultados!G53),2,IF(((F53&gt;G53)=(Resultados!F53&gt;Resultados!G53))*((F53&lt;G53)=(Resultados!F53&lt;Resultados!G53)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="77"/>
+      <c r="A54" s="97"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -5295,7 +5329,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="77"/>
+      <c r="A55" s="97"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -5323,7 +5357,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="77"/>
+      <c r="A56" s="97"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -5351,7 +5385,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="78"/>
+      <c r="A57" s="98"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -5413,7 +5447,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="79" t="s">
+      <c r="A60" s="99" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -5443,7 +5477,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="80"/>
+      <c r="A61" s="100"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -5471,7 +5505,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="80"/>
+      <c r="A62" s="100"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -5499,7 +5533,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="80"/>
+      <c r="A63" s="100"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -5527,7 +5561,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="80"/>
+      <c r="A64" s="100"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -5555,7 +5589,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="81"/>
+      <c r="A65" s="101"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -5617,7 +5651,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="82" t="s">
+      <c r="A68" s="102" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -5641,13 +5675,13 @@
       <c r="H68" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="J68" s="1">
+      <c r="J68" s="65">
         <f>IF(OR(Resultados!F68="",Resultados!G68=""),"",IF(AND(F68=Resultados!F68,G68=Resultados!G68),2,IF(((F68&gt;G68)=(Resultados!F68&gt;Resultados!G68))*((F68&lt;G68)=(Resultados!F68&lt;Resultados!G68)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="83"/>
+      <c r="A69" s="103"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -5669,13 +5703,13 @@
       <c r="H69" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="J69" s="1">
+      <c r="J69" s="65">
         <f>IF(OR(Resultados!F69="",Resultados!G69=""),"",IF(AND(F69=Resultados!F69,G69=Resultados!G69),2,IF(((F69&gt;G69)=(Resultados!F69&gt;Resultados!G69))*((F69&lt;G69)=(Resultados!F69&lt;Resultados!G69)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="83"/>
+      <c r="A70" s="103"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -5703,7 +5737,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="83"/>
+      <c r="A71" s="103"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -5731,7 +5765,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="83"/>
+      <c r="A72" s="103"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -5759,7 +5793,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="84"/>
+      <c r="A73" s="104"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -5821,7 +5855,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="85" t="s">
+      <c r="A76" s="105" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -5845,13 +5879,13 @@
       <c r="H76" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="J76" s="1">
+      <c r="J76" s="64">
         <f>IF(OR(Resultados!F76="",Resultados!G76=""),"",IF(AND(F76=Resultados!F76,G76=Resultados!G76),2,IF(((F76&gt;G76)=(Resultados!F76&gt;Resultados!G76))*((F76&lt;G76)=(Resultados!F76&lt;Resultados!G76)),1,0)))</f>
         <v>2</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="86"/>
+      <c r="A77" s="106"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -5879,7 +5913,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="86"/>
+      <c r="A78" s="106"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -5907,7 +5941,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="86"/>
+      <c r="A79" s="106"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -5935,7 +5969,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="86"/>
+      <c r="A80" s="106"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -5963,7 +5997,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="87"/>
+      <c r="A81" s="107"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -6025,7 +6059,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="88" t="s">
+      <c r="A84" s="84" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -6055,7 +6089,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="89"/>
+      <c r="A85" s="85"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -6077,13 +6111,13 @@
       <c r="H85" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="J85" s="1">
+      <c r="J85" s="65">
         <f>IF(OR(Resultados!F85="",Resultados!G85=""),"",IF(AND(F85=Resultados!F85,G85=Resultados!G85),2,IF(((F85&gt;G85)=(Resultados!F85&gt;Resultados!G85))*((F85&lt;G85)=(Resultados!F85&lt;Resultados!G85)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="89"/>
+      <c r="A86" s="85"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -6111,7 +6145,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="89"/>
+      <c r="A87" s="85"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -6139,7 +6173,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="89"/>
+      <c r="A88" s="85"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -6167,7 +6201,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="90"/>
+      <c r="A89" s="86"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -6229,7 +6263,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="70" t="s">
+      <c r="A92" s="87" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -6259,7 +6293,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="71"/>
+      <c r="A93" s="88"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -6287,7 +6321,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="71"/>
+      <c r="A94" s="88"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -6315,7 +6349,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="71"/>
+      <c r="A95" s="88"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -6343,7 +6377,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="71"/>
+      <c r="A96" s="88"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -6371,7 +6405,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="72"/>
+      <c r="A97" s="89"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -6400,12 +6434,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A28:A33"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A4:A9"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="A20:A25"/>
     <mergeCell ref="A84:A89"/>
     <mergeCell ref="A92:A97"/>
     <mergeCell ref="A36:A41"/>
@@ -6414,6 +6442,12 @@
     <mergeCell ref="A60:A65"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="A76:A81"/>
+    <mergeCell ref="A28:A33"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:A9"/>
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="A20:A25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -6441,26 +6475,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="64" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="66"/>
+      <c r="A1" s="69" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="71"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="67"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="69"/>
+      <c r="A2" s="72"/>
+      <c r="B2" s="73"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="74"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -6493,7 +6527,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="91" t="s">
+      <c r="A4" s="75" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -6523,7 +6557,7 @@
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="92"/>
+      <c r="A5" s="76"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -6547,7 +6581,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="92"/>
+      <c r="A6" s="76"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -6569,13 +6603,13 @@
       <c r="H6" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="J6" s="1" t="str">
+      <c r="J6" s="1">
         <f>IF(OR(Resultados!F6="",Resultados!G6=""),"",IF(AND(F6=Resultados!F6,G6=Resultados!G6),2,IF(((F6&gt;G6)=(Resultados!F6&gt;Resultados!G6))*((F6&lt;G6)=(Resultados!F6&lt;Resultados!G6)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="92"/>
+      <c r="A7" s="76"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -6597,13 +6631,13 @@
       <c r="H7" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="J7" s="1" t="str">
+      <c r="J7" s="1">
         <f>IF(OR(Resultados!F7="",Resultados!G7=""),"",IF(AND(F7=Resultados!F7,G7=Resultados!G7),2,IF(((F7&gt;G7)=(Resultados!F7&gt;Resultados!G7))*((F7&lt;G7)=(Resultados!F7&lt;Resultados!G7)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="92"/>
+      <c r="A8" s="76"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -6631,7 +6665,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="93"/>
+      <c r="A9" s="77"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -6693,7 +6727,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="94" t="s">
+      <c r="A12" s="78" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -6719,7 +6753,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="95"/>
+      <c r="A13" s="79"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -6743,7 +6777,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="95"/>
+      <c r="A14" s="79"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -6765,13 +6799,13 @@
       <c r="H14" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="J14" s="1" t="str">
+      <c r="J14" s="1">
         <f>IF(OR(Resultados!F14="",Resultados!G14=""),"",IF(AND(F14=Resultados!F14,G14=Resultados!G14),2,IF(((F14&gt;G14)=(Resultados!F14&gt;Resultados!G14))*((F14&lt;G14)=(Resultados!F14&lt;Resultados!G14)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="95"/>
+      <c r="A15" s="79"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -6793,13 +6827,13 @@
       <c r="H15" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="J15" s="1" t="str">
+      <c r="J15" s="1">
         <f>IF(OR(Resultados!F15="",Resultados!G15=""),"",IF(AND(F15=Resultados!F15,G15=Resultados!G15),2,IF(((F15&gt;G15)=(Resultados!F15&gt;Resultados!G15))*((F15&lt;G15)=(Resultados!F15&lt;Resultados!G15)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="95"/>
+      <c r="A16" s="79"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -6827,7 +6861,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="96"/>
+      <c r="A17" s="80"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -6889,7 +6923,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="97" t="s">
+      <c r="A20" s="81" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -6915,7 +6949,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="98"/>
+      <c r="A21" s="82"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -6937,13 +6971,13 @@
       <c r="H21" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="J21" s="1">
+      <c r="J21" s="64">
         <f>IF(OR(Resultados!F21="",Resultados!G21=""),"",IF(AND(F21=Resultados!F21,G21=Resultados!G21),2,IF(((F21&gt;G21)=(Resultados!F21&gt;Resultados!G21))*((F21&lt;G21)=(Resultados!F21&lt;Resultados!G21)),1,0)))</f>
         <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="98"/>
+      <c r="A22" s="82"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -6971,7 +7005,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="98"/>
+      <c r="A23" s="82"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -6999,7 +7033,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="98"/>
+      <c r="A24" s="82"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -7027,7 +7061,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="99"/>
+      <c r="A25" s="83"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -7089,7 +7123,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="100" t="s">
+      <c r="A28" s="66" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -7115,7 +7149,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="101"/>
+      <c r="A29" s="67"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -7143,7 +7177,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="101"/>
+      <c r="A30" s="67"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -7171,7 +7205,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="101"/>
+      <c r="A31" s="67"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -7199,7 +7233,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="101"/>
+      <c r="A32" s="67"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -7227,7 +7261,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="102"/>
+      <c r="A33" s="68"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -7289,7 +7323,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="103" t="s">
+      <c r="A36" s="90" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -7313,13 +7347,13 @@
       <c r="H36" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="J36" s="1">
+      <c r="J36" s="65">
         <f>IF(OR(Resultados!F36="",Resultados!G36=""),"",IF(AND(F36=Resultados!F36,G36=Resultados!G36),2,IF(((F36&gt;G36)=(Resultados!F36&gt;Resultados!G36))*((F36&lt;G36)=(Resultados!F36&lt;Resultados!G36)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="104"/>
+      <c r="A37" s="91"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -7347,7 +7381,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="104"/>
+      <c r="A38" s="91"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -7375,7 +7409,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="104"/>
+      <c r="A39" s="91"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -7403,7 +7437,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="104"/>
+      <c r="A40" s="91"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -7431,7 +7465,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="105"/>
+      <c r="A41" s="92"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -7493,7 +7527,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="73" t="s">
+      <c r="A44" s="93" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -7523,7 +7557,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="74"/>
+      <c r="A45" s="94"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -7551,7 +7585,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="74"/>
+      <c r="A46" s="94"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -7579,7 +7613,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="74"/>
+      <c r="A47" s="94"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -7607,7 +7641,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="74"/>
+      <c r="A48" s="94"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -7635,7 +7669,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="75"/>
+      <c r="A49" s="95"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -7697,7 +7731,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="76" t="s">
+      <c r="A52" s="96" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -7721,13 +7755,13 @@
       <c r="H52" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="J52" s="1">
+      <c r="J52" s="64">
         <f>IF(OR(Resultados!F52="",Resultados!G52=""),"",IF(AND(F52=Resultados!F52,G52=Resultados!G52),2,IF(((F52&gt;G52)=(Resultados!F52&gt;Resultados!G52))*((F52&lt;G52)=(Resultados!F52&lt;Resultados!G52)),1,0)))</f>
         <v>2</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="77"/>
+      <c r="A53" s="97"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -7749,13 +7783,13 @@
       <c r="H53" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="J53" s="1">
+      <c r="J53" s="65">
         <f>IF(OR(Resultados!F53="",Resultados!G53=""),"",IF(AND(F53=Resultados!F53,G53=Resultados!G53),2,IF(((F53&gt;G53)=(Resultados!F53&gt;Resultados!G53))*((F53&lt;G53)=(Resultados!F53&lt;Resultados!G53)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="77"/>
+      <c r="A54" s="97"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -7783,7 +7817,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="77"/>
+      <c r="A55" s="97"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -7811,7 +7845,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="77"/>
+      <c r="A56" s="97"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -7839,7 +7873,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="78"/>
+      <c r="A57" s="98"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -7901,7 +7935,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="79" t="s">
+      <c r="A60" s="99" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -7931,7 +7965,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="80"/>
+      <c r="A61" s="100"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -7959,7 +7993,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="80"/>
+      <c r="A62" s="100"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -7987,7 +8021,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="80"/>
+      <c r="A63" s="100"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -8015,7 +8049,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="80"/>
+      <c r="A64" s="100"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -8043,7 +8077,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="81"/>
+      <c r="A65" s="101"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -8105,7 +8139,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="82" t="s">
+      <c r="A68" s="102" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -8129,13 +8163,13 @@
       <c r="H68" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="J68" s="1">
+      <c r="J68" s="65">
         <f>IF(OR(Resultados!F68="",Resultados!G68=""),"",IF(AND(F68=Resultados!F68,G68=Resultados!G68),2,IF(((F68&gt;G68)=(Resultados!F68&gt;Resultados!G68))*((F68&lt;G68)=(Resultados!F68&lt;Resultados!G68)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="83"/>
+      <c r="A69" s="103"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -8157,13 +8191,13 @@
       <c r="H69" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="J69" s="1">
+      <c r="J69" s="65">
         <f>IF(OR(Resultados!F69="",Resultados!G69=""),"",IF(AND(F69=Resultados!F69,G69=Resultados!G69),2,IF(((F69&gt;G69)=(Resultados!F69&gt;Resultados!G69))*((F69&lt;G69)=(Resultados!F69&lt;Resultados!G69)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="83"/>
+      <c r="A70" s="103"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -8191,7 +8225,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="83"/>
+      <c r="A71" s="103"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -8219,7 +8253,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="83"/>
+      <c r="A72" s="103"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -8247,7 +8281,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="84"/>
+      <c r="A73" s="104"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -8309,7 +8343,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="85" t="s">
+      <c r="A76" s="105" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -8333,13 +8367,13 @@
       <c r="H76" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="J76" s="1">
+      <c r="J76" s="65">
         <f>IF(OR(Resultados!F76="",Resultados!G76=""),"",IF(AND(F76=Resultados!F76,G76=Resultados!G76),2,IF(((F76&gt;G76)=(Resultados!F76&gt;Resultados!G76))*((F76&lt;G76)=(Resultados!F76&lt;Resultados!G76)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="86"/>
+      <c r="A77" s="106"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -8361,13 +8395,13 @@
       <c r="H77" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="J77" s="1">
+      <c r="J77" s="65">
         <f>IF(OR(Resultados!F77="",Resultados!G77=""),"",IF(AND(F77=Resultados!F77,G77=Resultados!G77),2,IF(((F77&gt;G77)=(Resultados!F77&gt;Resultados!G77))*((F77&lt;G77)=(Resultados!F77&lt;Resultados!G77)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="86"/>
+      <c r="A78" s="106"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -8395,7 +8429,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="86"/>
+      <c r="A79" s="106"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -8423,7 +8457,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="86"/>
+      <c r="A80" s="106"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -8451,7 +8485,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="87"/>
+      <c r="A81" s="107"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -8513,7 +8547,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="88" t="s">
+      <c r="A84" s="84" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -8543,7 +8577,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="89"/>
+      <c r="A85" s="85"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -8565,13 +8599,13 @@
       <c r="H85" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="J85" s="1">
+      <c r="J85" s="65">
         <f>IF(OR(Resultados!F85="",Resultados!G85=""),"",IF(AND(F85=Resultados!F85,G85=Resultados!G85),2,IF(((F85&gt;G85)=(Resultados!F85&gt;Resultados!G85))*((F85&lt;G85)=(Resultados!F85&lt;Resultados!G85)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="89"/>
+      <c r="A86" s="85"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -8599,7 +8633,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="89"/>
+      <c r="A87" s="85"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -8627,7 +8661,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="89"/>
+      <c r="A88" s="85"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -8655,7 +8689,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="90"/>
+      <c r="A89" s="86"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -8717,7 +8751,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="70" t="s">
+      <c r="A92" s="87" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -8741,13 +8775,13 @@
       <c r="H92" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="J92" s="1">
+      <c r="J92" s="65">
         <f>IF(OR(Resultados!F92="",Resultados!G92=""),"",IF(AND(F92=Resultados!F92,G92=Resultados!G92),2,IF(((F92&gt;G92)=(Resultados!F92&gt;Resultados!G92))*((F92&lt;G92)=(Resultados!F92&lt;Resultados!G92)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="71"/>
+      <c r="A93" s="88"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -8775,7 +8809,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="71"/>
+      <c r="A94" s="88"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -8803,7 +8837,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="71"/>
+      <c r="A95" s="88"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -8831,7 +8865,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="71"/>
+      <c r="A96" s="88"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -8859,7 +8893,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="72"/>
+      <c r="A97" s="89"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -8888,12 +8922,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A28:A33"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A4:A9"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="A20:A25"/>
     <mergeCell ref="A84:A89"/>
     <mergeCell ref="A92:A97"/>
     <mergeCell ref="A36:A41"/>
@@ -8902,6 +8930,12 @@
     <mergeCell ref="A60:A65"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="A76:A81"/>
+    <mergeCell ref="A28:A33"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:A9"/>
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="A20:A25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -8924,18 +8958,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D1" s="106" t="s">
+      <c r="D1" s="108" t="s">
         <v>74</v>
       </c>
-      <c r="E1" s="107"/>
-      <c r="F1" s="108"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="110"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D2" s="109" t="s">
+      <c r="D2" s="111" t="s">
         <v>75</v>
       </c>
-      <c r="E2" s="110"/>
-      <c r="F2" s="111"/>
+      <c r="E2" s="112"/>
+      <c r="F2" s="113"/>
     </row>
     <row r="4" spans="1:6" s="29" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="57" t="s">
@@ -8960,17 +8994,17 @@
       </c>
       <c r="B5" s="58">
         <f>Cindy!L4</f>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D5" s="59">
         <v>1</v>
       </c>
       <c r="E5" s="59" t="str" cm="1">
         <f t="array" ref="E5:F13">_xlfn._xlws.SORT(A5:B13,2,-1)</f>
-        <v>Packy</v>
+        <v>Erik</v>
       </c>
       <c r="F5" s="59">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -8979,16 +9013,16 @@
       </c>
       <c r="B6" s="58">
         <f>Wendy!L4</f>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D6" s="55">
         <v>2</v>
       </c>
       <c r="E6" s="55" t="str">
-        <v>Bere</v>
+        <v>Packy</v>
       </c>
       <c r="F6" s="55">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -8997,16 +9031,16 @@
       </c>
       <c r="B7" s="58">
         <f>Jimmy!L4</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D7" s="56">
         <v>3</v>
       </c>
       <c r="E7" s="56" t="str">
-        <v>Jimmy</v>
+        <v>Bere</v>
       </c>
       <c r="F7" s="56">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -9015,16 +9049,16 @@
       </c>
       <c r="B8" s="58">
         <f>Erick!L4</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D8" s="28">
         <v>4</v>
       </c>
       <c r="E8" s="28" t="str">
-        <v>Erik</v>
+        <v>Wendy</v>
       </c>
       <c r="F8" s="28">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -9033,16 +9067,16 @@
       </c>
       <c r="B9" s="58">
         <f>Erik!L4</f>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D9" s="28">
         <v>5</v>
       </c>
       <c r="E9" s="28" t="str">
-        <v>Wendy</v>
+        <v>Jimmy</v>
       </c>
       <c r="F9" s="28">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -9057,10 +9091,10 @@
         <v>6</v>
       </c>
       <c r="E10" s="28" t="str">
-        <v>Lennon</v>
+        <v>Cindy</v>
       </c>
       <c r="F10" s="28">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -9075,7 +9109,7 @@
         <v>7</v>
       </c>
       <c r="E11" s="28" t="str">
-        <v>Yulian</v>
+        <v>Lennon</v>
       </c>
       <c r="F11" s="28">
         <v>12</v>
@@ -9087,16 +9121,16 @@
       </c>
       <c r="B12" s="58">
         <f>Packy!L4</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D12" s="28">
         <v>8</v>
       </c>
       <c r="E12" s="28" t="str">
-        <v>Cindy</v>
+        <v>Yulian</v>
       </c>
       <c r="F12" s="28">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -9105,7 +9139,7 @@
       </c>
       <c r="B13" s="58">
         <f>Bere!L4</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D13" s="28">
         <v>9</v>
@@ -9114,7 +9148,7 @@
         <v>Erick</v>
       </c>
       <c r="F13" s="28">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -9148,26 +9182,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="64" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="66"/>
+      <c r="A1" s="69" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="71"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="67"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="69"/>
+      <c r="A2" s="72"/>
+      <c r="B2" s="73"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="74"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="31"/>
@@ -9200,7 +9234,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="139" t="s">
+      <c r="A4" s="117" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="35">
@@ -9226,11 +9260,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="140"/>
+      <c r="A5" s="118"/>
       <c r="B5" s="35">
         <v>46185</v>
       </c>
@@ -9254,7 +9288,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="140"/>
+      <c r="A6" s="118"/>
       <c r="B6" s="35">
         <v>46191</v>
       </c>
@@ -9276,13 +9310,13 @@
       <c r="H6" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="J6" s="1" t="str">
+      <c r="J6" s="1">
         <f>IF(OR(Resultados!F6="",Resultados!G6=""),"",IF(AND(F6=Resultados!F6,G6=Resultados!G6),2,IF(((F6&gt;G6)=(Resultados!F6&gt;Resultados!G6))*((F6&lt;G6)=(Resultados!F6&lt;Resultados!G6)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="140"/>
+      <c r="A7" s="118"/>
       <c r="B7" s="35">
         <v>46192</v>
       </c>
@@ -9304,13 +9338,13 @@
       <c r="H7" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="J7" s="1" t="str">
+      <c r="J7" s="1">
         <f>IF(OR(Resultados!F7="",Resultados!G7=""),"",IF(AND(F7=Resultados!F7,G7=Resultados!G7),2,IF(((F7&gt;G7)=(Resultados!F7&gt;Resultados!G7))*((F7&lt;G7)=(Resultados!F7&lt;Resultados!G7)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="140"/>
+      <c r="A8" s="118"/>
       <c r="B8" s="35">
         <v>46198</v>
       </c>
@@ -9338,7 +9372,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="141"/>
+      <c r="A9" s="119"/>
       <c r="B9" s="42">
         <v>46198</v>
       </c>
@@ -9400,7 +9434,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="142" t="s">
+      <c r="A12" s="120" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="35">
@@ -9426,7 +9460,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="143"/>
+      <c r="A13" s="121"/>
       <c r="B13" s="35">
         <v>46186</v>
       </c>
@@ -9450,7 +9484,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="143"/>
+      <c r="A14" s="121"/>
       <c r="B14" s="35">
         <v>46191</v>
       </c>
@@ -9472,13 +9506,13 @@
       <c r="H14" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="J14" s="1" t="str">
+      <c r="J14" s="1">
         <f>IF(OR(Resultados!F14="",Resultados!G14=""),"",IF(AND(F14=Resultados!F14,G14=Resultados!G14),2,IF(((F14&gt;G14)=(Resultados!F14&gt;Resultados!G14))*((F14&lt;G14)=(Resultados!F14&lt;Resultados!G14)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="143"/>
+      <c r="A15" s="121"/>
       <c r="B15" s="35">
         <v>46192</v>
       </c>
@@ -9500,13 +9534,13 @@
       <c r="H15" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="J15" s="1" t="str">
+      <c r="J15" s="1">
         <f>IF(OR(Resultados!F15="",Resultados!G15=""),"",IF(AND(F15=Resultados!F15,G15=Resultados!G15),2,IF(((F15&gt;G15)=(Resultados!F15&gt;Resultados!G15))*((F15&lt;G15)=(Resultados!F15&lt;Resultados!G15)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="143"/>
+      <c r="A16" s="121"/>
       <c r="B16" s="35">
         <v>46197</v>
       </c>
@@ -9534,7 +9568,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="144"/>
+      <c r="A17" s="122"/>
       <c r="B17" s="42">
         <v>46197</v>
       </c>
@@ -9596,7 +9630,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="145" t="s">
+      <c r="A20" s="123" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="35">
@@ -9622,7 +9656,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="146"/>
+      <c r="A21" s="124"/>
       <c r="B21" s="35">
         <v>46187</v>
       </c>
@@ -9644,13 +9678,13 @@
       <c r="H21" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="J21" s="1">
+      <c r="J21" s="65">
         <f>IF(OR(Resultados!F21="",Resultados!G21=""),"",IF(AND(F21=Resultados!F21,G21=Resultados!G21),2,IF(((F21&gt;G21)=(Resultados!F21&gt;Resultados!G21))*((F21&lt;G21)=(Resultados!F21&lt;Resultados!G21)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="146"/>
+      <c r="A22" s="124"/>
       <c r="B22" s="35">
         <v>46193</v>
       </c>
@@ -9678,7 +9712,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="146"/>
+      <c r="A23" s="124"/>
       <c r="B23" s="35">
         <v>46193</v>
       </c>
@@ -9706,7 +9740,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="146"/>
+      <c r="A24" s="124"/>
       <c r="B24" s="35">
         <v>46198</v>
       </c>
@@ -9734,7 +9768,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="147"/>
+      <c r="A25" s="125"/>
       <c r="B25" s="42">
         <v>46198</v>
       </c>
@@ -9796,7 +9830,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="136" t="s">
+      <c r="A28" s="114" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="35">
@@ -9822,7 +9856,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="137"/>
+      <c r="A29" s="115"/>
       <c r="B29" s="35">
         <v>46187</v>
       </c>
@@ -9850,7 +9884,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="137"/>
+      <c r="A30" s="115"/>
       <c r="B30" s="35">
         <v>46192</v>
       </c>
@@ -9878,7 +9912,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="137"/>
+      <c r="A31" s="115"/>
       <c r="B31" s="35">
         <v>46193</v>
       </c>
@@ -9906,7 +9940,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="137"/>
+      <c r="A32" s="115"/>
       <c r="B32" s="35">
         <v>46199</v>
       </c>
@@ -9934,7 +9968,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="138"/>
+      <c r="A33" s="116"/>
       <c r="B33" s="42">
         <v>46199</v>
       </c>
@@ -9996,7 +10030,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="118" t="s">
+      <c r="A36" s="132" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="35">
@@ -10020,13 +10054,13 @@
       <c r="H36" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="J36" s="1">
+      <c r="J36" s="65">
         <f>IF(OR(Resultados!F36="",Resultados!G36=""),"",IF(AND(F36=Resultados!F36,G36=Resultados!G36),2,IF(((F36&gt;G36)=(Resultados!F36&gt;Resultados!G36))*((F36&lt;G36)=(Resultados!F36&lt;Resultados!G36)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="119"/>
+      <c r="A37" s="133"/>
       <c r="B37" s="35">
         <v>46188</v>
       </c>
@@ -10054,7 +10088,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="119"/>
+      <c r="A38" s="133"/>
       <c r="B38" s="35">
         <v>46193</v>
       </c>
@@ -10082,7 +10116,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="119"/>
+      <c r="A39" s="133"/>
       <c r="B39" s="35">
         <v>46194</v>
       </c>
@@ -10110,7 +10144,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="119"/>
+      <c r="A40" s="133"/>
       <c r="B40" s="35">
         <v>46198</v>
       </c>
@@ -10138,7 +10172,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="120"/>
+      <c r="A41" s="134"/>
       <c r="B41" s="42">
         <v>46198</v>
       </c>
@@ -10200,7 +10234,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="121" t="s">
+      <c r="A44" s="135" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="35">
@@ -10230,7 +10264,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="122"/>
+      <c r="A45" s="136"/>
       <c r="B45" s="35">
         <v>46188</v>
       </c>
@@ -10252,13 +10286,13 @@
       <c r="H45" s="46" t="s">
         <v>39</v>
       </c>
-      <c r="J45" s="1">
+      <c r="J45" s="65">
         <f>IF(OR(Resultados!F45="",Resultados!G45=""),"",IF(AND(F45=Resultados!F45,G45=Resultados!G45),2,IF(((F45&gt;G45)=(Resultados!F45&gt;Resultados!G45))*((F45&lt;G45)=(Resultados!F45&lt;Resultados!G45)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="122"/>
+      <c r="A46" s="136"/>
       <c r="B46" s="35">
         <v>46193</v>
       </c>
@@ -10286,7 +10320,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="122"/>
+      <c r="A47" s="136"/>
       <c r="B47" s="35">
         <v>46194</v>
       </c>
@@ -10314,7 +10348,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="122"/>
+      <c r="A48" s="136"/>
       <c r="B48" s="35">
         <v>46199</v>
       </c>
@@ -10342,7 +10376,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="123"/>
+      <c r="A49" s="137"/>
       <c r="B49" s="42">
         <v>46199</v>
       </c>
@@ -10404,7 +10438,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="124" t="s">
+      <c r="A52" s="138" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="35">
@@ -10434,7 +10468,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="125"/>
+      <c r="A53" s="139"/>
       <c r="B53" s="35">
         <v>46189</v>
       </c>
@@ -10462,7 +10496,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="125"/>
+      <c r="A54" s="139"/>
       <c r="B54" s="35">
         <v>46194</v>
       </c>
@@ -10490,7 +10524,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="125"/>
+      <c r="A55" s="139"/>
       <c r="B55" s="35">
         <v>46195</v>
       </c>
@@ -10518,7 +10552,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="125"/>
+      <c r="A56" s="139"/>
       <c r="B56" s="35">
         <v>46200</v>
       </c>
@@ -10546,7 +10580,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="126"/>
+      <c r="A57" s="140"/>
       <c r="B57" s="42">
         <v>46200</v>
       </c>
@@ -10608,7 +10642,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="127" t="s">
+      <c r="A60" s="141" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="35">
@@ -10638,7 +10672,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="128"/>
+      <c r="A61" s="142"/>
       <c r="B61" s="35">
         <v>46189</v>
       </c>
@@ -10666,7 +10700,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="128"/>
+      <c r="A62" s="142"/>
       <c r="B62" s="35">
         <v>46194</v>
       </c>
@@ -10694,7 +10728,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="128"/>
+      <c r="A63" s="142"/>
       <c r="B63" s="35">
         <v>46195</v>
       </c>
@@ -10722,7 +10756,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="128"/>
+      <c r="A64" s="142"/>
       <c r="B64" s="35">
         <v>46200</v>
       </c>
@@ -10750,7 +10784,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="129"/>
+      <c r="A65" s="143"/>
       <c r="B65" s="42">
         <v>46200</v>
       </c>
@@ -10812,7 +10846,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="130" t="s">
+      <c r="A68" s="144" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="35">
@@ -10836,13 +10870,13 @@
       <c r="H68" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="J68" s="1">
+      <c r="J68" s="65">
         <f>IF(OR(Resultados!F68="",Resultados!G68=""),"",IF(AND(F68=Resultados!F68,G68=Resultados!G68),2,IF(((F68&gt;G68)=(Resultados!F68&gt;Resultados!G68))*((F68&lt;G68)=(Resultados!F68&lt;Resultados!G68)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="131"/>
+      <c r="A69" s="145"/>
       <c r="B69" s="35">
         <v>46190</v>
       </c>
@@ -10864,13 +10898,13 @@
       <c r="H69" s="46" t="s">
         <v>54</v>
       </c>
-      <c r="J69" s="1">
+      <c r="J69" s="65">
         <f>IF(OR(Resultados!F69="",Resultados!G69=""),"",IF(AND(F69=Resultados!F69,G69=Resultados!G69),2,IF(((F69&gt;G69)=(Resultados!F69&gt;Resultados!G69))*((F69&lt;G69)=(Resultados!F69&lt;Resultados!G69)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="131"/>
+      <c r="A70" s="145"/>
       <c r="B70" s="35">
         <v>46195</v>
       </c>
@@ -10898,7 +10932,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="131"/>
+      <c r="A71" s="145"/>
       <c r="B71" s="35">
         <v>46196</v>
       </c>
@@ -10926,7 +10960,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="131"/>
+      <c r="A72" s="145"/>
       <c r="B72" s="35">
         <v>46199</v>
       </c>
@@ -10954,7 +10988,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="132"/>
+      <c r="A73" s="146"/>
       <c r="B73" s="42">
         <v>46199</v>
       </c>
@@ -11016,7 +11050,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="133" t="s">
+      <c r="A76" s="147" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="35">
@@ -11040,13 +11074,13 @@
       <c r="H76" s="46" t="s">
         <v>57</v>
       </c>
-      <c r="J76" s="1">
+      <c r="J76" s="65">
         <f>IF(OR(Resultados!F76="",Resultados!G76=""),"",IF(AND(F76=Resultados!F76,G76=Resultados!G76),2,IF(((F76&gt;G76)=(Resultados!F76&gt;Resultados!G76))*((F76&lt;G76)=(Resultados!F76&lt;Resultados!G76)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="134"/>
+      <c r="A77" s="148"/>
       <c r="B77" s="35">
         <v>46190</v>
       </c>
@@ -11068,13 +11102,13 @@
       <c r="H77" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="J77" s="1">
+      <c r="J77" s="65">
         <f>IF(OR(Resultados!F77="",Resultados!G77=""),"",IF(AND(F77=Resultados!F77,G77=Resultados!G77),2,IF(((F77&gt;G77)=(Resultados!F77&gt;Resultados!G77))*((F77&lt;G77)=(Resultados!F77&lt;Resultados!G77)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="134"/>
+      <c r="A78" s="148"/>
       <c r="B78" s="35">
         <v>46195</v>
       </c>
@@ -11102,7 +11136,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="134"/>
+      <c r="A79" s="148"/>
       <c r="B79" s="35">
         <v>46196</v>
       </c>
@@ -11130,7 +11164,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="134"/>
+      <c r="A80" s="148"/>
       <c r="B80" s="35">
         <v>46201</v>
       </c>
@@ -11158,7 +11192,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="135"/>
+      <c r="A81" s="149"/>
       <c r="B81" s="42">
         <v>46201</v>
       </c>
@@ -11220,7 +11254,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="112" t="s">
+      <c r="A84" s="126" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="35">
@@ -11250,7 +11284,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="113"/>
+      <c r="A85" s="127"/>
       <c r="B85" s="35">
         <v>46191</v>
       </c>
@@ -11272,13 +11306,13 @@
       <c r="H85" s="46" t="s">
         <v>64</v>
       </c>
-      <c r="J85" s="1">
+      <c r="J85" s="65">
         <f>IF(OR(Resultados!F85="",Resultados!G85=""),"",IF(AND(F85=Resultados!F85,G85=Resultados!G85),2,IF(((F85&gt;G85)=(Resultados!F85&gt;Resultados!G85))*((F85&lt;G85)=(Resultados!F85&lt;Resultados!G85)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="113"/>
+      <c r="A86" s="127"/>
       <c r="B86" s="35">
         <v>46196</v>
       </c>
@@ -11306,7 +11340,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="113"/>
+      <c r="A87" s="127"/>
       <c r="B87" s="35">
         <v>46197</v>
       </c>
@@ -11334,7 +11368,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="113"/>
+      <c r="A88" s="127"/>
       <c r="B88" s="35">
         <v>46201</v>
       </c>
@@ -11362,7 +11396,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="114"/>
+      <c r="A89" s="128"/>
       <c r="B89" s="42">
         <v>46201</v>
       </c>
@@ -11424,7 +11458,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="115" t="s">
+      <c r="A92" s="129" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="35">
@@ -11454,7 +11488,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="116"/>
+      <c r="A93" s="130"/>
       <c r="B93" s="35">
         <v>46191</v>
       </c>
@@ -11476,13 +11510,13 @@
       <c r="H93" s="46" t="s">
         <v>69</v>
       </c>
-      <c r="J93" s="1">
+      <c r="J93" s="64">
         <f>IF(OR(Resultados!F93="",Resultados!G93=""),"",IF(AND(F93=Resultados!F93,G93=Resultados!G93),2,IF(((F93&gt;G93)=(Resultados!F93&gt;Resultados!G93))*((F93&lt;G93)=(Resultados!F93&lt;Resultados!G93)),1,0)))</f>
         <v>2</v>
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="116"/>
+      <c r="A94" s="130"/>
       <c r="B94" s="35">
         <v>46196</v>
       </c>
@@ -11510,7 +11544,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="116"/>
+      <c r="A95" s="130"/>
       <c r="B95" s="35">
         <v>46197</v>
       </c>
@@ -11538,7 +11572,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="116"/>
+      <c r="A96" s="130"/>
       <c r="B96" s="35">
         <v>46200</v>
       </c>
@@ -11566,7 +11600,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="117"/>
+      <c r="A97" s="131"/>
       <c r="B97" s="42">
         <v>46200</v>
       </c>
@@ -11595,12 +11629,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A28:A33"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A4:A9"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="A20:A25"/>
     <mergeCell ref="A84:A89"/>
     <mergeCell ref="A92:A97"/>
     <mergeCell ref="A36:A41"/>
@@ -11609,6 +11637,12 @@
     <mergeCell ref="A60:A65"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="A76:A81"/>
+    <mergeCell ref="A28:A33"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:A9"/>
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="A20:A25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -11637,26 +11671,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="64" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="66"/>
+      <c r="A1" s="69" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="71"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="67"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="69"/>
+      <c r="A2" s="72"/>
+      <c r="B2" s="73"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="74"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="31"/>
@@ -11689,7 +11723,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="139" t="s">
+      <c r="A4" s="117" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="35">
@@ -11715,11 +11749,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="140"/>
+      <c r="A5" s="118"/>
       <c r="B5" s="35">
         <v>46185</v>
       </c>
@@ -11743,7 +11777,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="140"/>
+      <c r="A6" s="118"/>
       <c r="B6" s="35">
         <v>46191</v>
       </c>
@@ -11765,13 +11799,13 @@
       <c r="H6" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="J6" s="1" t="str">
+      <c r="J6" s="1">
         <f>IF(OR(Resultados!F6="",Resultados!G6=""),"",IF(AND(F6=Resultados!F6,G6=Resultados!G6),2,IF(((F6&gt;G6)=(Resultados!F6&gt;Resultados!G6))*((F6&lt;G6)=(Resultados!F6&lt;Resultados!G6)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="140"/>
+      <c r="A7" s="118"/>
       <c r="B7" s="35">
         <v>46192</v>
       </c>
@@ -11793,13 +11827,13 @@
       <c r="H7" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="J7" s="1" t="str">
+      <c r="J7" s="1">
         <f>IF(OR(Resultados!F7="",Resultados!G7=""),"",IF(AND(F7=Resultados!F7,G7=Resultados!G7),2,IF(((F7&gt;G7)=(Resultados!F7&gt;Resultados!G7))*((F7&lt;G7)=(Resultados!F7&lt;Resultados!G7)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="140"/>
+      <c r="A8" s="118"/>
       <c r="B8" s="35">
         <v>46198</v>
       </c>
@@ -11827,7 +11861,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="141"/>
+      <c r="A9" s="119"/>
       <c r="B9" s="42">
         <v>46198</v>
       </c>
@@ -11889,7 +11923,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="142" t="s">
+      <c r="A12" s="120" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="35">
@@ -11915,7 +11949,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="143"/>
+      <c r="A13" s="121"/>
       <c r="B13" s="35">
         <v>46186</v>
       </c>
@@ -11939,7 +11973,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="143"/>
+      <c r="A14" s="121"/>
       <c r="B14" s="35">
         <v>46191</v>
       </c>
@@ -11961,13 +11995,13 @@
       <c r="H14" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="J14" s="1" t="str">
+      <c r="J14" s="1">
         <f>IF(OR(Resultados!F14="",Resultados!G14=""),"",IF(AND(F14=Resultados!F14,G14=Resultados!G14),2,IF(((F14&gt;G14)=(Resultados!F14&gt;Resultados!G14))*((F14&lt;G14)=(Resultados!F14&lt;Resultados!G14)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="143"/>
+      <c r="A15" s="121"/>
       <c r="B15" s="35">
         <v>46192</v>
       </c>
@@ -11989,13 +12023,13 @@
       <c r="H15" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="J15" s="1" t="str">
+      <c r="J15" s="1">
         <f>IF(OR(Resultados!F15="",Resultados!G15=""),"",IF(AND(F15=Resultados!F15,G15=Resultados!G15),2,IF(((F15&gt;G15)=(Resultados!F15&gt;Resultados!G15))*((F15&lt;G15)=(Resultados!F15&lt;Resultados!G15)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="143"/>
+      <c r="A16" s="121"/>
       <c r="B16" s="35">
         <v>46197</v>
       </c>
@@ -12023,7 +12057,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="144"/>
+      <c r="A17" s="122"/>
       <c r="B17" s="42">
         <v>46197</v>
       </c>
@@ -12085,7 +12119,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="145" t="s">
+      <c r="A20" s="123" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="35">
@@ -12111,7 +12145,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="146"/>
+      <c r="A21" s="124"/>
       <c r="B21" s="35">
         <v>46187</v>
       </c>
@@ -12133,13 +12167,13 @@
       <c r="H21" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="J21" s="1">
+      <c r="J21" s="65">
         <f>IF(OR(Resultados!F21="",Resultados!G21=""),"",IF(AND(F21=Resultados!F21,G21=Resultados!G21),2,IF(((F21&gt;G21)=(Resultados!F21&gt;Resultados!G21))*((F21&lt;G21)=(Resultados!F21&lt;Resultados!G21)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="146"/>
+      <c r="A22" s="124"/>
       <c r="B22" s="35">
         <v>46193</v>
       </c>
@@ -12167,7 +12201,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="146"/>
+      <c r="A23" s="124"/>
       <c r="B23" s="35">
         <v>46193</v>
       </c>
@@ -12195,7 +12229,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="146"/>
+      <c r="A24" s="124"/>
       <c r="B24" s="35">
         <v>46198</v>
       </c>
@@ -12223,7 +12257,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="147"/>
+      <c r="A25" s="125"/>
       <c r="B25" s="42">
         <v>46198</v>
       </c>
@@ -12285,7 +12319,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="136" t="s">
+      <c r="A28" s="114" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="35">
@@ -12311,7 +12345,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="137"/>
+      <c r="A29" s="115"/>
       <c r="B29" s="35">
         <v>46187</v>
       </c>
@@ -12333,13 +12367,13 @@
       <c r="H29" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="J29" s="1">
+      <c r="J29" s="65">
         <f>IF(OR(Resultados!F29="",Resultados!G29=""),"",IF(AND(F29=Resultados!F29,G29=Resultados!G29),2,IF(((F29&gt;G29)=(Resultados!F29&gt;Resultados!G29))*((F29&lt;G29)=(Resultados!F29&lt;Resultados!G29)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="137"/>
+      <c r="A30" s="115"/>
       <c r="B30" s="35">
         <v>46192</v>
       </c>
@@ -12367,7 +12401,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="137"/>
+      <c r="A31" s="115"/>
       <c r="B31" s="35">
         <v>46193</v>
       </c>
@@ -12395,7 +12429,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="137"/>
+      <c r="A32" s="115"/>
       <c r="B32" s="35">
         <v>46199</v>
       </c>
@@ -12423,7 +12457,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="138"/>
+      <c r="A33" s="116"/>
       <c r="B33" s="42">
         <v>46199</v>
       </c>
@@ -12485,7 +12519,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="118" t="s">
+      <c r="A36" s="132" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="35">
@@ -12509,13 +12543,13 @@
       <c r="H36" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="J36" s="1">
+      <c r="J36" s="65">
         <f>IF(OR(Resultados!F36="",Resultados!G36=""),"",IF(AND(F36=Resultados!F36,G36=Resultados!G36),2,IF(((F36&gt;G36)=(Resultados!F36&gt;Resultados!G36))*((F36&lt;G36)=(Resultados!F36&lt;Resultados!G36)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="119"/>
+      <c r="A37" s="133"/>
       <c r="B37" s="35">
         <v>46188</v>
       </c>
@@ -12543,7 +12577,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="119"/>
+      <c r="A38" s="133"/>
       <c r="B38" s="35">
         <v>46193</v>
       </c>
@@ -12571,7 +12605,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="119"/>
+      <c r="A39" s="133"/>
       <c r="B39" s="35">
         <v>46194</v>
       </c>
@@ -12599,7 +12633,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="119"/>
+      <c r="A40" s="133"/>
       <c r="B40" s="35">
         <v>46198</v>
       </c>
@@ -12627,7 +12661,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="120"/>
+      <c r="A41" s="134"/>
       <c r="B41" s="42">
         <v>46198</v>
       </c>
@@ -12689,7 +12723,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="121" t="s">
+      <c r="A44" s="135" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="35">
@@ -12719,7 +12753,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="122"/>
+      <c r="A45" s="136"/>
       <c r="B45" s="35">
         <v>46188</v>
       </c>
@@ -12741,13 +12775,13 @@
       <c r="H45" s="46" t="s">
         <v>39</v>
       </c>
-      <c r="J45" s="1">
+      <c r="J45" s="65">
         <f>IF(OR(Resultados!F45="",Resultados!G45=""),"",IF(AND(F45=Resultados!F45,G45=Resultados!G45),2,IF(((F45&gt;G45)=(Resultados!F45&gt;Resultados!G45))*((F45&lt;G45)=(Resultados!F45&lt;Resultados!G45)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="122"/>
+      <c r="A46" s="136"/>
       <c r="B46" s="35">
         <v>46193</v>
       </c>
@@ -12775,7 +12809,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="122"/>
+      <c r="A47" s="136"/>
       <c r="B47" s="35">
         <v>46194</v>
       </c>
@@ -12803,7 +12837,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="122"/>
+      <c r="A48" s="136"/>
       <c r="B48" s="35">
         <v>46199</v>
       </c>
@@ -12831,7 +12865,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="123"/>
+      <c r="A49" s="137"/>
       <c r="B49" s="42">
         <v>46199</v>
       </c>
@@ -12893,7 +12927,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="124" t="s">
+      <c r="A52" s="138" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="35">
@@ -12923,7 +12957,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="125"/>
+      <c r="A53" s="139"/>
       <c r="B53" s="35">
         <v>46189</v>
       </c>
@@ -12945,13 +12979,13 @@
       <c r="H53" s="46" t="s">
         <v>44</v>
       </c>
-      <c r="J53" s="1">
+      <c r="J53" s="65">
         <f>IF(OR(Resultados!F53="",Resultados!G53=""),"",IF(AND(F53=Resultados!F53,G53=Resultados!G53),2,IF(((F53&gt;G53)=(Resultados!F53&gt;Resultados!G53))*((F53&lt;G53)=(Resultados!F53&lt;Resultados!G53)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="125"/>
+      <c r="A54" s="139"/>
       <c r="B54" s="35">
         <v>46194</v>
       </c>
@@ -12979,7 +13013,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="125"/>
+      <c r="A55" s="139"/>
       <c r="B55" s="35">
         <v>46195</v>
       </c>
@@ -13007,7 +13041,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="125"/>
+      <c r="A56" s="139"/>
       <c r="B56" s="35">
         <v>46200</v>
       </c>
@@ -13035,7 +13069,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="126"/>
+      <c r="A57" s="140"/>
       <c r="B57" s="42">
         <v>46200</v>
       </c>
@@ -13097,7 +13131,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="127" t="s">
+      <c r="A60" s="141" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="35">
@@ -13127,7 +13161,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="128"/>
+      <c r="A61" s="142"/>
       <c r="B61" s="35">
         <v>46189</v>
       </c>
@@ -13155,7 +13189,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="128"/>
+      <c r="A62" s="142"/>
       <c r="B62" s="35">
         <v>46194</v>
       </c>
@@ -13183,7 +13217,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="128"/>
+      <c r="A63" s="142"/>
       <c r="B63" s="35">
         <v>46195</v>
       </c>
@@ -13211,7 +13245,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="128"/>
+      <c r="A64" s="142"/>
       <c r="B64" s="35">
         <v>46200</v>
       </c>
@@ -13239,7 +13273,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="129"/>
+      <c r="A65" s="143"/>
       <c r="B65" s="42">
         <v>46200</v>
       </c>
@@ -13301,7 +13335,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="130" t="s">
+      <c r="A68" s="144" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="35">
@@ -13331,7 +13365,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="131"/>
+      <c r="A69" s="145"/>
       <c r="B69" s="35">
         <v>46190</v>
       </c>
@@ -13353,13 +13387,13 @@
       <c r="H69" s="46" t="s">
         <v>54</v>
       </c>
-      <c r="J69" s="1">
+      <c r="J69" s="65">
         <f>IF(OR(Resultados!F69="",Resultados!G69=""),"",IF(AND(F69=Resultados!F69,G69=Resultados!G69),2,IF(((F69&gt;G69)=(Resultados!F69&gt;Resultados!G69))*((F69&lt;G69)=(Resultados!F69&lt;Resultados!G69)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="131"/>
+      <c r="A70" s="145"/>
       <c r="B70" s="35">
         <v>46195</v>
       </c>
@@ -13387,7 +13421,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="131"/>
+      <c r="A71" s="145"/>
       <c r="B71" s="35">
         <v>46196</v>
       </c>
@@ -13415,7 +13449,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="131"/>
+      <c r="A72" s="145"/>
       <c r="B72" s="35">
         <v>46199</v>
       </c>
@@ -13443,7 +13477,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="132"/>
+      <c r="A73" s="146"/>
       <c r="B73" s="42">
         <v>46199</v>
       </c>
@@ -13505,7 +13539,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="133" t="s">
+      <c r="A76" s="147" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="35">
@@ -13535,7 +13569,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="134"/>
+      <c r="A77" s="148"/>
       <c r="B77" s="35">
         <v>46190</v>
       </c>
@@ -13557,13 +13591,13 @@
       <c r="H77" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="J77" s="1">
+      <c r="J77" s="65">
         <f>IF(OR(Resultados!F77="",Resultados!G77=""),"",IF(AND(F77=Resultados!F77,G77=Resultados!G77),2,IF(((F77&gt;G77)=(Resultados!F77&gt;Resultados!G77))*((F77&lt;G77)=(Resultados!F77&lt;Resultados!G77)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="134"/>
+      <c r="A78" s="148"/>
       <c r="B78" s="35">
         <v>46195</v>
       </c>
@@ -13591,7 +13625,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="134"/>
+      <c r="A79" s="148"/>
       <c r="B79" s="35">
         <v>46196</v>
       </c>
@@ -13619,7 +13653,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="134"/>
+      <c r="A80" s="148"/>
       <c r="B80" s="35">
         <v>46201</v>
       </c>
@@ -13647,7 +13681,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="135"/>
+      <c r="A81" s="149"/>
       <c r="B81" s="42">
         <v>46201</v>
       </c>
@@ -13709,7 +13743,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="112" t="s">
+      <c r="A84" s="126" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="35">
@@ -13739,7 +13773,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="113"/>
+      <c r="A85" s="127"/>
       <c r="B85" s="35">
         <v>46191</v>
       </c>
@@ -13761,13 +13795,13 @@
       <c r="H85" s="46" t="s">
         <v>64</v>
       </c>
-      <c r="J85" s="1">
+      <c r="J85" s="65">
         <f>IF(OR(Resultados!F85="",Resultados!G85=""),"",IF(AND(F85=Resultados!F85,G85=Resultados!G85),2,IF(((F85&gt;G85)=(Resultados!F85&gt;Resultados!G85))*((F85&lt;G85)=(Resultados!F85&lt;Resultados!G85)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="113"/>
+      <c r="A86" s="127"/>
       <c r="B86" s="35">
         <v>46196</v>
       </c>
@@ -13795,7 +13829,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="113"/>
+      <c r="A87" s="127"/>
       <c r="B87" s="35">
         <v>46197</v>
       </c>
@@ -13823,7 +13857,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="113"/>
+      <c r="A88" s="127"/>
       <c r="B88" s="35">
         <v>46201</v>
       </c>
@@ -13851,7 +13885,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="114"/>
+      <c r="A89" s="128"/>
       <c r="B89" s="42">
         <v>46201</v>
       </c>
@@ -13913,7 +13947,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="115" t="s">
+      <c r="A92" s="129" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="35">
@@ -13943,7 +13977,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="116"/>
+      <c r="A93" s="130"/>
       <c r="B93" s="35">
         <v>46191</v>
       </c>
@@ -13971,7 +14005,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="116"/>
+      <c r="A94" s="130"/>
       <c r="B94" s="35">
         <v>46196</v>
       </c>
@@ -13999,7 +14033,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="116"/>
+      <c r="A95" s="130"/>
       <c r="B95" s="35">
         <v>46197</v>
       </c>
@@ -14027,7 +14061,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="116"/>
+      <c r="A96" s="130"/>
       <c r="B96" s="35">
         <v>46200</v>
       </c>
@@ -14055,7 +14089,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="117"/>
+      <c r="A97" s="131"/>
       <c r="B97" s="42">
         <v>46200</v>
       </c>
@@ -14084,12 +14118,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A28:A33"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A4:A9"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="A20:A25"/>
     <mergeCell ref="A84:A89"/>
     <mergeCell ref="A92:A97"/>
     <mergeCell ref="A36:A41"/>
@@ -14098,6 +14126,12 @@
     <mergeCell ref="A60:A65"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="A76:A81"/>
+    <mergeCell ref="A28:A33"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:A9"/>
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="A20:A25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -14125,26 +14159,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="64" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="66"/>
+      <c r="A1" s="69" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="71"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="67"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="69"/>
+      <c r="A2" s="72"/>
+      <c r="B2" s="73"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="74"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -14177,7 +14211,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="91" t="s">
+      <c r="A4" s="75" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -14203,11 +14237,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="92"/>
+      <c r="A5" s="76"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -14231,7 +14265,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="92"/>
+      <c r="A6" s="76"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -14253,13 +14287,13 @@
       <c r="H6" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="J6" s="1" t="str">
+      <c r="J6" s="1">
         <f>IF(OR(Resultados!F6="",Resultados!G6=""),"",IF(AND(F6=Resultados!F6,G6=Resultados!G6),2,IF(((F6&gt;G6)=(Resultados!F6&gt;Resultados!G6))*((F6&lt;G6)=(Resultados!F6&lt;Resultados!G6)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="92"/>
+      <c r="A7" s="76"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -14281,13 +14315,13 @@
       <c r="H7" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="J7" s="1" t="str">
+      <c r="J7" s="1">
         <f>IF(OR(Resultados!F7="",Resultados!G7=""),"",IF(AND(F7=Resultados!F7,G7=Resultados!G7),2,IF(((F7&gt;G7)=(Resultados!F7&gt;Resultados!G7))*((F7&lt;G7)=(Resultados!F7&lt;Resultados!G7)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="92"/>
+      <c r="A8" s="76"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -14315,7 +14349,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="93"/>
+      <c r="A9" s="77"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -14377,7 +14411,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="94" t="s">
+      <c r="A12" s="78" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -14403,7 +14437,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="95"/>
+      <c r="A13" s="79"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -14427,7 +14461,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="95"/>
+      <c r="A14" s="79"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -14449,13 +14483,13 @@
       <c r="H14" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="J14" s="1" t="str">
+      <c r="J14" s="1">
         <f>IF(OR(Resultados!F14="",Resultados!G14=""),"",IF(AND(F14=Resultados!F14,G14=Resultados!G14),2,IF(((F14&gt;G14)=(Resultados!F14&gt;Resultados!G14))*((F14&lt;G14)=(Resultados!F14&lt;Resultados!G14)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="95"/>
+      <c r="A15" s="79"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -14477,13 +14511,13 @@
       <c r="H15" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="J15" s="1" t="str">
+      <c r="J15" s="1">
         <f>IF(OR(Resultados!F15="",Resultados!G15=""),"",IF(AND(F15=Resultados!F15,G15=Resultados!G15),2,IF(((F15&gt;G15)=(Resultados!F15&gt;Resultados!G15))*((F15&lt;G15)=(Resultados!F15&lt;Resultados!G15)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="95"/>
+      <c r="A16" s="79"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -14511,7 +14545,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="96"/>
+      <c r="A17" s="80"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -14573,7 +14607,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="97" t="s">
+      <c r="A20" s="81" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -14599,7 +14633,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="98"/>
+      <c r="A21" s="82"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -14621,13 +14655,13 @@
       <c r="H21" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="J21" s="1">
+      <c r="J21" s="65">
         <f>IF(OR(Resultados!F21="",Resultados!G21=""),"",IF(AND(F21=Resultados!F21,G21=Resultados!G21),2,IF(((F21&gt;G21)=(Resultados!F21&gt;Resultados!G21))*((F21&lt;G21)=(Resultados!F21&lt;Resultados!G21)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="98"/>
+      <c r="A22" s="82"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -14655,7 +14689,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="98"/>
+      <c r="A23" s="82"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -14683,7 +14717,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="98"/>
+      <c r="A24" s="82"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -14711,7 +14745,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="99"/>
+      <c r="A25" s="83"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -14773,7 +14807,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="100" t="s">
+      <c r="A28" s="66" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -14799,7 +14833,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="101"/>
+      <c r="A29" s="67"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -14827,7 +14861,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="101"/>
+      <c r="A30" s="67"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -14855,7 +14889,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="101"/>
+      <c r="A31" s="67"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -14883,7 +14917,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="101"/>
+      <c r="A32" s="67"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -14911,7 +14945,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="102"/>
+      <c r="A33" s="68"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -14973,7 +15007,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="103" t="s">
+      <c r="A36" s="90" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -14997,13 +15031,13 @@
       <c r="H36" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="J36" s="1">
+      <c r="J36" s="65">
         <f>IF(OR(Resultados!F36="",Resultados!G36=""),"",IF(AND(F36=Resultados!F36,G36=Resultados!G36),2,IF(((F36&gt;G36)=(Resultados!F36&gt;Resultados!G36))*((F36&lt;G36)=(Resultados!F36&lt;Resultados!G36)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="104"/>
+      <c r="A37" s="91"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -15031,7 +15065,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="104"/>
+      <c r="A38" s="91"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -15059,7 +15093,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="104"/>
+      <c r="A39" s="91"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -15087,7 +15121,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="104"/>
+      <c r="A40" s="91"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -15115,7 +15149,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="105"/>
+      <c r="A41" s="92"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -15177,7 +15211,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="73" t="s">
+      <c r="A44" s="93" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -15207,7 +15241,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="74"/>
+      <c r="A45" s="94"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -15229,13 +15263,13 @@
       <c r="H45" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="J45" s="1">
+      <c r="J45" s="65">
         <f>IF(OR(Resultados!F45="",Resultados!G45=""),"",IF(AND(F45=Resultados!F45,G45=Resultados!G45),2,IF(((F45&gt;G45)=(Resultados!F45&gt;Resultados!G45))*((F45&lt;G45)=(Resultados!F45&lt;Resultados!G45)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="74"/>
+      <c r="A46" s="94"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -15263,7 +15297,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="74"/>
+      <c r="A47" s="94"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -15291,7 +15325,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="74"/>
+      <c r="A48" s="94"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -15319,7 +15353,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="75"/>
+      <c r="A49" s="95"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -15381,7 +15415,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="76" t="s">
+      <c r="A52" s="96" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -15411,7 +15445,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="77"/>
+      <c r="A53" s="97"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -15433,13 +15467,13 @@
       <c r="H53" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="J53" s="1">
+      <c r="J53" s="64">
         <f>IF(OR(Resultados!F53="",Resultados!G53=""),"",IF(AND(F53=Resultados!F53,G53=Resultados!G53),2,IF(((F53&gt;G53)=(Resultados!F53&gt;Resultados!G53))*((F53&lt;G53)=(Resultados!F53&lt;Resultados!G53)),1,0)))</f>
         <v>2</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="77"/>
+      <c r="A54" s="97"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -15467,7 +15501,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="77"/>
+      <c r="A55" s="97"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -15495,7 +15529,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="77"/>
+      <c r="A56" s="97"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -15523,7 +15557,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="78"/>
+      <c r="A57" s="98"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -15585,7 +15619,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="79" t="s">
+      <c r="A60" s="99" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -15615,7 +15649,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="80"/>
+      <c r="A61" s="100"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -15643,7 +15677,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="80"/>
+      <c r="A62" s="100"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -15671,7 +15705,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="80"/>
+      <c r="A63" s="100"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -15699,7 +15733,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="80"/>
+      <c r="A64" s="100"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -15727,7 +15761,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="81"/>
+      <c r="A65" s="101"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -15789,7 +15823,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="82" t="s">
+      <c r="A68" s="102" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -15813,13 +15847,13 @@
       <c r="H68" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="J68" s="1">
+      <c r="J68" s="65">
         <f>IF(OR(Resultados!F68="",Resultados!G68=""),"",IF(AND(F68=Resultados!F68,G68=Resultados!G68),2,IF(((F68&gt;G68)=(Resultados!F68&gt;Resultados!G68))*((F68&lt;G68)=(Resultados!F68&lt;Resultados!G68)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="83"/>
+      <c r="A69" s="103"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -15841,13 +15875,13 @@
       <c r="H69" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="J69" s="1">
+      <c r="J69" s="65">
         <f>IF(OR(Resultados!F69="",Resultados!G69=""),"",IF(AND(F69=Resultados!F69,G69=Resultados!G69),2,IF(((F69&gt;G69)=(Resultados!F69&gt;Resultados!G69))*((F69&lt;G69)=(Resultados!F69&lt;Resultados!G69)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="83"/>
+      <c r="A70" s="103"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -15875,7 +15909,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="83"/>
+      <c r="A71" s="103"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -15903,7 +15937,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="83"/>
+      <c r="A72" s="103"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -15931,7 +15965,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="84"/>
+      <c r="A73" s="104"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -15993,7 +16027,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="85" t="s">
+      <c r="A76" s="105" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -16017,13 +16051,13 @@
       <c r="H76" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="J76" s="1">
+      <c r="J76" s="64">
         <f>IF(OR(Resultados!F76="",Resultados!G76=""),"",IF(AND(F76=Resultados!F76,G76=Resultados!G76),2,IF(((F76&gt;G76)=(Resultados!F76&gt;Resultados!G76))*((F76&lt;G76)=(Resultados!F76&lt;Resultados!G76)),1,0)))</f>
         <v>2</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="86"/>
+      <c r="A77" s="106"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -16045,13 +16079,13 @@
       <c r="H77" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="J77" s="1">
+      <c r="J77" s="65">
         <f>IF(OR(Resultados!F77="",Resultados!G77=""),"",IF(AND(F77=Resultados!F77,G77=Resultados!G77),2,IF(((F77&gt;G77)=(Resultados!F77&gt;Resultados!G77))*((F77&lt;G77)=(Resultados!F77&lt;Resultados!G77)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="86"/>
+      <c r="A78" s="106"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -16079,7 +16113,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="86"/>
+      <c r="A79" s="106"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -16107,7 +16141,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="86"/>
+      <c r="A80" s="106"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -16135,7 +16169,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="87"/>
+      <c r="A81" s="107"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -16197,7 +16231,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="88" t="s">
+      <c r="A84" s="84" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -16227,7 +16261,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="89"/>
+      <c r="A85" s="85"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -16249,13 +16283,13 @@
       <c r="H85" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="J85" s="1">
+      <c r="J85" s="65">
         <f>IF(OR(Resultados!F85="",Resultados!G85=""),"",IF(AND(F85=Resultados!F85,G85=Resultados!G85),2,IF(((F85&gt;G85)=(Resultados!F85&gt;Resultados!G85))*((F85&lt;G85)=(Resultados!F85&lt;Resultados!G85)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="89"/>
+      <c r="A86" s="85"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -16283,7 +16317,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="89"/>
+      <c r="A87" s="85"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -16311,7 +16345,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="89"/>
+      <c r="A88" s="85"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -16339,7 +16373,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="90"/>
+      <c r="A89" s="86"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -16401,7 +16435,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="70" t="s">
+      <c r="A92" s="87" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -16425,13 +16459,13 @@
       <c r="H92" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="J92" s="1">
+      <c r="J92" s="65">
         <f>IF(OR(Resultados!F92="",Resultados!G92=""),"",IF(AND(F92=Resultados!F92,G92=Resultados!G92),2,IF(((F92&gt;G92)=(Resultados!F92&gt;Resultados!G92))*((F92&lt;G92)=(Resultados!F92&lt;Resultados!G92)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="71"/>
+      <c r="A93" s="88"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -16453,13 +16487,13 @@
       <c r="H93" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="J93" s="1">
+      <c r="J93" s="64">
         <f>IF(OR(Resultados!F93="",Resultados!G93=""),"",IF(AND(F93=Resultados!F93,G93=Resultados!G93),2,IF(((F93&gt;G93)=(Resultados!F93&gt;Resultados!G93))*((F93&lt;G93)=(Resultados!F93&lt;Resultados!G93)),1,0)))</f>
         <v>2</v>
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="71"/>
+      <c r="A94" s="88"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -16487,7 +16521,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="71"/>
+      <c r="A95" s="88"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -16515,7 +16549,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="71"/>
+      <c r="A96" s="88"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -16543,7 +16577,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="72"/>
+      <c r="A97" s="89"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -16572,12 +16606,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A28:A33"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A4:A9"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="A20:A25"/>
     <mergeCell ref="A84:A89"/>
     <mergeCell ref="A92:A97"/>
     <mergeCell ref="A36:A41"/>
@@ -16586,6 +16614,12 @@
     <mergeCell ref="A60:A65"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="A76:A81"/>
+    <mergeCell ref="A28:A33"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:A9"/>
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="A20:A25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -16613,26 +16647,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="64" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="66"/>
+      <c r="A1" s="69" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="71"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="67"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="69"/>
+      <c r="A2" s="72"/>
+      <c r="B2" s="73"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="74"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -16665,7 +16699,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="91" t="s">
+      <c r="A4" s="75" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -16691,11 +16725,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="92"/>
+      <c r="A5" s="76"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -16719,7 +16753,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="92"/>
+      <c r="A6" s="76"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -16741,13 +16775,13 @@
       <c r="H6" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="J6" s="1" t="str">
+      <c r="J6" s="1">
         <f>IF(OR(Resultados!F6="",Resultados!G6=""),"",IF(AND(F6=Resultados!F6,G6=Resultados!G6),2,IF(((F6&gt;G6)=(Resultados!F6&gt;Resultados!G6))*((F6&lt;G6)=(Resultados!F6&lt;Resultados!G6)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="92"/>
+      <c r="A7" s="76"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -16769,13 +16803,13 @@
       <c r="H7" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="J7" s="1" t="str">
+      <c r="J7" s="1">
         <f>IF(OR(Resultados!F7="",Resultados!G7=""),"",IF(AND(F7=Resultados!F7,G7=Resultados!G7),2,IF(((F7&gt;G7)=(Resultados!F7&gt;Resultados!G7))*((F7&lt;G7)=(Resultados!F7&lt;Resultados!G7)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="92"/>
+      <c r="A8" s="76"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -16803,7 +16837,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="93"/>
+      <c r="A9" s="77"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -16865,7 +16899,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="94" t="s">
+      <c r="A12" s="78" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -16891,7 +16925,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="95"/>
+      <c r="A13" s="79"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -16915,7 +16949,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="95"/>
+      <c r="A14" s="79"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -16937,13 +16971,13 @@
       <c r="H14" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="J14" s="1" t="str">
+      <c r="J14" s="1">
         <f>IF(OR(Resultados!F14="",Resultados!G14=""),"",IF(AND(F14=Resultados!F14,G14=Resultados!G14),2,IF(((F14&gt;G14)=(Resultados!F14&gt;Resultados!G14))*((F14&lt;G14)=(Resultados!F14&lt;Resultados!G14)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="95"/>
+      <c r="A15" s="79"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -16965,13 +16999,13 @@
       <c r="H15" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="J15" s="1" t="str">
+      <c r="J15" s="1">
         <f>IF(OR(Resultados!F15="",Resultados!G15=""),"",IF(AND(F15=Resultados!F15,G15=Resultados!G15),2,IF(((F15&gt;G15)=(Resultados!F15&gt;Resultados!G15))*((F15&lt;G15)=(Resultados!F15&lt;Resultados!G15)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="95"/>
+      <c r="A16" s="79"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -16999,7 +17033,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="96"/>
+      <c r="A17" s="80"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -17061,7 +17095,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="97" t="s">
+      <c r="A20" s="81" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -17087,7 +17121,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="98"/>
+      <c r="A21" s="82"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -17109,13 +17143,13 @@
       <c r="H21" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="J21" s="1">
+      <c r="J21" s="64">
         <f>IF(OR(Resultados!F21="",Resultados!G21=""),"",IF(AND(F21=Resultados!F21,G21=Resultados!G21),2,IF(((F21&gt;G21)=(Resultados!F21&gt;Resultados!G21))*((F21&lt;G21)=(Resultados!F21&lt;Resultados!G21)),1,0)))</f>
         <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="98"/>
+      <c r="A22" s="82"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -17143,7 +17177,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="98"/>
+      <c r="A23" s="82"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -17171,7 +17205,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="98"/>
+      <c r="A24" s="82"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -17199,7 +17233,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="99"/>
+      <c r="A25" s="83"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -17261,7 +17295,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="100" t="s">
+      <c r="A28" s="66" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -17287,7 +17321,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="101"/>
+      <c r="A29" s="67"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -17315,7 +17349,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="101"/>
+      <c r="A30" s="67"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -17343,7 +17377,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="101"/>
+      <c r="A31" s="67"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -17371,7 +17405,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="101"/>
+      <c r="A32" s="67"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -17399,7 +17433,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="102"/>
+      <c r="A33" s="68"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -17461,7 +17495,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="103" t="s">
+      <c r="A36" s="90" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -17485,13 +17519,13 @@
       <c r="H36" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="J36" s="1">
+      <c r="J36" s="65">
         <f>IF(OR(Resultados!F36="",Resultados!G36=""),"",IF(AND(F36=Resultados!F36,G36=Resultados!G36),2,IF(((F36&gt;G36)=(Resultados!F36&gt;Resultados!G36))*((F36&lt;G36)=(Resultados!F36&lt;Resultados!G36)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="104"/>
+      <c r="A37" s="91"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -17519,7 +17553,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="104"/>
+      <c r="A38" s="91"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -17547,7 +17581,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="104"/>
+      <c r="A39" s="91"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -17575,7 +17609,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="104"/>
+      <c r="A40" s="91"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -17603,7 +17637,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="105"/>
+      <c r="A41" s="92"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -17665,7 +17699,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="73" t="s">
+      <c r="A44" s="93" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -17695,7 +17729,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="74"/>
+      <c r="A45" s="94"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -17717,13 +17751,13 @@
       <c r="H45" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="J45" s="1">
+      <c r="J45" s="65">
         <f>IF(OR(Resultados!F45="",Resultados!G45=""),"",IF(AND(F45=Resultados!F45,G45=Resultados!G45),2,IF(((F45&gt;G45)=(Resultados!F45&gt;Resultados!G45))*((F45&lt;G45)=(Resultados!F45&lt;Resultados!G45)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="74"/>
+      <c r="A46" s="94"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -17751,7 +17785,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="74"/>
+      <c r="A47" s="94"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -17779,7 +17813,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="74"/>
+      <c r="A48" s="94"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -17807,7 +17841,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="75"/>
+      <c r="A49" s="95"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -17869,7 +17903,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="76" t="s">
+      <c r="A52" s="96" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -17899,7 +17933,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="77"/>
+      <c r="A53" s="97"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -17927,7 +17961,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="77"/>
+      <c r="A54" s="97"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -17955,7 +17989,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="77"/>
+      <c r="A55" s="97"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -17983,7 +18017,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="77"/>
+      <c r="A56" s="97"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -18011,7 +18045,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="78"/>
+      <c r="A57" s="98"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -18073,7 +18107,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="79" t="s">
+      <c r="A60" s="99" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -18103,7 +18137,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="80"/>
+      <c r="A61" s="100"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -18131,7 +18165,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="80"/>
+      <c r="A62" s="100"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -18159,7 +18193,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="80"/>
+      <c r="A63" s="100"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -18187,7 +18221,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="80"/>
+      <c r="A64" s="100"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -18215,7 +18249,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="81"/>
+      <c r="A65" s="101"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -18277,7 +18311,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="82" t="s">
+      <c r="A68" s="102" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -18301,13 +18335,13 @@
       <c r="H68" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="J68" s="1">
+      <c r="J68" s="64">
         <f>IF(OR(Resultados!F68="",Resultados!G68=""),"",IF(AND(F68=Resultados!F68,G68=Resultados!G68),2,IF(((F68&gt;G68)=(Resultados!F68&gt;Resultados!G68))*((F68&lt;G68)=(Resultados!F68&lt;Resultados!G68)),1,0)))</f>
         <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="83"/>
+      <c r="A69" s="103"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -18329,13 +18363,13 @@
       <c r="H69" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="J69" s="1">
+      <c r="J69" s="65">
         <f>IF(OR(Resultados!F69="",Resultados!G69=""),"",IF(AND(F69=Resultados!F69,G69=Resultados!G69),2,IF(((F69&gt;G69)=(Resultados!F69&gt;Resultados!G69))*((F69&lt;G69)=(Resultados!F69&lt;Resultados!G69)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="83"/>
+      <c r="A70" s="103"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -18363,7 +18397,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="83"/>
+      <c r="A71" s="103"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -18391,7 +18425,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="83"/>
+      <c r="A72" s="103"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -18419,7 +18453,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="84"/>
+      <c r="A73" s="104"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -18481,7 +18515,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="85" t="s">
+      <c r="A76" s="105" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -18505,13 +18539,13 @@
       <c r="H76" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="J76" s="1">
+      <c r="J76" s="65">
         <f>IF(OR(Resultados!F76="",Resultados!G76=""),"",IF(AND(F76=Resultados!F76,G76=Resultados!G76),2,IF(((F76&gt;G76)=(Resultados!F76&gt;Resultados!G76))*((F76&lt;G76)=(Resultados!F76&lt;Resultados!G76)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="86"/>
+      <c r="A77" s="106"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -18533,13 +18567,13 @@
       <c r="H77" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="J77" s="1">
+      <c r="J77" s="65">
         <f>IF(OR(Resultados!F77="",Resultados!G77=""),"",IF(AND(F77=Resultados!F77,G77=Resultados!G77),2,IF(((F77&gt;G77)=(Resultados!F77&gt;Resultados!G77))*((F77&lt;G77)=(Resultados!F77&lt;Resultados!G77)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="86"/>
+      <c r="A78" s="106"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -18567,7 +18601,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="86"/>
+      <c r="A79" s="106"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -18595,7 +18629,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="86"/>
+      <c r="A80" s="106"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -18623,7 +18657,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="87"/>
+      <c r="A81" s="107"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -18685,7 +18719,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="88" t="s">
+      <c r="A84" s="84" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -18715,7 +18749,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="89"/>
+      <c r="A85" s="85"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -18737,13 +18771,13 @@
       <c r="H85" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="J85" s="1">
+      <c r="J85" s="64">
         <f>IF(OR(Resultados!F85="",Resultados!G85=""),"",IF(AND(F85=Resultados!F85,G85=Resultados!G85),2,IF(((F85&gt;G85)=(Resultados!F85&gt;Resultados!G85))*((F85&lt;G85)=(Resultados!F85&lt;Resultados!G85)),1,0)))</f>
         <v>2</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="89"/>
+      <c r="A86" s="85"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -18771,7 +18805,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="89"/>
+      <c r="A87" s="85"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -18799,7 +18833,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="89"/>
+      <c r="A88" s="85"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -18827,7 +18861,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="90"/>
+      <c r="A89" s="86"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -18889,7 +18923,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="70" t="s">
+      <c r="A92" s="87" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -18913,13 +18947,13 @@
       <c r="H92" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="J92" s="1">
+      <c r="J92" s="65">
         <f>IF(OR(Resultados!F92="",Resultados!G92=""),"",IF(AND(F92=Resultados!F92,G92=Resultados!G92),2,IF(((F92&gt;G92)=(Resultados!F92&gt;Resultados!G92))*((F92&lt;G92)=(Resultados!F92&lt;Resultados!G92)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="71"/>
+      <c r="A93" s="88"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -18941,13 +18975,13 @@
       <c r="H93" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="J93" s="1">
+      <c r="J93" s="65">
         <f>IF(OR(Resultados!F93="",Resultados!G93=""),"",IF(AND(F93=Resultados!F93,G93=Resultados!G93),2,IF(((F93&gt;G93)=(Resultados!F93&gt;Resultados!G93))*((F93&lt;G93)=(Resultados!F93&lt;Resultados!G93)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="71"/>
+      <c r="A94" s="88"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -18975,7 +19009,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="71"/>
+      <c r="A95" s="88"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -19003,7 +19037,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="71"/>
+      <c r="A96" s="88"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -19031,7 +19065,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="72"/>
+      <c r="A97" s="89"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -19060,12 +19094,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A28:A33"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A4:A9"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="A20:A25"/>
     <mergeCell ref="A84:A89"/>
     <mergeCell ref="A92:A97"/>
     <mergeCell ref="A36:A41"/>
@@ -19074,6 +19102,12 @@
     <mergeCell ref="A60:A65"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="A76:A81"/>
+    <mergeCell ref="A28:A33"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:A9"/>
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="A20:A25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19101,26 +19135,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="64" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="66"/>
+      <c r="A1" s="69" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="71"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="67"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="69"/>
+      <c r="A2" s="72"/>
+      <c r="B2" s="73"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="74"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -19153,7 +19187,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="91" t="s">
+      <c r="A4" s="75" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -19179,11 +19213,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="92"/>
+      <c r="A5" s="76"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -19207,7 +19241,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="92"/>
+      <c r="A6" s="76"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -19220,22 +19254,22 @@
       <c r="E6" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="25">
+      <c r="F6" s="150">
         <v>3</v>
       </c>
-      <c r="G6" s="25">
+      <c r="G6" s="150">
         <v>0</v>
       </c>
       <c r="H6" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="J6" s="1" t="str">
+      <c r="J6" s="1">
         <f>IF(OR(Resultados!F6="",Resultados!G6=""),"",IF(AND(F6=Resultados!F6,G6=Resultados!G6),2,IF(((F6&gt;G6)=(Resultados!F6&gt;Resultados!G6))*((F6&lt;G6)=(Resultados!F6&lt;Resultados!G6)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="92"/>
+      <c r="A7" s="76"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -19248,22 +19282,22 @@
       <c r="E7" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="25">
-        <v>1</v>
-      </c>
-      <c r="G7" s="25">
+      <c r="F7" s="150">
+        <v>1</v>
+      </c>
+      <c r="G7" s="150">
         <v>1</v>
       </c>
       <c r="H7" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="J7" s="1" t="str">
+      <c r="J7" s="1">
         <f>IF(OR(Resultados!F7="",Resultados!G7=""),"",IF(AND(F7=Resultados!F7,G7=Resultados!G7),2,IF(((F7&gt;G7)=(Resultados!F7&gt;Resultados!G7))*((F7&lt;G7)=(Resultados!F7&lt;Resultados!G7)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="92"/>
+      <c r="A8" s="76"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -19291,7 +19325,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="93"/>
+      <c r="A9" s="77"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -19353,7 +19387,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="94" t="s">
+      <c r="A12" s="78" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -19379,7 +19413,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="95"/>
+      <c r="A13" s="79"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -19403,7 +19437,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="95"/>
+      <c r="A14" s="79"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -19416,22 +19450,22 @@
       <c r="E14" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F14" s="25">
-        <v>1</v>
-      </c>
-      <c r="G14" s="25">
+      <c r="F14" s="150">
+        <v>1</v>
+      </c>
+      <c r="G14" s="150">
         <v>0</v>
       </c>
       <c r="H14" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="J14" s="1" t="str">
+      <c r="J14" s="65">
         <f>IF(OR(Resultados!F14="",Resultados!G14=""),"",IF(AND(F14=Resultados!F14,G14=Resultados!G14),2,IF(((F14&gt;G14)=(Resultados!F14&gt;Resultados!G14))*((F14&lt;G14)=(Resultados!F14&lt;Resultados!G14)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="95"/>
+      <c r="A15" s="79"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -19444,22 +19478,22 @@
       <c r="E15" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="F15" s="25">
-        <v>2</v>
-      </c>
-      <c r="G15" s="25">
+      <c r="F15" s="150">
+        <v>2</v>
+      </c>
+      <c r="G15" s="150">
         <v>1</v>
       </c>
       <c r="H15" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="J15" s="1" t="str">
+      <c r="J15" s="65">
         <f>IF(OR(Resultados!F15="",Resultados!G15=""),"",IF(AND(F15=Resultados!F15,G15=Resultados!G15),2,IF(((F15&gt;G15)=(Resultados!F15&gt;Resultados!G15))*((F15&lt;G15)=(Resultados!F15&lt;Resultados!G15)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="95"/>
+      <c r="A16" s="79"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -19487,7 +19521,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="96"/>
+      <c r="A17" s="80"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -19549,7 +19583,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="97" t="s">
+      <c r="A20" s="81" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -19575,7 +19609,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="98"/>
+      <c r="A21" s="82"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -19588,22 +19622,22 @@
       <c r="E21" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="F21" s="26">
-        <v>1</v>
-      </c>
-      <c r="G21" s="26">
+      <c r="F21" s="62">
+        <v>1</v>
+      </c>
+      <c r="G21" s="62">
         <v>3</v>
       </c>
       <c r="H21" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="J21" s="1">
+      <c r="J21" s="65">
         <f>IF(OR(Resultados!F21="",Resultados!G21=""),"",IF(AND(F21=Resultados!F21,G21=Resultados!G21),2,IF(((F21&gt;G21)=(Resultados!F21&gt;Resultados!G21))*((F21&lt;G21)=(Resultados!F21&lt;Resultados!G21)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="98"/>
+      <c r="A22" s="82"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -19631,7 +19665,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="98"/>
+      <c r="A23" s="82"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -19659,7 +19693,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="98"/>
+      <c r="A24" s="82"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -19687,7 +19721,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="99"/>
+      <c r="A25" s="83"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -19749,7 +19783,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="100" t="s">
+      <c r="A28" s="66" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -19775,7 +19809,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="101"/>
+      <c r="A29" s="67"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -19803,7 +19837,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="101"/>
+      <c r="A30" s="67"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -19831,7 +19865,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="101"/>
+      <c r="A31" s="67"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -19859,7 +19893,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="101"/>
+      <c r="A32" s="67"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -19883,7 +19917,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="102"/>
+      <c r="A33" s="68"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -19941,7 +19975,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="103" t="s">
+      <c r="A36" s="90" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -19965,13 +19999,13 @@
       <c r="H36" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="J36" s="1">
+      <c r="J36" s="65">
         <f>IF(OR(Resultados!F36="",Resultados!G36=""),"",IF(AND(F36=Resultados!F36,G36=Resultados!G36),2,IF(((F36&gt;G36)=(Resultados!F36&gt;Resultados!G36))*((F36&lt;G36)=(Resultados!F36&lt;Resultados!G36)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="104"/>
+      <c r="A37" s="91"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -19999,7 +20033,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="104"/>
+      <c r="A38" s="91"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -20023,7 +20057,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="104"/>
+      <c r="A39" s="91"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -20047,7 +20081,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="104"/>
+      <c r="A40" s="91"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -20071,7 +20105,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="105"/>
+      <c r="A41" s="92"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -20129,7 +20163,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="73" t="s">
+      <c r="A44" s="93" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -20153,13 +20187,13 @@
       <c r="H44" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="J44" s="1">
+      <c r="J44" s="64">
         <f>IF(OR(Resultados!F44="",Resultados!G44=""),"",IF(AND(F44=Resultados!F44,G44=Resultados!G44),2,IF(((F44&gt;G44)=(Resultados!F44&gt;Resultados!G44))*((F44&lt;G44)=(Resultados!F44&lt;Resultados!G44)),1,0)))</f>
         <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="74"/>
+      <c r="A45" s="94"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -20181,13 +20215,13 @@
       <c r="H45" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="J45" s="1">
+      <c r="J45" s="65">
         <f>IF(OR(Resultados!F45="",Resultados!G45=""),"",IF(AND(F45=Resultados!F45,G45=Resultados!G45),2,IF(((F45&gt;G45)=(Resultados!F45&gt;Resultados!G45))*((F45&lt;G45)=(Resultados!F45&lt;Resultados!G45)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="74"/>
+      <c r="A46" s="94"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -20211,7 +20245,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="74"/>
+      <c r="A47" s="94"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -20235,7 +20269,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="74"/>
+      <c r="A48" s="94"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -20259,7 +20293,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="75"/>
+      <c r="A49" s="95"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -20317,7 +20351,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="76" t="s">
+      <c r="A52" s="96" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -20347,7 +20381,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="77"/>
+      <c r="A53" s="97"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -20375,7 +20409,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="77"/>
+      <c r="A54" s="97"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -20399,7 +20433,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="77"/>
+      <c r="A55" s="97"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -20423,7 +20457,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="77"/>
+      <c r="A56" s="97"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -20447,7 +20481,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="78"/>
+      <c r="A57" s="98"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -20505,7 +20539,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="79" t="s">
+      <c r="A60" s="99" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -20535,7 +20569,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="80"/>
+      <c r="A61" s="100"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -20563,7 +20597,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="80"/>
+      <c r="A62" s="100"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -20587,7 +20621,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="80"/>
+      <c r="A63" s="100"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -20611,7 +20645,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="80"/>
+      <c r="A64" s="100"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -20635,7 +20669,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="81"/>
+      <c r="A65" s="101"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -20693,7 +20727,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="82" t="s">
+      <c r="A68" s="102" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -20717,13 +20751,13 @@
       <c r="H68" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="J68" s="1">
+      <c r="J68" s="64">
         <f>IF(OR(Resultados!F68="",Resultados!G68=""),"",IF(AND(F68=Resultados!F68,G68=Resultados!G68),2,IF(((F68&gt;G68)=(Resultados!F68&gt;Resultados!G68))*((F68&lt;G68)=(Resultados!F68&lt;Resultados!G68)),1,0)))</f>
         <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="83"/>
+      <c r="A69" s="103"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -20745,13 +20779,13 @@
       <c r="H69" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="J69" s="1">
+      <c r="J69" s="65">
         <f>IF(OR(Resultados!F69="",Resultados!G69=""),"",IF(AND(F69=Resultados!F69,G69=Resultados!G69),2,IF(((F69&gt;G69)=(Resultados!F69&gt;Resultados!G69))*((F69&lt;G69)=(Resultados!F69&lt;Resultados!G69)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="83"/>
+      <c r="A70" s="103"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -20775,7 +20809,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="83"/>
+      <c r="A71" s="103"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -20799,7 +20833,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="83"/>
+      <c r="A72" s="103"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -20823,7 +20857,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="84"/>
+      <c r="A73" s="104"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -20881,7 +20915,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="85" t="s">
+      <c r="A76" s="105" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -20905,13 +20939,13 @@
       <c r="H76" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="J76" s="1">
+      <c r="J76" s="65">
         <f>IF(OR(Resultados!F76="",Resultados!G76=""),"",IF(AND(F76=Resultados!F76,G76=Resultados!G76),2,IF(((F76&gt;G76)=(Resultados!F76&gt;Resultados!G76))*((F76&lt;G76)=(Resultados!F76&lt;Resultados!G76)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="86"/>
+      <c r="A77" s="106"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -20933,13 +20967,13 @@
       <c r="H77" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="J77" s="1">
+      <c r="J77" s="65">
         <f>IF(OR(Resultados!F77="",Resultados!G77=""),"",IF(AND(F77=Resultados!F77,G77=Resultados!G77),2,IF(((F77&gt;G77)=(Resultados!F77&gt;Resultados!G77))*((F77&lt;G77)=(Resultados!F77&lt;Resultados!G77)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="86"/>
+      <c r="A78" s="106"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -20963,7 +20997,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="86"/>
+      <c r="A79" s="106"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -20987,7 +21021,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="86"/>
+      <c r="A80" s="106"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -21011,7 +21045,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="87"/>
+      <c r="A81" s="107"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -21069,7 +21103,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="88" t="s">
+      <c r="A84" s="84" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -21099,7 +21133,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="89"/>
+      <c r="A85" s="85"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -21121,13 +21155,13 @@
       <c r="H85" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="J85" s="1">
+      <c r="J85" s="65">
         <f>IF(OR(Resultados!F85="",Resultados!G85=""),"",IF(AND(F85=Resultados!F85,G85=Resultados!G85),2,IF(((F85&gt;G85)=(Resultados!F85&gt;Resultados!G85))*((F85&lt;G85)=(Resultados!F85&lt;Resultados!G85)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="89"/>
+      <c r="A86" s="85"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -21151,7 +21185,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="89"/>
+      <c r="A87" s="85"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -21175,7 +21209,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="89"/>
+      <c r="A88" s="85"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -21199,7 +21233,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="90"/>
+      <c r="A89" s="86"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -21257,7 +21291,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="70" t="s">
+      <c r="A92" s="87" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -21281,13 +21315,13 @@
       <c r="H92" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="J92" s="1">
+      <c r="J92" s="65">
         <f>IF(OR(Resultados!F92="",Resultados!G92=""),"",IF(AND(F92=Resultados!F92,G92=Resultados!G92),2,IF(((F92&gt;G92)=(Resultados!F92&gt;Resultados!G92))*((F92&lt;G92)=(Resultados!F92&lt;Resultados!G92)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="71"/>
+      <c r="A93" s="88"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -21309,13 +21343,13 @@
       <c r="H93" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="J93" s="1">
+      <c r="J93" s="64">
         <f>IF(OR(Resultados!F93="",Resultados!G93=""),"",IF(AND(F93=Resultados!F93,G93=Resultados!G93),2,IF(((F93&gt;G93)=(Resultados!F93&gt;Resultados!G93))*((F93&lt;G93)=(Resultados!F93&lt;Resultados!G93)),1,0)))</f>
         <v>2</v>
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="71"/>
+      <c r="A94" s="88"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -21339,7 +21373,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="71"/>
+      <c r="A95" s="88"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -21363,7 +21397,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="71"/>
+      <c r="A96" s="88"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -21387,7 +21421,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="72"/>
+      <c r="A97" s="89"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -21412,12 +21446,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A28:A33"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A4:A9"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="A20:A25"/>
     <mergeCell ref="A84:A89"/>
     <mergeCell ref="A92:A97"/>
     <mergeCell ref="A36:A41"/>
@@ -21426,6 +21454,12 @@
     <mergeCell ref="A60:A65"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="A76:A81"/>
+    <mergeCell ref="A28:A33"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:A9"/>
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="A20:A25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21453,26 +21487,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="64" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="66"/>
+      <c r="A1" s="69" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="71"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="67"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="69"/>
+      <c r="A2" s="72"/>
+      <c r="B2" s="73"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="74"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -21505,7 +21539,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="91" t="s">
+      <c r="A4" s="75" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -21531,11 +21565,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="92"/>
+      <c r="A5" s="76"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -21559,7 +21593,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="92"/>
+      <c r="A6" s="76"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -21581,13 +21615,13 @@
       <c r="H6" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="J6" s="1" t="str">
+      <c r="J6" s="1">
         <f>IF(OR(Resultados!F6="",Resultados!G6=""),"",IF(AND(F6=Resultados!F6,G6=Resultados!G6),2,IF(((F6&gt;G6)=(Resultados!F6&gt;Resultados!G6))*((F6&lt;G6)=(Resultados!F6&lt;Resultados!G6)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="92"/>
+      <c r="A7" s="76"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -21609,13 +21643,13 @@
       <c r="H7" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="J7" s="1" t="str">
+      <c r="J7" s="1">
         <f>IF(OR(Resultados!F7="",Resultados!G7=""),"",IF(AND(F7=Resultados!F7,G7=Resultados!G7),2,IF(((F7&gt;G7)=(Resultados!F7&gt;Resultados!G7))*((F7&lt;G7)=(Resultados!F7&lt;Resultados!G7)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="92"/>
+      <c r="A8" s="76"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -21643,7 +21677,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="93"/>
+      <c r="A9" s="77"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -21705,7 +21739,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="94" t="s">
+      <c r="A12" s="78" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -21731,7 +21765,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="95"/>
+      <c r="A13" s="79"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -21755,7 +21789,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="95"/>
+      <c r="A14" s="79"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -21777,13 +21811,13 @@
       <c r="H14" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="J14" s="1" t="str">
+      <c r="J14" s="1">
         <f>IF(OR(Resultados!F14="",Resultados!G14=""),"",IF(AND(F14=Resultados!F14,G14=Resultados!G14),2,IF(((F14&gt;G14)=(Resultados!F14&gt;Resultados!G14))*((F14&lt;G14)=(Resultados!F14&lt;Resultados!G14)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="95"/>
+      <c r="A15" s="79"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -21805,13 +21839,13 @@
       <c r="H15" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="J15" s="1" t="str">
+      <c r="J15" s="1">
         <f>IF(OR(Resultados!F15="",Resultados!G15=""),"",IF(AND(F15=Resultados!F15,G15=Resultados!G15),2,IF(((F15&gt;G15)=(Resultados!F15&gt;Resultados!G15))*((F15&lt;G15)=(Resultados!F15&lt;Resultados!G15)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="95"/>
+      <c r="A16" s="79"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -21839,7 +21873,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="96"/>
+      <c r="A17" s="80"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -21901,7 +21935,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="97" t="s">
+      <c r="A20" s="81" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -21927,7 +21961,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="98"/>
+      <c r="A21" s="82"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -21949,13 +21983,13 @@
       <c r="H21" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="J21" s="1">
+      <c r="J21" s="64">
         <f>IF(OR(Resultados!F21="",Resultados!G21=""),"",IF(AND(F21=Resultados!F21,G21=Resultados!G21),2,IF(((F21&gt;G21)=(Resultados!F21&gt;Resultados!G21))*((F21&lt;G21)=(Resultados!F21&lt;Resultados!G21)),1,0)))</f>
         <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="98"/>
+      <c r="A22" s="82"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -21983,7 +22017,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="98"/>
+      <c r="A23" s="82"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -22011,7 +22045,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="98"/>
+      <c r="A24" s="82"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -22039,7 +22073,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="99"/>
+      <c r="A25" s="83"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -22101,7 +22135,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="100" t="s">
+      <c r="A28" s="66" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -22127,7 +22161,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="101"/>
+      <c r="A29" s="67"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -22155,7 +22189,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="101"/>
+      <c r="A30" s="67"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -22183,7 +22217,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="101"/>
+      <c r="A31" s="67"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -22211,7 +22245,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="101"/>
+      <c r="A32" s="67"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -22239,7 +22273,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="102"/>
+      <c r="A33" s="68"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -22301,7 +22335,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="103" t="s">
+      <c r="A36" s="90" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -22325,13 +22359,13 @@
       <c r="H36" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="J36" s="1">
+      <c r="J36" s="65">
         <f>IF(OR(Resultados!F36="",Resultados!G36=""),"",IF(AND(F36=Resultados!F36,G36=Resultados!G36),2,IF(((F36&gt;G36)=(Resultados!F36&gt;Resultados!G36))*((F36&lt;G36)=(Resultados!F36&lt;Resultados!G36)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="104"/>
+      <c r="A37" s="91"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -22359,7 +22393,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="104"/>
+      <c r="A38" s="91"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -22387,7 +22421,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="104"/>
+      <c r="A39" s="91"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -22415,7 +22449,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="104"/>
+      <c r="A40" s="91"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -22443,7 +22477,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="105"/>
+      <c r="A41" s="92"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -22505,7 +22539,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="73" t="s">
+      <c r="A44" s="93" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -22529,13 +22563,13 @@
       <c r="H44" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="J44" s="1">
+      <c r="J44" s="65">
         <f>IF(OR(Resultados!F44="",Resultados!G44=""),"",IF(AND(F44=Resultados!F44,G44=Resultados!G44),2,IF(((F44&gt;G44)=(Resultados!F44&gt;Resultados!G44))*((F44&lt;G44)=(Resultados!F44&lt;Resultados!G44)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="74"/>
+      <c r="A45" s="94"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -22563,7 +22597,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="74"/>
+      <c r="A46" s="94"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -22591,7 +22625,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="74"/>
+      <c r="A47" s="94"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -22619,7 +22653,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="74"/>
+      <c r="A48" s="94"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -22647,7 +22681,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="75"/>
+      <c r="A49" s="95"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -22709,7 +22743,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="76" t="s">
+      <c r="A52" s="96" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -22739,7 +22773,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="77"/>
+      <c r="A53" s="97"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -22767,7 +22801,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="77"/>
+      <c r="A54" s="97"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -22795,7 +22829,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="77"/>
+      <c r="A55" s="97"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -22823,7 +22857,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="77"/>
+      <c r="A56" s="97"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -22851,7 +22885,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="78"/>
+      <c r="A57" s="98"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -22913,7 +22947,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="79" t="s">
+      <c r="A60" s="99" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -22943,7 +22977,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="80"/>
+      <c r="A61" s="100"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -22971,7 +23005,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="80"/>
+      <c r="A62" s="100"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -22999,7 +23033,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="80"/>
+      <c r="A63" s="100"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -23027,7 +23061,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="80"/>
+      <c r="A64" s="100"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -23055,7 +23089,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="81"/>
+      <c r="A65" s="101"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -23117,7 +23151,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="82" t="s">
+      <c r="A68" s="102" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -23141,13 +23175,13 @@
       <c r="H68" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="J68" s="1">
+      <c r="J68" s="65">
         <f>IF(OR(Resultados!F68="",Resultados!G68=""),"",IF(AND(F68=Resultados!F68,G68=Resultados!G68),2,IF(((F68&gt;G68)=(Resultados!F68&gt;Resultados!G68))*((F68&lt;G68)=(Resultados!F68&lt;Resultados!G68)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="83"/>
+      <c r="A69" s="103"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -23175,7 +23209,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="83"/>
+      <c r="A70" s="103"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -23203,7 +23237,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="83"/>
+      <c r="A71" s="103"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -23231,7 +23265,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="83"/>
+      <c r="A72" s="103"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -23259,7 +23293,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="84"/>
+      <c r="A73" s="104"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -23321,7 +23355,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="85" t="s">
+      <c r="A76" s="105" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -23345,13 +23379,13 @@
       <c r="H76" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="J76" s="1">
+      <c r="J76" s="65">
         <f>IF(OR(Resultados!F76="",Resultados!G76=""),"",IF(AND(F76=Resultados!F76,G76=Resultados!G76),2,IF(((F76&gt;G76)=(Resultados!F76&gt;Resultados!G76))*((F76&lt;G76)=(Resultados!F76&lt;Resultados!G76)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="86"/>
+      <c r="A77" s="106"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -23379,7 +23413,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="86"/>
+      <c r="A78" s="106"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -23407,7 +23441,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="86"/>
+      <c r="A79" s="106"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -23435,7 +23469,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="86"/>
+      <c r="A80" s="106"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -23463,7 +23497,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="87"/>
+      <c r="A81" s="107"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -23525,7 +23559,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="88" t="s">
+      <c r="A84" s="84" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -23555,7 +23589,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="89"/>
+      <c r="A85" s="85"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -23577,13 +23611,13 @@
       <c r="H85" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="J85" s="1">
+      <c r="J85" s="65">
         <f>IF(OR(Resultados!F85="",Resultados!G85=""),"",IF(AND(F85=Resultados!F85,G85=Resultados!G85),2,IF(((F85&gt;G85)=(Resultados!F85&gt;Resultados!G85))*((F85&lt;G85)=(Resultados!F85&lt;Resultados!G85)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="89"/>
+      <c r="A86" s="85"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -23611,7 +23645,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="89"/>
+      <c r="A87" s="85"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -23639,7 +23673,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="89"/>
+      <c r="A88" s="85"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -23667,7 +23701,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="90"/>
+      <c r="A89" s="86"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -23729,7 +23763,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="70" t="s">
+      <c r="A92" s="87" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -23753,13 +23787,13 @@
       <c r="H92" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="J92" s="1">
+      <c r="J92" s="65">
         <f>IF(OR(Resultados!F92="",Resultados!G92=""),"",IF(AND(F92=Resultados!F92,G92=Resultados!G92),2,IF(((F92&gt;G92)=(Resultados!F92&gt;Resultados!G92))*((F92&lt;G92)=(Resultados!F92&lt;Resultados!G92)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="71"/>
+      <c r="A93" s="88"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -23781,13 +23815,13 @@
       <c r="H93" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="J93" s="1">
+      <c r="J93" s="65">
         <f>IF(OR(Resultados!F93="",Resultados!G93=""),"",IF(AND(F93=Resultados!F93,G93=Resultados!G93),2,IF(((F93&gt;G93)=(Resultados!F93&gt;Resultados!G93))*((F93&lt;G93)=(Resultados!F93&lt;Resultados!G93)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="71"/>
+      <c r="A94" s="88"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -23815,7 +23849,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="71"/>
+      <c r="A95" s="88"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -23843,7 +23877,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="71"/>
+      <c r="A96" s="88"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -23871,7 +23905,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="72"/>
+      <c r="A97" s="89"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -23900,12 +23934,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A28:A33"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A4:A9"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="A20:A25"/>
     <mergeCell ref="A84:A89"/>
     <mergeCell ref="A92:A97"/>
     <mergeCell ref="A36:A41"/>
@@ -23914,6 +23942,12 @@
     <mergeCell ref="A60:A65"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="A76:A81"/>
+    <mergeCell ref="A28:A33"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:A9"/>
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="A20:A25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -23941,26 +23975,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="64" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="66"/>
+      <c r="A1" s="69" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="71"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="67"/>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="69"/>
+      <c r="A2" s="72"/>
+      <c r="B2" s="73"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="74"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -23993,7 +24027,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="91" t="s">
+      <c r="A4" s="75" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -24019,11 +24053,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="92"/>
+      <c r="A5" s="76"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -24047,7 +24081,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="92"/>
+      <c r="A6" s="76"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -24069,13 +24103,13 @@
       <c r="H6" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="J6" s="1" t="str">
+      <c r="J6" s="64">
         <f>IF(OR(Resultados!F6="",Resultados!G6=""),"",IF(AND(F6=Resultados!F6,G6=Resultados!G6),2,IF(((F6&gt;G6)=(Resultados!F6&gt;Resultados!G6))*((F6&lt;G6)=(Resultados!F6&lt;Resultados!G6)),1,0)))</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="92"/>
+      <c r="A7" s="76"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -24097,13 +24131,13 @@
       <c r="H7" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="J7" s="1" t="str">
+      <c r="J7" s="65">
         <f>IF(OR(Resultados!F7="",Resultados!G7=""),"",IF(AND(F7=Resultados!F7,G7=Resultados!G7),2,IF(((F7&gt;G7)=(Resultados!F7&gt;Resultados!G7))*((F7&lt;G7)=(Resultados!F7&lt;Resultados!G7)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="92"/>
+      <c r="A8" s="76"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -24131,7 +24165,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="93"/>
+      <c r="A9" s="77"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -24193,7 +24227,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="94" t="s">
+      <c r="A12" s="78" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -24219,7 +24253,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="95"/>
+      <c r="A13" s="79"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -24243,7 +24277,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="95"/>
+      <c r="A14" s="79"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -24265,13 +24299,13 @@
       <c r="H14" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="J14" s="1" t="str">
+      <c r="J14" s="65">
         <f>IF(OR(Resultados!F14="",Resultados!G14=""),"",IF(AND(F14=Resultados!F14,G14=Resultados!G14),2,IF(((F14&gt;G14)=(Resultados!F14&gt;Resultados!G14))*((F14&lt;G14)=(Resultados!F14&lt;Resultados!G14)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="95"/>
+      <c r="A15" s="79"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -24293,13 +24327,13 @@
       <c r="H15" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="J15" s="1" t="str">
+      <c r="J15" s="1">
         <f>IF(OR(Resultados!F15="",Resultados!G15=""),"",IF(AND(F15=Resultados!F15,G15=Resultados!G15),2,IF(((F15&gt;G15)=(Resultados!F15&gt;Resultados!G15))*((F15&lt;G15)=(Resultados!F15&lt;Resultados!G15)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="95"/>
+      <c r="A16" s="79"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -24327,7 +24361,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="96"/>
+      <c r="A17" s="80"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -24389,7 +24423,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="97" t="s">
+      <c r="A20" s="81" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -24415,7 +24449,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="98"/>
+      <c r="A21" s="82"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -24437,13 +24471,13 @@
       <c r="H21" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="J21" s="1">
+      <c r="J21" s="65">
         <f>IF(OR(Resultados!F21="",Resultados!G21=""),"",IF(AND(F21=Resultados!F21,G21=Resultados!G21),2,IF(((F21&gt;G21)=(Resultados!F21&gt;Resultados!G21))*((F21&lt;G21)=(Resultados!F21&lt;Resultados!G21)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="98"/>
+      <c r="A22" s="82"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -24471,7 +24505,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="98"/>
+      <c r="A23" s="82"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -24499,7 +24533,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="98"/>
+      <c r="A24" s="82"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -24527,7 +24561,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="99"/>
+      <c r="A25" s="83"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -24589,7 +24623,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="100" t="s">
+      <c r="A28" s="66" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -24615,7 +24649,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="101"/>
+      <c r="A29" s="67"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -24637,13 +24671,13 @@
       <c r="H29" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="J29" s="1">
+      <c r="J29" s="65">
         <f>IF(OR(Resultados!F29="",Resultados!G29=""),"",IF(AND(F29=Resultados!F29,G29=Resultados!G29),2,IF(((F29&gt;G29)=(Resultados!F29&gt;Resultados!G29))*((F29&lt;G29)=(Resultados!F29&lt;Resultados!G29)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="101"/>
+      <c r="A30" s="67"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -24671,7 +24705,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="101"/>
+      <c r="A31" s="67"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -24699,7 +24733,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="101"/>
+      <c r="A32" s="67"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -24727,7 +24761,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="102"/>
+      <c r="A33" s="68"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -24789,7 +24823,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="103" t="s">
+      <c r="A36" s="90" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -24813,13 +24847,13 @@
       <c r="H36" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="J36" s="1">
+      <c r="J36" s="65">
         <f>IF(OR(Resultados!F36="",Resultados!G36=""),"",IF(AND(F36=Resultados!F36,G36=Resultados!G36),2,IF(((F36&gt;G36)=(Resultados!F36&gt;Resultados!G36))*((F36&lt;G36)=(Resultados!F36&lt;Resultados!G36)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="104"/>
+      <c r="A37" s="91"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -24847,7 +24881,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="104"/>
+      <c r="A38" s="91"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -24875,7 +24909,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="104"/>
+      <c r="A39" s="91"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -24903,7 +24937,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="104"/>
+      <c r="A40" s="91"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -24931,7 +24965,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="105"/>
+      <c r="A41" s="92"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -24993,7 +25027,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="73" t="s">
+      <c r="A44" s="93" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -25023,7 +25057,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="74"/>
+      <c r="A45" s="94"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -25045,13 +25079,13 @@
       <c r="H45" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="J45" s="1">
+      <c r="J45" s="65">
         <f>IF(OR(Resultados!F45="",Resultados!G45=""),"",IF(AND(F45=Resultados!F45,G45=Resultados!G45),2,IF(((F45&gt;G45)=(Resultados!F45&gt;Resultados!G45))*((F45&lt;G45)=(Resultados!F45&lt;Resultados!G45)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="74"/>
+      <c r="A46" s="94"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -25079,7 +25113,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="74"/>
+      <c r="A47" s="94"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -25107,7 +25141,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="74"/>
+      <c r="A48" s="94"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -25135,7 +25169,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="75"/>
+      <c r="A49" s="95"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -25197,7 +25231,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="76" t="s">
+      <c r="A52" s="96" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -25221,13 +25255,13 @@
       <c r="H52" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="J52" s="1">
+      <c r="J52" s="64">
         <f>IF(OR(Resultados!F52="",Resultados!G52=""),"",IF(AND(F52=Resultados!F52,G52=Resultados!G52),2,IF(((F52&gt;G52)=(Resultados!F52&gt;Resultados!G52))*((F52&lt;G52)=(Resultados!F52&lt;Resultados!G52)),1,0)))</f>
         <v>2</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="77"/>
+      <c r="A53" s="97"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -25255,7 +25289,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="77"/>
+      <c r="A54" s="97"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -25283,7 +25317,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="77"/>
+      <c r="A55" s="97"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -25311,7 +25345,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="77"/>
+      <c r="A56" s="97"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -25339,7 +25373,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="78"/>
+      <c r="A57" s="98"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -25401,7 +25435,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="79" t="s">
+      <c r="A60" s="99" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -25431,7 +25465,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="80"/>
+      <c r="A61" s="100"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -25459,7 +25493,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="80"/>
+      <c r="A62" s="100"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -25487,7 +25521,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="80"/>
+      <c r="A63" s="100"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -25515,7 +25549,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="80"/>
+      <c r="A64" s="100"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -25543,7 +25577,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="81"/>
+      <c r="A65" s="101"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -25605,7 +25639,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="82" t="s">
+      <c r="A68" s="102" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -25629,13 +25663,13 @@
       <c r="H68" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="J68" s="1">
+      <c r="J68" s="65">
         <f>IF(OR(Resultados!F68="",Resultados!G68=""),"",IF(AND(F68=Resultados!F68,G68=Resultados!G68),2,IF(((F68&gt;G68)=(Resultados!F68&gt;Resultados!G68))*((F68&lt;G68)=(Resultados!F68&lt;Resultados!G68)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="83"/>
+      <c r="A69" s="103"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -25657,13 +25691,13 @@
       <c r="H69" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="J69" s="1">
+      <c r="J69" s="65">
         <f>IF(OR(Resultados!F69="",Resultados!G69=""),"",IF(AND(F69=Resultados!F69,G69=Resultados!G69),2,IF(((F69&gt;G69)=(Resultados!F69&gt;Resultados!G69))*((F69&lt;G69)=(Resultados!F69&lt;Resultados!G69)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="83"/>
+      <c r="A70" s="103"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -25691,7 +25725,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="83"/>
+      <c r="A71" s="103"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -25719,7 +25753,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="83"/>
+      <c r="A72" s="103"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -25747,7 +25781,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="84"/>
+      <c r="A73" s="104"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -25809,7 +25843,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="85" t="s">
+      <c r="A76" s="105" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -25833,13 +25867,13 @@
       <c r="H76" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="J76" s="1">
+      <c r="J76" s="65">
         <f>IF(OR(Resultados!F76="",Resultados!G76=""),"",IF(AND(F76=Resultados!F76,G76=Resultados!G76),2,IF(((F76&gt;G76)=(Resultados!F76&gt;Resultados!G76))*((F76&lt;G76)=(Resultados!F76&lt;Resultados!G76)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="86"/>
+      <c r="A77" s="106"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -25861,13 +25895,13 @@
       <c r="H77" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="J77" s="1">
+      <c r="J77" s="65">
         <f>IF(OR(Resultados!F77="",Resultados!G77=""),"",IF(AND(F77=Resultados!F77,G77=Resultados!G77),2,IF(((F77&gt;G77)=(Resultados!F77&gt;Resultados!G77))*((F77&lt;G77)=(Resultados!F77&lt;Resultados!G77)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="86"/>
+      <c r="A78" s="106"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -25895,7 +25929,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="86"/>
+      <c r="A79" s="106"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -25923,7 +25957,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="86"/>
+      <c r="A80" s="106"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -25951,7 +25985,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="87"/>
+      <c r="A81" s="107"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -26013,7 +26047,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="88" t="s">
+      <c r="A84" s="84" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -26043,7 +26077,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="89"/>
+      <c r="A85" s="85"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -26065,13 +26099,13 @@
       <c r="H85" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="J85" s="1">
+      <c r="J85" s="64">
         <f>IF(OR(Resultados!F85="",Resultados!G85=""),"",IF(AND(F85=Resultados!F85,G85=Resultados!G85),2,IF(((F85&gt;G85)=(Resultados!F85&gt;Resultados!G85))*((F85&lt;G85)=(Resultados!F85&lt;Resultados!G85)),1,0)))</f>
         <v>2</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="89"/>
+      <c r="A86" s="85"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -26099,7 +26133,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="89"/>
+      <c r="A87" s="85"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -26127,7 +26161,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="89"/>
+      <c r="A88" s="85"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -26155,7 +26189,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="90"/>
+      <c r="A89" s="86"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -26217,7 +26251,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="70" t="s">
+      <c r="A92" s="87" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -26241,13 +26275,13 @@
       <c r="H92" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="J92" s="1">
+      <c r="J92" s="65">
         <f>IF(OR(Resultados!F92="",Resultados!G92=""),"",IF(AND(F92=Resultados!F92,G92=Resultados!G92),2,IF(((F92&gt;G92)=(Resultados!F92&gt;Resultados!G92))*((F92&lt;G92)=(Resultados!F92&lt;Resultados!G92)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="71"/>
+      <c r="A93" s="88"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -26275,7 +26309,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="71"/>
+      <c r="A94" s="88"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -26303,7 +26337,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="71"/>
+      <c r="A95" s="88"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -26331,7 +26365,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="71"/>
+      <c r="A96" s="88"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -26359,7 +26393,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="72"/>
+      <c r="A97" s="89"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -26388,12 +26422,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A28:A33"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A4:A9"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="A20:A25"/>
     <mergeCell ref="A84:A89"/>
     <mergeCell ref="A92:A97"/>
     <mergeCell ref="A36:A41"/>
@@ -26402,6 +26430,12 @@
     <mergeCell ref="A60:A65"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="A76:A81"/>
+    <mergeCell ref="A28:A33"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:A9"/>
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="A20:A25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -26611,20 +26645,20 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="7461ab22-4e70-4395-beb5-078d6ab567bf" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="7461ab22-4e70-4395-beb5-078d6ab567bf" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -26646,14 +26680,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5511D132-9333-423C-BAEC-48101CE7245F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7DE79FC7-1424-4D12-B735-3F81ACD8E888}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
@@ -26667,4 +26693,12 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5511D132-9333-423C-BAEC-48101CE7245F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/Quiniela.xlsx
+++ b/data/Quiniela.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cindy\Desktop\QuinielaMundial\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94C55DEB-12F1-4435-B2D5-079D08705703}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B7048CD-B123-4B96-8F9B-1B08E4C3196B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{9503E40F-C0E1-49CE-B4EA-3C401754995E}"/>
   </bookViews>
@@ -1262,15 +1262,7 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1298,54 +1290,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1355,18 +1299,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="17" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1427,6 +1359,78 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1589,10 +1593,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1951,26 +1951,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="69" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="71"/>
+      <c r="A1" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="69"/>
     </row>
     <row r="2" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="72"/>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="74"/>
+      <c r="A2" s="70"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="72"/>
     </row>
     <row r="3" spans="1:8" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -1997,7 +1997,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="75" t="s">
+      <c r="A4" s="94" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -2023,7 +2023,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="76"/>
+      <c r="A5" s="95"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -2047,7 +2047,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="76"/>
+      <c r="A6" s="95"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -2060,10 +2060,10 @@
       <c r="E6" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="150">
-        <v>1</v>
-      </c>
-      <c r="G6" s="150">
+      <c r="F6" s="66">
+        <v>1</v>
+      </c>
+      <c r="G6" s="66">
         <v>1</v>
       </c>
       <c r="H6" s="61" t="s">
@@ -2071,7 +2071,7 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="76"/>
+      <c r="A7" s="95"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -2084,10 +2084,10 @@
       <c r="E7" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="150">
-        <v>1</v>
-      </c>
-      <c r="G7" s="150">
+      <c r="F7" s="66">
+        <v>1</v>
+      </c>
+      <c r="G7" s="66">
         <v>0</v>
       </c>
       <c r="H7" s="20" t="s">
@@ -2095,7 +2095,7 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="76"/>
+      <c r="A8" s="95"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -2115,7 +2115,7 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="77"/>
+      <c r="A9" s="96"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -2169,7 +2169,7 @@
       </c>
     </row>
     <row r="12" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="78" t="s">
+      <c r="A12" s="97" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -2195,7 +2195,7 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="79"/>
+      <c r="A13" s="98"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -2219,7 +2219,7 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="79"/>
+      <c r="A14" s="98"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -2232,10 +2232,10 @@
       <c r="E14" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="F14" s="150">
+      <c r="F14" s="66">
         <v>4</v>
       </c>
-      <c r="G14" s="150">
+      <c r="G14" s="66">
         <v>1</v>
       </c>
       <c r="H14" s="21" t="s">
@@ -2243,7 +2243,7 @@
       </c>
     </row>
     <row r="15" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="79"/>
+      <c r="A15" s="98"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -2256,10 +2256,10 @@
       <c r="E15" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="F15" s="150">
+      <c r="F15" s="66">
         <v>6</v>
       </c>
-      <c r="G15" s="150">
+      <c r="G15" s="66">
         <v>0</v>
       </c>
       <c r="H15" s="21" t="s">
@@ -2267,7 +2267,7 @@
       </c>
     </row>
     <row r="16" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="79"/>
+      <c r="A16" s="98"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -2287,7 +2287,7 @@
       </c>
     </row>
     <row r="17" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="80"/>
+      <c r="A17" s="99"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -2341,7 +2341,7 @@
       </c>
     </row>
     <row r="20" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="81" t="s">
+      <c r="A20" s="100" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -2367,7 +2367,7 @@
       </c>
     </row>
     <row r="21" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="82"/>
+      <c r="A21" s="101"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -2391,7 +2391,7 @@
       </c>
     </row>
     <row r="22" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="82"/>
+      <c r="A22" s="101"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -2404,14 +2404,18 @@
       <c r="E22" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="F22" s="25"/>
-      <c r="G22" s="25"/>
+      <c r="F22" s="25">
+        <v>0</v>
+      </c>
+      <c r="G22" s="25">
+        <v>1</v>
+      </c>
       <c r="H22" s="21" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="82"/>
+      <c r="A23" s="101"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -2431,7 +2435,7 @@
       </c>
     </row>
     <row r="24" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="82"/>
+      <c r="A24" s="101"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -2451,7 +2455,7 @@
       </c>
     </row>
     <row r="25" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="83"/>
+      <c r="A25" s="102"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -2505,7 +2509,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="66" t="s">
+      <c r="A28" s="103" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -2531,7 +2535,7 @@
       </c>
     </row>
     <row r="29" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="67"/>
+      <c r="A29" s="104"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -2555,7 +2559,7 @@
       </c>
     </row>
     <row r="30" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="67"/>
+      <c r="A30" s="104"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -2565,17 +2569,21 @@
       <c r="D30" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E30" s="10" t="s">
+      <c r="E30" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="F30" s="25"/>
-      <c r="G30" s="25"/>
+      <c r="F30" s="66">
+        <v>2</v>
+      </c>
+      <c r="G30" s="66">
+        <v>0</v>
+      </c>
       <c r="H30" s="21" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="67"/>
+      <c r="A31" s="104"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -2595,7 +2603,7 @@
       </c>
     </row>
     <row r="32" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="67"/>
+      <c r="A32" s="104"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -2615,7 +2623,7 @@
       </c>
     </row>
     <row r="33" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="68"/>
+      <c r="A33" s="105"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -2669,7 +2677,7 @@
       </c>
     </row>
     <row r="36" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="90" t="s">
+      <c r="A36" s="106" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -2695,7 +2703,7 @@
       </c>
     </row>
     <row r="37" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="91"/>
+      <c r="A37" s="107"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -2719,7 +2727,7 @@
       </c>
     </row>
     <row r="38" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="91"/>
+      <c r="A38" s="107"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -2739,7 +2747,7 @@
       </c>
     </row>
     <row r="39" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="91"/>
+      <c r="A39" s="107"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -2759,7 +2767,7 @@
       </c>
     </row>
     <row r="40" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="91"/>
+      <c r="A40" s="107"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -2779,7 +2787,7 @@
       </c>
     </row>
     <row r="41" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="92"/>
+      <c r="A41" s="108"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -2833,7 +2841,7 @@
       </c>
     </row>
     <row r="44" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="93" t="s">
+      <c r="A44" s="76" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -2859,7 +2867,7 @@
       </c>
     </row>
     <row r="45" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="94"/>
+      <c r="A45" s="77"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -2883,7 +2891,7 @@
       </c>
     </row>
     <row r="46" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="94"/>
+      <c r="A46" s="77"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -2903,7 +2911,7 @@
       </c>
     </row>
     <row r="47" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="94"/>
+      <c r="A47" s="77"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -2923,7 +2931,7 @@
       </c>
     </row>
     <row r="48" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="94"/>
+      <c r="A48" s="77"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -2943,7 +2951,7 @@
       </c>
     </row>
     <row r="49" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="95"/>
+      <c r="A49" s="78"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -2997,7 +3005,7 @@
       </c>
     </row>
     <row r="52" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="96" t="s">
+      <c r="A52" s="79" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -3023,7 +3031,7 @@
       </c>
     </row>
     <row r="53" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="97"/>
+      <c r="A53" s="80"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -3047,7 +3055,7 @@
       </c>
     </row>
     <row r="54" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="97"/>
+      <c r="A54" s="80"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -3067,7 +3075,7 @@
       </c>
     </row>
     <row r="55" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="97"/>
+      <c r="A55" s="80"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -3087,7 +3095,7 @@
       </c>
     </row>
     <row r="56" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="97"/>
+      <c r="A56" s="80"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -3107,7 +3115,7 @@
       </c>
     </row>
     <row r="57" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="98"/>
+      <c r="A57" s="81"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -3161,7 +3169,7 @@
       </c>
     </row>
     <row r="60" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="99" t="s">
+      <c r="A60" s="82" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -3187,7 +3195,7 @@
       </c>
     </row>
     <row r="61" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="100"/>
+      <c r="A61" s="83"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -3211,7 +3219,7 @@
       </c>
     </row>
     <row r="62" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="100"/>
+      <c r="A62" s="83"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -3231,7 +3239,7 @@
       </c>
     </row>
     <row r="63" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="100"/>
+      <c r="A63" s="83"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -3251,7 +3259,7 @@
       </c>
     </row>
     <row r="64" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="100"/>
+      <c r="A64" s="83"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -3271,7 +3279,7 @@
       </c>
     </row>
     <row r="65" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="101"/>
+      <c r="A65" s="84"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -3325,7 +3333,7 @@
       </c>
     </row>
     <row r="68" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="102" t="s">
+      <c r="A68" s="85" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -3351,7 +3359,7 @@
       </c>
     </row>
     <row r="69" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="103"/>
+      <c r="A69" s="86"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -3375,7 +3383,7 @@
       </c>
     </row>
     <row r="70" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="103"/>
+      <c r="A70" s="86"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -3395,7 +3403,7 @@
       </c>
     </row>
     <row r="71" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="103"/>
+      <c r="A71" s="86"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -3415,7 +3423,7 @@
       </c>
     </row>
     <row r="72" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="103"/>
+      <c r="A72" s="86"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -3435,7 +3443,7 @@
       </c>
     </row>
     <row r="73" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="104"/>
+      <c r="A73" s="87"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -3489,7 +3497,7 @@
       </c>
     </row>
     <row r="76" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="105" t="s">
+      <c r="A76" s="88" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -3515,7 +3523,7 @@
       </c>
     </row>
     <row r="77" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="106"/>
+      <c r="A77" s="89"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -3539,7 +3547,7 @@
       </c>
     </row>
     <row r="78" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="106"/>
+      <c r="A78" s="89"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -3559,7 +3567,7 @@
       </c>
     </row>
     <row r="79" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="106"/>
+      <c r="A79" s="89"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -3579,7 +3587,7 @@
       </c>
     </row>
     <row r="80" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="106"/>
+      <c r="A80" s="89"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -3599,7 +3607,7 @@
       </c>
     </row>
     <row r="81" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="107"/>
+      <c r="A81" s="90"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -3653,7 +3661,7 @@
       </c>
     </row>
     <row r="84" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="84" t="s">
+      <c r="A84" s="91" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -3679,7 +3687,7 @@
       </c>
     </row>
     <row r="85" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="85"/>
+      <c r="A85" s="92"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -3703,7 +3711,7 @@
       </c>
     </row>
     <row r="86" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="85"/>
+      <c r="A86" s="92"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -3723,7 +3731,7 @@
       </c>
     </row>
     <row r="87" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="85"/>
+      <c r="A87" s="92"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -3743,7 +3751,7 @@
       </c>
     </row>
     <row r="88" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="85"/>
+      <c r="A88" s="92"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -3763,7 +3771,7 @@
       </c>
     </row>
     <row r="89" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="86"/>
+      <c r="A89" s="93"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -3817,7 +3825,7 @@
       </c>
     </row>
     <row r="92" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="87" t="s">
+      <c r="A92" s="73" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -3843,7 +3851,7 @@
       </c>
     </row>
     <row r="93" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="88"/>
+      <c r="A93" s="74"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -3867,7 +3875,7 @@
       </c>
     </row>
     <row r="94" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="88"/>
+      <c r="A94" s="74"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -3887,7 +3895,7 @@
       </c>
     </row>
     <row r="95" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="88"/>
+      <c r="A95" s="74"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -3907,7 +3915,7 @@
       </c>
     </row>
     <row r="96" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="88"/>
+      <c r="A96" s="74"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -3927,7 +3935,7 @@
       </c>
     </row>
     <row r="97" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="89"/>
+      <c r="A97" s="75"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -3987,26 +3995,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="69" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="71"/>
+      <c r="A1" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="69"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="72"/>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="74"/>
+      <c r="A2" s="70"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="72"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -4039,7 +4047,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="75" t="s">
+      <c r="A4" s="94" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -4065,11 +4073,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="76"/>
+      <c r="A5" s="95"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -4093,7 +4101,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="76"/>
+      <c r="A6" s="95"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -4121,7 +4129,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="76"/>
+      <c r="A7" s="95"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -4149,7 +4157,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="76"/>
+      <c r="A8" s="95"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -4177,7 +4185,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="77"/>
+      <c r="A9" s="96"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -4239,7 +4247,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="78" t="s">
+      <c r="A12" s="97" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -4265,7 +4273,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="79"/>
+      <c r="A13" s="98"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -4289,7 +4297,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="79"/>
+      <c r="A14" s="98"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -4317,7 +4325,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="79"/>
+      <c r="A15" s="98"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -4345,7 +4353,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="79"/>
+      <c r="A16" s="98"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -4373,7 +4381,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="80"/>
+      <c r="A17" s="99"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -4435,7 +4443,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="81" t="s">
+      <c r="A20" s="100" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -4461,7 +4469,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="82"/>
+      <c r="A21" s="101"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -4489,7 +4497,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="82"/>
+      <c r="A22" s="101"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -4511,13 +4519,13 @@
       <c r="H22" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="J22" s="1" t="str">
+      <c r="J22" s="1">
         <f>IF(OR(Resultados!F22="",Resultados!G22=""),"",IF(AND(F22=Resultados!F22,G22=Resultados!G22),2,IF(((F22&gt;G22)=(Resultados!F22&gt;Resultados!G22))*((F22&lt;G22)=(Resultados!F22&lt;Resultados!G22)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="82"/>
+      <c r="A23" s="101"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -4545,7 +4553,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="82"/>
+      <c r="A24" s="101"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -4573,7 +4581,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="83"/>
+      <c r="A25" s="102"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -4635,7 +4643,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="66" t="s">
+      <c r="A28" s="103" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -4661,7 +4669,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="67"/>
+      <c r="A29" s="104"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -4689,7 +4697,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="67"/>
+      <c r="A30" s="104"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -4711,13 +4719,13 @@
       <c r="H30" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="J30" s="1" t="str">
+      <c r="J30" s="1">
         <f>IF(OR(Resultados!F30="",Resultados!G30=""),"",IF(AND(F30=Resultados!F30,G30=Resultados!G30),2,IF(((F30&gt;G30)=(Resultados!F30&gt;Resultados!G30))*((F30&lt;G30)=(Resultados!F30&lt;Resultados!G30)),1,0)))</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="67"/>
+      <c r="A31" s="104"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -4745,7 +4753,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="67"/>
+      <c r="A32" s="104"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -4773,7 +4781,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="68"/>
+      <c r="A33" s="105"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -4835,7 +4843,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="90" t="s">
+      <c r="A36" s="106" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -4865,7 +4873,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="91"/>
+      <c r="A37" s="107"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -4893,7 +4901,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="91"/>
+      <c r="A38" s="107"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -4921,7 +4929,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="91"/>
+      <c r="A39" s="107"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -4949,7 +4957,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="91"/>
+      <c r="A40" s="107"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -4977,7 +4985,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="92"/>
+      <c r="A41" s="108"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -5039,7 +5047,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="93" t="s">
+      <c r="A44" s="76" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -5069,7 +5077,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="94"/>
+      <c r="A45" s="77"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -5097,7 +5105,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="94"/>
+      <c r="A46" s="77"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -5125,7 +5133,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="94"/>
+      <c r="A47" s="77"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -5153,7 +5161,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="94"/>
+      <c r="A48" s="77"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -5181,7 +5189,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="95"/>
+      <c r="A49" s="78"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -5243,7 +5251,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="96" t="s">
+      <c r="A52" s="79" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -5273,7 +5281,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="97"/>
+      <c r="A53" s="80"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -5301,7 +5309,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="97"/>
+      <c r="A54" s="80"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -5329,7 +5337,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="97"/>
+      <c r="A55" s="80"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -5357,7 +5365,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="97"/>
+      <c r="A56" s="80"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -5385,7 +5393,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="98"/>
+      <c r="A57" s="81"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -5447,7 +5455,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="99" t="s">
+      <c r="A60" s="82" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -5477,7 +5485,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="100"/>
+      <c r="A61" s="83"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -5505,7 +5513,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="100"/>
+      <c r="A62" s="83"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -5533,7 +5541,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="100"/>
+      <c r="A63" s="83"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -5561,7 +5569,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="100"/>
+      <c r="A64" s="83"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -5589,7 +5597,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="101"/>
+      <c r="A65" s="84"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -5651,7 +5659,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="102" t="s">
+      <c r="A68" s="85" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -5681,7 +5689,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="103"/>
+      <c r="A69" s="86"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -5709,7 +5717,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="103"/>
+      <c r="A70" s="86"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -5737,7 +5745,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="103"/>
+      <c r="A71" s="86"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -5765,7 +5773,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="103"/>
+      <c r="A72" s="86"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -5793,7 +5801,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="104"/>
+      <c r="A73" s="87"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -5855,7 +5863,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="105" t="s">
+      <c r="A76" s="88" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -5885,7 +5893,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="106"/>
+      <c r="A77" s="89"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -5913,7 +5921,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="106"/>
+      <c r="A78" s="89"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -5941,7 +5949,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="106"/>
+      <c r="A79" s="89"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -5969,7 +5977,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="106"/>
+      <c r="A80" s="89"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -5997,7 +6005,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="107"/>
+      <c r="A81" s="90"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -6059,7 +6067,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="84" t="s">
+      <c r="A84" s="91" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -6089,7 +6097,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="85"/>
+      <c r="A85" s="92"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -6117,7 +6125,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="85"/>
+      <c r="A86" s="92"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -6145,7 +6153,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="85"/>
+      <c r="A87" s="92"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -6173,7 +6181,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="85"/>
+      <c r="A88" s="92"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -6201,7 +6209,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="86"/>
+      <c r="A89" s="93"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -6263,7 +6271,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="87" t="s">
+      <c r="A92" s="73" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -6293,7 +6301,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="88"/>
+      <c r="A93" s="74"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -6321,7 +6329,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="88"/>
+      <c r="A94" s="74"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -6349,7 +6357,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="88"/>
+      <c r="A95" s="74"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -6377,7 +6385,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="88"/>
+      <c r="A96" s="74"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -6405,7 +6413,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="89"/>
+      <c r="A97" s="75"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -6475,26 +6483,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="69" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="71"/>
+      <c r="A1" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="69"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="72"/>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="74"/>
+      <c r="A2" s="70"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="72"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -6527,7 +6535,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="75" t="s">
+      <c r="A4" s="94" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -6553,11 +6561,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="76"/>
+      <c r="A5" s="95"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -6581,7 +6589,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="76"/>
+      <c r="A6" s="95"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -6609,7 +6617,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="76"/>
+      <c r="A7" s="95"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -6637,7 +6645,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="76"/>
+      <c r="A8" s="95"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -6665,7 +6673,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="77"/>
+      <c r="A9" s="96"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -6727,7 +6735,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="78" t="s">
+      <c r="A12" s="97" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -6753,7 +6761,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="79"/>
+      <c r="A13" s="98"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -6777,7 +6785,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="79"/>
+      <c r="A14" s="98"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -6805,7 +6813,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="79"/>
+      <c r="A15" s="98"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -6833,7 +6841,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="79"/>
+      <c r="A16" s="98"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -6861,7 +6869,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="80"/>
+      <c r="A17" s="99"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -6923,7 +6931,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="81" t="s">
+      <c r="A20" s="100" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -6949,7 +6957,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="82"/>
+      <c r="A21" s="101"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -6977,7 +6985,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="82"/>
+      <c r="A22" s="101"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -6999,13 +7007,13 @@
       <c r="H22" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="J22" s="1" t="str">
+      <c r="J22" s="1">
         <f>IF(OR(Resultados!F22="",Resultados!G22=""),"",IF(AND(F22=Resultados!F22,G22=Resultados!G22),2,IF(((F22&gt;G22)=(Resultados!F22&gt;Resultados!G22))*((F22&lt;G22)=(Resultados!F22&lt;Resultados!G22)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="82"/>
+      <c r="A23" s="101"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -7033,7 +7041,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="82"/>
+      <c r="A24" s="101"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -7061,7 +7069,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="83"/>
+      <c r="A25" s="102"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -7123,7 +7131,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="66" t="s">
+      <c r="A28" s="103" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -7149,7 +7157,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="67"/>
+      <c r="A29" s="104"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -7177,7 +7185,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="67"/>
+      <c r="A30" s="104"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -7199,13 +7207,13 @@
       <c r="H30" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="J30" s="1" t="str">
+      <c r="J30" s="1">
         <f>IF(OR(Resultados!F30="",Resultados!G30=""),"",IF(AND(F30=Resultados!F30,G30=Resultados!G30),2,IF(((F30&gt;G30)=(Resultados!F30&gt;Resultados!G30))*((F30&lt;G30)=(Resultados!F30&lt;Resultados!G30)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="67"/>
+      <c r="A31" s="104"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -7233,7 +7241,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="67"/>
+      <c r="A32" s="104"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -7261,7 +7269,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="68"/>
+      <c r="A33" s="105"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -7323,7 +7331,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="90" t="s">
+      <c r="A36" s="106" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -7353,7 +7361,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="91"/>
+      <c r="A37" s="107"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -7381,7 +7389,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="91"/>
+      <c r="A38" s="107"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -7409,7 +7417,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="91"/>
+      <c r="A39" s="107"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -7437,7 +7445,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="91"/>
+      <c r="A40" s="107"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -7465,7 +7473,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="92"/>
+      <c r="A41" s="108"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -7527,7 +7535,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="93" t="s">
+      <c r="A44" s="76" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -7557,7 +7565,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="94"/>
+      <c r="A45" s="77"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -7585,7 +7593,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="94"/>
+      <c r="A46" s="77"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -7613,7 +7621,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="94"/>
+      <c r="A47" s="77"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -7641,7 +7649,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="94"/>
+      <c r="A48" s="77"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -7669,7 +7677,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="95"/>
+      <c r="A49" s="78"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -7731,7 +7739,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="96" t="s">
+      <c r="A52" s="79" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -7761,7 +7769,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="97"/>
+      <c r="A53" s="80"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -7789,7 +7797,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="97"/>
+      <c r="A54" s="80"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -7817,7 +7825,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="97"/>
+      <c r="A55" s="80"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -7845,7 +7853,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="97"/>
+      <c r="A56" s="80"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -7873,7 +7881,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="98"/>
+      <c r="A57" s="81"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -7935,7 +7943,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="99" t="s">
+      <c r="A60" s="82" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -7965,7 +7973,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="100"/>
+      <c r="A61" s="83"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -7993,7 +8001,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="100"/>
+      <c r="A62" s="83"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -8021,7 +8029,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="100"/>
+      <c r="A63" s="83"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -8049,7 +8057,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="100"/>
+      <c r="A64" s="83"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -8077,7 +8085,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="101"/>
+      <c r="A65" s="84"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -8139,7 +8147,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="102" t="s">
+      <c r="A68" s="85" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -8169,7 +8177,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="103"/>
+      <c r="A69" s="86"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -8197,7 +8205,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="103"/>
+      <c r="A70" s="86"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -8225,7 +8233,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="103"/>
+      <c r="A71" s="86"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -8253,7 +8261,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="103"/>
+      <c r="A72" s="86"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -8281,7 +8289,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="104"/>
+      <c r="A73" s="87"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -8343,7 +8351,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="105" t="s">
+      <c r="A76" s="88" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -8373,7 +8381,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="106"/>
+      <c r="A77" s="89"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -8401,7 +8409,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="106"/>
+      <c r="A78" s="89"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -8429,7 +8437,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="106"/>
+      <c r="A79" s="89"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -8457,7 +8465,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="106"/>
+      <c r="A80" s="89"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -8485,7 +8493,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="107"/>
+      <c r="A81" s="90"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -8547,7 +8555,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="84" t="s">
+      <c r="A84" s="91" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -8577,7 +8585,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="85"/>
+      <c r="A85" s="92"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -8605,7 +8613,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="85"/>
+      <c r="A86" s="92"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -8633,7 +8641,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="85"/>
+      <c r="A87" s="92"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -8661,7 +8669,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="85"/>
+      <c r="A88" s="92"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -8689,7 +8697,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="86"/>
+      <c r="A89" s="93"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -8751,7 +8759,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="87" t="s">
+      <c r="A92" s="73" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -8781,7 +8789,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="88"/>
+      <c r="A93" s="74"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -8809,7 +8817,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="88"/>
+      <c r="A94" s="74"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -8837,7 +8845,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="88"/>
+      <c r="A95" s="74"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -8865,7 +8873,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="88"/>
+      <c r="A96" s="74"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -8893,7 +8901,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="89"/>
+      <c r="A97" s="75"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -8958,18 +8966,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D1" s="108" t="s">
+      <c r="D1" s="109" t="s">
         <v>74</v>
       </c>
-      <c r="E1" s="109"/>
-      <c r="F1" s="110"/>
+      <c r="E1" s="110"/>
+      <c r="F1" s="111"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D2" s="111" t="s">
+      <c r="D2" s="112" t="s">
         <v>75</v>
       </c>
-      <c r="E2" s="112"/>
-      <c r="F2" s="113"/>
+      <c r="E2" s="113"/>
+      <c r="F2" s="114"/>
     </row>
     <row r="4" spans="1:6" s="29" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="57" t="s">
@@ -8994,7 +9002,7 @@
       </c>
       <c r="B5" s="58">
         <f>Cindy!L4</f>
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D5" s="59">
         <v>1</v>
@@ -9004,7 +9012,7 @@
         <v>Erik</v>
       </c>
       <c r="F5" s="59">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -9013,7 +9021,7 @@
       </c>
       <c r="B6" s="58">
         <f>Wendy!L4</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6" s="55">
         <v>2</v>
@@ -9022,7 +9030,7 @@
         <v>Packy</v>
       </c>
       <c r="F6" s="55">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -9031,7 +9039,7 @@
       </c>
       <c r="B7" s="58">
         <f>Jimmy!L4</f>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D7" s="56">
         <v>3</v>
@@ -9040,7 +9048,7 @@
         <v>Bere</v>
       </c>
       <c r="F7" s="56">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -9049,16 +9057,16 @@
       </c>
       <c r="B8" s="58">
         <f>Erick!L4</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D8" s="28">
         <v>4</v>
       </c>
       <c r="E8" s="28" t="str">
-        <v>Wendy</v>
+        <v>Jimmy</v>
       </c>
       <c r="F8" s="28">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -9067,16 +9075,16 @@
       </c>
       <c r="B9" s="58">
         <f>Erik!L4</f>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D9" s="28">
         <v>5</v>
       </c>
       <c r="E9" s="28" t="str">
-        <v>Jimmy</v>
+        <v>Cindy</v>
       </c>
       <c r="F9" s="28">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -9085,16 +9093,16 @@
       </c>
       <c r="B10" s="58">
         <f>Lennon!L4</f>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D10" s="28">
         <v>6</v>
       </c>
       <c r="E10" s="28" t="str">
-        <v>Cindy</v>
+        <v>Wendy</v>
       </c>
       <c r="F10" s="28">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -9103,7 +9111,7 @@
       </c>
       <c r="B11" s="58">
         <f>Yulian!L4</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D11" s="28">
         <v>7</v>
@@ -9112,7 +9120,7 @@
         <v>Lennon</v>
       </c>
       <c r="F11" s="28">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -9121,7 +9129,7 @@
       </c>
       <c r="B12" s="58">
         <f>Packy!L4</f>
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D12" s="28">
         <v>8</v>
@@ -9130,7 +9138,7 @@
         <v>Yulian</v>
       </c>
       <c r="F12" s="28">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -9139,7 +9147,7 @@
       </c>
       <c r="B13" s="58">
         <f>Bere!L4</f>
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D13" s="28">
         <v>9</v>
@@ -9148,7 +9156,7 @@
         <v>Erick</v>
       </c>
       <c r="F13" s="28">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -9182,26 +9190,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="69" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="71"/>
+      <c r="A1" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="69"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="72"/>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="74"/>
+      <c r="A2" s="70"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="72"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="31"/>
@@ -9234,7 +9242,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="117" t="s">
+      <c r="A4" s="118" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="35">
@@ -9260,11 +9268,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="118"/>
+      <c r="A5" s="119"/>
       <c r="B5" s="35">
         <v>46185</v>
       </c>
@@ -9288,7 +9296,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="118"/>
+      <c r="A6" s="119"/>
       <c r="B6" s="35">
         <v>46191</v>
       </c>
@@ -9316,7 +9324,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="118"/>
+      <c r="A7" s="119"/>
       <c r="B7" s="35">
         <v>46192</v>
       </c>
@@ -9344,7 +9352,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="118"/>
+      <c r="A8" s="119"/>
       <c r="B8" s="35">
         <v>46198</v>
       </c>
@@ -9372,7 +9380,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="119"/>
+      <c r="A9" s="120"/>
       <c r="B9" s="42">
         <v>46198</v>
       </c>
@@ -9434,7 +9442,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="120" t="s">
+      <c r="A12" s="121" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="35">
@@ -9460,7 +9468,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="121"/>
+      <c r="A13" s="122"/>
       <c r="B13" s="35">
         <v>46186</v>
       </c>
@@ -9484,7 +9492,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="121"/>
+      <c r="A14" s="122"/>
       <c r="B14" s="35">
         <v>46191</v>
       </c>
@@ -9512,7 +9520,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="121"/>
+      <c r="A15" s="122"/>
       <c r="B15" s="35">
         <v>46192</v>
       </c>
@@ -9540,7 +9548,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="121"/>
+      <c r="A16" s="122"/>
       <c r="B16" s="35">
         <v>46197</v>
       </c>
@@ -9568,7 +9576,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="122"/>
+      <c r="A17" s="123"/>
       <c r="B17" s="42">
         <v>46197</v>
       </c>
@@ -9630,7 +9638,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="123" t="s">
+      <c r="A20" s="124" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="35">
@@ -9656,7 +9664,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="124"/>
+      <c r="A21" s="125"/>
       <c r="B21" s="35">
         <v>46187</v>
       </c>
@@ -9684,7 +9692,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="124"/>
+      <c r="A22" s="125"/>
       <c r="B22" s="35">
         <v>46193</v>
       </c>
@@ -9706,13 +9714,13 @@
       <c r="H22" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="J22" s="1" t="str">
+      <c r="J22" s="1">
         <f>IF(OR(Resultados!F22="",Resultados!G22=""),"",IF(AND(F22=Resultados!F22,G22=Resultados!G22),2,IF(((F22&gt;G22)=(Resultados!F22&gt;Resultados!G22))*((F22&lt;G22)=(Resultados!F22&lt;Resultados!G22)),1,0)))</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="124"/>
+      <c r="A23" s="125"/>
       <c r="B23" s="35">
         <v>46193</v>
       </c>
@@ -9740,7 +9748,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="124"/>
+      <c r="A24" s="125"/>
       <c r="B24" s="35">
         <v>46198</v>
       </c>
@@ -9768,7 +9776,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="125"/>
+      <c r="A25" s="126"/>
       <c r="B25" s="42">
         <v>46198</v>
       </c>
@@ -9830,7 +9838,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="114" t="s">
+      <c r="A28" s="115" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="35">
@@ -9856,7 +9864,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="115"/>
+      <c r="A29" s="116"/>
       <c r="B29" s="35">
         <v>46187</v>
       </c>
@@ -9884,7 +9892,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="115"/>
+      <c r="A30" s="116"/>
       <c r="B30" s="35">
         <v>46192</v>
       </c>
@@ -9906,13 +9914,13 @@
       <c r="H30" s="46" t="s">
         <v>28</v>
       </c>
-      <c r="J30" s="1" t="str">
+      <c r="J30" s="1">
         <f>IF(OR(Resultados!F30="",Resultados!G30=""),"",IF(AND(F30=Resultados!F30,G30=Resultados!G30),2,IF(((F30&gt;G30)=(Resultados!F30&gt;Resultados!G30))*((F30&lt;G30)=(Resultados!F30&lt;Resultados!G30)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="115"/>
+      <c r="A31" s="116"/>
       <c r="B31" s="35">
         <v>46193</v>
       </c>
@@ -9940,7 +9948,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="115"/>
+      <c r="A32" s="116"/>
       <c r="B32" s="35">
         <v>46199</v>
       </c>
@@ -9968,7 +9976,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="116"/>
+      <c r="A33" s="117"/>
       <c r="B33" s="42">
         <v>46199</v>
       </c>
@@ -10030,7 +10038,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="132" t="s">
+      <c r="A36" s="133" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="35">
@@ -10060,7 +10068,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="133"/>
+      <c r="A37" s="134"/>
       <c r="B37" s="35">
         <v>46188</v>
       </c>
@@ -10088,7 +10096,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="133"/>
+      <c r="A38" s="134"/>
       <c r="B38" s="35">
         <v>46193</v>
       </c>
@@ -10116,7 +10124,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="133"/>
+      <c r="A39" s="134"/>
       <c r="B39" s="35">
         <v>46194</v>
       </c>
@@ -10144,7 +10152,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="133"/>
+      <c r="A40" s="134"/>
       <c r="B40" s="35">
         <v>46198</v>
       </c>
@@ -10172,7 +10180,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="134"/>
+      <c r="A41" s="135"/>
       <c r="B41" s="42">
         <v>46198</v>
       </c>
@@ -10234,7 +10242,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="135" t="s">
+      <c r="A44" s="136" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="35">
@@ -10264,7 +10272,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="136"/>
+      <c r="A45" s="137"/>
       <c r="B45" s="35">
         <v>46188</v>
       </c>
@@ -10292,7 +10300,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="136"/>
+      <c r="A46" s="137"/>
       <c r="B46" s="35">
         <v>46193</v>
       </c>
@@ -10320,7 +10328,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="136"/>
+      <c r="A47" s="137"/>
       <c r="B47" s="35">
         <v>46194</v>
       </c>
@@ -10348,7 +10356,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="136"/>
+      <c r="A48" s="137"/>
       <c r="B48" s="35">
         <v>46199</v>
       </c>
@@ -10376,7 +10384,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="137"/>
+      <c r="A49" s="138"/>
       <c r="B49" s="42">
         <v>46199</v>
       </c>
@@ -10438,7 +10446,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="138" t="s">
+      <c r="A52" s="139" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="35">
@@ -10468,7 +10476,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="139"/>
+      <c r="A53" s="140"/>
       <c r="B53" s="35">
         <v>46189</v>
       </c>
@@ -10496,7 +10504,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="139"/>
+      <c r="A54" s="140"/>
       <c r="B54" s="35">
         <v>46194</v>
       </c>
@@ -10524,7 +10532,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="139"/>
+      <c r="A55" s="140"/>
       <c r="B55" s="35">
         <v>46195</v>
       </c>
@@ -10552,7 +10560,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="139"/>
+      <c r="A56" s="140"/>
       <c r="B56" s="35">
         <v>46200</v>
       </c>
@@ -10580,7 +10588,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="140"/>
+      <c r="A57" s="141"/>
       <c r="B57" s="42">
         <v>46200</v>
       </c>
@@ -10642,7 +10650,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="141" t="s">
+      <c r="A60" s="142" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="35">
@@ -10672,7 +10680,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="142"/>
+      <c r="A61" s="143"/>
       <c r="B61" s="35">
         <v>46189</v>
       </c>
@@ -10700,7 +10708,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="142"/>
+      <c r="A62" s="143"/>
       <c r="B62" s="35">
         <v>46194</v>
       </c>
@@ -10728,7 +10736,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="142"/>
+      <c r="A63" s="143"/>
       <c r="B63" s="35">
         <v>46195</v>
       </c>
@@ -10756,7 +10764,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="142"/>
+      <c r="A64" s="143"/>
       <c r="B64" s="35">
         <v>46200</v>
       </c>
@@ -10784,7 +10792,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="143"/>
+      <c r="A65" s="144"/>
       <c r="B65" s="42">
         <v>46200</v>
       </c>
@@ -10846,7 +10854,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="144" t="s">
+      <c r="A68" s="145" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="35">
@@ -10876,7 +10884,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="145"/>
+      <c r="A69" s="146"/>
       <c r="B69" s="35">
         <v>46190</v>
       </c>
@@ -10904,7 +10912,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="145"/>
+      <c r="A70" s="146"/>
       <c r="B70" s="35">
         <v>46195</v>
       </c>
@@ -10932,7 +10940,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="145"/>
+      <c r="A71" s="146"/>
       <c r="B71" s="35">
         <v>46196</v>
       </c>
@@ -10960,7 +10968,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="145"/>
+      <c r="A72" s="146"/>
       <c r="B72" s="35">
         <v>46199</v>
       </c>
@@ -10988,7 +10996,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="146"/>
+      <c r="A73" s="147"/>
       <c r="B73" s="42">
         <v>46199</v>
       </c>
@@ -11050,7 +11058,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="147" t="s">
+      <c r="A76" s="148" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="35">
@@ -11080,7 +11088,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="148"/>
+      <c r="A77" s="149"/>
       <c r="B77" s="35">
         <v>46190</v>
       </c>
@@ -11108,7 +11116,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="148"/>
+      <c r="A78" s="149"/>
       <c r="B78" s="35">
         <v>46195</v>
       </c>
@@ -11136,7 +11144,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="148"/>
+      <c r="A79" s="149"/>
       <c r="B79" s="35">
         <v>46196</v>
       </c>
@@ -11164,7 +11172,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="148"/>
+      <c r="A80" s="149"/>
       <c r="B80" s="35">
         <v>46201</v>
       </c>
@@ -11192,7 +11200,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="149"/>
+      <c r="A81" s="150"/>
       <c r="B81" s="42">
         <v>46201</v>
       </c>
@@ -11254,7 +11262,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="126" t="s">
+      <c r="A84" s="127" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="35">
@@ -11284,7 +11292,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="127"/>
+      <c r="A85" s="128"/>
       <c r="B85" s="35">
         <v>46191</v>
       </c>
@@ -11312,7 +11320,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="127"/>
+      <c r="A86" s="128"/>
       <c r="B86" s="35">
         <v>46196</v>
       </c>
@@ -11340,7 +11348,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="127"/>
+      <c r="A87" s="128"/>
       <c r="B87" s="35">
         <v>46197</v>
       </c>
@@ -11368,7 +11376,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="127"/>
+      <c r="A88" s="128"/>
       <c r="B88" s="35">
         <v>46201</v>
       </c>
@@ -11396,7 +11404,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="128"/>
+      <c r="A89" s="129"/>
       <c r="B89" s="42">
         <v>46201</v>
       </c>
@@ -11458,7 +11466,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="129" t="s">
+      <c r="A92" s="130" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="35">
@@ -11488,7 +11496,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="130"/>
+      <c r="A93" s="131"/>
       <c r="B93" s="35">
         <v>46191</v>
       </c>
@@ -11516,7 +11524,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="130"/>
+      <c r="A94" s="131"/>
       <c r="B94" s="35">
         <v>46196</v>
       </c>
@@ -11544,7 +11552,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="130"/>
+      <c r="A95" s="131"/>
       <c r="B95" s="35">
         <v>46197</v>
       </c>
@@ -11572,7 +11580,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="130"/>
+      <c r="A96" s="131"/>
       <c r="B96" s="35">
         <v>46200</v>
       </c>
@@ -11600,7 +11608,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="131"/>
+      <c r="A97" s="132"/>
       <c r="B97" s="42">
         <v>46200</v>
       </c>
@@ -11671,26 +11679,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="69" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="71"/>
+      <c r="A1" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="69"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="72"/>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="74"/>
+      <c r="A2" s="70"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="72"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="31"/>
@@ -11723,7 +11731,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="117" t="s">
+      <c r="A4" s="118" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="35">
@@ -11749,11 +11757,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="118"/>
+      <c r="A5" s="119"/>
       <c r="B5" s="35">
         <v>46185</v>
       </c>
@@ -11777,7 +11785,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="118"/>
+      <c r="A6" s="119"/>
       <c r="B6" s="35">
         <v>46191</v>
       </c>
@@ -11805,7 +11813,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="118"/>
+      <c r="A7" s="119"/>
       <c r="B7" s="35">
         <v>46192</v>
       </c>
@@ -11833,7 +11841,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="118"/>
+      <c r="A8" s="119"/>
       <c r="B8" s="35">
         <v>46198</v>
       </c>
@@ -11861,7 +11869,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="119"/>
+      <c r="A9" s="120"/>
       <c r="B9" s="42">
         <v>46198</v>
       </c>
@@ -11923,7 +11931,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="120" t="s">
+      <c r="A12" s="121" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="35">
@@ -11949,7 +11957,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="121"/>
+      <c r="A13" s="122"/>
       <c r="B13" s="35">
         <v>46186</v>
       </c>
@@ -11973,7 +11981,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="121"/>
+      <c r="A14" s="122"/>
       <c r="B14" s="35">
         <v>46191</v>
       </c>
@@ -12001,7 +12009,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="121"/>
+      <c r="A15" s="122"/>
       <c r="B15" s="35">
         <v>46192</v>
       </c>
@@ -12029,7 +12037,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="121"/>
+      <c r="A16" s="122"/>
       <c r="B16" s="35">
         <v>46197</v>
       </c>
@@ -12057,7 +12065,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="122"/>
+      <c r="A17" s="123"/>
       <c r="B17" s="42">
         <v>46197</v>
       </c>
@@ -12119,7 +12127,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="123" t="s">
+      <c r="A20" s="124" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="35">
@@ -12145,7 +12153,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="124"/>
+      <c r="A21" s="125"/>
       <c r="B21" s="35">
         <v>46187</v>
       </c>
@@ -12173,7 +12181,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="124"/>
+      <c r="A22" s="125"/>
       <c r="B22" s="35">
         <v>46193</v>
       </c>
@@ -12195,13 +12203,13 @@
       <c r="H22" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="J22" s="1" t="str">
+      <c r="J22" s="1">
         <f>IF(OR(Resultados!F22="",Resultados!G22=""),"",IF(AND(F22=Resultados!F22,G22=Resultados!G22),2,IF(((F22&gt;G22)=(Resultados!F22&gt;Resultados!G22))*((F22&lt;G22)=(Resultados!F22&lt;Resultados!G22)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="124"/>
+      <c r="A23" s="125"/>
       <c r="B23" s="35">
         <v>46193</v>
       </c>
@@ -12229,7 +12237,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="124"/>
+      <c r="A24" s="125"/>
       <c r="B24" s="35">
         <v>46198</v>
       </c>
@@ -12257,7 +12265,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="125"/>
+      <c r="A25" s="126"/>
       <c r="B25" s="42">
         <v>46198</v>
       </c>
@@ -12319,7 +12327,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="114" t="s">
+      <c r="A28" s="115" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="35">
@@ -12345,7 +12353,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="115"/>
+      <c r="A29" s="116"/>
       <c r="B29" s="35">
         <v>46187</v>
       </c>
@@ -12373,7 +12381,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="115"/>
+      <c r="A30" s="116"/>
       <c r="B30" s="35">
         <v>46192</v>
       </c>
@@ -12395,13 +12403,13 @@
       <c r="H30" s="46" t="s">
         <v>28</v>
       </c>
-      <c r="J30" s="1" t="str">
+      <c r="J30" s="1">
         <f>IF(OR(Resultados!F30="",Resultados!G30=""),"",IF(AND(F30=Resultados!F30,G30=Resultados!G30),2,IF(((F30&gt;G30)=(Resultados!F30&gt;Resultados!G30))*((F30&lt;G30)=(Resultados!F30&lt;Resultados!G30)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="115"/>
+      <c r="A31" s="116"/>
       <c r="B31" s="35">
         <v>46193</v>
       </c>
@@ -12429,7 +12437,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="115"/>
+      <c r="A32" s="116"/>
       <c r="B32" s="35">
         <v>46199</v>
       </c>
@@ -12457,7 +12465,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="116"/>
+      <c r="A33" s="117"/>
       <c r="B33" s="42">
         <v>46199</v>
       </c>
@@ -12519,7 +12527,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="132" t="s">
+      <c r="A36" s="133" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="35">
@@ -12549,7 +12557,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="133"/>
+      <c r="A37" s="134"/>
       <c r="B37" s="35">
         <v>46188</v>
       </c>
@@ -12577,7 +12585,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="133"/>
+      <c r="A38" s="134"/>
       <c r="B38" s="35">
         <v>46193</v>
       </c>
@@ -12605,7 +12613,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="133"/>
+      <c r="A39" s="134"/>
       <c r="B39" s="35">
         <v>46194</v>
       </c>
@@ -12633,7 +12641,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="133"/>
+      <c r="A40" s="134"/>
       <c r="B40" s="35">
         <v>46198</v>
       </c>
@@ -12661,7 +12669,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="134"/>
+      <c r="A41" s="135"/>
       <c r="B41" s="42">
         <v>46198</v>
       </c>
@@ -12723,7 +12731,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="135" t="s">
+      <c r="A44" s="136" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="35">
@@ -12753,7 +12761,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="136"/>
+      <c r="A45" s="137"/>
       <c r="B45" s="35">
         <v>46188</v>
       </c>
@@ -12781,7 +12789,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="136"/>
+      <c r="A46" s="137"/>
       <c r="B46" s="35">
         <v>46193</v>
       </c>
@@ -12809,7 +12817,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="136"/>
+      <c r="A47" s="137"/>
       <c r="B47" s="35">
         <v>46194</v>
       </c>
@@ -12837,7 +12845,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="136"/>
+      <c r="A48" s="137"/>
       <c r="B48" s="35">
         <v>46199</v>
       </c>
@@ -12865,7 +12873,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="137"/>
+      <c r="A49" s="138"/>
       <c r="B49" s="42">
         <v>46199</v>
       </c>
@@ -12927,7 +12935,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="138" t="s">
+      <c r="A52" s="139" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="35">
@@ -12957,7 +12965,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="139"/>
+      <c r="A53" s="140"/>
       <c r="B53" s="35">
         <v>46189</v>
       </c>
@@ -12985,7 +12993,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="139"/>
+      <c r="A54" s="140"/>
       <c r="B54" s="35">
         <v>46194</v>
       </c>
@@ -13013,7 +13021,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="139"/>
+      <c r="A55" s="140"/>
       <c r="B55" s="35">
         <v>46195</v>
       </c>
@@ -13041,7 +13049,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="139"/>
+      <c r="A56" s="140"/>
       <c r="B56" s="35">
         <v>46200</v>
       </c>
@@ -13069,7 +13077,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="140"/>
+      <c r="A57" s="141"/>
       <c r="B57" s="42">
         <v>46200</v>
       </c>
@@ -13131,7 +13139,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="141" t="s">
+      <c r="A60" s="142" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="35">
@@ -13161,7 +13169,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="142"/>
+      <c r="A61" s="143"/>
       <c r="B61" s="35">
         <v>46189</v>
       </c>
@@ -13189,7 +13197,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="142"/>
+      <c r="A62" s="143"/>
       <c r="B62" s="35">
         <v>46194</v>
       </c>
@@ -13217,7 +13225,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="142"/>
+      <c r="A63" s="143"/>
       <c r="B63" s="35">
         <v>46195</v>
       </c>
@@ -13245,7 +13253,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="142"/>
+      <c r="A64" s="143"/>
       <c r="B64" s="35">
         <v>46200</v>
       </c>
@@ -13273,7 +13281,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="143"/>
+      <c r="A65" s="144"/>
       <c r="B65" s="42">
         <v>46200</v>
       </c>
@@ -13335,7 +13343,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="144" t="s">
+      <c r="A68" s="145" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="35">
@@ -13365,7 +13373,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="145"/>
+      <c r="A69" s="146"/>
       <c r="B69" s="35">
         <v>46190</v>
       </c>
@@ -13393,7 +13401,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="145"/>
+      <c r="A70" s="146"/>
       <c r="B70" s="35">
         <v>46195</v>
       </c>
@@ -13421,7 +13429,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="145"/>
+      <c r="A71" s="146"/>
       <c r="B71" s="35">
         <v>46196</v>
       </c>
@@ -13449,7 +13457,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="145"/>
+      <c r="A72" s="146"/>
       <c r="B72" s="35">
         <v>46199</v>
       </c>
@@ -13477,7 +13485,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="146"/>
+      <c r="A73" s="147"/>
       <c r="B73" s="42">
         <v>46199</v>
       </c>
@@ -13539,7 +13547,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="147" t="s">
+      <c r="A76" s="148" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="35">
@@ -13569,7 +13577,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="148"/>
+      <c r="A77" s="149"/>
       <c r="B77" s="35">
         <v>46190</v>
       </c>
@@ -13597,7 +13605,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="148"/>
+      <c r="A78" s="149"/>
       <c r="B78" s="35">
         <v>46195</v>
       </c>
@@ -13625,7 +13633,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="148"/>
+      <c r="A79" s="149"/>
       <c r="B79" s="35">
         <v>46196</v>
       </c>
@@ -13653,7 +13661,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="148"/>
+      <c r="A80" s="149"/>
       <c r="B80" s="35">
         <v>46201</v>
       </c>
@@ -13681,7 +13689,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="149"/>
+      <c r="A81" s="150"/>
       <c r="B81" s="42">
         <v>46201</v>
       </c>
@@ -13743,7 +13751,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="126" t="s">
+      <c r="A84" s="127" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="35">
@@ -13773,7 +13781,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="127"/>
+      <c r="A85" s="128"/>
       <c r="B85" s="35">
         <v>46191</v>
       </c>
@@ -13801,7 +13809,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="127"/>
+      <c r="A86" s="128"/>
       <c r="B86" s="35">
         <v>46196</v>
       </c>
@@ -13829,7 +13837,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="127"/>
+      <c r="A87" s="128"/>
       <c r="B87" s="35">
         <v>46197</v>
       </c>
@@ -13857,7 +13865,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="127"/>
+      <c r="A88" s="128"/>
       <c r="B88" s="35">
         <v>46201</v>
       </c>
@@ -13885,7 +13893,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="128"/>
+      <c r="A89" s="129"/>
       <c r="B89" s="42">
         <v>46201</v>
       </c>
@@ -13947,7 +13955,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="129" t="s">
+      <c r="A92" s="130" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="35">
@@ -13977,7 +13985,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="130"/>
+      <c r="A93" s="131"/>
       <c r="B93" s="35">
         <v>46191</v>
       </c>
@@ -14005,7 +14013,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="130"/>
+      <c r="A94" s="131"/>
       <c r="B94" s="35">
         <v>46196</v>
       </c>
@@ -14033,7 +14041,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="130"/>
+      <c r="A95" s="131"/>
       <c r="B95" s="35">
         <v>46197</v>
       </c>
@@ -14061,7 +14069,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="130"/>
+      <c r="A96" s="131"/>
       <c r="B96" s="35">
         <v>46200</v>
       </c>
@@ -14089,7 +14097,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="131"/>
+      <c r="A97" s="132"/>
       <c r="B97" s="42">
         <v>46200</v>
       </c>
@@ -14159,26 +14167,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="69" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="71"/>
+      <c r="A1" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="69"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="72"/>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="74"/>
+      <c r="A2" s="70"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="72"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -14211,7 +14219,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="75" t="s">
+      <c r="A4" s="94" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -14237,11 +14245,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="76"/>
+      <c r="A5" s="95"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -14265,7 +14273,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="76"/>
+      <c r="A6" s="95"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -14293,7 +14301,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="76"/>
+      <c r="A7" s="95"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -14321,7 +14329,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="76"/>
+      <c r="A8" s="95"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -14349,7 +14357,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="77"/>
+      <c r="A9" s="96"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -14411,7 +14419,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="78" t="s">
+      <c r="A12" s="97" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -14437,7 +14445,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="79"/>
+      <c r="A13" s="98"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -14461,7 +14469,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="79"/>
+      <c r="A14" s="98"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -14489,7 +14497,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="79"/>
+      <c r="A15" s="98"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -14517,7 +14525,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="79"/>
+      <c r="A16" s="98"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -14545,7 +14553,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="80"/>
+      <c r="A17" s="99"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -14607,7 +14615,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="81" t="s">
+      <c r="A20" s="100" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -14633,7 +14641,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="82"/>
+      <c r="A21" s="101"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -14661,7 +14669,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="82"/>
+      <c r="A22" s="101"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -14683,13 +14691,13 @@
       <c r="H22" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="J22" s="1" t="str">
+      <c r="J22" s="1">
         <f>IF(OR(Resultados!F22="",Resultados!G22=""),"",IF(AND(F22=Resultados!F22,G22=Resultados!G22),2,IF(((F22&gt;G22)=(Resultados!F22&gt;Resultados!G22))*((F22&lt;G22)=(Resultados!F22&lt;Resultados!G22)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="82"/>
+      <c r="A23" s="101"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -14717,7 +14725,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="82"/>
+      <c r="A24" s="101"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -14745,7 +14753,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="83"/>
+      <c r="A25" s="102"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -14807,7 +14815,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="66" t="s">
+      <c r="A28" s="103" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -14833,7 +14841,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="67"/>
+      <c r="A29" s="104"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -14861,7 +14869,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="67"/>
+      <c r="A30" s="104"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -14883,13 +14891,13 @@
       <c r="H30" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="J30" s="1" t="str">
+      <c r="J30" s="1">
         <f>IF(OR(Resultados!F30="",Resultados!G30=""),"",IF(AND(F30=Resultados!F30,G30=Resultados!G30),2,IF(((F30&gt;G30)=(Resultados!F30&gt;Resultados!G30))*((F30&lt;G30)=(Resultados!F30&lt;Resultados!G30)),1,0)))</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="67"/>
+      <c r="A31" s="104"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -14917,7 +14925,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="67"/>
+      <c r="A32" s="104"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -14945,7 +14953,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="68"/>
+      <c r="A33" s="105"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -15007,7 +15015,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="90" t="s">
+      <c r="A36" s="106" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -15037,7 +15045,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="91"/>
+      <c r="A37" s="107"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -15065,7 +15073,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="91"/>
+      <c r="A38" s="107"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -15093,7 +15101,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="91"/>
+      <c r="A39" s="107"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -15121,7 +15129,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="91"/>
+      <c r="A40" s="107"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -15149,7 +15157,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="92"/>
+      <c r="A41" s="108"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -15211,7 +15219,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="93" t="s">
+      <c r="A44" s="76" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -15241,7 +15249,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="94"/>
+      <c r="A45" s="77"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -15269,7 +15277,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="94"/>
+      <c r="A46" s="77"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -15297,7 +15305,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="94"/>
+      <c r="A47" s="77"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -15325,7 +15333,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="94"/>
+      <c r="A48" s="77"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -15353,7 +15361,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="95"/>
+      <c r="A49" s="78"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -15415,7 +15423,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="96" t="s">
+      <c r="A52" s="79" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -15445,7 +15453,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="97"/>
+      <c r="A53" s="80"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -15473,7 +15481,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="97"/>
+      <c r="A54" s="80"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -15501,7 +15509,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="97"/>
+      <c r="A55" s="80"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -15529,7 +15537,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="97"/>
+      <c r="A56" s="80"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -15557,7 +15565,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="98"/>
+      <c r="A57" s="81"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -15619,7 +15627,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="99" t="s">
+      <c r="A60" s="82" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -15649,7 +15657,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="100"/>
+      <c r="A61" s="83"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -15677,7 +15685,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="100"/>
+      <c r="A62" s="83"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -15705,7 +15713,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="100"/>
+      <c r="A63" s="83"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -15733,7 +15741,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="100"/>
+      <c r="A64" s="83"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -15761,7 +15769,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="101"/>
+      <c r="A65" s="84"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -15823,7 +15831,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="102" t="s">
+      <c r="A68" s="85" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -15853,7 +15861,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="103"/>
+      <c r="A69" s="86"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -15881,7 +15889,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="103"/>
+      <c r="A70" s="86"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -15909,7 +15917,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="103"/>
+      <c r="A71" s="86"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -15937,7 +15945,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="103"/>
+      <c r="A72" s="86"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -15965,7 +15973,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="104"/>
+      <c r="A73" s="87"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -16027,7 +16035,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="105" t="s">
+      <c r="A76" s="88" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -16057,7 +16065,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="106"/>
+      <c r="A77" s="89"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -16085,7 +16093,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="106"/>
+      <c r="A78" s="89"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -16113,7 +16121,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="106"/>
+      <c r="A79" s="89"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -16141,7 +16149,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="106"/>
+      <c r="A80" s="89"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -16169,7 +16177,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="107"/>
+      <c r="A81" s="90"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -16231,7 +16239,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="84" t="s">
+      <c r="A84" s="91" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -16261,7 +16269,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="85"/>
+      <c r="A85" s="92"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -16289,7 +16297,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="85"/>
+      <c r="A86" s="92"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -16317,7 +16325,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="85"/>
+      <c r="A87" s="92"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -16345,7 +16353,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="85"/>
+      <c r="A88" s="92"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -16373,7 +16381,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="86"/>
+      <c r="A89" s="93"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -16435,7 +16443,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="87" t="s">
+      <c r="A92" s="73" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -16465,7 +16473,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="88"/>
+      <c r="A93" s="74"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -16493,7 +16501,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="88"/>
+      <c r="A94" s="74"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -16521,7 +16529,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="88"/>
+      <c r="A95" s="74"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -16549,7 +16557,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="88"/>
+      <c r="A96" s="74"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -16577,7 +16585,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="89"/>
+      <c r="A97" s="75"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -16647,26 +16655,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="69" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="71"/>
+      <c r="A1" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="69"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="72"/>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="74"/>
+      <c r="A2" s="70"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="72"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -16699,7 +16707,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="75" t="s">
+      <c r="A4" s="94" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -16725,11 +16733,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="76"/>
+      <c r="A5" s="95"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -16753,7 +16761,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="76"/>
+      <c r="A6" s="95"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -16781,7 +16789,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="76"/>
+      <c r="A7" s="95"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -16809,7 +16817,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="76"/>
+      <c r="A8" s="95"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -16837,7 +16845,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="77"/>
+      <c r="A9" s="96"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -16899,7 +16907,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="78" t="s">
+      <c r="A12" s="97" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -16925,7 +16933,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="79"/>
+      <c r="A13" s="98"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -16949,7 +16957,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="79"/>
+      <c r="A14" s="98"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -16977,7 +16985,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="79"/>
+      <c r="A15" s="98"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -17005,7 +17013,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="79"/>
+      <c r="A16" s="98"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -17033,7 +17041,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="80"/>
+      <c r="A17" s="99"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -17095,7 +17103,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="81" t="s">
+      <c r="A20" s="100" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -17121,7 +17129,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="82"/>
+      <c r="A21" s="101"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -17149,7 +17157,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="82"/>
+      <c r="A22" s="101"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -17171,13 +17179,13 @@
       <c r="H22" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="J22" s="1" t="str">
+      <c r="J22" s="1">
         <f>IF(OR(Resultados!F22="",Resultados!G22=""),"",IF(AND(F22=Resultados!F22,G22=Resultados!G22),2,IF(((F22&gt;G22)=(Resultados!F22&gt;Resultados!G22))*((F22&lt;G22)=(Resultados!F22&lt;Resultados!G22)),1,0)))</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="82"/>
+      <c r="A23" s="101"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -17205,7 +17213,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="82"/>
+      <c r="A24" s="101"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -17233,7 +17241,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="83"/>
+      <c r="A25" s="102"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -17295,7 +17303,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="66" t="s">
+      <c r="A28" s="103" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -17321,7 +17329,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="67"/>
+      <c r="A29" s="104"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -17349,7 +17357,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="67"/>
+      <c r="A30" s="104"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -17371,13 +17379,13 @@
       <c r="H30" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="J30" s="1" t="str">
+      <c r="J30" s="1">
         <f>IF(OR(Resultados!F30="",Resultados!G30=""),"",IF(AND(F30=Resultados!F30,G30=Resultados!G30),2,IF(((F30&gt;G30)=(Resultados!F30&gt;Resultados!G30))*((F30&lt;G30)=(Resultados!F30&lt;Resultados!G30)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="67"/>
+      <c r="A31" s="104"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -17405,7 +17413,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="67"/>
+      <c r="A32" s="104"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -17433,7 +17441,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="68"/>
+      <c r="A33" s="105"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -17495,7 +17503,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="90" t="s">
+      <c r="A36" s="106" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -17525,7 +17533,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="91"/>
+      <c r="A37" s="107"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -17553,7 +17561,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="91"/>
+      <c r="A38" s="107"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -17581,7 +17589,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="91"/>
+      <c r="A39" s="107"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -17609,7 +17617,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="91"/>
+      <c r="A40" s="107"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -17637,7 +17645,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="92"/>
+      <c r="A41" s="108"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -17699,7 +17707,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="93" t="s">
+      <c r="A44" s="76" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -17729,7 +17737,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="94"/>
+      <c r="A45" s="77"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -17757,7 +17765,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="94"/>
+      <c r="A46" s="77"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -17785,7 +17793,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="94"/>
+      <c r="A47" s="77"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -17813,7 +17821,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="94"/>
+      <c r="A48" s="77"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -17841,7 +17849,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="95"/>
+      <c r="A49" s="78"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -17903,7 +17911,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="96" t="s">
+      <c r="A52" s="79" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -17933,7 +17941,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="97"/>
+      <c r="A53" s="80"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -17961,7 +17969,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="97"/>
+      <c r="A54" s="80"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -17989,7 +17997,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="97"/>
+      <c r="A55" s="80"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -18017,7 +18025,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="97"/>
+      <c r="A56" s="80"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -18045,7 +18053,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="98"/>
+      <c r="A57" s="81"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -18107,7 +18115,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="99" t="s">
+      <c r="A60" s="82" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -18137,7 +18145,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="100"/>
+      <c r="A61" s="83"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -18165,7 +18173,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="100"/>
+      <c r="A62" s="83"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -18193,7 +18201,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="100"/>
+      <c r="A63" s="83"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -18221,7 +18229,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="100"/>
+      <c r="A64" s="83"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -18249,7 +18257,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="101"/>
+      <c r="A65" s="84"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -18311,7 +18319,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="102" t="s">
+      <c r="A68" s="85" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -18341,7 +18349,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="103"/>
+      <c r="A69" s="86"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -18369,7 +18377,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="103"/>
+      <c r="A70" s="86"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -18397,7 +18405,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="103"/>
+      <c r="A71" s="86"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -18425,7 +18433,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="103"/>
+      <c r="A72" s="86"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -18453,7 +18461,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="104"/>
+      <c r="A73" s="87"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -18515,7 +18523,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="105" t="s">
+      <c r="A76" s="88" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -18545,7 +18553,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="106"/>
+      <c r="A77" s="89"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -18573,7 +18581,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="106"/>
+      <c r="A78" s="89"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -18601,7 +18609,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="106"/>
+      <c r="A79" s="89"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -18629,7 +18637,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="106"/>
+      <c r="A80" s="89"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -18657,7 +18665,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="107"/>
+      <c r="A81" s="90"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -18719,7 +18727,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="84" t="s">
+      <c r="A84" s="91" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -18749,7 +18757,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="85"/>
+      <c r="A85" s="92"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -18777,7 +18785,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="85"/>
+      <c r="A86" s="92"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -18805,7 +18813,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="85"/>
+      <c r="A87" s="92"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -18833,7 +18841,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="85"/>
+      <c r="A88" s="92"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -18861,7 +18869,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="86"/>
+      <c r="A89" s="93"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -18923,7 +18931,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="87" t="s">
+      <c r="A92" s="73" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -18953,7 +18961,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="88"/>
+      <c r="A93" s="74"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -18981,7 +18989,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="88"/>
+      <c r="A94" s="74"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -19009,7 +19017,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="88"/>
+      <c r="A95" s="74"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -19037,7 +19045,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="88"/>
+      <c r="A96" s="74"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -19065,7 +19073,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="89"/>
+      <c r="A97" s="75"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -19135,26 +19143,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="69" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="71"/>
+      <c r="A1" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="69"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="72"/>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="74"/>
+      <c r="A2" s="70"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="72"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -19187,7 +19195,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="75" t="s">
+      <c r="A4" s="94" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -19213,11 +19221,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="76"/>
+      <c r="A5" s="95"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -19241,7 +19249,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="76"/>
+      <c r="A6" s="95"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -19254,10 +19262,10 @@
       <c r="E6" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="150">
+      <c r="F6" s="66">
         <v>3</v>
       </c>
-      <c r="G6" s="150">
+      <c r="G6" s="66">
         <v>0</v>
       </c>
       <c r="H6" s="20" t="s">
@@ -19269,7 +19277,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="76"/>
+      <c r="A7" s="95"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -19282,10 +19290,10 @@
       <c r="E7" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="150">
-        <v>1</v>
-      </c>
-      <c r="G7" s="150">
+      <c r="F7" s="66">
+        <v>1</v>
+      </c>
+      <c r="G7" s="66">
         <v>1</v>
       </c>
       <c r="H7" s="20" t="s">
@@ -19297,7 +19305,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="76"/>
+      <c r="A8" s="95"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -19325,7 +19333,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="77"/>
+      <c r="A9" s="96"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -19387,7 +19395,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="78" t="s">
+      <c r="A12" s="97" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -19413,7 +19421,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="79"/>
+      <c r="A13" s="98"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -19437,7 +19445,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="79"/>
+      <c r="A14" s="98"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -19450,10 +19458,10 @@
       <c r="E14" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F14" s="150">
-        <v>1</v>
-      </c>
-      <c r="G14" s="150">
+      <c r="F14" s="66">
+        <v>1</v>
+      </c>
+      <c r="G14" s="66">
         <v>0</v>
       </c>
       <c r="H14" s="21" t="s">
@@ -19465,7 +19473,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="79"/>
+      <c r="A15" s="98"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -19478,10 +19486,10 @@
       <c r="E15" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="F15" s="150">
-        <v>2</v>
-      </c>
-      <c r="G15" s="150">
+      <c r="F15" s="66">
+        <v>2</v>
+      </c>
+      <c r="G15" s="66">
         <v>1</v>
       </c>
       <c r="H15" s="21" t="s">
@@ -19493,7 +19501,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="79"/>
+      <c r="A16" s="98"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -19521,7 +19529,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="80"/>
+      <c r="A17" s="99"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -19583,7 +19591,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="81" t="s">
+      <c r="A20" s="100" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -19609,7 +19617,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="82"/>
+      <c r="A21" s="101"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -19637,7 +19645,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="82"/>
+      <c r="A22" s="101"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -19659,13 +19667,13 @@
       <c r="H22" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="J22" s="1" t="str">
+      <c r="J22" s="1">
         <f>IF(OR(Resultados!F22="",Resultados!G22=""),"",IF(AND(F22=Resultados!F22,G22=Resultados!G22),2,IF(((F22&gt;G22)=(Resultados!F22&gt;Resultados!G22))*((F22&lt;G22)=(Resultados!F22&lt;Resultados!G22)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="82"/>
+      <c r="A23" s="101"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -19693,7 +19701,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="82"/>
+      <c r="A24" s="101"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -19721,7 +19729,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="83"/>
+      <c r="A25" s="102"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -19783,7 +19791,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="66" t="s">
+      <c r="A28" s="103" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -19809,7 +19817,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="67"/>
+      <c r="A29" s="104"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -19837,7 +19845,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="67"/>
+      <c r="A30" s="104"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -19859,13 +19867,13 @@
       <c r="H30" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="J30" s="1" t="str">
+      <c r="J30" s="1">
         <f>IF(OR(Resultados!F30="",Resultados!G30=""),"",IF(AND(F30=Resultados!F30,G30=Resultados!G30),2,IF(((F30&gt;G30)=(Resultados!F30&gt;Resultados!G30))*((F30&lt;G30)=(Resultados!F30&lt;Resultados!G30)),1,0)))</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="67"/>
+      <c r="A31" s="104"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -19893,7 +19901,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="67"/>
+      <c r="A32" s="104"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -19917,7 +19925,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="68"/>
+      <c r="A33" s="105"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -19975,7 +19983,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="90" t="s">
+      <c r="A36" s="106" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -20005,7 +20013,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="91"/>
+      <c r="A37" s="107"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -20033,7 +20041,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="91"/>
+      <c r="A38" s="107"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -20057,7 +20065,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="91"/>
+      <c r="A39" s="107"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -20081,7 +20089,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="91"/>
+      <c r="A40" s="107"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -20105,7 +20113,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="92"/>
+      <c r="A41" s="108"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -20163,7 +20171,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="93" t="s">
+      <c r="A44" s="76" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -20193,7 +20201,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="94"/>
+      <c r="A45" s="77"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -20221,7 +20229,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="94"/>
+      <c r="A46" s="77"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -20245,7 +20253,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="94"/>
+      <c r="A47" s="77"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -20269,7 +20277,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="94"/>
+      <c r="A48" s="77"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -20293,7 +20301,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="95"/>
+      <c r="A49" s="78"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -20351,7 +20359,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="96" t="s">
+      <c r="A52" s="79" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -20381,7 +20389,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="97"/>
+      <c r="A53" s="80"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -20409,7 +20417,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="97"/>
+      <c r="A54" s="80"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -20433,7 +20441,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="97"/>
+      <c r="A55" s="80"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -20457,7 +20465,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="97"/>
+      <c r="A56" s="80"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -20481,7 +20489,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="98"/>
+      <c r="A57" s="81"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -20539,7 +20547,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="99" t="s">
+      <c r="A60" s="82" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -20569,7 +20577,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="100"/>
+      <c r="A61" s="83"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -20597,7 +20605,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="100"/>
+      <c r="A62" s="83"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -20621,7 +20629,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="100"/>
+      <c r="A63" s="83"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -20645,7 +20653,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="100"/>
+      <c r="A64" s="83"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -20669,7 +20677,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="101"/>
+      <c r="A65" s="84"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -20727,7 +20735,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="102" t="s">
+      <c r="A68" s="85" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -20757,7 +20765,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="103"/>
+      <c r="A69" s="86"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -20785,7 +20793,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="103"/>
+      <c r="A70" s="86"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -20809,7 +20817,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="103"/>
+      <c r="A71" s="86"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -20833,7 +20841,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="103"/>
+      <c r="A72" s="86"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -20857,7 +20865,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="104"/>
+      <c r="A73" s="87"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -20915,7 +20923,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="105" t="s">
+      <c r="A76" s="88" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -20945,7 +20953,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="106"/>
+      <c r="A77" s="89"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -20973,7 +20981,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="106"/>
+      <c r="A78" s="89"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -20997,7 +21005,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="106"/>
+      <c r="A79" s="89"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -21021,7 +21029,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="106"/>
+      <c r="A80" s="89"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -21045,7 +21053,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="107"/>
+      <c r="A81" s="90"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -21103,7 +21111,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="84" t="s">
+      <c r="A84" s="91" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -21133,7 +21141,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="85"/>
+      <c r="A85" s="92"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -21161,7 +21169,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="85"/>
+      <c r="A86" s="92"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -21185,7 +21193,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="85"/>
+      <c r="A87" s="92"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -21209,7 +21217,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="85"/>
+      <c r="A88" s="92"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -21233,7 +21241,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="86"/>
+      <c r="A89" s="93"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -21291,7 +21299,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="87" t="s">
+      <c r="A92" s="73" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -21321,7 +21329,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="88"/>
+      <c r="A93" s="74"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -21349,7 +21357,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="88"/>
+      <c r="A94" s="74"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -21373,7 +21381,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="88"/>
+      <c r="A95" s="74"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -21397,7 +21405,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="88"/>
+      <c r="A96" s="74"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -21421,7 +21429,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="89"/>
+      <c r="A97" s="75"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -21487,26 +21495,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="69" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="71"/>
+      <c r="A1" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="69"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="72"/>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="74"/>
+      <c r="A2" s="70"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="72"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -21539,7 +21547,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="75" t="s">
+      <c r="A4" s="94" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -21565,11 +21573,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="76"/>
+      <c r="A5" s="95"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -21593,7 +21601,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="76"/>
+      <c r="A6" s="95"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -21621,7 +21629,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="76"/>
+      <c r="A7" s="95"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -21649,7 +21657,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="76"/>
+      <c r="A8" s="95"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -21677,7 +21685,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="77"/>
+      <c r="A9" s="96"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -21739,7 +21747,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="78" t="s">
+      <c r="A12" s="97" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -21765,7 +21773,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="79"/>
+      <c r="A13" s="98"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -21789,7 +21797,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="79"/>
+      <c r="A14" s="98"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -21817,7 +21825,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="79"/>
+      <c r="A15" s="98"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -21845,7 +21853,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="79"/>
+      <c r="A16" s="98"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -21873,7 +21881,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="80"/>
+      <c r="A17" s="99"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -21935,7 +21943,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="81" t="s">
+      <c r="A20" s="100" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -21961,7 +21969,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="82"/>
+      <c r="A21" s="101"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -21989,7 +21997,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="82"/>
+      <c r="A22" s="101"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -22011,13 +22019,13 @@
       <c r="H22" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="J22" s="1" t="str">
+      <c r="J22" s="1">
         <f>IF(OR(Resultados!F22="",Resultados!G22=""),"",IF(AND(F22=Resultados!F22,G22=Resultados!G22),2,IF(((F22&gt;G22)=(Resultados!F22&gt;Resultados!G22))*((F22&lt;G22)=(Resultados!F22&lt;Resultados!G22)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="82"/>
+      <c r="A23" s="101"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -22045,7 +22053,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="82"/>
+      <c r="A24" s="101"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -22073,7 +22081,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="83"/>
+      <c r="A25" s="102"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -22135,7 +22143,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="66" t="s">
+      <c r="A28" s="103" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -22161,7 +22169,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="67"/>
+      <c r="A29" s="104"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -22189,7 +22197,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="67"/>
+      <c r="A30" s="104"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -22211,13 +22219,13 @@
       <c r="H30" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="J30" s="1" t="str">
+      <c r="J30" s="1">
         <f>IF(OR(Resultados!F30="",Resultados!G30=""),"",IF(AND(F30=Resultados!F30,G30=Resultados!G30),2,IF(((F30&gt;G30)=(Resultados!F30&gt;Resultados!G30))*((F30&lt;G30)=(Resultados!F30&lt;Resultados!G30)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="67"/>
+      <c r="A31" s="104"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -22245,7 +22253,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="67"/>
+      <c r="A32" s="104"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -22273,7 +22281,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="68"/>
+      <c r="A33" s="105"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -22335,7 +22343,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="90" t="s">
+      <c r="A36" s="106" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -22365,7 +22373,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="91"/>
+      <c r="A37" s="107"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -22393,7 +22401,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="91"/>
+      <c r="A38" s="107"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -22421,7 +22429,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="91"/>
+      <c r="A39" s="107"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -22449,7 +22457,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="91"/>
+      <c r="A40" s="107"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -22477,7 +22485,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="92"/>
+      <c r="A41" s="108"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -22539,7 +22547,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="93" t="s">
+      <c r="A44" s="76" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -22569,7 +22577,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="94"/>
+      <c r="A45" s="77"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -22597,7 +22605,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="94"/>
+      <c r="A46" s="77"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -22625,7 +22633,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="94"/>
+      <c r="A47" s="77"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -22653,7 +22661,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="94"/>
+      <c r="A48" s="77"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -22681,7 +22689,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="95"/>
+      <c r="A49" s="78"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -22743,7 +22751,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="96" t="s">
+      <c r="A52" s="79" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -22773,7 +22781,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="97"/>
+      <c r="A53" s="80"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -22801,7 +22809,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="97"/>
+      <c r="A54" s="80"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -22829,7 +22837,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="97"/>
+      <c r="A55" s="80"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -22857,7 +22865,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="97"/>
+      <c r="A56" s="80"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -22885,7 +22893,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="98"/>
+      <c r="A57" s="81"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -22947,7 +22955,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="99" t="s">
+      <c r="A60" s="82" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -22977,7 +22985,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="100"/>
+      <c r="A61" s="83"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -23005,7 +23013,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="100"/>
+      <c r="A62" s="83"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -23033,7 +23041,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="100"/>
+      <c r="A63" s="83"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -23061,7 +23069,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="100"/>
+      <c r="A64" s="83"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -23089,7 +23097,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="101"/>
+      <c r="A65" s="84"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -23151,7 +23159,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="102" t="s">
+      <c r="A68" s="85" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -23181,7 +23189,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="103"/>
+      <c r="A69" s="86"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -23209,7 +23217,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="103"/>
+      <c r="A70" s="86"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -23237,7 +23245,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="103"/>
+      <c r="A71" s="86"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -23265,7 +23273,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="103"/>
+      <c r="A72" s="86"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -23293,7 +23301,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="104"/>
+      <c r="A73" s="87"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -23355,7 +23363,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="105" t="s">
+      <c r="A76" s="88" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -23385,7 +23393,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="106"/>
+      <c r="A77" s="89"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -23413,7 +23421,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="106"/>
+      <c r="A78" s="89"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -23441,7 +23449,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="106"/>
+      <c r="A79" s="89"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -23469,7 +23477,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="106"/>
+      <c r="A80" s="89"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -23497,7 +23505,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="107"/>
+      <c r="A81" s="90"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -23559,7 +23567,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="84" t="s">
+      <c r="A84" s="91" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -23589,7 +23597,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="85"/>
+      <c r="A85" s="92"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -23617,7 +23625,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="85"/>
+      <c r="A86" s="92"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -23645,7 +23653,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="85"/>
+      <c r="A87" s="92"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -23673,7 +23681,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="85"/>
+      <c r="A88" s="92"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -23701,7 +23709,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="86"/>
+      <c r="A89" s="93"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -23763,7 +23771,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="87" t="s">
+      <c r="A92" s="73" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -23793,7 +23801,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="88"/>
+      <c r="A93" s="74"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -23821,7 +23829,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="88"/>
+      <c r="A94" s="74"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -23849,7 +23857,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="88"/>
+      <c r="A95" s="74"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -23877,7 +23885,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="88"/>
+      <c r="A96" s="74"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -23905,7 +23913,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="89"/>
+      <c r="A97" s="75"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -23975,26 +23983,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="69" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="71"/>
+      <c r="A1" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="69"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="72"/>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="74"/>
+      <c r="A2" s="70"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="72"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -24027,7 +24035,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="75" t="s">
+      <c r="A4" s="94" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -24053,11 +24061,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="76"/>
+      <c r="A5" s="95"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -24081,7 +24089,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="76"/>
+      <c r="A6" s="95"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -24109,7 +24117,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="76"/>
+      <c r="A7" s="95"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -24137,7 +24145,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="76"/>
+      <c r="A8" s="95"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -24165,7 +24173,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="77"/>
+      <c r="A9" s="96"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -24227,7 +24235,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="78" t="s">
+      <c r="A12" s="97" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -24253,7 +24261,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="79"/>
+      <c r="A13" s="98"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -24277,7 +24285,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="79"/>
+      <c r="A14" s="98"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -24305,7 +24313,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="79"/>
+      <c r="A15" s="98"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -24333,7 +24341,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="79"/>
+      <c r="A16" s="98"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -24361,7 +24369,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="80"/>
+      <c r="A17" s="99"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -24423,7 +24431,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="81" t="s">
+      <c r="A20" s="100" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -24449,7 +24457,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="82"/>
+      <c r="A21" s="101"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -24477,7 +24485,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="82"/>
+      <c r="A22" s="101"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -24499,13 +24507,13 @@
       <c r="H22" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="J22" s="1" t="str">
+      <c r="J22" s="1">
         <f>IF(OR(Resultados!F22="",Resultados!G22=""),"",IF(AND(F22=Resultados!F22,G22=Resultados!G22),2,IF(((F22&gt;G22)=(Resultados!F22&gt;Resultados!G22))*((F22&lt;G22)=(Resultados!F22&lt;Resultados!G22)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="82"/>
+      <c r="A23" s="101"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -24533,7 +24541,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="82"/>
+      <c r="A24" s="101"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -24561,7 +24569,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="83"/>
+      <c r="A25" s="102"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -24623,7 +24631,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="66" t="s">
+      <c r="A28" s="103" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -24649,7 +24657,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="67"/>
+      <c r="A29" s="104"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -24677,7 +24685,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="67"/>
+      <c r="A30" s="104"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -24699,13 +24707,13 @@
       <c r="H30" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="J30" s="1" t="str">
+      <c r="J30" s="1">
         <f>IF(OR(Resultados!F30="",Resultados!G30=""),"",IF(AND(F30=Resultados!F30,G30=Resultados!G30),2,IF(((F30&gt;G30)=(Resultados!F30&gt;Resultados!G30))*((F30&lt;G30)=(Resultados!F30&lt;Resultados!G30)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="67"/>
+      <c r="A31" s="104"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -24733,7 +24741,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="67"/>
+      <c r="A32" s="104"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -24761,7 +24769,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="68"/>
+      <c r="A33" s="105"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -24823,7 +24831,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="90" t="s">
+      <c r="A36" s="106" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -24853,7 +24861,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="91"/>
+      <c r="A37" s="107"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -24881,7 +24889,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="91"/>
+      <c r="A38" s="107"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -24909,7 +24917,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="91"/>
+      <c r="A39" s="107"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -24937,7 +24945,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="91"/>
+      <c r="A40" s="107"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -24965,7 +24973,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="92"/>
+      <c r="A41" s="108"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -25027,7 +25035,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="93" t="s">
+      <c r="A44" s="76" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -25057,7 +25065,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="94"/>
+      <c r="A45" s="77"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -25085,7 +25093,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="94"/>
+      <c r="A46" s="77"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -25113,7 +25121,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="94"/>
+      <c r="A47" s="77"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -25141,7 +25149,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="94"/>
+      <c r="A48" s="77"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -25169,7 +25177,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="95"/>
+      <c r="A49" s="78"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -25231,7 +25239,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="96" t="s">
+      <c r="A52" s="79" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -25261,7 +25269,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="97"/>
+      <c r="A53" s="80"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -25289,7 +25297,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="97"/>
+      <c r="A54" s="80"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -25317,7 +25325,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="97"/>
+      <c r="A55" s="80"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -25345,7 +25353,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="97"/>
+      <c r="A56" s="80"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -25373,7 +25381,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="98"/>
+      <c r="A57" s="81"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -25435,7 +25443,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="99" t="s">
+      <c r="A60" s="82" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -25465,7 +25473,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="100"/>
+      <c r="A61" s="83"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -25493,7 +25501,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="100"/>
+      <c r="A62" s="83"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -25521,7 +25529,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="100"/>
+      <c r="A63" s="83"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -25549,7 +25557,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="100"/>
+      <c r="A64" s="83"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -25577,7 +25585,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="101"/>
+      <c r="A65" s="84"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -25639,7 +25647,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="102" t="s">
+      <c r="A68" s="85" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -25669,7 +25677,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="103"/>
+      <c r="A69" s="86"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -25697,7 +25705,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="103"/>
+      <c r="A70" s="86"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -25725,7 +25733,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="103"/>
+      <c r="A71" s="86"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -25753,7 +25761,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="103"/>
+      <c r="A72" s="86"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -25781,7 +25789,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="104"/>
+      <c r="A73" s="87"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -25843,7 +25851,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="105" t="s">
+      <c r="A76" s="88" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -25873,7 +25881,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="106"/>
+      <c r="A77" s="89"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -25901,7 +25909,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="106"/>
+      <c r="A78" s="89"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -25929,7 +25937,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="106"/>
+      <c r="A79" s="89"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -25957,7 +25965,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="106"/>
+      <c r="A80" s="89"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -25985,7 +25993,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="107"/>
+      <c r="A81" s="90"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -26047,7 +26055,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="84" t="s">
+      <c r="A84" s="91" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -26077,7 +26085,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="85"/>
+      <c r="A85" s="92"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -26105,7 +26113,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="85"/>
+      <c r="A86" s="92"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -26133,7 +26141,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="85"/>
+      <c r="A87" s="92"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -26161,7 +26169,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="85"/>
+      <c r="A88" s="92"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -26189,7 +26197,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="86"/>
+      <c r="A89" s="93"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -26251,7 +26259,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="87" t="s">
+      <c r="A92" s="73" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -26281,7 +26289,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="88"/>
+      <c r="A93" s="74"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -26309,7 +26317,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="88"/>
+      <c r="A94" s="74"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -26337,7 +26345,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="88"/>
+      <c r="A95" s="74"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -26365,7 +26373,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="88"/>
+      <c r="A96" s="74"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -26393,7 +26401,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="89"/>
+      <c r="A97" s="75"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>

--- a/data/Quiniela.xlsx
+++ b/data/Quiniela.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cindy\Desktop\QuinielaMundial\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B7048CD-B123-4B96-8F9B-1B08E4C3196B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{980172C7-F52C-4881-9CD5-2B416E024D10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{9503E40F-C0E1-49CE-B4EA-3C401754995E}"/>
   </bookViews>
@@ -1266,6 +1266,24 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="49" fontId="20" fillId="20" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="20" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="20" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="20" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="20" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="20" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1434,72 +1452,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="20" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="20" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="20" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="20" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="20" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="20" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1593,6 +1545,54 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1951,26 +1951,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="67" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="69"/>
+      <c r="A1" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
+      <c r="H1" s="75"/>
     </row>
     <row r="2" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="70"/>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
-      <c r="H2" s="72"/>
+      <c r="A2" s="76"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="78"/>
     </row>
     <row r="3" spans="1:8" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -1997,7 +1997,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="94" t="s">
+      <c r="A4" s="100" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -2023,7 +2023,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="95"/>
+      <c r="A5" s="101"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -2047,7 +2047,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="95"/>
+      <c r="A6" s="101"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -2071,7 +2071,7 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="95"/>
+      <c r="A7" s="101"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -2095,7 +2095,7 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="95"/>
+      <c r="A8" s="101"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -2115,7 +2115,7 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="96"/>
+      <c r="A9" s="102"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -2169,7 +2169,7 @@
       </c>
     </row>
     <row r="12" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="97" t="s">
+      <c r="A12" s="103" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -2195,7 +2195,7 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="98"/>
+      <c r="A13" s="104"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -2219,7 +2219,7 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="98"/>
+      <c r="A14" s="104"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -2243,7 +2243,7 @@
       </c>
     </row>
     <row r="15" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="98"/>
+      <c r="A15" s="104"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -2267,7 +2267,7 @@
       </c>
     </row>
     <row r="16" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="98"/>
+      <c r="A16" s="104"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -2287,7 +2287,7 @@
       </c>
     </row>
     <row r="17" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="99"/>
+      <c r="A17" s="105"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -2341,7 +2341,7 @@
       </c>
     </row>
     <row r="20" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="100" t="s">
+      <c r="A20" s="106" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -2367,7 +2367,7 @@
       </c>
     </row>
     <row r="21" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="101"/>
+      <c r="A21" s="107"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -2391,7 +2391,7 @@
       </c>
     </row>
     <row r="22" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="101"/>
+      <c r="A22" s="107"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -2404,18 +2404,18 @@
       <c r="E22" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="F22" s="25">
-        <v>0</v>
-      </c>
-      <c r="G22" s="25">
-        <v>1</v>
-      </c>
-      <c r="H22" s="21" t="s">
+      <c r="F22" s="66">
+        <v>0</v>
+      </c>
+      <c r="G22" s="66">
+        <v>1</v>
+      </c>
+      <c r="H22" s="27" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="101"/>
+      <c r="A23" s="107"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -2425,17 +2425,21 @@
       <c r="D23" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E23" s="10" t="s">
+      <c r="E23" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="F23" s="25"/>
-      <c r="G23" s="25"/>
+      <c r="F23" s="66">
+        <v>3</v>
+      </c>
+      <c r="G23" s="66">
+        <v>0</v>
+      </c>
       <c r="H23" s="21" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="101"/>
+      <c r="A24" s="107"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -2455,7 +2459,7 @@
       </c>
     </row>
     <row r="25" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="102"/>
+      <c r="A25" s="108"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -2509,7 +2513,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="103" t="s">
+      <c r="A28" s="109" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -2535,7 +2539,7 @@
       </c>
     </row>
     <row r="29" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="104"/>
+      <c r="A29" s="110"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -2559,7 +2563,7 @@
       </c>
     </row>
     <row r="30" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="104"/>
+      <c r="A30" s="110"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -2583,7 +2587,7 @@
       </c>
     </row>
     <row r="31" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="104"/>
+      <c r="A31" s="110"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -2596,14 +2600,18 @@
       <c r="E31" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="F31" s="25"/>
-      <c r="G31" s="25"/>
-      <c r="H31" s="21" t="s">
+      <c r="F31" s="66">
+        <v>0</v>
+      </c>
+      <c r="G31" s="66">
+        <v>1</v>
+      </c>
+      <c r="H31" s="27" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="104"/>
+      <c r="A32" s="110"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -2623,7 +2631,7 @@
       </c>
     </row>
     <row r="33" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="105"/>
+      <c r="A33" s="111"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -2677,7 +2685,7 @@
       </c>
     </row>
     <row r="36" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="106" t="s">
+      <c r="A36" s="112" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -2703,7 +2711,7 @@
       </c>
     </row>
     <row r="37" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="107"/>
+      <c r="A37" s="113"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -2727,7 +2735,7 @@
       </c>
     </row>
     <row r="38" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="107"/>
+      <c r="A38" s="113"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -2747,7 +2755,7 @@
       </c>
     </row>
     <row r="39" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="107"/>
+      <c r="A39" s="113"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -2767,7 +2775,7 @@
       </c>
     </row>
     <row r="40" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="107"/>
+      <c r="A40" s="113"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -2787,7 +2795,7 @@
       </c>
     </row>
     <row r="41" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="108"/>
+      <c r="A41" s="114"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -2841,7 +2849,7 @@
       </c>
     </row>
     <row r="44" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="76" t="s">
+      <c r="A44" s="82" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -2867,7 +2875,7 @@
       </c>
     </row>
     <row r="45" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="77"/>
+      <c r="A45" s="83"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -2891,7 +2899,7 @@
       </c>
     </row>
     <row r="46" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="77"/>
+      <c r="A46" s="83"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -2911,7 +2919,7 @@
       </c>
     </row>
     <row r="47" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="77"/>
+      <c r="A47" s="83"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -2931,7 +2939,7 @@
       </c>
     </row>
     <row r="48" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="77"/>
+      <c r="A48" s="83"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -2951,7 +2959,7 @@
       </c>
     </row>
     <row r="49" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="78"/>
+      <c r="A49" s="84"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -3005,7 +3013,7 @@
       </c>
     </row>
     <row r="52" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="79" t="s">
+      <c r="A52" s="85" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -3031,7 +3039,7 @@
       </c>
     </row>
     <row r="53" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="80"/>
+      <c r="A53" s="86"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -3055,7 +3063,7 @@
       </c>
     </row>
     <row r="54" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="80"/>
+      <c r="A54" s="86"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -3075,7 +3083,7 @@
       </c>
     </row>
     <row r="55" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="80"/>
+      <c r="A55" s="86"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -3095,7 +3103,7 @@
       </c>
     </row>
     <row r="56" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="80"/>
+      <c r="A56" s="86"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -3115,7 +3123,7 @@
       </c>
     </row>
     <row r="57" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="81"/>
+      <c r="A57" s="87"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -3169,7 +3177,7 @@
       </c>
     </row>
     <row r="60" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="82" t="s">
+      <c r="A60" s="88" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -3195,7 +3203,7 @@
       </c>
     </row>
     <row r="61" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="83"/>
+      <c r="A61" s="89"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -3219,7 +3227,7 @@
       </c>
     </row>
     <row r="62" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="83"/>
+      <c r="A62" s="89"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -3239,7 +3247,7 @@
       </c>
     </row>
     <row r="63" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="83"/>
+      <c r="A63" s="89"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -3259,7 +3267,7 @@
       </c>
     </row>
     <row r="64" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="83"/>
+      <c r="A64" s="89"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -3279,7 +3287,7 @@
       </c>
     </row>
     <row r="65" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="84"/>
+      <c r="A65" s="90"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -3333,7 +3341,7 @@
       </c>
     </row>
     <row r="68" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="85" t="s">
+      <c r="A68" s="91" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -3359,7 +3367,7 @@
       </c>
     </row>
     <row r="69" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="86"/>
+      <c r="A69" s="92"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -3383,7 +3391,7 @@
       </c>
     </row>
     <row r="70" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="86"/>
+      <c r="A70" s="92"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -3403,7 +3411,7 @@
       </c>
     </row>
     <row r="71" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="86"/>
+      <c r="A71" s="92"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -3423,7 +3431,7 @@
       </c>
     </row>
     <row r="72" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="86"/>
+      <c r="A72" s="92"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -3443,7 +3451,7 @@
       </c>
     </row>
     <row r="73" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="87"/>
+      <c r="A73" s="93"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -3497,7 +3505,7 @@
       </c>
     </row>
     <row r="76" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="88" t="s">
+      <c r="A76" s="94" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -3523,7 +3531,7 @@
       </c>
     </row>
     <row r="77" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="89"/>
+      <c r="A77" s="95"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -3547,7 +3555,7 @@
       </c>
     </row>
     <row r="78" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="89"/>
+      <c r="A78" s="95"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -3567,7 +3575,7 @@
       </c>
     </row>
     <row r="79" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="89"/>
+      <c r="A79" s="95"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -3587,7 +3595,7 @@
       </c>
     </row>
     <row r="80" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="89"/>
+      <c r="A80" s="95"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -3607,7 +3615,7 @@
       </c>
     </row>
     <row r="81" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="90"/>
+      <c r="A81" s="96"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -3661,7 +3669,7 @@
       </c>
     </row>
     <row r="84" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="91" t="s">
+      <c r="A84" s="97" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -3687,7 +3695,7 @@
       </c>
     </row>
     <row r="85" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="92"/>
+      <c r="A85" s="98"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -3700,10 +3708,10 @@
       <c r="E85" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="F85" s="26">
-        <v>1</v>
-      </c>
-      <c r="G85" s="26">
+      <c r="F85" s="62">
+        <v>1</v>
+      </c>
+      <c r="G85" s="62">
         <v>3</v>
       </c>
       <c r="H85" s="27" t="s">
@@ -3711,7 +3719,7 @@
       </c>
     </row>
     <row r="86" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="92"/>
+      <c r="A86" s="98"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -3731,7 +3739,7 @@
       </c>
     </row>
     <row r="87" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="92"/>
+      <c r="A87" s="98"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -3751,7 +3759,7 @@
       </c>
     </row>
     <row r="88" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="92"/>
+      <c r="A88" s="98"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -3771,7 +3779,7 @@
       </c>
     </row>
     <row r="89" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="93"/>
+      <c r="A89" s="99"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -3825,7 +3833,7 @@
       </c>
     </row>
     <row r="92" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="73" t="s">
+      <c r="A92" s="79" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -3840,10 +3848,10 @@
       <c r="E92" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="F92" s="26">
+      <c r="F92" s="62">
         <v>4</v>
       </c>
-      <c r="G92" s="26">
+      <c r="G92" s="62">
         <v>2</v>
       </c>
       <c r="H92" s="21" t="s">
@@ -3851,7 +3859,7 @@
       </c>
     </row>
     <row r="93" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="74"/>
+      <c r="A93" s="80"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -3864,10 +3872,10 @@
       <c r="E93" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="F93" s="26">
-        <v>1</v>
-      </c>
-      <c r="G93" s="26">
+      <c r="F93" s="62">
+        <v>1</v>
+      </c>
+      <c r="G93" s="62">
         <v>0</v>
       </c>
       <c r="H93" s="21" t="s">
@@ -3875,7 +3883,7 @@
       </c>
     </row>
     <row r="94" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="74"/>
+      <c r="A94" s="80"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -3895,7 +3903,7 @@
       </c>
     </row>
     <row r="95" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="74"/>
+      <c r="A95" s="80"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -3915,7 +3923,7 @@
       </c>
     </row>
     <row r="96" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="74"/>
+      <c r="A96" s="80"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -3935,7 +3943,7 @@
       </c>
     </row>
     <row r="97" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="75"/>
+      <c r="A97" s="81"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -3995,26 +4003,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="67" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="69"/>
+      <c r="A1" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
+      <c r="H1" s="75"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="70"/>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
-      <c r="H2" s="72"/>
+      <c r="A2" s="76"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="78"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -4047,7 +4055,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="94" t="s">
+      <c r="A4" s="100" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -4073,11 +4081,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="95"/>
+      <c r="A5" s="101"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -4101,7 +4109,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="95"/>
+      <c r="A6" s="101"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -4129,7 +4137,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="95"/>
+      <c r="A7" s="101"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -4157,7 +4165,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="95"/>
+      <c r="A8" s="101"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -4185,7 +4193,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="96"/>
+      <c r="A9" s="102"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -4247,7 +4255,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="97" t="s">
+      <c r="A12" s="103" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -4273,7 +4281,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="98"/>
+      <c r="A13" s="104"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -4297,7 +4305,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="98"/>
+      <c r="A14" s="104"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -4325,7 +4333,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="98"/>
+      <c r="A15" s="104"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -4353,7 +4361,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="98"/>
+      <c r="A16" s="104"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -4381,7 +4389,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="99"/>
+      <c r="A17" s="105"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -4443,7 +4451,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="100" t="s">
+      <c r="A20" s="106" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -4469,7 +4477,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="101"/>
+      <c r="A21" s="107"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -4497,7 +4505,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="101"/>
+      <c r="A22" s="107"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -4519,13 +4527,13 @@
       <c r="H22" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="J22" s="1">
+      <c r="J22" s="65">
         <f>IF(OR(Resultados!F22="",Resultados!G22=""),"",IF(AND(F22=Resultados!F22,G22=Resultados!G22),2,IF(((F22&gt;G22)=(Resultados!F22&gt;Resultados!G22))*((F22&lt;G22)=(Resultados!F22&lt;Resultados!G22)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="101"/>
+      <c r="A23" s="107"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -4547,13 +4555,13 @@
       <c r="H23" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="J23" s="1" t="str">
+      <c r="J23" s="65">
         <f>IF(OR(Resultados!F23="",Resultados!G23=""),"",IF(AND(F23=Resultados!F23,G23=Resultados!G23),2,IF(((F23&gt;G23)=(Resultados!F23&gt;Resultados!G23))*((F23&lt;G23)=(Resultados!F23&lt;Resultados!G23)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="101"/>
+      <c r="A24" s="107"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -4581,7 +4589,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="102"/>
+      <c r="A25" s="108"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -4643,7 +4651,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="103" t="s">
+      <c r="A28" s="109" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -4669,7 +4677,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="104"/>
+      <c r="A29" s="110"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -4697,7 +4705,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="104"/>
+      <c r="A30" s="110"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -4719,13 +4727,13 @@
       <c r="H30" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="J30" s="1">
+      <c r="J30" s="64">
         <f>IF(OR(Resultados!F30="",Resultados!G30=""),"",IF(AND(F30=Resultados!F30,G30=Resultados!G30),2,IF(((F30&gt;G30)=(Resultados!F30&gt;Resultados!G30))*((F30&lt;G30)=(Resultados!F30&lt;Resultados!G30)),1,0)))</f>
         <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="104"/>
+      <c r="A31" s="110"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -4747,13 +4755,13 @@
       <c r="H31" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="J31" s="1" t="str">
+      <c r="J31" s="1">
         <f>IF(OR(Resultados!F31="",Resultados!G31=""),"",IF(AND(F31=Resultados!F31,G31=Resultados!G31),2,IF(((F31&gt;G31)=(Resultados!F31&gt;Resultados!G31))*((F31&lt;G31)=(Resultados!F31&lt;Resultados!G31)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="104"/>
+      <c r="A32" s="110"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -4781,7 +4789,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="105"/>
+      <c r="A33" s="111"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -4843,7 +4851,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="106" t="s">
+      <c r="A36" s="112" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -4873,7 +4881,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="107"/>
+      <c r="A37" s="113"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -4901,7 +4909,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="107"/>
+      <c r="A38" s="113"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -4929,7 +4937,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="107"/>
+      <c r="A39" s="113"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -4957,7 +4965,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="107"/>
+      <c r="A40" s="113"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -4985,7 +4993,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="108"/>
+      <c r="A41" s="114"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -5047,7 +5055,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="76" t="s">
+      <c r="A44" s="82" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -5077,7 +5085,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="77"/>
+      <c r="A45" s="83"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -5105,7 +5113,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="77"/>
+      <c r="A46" s="83"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -5133,7 +5141,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="77"/>
+      <c r="A47" s="83"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -5161,7 +5169,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="77"/>
+      <c r="A48" s="83"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -5189,7 +5197,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="78"/>
+      <c r="A49" s="84"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -5251,7 +5259,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="79" t="s">
+      <c r="A52" s="85" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -5281,7 +5289,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="80"/>
+      <c r="A53" s="86"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -5309,7 +5317,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="80"/>
+      <c r="A54" s="86"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -5337,7 +5345,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="80"/>
+      <c r="A55" s="86"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -5365,7 +5373,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="80"/>
+      <c r="A56" s="86"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -5393,7 +5401,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="81"/>
+      <c r="A57" s="87"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -5455,7 +5463,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="82" t="s">
+      <c r="A60" s="88" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -5485,7 +5493,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="83"/>
+      <c r="A61" s="89"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -5513,7 +5521,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="83"/>
+      <c r="A62" s="89"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -5541,7 +5549,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="83"/>
+      <c r="A63" s="89"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -5569,7 +5577,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="83"/>
+      <c r="A64" s="89"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -5597,7 +5605,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="84"/>
+      <c r="A65" s="90"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -5659,7 +5667,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="85" t="s">
+      <c r="A68" s="91" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -5689,7 +5697,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="86"/>
+      <c r="A69" s="92"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -5717,7 +5725,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="86"/>
+      <c r="A70" s="92"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -5745,7 +5753,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="86"/>
+      <c r="A71" s="92"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -5773,7 +5781,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="86"/>
+      <c r="A72" s="92"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -5801,7 +5809,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="87"/>
+      <c r="A73" s="93"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -5863,7 +5871,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="88" t="s">
+      <c r="A76" s="94" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -5893,7 +5901,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="89"/>
+      <c r="A77" s="95"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -5921,7 +5929,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="89"/>
+      <c r="A78" s="95"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -5949,7 +5957,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="89"/>
+      <c r="A79" s="95"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -5977,7 +5985,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="89"/>
+      <c r="A80" s="95"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -6005,7 +6013,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="90"/>
+      <c r="A81" s="96"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -6067,7 +6075,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="91" t="s">
+      <c r="A84" s="97" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -6097,7 +6105,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="92"/>
+      <c r="A85" s="98"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -6125,7 +6133,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="92"/>
+      <c r="A86" s="98"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -6153,7 +6161,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="92"/>
+      <c r="A87" s="98"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -6181,7 +6189,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="92"/>
+      <c r="A88" s="98"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -6209,7 +6217,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="93"/>
+      <c r="A89" s="99"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -6271,7 +6279,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="73" t="s">
+      <c r="A92" s="79" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -6301,7 +6309,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="74"/>
+      <c r="A93" s="80"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -6329,7 +6337,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="74"/>
+      <c r="A94" s="80"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -6357,7 +6365,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="74"/>
+      <c r="A95" s="80"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -6385,7 +6393,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="74"/>
+      <c r="A96" s="80"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -6413,7 +6421,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="75"/>
+      <c r="A97" s="81"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -6442,6 +6450,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A28:A33"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:A9"/>
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="A20:A25"/>
     <mergeCell ref="A84:A89"/>
     <mergeCell ref="A92:A97"/>
     <mergeCell ref="A36:A41"/>
@@ -6450,12 +6464,6 @@
     <mergeCell ref="A60:A65"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="A76:A81"/>
-    <mergeCell ref="A28:A33"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A4:A9"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="A20:A25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -6483,26 +6491,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="67" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="69"/>
+      <c r="A1" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
+      <c r="H1" s="75"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="70"/>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
-      <c r="H2" s="72"/>
+      <c r="A2" s="76"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="78"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -6535,7 +6543,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="94" t="s">
+      <c r="A4" s="100" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -6561,11 +6569,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="95"/>
+      <c r="A5" s="101"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -6589,7 +6597,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="95"/>
+      <c r="A6" s="101"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -6617,7 +6625,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="95"/>
+      <c r="A7" s="101"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -6645,7 +6653,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="95"/>
+      <c r="A8" s="101"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -6673,7 +6681,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="96"/>
+      <c r="A9" s="102"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -6735,7 +6743,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="97" t="s">
+      <c r="A12" s="103" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -6761,7 +6769,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="98"/>
+      <c r="A13" s="104"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -6785,7 +6793,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="98"/>
+      <c r="A14" s="104"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -6813,7 +6821,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="98"/>
+      <c r="A15" s="104"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -6841,7 +6849,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="98"/>
+      <c r="A16" s="104"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -6869,7 +6877,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="99"/>
+      <c r="A17" s="105"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -6931,7 +6939,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="100" t="s">
+      <c r="A20" s="106" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -6957,7 +6965,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="101"/>
+      <c r="A21" s="107"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -6985,7 +6993,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="101"/>
+      <c r="A22" s="107"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -7007,13 +7015,13 @@
       <c r="H22" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="J22" s="1">
+      <c r="J22" s="65">
         <f>IF(OR(Resultados!F22="",Resultados!G22=""),"",IF(AND(F22=Resultados!F22,G22=Resultados!G22),2,IF(((F22&gt;G22)=(Resultados!F22&gt;Resultados!G22))*((F22&lt;G22)=(Resultados!F22&lt;Resultados!G22)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="101"/>
+      <c r="A23" s="107"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -7035,13 +7043,13 @@
       <c r="H23" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="J23" s="1" t="str">
+      <c r="J23" s="65">
         <f>IF(OR(Resultados!F23="",Resultados!G23=""),"",IF(AND(F23=Resultados!F23,G23=Resultados!G23),2,IF(((F23&gt;G23)=(Resultados!F23&gt;Resultados!G23))*((F23&lt;G23)=(Resultados!F23&lt;Resultados!G23)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="101"/>
+      <c r="A24" s="107"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -7069,7 +7077,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="102"/>
+      <c r="A25" s="108"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -7131,7 +7139,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="103" t="s">
+      <c r="A28" s="109" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -7157,7 +7165,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="104"/>
+      <c r="A29" s="110"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -7185,7 +7193,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="104"/>
+      <c r="A30" s="110"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -7207,13 +7215,13 @@
       <c r="H30" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="J30" s="1">
+      <c r="J30" s="65">
         <f>IF(OR(Resultados!F30="",Resultados!G30=""),"",IF(AND(F30=Resultados!F30,G30=Resultados!G30),2,IF(((F30&gt;G30)=(Resultados!F30&gt;Resultados!G30))*((F30&lt;G30)=(Resultados!F30&lt;Resultados!G30)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="104"/>
+      <c r="A31" s="110"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -7235,13 +7243,13 @@
       <c r="H31" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="J31" s="1" t="str">
+      <c r="J31" s="1">
         <f>IF(OR(Resultados!F31="",Resultados!G31=""),"",IF(AND(F31=Resultados!F31,G31=Resultados!G31),2,IF(((F31&gt;G31)=(Resultados!F31&gt;Resultados!G31))*((F31&lt;G31)=(Resultados!F31&lt;Resultados!G31)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="104"/>
+      <c r="A32" s="110"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -7269,7 +7277,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="105"/>
+      <c r="A33" s="111"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -7331,7 +7339,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="106" t="s">
+      <c r="A36" s="112" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -7361,7 +7369,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="107"/>
+      <c r="A37" s="113"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -7389,7 +7397,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="107"/>
+      <c r="A38" s="113"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -7417,7 +7425,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="107"/>
+      <c r="A39" s="113"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -7445,7 +7453,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="107"/>
+      <c r="A40" s="113"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -7473,7 +7481,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="108"/>
+      <c r="A41" s="114"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -7535,7 +7543,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="76" t="s">
+      <c r="A44" s="82" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -7565,7 +7573,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="77"/>
+      <c r="A45" s="83"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -7593,7 +7601,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="77"/>
+      <c r="A46" s="83"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -7621,7 +7629,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="77"/>
+      <c r="A47" s="83"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -7649,7 +7657,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="77"/>
+      <c r="A48" s="83"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -7677,7 +7685,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="78"/>
+      <c r="A49" s="84"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -7739,7 +7747,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="79" t="s">
+      <c r="A52" s="85" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -7769,7 +7777,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="80"/>
+      <c r="A53" s="86"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -7797,7 +7805,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="80"/>
+      <c r="A54" s="86"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -7825,7 +7833,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="80"/>
+      <c r="A55" s="86"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -7853,7 +7861,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="80"/>
+      <c r="A56" s="86"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -7881,7 +7889,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="81"/>
+      <c r="A57" s="87"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -7943,7 +7951,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="82" t="s">
+      <c r="A60" s="88" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -7973,7 +7981,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="83"/>
+      <c r="A61" s="89"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -8001,7 +8009,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="83"/>
+      <c r="A62" s="89"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -8029,7 +8037,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="83"/>
+      <c r="A63" s="89"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -8057,7 +8065,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="83"/>
+      <c r="A64" s="89"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -8085,7 +8093,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="84"/>
+      <c r="A65" s="90"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -8147,7 +8155,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="85" t="s">
+      <c r="A68" s="91" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -8177,7 +8185,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="86"/>
+      <c r="A69" s="92"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -8205,7 +8213,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="86"/>
+      <c r="A70" s="92"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -8233,7 +8241,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="86"/>
+      <c r="A71" s="92"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -8261,7 +8269,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="86"/>
+      <c r="A72" s="92"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -8289,7 +8297,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="87"/>
+      <c r="A73" s="93"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -8351,7 +8359,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="88" t="s">
+      <c r="A76" s="94" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -8381,7 +8389,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="89"/>
+      <c r="A77" s="95"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -8409,7 +8417,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="89"/>
+      <c r="A78" s="95"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -8437,7 +8445,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="89"/>
+      <c r="A79" s="95"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -8465,7 +8473,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="89"/>
+      <c r="A80" s="95"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -8493,7 +8501,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="90"/>
+      <c r="A81" s="96"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -8555,7 +8563,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="91" t="s">
+      <c r="A84" s="97" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -8585,7 +8593,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="92"/>
+      <c r="A85" s="98"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -8613,7 +8621,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="92"/>
+      <c r="A86" s="98"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -8641,7 +8649,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="92"/>
+      <c r="A87" s="98"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -8669,7 +8677,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="92"/>
+      <c r="A88" s="98"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -8697,7 +8705,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="93"/>
+      <c r="A89" s="99"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -8759,7 +8767,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="73" t="s">
+      <c r="A92" s="79" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -8789,7 +8797,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="74"/>
+      <c r="A93" s="80"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -8817,7 +8825,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="74"/>
+      <c r="A94" s="80"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -8845,7 +8853,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="74"/>
+      <c r="A95" s="80"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -8873,7 +8881,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="74"/>
+      <c r="A96" s="80"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -8901,7 +8909,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="75"/>
+      <c r="A97" s="81"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -8930,6 +8938,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A28:A33"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:A9"/>
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="A20:A25"/>
     <mergeCell ref="A84:A89"/>
     <mergeCell ref="A92:A97"/>
     <mergeCell ref="A36:A41"/>
@@ -8938,12 +8952,6 @@
     <mergeCell ref="A60:A65"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="A76:A81"/>
-    <mergeCell ref="A28:A33"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A4:A9"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="A20:A25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -8966,18 +8974,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D1" s="109" t="s">
+      <c r="D1" s="67" t="s">
         <v>74</v>
       </c>
-      <c r="E1" s="110"/>
-      <c r="F1" s="111"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="69"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D2" s="112" t="s">
+      <c r="D2" s="70" t="s">
         <v>75</v>
       </c>
-      <c r="E2" s="113"/>
-      <c r="F2" s="114"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="72"/>
     </row>
     <row r="4" spans="1:6" s="29" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="57" t="s">
@@ -9002,7 +9010,7 @@
       </c>
       <c r="B5" s="58">
         <f>Cindy!L4</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D5" s="59">
         <v>1</v>
@@ -9012,7 +9020,7 @@
         <v>Erik</v>
       </c>
       <c r="F5" s="59">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -9021,16 +9029,16 @@
       </c>
       <c r="B6" s="58">
         <f>Wendy!L4</f>
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D6" s="55">
         <v>2</v>
       </c>
       <c r="E6" s="55" t="str">
-        <v>Packy</v>
+        <v>Bere</v>
       </c>
       <c r="F6" s="55">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -9039,16 +9047,16 @@
       </c>
       <c r="B7" s="58">
         <f>Jimmy!L4</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D7" s="56">
         <v>3</v>
       </c>
       <c r="E7" s="56" t="str">
-        <v>Bere</v>
+        <v>Packy</v>
       </c>
       <c r="F7" s="56">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -9057,16 +9065,16 @@
       </c>
       <c r="B8" s="58">
         <f>Erick!L4</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D8" s="28">
         <v>4</v>
       </c>
       <c r="E8" s="28" t="str">
-        <v>Jimmy</v>
+        <v>Wendy</v>
       </c>
       <c r="F8" s="28">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -9075,7 +9083,7 @@
       </c>
       <c r="B9" s="58">
         <f>Erik!L4</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D9" s="28">
         <v>5</v>
@@ -9084,7 +9092,7 @@
         <v>Cindy</v>
       </c>
       <c r="F9" s="28">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -9093,16 +9101,16 @@
       </c>
       <c r="B10" s="58">
         <f>Lennon!L4</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D10" s="28">
         <v>6</v>
       </c>
       <c r="E10" s="28" t="str">
-        <v>Wendy</v>
+        <v>Jimmy</v>
       </c>
       <c r="F10" s="28">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -9111,7 +9119,7 @@
       </c>
       <c r="B11" s="58">
         <f>Yulian!L4</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D11" s="28">
         <v>7</v>
@@ -9120,7 +9128,7 @@
         <v>Lennon</v>
       </c>
       <c r="F11" s="28">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -9129,7 +9137,7 @@
       </c>
       <c r="B12" s="58">
         <f>Packy!L4</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D12" s="28">
         <v>8</v>
@@ -9138,7 +9146,7 @@
         <v>Yulian</v>
       </c>
       <c r="F12" s="28">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -9147,7 +9155,7 @@
       </c>
       <c r="B13" s="58">
         <f>Bere!L4</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D13" s="28">
         <v>9</v>
@@ -9156,7 +9164,7 @@
         <v>Erick</v>
       </c>
       <c r="F13" s="28">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -9190,26 +9198,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="67" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="69"/>
+      <c r="A1" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
+      <c r="H1" s="75"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="70"/>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
-      <c r="H2" s="72"/>
+      <c r="A2" s="76"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="78"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="31"/>
@@ -9242,7 +9250,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="118" t="s">
+      <c r="A4" s="142" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="35">
@@ -9268,11 +9276,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="119"/>
+      <c r="A5" s="143"/>
       <c r="B5" s="35">
         <v>46185</v>
       </c>
@@ -9296,7 +9304,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="119"/>
+      <c r="A6" s="143"/>
       <c r="B6" s="35">
         <v>46191</v>
       </c>
@@ -9324,7 +9332,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="119"/>
+      <c r="A7" s="143"/>
       <c r="B7" s="35">
         <v>46192</v>
       </c>
@@ -9352,7 +9360,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="119"/>
+      <c r="A8" s="143"/>
       <c r="B8" s="35">
         <v>46198</v>
       </c>
@@ -9380,7 +9388,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="120"/>
+      <c r="A9" s="144"/>
       <c r="B9" s="42">
         <v>46198</v>
       </c>
@@ -9442,7 +9450,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="121" t="s">
+      <c r="A12" s="145" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="35">
@@ -9468,7 +9476,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="122"/>
+      <c r="A13" s="146"/>
       <c r="B13" s="35">
         <v>46186</v>
       </c>
@@ -9492,7 +9500,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="122"/>
+      <c r="A14" s="146"/>
       <c r="B14" s="35">
         <v>46191</v>
       </c>
@@ -9514,13 +9522,13 @@
       <c r="H14" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="J14" s="1">
+      <c r="J14" s="65">
         <f>IF(OR(Resultados!F14="",Resultados!G14=""),"",IF(AND(F14=Resultados!F14,G14=Resultados!G14),2,IF(((F14&gt;G14)=(Resultados!F14&gt;Resultados!G14))*((F14&lt;G14)=(Resultados!F14&lt;Resultados!G14)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="122"/>
+      <c r="A15" s="146"/>
       <c r="B15" s="35">
         <v>46192</v>
       </c>
@@ -9542,13 +9550,13 @@
       <c r="H15" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="J15" s="1">
+      <c r="J15" s="65">
         <f>IF(OR(Resultados!F15="",Resultados!G15=""),"",IF(AND(F15=Resultados!F15,G15=Resultados!G15),2,IF(((F15&gt;G15)=(Resultados!F15&gt;Resultados!G15))*((F15&lt;G15)=(Resultados!F15&lt;Resultados!G15)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="122"/>
+      <c r="A16" s="146"/>
       <c r="B16" s="35">
         <v>46197</v>
       </c>
@@ -9576,7 +9584,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="123"/>
+      <c r="A17" s="147"/>
       <c r="B17" s="42">
         <v>46197</v>
       </c>
@@ -9638,7 +9646,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="124" t="s">
+      <c r="A20" s="148" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="35">
@@ -9664,7 +9672,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="125"/>
+      <c r="A21" s="149"/>
       <c r="B21" s="35">
         <v>46187</v>
       </c>
@@ -9692,7 +9700,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="125"/>
+      <c r="A22" s="149"/>
       <c r="B22" s="35">
         <v>46193</v>
       </c>
@@ -9714,13 +9722,13 @@
       <c r="H22" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="J22" s="1">
+      <c r="J22" s="64">
         <f>IF(OR(Resultados!F22="",Resultados!G22=""),"",IF(AND(F22=Resultados!F22,G22=Resultados!G22),2,IF(((F22&gt;G22)=(Resultados!F22&gt;Resultados!G22))*((F22&lt;G22)=(Resultados!F22&lt;Resultados!G22)),1,0)))</f>
         <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="125"/>
+      <c r="A23" s="149"/>
       <c r="B23" s="35">
         <v>46193</v>
       </c>
@@ -9742,13 +9750,13 @@
       <c r="H23" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="J23" s="1" t="str">
+      <c r="J23" s="64">
         <f>IF(OR(Resultados!F23="",Resultados!G23=""),"",IF(AND(F23=Resultados!F23,G23=Resultados!G23),2,IF(((F23&gt;G23)=(Resultados!F23&gt;Resultados!G23))*((F23&lt;G23)=(Resultados!F23&lt;Resultados!G23)),1,0)))</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="125"/>
+      <c r="A24" s="149"/>
       <c r="B24" s="35">
         <v>46198</v>
       </c>
@@ -9776,7 +9784,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="126"/>
+      <c r="A25" s="150"/>
       <c r="B25" s="42">
         <v>46198</v>
       </c>
@@ -9838,7 +9846,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="115" t="s">
+      <c r="A28" s="139" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="35">
@@ -9864,7 +9872,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="116"/>
+      <c r="A29" s="140"/>
       <c r="B29" s="35">
         <v>46187</v>
       </c>
@@ -9892,7 +9900,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="116"/>
+      <c r="A30" s="140"/>
       <c r="B30" s="35">
         <v>46192</v>
       </c>
@@ -9914,13 +9922,13 @@
       <c r="H30" s="46" t="s">
         <v>28</v>
       </c>
-      <c r="J30" s="1">
+      <c r="J30" s="65">
         <f>IF(OR(Resultados!F30="",Resultados!G30=""),"",IF(AND(F30=Resultados!F30,G30=Resultados!G30),2,IF(((F30&gt;G30)=(Resultados!F30&gt;Resultados!G30))*((F30&lt;G30)=(Resultados!F30&lt;Resultados!G30)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="116"/>
+      <c r="A31" s="140"/>
       <c r="B31" s="35">
         <v>46193</v>
       </c>
@@ -9942,13 +9950,13 @@
       <c r="H31" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="J31" s="1" t="str">
+      <c r="J31" s="1">
         <f>IF(OR(Resultados!F31="",Resultados!G31=""),"",IF(AND(F31=Resultados!F31,G31=Resultados!G31),2,IF(((F31&gt;G31)=(Resultados!F31&gt;Resultados!G31))*((F31&lt;G31)=(Resultados!F31&lt;Resultados!G31)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="116"/>
+      <c r="A32" s="140"/>
       <c r="B32" s="35">
         <v>46199</v>
       </c>
@@ -9976,7 +9984,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="117"/>
+      <c r="A33" s="141"/>
       <c r="B33" s="42">
         <v>46199</v>
       </c>
@@ -10038,7 +10046,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="133" t="s">
+      <c r="A36" s="121" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="35">
@@ -10068,7 +10076,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="134"/>
+      <c r="A37" s="122"/>
       <c r="B37" s="35">
         <v>46188</v>
       </c>
@@ -10096,7 +10104,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="134"/>
+      <c r="A38" s="122"/>
       <c r="B38" s="35">
         <v>46193</v>
       </c>
@@ -10124,7 +10132,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="134"/>
+      <c r="A39" s="122"/>
       <c r="B39" s="35">
         <v>46194</v>
       </c>
@@ -10152,7 +10160,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="134"/>
+      <c r="A40" s="122"/>
       <c r="B40" s="35">
         <v>46198</v>
       </c>
@@ -10180,7 +10188,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="135"/>
+      <c r="A41" s="123"/>
       <c r="B41" s="42">
         <v>46198</v>
       </c>
@@ -10242,7 +10250,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="136" t="s">
+      <c r="A44" s="124" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="35">
@@ -10272,7 +10280,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="137"/>
+      <c r="A45" s="125"/>
       <c r="B45" s="35">
         <v>46188</v>
       </c>
@@ -10300,7 +10308,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="137"/>
+      <c r="A46" s="125"/>
       <c r="B46" s="35">
         <v>46193</v>
       </c>
@@ -10328,7 +10336,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="137"/>
+      <c r="A47" s="125"/>
       <c r="B47" s="35">
         <v>46194</v>
       </c>
@@ -10356,7 +10364,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="137"/>
+      <c r="A48" s="125"/>
       <c r="B48" s="35">
         <v>46199</v>
       </c>
@@ -10384,7 +10392,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="138"/>
+      <c r="A49" s="126"/>
       <c r="B49" s="42">
         <v>46199</v>
       </c>
@@ -10446,7 +10454,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="139" t="s">
+      <c r="A52" s="127" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="35">
@@ -10476,7 +10484,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="140"/>
+      <c r="A53" s="128"/>
       <c r="B53" s="35">
         <v>46189</v>
       </c>
@@ -10504,7 +10512,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="140"/>
+      <c r="A54" s="128"/>
       <c r="B54" s="35">
         <v>46194</v>
       </c>
@@ -10532,7 +10540,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="140"/>
+      <c r="A55" s="128"/>
       <c r="B55" s="35">
         <v>46195</v>
       </c>
@@ -10560,7 +10568,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="140"/>
+      <c r="A56" s="128"/>
       <c r="B56" s="35">
         <v>46200</v>
       </c>
@@ -10588,7 +10596,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="141"/>
+      <c r="A57" s="129"/>
       <c r="B57" s="42">
         <v>46200</v>
       </c>
@@ -10650,7 +10658,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="142" t="s">
+      <c r="A60" s="130" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="35">
@@ -10680,7 +10688,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="143"/>
+      <c r="A61" s="131"/>
       <c r="B61" s="35">
         <v>46189</v>
       </c>
@@ -10708,7 +10716,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="143"/>
+      <c r="A62" s="131"/>
       <c r="B62" s="35">
         <v>46194</v>
       </c>
@@ -10736,7 +10744,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="143"/>
+      <c r="A63" s="131"/>
       <c r="B63" s="35">
         <v>46195</v>
       </c>
@@ -10764,7 +10772,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="143"/>
+      <c r="A64" s="131"/>
       <c r="B64" s="35">
         <v>46200</v>
       </c>
@@ -10792,7 +10800,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="144"/>
+      <c r="A65" s="132"/>
       <c r="B65" s="42">
         <v>46200</v>
       </c>
@@ -10854,7 +10862,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="145" t="s">
+      <c r="A68" s="133" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="35">
@@ -10884,7 +10892,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="146"/>
+      <c r="A69" s="134"/>
       <c r="B69" s="35">
         <v>46190</v>
       </c>
@@ -10912,7 +10920,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="146"/>
+      <c r="A70" s="134"/>
       <c r="B70" s="35">
         <v>46195</v>
       </c>
@@ -10940,7 +10948,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="146"/>
+      <c r="A71" s="134"/>
       <c r="B71" s="35">
         <v>46196</v>
       </c>
@@ -10968,7 +10976,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="146"/>
+      <c r="A72" s="134"/>
       <c r="B72" s="35">
         <v>46199</v>
       </c>
@@ -10996,7 +11004,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="147"/>
+      <c r="A73" s="135"/>
       <c r="B73" s="42">
         <v>46199</v>
       </c>
@@ -11058,7 +11066,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="148" t="s">
+      <c r="A76" s="136" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="35">
@@ -11088,7 +11096,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="149"/>
+      <c r="A77" s="137"/>
       <c r="B77" s="35">
         <v>46190</v>
       </c>
@@ -11116,7 +11124,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="149"/>
+      <c r="A78" s="137"/>
       <c r="B78" s="35">
         <v>46195</v>
       </c>
@@ -11144,7 +11152,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="149"/>
+      <c r="A79" s="137"/>
       <c r="B79" s="35">
         <v>46196</v>
       </c>
@@ -11172,7 +11180,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="149"/>
+      <c r="A80" s="137"/>
       <c r="B80" s="35">
         <v>46201</v>
       </c>
@@ -11200,7 +11208,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="150"/>
+      <c r="A81" s="138"/>
       <c r="B81" s="42">
         <v>46201</v>
       </c>
@@ -11262,7 +11270,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="127" t="s">
+      <c r="A84" s="115" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="35">
@@ -11292,7 +11300,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="128"/>
+      <c r="A85" s="116"/>
       <c r="B85" s="35">
         <v>46191</v>
       </c>
@@ -11320,7 +11328,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="128"/>
+      <c r="A86" s="116"/>
       <c r="B86" s="35">
         <v>46196</v>
       </c>
@@ -11348,7 +11356,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="128"/>
+      <c r="A87" s="116"/>
       <c r="B87" s="35">
         <v>46197</v>
       </c>
@@ -11376,7 +11384,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="128"/>
+      <c r="A88" s="116"/>
       <c r="B88" s="35">
         <v>46201</v>
       </c>
@@ -11404,7 +11412,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="129"/>
+      <c r="A89" s="117"/>
       <c r="B89" s="42">
         <v>46201</v>
       </c>
@@ -11466,7 +11474,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="130" t="s">
+      <c r="A92" s="118" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="35">
@@ -11496,7 +11504,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="131"/>
+      <c r="A93" s="119"/>
       <c r="B93" s="35">
         <v>46191</v>
       </c>
@@ -11524,7 +11532,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="131"/>
+      <c r="A94" s="119"/>
       <c r="B94" s="35">
         <v>46196</v>
       </c>
@@ -11552,7 +11560,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="131"/>
+      <c r="A95" s="119"/>
       <c r="B95" s="35">
         <v>46197</v>
       </c>
@@ -11580,7 +11588,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="131"/>
+      <c r="A96" s="119"/>
       <c r="B96" s="35">
         <v>46200</v>
       </c>
@@ -11608,7 +11616,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="132"/>
+      <c r="A97" s="120"/>
       <c r="B97" s="42">
         <v>46200</v>
       </c>
@@ -11637,6 +11645,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A28:A33"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:A9"/>
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="A20:A25"/>
     <mergeCell ref="A84:A89"/>
     <mergeCell ref="A92:A97"/>
     <mergeCell ref="A36:A41"/>
@@ -11645,12 +11659,6 @@
     <mergeCell ref="A60:A65"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="A76:A81"/>
-    <mergeCell ref="A28:A33"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A4:A9"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="A20:A25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -11679,26 +11687,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="67" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="69"/>
+      <c r="A1" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
+      <c r="H1" s="75"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="70"/>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
-      <c r="H2" s="72"/>
+      <c r="A2" s="76"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="78"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="31"/>
@@ -11731,7 +11739,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="118" t="s">
+      <c r="A4" s="142" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="35">
@@ -11757,11 +11765,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="119"/>
+      <c r="A5" s="143"/>
       <c r="B5" s="35">
         <v>46185</v>
       </c>
@@ -11785,7 +11793,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="119"/>
+      <c r="A6" s="143"/>
       <c r="B6" s="35">
         <v>46191</v>
       </c>
@@ -11813,7 +11821,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="119"/>
+      <c r="A7" s="143"/>
       <c r="B7" s="35">
         <v>46192</v>
       </c>
@@ -11841,7 +11849,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="119"/>
+      <c r="A8" s="143"/>
       <c r="B8" s="35">
         <v>46198</v>
       </c>
@@ -11869,7 +11877,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="120"/>
+      <c r="A9" s="144"/>
       <c r="B9" s="42">
         <v>46198</v>
       </c>
@@ -11931,7 +11939,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="121" t="s">
+      <c r="A12" s="145" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="35">
@@ -11957,7 +11965,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="122"/>
+      <c r="A13" s="146"/>
       <c r="B13" s="35">
         <v>46186</v>
       </c>
@@ -11981,7 +11989,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="122"/>
+      <c r="A14" s="146"/>
       <c r="B14" s="35">
         <v>46191</v>
       </c>
@@ -12003,13 +12011,13 @@
       <c r="H14" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="J14" s="1">
+      <c r="J14" s="65">
         <f>IF(OR(Resultados!F14="",Resultados!G14=""),"",IF(AND(F14=Resultados!F14,G14=Resultados!G14),2,IF(((F14&gt;G14)=(Resultados!F14&gt;Resultados!G14))*((F14&lt;G14)=(Resultados!F14&lt;Resultados!G14)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="122"/>
+      <c r="A15" s="146"/>
       <c r="B15" s="35">
         <v>46192</v>
       </c>
@@ -12031,13 +12039,13 @@
       <c r="H15" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="J15" s="1">
+      <c r="J15" s="65">
         <f>IF(OR(Resultados!F15="",Resultados!G15=""),"",IF(AND(F15=Resultados!F15,G15=Resultados!G15),2,IF(((F15&gt;G15)=(Resultados!F15&gt;Resultados!G15))*((F15&lt;G15)=(Resultados!F15&lt;Resultados!G15)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="122"/>
+      <c r="A16" s="146"/>
       <c r="B16" s="35">
         <v>46197</v>
       </c>
@@ -12065,7 +12073,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="123"/>
+      <c r="A17" s="147"/>
       <c r="B17" s="42">
         <v>46197</v>
       </c>
@@ -12127,7 +12135,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="124" t="s">
+      <c r="A20" s="148" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="35">
@@ -12153,7 +12161,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="125"/>
+      <c r="A21" s="149"/>
       <c r="B21" s="35">
         <v>46187</v>
       </c>
@@ -12181,7 +12189,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="125"/>
+      <c r="A22" s="149"/>
       <c r="B22" s="35">
         <v>46193</v>
       </c>
@@ -12209,7 +12217,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="125"/>
+      <c r="A23" s="149"/>
       <c r="B23" s="35">
         <v>46193</v>
       </c>
@@ -12231,13 +12239,13 @@
       <c r="H23" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="J23" s="1" t="str">
+      <c r="J23" s="65">
         <f>IF(OR(Resultados!F23="",Resultados!G23=""),"",IF(AND(F23=Resultados!F23,G23=Resultados!G23),2,IF(((F23&gt;G23)=(Resultados!F23&gt;Resultados!G23))*((F23&lt;G23)=(Resultados!F23&lt;Resultados!G23)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="125"/>
+      <c r="A24" s="149"/>
       <c r="B24" s="35">
         <v>46198</v>
       </c>
@@ -12265,7 +12273,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="126"/>
+      <c r="A25" s="150"/>
       <c r="B25" s="42">
         <v>46198</v>
       </c>
@@ -12327,7 +12335,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="115" t="s">
+      <c r="A28" s="139" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="35">
@@ -12353,7 +12361,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="116"/>
+      <c r="A29" s="140"/>
       <c r="B29" s="35">
         <v>46187</v>
       </c>
@@ -12381,7 +12389,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="116"/>
+      <c r="A30" s="140"/>
       <c r="B30" s="35">
         <v>46192</v>
       </c>
@@ -12403,13 +12411,13 @@
       <c r="H30" s="46" t="s">
         <v>28</v>
       </c>
-      <c r="J30" s="1">
+      <c r="J30" s="65">
         <f>IF(OR(Resultados!F30="",Resultados!G30=""),"",IF(AND(F30=Resultados!F30,G30=Resultados!G30),2,IF(((F30&gt;G30)=(Resultados!F30&gt;Resultados!G30))*((F30&lt;G30)=(Resultados!F30&lt;Resultados!G30)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="116"/>
+      <c r="A31" s="140"/>
       <c r="B31" s="35">
         <v>46193</v>
       </c>
@@ -12431,13 +12439,13 @@
       <c r="H31" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="J31" s="1" t="str">
+      <c r="J31" s="64">
         <f>IF(OR(Resultados!F31="",Resultados!G31=""),"",IF(AND(F31=Resultados!F31,G31=Resultados!G31),2,IF(((F31&gt;G31)=(Resultados!F31&gt;Resultados!G31))*((F31&lt;G31)=(Resultados!F31&lt;Resultados!G31)),1,0)))</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="116"/>
+      <c r="A32" s="140"/>
       <c r="B32" s="35">
         <v>46199</v>
       </c>
@@ -12465,7 +12473,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="117"/>
+      <c r="A33" s="141"/>
       <c r="B33" s="42">
         <v>46199</v>
       </c>
@@ -12527,7 +12535,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="133" t="s">
+      <c r="A36" s="121" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="35">
@@ -12557,7 +12565,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="134"/>
+      <c r="A37" s="122"/>
       <c r="B37" s="35">
         <v>46188</v>
       </c>
@@ -12585,7 +12593,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="134"/>
+      <c r="A38" s="122"/>
       <c r="B38" s="35">
         <v>46193</v>
       </c>
@@ -12613,7 +12621,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="134"/>
+      <c r="A39" s="122"/>
       <c r="B39" s="35">
         <v>46194</v>
       </c>
@@ -12641,7 +12649,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="134"/>
+      <c r="A40" s="122"/>
       <c r="B40" s="35">
         <v>46198</v>
       </c>
@@ -12669,7 +12677,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="135"/>
+      <c r="A41" s="123"/>
       <c r="B41" s="42">
         <v>46198</v>
       </c>
@@ -12731,7 +12739,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="136" t="s">
+      <c r="A44" s="124" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="35">
@@ -12761,7 +12769,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="137"/>
+      <c r="A45" s="125"/>
       <c r="B45" s="35">
         <v>46188</v>
       </c>
@@ -12789,7 +12797,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="137"/>
+      <c r="A46" s="125"/>
       <c r="B46" s="35">
         <v>46193</v>
       </c>
@@ -12817,7 +12825,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="137"/>
+      <c r="A47" s="125"/>
       <c r="B47" s="35">
         <v>46194</v>
       </c>
@@ -12845,7 +12853,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="137"/>
+      <c r="A48" s="125"/>
       <c r="B48" s="35">
         <v>46199</v>
       </c>
@@ -12873,7 +12881,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="138"/>
+      <c r="A49" s="126"/>
       <c r="B49" s="42">
         <v>46199</v>
       </c>
@@ -12935,7 +12943,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="139" t="s">
+      <c r="A52" s="127" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="35">
@@ -12965,7 +12973,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="140"/>
+      <c r="A53" s="128"/>
       <c r="B53" s="35">
         <v>46189</v>
       </c>
@@ -12993,7 +13001,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="140"/>
+      <c r="A54" s="128"/>
       <c r="B54" s="35">
         <v>46194</v>
       </c>
@@ -13021,7 +13029,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="140"/>
+      <c r="A55" s="128"/>
       <c r="B55" s="35">
         <v>46195</v>
       </c>
@@ -13049,7 +13057,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="140"/>
+      <c r="A56" s="128"/>
       <c r="B56" s="35">
         <v>46200</v>
       </c>
@@ -13077,7 +13085,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="141"/>
+      <c r="A57" s="129"/>
       <c r="B57" s="42">
         <v>46200</v>
       </c>
@@ -13139,7 +13147,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="142" t="s">
+      <c r="A60" s="130" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="35">
@@ -13169,7 +13177,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="143"/>
+      <c r="A61" s="131"/>
       <c r="B61" s="35">
         <v>46189</v>
       </c>
@@ -13197,7 +13205,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="143"/>
+      <c r="A62" s="131"/>
       <c r="B62" s="35">
         <v>46194</v>
       </c>
@@ -13225,7 +13233,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="143"/>
+      <c r="A63" s="131"/>
       <c r="B63" s="35">
         <v>46195</v>
       </c>
@@ -13253,7 +13261,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="143"/>
+      <c r="A64" s="131"/>
       <c r="B64" s="35">
         <v>46200</v>
       </c>
@@ -13281,7 +13289,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="144"/>
+      <c r="A65" s="132"/>
       <c r="B65" s="42">
         <v>46200</v>
       </c>
@@ -13343,7 +13351,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="145" t="s">
+      <c r="A68" s="133" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="35">
@@ -13367,13 +13375,13 @@
       <c r="H68" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="J68" s="1">
+      <c r="J68" s="64">
         <f>IF(OR(Resultados!F68="",Resultados!G68=""),"",IF(AND(F68=Resultados!F68,G68=Resultados!G68),2,IF(((F68&gt;G68)=(Resultados!F68&gt;Resultados!G68))*((F68&lt;G68)=(Resultados!F68&lt;Resultados!G68)),1,0)))</f>
         <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="146"/>
+      <c r="A69" s="134"/>
       <c r="B69" s="35">
         <v>46190</v>
       </c>
@@ -13401,7 +13409,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="146"/>
+      <c r="A70" s="134"/>
       <c r="B70" s="35">
         <v>46195</v>
       </c>
@@ -13429,7 +13437,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="146"/>
+      <c r="A71" s="134"/>
       <c r="B71" s="35">
         <v>46196</v>
       </c>
@@ -13457,7 +13465,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="146"/>
+      <c r="A72" s="134"/>
       <c r="B72" s="35">
         <v>46199</v>
       </c>
@@ -13485,7 +13493,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="147"/>
+      <c r="A73" s="135"/>
       <c r="B73" s="42">
         <v>46199</v>
       </c>
@@ -13547,7 +13555,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="148" t="s">
+      <c r="A76" s="136" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="35">
@@ -13571,13 +13579,13 @@
       <c r="H76" s="46" t="s">
         <v>57</v>
       </c>
-      <c r="J76" s="1">
+      <c r="J76" s="64">
         <f>IF(OR(Resultados!F76="",Resultados!G76=""),"",IF(AND(F76=Resultados!F76,G76=Resultados!G76),2,IF(((F76&gt;G76)=(Resultados!F76&gt;Resultados!G76))*((F76&lt;G76)=(Resultados!F76&lt;Resultados!G76)),1,0)))</f>
         <v>2</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="149"/>
+      <c r="A77" s="137"/>
       <c r="B77" s="35">
         <v>46190</v>
       </c>
@@ -13605,7 +13613,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="149"/>
+      <c r="A78" s="137"/>
       <c r="B78" s="35">
         <v>46195</v>
       </c>
@@ -13633,7 +13641,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="149"/>
+      <c r="A79" s="137"/>
       <c r="B79" s="35">
         <v>46196</v>
       </c>
@@ -13661,7 +13669,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="149"/>
+      <c r="A80" s="137"/>
       <c r="B80" s="35">
         <v>46201</v>
       </c>
@@ -13689,7 +13697,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="150"/>
+      <c r="A81" s="138"/>
       <c r="B81" s="42">
         <v>46201</v>
       </c>
@@ -13751,7 +13759,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="127" t="s">
+      <c r="A84" s="115" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="35">
@@ -13781,7 +13789,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="128"/>
+      <c r="A85" s="116"/>
       <c r="B85" s="35">
         <v>46191</v>
       </c>
@@ -13809,7 +13817,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="128"/>
+      <c r="A86" s="116"/>
       <c r="B86" s="35">
         <v>46196</v>
       </c>
@@ -13837,7 +13845,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="128"/>
+      <c r="A87" s="116"/>
       <c r="B87" s="35">
         <v>46197</v>
       </c>
@@ -13865,7 +13873,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="128"/>
+      <c r="A88" s="116"/>
       <c r="B88" s="35">
         <v>46201</v>
       </c>
@@ -13893,7 +13901,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="129"/>
+      <c r="A89" s="117"/>
       <c r="B89" s="42">
         <v>46201</v>
       </c>
@@ -13955,7 +13963,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="130" t="s">
+      <c r="A92" s="118" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="35">
@@ -13985,7 +13993,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="131"/>
+      <c r="A93" s="119"/>
       <c r="B93" s="35">
         <v>46191</v>
       </c>
@@ -14013,7 +14021,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="131"/>
+      <c r="A94" s="119"/>
       <c r="B94" s="35">
         <v>46196</v>
       </c>
@@ -14041,7 +14049,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="131"/>
+      <c r="A95" s="119"/>
       <c r="B95" s="35">
         <v>46197</v>
       </c>
@@ -14069,7 +14077,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="131"/>
+      <c r="A96" s="119"/>
       <c r="B96" s="35">
         <v>46200</v>
       </c>
@@ -14097,7 +14105,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="132"/>
+      <c r="A97" s="120"/>
       <c r="B97" s="42">
         <v>46200</v>
       </c>
@@ -14126,6 +14134,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A28:A33"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:A9"/>
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="A20:A25"/>
     <mergeCell ref="A84:A89"/>
     <mergeCell ref="A92:A97"/>
     <mergeCell ref="A36:A41"/>
@@ -14134,12 +14148,6 @@
     <mergeCell ref="A60:A65"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="A76:A81"/>
-    <mergeCell ref="A28:A33"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A4:A9"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="A20:A25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -14167,26 +14175,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="67" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="69"/>
+      <c r="A1" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
+      <c r="H1" s="75"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="70"/>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
-      <c r="H2" s="72"/>
+      <c r="A2" s="76"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="78"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -14219,7 +14227,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="94" t="s">
+      <c r="A4" s="100" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -14245,11 +14253,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="95"/>
+      <c r="A5" s="101"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -14273,7 +14281,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="95"/>
+      <c r="A6" s="101"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -14301,7 +14309,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="95"/>
+      <c r="A7" s="101"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -14329,7 +14337,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="95"/>
+      <c r="A8" s="101"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -14357,7 +14365,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="96"/>
+      <c r="A9" s="102"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -14419,7 +14427,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="97" t="s">
+      <c r="A12" s="103" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -14445,7 +14453,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="98"/>
+      <c r="A13" s="104"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -14469,7 +14477,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="98"/>
+      <c r="A14" s="104"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -14491,13 +14499,13 @@
       <c r="H14" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="J14" s="1">
+      <c r="J14" s="65">
         <f>IF(OR(Resultados!F14="",Resultados!G14=""),"",IF(AND(F14=Resultados!F14,G14=Resultados!G14),2,IF(((F14&gt;G14)=(Resultados!F14&gt;Resultados!G14))*((F14&lt;G14)=(Resultados!F14&lt;Resultados!G14)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="98"/>
+      <c r="A15" s="104"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -14519,13 +14527,13 @@
       <c r="H15" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="J15" s="1">
+      <c r="J15" s="65">
         <f>IF(OR(Resultados!F15="",Resultados!G15=""),"",IF(AND(F15=Resultados!F15,G15=Resultados!G15),2,IF(((F15&gt;G15)=(Resultados!F15&gt;Resultados!G15))*((F15&lt;G15)=(Resultados!F15&lt;Resultados!G15)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="98"/>
+      <c r="A16" s="104"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -14553,7 +14561,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="99"/>
+      <c r="A17" s="105"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -14615,7 +14623,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="100" t="s">
+      <c r="A20" s="106" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -14641,7 +14649,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="101"/>
+      <c r="A21" s="107"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -14669,7 +14677,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="101"/>
+      <c r="A22" s="107"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -14691,13 +14699,13 @@
       <c r="H22" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="J22" s="1">
+      <c r="J22" s="65">
         <f>IF(OR(Resultados!F22="",Resultados!G22=""),"",IF(AND(F22=Resultados!F22,G22=Resultados!G22),2,IF(((F22&gt;G22)=(Resultados!F22&gt;Resultados!G22))*((F22&lt;G22)=(Resultados!F22&lt;Resultados!G22)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="101"/>
+      <c r="A23" s="107"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -14719,13 +14727,13 @@
       <c r="H23" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="J23" s="1" t="str">
+      <c r="J23" s="65">
         <f>IF(OR(Resultados!F23="",Resultados!G23=""),"",IF(AND(F23=Resultados!F23,G23=Resultados!G23),2,IF(((F23&gt;G23)=(Resultados!F23&gt;Resultados!G23))*((F23&lt;G23)=(Resultados!F23&lt;Resultados!G23)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="101"/>
+      <c r="A24" s="107"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -14753,7 +14761,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="102"/>
+      <c r="A25" s="108"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -14815,7 +14823,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="103" t="s">
+      <c r="A28" s="109" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -14841,7 +14849,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="104"/>
+      <c r="A29" s="110"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -14869,7 +14877,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="104"/>
+      <c r="A30" s="110"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -14897,7 +14905,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="104"/>
+      <c r="A31" s="110"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -14919,13 +14927,13 @@
       <c r="H31" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="J31" s="1" t="str">
+      <c r="J31" s="1">
         <f>IF(OR(Resultados!F31="",Resultados!G31=""),"",IF(AND(F31=Resultados!F31,G31=Resultados!G31),2,IF(((F31&gt;G31)=(Resultados!F31&gt;Resultados!G31))*((F31&lt;G31)=(Resultados!F31&lt;Resultados!G31)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="104"/>
+      <c r="A32" s="110"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -14953,7 +14961,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="105"/>
+      <c r="A33" s="111"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -15015,7 +15023,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="106" t="s">
+      <c r="A36" s="112" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -15045,7 +15053,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="107"/>
+      <c r="A37" s="113"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -15073,7 +15081,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="107"/>
+      <c r="A38" s="113"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -15101,7 +15109,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="107"/>
+      <c r="A39" s="113"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -15129,7 +15137,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="107"/>
+      <c r="A40" s="113"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -15157,7 +15165,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="108"/>
+      <c r="A41" s="114"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -15219,7 +15227,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="76" t="s">
+      <c r="A44" s="82" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -15249,7 +15257,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="77"/>
+      <c r="A45" s="83"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -15277,7 +15285,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="77"/>
+      <c r="A46" s="83"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -15305,7 +15313,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="77"/>
+      <c r="A47" s="83"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -15333,7 +15341,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="77"/>
+      <c r="A48" s="83"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -15361,7 +15369,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="78"/>
+      <c r="A49" s="84"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -15423,7 +15431,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="79" t="s">
+      <c r="A52" s="85" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -15453,7 +15461,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="80"/>
+      <c r="A53" s="86"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -15481,7 +15489,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="80"/>
+      <c r="A54" s="86"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -15509,7 +15517,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="80"/>
+      <c r="A55" s="86"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -15537,7 +15545,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="80"/>
+      <c r="A56" s="86"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -15565,7 +15573,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="81"/>
+      <c r="A57" s="87"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -15627,7 +15635,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="82" t="s">
+      <c r="A60" s="88" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -15657,7 +15665,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="83"/>
+      <c r="A61" s="89"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -15685,7 +15693,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="83"/>
+      <c r="A62" s="89"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -15713,7 +15721,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="83"/>
+      <c r="A63" s="89"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -15741,7 +15749,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="83"/>
+      <c r="A64" s="89"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -15769,7 +15777,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="84"/>
+      <c r="A65" s="90"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -15831,7 +15839,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="85" t="s">
+      <c r="A68" s="91" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -15861,7 +15869,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="86"/>
+      <c r="A69" s="92"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -15889,7 +15897,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="86"/>
+      <c r="A70" s="92"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -15917,7 +15925,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="86"/>
+      <c r="A71" s="92"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -15945,7 +15953,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="86"/>
+      <c r="A72" s="92"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -15973,7 +15981,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="87"/>
+      <c r="A73" s="93"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -16035,7 +16043,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="88" t="s">
+      <c r="A76" s="94" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -16065,7 +16073,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="89"/>
+      <c r="A77" s="95"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -16093,7 +16101,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="89"/>
+      <c r="A78" s="95"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -16121,7 +16129,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="89"/>
+      <c r="A79" s="95"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -16149,7 +16157,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="89"/>
+      <c r="A80" s="95"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -16177,7 +16185,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="90"/>
+      <c r="A81" s="96"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -16239,7 +16247,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="91" t="s">
+      <c r="A84" s="97" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -16269,7 +16277,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="92"/>
+      <c r="A85" s="98"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -16297,7 +16305,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="92"/>
+      <c r="A86" s="98"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -16325,7 +16333,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="92"/>
+      <c r="A87" s="98"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -16353,7 +16361,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="92"/>
+      <c r="A88" s="98"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -16381,7 +16389,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="93"/>
+      <c r="A89" s="99"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -16443,7 +16451,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="73" t="s">
+      <c r="A92" s="79" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -16473,7 +16481,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="74"/>
+      <c r="A93" s="80"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -16501,7 +16509,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="74"/>
+      <c r="A94" s="80"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -16529,7 +16537,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="74"/>
+      <c r="A95" s="80"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -16557,7 +16565,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="74"/>
+      <c r="A96" s="80"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -16585,7 +16593,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="75"/>
+      <c r="A97" s="81"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -16614,6 +16622,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A28:A33"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:A9"/>
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="A20:A25"/>
     <mergeCell ref="A84:A89"/>
     <mergeCell ref="A92:A97"/>
     <mergeCell ref="A36:A41"/>
@@ -16622,12 +16636,6 @@
     <mergeCell ref="A60:A65"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="A76:A81"/>
-    <mergeCell ref="A28:A33"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A4:A9"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="A20:A25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -16655,26 +16663,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="67" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="69"/>
+      <c r="A1" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
+      <c r="H1" s="75"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="70"/>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
-      <c r="H2" s="72"/>
+      <c r="A2" s="76"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="78"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -16707,7 +16715,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="94" t="s">
+      <c r="A4" s="100" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -16733,11 +16741,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="95"/>
+      <c r="A5" s="101"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -16761,7 +16769,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="95"/>
+      <c r="A6" s="101"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -16789,7 +16797,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="95"/>
+      <c r="A7" s="101"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -16817,7 +16825,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="95"/>
+      <c r="A8" s="101"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -16845,7 +16853,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="96"/>
+      <c r="A9" s="102"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -16907,7 +16915,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="97" t="s">
+      <c r="A12" s="103" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -16933,7 +16941,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="98"/>
+      <c r="A13" s="104"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -16957,7 +16965,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="98"/>
+      <c r="A14" s="104"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -16985,7 +16993,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="98"/>
+      <c r="A15" s="104"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -17007,13 +17015,13 @@
       <c r="H15" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="J15" s="1">
+      <c r="J15" s="65">
         <f>IF(OR(Resultados!F15="",Resultados!G15=""),"",IF(AND(F15=Resultados!F15,G15=Resultados!G15),2,IF(((F15&gt;G15)=(Resultados!F15&gt;Resultados!G15))*((F15&lt;G15)=(Resultados!F15&lt;Resultados!G15)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="98"/>
+      <c r="A16" s="104"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -17041,7 +17049,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="99"/>
+      <c r="A17" s="105"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -17103,7 +17111,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="100" t="s">
+      <c r="A20" s="106" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -17129,7 +17137,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="101"/>
+      <c r="A21" s="107"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -17157,7 +17165,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="101"/>
+      <c r="A22" s="107"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -17179,13 +17187,13 @@
       <c r="H22" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="J22" s="1">
+      <c r="J22" s="64">
         <f>IF(OR(Resultados!F22="",Resultados!G22=""),"",IF(AND(F22=Resultados!F22,G22=Resultados!G22),2,IF(((F22&gt;G22)=(Resultados!F22&gt;Resultados!G22))*((F22&lt;G22)=(Resultados!F22&lt;Resultados!G22)),1,0)))</f>
         <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="101"/>
+      <c r="A23" s="107"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -17207,13 +17215,13 @@
       <c r="H23" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="J23" s="1" t="str">
+      <c r="J23" s="1">
         <f>IF(OR(Resultados!F23="",Resultados!G23=""),"",IF(AND(F23=Resultados!F23,G23=Resultados!G23),2,IF(((F23&gt;G23)=(Resultados!F23&gt;Resultados!G23))*((F23&lt;G23)=(Resultados!F23&lt;Resultados!G23)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="101"/>
+      <c r="A24" s="107"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -17241,7 +17249,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="102"/>
+      <c r="A25" s="108"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -17303,7 +17311,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="103" t="s">
+      <c r="A28" s="109" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -17329,7 +17337,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="104"/>
+      <c r="A29" s="110"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -17357,7 +17365,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="104"/>
+      <c r="A30" s="110"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -17379,13 +17387,13 @@
       <c r="H30" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="J30" s="1">
+      <c r="J30" s="65">
         <f>IF(OR(Resultados!F30="",Resultados!G30=""),"",IF(AND(F30=Resultados!F30,G30=Resultados!G30),2,IF(((F30&gt;G30)=(Resultados!F30&gt;Resultados!G30))*((F30&lt;G30)=(Resultados!F30&lt;Resultados!G30)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="104"/>
+      <c r="A31" s="110"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -17407,13 +17415,13 @@
       <c r="H31" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="J31" s="1" t="str">
+      <c r="J31" s="1">
         <f>IF(OR(Resultados!F31="",Resultados!G31=""),"",IF(AND(F31=Resultados!F31,G31=Resultados!G31),2,IF(((F31&gt;G31)=(Resultados!F31&gt;Resultados!G31))*((F31&lt;G31)=(Resultados!F31&lt;Resultados!G31)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="104"/>
+      <c r="A32" s="110"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -17441,7 +17449,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="105"/>
+      <c r="A33" s="111"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -17503,7 +17511,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="106" t="s">
+      <c r="A36" s="112" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -17533,7 +17541,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="107"/>
+      <c r="A37" s="113"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -17561,7 +17569,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="107"/>
+      <c r="A38" s="113"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -17589,7 +17597,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="107"/>
+      <c r="A39" s="113"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -17617,7 +17625,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="107"/>
+      <c r="A40" s="113"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -17645,7 +17653,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="108"/>
+      <c r="A41" s="114"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -17707,7 +17715,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="76" t="s">
+      <c r="A44" s="82" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -17737,7 +17745,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="77"/>
+      <c r="A45" s="83"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -17765,7 +17773,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="77"/>
+      <c r="A46" s="83"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -17793,7 +17801,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="77"/>
+      <c r="A47" s="83"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -17821,7 +17829,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="77"/>
+      <c r="A48" s="83"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -17849,7 +17857,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="78"/>
+      <c r="A49" s="84"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -17911,7 +17919,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="79" t="s">
+      <c r="A52" s="85" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -17941,7 +17949,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="80"/>
+      <c r="A53" s="86"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -17969,7 +17977,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="80"/>
+      <c r="A54" s="86"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -17997,7 +18005,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="80"/>
+      <c r="A55" s="86"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -18025,7 +18033,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="80"/>
+      <c r="A56" s="86"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -18053,7 +18061,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="81"/>
+      <c r="A57" s="87"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -18115,7 +18123,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="82" t="s">
+      <c r="A60" s="88" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -18145,7 +18153,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="83"/>
+      <c r="A61" s="89"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -18173,7 +18181,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="83"/>
+      <c r="A62" s="89"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -18201,7 +18209,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="83"/>
+      <c r="A63" s="89"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -18229,7 +18237,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="83"/>
+      <c r="A64" s="89"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -18257,7 +18265,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="84"/>
+      <c r="A65" s="90"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -18319,7 +18327,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="85" t="s">
+      <c r="A68" s="91" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -18349,7 +18357,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="86"/>
+      <c r="A69" s="92"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -18377,7 +18385,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="86"/>
+      <c r="A70" s="92"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -18405,7 +18413,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="86"/>
+      <c r="A71" s="92"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -18433,7 +18441,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="86"/>
+      <c r="A72" s="92"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -18461,7 +18469,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="87"/>
+      <c r="A73" s="93"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -18523,7 +18531,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="88" t="s">
+      <c r="A76" s="94" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -18553,7 +18561,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="89"/>
+      <c r="A77" s="95"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -18581,7 +18589,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="89"/>
+      <c r="A78" s="95"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -18609,7 +18617,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="89"/>
+      <c r="A79" s="95"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -18637,7 +18645,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="89"/>
+      <c r="A80" s="95"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -18665,7 +18673,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="90"/>
+      <c r="A81" s="96"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -18727,7 +18735,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="91" t="s">
+      <c r="A84" s="97" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -18757,7 +18765,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="92"/>
+      <c r="A85" s="98"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -18785,7 +18793,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="92"/>
+      <c r="A86" s="98"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -18813,7 +18821,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="92"/>
+      <c r="A87" s="98"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -18841,7 +18849,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="92"/>
+      <c r="A88" s="98"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -18869,7 +18877,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="93"/>
+      <c r="A89" s="99"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -18931,7 +18939,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="73" t="s">
+      <c r="A92" s="79" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -18961,7 +18969,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="74"/>
+      <c r="A93" s="80"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -18989,7 +18997,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="74"/>
+      <c r="A94" s="80"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -19017,7 +19025,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="74"/>
+      <c r="A95" s="80"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -19045,7 +19053,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="74"/>
+      <c r="A96" s="80"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -19073,7 +19081,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="75"/>
+      <c r="A97" s="81"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -19102,6 +19110,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A28:A33"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:A9"/>
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="A20:A25"/>
     <mergeCell ref="A84:A89"/>
     <mergeCell ref="A92:A97"/>
     <mergeCell ref="A36:A41"/>
@@ -19110,12 +19124,6 @@
     <mergeCell ref="A60:A65"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="A76:A81"/>
-    <mergeCell ref="A28:A33"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A4:A9"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="A20:A25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19143,26 +19151,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="67" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="69"/>
+      <c r="A1" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
+      <c r="H1" s="75"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="70"/>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
-      <c r="H2" s="72"/>
+      <c r="A2" s="76"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="78"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -19195,7 +19203,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="94" t="s">
+      <c r="A4" s="100" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -19221,11 +19229,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="95"/>
+      <c r="A5" s="101"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -19249,7 +19257,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="95"/>
+      <c r="A6" s="101"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -19277,7 +19285,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="95"/>
+      <c r="A7" s="101"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -19305,7 +19313,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="95"/>
+      <c r="A8" s="101"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -19333,7 +19341,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="96"/>
+      <c r="A9" s="102"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -19395,7 +19403,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="97" t="s">
+      <c r="A12" s="103" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -19421,7 +19429,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="98"/>
+      <c r="A13" s="104"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -19445,7 +19453,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="98"/>
+      <c r="A14" s="104"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -19473,7 +19481,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="98"/>
+      <c r="A15" s="104"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -19501,7 +19509,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="98"/>
+      <c r="A16" s="104"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -19529,7 +19537,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="99"/>
+      <c r="A17" s="105"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -19591,7 +19599,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="100" t="s">
+      <c r="A20" s="106" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -19617,7 +19625,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="101"/>
+      <c r="A21" s="107"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -19645,7 +19653,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="101"/>
+      <c r="A22" s="107"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -19667,13 +19675,13 @@
       <c r="H22" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="J22" s="1">
+      <c r="J22" s="65">
         <f>IF(OR(Resultados!F22="",Resultados!G22=""),"",IF(AND(F22=Resultados!F22,G22=Resultados!G22),2,IF(((F22&gt;G22)=(Resultados!F22&gt;Resultados!G22))*((F22&lt;G22)=(Resultados!F22&lt;Resultados!G22)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="101"/>
+      <c r="A23" s="107"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -19695,13 +19703,13 @@
       <c r="H23" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="J23" s="1" t="str">
+      <c r="J23" s="64">
         <f>IF(OR(Resultados!F23="",Resultados!G23=""),"",IF(AND(F23=Resultados!F23,G23=Resultados!G23),2,IF(((F23&gt;G23)=(Resultados!F23&gt;Resultados!G23))*((F23&lt;G23)=(Resultados!F23&lt;Resultados!G23)),1,0)))</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="101"/>
+      <c r="A24" s="107"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -19729,7 +19737,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="102"/>
+      <c r="A25" s="108"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -19791,7 +19799,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="103" t="s">
+      <c r="A28" s="109" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -19817,7 +19825,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="104"/>
+      <c r="A29" s="110"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -19845,7 +19853,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="104"/>
+      <c r="A30" s="110"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -19867,13 +19875,13 @@
       <c r="H30" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="J30" s="1">
+      <c r="J30" s="64">
         <f>IF(OR(Resultados!F30="",Resultados!G30=""),"",IF(AND(F30=Resultados!F30,G30=Resultados!G30),2,IF(((F30&gt;G30)=(Resultados!F30&gt;Resultados!G30))*((F30&lt;G30)=(Resultados!F30&lt;Resultados!G30)),1,0)))</f>
         <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="104"/>
+      <c r="A31" s="110"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -19895,13 +19903,13 @@
       <c r="H31" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="J31" s="1" t="str">
+      <c r="J31" s="1">
         <f>IF(OR(Resultados!F31="",Resultados!G31=""),"",IF(AND(F31=Resultados!F31,G31=Resultados!G31),2,IF(((F31&gt;G31)=(Resultados!F31&gt;Resultados!G31))*((F31&lt;G31)=(Resultados!F31&lt;Resultados!G31)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="104"/>
+      <c r="A32" s="110"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -19925,7 +19933,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="105"/>
+      <c r="A33" s="111"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -19983,7 +19991,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="106" t="s">
+      <c r="A36" s="112" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -20013,7 +20021,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="107"/>
+      <c r="A37" s="113"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -20041,7 +20049,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="107"/>
+      <c r="A38" s="113"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -20065,7 +20073,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="107"/>
+      <c r="A39" s="113"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -20089,7 +20097,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="107"/>
+      <c r="A40" s="113"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -20113,7 +20121,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="108"/>
+      <c r="A41" s="114"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -20171,7 +20179,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="76" t="s">
+      <c r="A44" s="82" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -20201,7 +20209,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="77"/>
+      <c r="A45" s="83"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -20229,7 +20237,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="77"/>
+      <c r="A46" s="83"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -20253,7 +20261,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="77"/>
+      <c r="A47" s="83"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -20277,7 +20285,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="77"/>
+      <c r="A48" s="83"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -20301,7 +20309,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="78"/>
+      <c r="A49" s="84"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -20359,7 +20367,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="79" t="s">
+      <c r="A52" s="85" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -20389,7 +20397,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="80"/>
+      <c r="A53" s="86"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -20417,7 +20425,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="80"/>
+      <c r="A54" s="86"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -20441,7 +20449,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="80"/>
+      <c r="A55" s="86"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -20465,7 +20473,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="80"/>
+      <c r="A56" s="86"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -20489,7 +20497,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="81"/>
+      <c r="A57" s="87"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -20547,7 +20555,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="82" t="s">
+      <c r="A60" s="88" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -20577,7 +20585,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="83"/>
+      <c r="A61" s="89"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -20605,7 +20613,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="83"/>
+      <c r="A62" s="89"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -20629,7 +20637,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="83"/>
+      <c r="A63" s="89"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -20653,7 +20661,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="83"/>
+      <c r="A64" s="89"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -20677,7 +20685,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="84"/>
+      <c r="A65" s="90"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -20735,7 +20743,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="85" t="s">
+      <c r="A68" s="91" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -20765,7 +20773,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="86"/>
+      <c r="A69" s="92"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -20793,7 +20801,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="86"/>
+      <c r="A70" s="92"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -20817,7 +20825,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="86"/>
+      <c r="A71" s="92"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -20841,7 +20849,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="86"/>
+      <c r="A72" s="92"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -20865,7 +20873,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="87"/>
+      <c r="A73" s="93"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -20923,7 +20931,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="88" t="s">
+      <c r="A76" s="94" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -20953,7 +20961,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="89"/>
+      <c r="A77" s="95"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -20981,7 +20989,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="89"/>
+      <c r="A78" s="95"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -21005,7 +21013,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="89"/>
+      <c r="A79" s="95"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -21029,7 +21037,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="89"/>
+      <c r="A80" s="95"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -21053,7 +21061,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="90"/>
+      <c r="A81" s="96"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -21111,7 +21119,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="91" t="s">
+      <c r="A84" s="97" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -21141,7 +21149,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="92"/>
+      <c r="A85" s="98"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -21169,7 +21177,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="92"/>
+      <c r="A86" s="98"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -21193,7 +21201,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="92"/>
+      <c r="A87" s="98"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -21217,7 +21225,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="92"/>
+      <c r="A88" s="98"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -21241,7 +21249,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="93"/>
+      <c r="A89" s="99"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -21299,7 +21307,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="73" t="s">
+      <c r="A92" s="79" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -21329,7 +21337,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="74"/>
+      <c r="A93" s="80"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -21357,7 +21365,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="74"/>
+      <c r="A94" s="80"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -21381,7 +21389,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="74"/>
+      <c r="A95" s="80"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -21405,7 +21413,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="74"/>
+      <c r="A96" s="80"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -21429,7 +21437,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="75"/>
+      <c r="A97" s="81"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -21454,6 +21462,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A28:A33"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:A9"/>
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="A20:A25"/>
     <mergeCell ref="A84:A89"/>
     <mergeCell ref="A92:A97"/>
     <mergeCell ref="A36:A41"/>
@@ -21462,12 +21476,6 @@
     <mergeCell ref="A60:A65"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="A76:A81"/>
-    <mergeCell ref="A28:A33"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A4:A9"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="A20:A25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21495,26 +21503,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="67" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="69"/>
+      <c r="A1" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
+      <c r="H1" s="75"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="70"/>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
-      <c r="H2" s="72"/>
+      <c r="A2" s="76"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="78"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -21547,7 +21555,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="94" t="s">
+      <c r="A4" s="100" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -21573,11 +21581,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="95"/>
+      <c r="A5" s="101"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -21601,7 +21609,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="95"/>
+      <c r="A6" s="101"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -21629,7 +21637,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="95"/>
+      <c r="A7" s="101"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -21651,13 +21659,13 @@
       <c r="H7" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="J7" s="1">
+      <c r="J7" s="65">
         <f>IF(OR(Resultados!F7="",Resultados!G7=""),"",IF(AND(F7=Resultados!F7,G7=Resultados!G7),2,IF(((F7&gt;G7)=(Resultados!F7&gt;Resultados!G7))*((F7&lt;G7)=(Resultados!F7&lt;Resultados!G7)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="95"/>
+      <c r="A8" s="101"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -21685,7 +21693,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="96"/>
+      <c r="A9" s="102"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -21747,7 +21755,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="97" t="s">
+      <c r="A12" s="103" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -21773,7 +21781,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="98"/>
+      <c r="A13" s="104"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -21797,7 +21805,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="98"/>
+      <c r="A14" s="104"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -21825,7 +21833,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="98"/>
+      <c r="A15" s="104"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -21847,13 +21855,13 @@
       <c r="H15" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="J15" s="1">
+      <c r="J15" s="65">
         <f>IF(OR(Resultados!F15="",Resultados!G15=""),"",IF(AND(F15=Resultados!F15,G15=Resultados!G15),2,IF(((F15&gt;G15)=(Resultados!F15&gt;Resultados!G15))*((F15&lt;G15)=(Resultados!F15&lt;Resultados!G15)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="98"/>
+      <c r="A16" s="104"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -21881,7 +21889,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="99"/>
+      <c r="A17" s="105"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -21943,7 +21951,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="100" t="s">
+      <c r="A20" s="106" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -21969,7 +21977,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="101"/>
+      <c r="A21" s="107"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -21997,7 +22005,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="101"/>
+      <c r="A22" s="107"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -22019,13 +22027,13 @@
       <c r="H22" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="J22" s="1">
+      <c r="J22" s="65">
         <f>IF(OR(Resultados!F22="",Resultados!G22=""),"",IF(AND(F22=Resultados!F22,G22=Resultados!G22),2,IF(((F22&gt;G22)=(Resultados!F22&gt;Resultados!G22))*((F22&lt;G22)=(Resultados!F22&lt;Resultados!G22)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="101"/>
+      <c r="A23" s="107"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -22047,13 +22055,13 @@
       <c r="H23" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="J23" s="1" t="str">
+      <c r="J23" s="65">
         <f>IF(OR(Resultados!F23="",Resultados!G23=""),"",IF(AND(F23=Resultados!F23,G23=Resultados!G23),2,IF(((F23&gt;G23)=(Resultados!F23&gt;Resultados!G23))*((F23&lt;G23)=(Resultados!F23&lt;Resultados!G23)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="101"/>
+      <c r="A24" s="107"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -22081,7 +22089,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="102"/>
+      <c r="A25" s="108"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -22143,7 +22151,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="103" t="s">
+      <c r="A28" s="109" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -22169,7 +22177,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="104"/>
+      <c r="A29" s="110"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -22197,7 +22205,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="104"/>
+      <c r="A30" s="110"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -22219,13 +22227,13 @@
       <c r="H30" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="J30" s="1">
+      <c r="J30" s="65">
         <f>IF(OR(Resultados!F30="",Resultados!G30=""),"",IF(AND(F30=Resultados!F30,G30=Resultados!G30),2,IF(((F30&gt;G30)=(Resultados!F30&gt;Resultados!G30))*((F30&lt;G30)=(Resultados!F30&lt;Resultados!G30)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="104"/>
+      <c r="A31" s="110"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -22247,13 +22255,13 @@
       <c r="H31" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="J31" s="1" t="str">
+      <c r="J31" s="1">
         <f>IF(OR(Resultados!F31="",Resultados!G31=""),"",IF(AND(F31=Resultados!F31,G31=Resultados!G31),2,IF(((F31&gt;G31)=(Resultados!F31&gt;Resultados!G31))*((F31&lt;G31)=(Resultados!F31&lt;Resultados!G31)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="104"/>
+      <c r="A32" s="110"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -22281,7 +22289,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="105"/>
+      <c r="A33" s="111"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -22343,7 +22351,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="106" t="s">
+      <c r="A36" s="112" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -22373,7 +22381,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="107"/>
+      <c r="A37" s="113"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -22401,7 +22409,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="107"/>
+      <c r="A38" s="113"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -22429,7 +22437,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="107"/>
+      <c r="A39" s="113"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -22457,7 +22465,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="107"/>
+      <c r="A40" s="113"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -22485,7 +22493,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="108"/>
+      <c r="A41" s="114"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -22547,7 +22555,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="76" t="s">
+      <c r="A44" s="82" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -22577,7 +22585,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="77"/>
+      <c r="A45" s="83"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -22605,7 +22613,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="77"/>
+      <c r="A46" s="83"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -22633,7 +22641,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="77"/>
+      <c r="A47" s="83"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -22661,7 +22669,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="77"/>
+      <c r="A48" s="83"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -22689,7 +22697,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="78"/>
+      <c r="A49" s="84"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -22751,7 +22759,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="79" t="s">
+      <c r="A52" s="85" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -22781,7 +22789,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="80"/>
+      <c r="A53" s="86"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -22809,7 +22817,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="80"/>
+      <c r="A54" s="86"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -22837,7 +22845,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="80"/>
+      <c r="A55" s="86"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -22865,7 +22873,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="80"/>
+      <c r="A56" s="86"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -22893,7 +22901,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="81"/>
+      <c r="A57" s="87"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -22955,7 +22963,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="82" t="s">
+      <c r="A60" s="88" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -22985,7 +22993,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="83"/>
+      <c r="A61" s="89"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -23013,7 +23021,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="83"/>
+      <c r="A62" s="89"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -23041,7 +23049,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="83"/>
+      <c r="A63" s="89"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -23069,7 +23077,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="83"/>
+      <c r="A64" s="89"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -23097,7 +23105,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="84"/>
+      <c r="A65" s="90"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -23159,7 +23167,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="85" t="s">
+      <c r="A68" s="91" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -23189,7 +23197,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="86"/>
+      <c r="A69" s="92"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -23217,7 +23225,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="86"/>
+      <c r="A70" s="92"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -23245,7 +23253,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="86"/>
+      <c r="A71" s="92"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -23273,7 +23281,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="86"/>
+      <c r="A72" s="92"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -23301,7 +23309,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="87"/>
+      <c r="A73" s="93"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -23363,7 +23371,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="88" t="s">
+      <c r="A76" s="94" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -23393,7 +23401,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="89"/>
+      <c r="A77" s="95"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -23421,7 +23429,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="89"/>
+      <c r="A78" s="95"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -23449,7 +23457,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="89"/>
+      <c r="A79" s="95"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -23477,7 +23485,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="89"/>
+      <c r="A80" s="95"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -23505,7 +23513,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="90"/>
+      <c r="A81" s="96"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -23567,7 +23575,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="91" t="s">
+      <c r="A84" s="97" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -23597,7 +23605,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="92"/>
+      <c r="A85" s="98"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -23625,7 +23633,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="92"/>
+      <c r="A86" s="98"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -23653,7 +23661,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="92"/>
+      <c r="A87" s="98"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -23681,7 +23689,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="92"/>
+      <c r="A88" s="98"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -23709,7 +23717,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="93"/>
+      <c r="A89" s="99"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -23771,7 +23779,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="73" t="s">
+      <c r="A92" s="79" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -23801,7 +23809,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="74"/>
+      <c r="A93" s="80"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -23829,7 +23837,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="74"/>
+      <c r="A94" s="80"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -23857,7 +23865,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="74"/>
+      <c r="A95" s="80"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -23885,7 +23893,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="74"/>
+      <c r="A96" s="80"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -23913,7 +23921,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="75"/>
+      <c r="A97" s="81"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -23942,6 +23950,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A28:A33"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:A9"/>
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="A20:A25"/>
     <mergeCell ref="A84:A89"/>
     <mergeCell ref="A92:A97"/>
     <mergeCell ref="A36:A41"/>
@@ -23950,12 +23964,6 @@
     <mergeCell ref="A60:A65"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="A76:A81"/>
-    <mergeCell ref="A28:A33"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A4:A9"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="A20:A25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -23983,26 +23991,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="67" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="69"/>
+      <c r="A1" s="73" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
+      <c r="H1" s="75"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="70"/>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
-      <c r="H2" s="72"/>
+      <c r="A2" s="76"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="78"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -24035,7 +24043,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="94" t="s">
+      <c r="A4" s="100" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -24061,11 +24069,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="95"/>
+      <c r="A5" s="101"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -24089,7 +24097,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="95"/>
+      <c r="A6" s="101"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -24117,7 +24125,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="95"/>
+      <c r="A7" s="101"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -24145,7 +24153,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="95"/>
+      <c r="A8" s="101"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -24173,7 +24181,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="96"/>
+      <c r="A9" s="102"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -24235,7 +24243,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="97" t="s">
+      <c r="A12" s="103" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -24261,7 +24269,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="98"/>
+      <c r="A13" s="104"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -24285,7 +24293,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="98"/>
+      <c r="A14" s="104"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -24313,7 +24321,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="98"/>
+      <c r="A15" s="104"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -24335,13 +24343,13 @@
       <c r="H15" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="J15" s="1">
+      <c r="J15" s="65">
         <f>IF(OR(Resultados!F15="",Resultados!G15=""),"",IF(AND(F15=Resultados!F15,G15=Resultados!G15),2,IF(((F15&gt;G15)=(Resultados!F15&gt;Resultados!G15))*((F15&lt;G15)=(Resultados!F15&lt;Resultados!G15)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="98"/>
+      <c r="A16" s="104"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -24369,7 +24377,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="99"/>
+      <c r="A17" s="105"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -24431,7 +24439,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="100" t="s">
+      <c r="A20" s="106" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -24457,7 +24465,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="101"/>
+      <c r="A21" s="107"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -24485,7 +24493,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="101"/>
+      <c r="A22" s="107"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -24507,13 +24515,13 @@
       <c r="H22" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="J22" s="1">
+      <c r="J22" s="65">
         <f>IF(OR(Resultados!F22="",Resultados!G22=""),"",IF(AND(F22=Resultados!F22,G22=Resultados!G22),2,IF(((F22&gt;G22)=(Resultados!F22&gt;Resultados!G22))*((F22&lt;G22)=(Resultados!F22&lt;Resultados!G22)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="101"/>
+      <c r="A23" s="107"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -24535,13 +24543,13 @@
       <c r="H23" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="J23" s="1" t="str">
+      <c r="J23" s="65">
         <f>IF(OR(Resultados!F23="",Resultados!G23=""),"",IF(AND(F23=Resultados!F23,G23=Resultados!G23),2,IF(((F23&gt;G23)=(Resultados!F23&gt;Resultados!G23))*((F23&lt;G23)=(Resultados!F23&lt;Resultados!G23)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="101"/>
+      <c r="A24" s="107"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -24569,7 +24577,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="102"/>
+      <c r="A25" s="108"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -24631,7 +24639,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="103" t="s">
+      <c r="A28" s="109" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -24657,7 +24665,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="104"/>
+      <c r="A29" s="110"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -24685,7 +24693,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="104"/>
+      <c r="A30" s="110"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -24707,13 +24715,13 @@
       <c r="H30" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="J30" s="1">
+      <c r="J30" s="65">
         <f>IF(OR(Resultados!F30="",Resultados!G30=""),"",IF(AND(F30=Resultados!F30,G30=Resultados!G30),2,IF(((F30&gt;G30)=(Resultados!F30&gt;Resultados!G30))*((F30&lt;G30)=(Resultados!F30&lt;Resultados!G30)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="104"/>
+      <c r="A31" s="110"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -24735,13 +24743,13 @@
       <c r="H31" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="J31" s="1" t="str">
+      <c r="J31" s="65">
         <f>IF(OR(Resultados!F31="",Resultados!G31=""),"",IF(AND(F31=Resultados!F31,G31=Resultados!G31),2,IF(((F31&gt;G31)=(Resultados!F31&gt;Resultados!G31))*((F31&lt;G31)=(Resultados!F31&lt;Resultados!G31)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="104"/>
+      <c r="A32" s="110"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -24769,7 +24777,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="105"/>
+      <c r="A33" s="111"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -24831,7 +24839,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="106" t="s">
+      <c r="A36" s="112" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -24861,7 +24869,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="107"/>
+      <c r="A37" s="113"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -24889,7 +24897,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="107"/>
+      <c r="A38" s="113"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -24917,7 +24925,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="107"/>
+      <c r="A39" s="113"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -24945,7 +24953,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="107"/>
+      <c r="A40" s="113"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -24973,7 +24981,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="108"/>
+      <c r="A41" s="114"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -25035,7 +25043,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="76" t="s">
+      <c r="A44" s="82" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -25065,7 +25073,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="77"/>
+      <c r="A45" s="83"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -25093,7 +25101,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="77"/>
+      <c r="A46" s="83"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -25121,7 +25129,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="77"/>
+      <c r="A47" s="83"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -25149,7 +25157,7 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="77"/>
+      <c r="A48" s="83"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -25177,7 +25185,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="78"/>
+      <c r="A49" s="84"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -25239,7 +25247,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="79" t="s">
+      <c r="A52" s="85" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -25269,7 +25277,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="80"/>
+      <c r="A53" s="86"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -25297,7 +25305,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="80"/>
+      <c r="A54" s="86"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -25325,7 +25333,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="80"/>
+      <c r="A55" s="86"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -25353,7 +25361,7 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="80"/>
+      <c r="A56" s="86"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -25381,7 +25389,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="81"/>
+      <c r="A57" s="87"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -25443,7 +25451,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="82" t="s">
+      <c r="A60" s="88" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -25473,7 +25481,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="83"/>
+      <c r="A61" s="89"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -25501,7 +25509,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="83"/>
+      <c r="A62" s="89"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -25529,7 +25537,7 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="83"/>
+      <c r="A63" s="89"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -25557,7 +25565,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="83"/>
+      <c r="A64" s="89"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -25585,7 +25593,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="84"/>
+      <c r="A65" s="90"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -25647,7 +25655,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="85" t="s">
+      <c r="A68" s="91" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -25677,7 +25685,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="86"/>
+      <c r="A69" s="92"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -25705,7 +25713,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="86"/>
+      <c r="A70" s="92"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -25733,7 +25741,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="86"/>
+      <c r="A71" s="92"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -25761,7 +25769,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="86"/>
+      <c r="A72" s="92"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -25789,7 +25797,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="87"/>
+      <c r="A73" s="93"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -25851,7 +25859,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="88" t="s">
+      <c r="A76" s="94" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -25881,7 +25889,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="89"/>
+      <c r="A77" s="95"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -25909,7 +25917,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="89"/>
+      <c r="A78" s="95"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -25937,7 +25945,7 @@
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="89"/>
+      <c r="A79" s="95"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -25965,7 +25973,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="89"/>
+      <c r="A80" s="95"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -25993,7 +26001,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="90"/>
+      <c r="A81" s="96"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -26055,7 +26063,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="91" t="s">
+      <c r="A84" s="97" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -26085,7 +26093,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="92"/>
+      <c r="A85" s="98"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -26113,7 +26121,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="92"/>
+      <c r="A86" s="98"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -26141,7 +26149,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="92"/>
+      <c r="A87" s="98"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -26169,7 +26177,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="92"/>
+      <c r="A88" s="98"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -26197,7 +26205,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="93"/>
+      <c r="A89" s="99"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -26259,7 +26267,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="73" t="s">
+      <c r="A92" s="79" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -26289,7 +26297,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="74"/>
+      <c r="A93" s="80"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -26317,7 +26325,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="74"/>
+      <c r="A94" s="80"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -26345,7 +26353,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="74"/>
+      <c r="A95" s="80"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -26373,7 +26381,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="74"/>
+      <c r="A96" s="80"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -26401,7 +26409,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="75"/>
+      <c r="A97" s="81"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -26430,6 +26438,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A28:A33"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:A9"/>
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="A20:A25"/>
     <mergeCell ref="A84:A89"/>
     <mergeCell ref="A92:A97"/>
     <mergeCell ref="A36:A41"/>
@@ -26438,12 +26452,6 @@
     <mergeCell ref="A60:A65"/>
     <mergeCell ref="A68:A73"/>
     <mergeCell ref="A76:A81"/>
-    <mergeCell ref="A28:A33"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A4:A9"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="A20:A25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -26653,20 +26661,20 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="7461ab22-4e70-4395-beb5-078d6ab567bf" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="7461ab22-4e70-4395-beb5-078d6ab567bf" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -26688,6 +26696,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5511D132-9333-423C-BAEC-48101CE7245F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7DE79FC7-1424-4D12-B735-3F81ACD8E888}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
@@ -26701,12 +26717,4 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5511D132-9333-423C-BAEC-48101CE7245F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/Quiniela.xlsx
+++ b/data/Quiniela.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cindy\Desktop\QuinielaMundial\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{980172C7-F52C-4881-9CD5-2B416E024D10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E41E6FF-6258-4168-9C7F-6E700C0BCEF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{9503E40F-C0E1-49CE-B4EA-3C401754995E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9503E40F-C0E1-49CE-B4EA-3C401754995E}"/>
   </bookViews>
   <sheets>
     <sheet name="Resultados" sheetId="1" r:id="rId1"/>
@@ -1013,7 +1013,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="151">
+  <cellXfs count="152">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1266,24 +1266,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="20" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="20" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="20" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="20" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="20" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="20" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1452,6 +1434,24 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="49" fontId="20" fillId="20" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="20" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="20" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="20" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="20" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="20" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1593,6 +1593,10 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="19" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1951,26 +1955,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="75"/>
+      <c r="A1" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="69"/>
     </row>
     <row r="2" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="76"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="78"/>
+      <c r="A2" s="70"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="72"/>
     </row>
     <row r="3" spans="1:8" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -1997,7 +2001,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="100" t="s">
+      <c r="A4" s="94" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -2009,7 +2013,7 @@
       <c r="D4" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="27" t="s">
+      <c r="E4" s="151" t="s">
         <v>9</v>
       </c>
       <c r="F4" s="62">
@@ -2023,7 +2027,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="101"/>
+      <c r="A5" s="95"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -2033,7 +2037,7 @@
       <c r="D5" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="27" t="s">
+      <c r="E5" s="151" t="s">
         <v>11</v>
       </c>
       <c r="F5" s="62">
@@ -2047,7 +2051,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="101"/>
+      <c r="A6" s="95"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -2071,7 +2075,7 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="101"/>
+      <c r="A7" s="95"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -2081,7 +2085,7 @@
       <c r="D7" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="27" t="s">
+      <c r="E7" s="151" t="s">
         <v>9</v>
       </c>
       <c r="F7" s="66">
@@ -2095,7 +2099,7 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="101"/>
+      <c r="A8" s="95"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -2115,7 +2119,7 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="102"/>
+      <c r="A9" s="96"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -2169,7 +2173,7 @@
       </c>
     </row>
     <row r="12" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="103" t="s">
+      <c r="A12" s="97" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -2195,7 +2199,7 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="104"/>
+      <c r="A13" s="98"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -2219,7 +2223,7 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="104"/>
+      <c r="A14" s="98"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -2243,7 +2247,7 @@
       </c>
     </row>
     <row r="15" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="104"/>
+      <c r="A15" s="98"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -2267,7 +2271,7 @@
       </c>
     </row>
     <row r="16" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="104"/>
+      <c r="A16" s="98"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -2287,7 +2291,7 @@
       </c>
     </row>
     <row r="17" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="105"/>
+      <c r="A17" s="99"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -2341,7 +2345,7 @@
       </c>
     </row>
     <row r="20" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="106" t="s">
+      <c r="A20" s="100" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -2367,7 +2371,7 @@
       </c>
     </row>
     <row r="21" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="107"/>
+      <c r="A21" s="101"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -2386,12 +2390,12 @@
       <c r="G21" s="62">
         <v>1</v>
       </c>
-      <c r="H21" s="27" t="s">
+      <c r="H21" s="151" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="107"/>
+      <c r="A22" s="101"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -2410,12 +2414,12 @@
       <c r="G22" s="66">
         <v>1</v>
       </c>
-      <c r="H22" s="27" t="s">
+      <c r="H22" s="151" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="107"/>
+      <c r="A23" s="101"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -2439,7 +2443,7 @@
       </c>
     </row>
     <row r="24" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="107"/>
+      <c r="A24" s="101"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -2459,7 +2463,7 @@
       </c>
     </row>
     <row r="25" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="108"/>
+      <c r="A25" s="102"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -2513,7 +2517,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="109" t="s">
+      <c r="A28" s="103" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -2539,7 +2543,7 @@
       </c>
     </row>
     <row r="29" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="110"/>
+      <c r="A29" s="104"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -2563,7 +2567,7 @@
       </c>
     </row>
     <row r="30" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="110"/>
+      <c r="A30" s="104"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -2587,7 +2591,7 @@
       </c>
     </row>
     <row r="31" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="110"/>
+      <c r="A31" s="104"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -2606,12 +2610,12 @@
       <c r="G31" s="66">
         <v>1</v>
       </c>
-      <c r="H31" s="27" t="s">
+      <c r="H31" s="151" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="110"/>
+      <c r="A32" s="104"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -2631,7 +2635,7 @@
       </c>
     </row>
     <row r="33" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="111"/>
+      <c r="A33" s="105"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -2685,7 +2689,7 @@
       </c>
     </row>
     <row r="36" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="112" t="s">
+      <c r="A36" s="106" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -2711,7 +2715,7 @@
       </c>
     </row>
     <row r="37" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="113"/>
+      <c r="A37" s="107"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -2735,7 +2739,7 @@
       </c>
     </row>
     <row r="38" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="113"/>
+      <c r="A38" s="107"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -2745,17 +2749,21 @@
       <c r="D38" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E38" s="10" t="s">
+      <c r="E38" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="F38" s="25"/>
-      <c r="G38" s="25"/>
+      <c r="F38" s="62">
+        <v>2</v>
+      </c>
+      <c r="G38" s="62">
+        <v>1</v>
+      </c>
       <c r="H38" s="21" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="113"/>
+      <c r="A39" s="107"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -2765,17 +2773,21 @@
       <c r="D39" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E39" s="10" t="s">
+      <c r="E39" s="61" t="s">
         <v>34</v>
       </c>
-      <c r="F39" s="25"/>
-      <c r="G39" s="25"/>
-      <c r="H39" s="21" t="s">
+      <c r="F39" s="62">
+        <v>0</v>
+      </c>
+      <c r="G39" s="62">
+        <v>0</v>
+      </c>
+      <c r="H39" s="61" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="113"/>
+      <c r="A40" s="107"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -2795,7 +2807,7 @@
       </c>
     </row>
     <row r="41" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="114"/>
+      <c r="A41" s="108"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -2849,7 +2861,7 @@
       </c>
     </row>
     <row r="44" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="82" t="s">
+      <c r="A44" s="76" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -2875,7 +2887,7 @@
       </c>
     </row>
     <row r="45" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="83"/>
+      <c r="A45" s="77"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -2899,7 +2911,7 @@
       </c>
     </row>
     <row r="46" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="83"/>
+      <c r="A46" s="77"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -2909,17 +2921,21 @@
       <c r="D46" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E46" s="10" t="s">
+      <c r="E46" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="F46" s="25"/>
-      <c r="G46" s="25"/>
+      <c r="F46" s="62">
+        <v>5</v>
+      </c>
+      <c r="G46" s="62">
+        <v>1</v>
+      </c>
       <c r="H46" s="21" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="83"/>
+      <c r="A47" s="77"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -2932,14 +2948,18 @@
       <c r="E47" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F47" s="25"/>
-      <c r="G47" s="25"/>
-      <c r="H47" s="21" t="s">
+      <c r="F47" s="66">
+        <v>0</v>
+      </c>
+      <c r="G47" s="66">
+        <v>4</v>
+      </c>
+      <c r="H47" s="151" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="83"/>
+      <c r="A48" s="77"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -2959,7 +2979,7 @@
       </c>
     </row>
     <row r="49" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="84"/>
+      <c r="A49" s="78"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -3013,7 +3033,7 @@
       </c>
     </row>
     <row r="52" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="85" t="s">
+      <c r="A52" s="79" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -3039,7 +3059,7 @@
       </c>
     </row>
     <row r="53" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="86"/>
+      <c r="A53" s="80"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -3063,7 +3083,7 @@
       </c>
     </row>
     <row r="54" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="86"/>
+      <c r="A54" s="80"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -3073,17 +3093,21 @@
       <c r="D54" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E54" s="10" t="s">
+      <c r="E54" s="61" t="s">
         <v>41</v>
       </c>
-      <c r="F54" s="25"/>
-      <c r="G54" s="25"/>
-      <c r="H54" s="21" t="s">
+      <c r="F54" s="63">
+        <v>0</v>
+      </c>
+      <c r="G54" s="63">
+        <v>0</v>
+      </c>
+      <c r="H54" s="61" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="86"/>
+      <c r="A55" s="80"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -3096,14 +3120,18 @@
       <c r="E55" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F55" s="25"/>
-      <c r="G55" s="25"/>
-      <c r="H55" s="21" t="s">
+      <c r="F55" s="63">
+        <v>1</v>
+      </c>
+      <c r="G55" s="63">
+        <v>3</v>
+      </c>
+      <c r="H55" s="151" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="86"/>
+      <c r="A56" s="80"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -3123,7 +3151,7 @@
       </c>
     </row>
     <row r="57" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="87"/>
+      <c r="A57" s="81"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -3177,7 +3205,7 @@
       </c>
     </row>
     <row r="60" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="88" t="s">
+      <c r="A60" s="82" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -3203,7 +3231,7 @@
       </c>
     </row>
     <row r="61" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="89"/>
+      <c r="A61" s="83"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -3227,7 +3255,7 @@
       </c>
     </row>
     <row r="62" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="89"/>
+      <c r="A62" s="83"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -3237,17 +3265,21 @@
       <c r="D62" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E62" s="10" t="s">
+      <c r="E62" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="F62" s="25"/>
-      <c r="G62" s="25"/>
+      <c r="F62" s="66">
+        <v>4</v>
+      </c>
+      <c r="G62" s="66">
+        <v>0</v>
+      </c>
       <c r="H62" s="21" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="89"/>
+      <c r="A63" s="83"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -3257,17 +3289,21 @@
       <c r="D63" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E63" s="10" t="s">
+      <c r="E63" s="61" t="s">
         <v>49</v>
       </c>
-      <c r="F63" s="25"/>
-      <c r="G63" s="25"/>
-      <c r="H63" s="21" t="s">
+      <c r="F63" s="66">
+        <v>2</v>
+      </c>
+      <c r="G63" s="66">
+        <v>2</v>
+      </c>
+      <c r="H63" s="61" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="89"/>
+      <c r="A64" s="83"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -3287,7 +3323,7 @@
       </c>
     </row>
     <row r="65" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="90"/>
+      <c r="A65" s="84"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -3341,7 +3377,7 @@
       </c>
     </row>
     <row r="68" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="91" t="s">
+      <c r="A68" s="85" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -3367,7 +3403,7 @@
       </c>
     </row>
     <row r="69" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="92"/>
+      <c r="A69" s="86"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -3386,12 +3422,12 @@
       <c r="G69" s="62">
         <v>4</v>
       </c>
-      <c r="H69" s="27" t="s">
+      <c r="H69" s="151" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="92"/>
+      <c r="A70" s="86"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -3411,7 +3447,7 @@
       </c>
     </row>
     <row r="71" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="92"/>
+      <c r="A71" s="86"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -3431,7 +3467,7 @@
       </c>
     </row>
     <row r="72" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="92"/>
+      <c r="A72" s="86"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -3451,7 +3487,7 @@
       </c>
     </row>
     <row r="73" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="93"/>
+      <c r="A73" s="87"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -3505,7 +3541,7 @@
       </c>
     </row>
     <row r="76" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="94" t="s">
+      <c r="A76" s="88" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -3531,7 +3567,7 @@
       </c>
     </row>
     <row r="77" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="95"/>
+      <c r="A77" s="89"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -3555,7 +3591,7 @@
       </c>
     </row>
     <row r="78" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="95"/>
+      <c r="A78" s="89"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -3565,17 +3601,21 @@
       <c r="D78" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E78" s="10" t="s">
+      <c r="E78" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="F78" s="25"/>
-      <c r="G78" s="25"/>
+      <c r="F78" s="62">
+        <v>2</v>
+      </c>
+      <c r="G78" s="62">
+        <v>0</v>
+      </c>
       <c r="H78" s="21" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="95"/>
+      <c r="A79" s="89"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -3595,7 +3635,7 @@
       </c>
     </row>
     <row r="80" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="95"/>
+      <c r="A80" s="89"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -3615,7 +3655,7 @@
       </c>
     </row>
     <row r="81" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="96"/>
+      <c r="A81" s="90"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -3669,7 +3709,7 @@
       </c>
     </row>
     <row r="84" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="97" t="s">
+      <c r="A84" s="91" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -3695,7 +3735,7 @@
       </c>
     </row>
     <row r="85" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="98"/>
+      <c r="A85" s="92"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -3714,12 +3754,12 @@
       <c r="G85" s="62">
         <v>3</v>
       </c>
-      <c r="H85" s="27" t="s">
+      <c r="H85" s="151" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="86" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="98"/>
+      <c r="A86" s="92"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -3739,7 +3779,7 @@
       </c>
     </row>
     <row r="87" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="98"/>
+      <c r="A87" s="92"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -3759,7 +3799,7 @@
       </c>
     </row>
     <row r="88" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="98"/>
+      <c r="A88" s="92"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -3779,7 +3819,7 @@
       </c>
     </row>
     <row r="89" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="99"/>
+      <c r="A89" s="93"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -3833,7 +3873,7 @@
       </c>
     </row>
     <row r="92" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="79" t="s">
+      <c r="A92" s="73" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -3859,7 +3899,7 @@
       </c>
     </row>
     <row r="93" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="80"/>
+      <c r="A93" s="74"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -3883,7 +3923,7 @@
       </c>
     </row>
     <row r="94" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="80"/>
+      <c r="A94" s="74"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -3903,7 +3943,7 @@
       </c>
     </row>
     <row r="95" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="80"/>
+      <c r="A95" s="74"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -3923,7 +3963,7 @@
       </c>
     </row>
     <row r="96" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="80"/>
+      <c r="A96" s="74"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -3943,7 +3983,7 @@
       </c>
     </row>
     <row r="97" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="81"/>
+      <c r="A97" s="75"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -4003,26 +4043,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="75"/>
+      <c r="A1" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="69"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="76"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="78"/>
+      <c r="A2" s="70"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="72"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -4055,7 +4095,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="100" t="s">
+      <c r="A4" s="94" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -4081,11 +4121,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="101"/>
+      <c r="A5" s="95"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -4109,7 +4149,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="101"/>
+      <c r="A6" s="95"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -4137,7 +4177,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="101"/>
+      <c r="A7" s="95"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -4165,7 +4205,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="101"/>
+      <c r="A8" s="95"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -4193,7 +4233,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="102"/>
+      <c r="A9" s="96"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -4255,7 +4295,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="103" t="s">
+      <c r="A12" s="97" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -4281,7 +4321,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="104"/>
+      <c r="A13" s="98"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -4305,7 +4345,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="104"/>
+      <c r="A14" s="98"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -4333,7 +4373,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="104"/>
+      <c r="A15" s="98"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -4361,7 +4401,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="104"/>
+      <c r="A16" s="98"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -4389,7 +4429,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="105"/>
+      <c r="A17" s="99"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -4451,7 +4491,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="106" t="s">
+      <c r="A20" s="100" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -4477,7 +4517,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="107"/>
+      <c r="A21" s="101"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -4505,7 +4545,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="107"/>
+      <c r="A22" s="101"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -4533,7 +4573,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="107"/>
+      <c r="A23" s="101"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -4561,7 +4601,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="107"/>
+      <c r="A24" s="101"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -4589,7 +4629,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="108"/>
+      <c r="A25" s="102"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -4651,7 +4691,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="109" t="s">
+      <c r="A28" s="103" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -4677,7 +4717,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="110"/>
+      <c r="A29" s="104"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -4705,7 +4745,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="110"/>
+      <c r="A30" s="104"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -4733,7 +4773,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="110"/>
+      <c r="A31" s="104"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -4761,7 +4801,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="110"/>
+      <c r="A32" s="104"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -4789,7 +4829,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="111"/>
+      <c r="A33" s="105"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -4851,7 +4891,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="112" t="s">
+      <c r="A36" s="106" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -4881,7 +4921,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="113"/>
+      <c r="A37" s="107"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -4909,7 +4949,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="113"/>
+      <c r="A38" s="107"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -4931,13 +4971,13 @@
       <c r="H38" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="J38" s="1" t="str">
+      <c r="J38" s="1">
         <f>IF(OR(Resultados!F38="",Resultados!G38=""),"",IF(AND(F38=Resultados!F38,G38=Resultados!G38),2,IF(((F38&gt;G38)=(Resultados!F38&gt;Resultados!G38))*((F38&lt;G38)=(Resultados!F38&lt;Resultados!G38)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="113"/>
+      <c r="A39" s="107"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -4959,13 +4999,13 @@
       <c r="H39" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="J39" s="1" t="str">
+      <c r="J39" s="1">
         <f>IF(OR(Resultados!F39="",Resultados!G39=""),"",IF(AND(F39=Resultados!F39,G39=Resultados!G39),2,IF(((F39&gt;G39)=(Resultados!F39&gt;Resultados!G39))*((F39&lt;G39)=(Resultados!F39&lt;Resultados!G39)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="113"/>
+      <c r="A40" s="107"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -4993,7 +5033,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="114"/>
+      <c r="A41" s="108"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -5055,7 +5095,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="82" t="s">
+      <c r="A44" s="76" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -5085,7 +5125,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="83"/>
+      <c r="A45" s="77"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -5113,7 +5153,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="83"/>
+      <c r="A46" s="77"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -5135,13 +5175,13 @@
       <c r="H46" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="J46" s="1" t="str">
+      <c r="J46" s="1">
         <f>IF(OR(Resultados!F46="",Resultados!G46=""),"",IF(AND(F46=Resultados!F46,G46=Resultados!G46),2,IF(((F46&gt;G46)=(Resultados!F46&gt;Resultados!G46))*((F46&lt;G46)=(Resultados!F46&lt;Resultados!G46)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="83"/>
+      <c r="A47" s="77"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -5163,13 +5203,13 @@
       <c r="H47" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="J47" s="1" t="str">
+      <c r="J47" s="1">
         <f>IF(OR(Resultados!F47="",Resultados!G47=""),"",IF(AND(F47=Resultados!F47,G47=Resultados!G47),2,IF(((F47&gt;G47)=(Resultados!F47&gt;Resultados!G47))*((F47&lt;G47)=(Resultados!F47&lt;Resultados!G47)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="83"/>
+      <c r="A48" s="77"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -5197,7 +5237,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="84"/>
+      <c r="A49" s="78"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -5259,7 +5299,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="85" t="s">
+      <c r="A52" s="79" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -5289,7 +5329,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="86"/>
+      <c r="A53" s="80"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -5317,7 +5357,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="86"/>
+      <c r="A54" s="80"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -5339,13 +5379,13 @@
       <c r="H54" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="J54" s="1" t="str">
+      <c r="J54" s="1">
         <f>IF(OR(Resultados!F54="",Resultados!G54=""),"",IF(AND(F54=Resultados!F54,G54=Resultados!G54),2,IF(((F54&gt;G54)=(Resultados!F54&gt;Resultados!G54))*((F54&lt;G54)=(Resultados!F54&lt;Resultados!G54)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="86"/>
+      <c r="A55" s="80"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -5367,13 +5407,13 @@
       <c r="H55" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="J55" s="1" t="str">
+      <c r="J55" s="1">
         <f>IF(OR(Resultados!F55="",Resultados!G55=""),"",IF(AND(F55=Resultados!F55,G55=Resultados!G55),2,IF(((F55&gt;G55)=(Resultados!F55&gt;Resultados!G55))*((F55&lt;G55)=(Resultados!F55&lt;Resultados!G55)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="86"/>
+      <c r="A56" s="80"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -5401,7 +5441,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="87"/>
+      <c r="A57" s="81"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -5463,7 +5503,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="88" t="s">
+      <c r="A60" s="82" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -5493,7 +5533,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="89"/>
+      <c r="A61" s="83"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -5521,7 +5561,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="89"/>
+      <c r="A62" s="83"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -5543,13 +5583,13 @@
       <c r="H62" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="J62" s="1" t="str">
+      <c r="J62" s="1">
         <f>IF(OR(Resultados!F62="",Resultados!G62=""),"",IF(AND(F62=Resultados!F62,G62=Resultados!G62),2,IF(((F62&gt;G62)=(Resultados!F62&gt;Resultados!G62))*((F62&lt;G62)=(Resultados!F62&lt;Resultados!G62)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="89"/>
+      <c r="A63" s="83"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -5571,13 +5611,13 @@
       <c r="H63" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="J63" s="1" t="str">
+      <c r="J63" s="1">
         <f>IF(OR(Resultados!F63="",Resultados!G63=""),"",IF(AND(F63=Resultados!F63,G63=Resultados!G63),2,IF(((F63&gt;G63)=(Resultados!F63&gt;Resultados!G63))*((F63&lt;G63)=(Resultados!F63&lt;Resultados!G63)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="89"/>
+      <c r="A64" s="83"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -5605,7 +5645,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="90"/>
+      <c r="A65" s="84"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -5667,7 +5707,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="91" t="s">
+      <c r="A68" s="85" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -5697,7 +5737,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="92"/>
+      <c r="A69" s="86"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -5725,7 +5765,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="92"/>
+      <c r="A70" s="86"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -5753,7 +5793,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="92"/>
+      <c r="A71" s="86"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -5781,7 +5821,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="92"/>
+      <c r="A72" s="86"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -5809,7 +5849,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="93"/>
+      <c r="A73" s="87"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -5871,7 +5911,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="94" t="s">
+      <c r="A76" s="88" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -5901,7 +5941,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="95"/>
+      <c r="A77" s="89"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -5929,7 +5969,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="95"/>
+      <c r="A78" s="89"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -5951,13 +5991,13 @@
       <c r="H78" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="J78" s="1" t="str">
+      <c r="J78" s="1">
         <f>IF(OR(Resultados!F78="",Resultados!G78=""),"",IF(AND(F78=Resultados!F78,G78=Resultados!G78),2,IF(((F78&gt;G78)=(Resultados!F78&gt;Resultados!G78))*((F78&lt;G78)=(Resultados!F78&lt;Resultados!G78)),1,0)))</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="95"/>
+      <c r="A79" s="89"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -5985,7 +6025,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="95"/>
+      <c r="A80" s="89"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -6013,7 +6053,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="96"/>
+      <c r="A81" s="90"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -6075,7 +6115,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="97" t="s">
+      <c r="A84" s="91" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -6105,7 +6145,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="98"/>
+      <c r="A85" s="92"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -6133,7 +6173,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="98"/>
+      <c r="A86" s="92"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -6161,7 +6201,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="98"/>
+      <c r="A87" s="92"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -6189,7 +6229,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="98"/>
+      <c r="A88" s="92"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -6217,7 +6257,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="99"/>
+      <c r="A89" s="93"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -6279,7 +6319,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="79" t="s">
+      <c r="A92" s="73" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -6309,7 +6349,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="80"/>
+      <c r="A93" s="74"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -6337,7 +6377,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="80"/>
+      <c r="A94" s="74"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -6365,7 +6405,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="80"/>
+      <c r="A95" s="74"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -6393,7 +6433,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="80"/>
+      <c r="A96" s="74"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -6421,7 +6461,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="81"/>
+      <c r="A97" s="75"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -6491,26 +6531,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="75"/>
+      <c r="A1" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="69"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="76"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="78"/>
+      <c r="A2" s="70"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="72"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -6543,7 +6583,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="100" t="s">
+      <c r="A4" s="94" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -6569,11 +6609,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="101"/>
+      <c r="A5" s="95"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -6597,7 +6637,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="101"/>
+      <c r="A6" s="95"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -6625,7 +6665,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="101"/>
+      <c r="A7" s="95"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -6653,7 +6693,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="101"/>
+      <c r="A8" s="95"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -6681,7 +6721,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="102"/>
+      <c r="A9" s="96"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -6743,7 +6783,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="103" t="s">
+      <c r="A12" s="97" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -6769,7 +6809,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="104"/>
+      <c r="A13" s="98"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -6793,7 +6833,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="104"/>
+      <c r="A14" s="98"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -6821,7 +6861,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="104"/>
+      <c r="A15" s="98"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -6849,7 +6889,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="104"/>
+      <c r="A16" s="98"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -6877,7 +6917,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="105"/>
+      <c r="A17" s="99"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -6939,7 +6979,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="106" t="s">
+      <c r="A20" s="100" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -6965,7 +7005,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="107"/>
+      <c r="A21" s="101"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -6993,7 +7033,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="107"/>
+      <c r="A22" s="101"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -7021,7 +7061,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="107"/>
+      <c r="A23" s="101"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -7049,7 +7089,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="107"/>
+      <c r="A24" s="101"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -7077,7 +7117,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="108"/>
+      <c r="A25" s="102"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -7139,7 +7179,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="109" t="s">
+      <c r="A28" s="103" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -7165,7 +7205,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="110"/>
+      <c r="A29" s="104"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -7193,7 +7233,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="110"/>
+      <c r="A30" s="104"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -7221,7 +7261,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="110"/>
+      <c r="A31" s="104"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -7249,7 +7289,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="110"/>
+      <c r="A32" s="104"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -7277,7 +7317,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="111"/>
+      <c r="A33" s="105"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -7339,7 +7379,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="112" t="s">
+      <c r="A36" s="106" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -7369,7 +7409,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="113"/>
+      <c r="A37" s="107"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -7397,7 +7437,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="113"/>
+      <c r="A38" s="107"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -7419,13 +7459,13 @@
       <c r="H38" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="J38" s="1" t="str">
+      <c r="J38" s="1">
         <f>IF(OR(Resultados!F38="",Resultados!G38=""),"",IF(AND(F38=Resultados!F38,G38=Resultados!G38),2,IF(((F38&gt;G38)=(Resultados!F38&gt;Resultados!G38))*((F38&lt;G38)=(Resultados!F38&lt;Resultados!G38)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="113"/>
+      <c r="A39" s="107"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -7447,13 +7487,13 @@
       <c r="H39" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="J39" s="1" t="str">
+      <c r="J39" s="1">
         <f>IF(OR(Resultados!F39="",Resultados!G39=""),"",IF(AND(F39=Resultados!F39,G39=Resultados!G39),2,IF(((F39&gt;G39)=(Resultados!F39&gt;Resultados!G39))*((F39&lt;G39)=(Resultados!F39&lt;Resultados!G39)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="113"/>
+      <c r="A40" s="107"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -7481,7 +7521,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="114"/>
+      <c r="A41" s="108"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -7543,7 +7583,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="82" t="s">
+      <c r="A44" s="76" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -7573,7 +7613,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="83"/>
+      <c r="A45" s="77"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -7601,7 +7641,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="83"/>
+      <c r="A46" s="77"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -7623,13 +7663,13 @@
       <c r="H46" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="J46" s="1" t="str">
+      <c r="J46" s="1">
         <f>IF(OR(Resultados!F46="",Resultados!G46=""),"",IF(AND(F46=Resultados!F46,G46=Resultados!G46),2,IF(((F46&gt;G46)=(Resultados!F46&gt;Resultados!G46))*((F46&lt;G46)=(Resultados!F46&lt;Resultados!G46)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="83"/>
+      <c r="A47" s="77"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -7651,13 +7691,13 @@
       <c r="H47" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="J47" s="1" t="str">
+      <c r="J47" s="1">
         <f>IF(OR(Resultados!F47="",Resultados!G47=""),"",IF(AND(F47=Resultados!F47,G47=Resultados!G47),2,IF(((F47&gt;G47)=(Resultados!F47&gt;Resultados!G47))*((F47&lt;G47)=(Resultados!F47&lt;Resultados!G47)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="83"/>
+      <c r="A48" s="77"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -7685,7 +7725,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="84"/>
+      <c r="A49" s="78"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -7747,7 +7787,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="85" t="s">
+      <c r="A52" s="79" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -7777,7 +7817,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="86"/>
+      <c r="A53" s="80"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -7805,7 +7845,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="86"/>
+      <c r="A54" s="80"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -7827,13 +7867,13 @@
       <c r="H54" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="J54" s="1" t="str">
+      <c r="J54" s="1">
         <f>IF(OR(Resultados!F54="",Resultados!G54=""),"",IF(AND(F54=Resultados!F54,G54=Resultados!G54),2,IF(((F54&gt;G54)=(Resultados!F54&gt;Resultados!G54))*((F54&lt;G54)=(Resultados!F54&lt;Resultados!G54)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="86"/>
+      <c r="A55" s="80"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -7855,13 +7895,13 @@
       <c r="H55" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="J55" s="1" t="str">
+      <c r="J55" s="1">
         <f>IF(OR(Resultados!F55="",Resultados!G55=""),"",IF(AND(F55=Resultados!F55,G55=Resultados!G55),2,IF(((F55&gt;G55)=(Resultados!F55&gt;Resultados!G55))*((F55&lt;G55)=(Resultados!F55&lt;Resultados!G55)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="86"/>
+      <c r="A56" s="80"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -7889,7 +7929,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="87"/>
+      <c r="A57" s="81"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -7951,7 +7991,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="88" t="s">
+      <c r="A60" s="82" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -7981,7 +8021,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="89"/>
+      <c r="A61" s="83"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -8009,7 +8049,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="89"/>
+      <c r="A62" s="83"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -8031,13 +8071,13 @@
       <c r="H62" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="J62" s="1" t="str">
+      <c r="J62" s="1">
         <f>IF(OR(Resultados!F62="",Resultados!G62=""),"",IF(AND(F62=Resultados!F62,G62=Resultados!G62),2,IF(((F62&gt;G62)=(Resultados!F62&gt;Resultados!G62))*((F62&lt;G62)=(Resultados!F62&lt;Resultados!G62)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="89"/>
+      <c r="A63" s="83"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -8059,13 +8099,13 @@
       <c r="H63" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="J63" s="1" t="str">
+      <c r="J63" s="1">
         <f>IF(OR(Resultados!F63="",Resultados!G63=""),"",IF(AND(F63=Resultados!F63,G63=Resultados!G63),2,IF(((F63&gt;G63)=(Resultados!F63&gt;Resultados!G63))*((F63&lt;G63)=(Resultados!F63&lt;Resultados!G63)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="89"/>
+      <c r="A64" s="83"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -8093,7 +8133,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="90"/>
+      <c r="A65" s="84"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -8155,7 +8195,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="91" t="s">
+      <c r="A68" s="85" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -8185,7 +8225,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="92"/>
+      <c r="A69" s="86"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -8213,7 +8253,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="92"/>
+      <c r="A70" s="86"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -8241,7 +8281,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="92"/>
+      <c r="A71" s="86"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -8269,7 +8309,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="92"/>
+      <c r="A72" s="86"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -8297,7 +8337,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="93"/>
+      <c r="A73" s="87"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -8359,7 +8399,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="94" t="s">
+      <c r="A76" s="88" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -8389,7 +8429,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="95"/>
+      <c r="A77" s="89"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -8417,7 +8457,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="95"/>
+      <c r="A78" s="89"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -8439,13 +8479,13 @@
       <c r="H78" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="J78" s="1" t="str">
+      <c r="J78" s="1">
         <f>IF(OR(Resultados!F78="",Resultados!G78=""),"",IF(AND(F78=Resultados!F78,G78=Resultados!G78),2,IF(((F78&gt;G78)=(Resultados!F78&gt;Resultados!G78))*((F78&lt;G78)=(Resultados!F78&lt;Resultados!G78)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="95"/>
+      <c r="A79" s="89"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -8473,7 +8513,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="95"/>
+      <c r="A80" s="89"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -8501,7 +8541,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="96"/>
+      <c r="A81" s="90"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -8563,7 +8603,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="97" t="s">
+      <c r="A84" s="91" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -8593,7 +8633,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="98"/>
+      <c r="A85" s="92"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -8621,7 +8661,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="98"/>
+      <c r="A86" s="92"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -8649,7 +8689,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="98"/>
+      <c r="A87" s="92"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -8677,7 +8717,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="98"/>
+      <c r="A88" s="92"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -8705,7 +8745,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="99"/>
+      <c r="A89" s="93"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -8767,7 +8807,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="79" t="s">
+      <c r="A92" s="73" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -8797,7 +8837,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="80"/>
+      <c r="A93" s="74"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -8825,7 +8865,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="80"/>
+      <c r="A94" s="74"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -8853,7 +8893,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="80"/>
+      <c r="A95" s="74"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -8881,7 +8921,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="80"/>
+      <c r="A96" s="74"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -8909,7 +8949,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="81"/>
+      <c r="A97" s="75"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -8974,18 +9014,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D1" s="67" t="s">
+      <c r="D1" s="109" t="s">
         <v>74</v>
       </c>
-      <c r="E1" s="68"/>
-      <c r="F1" s="69"/>
+      <c r="E1" s="110"/>
+      <c r="F1" s="111"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D2" s="70" t="s">
+      <c r="D2" s="112" t="s">
         <v>75</v>
       </c>
-      <c r="E2" s="71"/>
-      <c r="F2" s="72"/>
+      <c r="E2" s="113"/>
+      <c r="F2" s="114"/>
     </row>
     <row r="4" spans="1:6" s="29" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="57" t="s">
@@ -9010,17 +9050,17 @@
       </c>
       <c r="B5" s="58">
         <f>Cindy!L4</f>
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D5" s="59">
         <v>1</v>
       </c>
       <c r="E5" s="59" t="str" cm="1">
         <f t="array" ref="E5:F13">_xlfn._xlws.SORT(A5:B13,2,-1)</f>
-        <v>Erik</v>
+        <v>Bere</v>
       </c>
       <c r="F5" s="59">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -9029,16 +9069,16 @@
       </c>
       <c r="B6" s="58">
         <f>Wendy!L4</f>
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D6" s="55">
         <v>2</v>
       </c>
       <c r="E6" s="55" t="str">
-        <v>Bere</v>
+        <v>Erik</v>
       </c>
       <c r="F6" s="55">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -9047,16 +9087,16 @@
       </c>
       <c r="B7" s="58">
         <f>Jimmy!L4</f>
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D7" s="56">
         <v>3</v>
       </c>
       <c r="E7" s="56" t="str">
-        <v>Packy</v>
+        <v>Jimmy</v>
       </c>
       <c r="F7" s="56">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -9065,16 +9105,16 @@
       </c>
       <c r="B8" s="58">
         <f>Erick!L4</f>
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D8" s="28">
         <v>4</v>
       </c>
       <c r="E8" s="28" t="str">
-        <v>Wendy</v>
+        <v>Packy</v>
       </c>
       <c r="F8" s="28">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -9083,7 +9123,7 @@
       </c>
       <c r="B9" s="58">
         <f>Erik!L4</f>
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D9" s="28">
         <v>5</v>
@@ -9092,7 +9132,7 @@
         <v>Cindy</v>
       </c>
       <c r="F9" s="28">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -9101,16 +9141,16 @@
       </c>
       <c r="B10" s="58">
         <f>Lennon!L4</f>
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D10" s="28">
         <v>6</v>
       </c>
       <c r="E10" s="28" t="str">
-        <v>Jimmy</v>
+        <v>Wendy</v>
       </c>
       <c r="F10" s="28">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -9119,7 +9159,7 @@
       </c>
       <c r="B11" s="58">
         <f>Yulian!L4</f>
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D11" s="28">
         <v>7</v>
@@ -9128,7 +9168,7 @@
         <v>Lennon</v>
       </c>
       <c r="F11" s="28">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -9137,16 +9177,16 @@
       </c>
       <c r="B12" s="58">
         <f>Packy!L4</f>
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D12" s="28">
         <v>8</v>
       </c>
       <c r="E12" s="28" t="str">
-        <v>Yulian</v>
+        <v>Erick</v>
       </c>
       <c r="F12" s="28">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -9155,16 +9195,16 @@
       </c>
       <c r="B13" s="58">
         <f>Bere!L4</f>
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D13" s="28">
         <v>9</v>
       </c>
       <c r="E13" s="28" t="str">
-        <v>Erick</v>
+        <v>Yulian</v>
       </c>
       <c r="F13" s="28">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -9198,26 +9238,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="75"/>
+      <c r="A1" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="69"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="76"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="78"/>
+      <c r="A2" s="70"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="72"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="31"/>
@@ -9276,7 +9316,7 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -10126,9 +10166,9 @@
       <c r="H38" s="46" t="s">
         <v>33</v>
       </c>
-      <c r="J38" s="1" t="str">
+      <c r="J38" s="1">
         <f>IF(OR(Resultados!F38="",Resultados!G38=""),"",IF(AND(F38=Resultados!F38,G38=Resultados!G38),2,IF(((F38&gt;G38)=(Resultados!F38&gt;Resultados!G38))*((F38&lt;G38)=(Resultados!F38&lt;Resultados!G38)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -10154,9 +10194,9 @@
       <c r="H39" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="J39" s="1" t="str">
+      <c r="J39" s="1">
         <f>IF(OR(Resultados!F39="",Resultados!G39=""),"",IF(AND(F39=Resultados!F39,G39=Resultados!G39),2,IF(((F39&gt;G39)=(Resultados!F39&gt;Resultados!G39))*((F39&lt;G39)=(Resultados!F39&lt;Resultados!G39)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -10330,9 +10370,9 @@
       <c r="H46" s="46" t="s">
         <v>38</v>
       </c>
-      <c r="J46" s="1" t="str">
+      <c r="J46" s="1">
         <f>IF(OR(Resultados!F46="",Resultados!G46=""),"",IF(AND(F46=Resultados!F46,G46=Resultados!G46),2,IF(((F46&gt;G46)=(Resultados!F46&gt;Resultados!G46))*((F46&lt;G46)=(Resultados!F46&lt;Resultados!G46)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -10358,9 +10398,9 @@
       <c r="H47" s="46" t="s">
         <v>37</v>
       </c>
-      <c r="J47" s="1" t="str">
+      <c r="J47" s="1">
         <f>IF(OR(Resultados!F47="",Resultados!G47=""),"",IF(AND(F47=Resultados!F47,G47=Resultados!G47),2,IF(((F47&gt;G47)=(Resultados!F47&gt;Resultados!G47))*((F47&lt;G47)=(Resultados!F47&lt;Resultados!G47)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -10534,9 +10574,9 @@
       <c r="H54" s="46" t="s">
         <v>43</v>
       </c>
-      <c r="J54" s="1" t="str">
+      <c r="J54" s="1">
         <f>IF(OR(Resultados!F54="",Resultados!G54=""),"",IF(AND(F54=Resultados!F54,G54=Resultados!G54),2,IF(((F54&gt;G54)=(Resultados!F54&gt;Resultados!G54))*((F54&lt;G54)=(Resultados!F54&lt;Resultados!G54)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -10562,9 +10602,9 @@
       <c r="H55" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="J55" s="1" t="str">
+      <c r="J55" s="1">
         <f>IF(OR(Resultados!F55="",Resultados!G55=""),"",IF(AND(F55=Resultados!F55,G55=Resultados!G55),2,IF(((F55&gt;G55)=(Resultados!F55&gt;Resultados!G55))*((F55&lt;G55)=(Resultados!F55&lt;Resultados!G55)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -10738,9 +10778,9 @@
       <c r="H62" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="J62" s="1" t="str">
+      <c r="J62" s="1">
         <f>IF(OR(Resultados!F62="",Resultados!G62=""),"",IF(AND(F62=Resultados!F62,G62=Resultados!G62),2,IF(((F62&gt;G62)=(Resultados!F62&gt;Resultados!G62))*((F62&lt;G62)=(Resultados!F62&lt;Resultados!G62)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -10766,9 +10806,9 @@
       <c r="H63" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="J63" s="1" t="str">
+      <c r="J63" s="1">
         <f>IF(OR(Resultados!F63="",Resultados!G63=""),"",IF(AND(F63=Resultados!F63,G63=Resultados!G63),2,IF(((F63&gt;G63)=(Resultados!F63&gt;Resultados!G63))*((F63&lt;G63)=(Resultados!F63&lt;Resultados!G63)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -11146,9 +11186,9 @@
       <c r="H78" s="46" t="s">
         <v>58</v>
       </c>
-      <c r="J78" s="1" t="str">
+      <c r="J78" s="1">
         <f>IF(OR(Resultados!F78="",Resultados!G78=""),"",IF(AND(F78=Resultados!F78,G78=Resultados!G78),2,IF(((F78&gt;G78)=(Resultados!F78&gt;Resultados!G78))*((F78&lt;G78)=(Resultados!F78&lt;Resultados!G78)),1,0)))</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -11687,26 +11727,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="75"/>
+      <c r="A1" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="69"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="76"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="78"/>
+      <c r="A2" s="70"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="72"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="31"/>
@@ -11765,7 +11805,7 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -12615,9 +12655,9 @@
       <c r="H38" s="46" t="s">
         <v>33</v>
       </c>
-      <c r="J38" s="1" t="str">
+      <c r="J38" s="1">
         <f>IF(OR(Resultados!F38="",Resultados!G38=""),"",IF(AND(F38=Resultados!F38,G38=Resultados!G38),2,IF(((F38&gt;G38)=(Resultados!F38&gt;Resultados!G38))*((F38&lt;G38)=(Resultados!F38&lt;Resultados!G38)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -12643,9 +12683,9 @@
       <c r="H39" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="J39" s="1" t="str">
+      <c r="J39" s="1">
         <f>IF(OR(Resultados!F39="",Resultados!G39=""),"",IF(AND(F39=Resultados!F39,G39=Resultados!G39),2,IF(((F39&gt;G39)=(Resultados!F39&gt;Resultados!G39))*((F39&lt;G39)=(Resultados!F39&lt;Resultados!G39)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -12819,9 +12859,9 @@
       <c r="H46" s="46" t="s">
         <v>38</v>
       </c>
-      <c r="J46" s="1" t="str">
+      <c r="J46" s="1">
         <f>IF(OR(Resultados!F46="",Resultados!G46=""),"",IF(AND(F46=Resultados!F46,G46=Resultados!G46),2,IF(((F46&gt;G46)=(Resultados!F46&gt;Resultados!G46))*((F46&lt;G46)=(Resultados!F46&lt;Resultados!G46)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -12847,9 +12887,9 @@
       <c r="H47" s="46" t="s">
         <v>37</v>
       </c>
-      <c r="J47" s="1" t="str">
+      <c r="J47" s="1">
         <f>IF(OR(Resultados!F47="",Resultados!G47=""),"",IF(AND(F47=Resultados!F47,G47=Resultados!G47),2,IF(((F47&gt;G47)=(Resultados!F47&gt;Resultados!G47))*((F47&lt;G47)=(Resultados!F47&lt;Resultados!G47)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -13023,9 +13063,9 @@
       <c r="H54" s="46" t="s">
         <v>43</v>
       </c>
-      <c r="J54" s="1" t="str">
+      <c r="J54" s="1">
         <f>IF(OR(Resultados!F54="",Resultados!G54=""),"",IF(AND(F54=Resultados!F54,G54=Resultados!G54),2,IF(((F54&gt;G54)=(Resultados!F54&gt;Resultados!G54))*((F54&lt;G54)=(Resultados!F54&lt;Resultados!G54)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -13051,9 +13091,9 @@
       <c r="H55" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="J55" s="1" t="str">
+      <c r="J55" s="1">
         <f>IF(OR(Resultados!F55="",Resultados!G55=""),"",IF(AND(F55=Resultados!F55,G55=Resultados!G55),2,IF(((F55&gt;G55)=(Resultados!F55&gt;Resultados!G55))*((F55&lt;G55)=(Resultados!F55&lt;Resultados!G55)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -13227,9 +13267,9 @@
       <c r="H62" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="J62" s="1" t="str">
+      <c r="J62" s="1">
         <f>IF(OR(Resultados!F62="",Resultados!G62=""),"",IF(AND(F62=Resultados!F62,G62=Resultados!G62),2,IF(((F62&gt;G62)=(Resultados!F62&gt;Resultados!G62))*((F62&lt;G62)=(Resultados!F62&lt;Resultados!G62)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -13255,9 +13295,9 @@
       <c r="H63" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="J63" s="1" t="str">
+      <c r="J63" s="1">
         <f>IF(OR(Resultados!F63="",Resultados!G63=""),"",IF(AND(F63=Resultados!F63,G63=Resultados!G63),2,IF(((F63&gt;G63)=(Resultados!F63&gt;Resultados!G63))*((F63&lt;G63)=(Resultados!F63&lt;Resultados!G63)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -13635,9 +13675,9 @@
       <c r="H78" s="46" t="s">
         <v>58</v>
       </c>
-      <c r="J78" s="1" t="str">
+      <c r="J78" s="1">
         <f>IF(OR(Resultados!F78="",Resultados!G78=""),"",IF(AND(F78=Resultados!F78,G78=Resultados!G78),2,IF(((F78&gt;G78)=(Resultados!F78&gt;Resultados!G78))*((F78&lt;G78)=(Resultados!F78&lt;Resultados!G78)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -14175,26 +14215,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="75"/>
+      <c r="A1" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="69"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="76"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="78"/>
+      <c r="A2" s="70"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="72"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -14227,7 +14267,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="100" t="s">
+      <c r="A4" s="94" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -14253,11 +14293,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="101"/>
+      <c r="A5" s="95"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -14281,7 +14321,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="101"/>
+      <c r="A6" s="95"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -14309,7 +14349,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="101"/>
+      <c r="A7" s="95"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -14337,7 +14377,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="101"/>
+      <c r="A8" s="95"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -14365,7 +14405,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="102"/>
+      <c r="A9" s="96"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -14427,7 +14467,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="103" t="s">
+      <c r="A12" s="97" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -14453,7 +14493,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="104"/>
+      <c r="A13" s="98"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -14477,7 +14517,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="104"/>
+      <c r="A14" s="98"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -14505,7 +14545,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="104"/>
+      <c r="A15" s="98"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -14533,7 +14573,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="104"/>
+      <c r="A16" s="98"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -14561,7 +14601,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="105"/>
+      <c r="A17" s="99"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -14623,7 +14663,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="106" t="s">
+      <c r="A20" s="100" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -14649,7 +14689,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="107"/>
+      <c r="A21" s="101"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -14677,7 +14717,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="107"/>
+      <c r="A22" s="101"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -14705,7 +14745,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="107"/>
+      <c r="A23" s="101"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -14733,7 +14773,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="107"/>
+      <c r="A24" s="101"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -14761,7 +14801,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="108"/>
+      <c r="A25" s="102"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -14823,7 +14863,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="109" t="s">
+      <c r="A28" s="103" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -14849,7 +14889,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="110"/>
+      <c r="A29" s="104"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -14877,7 +14917,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="110"/>
+      <c r="A30" s="104"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -14905,7 +14945,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="110"/>
+      <c r="A31" s="104"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -14933,7 +14973,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="110"/>
+      <c r="A32" s="104"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -14961,7 +15001,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="111"/>
+      <c r="A33" s="105"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -15023,7 +15063,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="112" t="s">
+      <c r="A36" s="106" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -15053,7 +15093,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="113"/>
+      <c r="A37" s="107"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -15081,7 +15121,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="113"/>
+      <c r="A38" s="107"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -15103,13 +15143,13 @@
       <c r="H38" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="J38" s="1" t="str">
+      <c r="J38" s="1">
         <f>IF(OR(Resultados!F38="",Resultados!G38=""),"",IF(AND(F38=Resultados!F38,G38=Resultados!G38),2,IF(((F38&gt;G38)=(Resultados!F38&gt;Resultados!G38))*((F38&lt;G38)=(Resultados!F38&lt;Resultados!G38)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="113"/>
+      <c r="A39" s="107"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -15131,13 +15171,13 @@
       <c r="H39" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="J39" s="1" t="str">
+      <c r="J39" s="1">
         <f>IF(OR(Resultados!F39="",Resultados!G39=""),"",IF(AND(F39=Resultados!F39,G39=Resultados!G39),2,IF(((F39&gt;G39)=(Resultados!F39&gt;Resultados!G39))*((F39&lt;G39)=(Resultados!F39&lt;Resultados!G39)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="113"/>
+      <c r="A40" s="107"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -15165,7 +15205,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="114"/>
+      <c r="A41" s="108"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -15227,7 +15267,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="82" t="s">
+      <c r="A44" s="76" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -15257,7 +15297,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="83"/>
+      <c r="A45" s="77"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -15285,7 +15325,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="83"/>
+      <c r="A46" s="77"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -15307,13 +15347,13 @@
       <c r="H46" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="J46" s="1" t="str">
+      <c r="J46" s="1">
         <f>IF(OR(Resultados!F46="",Resultados!G46=""),"",IF(AND(F46=Resultados!F46,G46=Resultados!G46),2,IF(((F46&gt;G46)=(Resultados!F46&gt;Resultados!G46))*((F46&lt;G46)=(Resultados!F46&lt;Resultados!G46)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="83"/>
+      <c r="A47" s="77"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -15335,13 +15375,13 @@
       <c r="H47" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="J47" s="1" t="str">
+      <c r="J47" s="1">
         <f>IF(OR(Resultados!F47="",Resultados!G47=""),"",IF(AND(F47=Resultados!F47,G47=Resultados!G47),2,IF(((F47&gt;G47)=(Resultados!F47&gt;Resultados!G47))*((F47&lt;G47)=(Resultados!F47&lt;Resultados!G47)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="83"/>
+      <c r="A48" s="77"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -15369,7 +15409,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="84"/>
+      <c r="A49" s="78"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -15431,7 +15471,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="85" t="s">
+      <c r="A52" s="79" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -15461,7 +15501,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="86"/>
+      <c r="A53" s="80"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -15489,7 +15529,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="86"/>
+      <c r="A54" s="80"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -15511,13 +15551,13 @@
       <c r="H54" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="J54" s="1" t="str">
+      <c r="J54" s="1">
         <f>IF(OR(Resultados!F54="",Resultados!G54=""),"",IF(AND(F54=Resultados!F54,G54=Resultados!G54),2,IF(((F54&gt;G54)=(Resultados!F54&gt;Resultados!G54))*((F54&lt;G54)=(Resultados!F54&lt;Resultados!G54)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="86"/>
+      <c r="A55" s="80"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -15539,13 +15579,13 @@
       <c r="H55" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="J55" s="1" t="str">
+      <c r="J55" s="1">
         <f>IF(OR(Resultados!F55="",Resultados!G55=""),"",IF(AND(F55=Resultados!F55,G55=Resultados!G55),2,IF(((F55&gt;G55)=(Resultados!F55&gt;Resultados!G55))*((F55&lt;G55)=(Resultados!F55&lt;Resultados!G55)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="86"/>
+      <c r="A56" s="80"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -15573,7 +15613,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="87"/>
+      <c r="A57" s="81"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -15635,7 +15675,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="88" t="s">
+      <c r="A60" s="82" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -15665,7 +15705,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="89"/>
+      <c r="A61" s="83"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -15693,7 +15733,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="89"/>
+      <c r="A62" s="83"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -15715,13 +15755,13 @@
       <c r="H62" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="J62" s="1" t="str">
+      <c r="J62" s="1">
         <f>IF(OR(Resultados!F62="",Resultados!G62=""),"",IF(AND(F62=Resultados!F62,G62=Resultados!G62),2,IF(((F62&gt;G62)=(Resultados!F62&gt;Resultados!G62))*((F62&lt;G62)=(Resultados!F62&lt;Resultados!G62)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="89"/>
+      <c r="A63" s="83"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -15743,13 +15783,13 @@
       <c r="H63" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="J63" s="1" t="str">
+      <c r="J63" s="1">
         <f>IF(OR(Resultados!F63="",Resultados!G63=""),"",IF(AND(F63=Resultados!F63,G63=Resultados!G63),2,IF(((F63&gt;G63)=(Resultados!F63&gt;Resultados!G63))*((F63&lt;G63)=(Resultados!F63&lt;Resultados!G63)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="89"/>
+      <c r="A64" s="83"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -15777,7 +15817,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="90"/>
+      <c r="A65" s="84"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -15839,7 +15879,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="91" t="s">
+      <c r="A68" s="85" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -15869,7 +15909,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="92"/>
+      <c r="A69" s="86"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -15897,7 +15937,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="92"/>
+      <c r="A70" s="86"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -15925,7 +15965,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="92"/>
+      <c r="A71" s="86"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -15953,7 +15993,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="92"/>
+      <c r="A72" s="86"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -15981,7 +16021,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="93"/>
+      <c r="A73" s="87"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -16043,7 +16083,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="94" t="s">
+      <c r="A76" s="88" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -16073,7 +16113,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="95"/>
+      <c r="A77" s="89"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -16101,7 +16141,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="95"/>
+      <c r="A78" s="89"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -16123,13 +16163,13 @@
       <c r="H78" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="J78" s="1" t="str">
+      <c r="J78" s="1">
         <f>IF(OR(Resultados!F78="",Resultados!G78=""),"",IF(AND(F78=Resultados!F78,G78=Resultados!G78),2,IF(((F78&gt;G78)=(Resultados!F78&gt;Resultados!G78))*((F78&lt;G78)=(Resultados!F78&lt;Resultados!G78)),1,0)))</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="95"/>
+      <c r="A79" s="89"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -16157,7 +16197,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="95"/>
+      <c r="A80" s="89"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -16185,7 +16225,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="96"/>
+      <c r="A81" s="90"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -16247,7 +16287,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="97" t="s">
+      <c r="A84" s="91" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -16277,7 +16317,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="98"/>
+      <c r="A85" s="92"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -16305,7 +16345,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="98"/>
+      <c r="A86" s="92"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -16333,7 +16373,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="98"/>
+      <c r="A87" s="92"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -16361,7 +16401,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="98"/>
+      <c r="A88" s="92"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -16389,7 +16429,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="99"/>
+      <c r="A89" s="93"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -16451,7 +16491,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="79" t="s">
+      <c r="A92" s="73" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -16481,7 +16521,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="80"/>
+      <c r="A93" s="74"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -16509,7 +16549,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="80"/>
+      <c r="A94" s="74"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -16537,7 +16577,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="80"/>
+      <c r="A95" s="74"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -16565,7 +16605,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="80"/>
+      <c r="A96" s="74"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -16593,7 +16633,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="81"/>
+      <c r="A97" s="75"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -16663,26 +16703,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="75"/>
+      <c r="A1" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="69"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="76"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="78"/>
+      <c r="A2" s="70"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="72"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -16715,7 +16755,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="100" t="s">
+      <c r="A4" s="94" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -16741,11 +16781,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="101"/>
+      <c r="A5" s="95"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -16769,7 +16809,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="101"/>
+      <c r="A6" s="95"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -16797,7 +16837,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="101"/>
+      <c r="A7" s="95"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -16825,7 +16865,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="101"/>
+      <c r="A8" s="95"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -16853,7 +16893,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="102"/>
+      <c r="A9" s="96"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -16915,7 +16955,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="103" t="s">
+      <c r="A12" s="97" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -16941,7 +16981,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="104"/>
+      <c r="A13" s="98"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -16965,7 +17005,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="104"/>
+      <c r="A14" s="98"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -16993,7 +17033,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="104"/>
+      <c r="A15" s="98"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -17021,7 +17061,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="104"/>
+      <c r="A16" s="98"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -17049,7 +17089,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="105"/>
+      <c r="A17" s="99"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -17111,7 +17151,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="106" t="s">
+      <c r="A20" s="100" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -17137,7 +17177,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="107"/>
+      <c r="A21" s="101"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -17165,7 +17205,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="107"/>
+      <c r="A22" s="101"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -17193,7 +17233,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="107"/>
+      <c r="A23" s="101"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -17221,7 +17261,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="107"/>
+      <c r="A24" s="101"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -17249,7 +17289,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="108"/>
+      <c r="A25" s="102"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -17311,7 +17351,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="109" t="s">
+      <c r="A28" s="103" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -17337,7 +17377,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="110"/>
+      <c r="A29" s="104"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -17365,7 +17405,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="110"/>
+      <c r="A30" s="104"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -17393,7 +17433,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="110"/>
+      <c r="A31" s="104"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -17421,7 +17461,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="110"/>
+      <c r="A32" s="104"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -17449,7 +17489,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="111"/>
+      <c r="A33" s="105"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -17511,7 +17551,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="112" t="s">
+      <c r="A36" s="106" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -17541,7 +17581,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="113"/>
+      <c r="A37" s="107"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -17569,7 +17609,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="113"/>
+      <c r="A38" s="107"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -17591,13 +17631,13 @@
       <c r="H38" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="J38" s="1" t="str">
+      <c r="J38" s="1">
         <f>IF(OR(Resultados!F38="",Resultados!G38=""),"",IF(AND(F38=Resultados!F38,G38=Resultados!G38),2,IF(((F38&gt;G38)=(Resultados!F38&gt;Resultados!G38))*((F38&lt;G38)=(Resultados!F38&lt;Resultados!G38)),1,0)))</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="113"/>
+      <c r="A39" s="107"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -17619,13 +17659,13 @@
       <c r="H39" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="J39" s="1" t="str">
+      <c r="J39" s="1">
         <f>IF(OR(Resultados!F39="",Resultados!G39=""),"",IF(AND(F39=Resultados!F39,G39=Resultados!G39),2,IF(((F39&gt;G39)=(Resultados!F39&gt;Resultados!G39))*((F39&lt;G39)=(Resultados!F39&lt;Resultados!G39)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="113"/>
+      <c r="A40" s="107"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -17653,7 +17693,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="114"/>
+      <c r="A41" s="108"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -17715,7 +17755,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="82" t="s">
+      <c r="A44" s="76" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -17745,7 +17785,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="83"/>
+      <c r="A45" s="77"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -17773,7 +17813,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="83"/>
+      <c r="A46" s="77"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -17795,13 +17835,13 @@
       <c r="H46" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="J46" s="1" t="str">
+      <c r="J46" s="1">
         <f>IF(OR(Resultados!F46="",Resultados!G46=""),"",IF(AND(F46=Resultados!F46,G46=Resultados!G46),2,IF(((F46&gt;G46)=(Resultados!F46&gt;Resultados!G46))*((F46&lt;G46)=(Resultados!F46&lt;Resultados!G46)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="83"/>
+      <c r="A47" s="77"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -17823,13 +17863,13 @@
       <c r="H47" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="J47" s="1" t="str">
+      <c r="J47" s="1">
         <f>IF(OR(Resultados!F47="",Resultados!G47=""),"",IF(AND(F47=Resultados!F47,G47=Resultados!G47),2,IF(((F47&gt;G47)=(Resultados!F47&gt;Resultados!G47))*((F47&lt;G47)=(Resultados!F47&lt;Resultados!G47)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="83"/>
+      <c r="A48" s="77"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -17857,7 +17897,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="84"/>
+      <c r="A49" s="78"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -17919,7 +17959,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="85" t="s">
+      <c r="A52" s="79" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -17949,7 +17989,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="86"/>
+      <c r="A53" s="80"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -17977,7 +18017,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="86"/>
+      <c r="A54" s="80"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -17999,13 +18039,13 @@
       <c r="H54" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="J54" s="1" t="str">
+      <c r="J54" s="1">
         <f>IF(OR(Resultados!F54="",Resultados!G54=""),"",IF(AND(F54=Resultados!F54,G54=Resultados!G54),2,IF(((F54&gt;G54)=(Resultados!F54&gt;Resultados!G54))*((F54&lt;G54)=(Resultados!F54&lt;Resultados!G54)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="86"/>
+      <c r="A55" s="80"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -18027,13 +18067,13 @@
       <c r="H55" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="J55" s="1" t="str">
+      <c r="J55" s="1">
         <f>IF(OR(Resultados!F55="",Resultados!G55=""),"",IF(AND(F55=Resultados!F55,G55=Resultados!G55),2,IF(((F55&gt;G55)=(Resultados!F55&gt;Resultados!G55))*((F55&lt;G55)=(Resultados!F55&lt;Resultados!G55)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="86"/>
+      <c r="A56" s="80"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -18061,7 +18101,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="87"/>
+      <c r="A57" s="81"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -18123,7 +18163,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="88" t="s">
+      <c r="A60" s="82" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -18153,7 +18193,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="89"/>
+      <c r="A61" s="83"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -18181,7 +18221,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="89"/>
+      <c r="A62" s="83"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -18203,13 +18243,13 @@
       <c r="H62" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="J62" s="1" t="str">
+      <c r="J62" s="1">
         <f>IF(OR(Resultados!F62="",Resultados!G62=""),"",IF(AND(F62=Resultados!F62,G62=Resultados!G62),2,IF(((F62&gt;G62)=(Resultados!F62&gt;Resultados!G62))*((F62&lt;G62)=(Resultados!F62&lt;Resultados!G62)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="89"/>
+      <c r="A63" s="83"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -18231,13 +18271,13 @@
       <c r="H63" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="J63" s="1" t="str">
+      <c r="J63" s="1">
         <f>IF(OR(Resultados!F63="",Resultados!G63=""),"",IF(AND(F63=Resultados!F63,G63=Resultados!G63),2,IF(((F63&gt;G63)=(Resultados!F63&gt;Resultados!G63))*((F63&lt;G63)=(Resultados!F63&lt;Resultados!G63)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="89"/>
+      <c r="A64" s="83"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -18265,7 +18305,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="90"/>
+      <c r="A65" s="84"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -18327,7 +18367,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="91" t="s">
+      <c r="A68" s="85" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -18357,7 +18397,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="92"/>
+      <c r="A69" s="86"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -18385,7 +18425,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="92"/>
+      <c r="A70" s="86"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -18413,7 +18453,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="92"/>
+      <c r="A71" s="86"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -18441,7 +18481,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="92"/>
+      <c r="A72" s="86"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -18469,7 +18509,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="93"/>
+      <c r="A73" s="87"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -18531,7 +18571,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="94" t="s">
+      <c r="A76" s="88" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -18561,7 +18601,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="95"/>
+      <c r="A77" s="89"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -18589,7 +18629,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="95"/>
+      <c r="A78" s="89"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -18611,13 +18651,13 @@
       <c r="H78" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="J78" s="1" t="str">
+      <c r="J78" s="1">
         <f>IF(OR(Resultados!F78="",Resultados!G78=""),"",IF(AND(F78=Resultados!F78,G78=Resultados!G78),2,IF(((F78&gt;G78)=(Resultados!F78&gt;Resultados!G78))*((F78&lt;G78)=(Resultados!F78&lt;Resultados!G78)),1,0)))</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="95"/>
+      <c r="A79" s="89"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -18645,7 +18685,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="95"/>
+      <c r="A80" s="89"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -18673,7 +18713,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="96"/>
+      <c r="A81" s="90"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -18735,7 +18775,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="97" t="s">
+      <c r="A84" s="91" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -18765,7 +18805,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="98"/>
+      <c r="A85" s="92"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -18793,7 +18833,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="98"/>
+      <c r="A86" s="92"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -18821,7 +18861,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="98"/>
+      <c r="A87" s="92"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -18849,7 +18889,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="98"/>
+      <c r="A88" s="92"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -18877,7 +18917,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="99"/>
+      <c r="A89" s="93"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -18939,7 +18979,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="79" t="s">
+      <c r="A92" s="73" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -18969,7 +19009,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="80"/>
+      <c r="A93" s="74"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -18997,7 +19037,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="80"/>
+      <c r="A94" s="74"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -19025,7 +19065,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="80"/>
+      <c r="A95" s="74"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -19053,7 +19093,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="80"/>
+      <c r="A96" s="74"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -19081,7 +19121,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="81"/>
+      <c r="A97" s="75"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -19151,26 +19191,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="75"/>
+      <c r="A1" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="69"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="76"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="78"/>
+      <c r="A2" s="70"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="72"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -19203,7 +19243,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="100" t="s">
+      <c r="A4" s="94" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -19229,11 +19269,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="101"/>
+      <c r="A5" s="95"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -19257,7 +19297,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="101"/>
+      <c r="A6" s="95"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -19285,7 +19325,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="101"/>
+      <c r="A7" s="95"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -19313,7 +19353,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="101"/>
+      <c r="A8" s="95"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -19341,7 +19381,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="102"/>
+      <c r="A9" s="96"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -19403,7 +19443,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="103" t="s">
+      <c r="A12" s="97" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -19429,7 +19469,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="104"/>
+      <c r="A13" s="98"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -19453,7 +19493,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="104"/>
+      <c r="A14" s="98"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -19481,7 +19521,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="104"/>
+      <c r="A15" s="98"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -19509,7 +19549,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="104"/>
+      <c r="A16" s="98"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -19537,7 +19577,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="105"/>
+      <c r="A17" s="99"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -19599,7 +19639,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="106" t="s">
+      <c r="A20" s="100" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -19625,7 +19665,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="107"/>
+      <c r="A21" s="101"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -19653,7 +19693,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="107"/>
+      <c r="A22" s="101"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -19681,7 +19721,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="107"/>
+      <c r="A23" s="101"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -19709,7 +19749,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="107"/>
+      <c r="A24" s="101"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -19737,7 +19777,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="108"/>
+      <c r="A25" s="102"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -19799,7 +19839,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="109" t="s">
+      <c r="A28" s="103" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -19825,7 +19865,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="110"/>
+      <c r="A29" s="104"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -19853,7 +19893,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="110"/>
+      <c r="A30" s="104"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -19881,7 +19921,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="110"/>
+      <c r="A31" s="104"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -19909,7 +19949,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="110"/>
+      <c r="A32" s="104"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -19933,7 +19973,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="111"/>
+      <c r="A33" s="105"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -19991,7 +20031,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="112" t="s">
+      <c r="A36" s="106" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -20021,7 +20061,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="113"/>
+      <c r="A37" s="107"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -20049,7 +20089,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="113"/>
+      <c r="A38" s="107"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -20062,18 +20102,22 @@
       <c r="E38" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="F38" s="25"/>
-      <c r="G38" s="25"/>
+      <c r="F38" s="25">
+        <v>4</v>
+      </c>
+      <c r="G38" s="25">
+        <v>2</v>
+      </c>
       <c r="H38" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="J38" s="1" t="str">
+      <c r="J38" s="1">
         <f>IF(OR(Resultados!F38="",Resultados!G38=""),"",IF(AND(F38=Resultados!F38,G38=Resultados!G38),2,IF(((F38&gt;G38)=(Resultados!F38&gt;Resultados!G38))*((F38&lt;G38)=(Resultados!F38&lt;Resultados!G38)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="113"/>
+      <c r="A39" s="107"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -20086,18 +20130,22 @@
       <c r="E39" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="F39" s="25"/>
-      <c r="G39" s="25"/>
+      <c r="F39" s="25">
+        <v>2</v>
+      </c>
+      <c r="G39" s="25">
+        <v>1</v>
+      </c>
       <c r="H39" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="J39" s="1" t="str">
+      <c r="J39" s="1">
         <f>IF(OR(Resultados!F39="",Resultados!G39=""),"",IF(AND(F39=Resultados!F39,G39=Resultados!G39),2,IF(((F39&gt;G39)=(Resultados!F39&gt;Resultados!G39))*((F39&lt;G39)=(Resultados!F39&lt;Resultados!G39)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="113"/>
+      <c r="A40" s="107"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -20121,7 +20169,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="114"/>
+      <c r="A41" s="108"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -20179,7 +20227,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="82" t="s">
+      <c r="A44" s="76" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -20209,7 +20257,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="83"/>
+      <c r="A45" s="77"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -20237,7 +20285,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="83"/>
+      <c r="A46" s="77"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -20250,18 +20298,22 @@
       <c r="E46" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="F46" s="25"/>
-      <c r="G46" s="25"/>
+      <c r="F46" s="25">
+        <v>3</v>
+      </c>
+      <c r="G46" s="25">
+        <v>1</v>
+      </c>
       <c r="H46" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="J46" s="1" t="str">
+      <c r="J46" s="1">
         <f>IF(OR(Resultados!F46="",Resultados!G46=""),"",IF(AND(F46=Resultados!F46,G46=Resultados!G46),2,IF(((F46&gt;G46)=(Resultados!F46&gt;Resultados!G46))*((F46&lt;G46)=(Resultados!F46&lt;Resultados!G46)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="83"/>
+      <c r="A47" s="77"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -20274,18 +20326,22 @@
       <c r="E47" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F47" s="25"/>
-      <c r="G47" s="25"/>
+      <c r="F47" s="25">
+        <v>1</v>
+      </c>
+      <c r="G47" s="25">
+        <v>2</v>
+      </c>
       <c r="H47" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="J47" s="1" t="str">
+      <c r="J47" s="1">
         <f>IF(OR(Resultados!F47="",Resultados!G47=""),"",IF(AND(F47=Resultados!F47,G47=Resultados!G47),2,IF(((F47&gt;G47)=(Resultados!F47&gt;Resultados!G47))*((F47&lt;G47)=(Resultados!F47&lt;Resultados!G47)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="83"/>
+      <c r="A48" s="77"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -20309,7 +20365,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="84"/>
+      <c r="A49" s="78"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -20367,7 +20423,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="85" t="s">
+      <c r="A52" s="79" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -20397,7 +20453,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="86"/>
+      <c r="A53" s="80"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -20414,18 +20470,18 @@
         <v>0</v>
       </c>
       <c r="G53" s="26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H53" s="21" t="s">
         <v>44</v>
       </c>
       <c r="J53" s="1">
         <f>IF(OR(Resultados!F53="",Resultados!G53=""),"",IF(AND(F53=Resultados!F53,G53=Resultados!G53),2,IF(((F53&gt;G53)=(Resultados!F53&gt;Resultados!G53))*((F53&lt;G53)=(Resultados!F53&lt;Resultados!G53)),1,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="86"/>
+      <c r="A54" s="80"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -20438,18 +20494,22 @@
       <c r="E54" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="F54" s="25"/>
-      <c r="G54" s="25"/>
+      <c r="F54" s="25">
+        <v>4</v>
+      </c>
+      <c r="G54" s="25">
+        <v>1</v>
+      </c>
       <c r="H54" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="J54" s="1" t="str">
+      <c r="J54" s="1">
         <f>IF(OR(Resultados!F54="",Resultados!G54=""),"",IF(AND(F54=Resultados!F54,G54=Resultados!G54),2,IF(((F54&gt;G54)=(Resultados!F54&gt;Resultados!G54))*((F54&lt;G54)=(Resultados!F54&lt;Resultados!G54)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="86"/>
+      <c r="A55" s="80"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -20462,18 +20522,22 @@
       <c r="E55" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F55" s="25"/>
-      <c r="G55" s="25"/>
+      <c r="F55" s="25">
+        <v>1</v>
+      </c>
+      <c r="G55" s="25">
+        <v>3</v>
+      </c>
       <c r="H55" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="J55" s="1" t="str">
+      <c r="J55" s="1">
         <f>IF(OR(Resultados!F55="",Resultados!G55=""),"",IF(AND(F55=Resultados!F55,G55=Resultados!G55),2,IF(((F55&gt;G55)=(Resultados!F55&gt;Resultados!G55))*((F55&lt;G55)=(Resultados!F55&lt;Resultados!G55)),1,0)))</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="86"/>
+      <c r="A56" s="80"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -20497,7 +20561,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="87"/>
+      <c r="A57" s="81"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -20555,7 +20619,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="88" t="s">
+      <c r="A60" s="82" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -20585,7 +20649,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="89"/>
+      <c r="A61" s="83"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -20613,7 +20677,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="89"/>
+      <c r="A62" s="83"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -20626,18 +20690,22 @@
       <c r="E62" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="F62" s="25"/>
-      <c r="G62" s="25"/>
+      <c r="F62" s="25">
+        <v>4</v>
+      </c>
+      <c r="G62" s="25">
+        <v>1</v>
+      </c>
       <c r="H62" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="J62" s="1" t="str">
+      <c r="J62" s="1">
         <f>IF(OR(Resultados!F62="",Resultados!G62=""),"",IF(AND(F62=Resultados!F62,G62=Resultados!G62),2,IF(((F62&gt;G62)=(Resultados!F62&gt;Resultados!G62))*((F62&lt;G62)=(Resultados!F62&lt;Resultados!G62)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="89"/>
+      <c r="A63" s="83"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -20650,18 +20718,22 @@
       <c r="E63" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="F63" s="25"/>
-      <c r="G63" s="25"/>
+      <c r="F63" s="25">
+        <v>2</v>
+      </c>
+      <c r="G63" s="25">
+        <v>1</v>
+      </c>
       <c r="H63" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="J63" s="1" t="str">
+      <c r="J63" s="1">
         <f>IF(OR(Resultados!F63="",Resultados!G63=""),"",IF(AND(F63=Resultados!F63,G63=Resultados!G63),2,IF(((F63&gt;G63)=(Resultados!F63&gt;Resultados!G63))*((F63&lt;G63)=(Resultados!F63&lt;Resultados!G63)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="89"/>
+      <c r="A64" s="83"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -20685,7 +20757,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="90"/>
+      <c r="A65" s="84"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -20743,7 +20815,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="91" t="s">
+      <c r="A68" s="85" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -20773,7 +20845,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="92"/>
+      <c r="A69" s="86"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -20801,7 +20873,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="92"/>
+      <c r="A70" s="86"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -20814,8 +20886,12 @@
       <c r="E70" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F70" s="25"/>
-      <c r="G70" s="25"/>
+      <c r="F70" s="25">
+        <v>3</v>
+      </c>
+      <c r="G70" s="25">
+        <v>0</v>
+      </c>
       <c r="H70" s="21" t="s">
         <v>53</v>
       </c>
@@ -20825,7 +20901,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="92"/>
+      <c r="A71" s="86"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -20838,8 +20914,12 @@
       <c r="E71" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="F71" s="25"/>
-      <c r="G71" s="25"/>
+      <c r="F71" s="25">
+        <v>3</v>
+      </c>
+      <c r="G71" s="25">
+        <v>1</v>
+      </c>
       <c r="H71" s="21" t="s">
         <v>52</v>
       </c>
@@ -20849,7 +20929,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="92"/>
+      <c r="A72" s="86"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -20873,7 +20953,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="93"/>
+      <c r="A73" s="87"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -20931,7 +21011,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="94" t="s">
+      <c r="A76" s="88" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -20961,7 +21041,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="95"/>
+      <c r="A77" s="89"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -20989,7 +21069,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="95"/>
+      <c r="A78" s="89"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -21002,18 +21082,22 @@
       <c r="E78" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="F78" s="25"/>
-      <c r="G78" s="25"/>
+      <c r="F78" s="25">
+        <v>2</v>
+      </c>
+      <c r="G78" s="25">
+        <v>1</v>
+      </c>
       <c r="H78" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="J78" s="1" t="str">
+      <c r="J78" s="1">
         <f>IF(OR(Resultados!F78="",Resultados!G78=""),"",IF(AND(F78=Resultados!F78,G78=Resultados!G78),2,IF(((F78&gt;G78)=(Resultados!F78&gt;Resultados!G78))*((F78&lt;G78)=(Resultados!F78&lt;Resultados!G78)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="95"/>
+      <c r="A79" s="89"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -21026,8 +21110,12 @@
       <c r="E79" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="F79" s="25"/>
-      <c r="G79" s="25"/>
+      <c r="F79" s="25">
+        <v>0</v>
+      </c>
+      <c r="G79" s="25">
+        <v>2</v>
+      </c>
       <c r="H79" s="21" t="s">
         <v>57</v>
       </c>
@@ -21037,7 +21125,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="95"/>
+      <c r="A80" s="89"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -21061,7 +21149,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="96"/>
+      <c r="A81" s="90"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -21119,7 +21207,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="97" t="s">
+      <c r="A84" s="91" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -21149,7 +21237,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="98"/>
+      <c r="A85" s="92"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -21177,7 +21265,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="98"/>
+      <c r="A86" s="92"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -21190,8 +21278,12 @@
       <c r="E86" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="F86" s="25"/>
-      <c r="G86" s="25"/>
+      <c r="F86" s="25">
+        <v>3</v>
+      </c>
+      <c r="G86" s="25">
+        <v>0</v>
+      </c>
       <c r="H86" s="21" t="s">
         <v>63</v>
       </c>
@@ -21201,7 +21293,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="98"/>
+      <c r="A87" s="92"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -21214,8 +21306,12 @@
       <c r="E87" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="F87" s="25"/>
-      <c r="G87" s="25"/>
+      <c r="F87" s="25">
+        <v>2</v>
+      </c>
+      <c r="G87" s="25">
+        <v>1</v>
+      </c>
       <c r="H87" s="21" t="s">
         <v>62</v>
       </c>
@@ -21225,7 +21321,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="98"/>
+      <c r="A88" s="92"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -21249,7 +21345,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="99"/>
+      <c r="A89" s="93"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -21307,7 +21403,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="79" t="s">
+      <c r="A92" s="73" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -21337,7 +21433,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="80"/>
+      <c r="A93" s="74"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -21365,7 +21461,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="80"/>
+      <c r="A94" s="74"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -21378,8 +21474,12 @@
       <c r="E94" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="F94" s="25"/>
-      <c r="G94" s="25"/>
+      <c r="F94" s="25">
+        <v>3</v>
+      </c>
+      <c r="G94" s="25">
+        <v>0</v>
+      </c>
       <c r="H94" s="21" t="s">
         <v>68</v>
       </c>
@@ -21389,7 +21489,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="80"/>
+      <c r="A95" s="74"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -21402,8 +21502,12 @@
       <c r="E95" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="F95" s="25"/>
-      <c r="G95" s="25"/>
+      <c r="F95" s="25">
+        <v>1</v>
+      </c>
+      <c r="G95" s="25">
+        <v>3</v>
+      </c>
       <c r="H95" s="21" t="s">
         <v>67</v>
       </c>
@@ -21413,7 +21517,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="80"/>
+      <c r="A96" s="74"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -21437,7 +21541,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="81"/>
+      <c r="A97" s="75"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -21503,26 +21607,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="75"/>
+      <c r="A1" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="69"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="76"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="78"/>
+      <c r="A2" s="70"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="72"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -21555,7 +21659,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="100" t="s">
+      <c r="A4" s="94" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -21581,11 +21685,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="101"/>
+      <c r="A5" s="95"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -21609,7 +21713,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="101"/>
+      <c r="A6" s="95"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -21637,7 +21741,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="101"/>
+      <c r="A7" s="95"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -21665,7 +21769,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="101"/>
+      <c r="A8" s="95"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -21693,7 +21797,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="102"/>
+      <c r="A9" s="96"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -21755,7 +21859,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="103" t="s">
+      <c r="A12" s="97" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -21781,7 +21885,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="104"/>
+      <c r="A13" s="98"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -21805,7 +21909,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="104"/>
+      <c r="A14" s="98"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -21833,7 +21937,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="104"/>
+      <c r="A15" s="98"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -21861,7 +21965,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="104"/>
+      <c r="A16" s="98"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -21889,7 +21993,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="105"/>
+      <c r="A17" s="99"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -21951,7 +22055,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="106" t="s">
+      <c r="A20" s="100" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -21977,7 +22081,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="107"/>
+      <c r="A21" s="101"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -22005,7 +22109,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="107"/>
+      <c r="A22" s="101"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -22033,7 +22137,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="107"/>
+      <c r="A23" s="101"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -22061,7 +22165,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="107"/>
+      <c r="A24" s="101"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -22089,7 +22193,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="108"/>
+      <c r="A25" s="102"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -22151,7 +22255,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="109" t="s">
+      <c r="A28" s="103" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -22177,7 +22281,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="110"/>
+      <c r="A29" s="104"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -22205,7 +22309,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="110"/>
+      <c r="A30" s="104"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -22233,7 +22337,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="110"/>
+      <c r="A31" s="104"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -22261,7 +22365,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="110"/>
+      <c r="A32" s="104"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -22289,7 +22393,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="111"/>
+      <c r="A33" s="105"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -22351,7 +22455,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="112" t="s">
+      <c r="A36" s="106" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -22381,7 +22485,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="113"/>
+      <c r="A37" s="107"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -22409,7 +22513,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="113"/>
+      <c r="A38" s="107"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -22431,13 +22535,13 @@
       <c r="H38" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="J38" s="1" t="str">
+      <c r="J38" s="1">
         <f>IF(OR(Resultados!F38="",Resultados!G38=""),"",IF(AND(F38=Resultados!F38,G38=Resultados!G38),2,IF(((F38&gt;G38)=(Resultados!F38&gt;Resultados!G38))*((F38&lt;G38)=(Resultados!F38&lt;Resultados!G38)),1,0)))</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="113"/>
+      <c r="A39" s="107"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -22459,13 +22563,13 @@
       <c r="H39" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="J39" s="1" t="str">
+      <c r="J39" s="1">
         <f>IF(OR(Resultados!F39="",Resultados!G39=""),"",IF(AND(F39=Resultados!F39,G39=Resultados!G39),2,IF(((F39&gt;G39)=(Resultados!F39&gt;Resultados!G39))*((F39&lt;G39)=(Resultados!F39&lt;Resultados!G39)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="113"/>
+      <c r="A40" s="107"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -22493,7 +22597,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="114"/>
+      <c r="A41" s="108"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -22555,7 +22659,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="82" t="s">
+      <c r="A44" s="76" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -22585,7 +22689,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="83"/>
+      <c r="A45" s="77"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -22613,7 +22717,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="83"/>
+      <c r="A46" s="77"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -22635,13 +22739,13 @@
       <c r="H46" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="J46" s="1" t="str">
+      <c r="J46" s="1">
         <f>IF(OR(Resultados!F46="",Resultados!G46=""),"",IF(AND(F46=Resultados!F46,G46=Resultados!G46),2,IF(((F46&gt;G46)=(Resultados!F46&gt;Resultados!G46))*((F46&lt;G46)=(Resultados!F46&lt;Resultados!G46)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="83"/>
+      <c r="A47" s="77"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -22663,13 +22767,13 @@
       <c r="H47" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="J47" s="1" t="str">
+      <c r="J47" s="1">
         <f>IF(OR(Resultados!F47="",Resultados!G47=""),"",IF(AND(F47=Resultados!F47,G47=Resultados!G47),2,IF(((F47&gt;G47)=(Resultados!F47&gt;Resultados!G47))*((F47&lt;G47)=(Resultados!F47&lt;Resultados!G47)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="83"/>
+      <c r="A48" s="77"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -22697,7 +22801,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="84"/>
+      <c r="A49" s="78"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -22759,7 +22863,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="85" t="s">
+      <c r="A52" s="79" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -22789,7 +22893,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="86"/>
+      <c r="A53" s="80"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -22817,7 +22921,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="86"/>
+      <c r="A54" s="80"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -22839,13 +22943,13 @@
       <c r="H54" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="J54" s="1" t="str">
+      <c r="J54" s="1">
         <f>IF(OR(Resultados!F54="",Resultados!G54=""),"",IF(AND(F54=Resultados!F54,G54=Resultados!G54),2,IF(((F54&gt;G54)=(Resultados!F54&gt;Resultados!G54))*((F54&lt;G54)=(Resultados!F54&lt;Resultados!G54)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="86"/>
+      <c r="A55" s="80"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -22867,13 +22971,13 @@
       <c r="H55" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="J55" s="1" t="str">
+      <c r="J55" s="1">
         <f>IF(OR(Resultados!F55="",Resultados!G55=""),"",IF(AND(F55=Resultados!F55,G55=Resultados!G55),2,IF(((F55&gt;G55)=(Resultados!F55&gt;Resultados!G55))*((F55&lt;G55)=(Resultados!F55&lt;Resultados!G55)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="86"/>
+      <c r="A56" s="80"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -22901,7 +23005,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="87"/>
+      <c r="A57" s="81"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -22963,7 +23067,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="88" t="s">
+      <c r="A60" s="82" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -22993,7 +23097,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="89"/>
+      <c r="A61" s="83"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -23021,7 +23125,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="89"/>
+      <c r="A62" s="83"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -23043,13 +23147,13 @@
       <c r="H62" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="J62" s="1" t="str">
+      <c r="J62" s="1">
         <f>IF(OR(Resultados!F62="",Resultados!G62=""),"",IF(AND(F62=Resultados!F62,G62=Resultados!G62),2,IF(((F62&gt;G62)=(Resultados!F62&gt;Resultados!G62))*((F62&lt;G62)=(Resultados!F62&lt;Resultados!G62)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="89"/>
+      <c r="A63" s="83"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -23071,13 +23175,13 @@
       <c r="H63" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="J63" s="1" t="str">
+      <c r="J63" s="1">
         <f>IF(OR(Resultados!F63="",Resultados!G63=""),"",IF(AND(F63=Resultados!F63,G63=Resultados!G63),2,IF(((F63&gt;G63)=(Resultados!F63&gt;Resultados!G63))*((F63&lt;G63)=(Resultados!F63&lt;Resultados!G63)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="89"/>
+      <c r="A64" s="83"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -23105,7 +23209,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="90"/>
+      <c r="A65" s="84"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -23167,7 +23271,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="91" t="s">
+      <c r="A68" s="85" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -23197,7 +23301,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="92"/>
+      <c r="A69" s="86"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -23225,7 +23329,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="92"/>
+      <c r="A70" s="86"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -23253,7 +23357,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="92"/>
+      <c r="A71" s="86"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -23281,7 +23385,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="92"/>
+      <c r="A72" s="86"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -23309,7 +23413,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="93"/>
+      <c r="A73" s="87"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -23371,7 +23475,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="94" t="s">
+      <c r="A76" s="88" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -23401,7 +23505,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="95"/>
+      <c r="A77" s="89"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -23429,7 +23533,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="95"/>
+      <c r="A78" s="89"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -23451,13 +23555,13 @@
       <c r="H78" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="J78" s="1" t="str">
+      <c r="J78" s="1">
         <f>IF(OR(Resultados!F78="",Resultados!G78=""),"",IF(AND(F78=Resultados!F78,G78=Resultados!G78),2,IF(((F78&gt;G78)=(Resultados!F78&gt;Resultados!G78))*((F78&lt;G78)=(Resultados!F78&lt;Resultados!G78)),1,0)))</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="95"/>
+      <c r="A79" s="89"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -23485,7 +23589,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="95"/>
+      <c r="A80" s="89"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -23513,7 +23617,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="96"/>
+      <c r="A81" s="90"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -23575,7 +23679,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="97" t="s">
+      <c r="A84" s="91" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -23605,7 +23709,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="98"/>
+      <c r="A85" s="92"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -23633,7 +23737,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="98"/>
+      <c r="A86" s="92"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -23661,7 +23765,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="98"/>
+      <c r="A87" s="92"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -23689,7 +23793,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="98"/>
+      <c r="A88" s="92"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -23717,7 +23821,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="99"/>
+      <c r="A89" s="93"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -23779,7 +23883,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="79" t="s">
+      <c r="A92" s="73" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -23809,7 +23913,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="80"/>
+      <c r="A93" s="74"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -23837,7 +23941,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="80"/>
+      <c r="A94" s="74"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -23865,7 +23969,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="80"/>
+      <c r="A95" s="74"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -23893,7 +23997,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="80"/>
+      <c r="A96" s="74"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -23921,7 +24025,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="81"/>
+      <c r="A97" s="75"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -23991,26 +24095,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="75"/>
+      <c r="A1" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="69"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="76"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="78"/>
+      <c r="A2" s="70"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="72"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -24043,7 +24147,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="100" t="s">
+      <c r="A4" s="94" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -24069,11 +24173,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="101"/>
+      <c r="A5" s="95"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -24097,7 +24201,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="101"/>
+      <c r="A6" s="95"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -24125,7 +24229,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="101"/>
+      <c r="A7" s="95"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -24153,7 +24257,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="101"/>
+      <c r="A8" s="95"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -24181,7 +24285,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="102"/>
+      <c r="A9" s="96"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -24243,7 +24347,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="103" t="s">
+      <c r="A12" s="97" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -24269,7 +24373,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="104"/>
+      <c r="A13" s="98"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -24293,7 +24397,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="104"/>
+      <c r="A14" s="98"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -24321,7 +24425,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="104"/>
+      <c r="A15" s="98"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -24349,7 +24453,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="104"/>
+      <c r="A16" s="98"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -24377,7 +24481,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="105"/>
+      <c r="A17" s="99"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -24439,7 +24543,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="106" t="s">
+      <c r="A20" s="100" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -24465,7 +24569,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="107"/>
+      <c r="A21" s="101"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -24493,7 +24597,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="107"/>
+      <c r="A22" s="101"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -24521,7 +24625,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="107"/>
+      <c r="A23" s="101"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -24549,7 +24653,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="107"/>
+      <c r="A24" s="101"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -24577,7 +24681,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="108"/>
+      <c r="A25" s="102"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -24639,7 +24743,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="109" t="s">
+      <c r="A28" s="103" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -24665,7 +24769,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="110"/>
+      <c r="A29" s="104"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -24693,7 +24797,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="110"/>
+      <c r="A30" s="104"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -24721,7 +24825,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="110"/>
+      <c r="A31" s="104"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -24749,7 +24853,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="110"/>
+      <c r="A32" s="104"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -24777,7 +24881,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="111"/>
+      <c r="A33" s="105"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -24839,7 +24943,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="112" t="s">
+      <c r="A36" s="106" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -24869,7 +24973,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="113"/>
+      <c r="A37" s="107"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -24897,7 +25001,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="113"/>
+      <c r="A38" s="107"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -24919,13 +25023,13 @@
       <c r="H38" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="J38" s="1" t="str">
+      <c r="J38" s="1">
         <f>IF(OR(Resultados!F38="",Resultados!G38=""),"",IF(AND(F38=Resultados!F38,G38=Resultados!G38),2,IF(((F38&gt;G38)=(Resultados!F38&gt;Resultados!G38))*((F38&lt;G38)=(Resultados!F38&lt;Resultados!G38)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="113"/>
+      <c r="A39" s="107"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -24947,13 +25051,13 @@
       <c r="H39" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="J39" s="1" t="str">
+      <c r="J39" s="1">
         <f>IF(OR(Resultados!F39="",Resultados!G39=""),"",IF(AND(F39=Resultados!F39,G39=Resultados!G39),2,IF(((F39&gt;G39)=(Resultados!F39&gt;Resultados!G39))*((F39&lt;G39)=(Resultados!F39&lt;Resultados!G39)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="113"/>
+      <c r="A40" s="107"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -24981,7 +25085,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="114"/>
+      <c r="A41" s="108"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -25043,7 +25147,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="82" t="s">
+      <c r="A44" s="76" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -25073,7 +25177,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="83"/>
+      <c r="A45" s="77"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -25101,7 +25205,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="83"/>
+      <c r="A46" s="77"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -25123,13 +25227,13 @@
       <c r="H46" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="J46" s="1" t="str">
+      <c r="J46" s="1">
         <f>IF(OR(Resultados!F46="",Resultados!G46=""),"",IF(AND(F46=Resultados!F46,G46=Resultados!G46),2,IF(((F46&gt;G46)=(Resultados!F46&gt;Resultados!G46))*((F46&lt;G46)=(Resultados!F46&lt;Resultados!G46)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="83"/>
+      <c r="A47" s="77"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -25151,13 +25255,13 @@
       <c r="H47" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="J47" s="1" t="str">
+      <c r="J47" s="1">
         <f>IF(OR(Resultados!F47="",Resultados!G47=""),"",IF(AND(F47=Resultados!F47,G47=Resultados!G47),2,IF(((F47&gt;G47)=(Resultados!F47&gt;Resultados!G47))*((F47&lt;G47)=(Resultados!F47&lt;Resultados!G47)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="83"/>
+      <c r="A48" s="77"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -25185,7 +25289,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="84"/>
+      <c r="A49" s="78"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -25247,7 +25351,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="85" t="s">
+      <c r="A52" s="79" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -25277,7 +25381,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="86"/>
+      <c r="A53" s="80"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -25305,7 +25409,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="86"/>
+      <c r="A54" s="80"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -25327,13 +25431,13 @@
       <c r="H54" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="J54" s="1" t="str">
+      <c r="J54" s="1">
         <f>IF(OR(Resultados!F54="",Resultados!G54=""),"",IF(AND(F54=Resultados!F54,G54=Resultados!G54),2,IF(((F54&gt;G54)=(Resultados!F54&gt;Resultados!G54))*((F54&lt;G54)=(Resultados!F54&lt;Resultados!G54)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="86"/>
+      <c r="A55" s="80"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -25355,13 +25459,13 @@
       <c r="H55" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="J55" s="1" t="str">
+      <c r="J55" s="1">
         <f>IF(OR(Resultados!F55="",Resultados!G55=""),"",IF(AND(F55=Resultados!F55,G55=Resultados!G55),2,IF(((F55&gt;G55)=(Resultados!F55&gt;Resultados!G55))*((F55&lt;G55)=(Resultados!F55&lt;Resultados!G55)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="86"/>
+      <c r="A56" s="80"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -25389,7 +25493,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="87"/>
+      <c r="A57" s="81"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -25451,7 +25555,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="88" t="s">
+      <c r="A60" s="82" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -25481,7 +25585,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="89"/>
+      <c r="A61" s="83"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -25509,7 +25613,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="89"/>
+      <c r="A62" s="83"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -25531,13 +25635,13 @@
       <c r="H62" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="J62" s="1" t="str">
+      <c r="J62" s="1">
         <f>IF(OR(Resultados!F62="",Resultados!G62=""),"",IF(AND(F62=Resultados!F62,G62=Resultados!G62),2,IF(((F62&gt;G62)=(Resultados!F62&gt;Resultados!G62))*((F62&lt;G62)=(Resultados!F62&lt;Resultados!G62)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="89"/>
+      <c r="A63" s="83"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -25559,13 +25663,13 @@
       <c r="H63" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="J63" s="1" t="str">
+      <c r="J63" s="1">
         <f>IF(OR(Resultados!F63="",Resultados!G63=""),"",IF(AND(F63=Resultados!F63,G63=Resultados!G63),2,IF(((F63&gt;G63)=(Resultados!F63&gt;Resultados!G63))*((F63&lt;G63)=(Resultados!F63&lt;Resultados!G63)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="89"/>
+      <c r="A64" s="83"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -25593,7 +25697,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="90"/>
+      <c r="A65" s="84"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -25655,7 +25759,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="91" t="s">
+      <c r="A68" s="85" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -25685,7 +25789,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="92"/>
+      <c r="A69" s="86"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -25713,7 +25817,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="92"/>
+      <c r="A70" s="86"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -25741,7 +25845,7 @@
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="92"/>
+      <c r="A71" s="86"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -25769,7 +25873,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="92"/>
+      <c r="A72" s="86"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -25797,7 +25901,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="93"/>
+      <c r="A73" s="87"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -25859,7 +25963,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="94" t="s">
+      <c r="A76" s="88" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -25889,7 +25993,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="95"/>
+      <c r="A77" s="89"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -25917,7 +26021,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="95"/>
+      <c r="A78" s="89"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -25939,13 +26043,13 @@
       <c r="H78" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="J78" s="1" t="str">
+      <c r="J78" s="1">
         <f>IF(OR(Resultados!F78="",Resultados!G78=""),"",IF(AND(F78=Resultados!F78,G78=Resultados!G78),2,IF(((F78&gt;G78)=(Resultados!F78&gt;Resultados!G78))*((F78&lt;G78)=(Resultados!F78&lt;Resultados!G78)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="95"/>
+      <c r="A79" s="89"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -25973,7 +26077,7 @@
       </c>
     </row>
     <row r="80" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="95"/>
+      <c r="A80" s="89"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -26001,7 +26105,7 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="96"/>
+      <c r="A81" s="90"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -26063,7 +26167,7 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="97" t="s">
+      <c r="A84" s="91" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -26093,7 +26197,7 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="98"/>
+      <c r="A85" s="92"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -26121,7 +26225,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="98"/>
+      <c r="A86" s="92"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -26149,7 +26253,7 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="98"/>
+      <c r="A87" s="92"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -26177,7 +26281,7 @@
       </c>
     </row>
     <row r="88" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="98"/>
+      <c r="A88" s="92"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -26205,7 +26309,7 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="99"/>
+      <c r="A89" s="93"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -26267,7 +26371,7 @@
       </c>
     </row>
     <row r="92" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="79" t="s">
+      <c r="A92" s="73" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -26297,7 +26401,7 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="80"/>
+      <c r="A93" s="74"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -26325,7 +26429,7 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="80"/>
+      <c r="A94" s="74"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -26353,7 +26457,7 @@
       </c>
     </row>
     <row r="95" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="80"/>
+      <c r="A95" s="74"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -26381,7 +26485,7 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="80"/>
+      <c r="A96" s="74"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -26409,7 +26513,7 @@
       </c>
     </row>
     <row r="97" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="81"/>
+      <c r="A97" s="75"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>

--- a/data/Quiniela.xlsx
+++ b/data/Quiniela.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cindy\Desktop\QuinielaMundial\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E41E6FF-6258-4168-9C7F-6E700C0BCEF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{428F4DA2-F4CD-48F5-89E5-AA2EDCD05616}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9503E40F-C0E1-49CE-B4EA-3C401754995E}"/>
   </bookViews>
@@ -1266,6 +1266,28 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="14" fontId="6" fillId="19" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="20" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="20" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="20" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="20" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="20" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="20" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1434,23 +1456,53 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="20" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="20" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="20" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="20" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="20" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="20" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1545,58 +1597,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="19" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1955,26 +1955,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="67" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="69"/>
+      <c r="A1" s="74" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
+      <c r="H1" s="76"/>
     </row>
     <row r="2" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="70"/>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
-      <c r="H2" s="72"/>
+      <c r="A2" s="77"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="79"/>
     </row>
     <row r="3" spans="1:8" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -2001,7 +2001,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="94" t="s">
+      <c r="A4" s="101" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -2013,7 +2013,7 @@
       <c r="D4" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="151" t="s">
+      <c r="E4" s="67" t="s">
         <v>9</v>
       </c>
       <c r="F4" s="62">
@@ -2027,7 +2027,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="95"/>
+      <c r="A5" s="102"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -2037,7 +2037,7 @@
       <c r="D5" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="151" t="s">
+      <c r="E5" s="67" t="s">
         <v>11</v>
       </c>
       <c r="F5" s="62">
@@ -2051,7 +2051,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="95"/>
+      <c r="A6" s="102"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -2075,7 +2075,7 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="95"/>
+      <c r="A7" s="102"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -2085,7 +2085,7 @@
       <c r="D7" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="151" t="s">
+      <c r="E7" s="67" t="s">
         <v>9</v>
       </c>
       <c r="F7" s="66">
@@ -2099,7 +2099,7 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="95"/>
+      <c r="A8" s="102"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -2119,7 +2119,7 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="96"/>
+      <c r="A9" s="103"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -2173,7 +2173,7 @@
       </c>
     </row>
     <row r="12" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="97" t="s">
+      <c r="A12" s="104" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -2199,7 +2199,7 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="98"/>
+      <c r="A13" s="105"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -2223,7 +2223,7 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="98"/>
+      <c r="A14" s="105"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -2247,7 +2247,7 @@
       </c>
     </row>
     <row r="15" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="98"/>
+      <c r="A15" s="105"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -2271,7 +2271,7 @@
       </c>
     </row>
     <row r="16" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="98"/>
+      <c r="A16" s="105"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -2291,7 +2291,7 @@
       </c>
     </row>
     <row r="17" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="99"/>
+      <c r="A17" s="106"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -2345,7 +2345,7 @@
       </c>
     </row>
     <row r="20" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="100" t="s">
+      <c r="A20" s="107" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -2371,7 +2371,7 @@
       </c>
     </row>
     <row r="21" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="101"/>
+      <c r="A21" s="108"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -2390,12 +2390,12 @@
       <c r="G21" s="62">
         <v>1</v>
       </c>
-      <c r="H21" s="151" t="s">
+      <c r="H21" s="67" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="101"/>
+      <c r="A22" s="108"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -2414,12 +2414,12 @@
       <c r="G22" s="66">
         <v>1</v>
       </c>
-      <c r="H22" s="151" t="s">
+      <c r="H22" s="67" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="101"/>
+      <c r="A23" s="108"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -2443,7 +2443,7 @@
       </c>
     </row>
     <row r="24" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="101"/>
+      <c r="A24" s="108"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -2463,7 +2463,7 @@
       </c>
     </row>
     <row r="25" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="102"/>
+      <c r="A25" s="109"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -2517,7 +2517,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="103" t="s">
+      <c r="A28" s="110" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -2543,7 +2543,7 @@
       </c>
     </row>
     <row r="29" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="104"/>
+      <c r="A29" s="111"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -2567,7 +2567,7 @@
       </c>
     </row>
     <row r="30" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="104"/>
+      <c r="A30" s="111"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -2591,7 +2591,7 @@
       </c>
     </row>
     <row r="31" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="104"/>
+      <c r="A31" s="111"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -2610,12 +2610,12 @@
       <c r="G31" s="66">
         <v>1</v>
       </c>
-      <c r="H31" s="151" t="s">
+      <c r="H31" s="67" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="104"/>
+      <c r="A32" s="111"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -2635,7 +2635,7 @@
       </c>
     </row>
     <row r="33" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="105"/>
+      <c r="A33" s="112"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -2689,7 +2689,7 @@
       </c>
     </row>
     <row r="36" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="106" t="s">
+      <c r="A36" s="113" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -2715,7 +2715,7 @@
       </c>
     </row>
     <row r="37" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="107"/>
+      <c r="A37" s="114"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -2739,7 +2739,7 @@
       </c>
     </row>
     <row r="38" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="107"/>
+      <c r="A38" s="114"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -2763,7 +2763,7 @@
       </c>
     </row>
     <row r="39" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="107"/>
+      <c r="A39" s="114"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -2787,7 +2787,7 @@
       </c>
     </row>
     <row r="40" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="107"/>
+      <c r="A40" s="114"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -2807,7 +2807,7 @@
       </c>
     </row>
     <row r="41" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="108"/>
+      <c r="A41" s="115"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -2861,7 +2861,7 @@
       </c>
     </row>
     <row r="44" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="76" t="s">
+      <c r="A44" s="83" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -2887,7 +2887,7 @@
       </c>
     </row>
     <row r="45" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="77"/>
+      <c r="A45" s="84"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -2911,7 +2911,7 @@
       </c>
     </row>
     <row r="46" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="77"/>
+      <c r="A46" s="84"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -2935,7 +2935,7 @@
       </c>
     </row>
     <row r="47" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="77"/>
+      <c r="A47" s="84"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -2954,12 +2954,12 @@
       <c r="G47" s="66">
         <v>4</v>
       </c>
-      <c r="H47" s="151" t="s">
+      <c r="H47" s="67" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="77"/>
+      <c r="A48" s="84"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -2979,7 +2979,7 @@
       </c>
     </row>
     <row r="49" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="78"/>
+      <c r="A49" s="85"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -3033,7 +3033,7 @@
       </c>
     </row>
     <row r="52" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="79" t="s">
+      <c r="A52" s="86" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -3059,7 +3059,7 @@
       </c>
     </row>
     <row r="53" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="80"/>
+      <c r="A53" s="87"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -3083,7 +3083,7 @@
       </c>
     </row>
     <row r="54" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="80"/>
+      <c r="A54" s="87"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -3107,7 +3107,7 @@
       </c>
     </row>
     <row r="55" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="80"/>
+      <c r="A55" s="87"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -3126,12 +3126,12 @@
       <c r="G55" s="63">
         <v>3</v>
       </c>
-      <c r="H55" s="151" t="s">
+      <c r="H55" s="67" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="80"/>
+      <c r="A56" s="87"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -3151,7 +3151,7 @@
       </c>
     </row>
     <row r="57" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="81"/>
+      <c r="A57" s="88"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -3205,7 +3205,7 @@
       </c>
     </row>
     <row r="60" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="82" t="s">
+      <c r="A60" s="89" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -3231,7 +3231,7 @@
       </c>
     </row>
     <row r="61" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="83"/>
+      <c r="A61" s="90"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -3255,7 +3255,7 @@
       </c>
     </row>
     <row r="62" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="83"/>
+      <c r="A62" s="90"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -3279,7 +3279,7 @@
       </c>
     </row>
     <row r="63" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="83"/>
+      <c r="A63" s="90"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -3303,7 +3303,7 @@
       </c>
     </row>
     <row r="64" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="83"/>
+      <c r="A64" s="90"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -3323,7 +3323,7 @@
       </c>
     </row>
     <row r="65" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="84"/>
+      <c r="A65" s="91"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -3377,7 +3377,7 @@
       </c>
     </row>
     <row r="68" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="85" t="s">
+      <c r="A68" s="92" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -3403,7 +3403,7 @@
       </c>
     </row>
     <row r="69" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="86"/>
+      <c r="A69" s="93"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -3422,12 +3422,12 @@
       <c r="G69" s="62">
         <v>4</v>
       </c>
-      <c r="H69" s="151" t="s">
+      <c r="H69" s="67" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="86"/>
+      <c r="A70" s="93"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -3437,17 +3437,21 @@
       <c r="D70" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E70" s="10" t="s">
+      <c r="E70" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="F70" s="25"/>
-      <c r="G70" s="25"/>
+      <c r="F70" s="66">
+        <v>3</v>
+      </c>
+      <c r="G70" s="66">
+        <v>0</v>
+      </c>
       <c r="H70" s="21" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="86"/>
+      <c r="A71" s="93"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -3457,17 +3461,21 @@
       <c r="D71" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E71" s="10" t="s">
+      <c r="E71" s="67" t="s">
         <v>54</v>
       </c>
-      <c r="F71" s="25"/>
-      <c r="G71" s="25"/>
+      <c r="F71" s="66">
+        <v>3</v>
+      </c>
+      <c r="G71" s="62">
+        <v>2</v>
+      </c>
       <c r="H71" s="21" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="86"/>
+      <c r="A72" s="93"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -3487,7 +3495,7 @@
       </c>
     </row>
     <row r="73" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="87"/>
+      <c r="A73" s="94"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -3541,7 +3549,7 @@
       </c>
     </row>
     <row r="76" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="88" t="s">
+      <c r="A76" s="95" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -3567,7 +3575,7 @@
       </c>
     </row>
     <row r="77" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="89"/>
+      <c r="A77" s="96"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -3591,7 +3599,7 @@
       </c>
     </row>
     <row r="78" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="89"/>
+      <c r="A78" s="96"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -3615,7 +3623,7 @@
       </c>
     </row>
     <row r="79" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="89"/>
+      <c r="A79" s="96"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -3628,14 +3636,18 @@
       <c r="E79" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="F79" s="25"/>
-      <c r="G79" s="25"/>
-      <c r="H79" s="21" t="s">
+      <c r="F79" s="62">
+        <v>1</v>
+      </c>
+      <c r="G79" s="62">
+        <v>2</v>
+      </c>
+      <c r="H79" s="67" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="80" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="89"/>
+      <c r="A80" s="96"/>
       <c r="B80" s="7">
         <v>46201</v>
       </c>
@@ -3655,7 +3667,7 @@
       </c>
     </row>
     <row r="81" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="90"/>
+      <c r="A81" s="97"/>
       <c r="B81" s="12">
         <v>46201</v>
       </c>
@@ -3709,7 +3721,7 @@
       </c>
     </row>
     <row r="84" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="91" t="s">
+      <c r="A84" s="98" t="s">
         <v>60</v>
       </c>
       <c r="B84" s="7">
@@ -3735,7 +3747,7 @@
       </c>
     </row>
     <row r="85" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="92"/>
+      <c r="A85" s="99"/>
       <c r="B85" s="7">
         <v>46191</v>
       </c>
@@ -3754,12 +3766,12 @@
       <c r="G85" s="62">
         <v>3</v>
       </c>
-      <c r="H85" s="151" t="s">
+      <c r="H85" s="67" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="86" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="92"/>
+      <c r="A86" s="99"/>
       <c r="B86" s="7">
         <v>46196</v>
       </c>
@@ -3779,7 +3791,7 @@
       </c>
     </row>
     <row r="87" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="92"/>
+      <c r="A87" s="99"/>
       <c r="B87" s="7">
         <v>46197</v>
       </c>
@@ -3799,7 +3811,7 @@
       </c>
     </row>
     <row r="88" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="92"/>
+      <c r="A88" s="99"/>
       <c r="B88" s="7">
         <v>46201</v>
       </c>
@@ -3819,7 +3831,7 @@
       </c>
     </row>
     <row r="89" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="93"/>
+      <c r="A89" s="100"/>
       <c r="B89" s="12">
         <v>46201</v>
       </c>
@@ -3873,7 +3885,7 @@
       </c>
     </row>
     <row r="92" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="73" t="s">
+      <c r="A92" s="80" t="s">
         <v>65</v>
       </c>
       <c r="B92" s="7">
@@ -3899,7 +3911,7 @@
       </c>
     </row>
     <row r="93" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="74"/>
+      <c r="A93" s="81"/>
       <c r="B93" s="7">
         <v>46191</v>
       </c>
@@ -3923,7 +3935,7 @@
       </c>
     </row>
     <row r="94" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="74"/>
+      <c r="A94" s="81"/>
       <c r="B94" s="7">
         <v>46196</v>
       </c>
@@ -3943,7 +3955,7 @@
       </c>
     </row>
     <row r="95" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="74"/>
+      <c r="A95" s="81"/>
       <c r="B95" s="7">
         <v>46197</v>
       </c>
@@ -3963,7 +3975,7 @@
       </c>
     </row>
     <row r="96" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="74"/>
+      <c r="A96" s="81"/>
       <c r="B96" s="7">
         <v>46200</v>
       </c>
@@ -3983,7 +3995,7 @@
       </c>
     </row>
     <row r="97" spans="1:8" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="75"/>
+      <c r="A97" s="82"/>
       <c r="B97" s="12">
         <v>46200</v>
       </c>
@@ -4043,26 +4055,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="67" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="69"/>
+      <c r="A1" s="74" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
+      <c r="H1" s="76"/>
     </row>
     <row r="2" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="70"/>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
-      <c r="H2" s="72"/>
+      <c r="A2" s="77"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="79"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
@@ -4095,7 +4107,7 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="94" t="s">
+      <c r="A4" s="101" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="7">
@@ -4121,11 +4133,11 @@
       </c>
       <c r="L4" s="1">
         <f>SUM(J:J)</f>
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="95"/>
+      <c r="A5" s="102"/>
       <c r="B5" s="7">
         <v>46185</v>
       </c>
@@ -4149,7 +4161,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="95"/>
+      <c r="A6" s="102"/>
       <c r="B6" s="7">
         <v>46191</v>
       </c>
@@ -4177,7 +4189,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="95"/>
+      <c r="A7" s="102"/>
       <c r="B7" s="7">
         <v>46192</v>
       </c>
@@ -4205,7 +4217,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="95"/>
+      <c r="A8" s="102"/>
       <c r="B8" s="7">
         <v>46198</v>
       </c>
@@ -4233,7 +4245,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="96"/>
+      <c r="A9" s="103"/>
       <c r="B9" s="12">
         <v>46198</v>
       </c>
@@ -4295,7 +4307,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="97" t="s">
+      <c r="A12" s="104" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="7">
@@ -4321,7 +4333,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="98"/>
+      <c r="A13" s="105"/>
       <c r="B13" s="7">
         <v>46186</v>
       </c>
@@ -4345,7 +4357,7 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="98"/>
+      <c r="A14" s="105"/>
       <c r="B14" s="7">
         <v>46191</v>
       </c>
@@ -4373,7 +4385,7 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="98"/>
+      <c r="A15" s="105"/>
       <c r="B15" s="7">
         <v>46192</v>
       </c>
@@ -4401,7 +4413,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="98"/>
+      <c r="A16" s="105"/>
       <c r="B16" s="7">
         <v>46197</v>
       </c>
@@ -4429,7 +4441,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="99"/>
+      <c r="A17" s="106"/>
       <c r="B17" s="12">
         <v>46197</v>
       </c>
@@ -4491,7 +4503,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="100" t="s">
+      <c r="A20" s="107" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="7">
@@ -4517,7 +4529,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="101"/>
+      <c r="A21" s="108"/>
       <c r="B21" s="7">
         <v>46187</v>
       </c>
@@ -4545,7 +4557,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="101"/>
+      <c r="A22" s="108"/>
       <c r="B22" s="7">
         <v>46193</v>
       </c>
@@ -4573,7 +4585,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="101"/>
+      <c r="A23" s="108"/>
       <c r="B23" s="7">
         <v>46193</v>
       </c>
@@ -4601,7 +4613,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="101"/>
+      <c r="A24" s="108"/>
       <c r="B24" s="7">
         <v>46198</v>
       </c>
@@ -4629,7 +4641,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="102"/>
+      <c r="A25" s="109"/>
       <c r="B25" s="12">
         <v>46198</v>
       </c>
@@ -4691,7 +4703,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="103" t="s">
+      <c r="A28" s="110" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="7">
@@ -4717,7 +4729,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="104"/>
+      <c r="A29" s="111"/>
       <c r="B29" s="7">
         <v>46187</v>
       </c>
@@ -4745,7 +4757,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="104"/>
+      <c r="A30" s="111"/>
       <c r="B30" s="7">
         <v>46192</v>
       </c>
@@ -4773,7 +4785,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="104"/>
+      <c r="A31" s="111"/>
       <c r="B31" s="7">
         <v>46193</v>
       </c>
@@ -4801,7 +4813,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="104"/>
+      <c r="A32" s="111"/>
       <c r="B32" s="7">
         <v>46199</v>
       </c>
@@ -4829,7 +4841,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="105"/>
+      <c r="A33" s="112"/>
       <c r="B33" s="12">
         <v>46199</v>
       </c>
@@ -4891,7 +4903,7 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="106" t="s">
+      <c r="A36" s="113" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -4921,7 +4933,7 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="107"/>
+      <c r="A37" s="114"/>
       <c r="B37" s="7">
         <v>46188</v>
       </c>
@@ -4949,7 +4961,7 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="107"/>
+      <c r="A38" s="114"/>
       <c r="B38" s="7">
         <v>46193</v>
       </c>
@@ -4977,7 +4989,7 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="107"/>
+      <c r="A39" s="114"/>
       <c r="B39" s="7">
         <v>46194</v>
       </c>
@@ -5005,7 +5017,7 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="107"/>
+      <c r="A40" s="114"/>
       <c r="B40" s="7">
         <v>46198</v>
       </c>
@@ -5033,7 +5045,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="108"/>
+      <c r="A41" s="115"/>
       <c r="B41" s="12">
         <v>46198</v>
       </c>
@@ -5095,7 +5107,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="76" t="s">
+      <c r="A44" s="83" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="7">
@@ -5125,7 +5137,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="77"/>
+      <c r="A45" s="84"/>
       <c r="B45" s="7">
         <v>46188</v>
       </c>
@@ -5153,7 +5165,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="77"/>
+      <c r="A46" s="84"/>
       <c r="B46" s="7">
         <v>46193</v>
       </c>
@@ -5175,13 +5187,13 @@
       <c r="H46" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="J46" s="1">
+      <c r="J46" s="65">
         <f>IF(OR(Resultados!F46="",Resultados!G46=""),"",IF(AND(F46=Resultados!F46,G46=Resultados!G46),2,IF(((F46&gt;G46)=(Resultados!F46&gt;Resultados!G46))*((F46&lt;G46)=(Resultados!F46&lt;Resultados!G46)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="77"/>
+      <c r="A47" s="84"/>
       <c r="B47" s="7">
         <v>46194</v>
       </c>
@@ -5203,13 +5215,13 @@
       <c r="H47" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="J47" s="1">
+      <c r="J47" s="65">
         <f>IF(OR(Resultados!F47="",Resultados!G47=""),"",IF(AND(F47=Resultados!F47,G47=Resultados!G47),2,IF(((F47&gt;G47)=(Resultados!F47&gt;Resultados!G47))*((F47&lt;G47)=(Resultados!F47&lt;Resultados!G47)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="77"/>
+      <c r="A48" s="84"/>
       <c r="B48" s="7">
         <v>46199</v>
       </c>
@@ -5237,7 +5249,7 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="78"/>
+      <c r="A49" s="85"/>
       <c r="B49" s="12">
         <v>46199</v>
       </c>
@@ -5299,7 +5311,7 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="79" t="s">
+      <c r="A52" s="86" t="s">
         <v>40</v>
       </c>
       <c r="B52" s="7">
@@ -5329,7 +5341,7 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="80"/>
+      <c r="A53" s="87"/>
       <c r="B53" s="7">
         <v>46189</v>
       </c>
@@ -5357,7 +5369,7 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="80"/>
+      <c r="A54" s="87"/>
       <c r="B54" s="7">
         <v>46194</v>
       </c>
@@ -5385,7 +5397,7 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="80"/>
+      <c r="A55" s="87"/>
       <c r="B55" s="7">
         <v>46195</v>
       </c>
@@ -5407,13 +5419,13 @@
       <c r="H55" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="J55" s="1">
+      <c r="J55" s="65">
         <f>IF(OR(Resultados!F55="",Resultados!G55=""),"",IF(AND(F55=Resultados!F55,G55=Resultados!G55),2,IF(((F55&gt;G55)=(Resultados!F55&gt;Resultados!G55))*((F55&lt;G55)=(Resultados!F55&lt;Resultados!G55)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="80"/>
+      <c r="A56" s="87"/>
       <c r="B56" s="7">
         <v>46200</v>
       </c>
@@ -5441,7 +5453,7 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="81"/>
+      <c r="A57" s="88"/>
       <c r="B57" s="12">
         <v>46200</v>
       </c>
@@ -5503,7 +5515,7 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="82" t="s">
+      <c r="A60" s="89" t="s">
         <v>45</v>
       </c>
       <c r="B60" s="7">
@@ -5533,7 +5545,7 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="83"/>
+      <c r="A61" s="90"/>
       <c r="B61" s="7">
         <v>46189</v>
       </c>
@@ -5561,7 +5573,7 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="83"/>
+      <c r="A62" s="90"/>
       <c r="B62" s="7">
         <v>46194</v>
       </c>
@@ -5583,13 +5595,13 @@
       <c r="H62" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="J62" s="1">
+      <c r="J62" s="65">
         <f>IF(OR(Resultados!F62="",Resultados!G62=""),"",IF(AND(F62=Resultados!F62,G62=Resultados!G62),2,IF(((F62&gt;G62)=(Resultados!F62&gt;Resultados!G62))*((F62&lt;G62)=(Resultados!F62&lt;Resultados!G62)),1,0)))</f>
         <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="83"/>
+      <c r="A63" s="90"/>
       <c r="B63" s="7">
         <v>46195</v>
       </c>
@@ -5617,7 +5629,7 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="83"/>
+      <c r="A64" s="90"/>
       <c r="B64" s="7">
         <v>46200</v>
       </c>
@@ -5645,7 +5657,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="84"/>
+      <c r="A65" s="91"/>
       <c r="B65" s="12">
         <v>46200</v>
       </c>
@@ -5707,7 +5719,7 @@
       </c>
     </row>
     <row r="68" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="85" t="s">
+      <c r="A68" s="92" t="s">
         <v>50</v>
       </c>
       <c r="B68" s="7">
@@ -5737,7 +5749,7 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="86"/>
+      <c r="A69" s="93"/>
       <c r="B69" s="7">
         <v>46190</v>
       </c>
@@ -5765,7 +5777,7 @@
       </c>
     </row>
     <row r="70" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="86"/>
+      <c r="A70" s="93"/>
       <c r="B70" s="7">
         <v>46195</v>
       </c>
@@ -5787,13 +5799,13 @@
       <c r="H70" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="J70" s="1" t="str">
+      <c r="J70" s="65">
         <f>IF(OR(Resultados!F70="",Resultados!G70=""),"",IF(AND(F70=Resultados!F70,G70=Resultados!G70),2,IF(((F70&gt;G70)=(Resultados!F70&gt;Resultados!G70))*((F70&lt;G70)=(Resultados!F70&lt;Resultados!G70)),1,0)))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="86"/>
+      <c r="A71" s="93"/>
       <c r="B71" s="7">
         <v>46196</v>
       </c>
@@ -5815,13 +5827,13 @@
       <c r="H71" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="J71" s="1" t="str">
+      <c r="J71" s="1">
         <f>IF(OR(Resultados!F71="",Resultados!G71=""),"",IF(AND(F71=Resultados!F71,G71=Resultados!G71),2,IF(((F71&gt;G71)=(Resultados!F71&gt;Resultados!G71))*((F71&lt;G71)=(Resultados!F71&lt;Resultados!G71)),1,0)))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="86"/>
+      <c r="A72" s="93"/>
       <c r="B72" s="7">
         <v>46199</v>
       </c>
@@ -5849,7 +5861,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="87"/>
+      <c r="A73" s="94"/>
       <c r="B73" s="12">
         <v>46199</v>
       </c>
@@ -5911,7 +5923,7 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="88" t="s">
+      <c r="A76" s="95" t="s">
         <v>55</v>
       </c>
       <c r="B76" s="7">
@@ -5941,7 +5953,7 @@
       </c>
     </row>
     <row r="77" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="89"/>
+      <c r="A77" s="96"/>
       <c r="B77" s="7">
         <v>46190</v>
       </c>
@@ -5969,7 +5981,7 @@
       </c>
     </row>
     <row r="78" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="89"/>
+      <c r="A78" s="96"/>
       <c r="B78" s="7">
         <v>46195</v>
       </c>
@@ -5991,13 +6003,13 @@
       <c r="H78" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="J78" s="1">
+      <c r="J78" s="64">
         <f>IF(OR(Resultados!F78="",Resultados!G78=""),"",IF(AND(F78=Resultados!F78,G78=Resultados!G78),2,IF(((F78&gt;G78)=(Resultados!F78&gt;Resultados!G78))*((F78&lt;G78)=(Resultados!F78&lt;Resultados!G78)),1,0)))</f>
         <v>2</v>
       </c>
     </row>
     <row r="79" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="89"/>
+      <c r="A79" s="96"/>
       <c r="B79" s="7">
         <v>46196</v>
       </c>
@@ -6019,13 +6031,13 @@
       <c r="H79" s="21" t="s">
         <v>57</v>
  